--- a/Forecast.xlsx
+++ b/Forecast.xlsx
@@ -76,511 +76,511 @@
     <t>Prediction_3D_Steel</t>
   </si>
   <si>
-    <t>18.02.202617</t>
-  </si>
-  <si>
-    <t>18.02.202618</t>
-  </si>
-  <si>
-    <t>18.02.202619</t>
-  </si>
-  <si>
-    <t>18.02.202620</t>
-  </si>
-  <si>
-    <t>18.02.202621</t>
-  </si>
-  <si>
-    <t>18.02.202622</t>
-  </si>
-  <si>
-    <t>18.02.202623</t>
-  </si>
-  <si>
-    <t>18.02.202624</t>
-  </si>
-  <si>
-    <t>19.02.20261</t>
-  </si>
-  <si>
-    <t>19.02.20262</t>
-  </si>
-  <si>
-    <t>19.02.20263</t>
-  </si>
-  <si>
-    <t>19.02.20264</t>
-  </si>
-  <si>
-    <t>19.02.20265</t>
-  </si>
-  <si>
-    <t>19.02.20266</t>
-  </si>
-  <si>
-    <t>19.02.20267</t>
-  </si>
-  <si>
-    <t>19.02.20268</t>
-  </si>
-  <si>
-    <t>19.02.20269</t>
-  </si>
-  <si>
-    <t>19.02.202610</t>
-  </si>
-  <si>
-    <t>19.02.202611</t>
-  </si>
-  <si>
-    <t>19.02.202612</t>
-  </si>
-  <si>
-    <t>19.02.202613</t>
-  </si>
-  <si>
-    <t>19.02.202614</t>
-  </si>
-  <si>
-    <t>19.02.202615</t>
-  </si>
-  <si>
-    <t>19.02.202616</t>
-  </si>
-  <si>
-    <t>19.02.202617</t>
-  </si>
-  <si>
-    <t>19.02.202618</t>
-  </si>
-  <si>
-    <t>19.02.202619</t>
-  </si>
-  <si>
-    <t>19.02.202620</t>
-  </si>
-  <si>
-    <t>19.02.202621</t>
-  </si>
-  <si>
-    <t>19.02.202622</t>
-  </si>
-  <si>
-    <t>19.02.202623</t>
-  </si>
-  <si>
-    <t>19.02.202624</t>
-  </si>
-  <si>
-    <t>20.02.20261</t>
-  </si>
-  <si>
-    <t>20.02.20262</t>
-  </si>
-  <si>
-    <t>20.02.20263</t>
-  </si>
-  <si>
-    <t>20.02.20264</t>
-  </si>
-  <si>
-    <t>20.02.20265</t>
-  </si>
-  <si>
-    <t>20.02.20266</t>
-  </si>
-  <si>
-    <t>20.02.20267</t>
-  </si>
-  <si>
-    <t>20.02.20268</t>
-  </si>
-  <si>
-    <t>20.02.20269</t>
-  </si>
-  <si>
-    <t>20.02.202610</t>
-  </si>
-  <si>
-    <t>20.02.202611</t>
-  </si>
-  <si>
-    <t>20.02.202612</t>
-  </si>
-  <si>
-    <t>20.02.202613</t>
-  </si>
-  <si>
-    <t>20.02.202614</t>
-  </si>
-  <si>
-    <t>20.02.202615</t>
-  </si>
-  <si>
-    <t>20.02.202616</t>
-  </si>
-  <si>
-    <t>20.02.202617</t>
-  </si>
-  <si>
-    <t>20.02.202618</t>
-  </si>
-  <si>
-    <t>20.02.202619</t>
-  </si>
-  <si>
-    <t>20.02.202620</t>
-  </si>
-  <si>
-    <t>20.02.202621</t>
-  </si>
-  <si>
-    <t>20.02.202622</t>
-  </si>
-  <si>
-    <t>20.02.202623</t>
-  </si>
-  <si>
-    <t>20.02.202624</t>
-  </si>
-  <si>
-    <t>21.02.20261</t>
-  </si>
-  <si>
-    <t>21.02.20262</t>
-  </si>
-  <si>
-    <t>21.02.20263</t>
-  </si>
-  <si>
-    <t>21.02.20264</t>
-  </si>
-  <si>
-    <t>21.02.20265</t>
-  </si>
-  <si>
-    <t>21.02.20266</t>
-  </si>
-  <si>
-    <t>21.02.20267</t>
-  </si>
-  <si>
-    <t>21.02.20268</t>
-  </si>
-  <si>
-    <t>21.02.20269</t>
-  </si>
-  <si>
-    <t>21.02.202610</t>
-  </si>
-  <si>
-    <t>21.02.202611</t>
-  </si>
-  <si>
-    <t>21.02.202612</t>
-  </si>
-  <si>
-    <t>21.02.202613</t>
-  </si>
-  <si>
-    <t>21.02.202614</t>
-  </si>
-  <si>
-    <t>21.02.202615</t>
-  </si>
-  <si>
-    <t>21.02.202616</t>
-  </si>
-  <si>
-    <t>21.02.202617</t>
-  </si>
-  <si>
-    <t>21.02.202618</t>
-  </si>
-  <si>
-    <t>21.02.202619</t>
-  </si>
-  <si>
-    <t>21.02.202620</t>
-  </si>
-  <si>
-    <t>21.02.202621</t>
-  </si>
-  <si>
-    <t>21.02.202622</t>
-  </si>
-  <si>
-    <t>21.02.202623</t>
-  </si>
-  <si>
-    <t>21.02.202624</t>
-  </si>
-  <si>
-    <t>22.02.20261</t>
-  </si>
-  <si>
-    <t>22.02.20262</t>
-  </si>
-  <si>
-    <t>22.02.20263</t>
-  </si>
-  <si>
-    <t>22.02.20264</t>
-  </si>
-  <si>
-    <t>22.02.20265</t>
-  </si>
-  <si>
-    <t>22.02.20266</t>
-  </si>
-  <si>
-    <t>22.02.20267</t>
-  </si>
-  <si>
-    <t>22.02.20268</t>
-  </si>
-  <si>
-    <t>22.02.20269</t>
-  </si>
-  <si>
-    <t>22.02.202610</t>
-  </si>
-  <si>
-    <t>22.02.202611</t>
-  </si>
-  <si>
-    <t>22.02.202612</t>
-  </si>
-  <si>
-    <t>22.02.202613</t>
-  </si>
-  <si>
-    <t>22.02.202614</t>
-  </si>
-  <si>
-    <t>22.02.202615</t>
-  </si>
-  <si>
-    <t>22.02.202616</t>
-  </si>
-  <si>
-    <t>22.02.202617</t>
-  </si>
-  <si>
-    <t>22.02.202618</t>
-  </si>
-  <si>
-    <t>22.02.202619</t>
-  </si>
-  <si>
-    <t>22.02.202620</t>
-  </si>
-  <si>
-    <t>22.02.202621</t>
-  </si>
-  <si>
-    <t>22.02.202622</t>
-  </si>
-  <si>
-    <t>22.02.202623</t>
-  </si>
-  <si>
-    <t>22.02.202624</t>
-  </si>
-  <si>
-    <t>23.02.20261</t>
-  </si>
-  <si>
-    <t>23.02.20262</t>
-  </si>
-  <si>
-    <t>23.02.20263</t>
-  </si>
-  <si>
-    <t>23.02.20264</t>
-  </si>
-  <si>
-    <t>23.02.20265</t>
-  </si>
-  <si>
-    <t>23.02.20266</t>
-  </si>
-  <si>
-    <t>23.02.20267</t>
-  </si>
-  <si>
-    <t>23.02.20268</t>
-  </si>
-  <si>
-    <t>23.02.20269</t>
-  </si>
-  <si>
-    <t>23.02.202610</t>
-  </si>
-  <si>
-    <t>23.02.202611</t>
-  </si>
-  <si>
-    <t>23.02.202612</t>
-  </si>
-  <si>
-    <t>23.02.202613</t>
-  </si>
-  <si>
-    <t>23.02.202614</t>
-  </si>
-  <si>
-    <t>23.02.202615</t>
-  </si>
-  <si>
-    <t>23.02.202616</t>
-  </si>
-  <si>
-    <t>23.02.202617</t>
-  </si>
-  <si>
-    <t>23.02.202618</t>
-  </si>
-  <si>
-    <t>23.02.202619</t>
-  </si>
-  <si>
-    <t>23.02.202620</t>
-  </si>
-  <si>
-    <t>23.02.202621</t>
-  </si>
-  <si>
-    <t>23.02.202622</t>
-  </si>
-  <si>
-    <t>23.02.202623</t>
-  </si>
-  <si>
-    <t>23.02.202624</t>
-  </si>
-  <si>
-    <t>24.02.20261</t>
-  </si>
-  <si>
-    <t>24.02.20262</t>
-  </si>
-  <si>
-    <t>24.02.20263</t>
-  </si>
-  <si>
-    <t>24.02.20264</t>
-  </si>
-  <si>
-    <t>24.02.20265</t>
-  </si>
-  <si>
-    <t>24.02.20266</t>
-  </si>
-  <si>
-    <t>24.02.20267</t>
-  </si>
-  <si>
-    <t>24.02.20268</t>
-  </si>
-  <si>
-    <t>24.02.20269</t>
-  </si>
-  <si>
-    <t>24.02.202610</t>
-  </si>
-  <si>
-    <t>24.02.202611</t>
-  </si>
-  <si>
-    <t>24.02.202612</t>
-  </si>
-  <si>
-    <t>24.02.202613</t>
-  </si>
-  <si>
-    <t>24.02.202614</t>
-  </si>
-  <si>
-    <t>24.02.202615</t>
-  </si>
-  <si>
-    <t>24.02.202616</t>
-  </si>
-  <si>
-    <t>24.02.202617</t>
-  </si>
-  <si>
-    <t>24.02.202618</t>
-  </si>
-  <si>
-    <t>24.02.202619</t>
-  </si>
-  <si>
-    <t>24.02.202620</t>
-  </si>
-  <si>
-    <t>24.02.202621</t>
-  </si>
-  <si>
-    <t>24.02.202622</t>
-  </si>
-  <si>
-    <t>24.02.202623</t>
-  </si>
-  <si>
-    <t>24.02.202624</t>
-  </si>
-  <si>
-    <t>25.02.20261</t>
-  </si>
-  <si>
-    <t>25.02.20262</t>
-  </si>
-  <si>
-    <t>25.02.20263</t>
-  </si>
-  <si>
-    <t>25.02.20264</t>
-  </si>
-  <si>
-    <t>25.02.20265</t>
-  </si>
-  <si>
-    <t>25.02.20266</t>
-  </si>
-  <si>
-    <t>25.02.20267</t>
-  </si>
-  <si>
-    <t>25.02.20268</t>
-  </si>
-  <si>
-    <t>25.02.20269</t>
-  </si>
-  <si>
-    <t>25.02.202610</t>
-  </si>
-  <si>
-    <t>25.02.202611</t>
-  </si>
-  <si>
-    <t>25.02.202612</t>
-  </si>
-  <si>
-    <t>25.02.202613</t>
-  </si>
-  <si>
-    <t>25.02.202614</t>
-  </si>
-  <si>
-    <t>25.02.202615</t>
-  </si>
-  <si>
-    <t>25.02.202616</t>
-  </si>
-  <si>
-    <t>25.02.202617</t>
+    <t>29.03.202611</t>
+  </si>
+  <si>
+    <t>29.03.202612</t>
+  </si>
+  <si>
+    <t>29.03.202613</t>
+  </si>
+  <si>
+    <t>29.03.202614</t>
+  </si>
+  <si>
+    <t>29.03.202615</t>
+  </si>
+  <si>
+    <t>29.03.202616</t>
+  </si>
+  <si>
+    <t>29.03.202617</t>
+  </si>
+  <si>
+    <t>29.03.202618</t>
+  </si>
+  <si>
+    <t>29.03.202619</t>
+  </si>
+  <si>
+    <t>29.03.202620</t>
+  </si>
+  <si>
+    <t>29.03.202621</t>
+  </si>
+  <si>
+    <t>29.03.202622</t>
+  </si>
+  <si>
+    <t>29.03.202623</t>
+  </si>
+  <si>
+    <t>29.03.202624</t>
+  </si>
+  <si>
+    <t>30.03.20261</t>
+  </si>
+  <si>
+    <t>30.03.20262</t>
+  </si>
+  <si>
+    <t>30.03.20263</t>
+  </si>
+  <si>
+    <t>30.03.20264</t>
+  </si>
+  <si>
+    <t>30.03.20265</t>
+  </si>
+  <si>
+    <t>30.03.20266</t>
+  </si>
+  <si>
+    <t>30.03.20267</t>
+  </si>
+  <si>
+    <t>30.03.20268</t>
+  </si>
+  <si>
+    <t>30.03.20269</t>
+  </si>
+  <si>
+    <t>30.03.202610</t>
+  </si>
+  <si>
+    <t>30.03.202611</t>
+  </si>
+  <si>
+    <t>30.03.202612</t>
+  </si>
+  <si>
+    <t>30.03.202613</t>
+  </si>
+  <si>
+    <t>30.03.202614</t>
+  </si>
+  <si>
+    <t>30.03.202615</t>
+  </si>
+  <si>
+    <t>30.03.202616</t>
+  </si>
+  <si>
+    <t>30.03.202617</t>
+  </si>
+  <si>
+    <t>30.03.202618</t>
+  </si>
+  <si>
+    <t>30.03.202619</t>
+  </si>
+  <si>
+    <t>30.03.202620</t>
+  </si>
+  <si>
+    <t>30.03.202621</t>
+  </si>
+  <si>
+    <t>30.03.202622</t>
+  </si>
+  <si>
+    <t>30.03.202623</t>
+  </si>
+  <si>
+    <t>30.03.202624</t>
+  </si>
+  <si>
+    <t>31.03.20261</t>
+  </si>
+  <si>
+    <t>31.03.20262</t>
+  </si>
+  <si>
+    <t>31.03.20263</t>
+  </si>
+  <si>
+    <t>31.03.20264</t>
+  </si>
+  <si>
+    <t>31.03.20265</t>
+  </si>
+  <si>
+    <t>31.03.20266</t>
+  </si>
+  <si>
+    <t>31.03.20267</t>
+  </si>
+  <si>
+    <t>31.03.20268</t>
+  </si>
+  <si>
+    <t>31.03.20269</t>
+  </si>
+  <si>
+    <t>31.03.202610</t>
+  </si>
+  <si>
+    <t>31.03.202611</t>
+  </si>
+  <si>
+    <t>31.03.202612</t>
+  </si>
+  <si>
+    <t>31.03.202613</t>
+  </si>
+  <si>
+    <t>31.03.202614</t>
+  </si>
+  <si>
+    <t>31.03.202615</t>
+  </si>
+  <si>
+    <t>31.03.202616</t>
+  </si>
+  <si>
+    <t>31.03.202617</t>
+  </si>
+  <si>
+    <t>31.03.202618</t>
+  </si>
+  <si>
+    <t>31.03.202619</t>
+  </si>
+  <si>
+    <t>31.03.202620</t>
+  </si>
+  <si>
+    <t>31.03.202621</t>
+  </si>
+  <si>
+    <t>31.03.202622</t>
+  </si>
+  <si>
+    <t>31.03.202623</t>
+  </si>
+  <si>
+    <t>31.03.202624</t>
+  </si>
+  <si>
+    <t>01.04.20261</t>
+  </si>
+  <si>
+    <t>01.04.20262</t>
+  </si>
+  <si>
+    <t>01.04.20263</t>
+  </si>
+  <si>
+    <t>01.04.20264</t>
+  </si>
+  <si>
+    <t>01.04.20265</t>
+  </si>
+  <si>
+    <t>01.04.20266</t>
+  </si>
+  <si>
+    <t>01.04.20267</t>
+  </si>
+  <si>
+    <t>01.04.20268</t>
+  </si>
+  <si>
+    <t>01.04.20269</t>
+  </si>
+  <si>
+    <t>01.04.202610</t>
+  </si>
+  <si>
+    <t>01.04.202611</t>
+  </si>
+  <si>
+    <t>01.04.202612</t>
+  </si>
+  <si>
+    <t>01.04.202613</t>
+  </si>
+  <si>
+    <t>01.04.202614</t>
+  </si>
+  <si>
+    <t>01.04.202615</t>
+  </si>
+  <si>
+    <t>01.04.202616</t>
+  </si>
+  <si>
+    <t>01.04.202617</t>
+  </si>
+  <si>
+    <t>01.04.202618</t>
+  </si>
+  <si>
+    <t>01.04.202619</t>
+  </si>
+  <si>
+    <t>01.04.202620</t>
+  </si>
+  <si>
+    <t>01.04.202621</t>
+  </si>
+  <si>
+    <t>01.04.202622</t>
+  </si>
+  <si>
+    <t>01.04.202623</t>
+  </si>
+  <si>
+    <t>01.04.202624</t>
+  </si>
+  <si>
+    <t>02.04.20261</t>
+  </si>
+  <si>
+    <t>02.04.20262</t>
+  </si>
+  <si>
+    <t>02.04.20263</t>
+  </si>
+  <si>
+    <t>02.04.20264</t>
+  </si>
+  <si>
+    <t>02.04.20265</t>
+  </si>
+  <si>
+    <t>02.04.20266</t>
+  </si>
+  <si>
+    <t>02.04.20267</t>
+  </si>
+  <si>
+    <t>02.04.20268</t>
+  </si>
+  <si>
+    <t>02.04.20269</t>
+  </si>
+  <si>
+    <t>02.04.202610</t>
+  </si>
+  <si>
+    <t>02.04.202611</t>
+  </si>
+  <si>
+    <t>02.04.202612</t>
+  </si>
+  <si>
+    <t>02.04.202613</t>
+  </si>
+  <si>
+    <t>02.04.202614</t>
+  </si>
+  <si>
+    <t>02.04.202615</t>
+  </si>
+  <si>
+    <t>02.04.202616</t>
+  </si>
+  <si>
+    <t>02.04.202617</t>
+  </si>
+  <si>
+    <t>02.04.202618</t>
+  </si>
+  <si>
+    <t>02.04.202619</t>
+  </si>
+  <si>
+    <t>02.04.202620</t>
+  </si>
+  <si>
+    <t>02.04.202621</t>
+  </si>
+  <si>
+    <t>02.04.202622</t>
+  </si>
+  <si>
+    <t>02.04.202623</t>
+  </si>
+  <si>
+    <t>02.04.202624</t>
+  </si>
+  <si>
+    <t>03.04.20261</t>
+  </si>
+  <si>
+    <t>03.04.20262</t>
+  </si>
+  <si>
+    <t>03.04.20263</t>
+  </si>
+  <si>
+    <t>03.04.20264</t>
+  </si>
+  <si>
+    <t>03.04.20265</t>
+  </si>
+  <si>
+    <t>03.04.20266</t>
+  </si>
+  <si>
+    <t>03.04.20267</t>
+  </si>
+  <si>
+    <t>03.04.20268</t>
+  </si>
+  <si>
+    <t>03.04.20269</t>
+  </si>
+  <si>
+    <t>03.04.202610</t>
+  </si>
+  <si>
+    <t>03.04.202611</t>
+  </si>
+  <si>
+    <t>03.04.202612</t>
+  </si>
+  <si>
+    <t>03.04.202613</t>
+  </si>
+  <si>
+    <t>03.04.202614</t>
+  </si>
+  <si>
+    <t>03.04.202615</t>
+  </si>
+  <si>
+    <t>03.04.202616</t>
+  </si>
+  <si>
+    <t>03.04.202617</t>
+  </si>
+  <si>
+    <t>03.04.202618</t>
+  </si>
+  <si>
+    <t>03.04.202619</t>
+  </si>
+  <si>
+    <t>03.04.202620</t>
+  </si>
+  <si>
+    <t>03.04.202621</t>
+  </si>
+  <si>
+    <t>03.04.202622</t>
+  </si>
+  <si>
+    <t>03.04.202623</t>
+  </si>
+  <si>
+    <t>03.04.202624</t>
+  </si>
+  <si>
+    <t>04.04.20261</t>
+  </si>
+  <si>
+    <t>04.04.20262</t>
+  </si>
+  <si>
+    <t>04.04.20263</t>
+  </si>
+  <si>
+    <t>04.04.20264</t>
+  </si>
+  <si>
+    <t>04.04.20265</t>
+  </si>
+  <si>
+    <t>04.04.20266</t>
+  </si>
+  <si>
+    <t>04.04.20267</t>
+  </si>
+  <si>
+    <t>04.04.20268</t>
+  </si>
+  <si>
+    <t>04.04.20269</t>
+  </si>
+  <si>
+    <t>04.04.202610</t>
+  </si>
+  <si>
+    <t>04.04.202611</t>
+  </si>
+  <si>
+    <t>04.04.202612</t>
+  </si>
+  <si>
+    <t>04.04.202613</t>
+  </si>
+  <si>
+    <t>04.04.202614</t>
+  </si>
+  <si>
+    <t>04.04.202615</t>
+  </si>
+  <si>
+    <t>04.04.202616</t>
+  </si>
+  <si>
+    <t>04.04.202617</t>
+  </si>
+  <si>
+    <t>04.04.202618</t>
+  </si>
+  <si>
+    <t>04.04.202619</t>
+  </si>
+  <si>
+    <t>04.04.202620</t>
+  </si>
+  <si>
+    <t>04.04.202621</t>
+  </si>
+  <si>
+    <t>04.04.202622</t>
+  </si>
+  <si>
+    <t>04.04.202623</t>
+  </si>
+  <si>
+    <t>04.04.202624</t>
+  </si>
+  <si>
+    <t>05.04.20261</t>
+  </si>
+  <si>
+    <t>05.04.20262</t>
+  </si>
+  <si>
+    <t>05.04.20263</t>
+  </si>
+  <si>
+    <t>05.04.20264</t>
+  </si>
+  <si>
+    <t>05.04.20265</t>
+  </si>
+  <si>
+    <t>05.04.20266</t>
+  </si>
+  <si>
+    <t>05.04.20267</t>
+  </si>
+  <si>
+    <t>05.04.20268</t>
+  </si>
+  <si>
+    <t>05.04.20269</t>
+  </si>
+  <si>
+    <t>05.04.202610</t>
+  </si>
+  <si>
+    <t>05.04.202611</t>
   </si>
 </sst>
 </file>
@@ -1009,10 +1009,10 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" s="2">
-        <v>46071</v>
+        <v>46110</v>
       </c>
       <c r="B2">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -1021,7 +1021,7 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>0.08599999999999999</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -1036,7 +1036,7 @@
         <v>0</v>
       </c>
       <c r="J2">
-        <v>0.012</v>
+        <v>0</v>
       </c>
       <c r="S2" t="s">
         <v>20</v>
@@ -1047,10 +1047,10 @@
     </row>
     <row r="3" spans="1:20">
       <c r="A3" s="2">
-        <v>46071</v>
+        <v>46110</v>
       </c>
       <c r="B3">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -1059,7 +1059,7 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>0.08599999999999999</v>
+        <v>0.083</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -1074,7 +1074,7 @@
         <v>0</v>
       </c>
       <c r="J3">
-        <v>0.012</v>
+        <v>0</v>
       </c>
       <c r="S3" t="s">
         <v>21</v>
@@ -1085,34 +1085,34 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" s="2">
-        <v>46071</v>
+        <v>46110</v>
       </c>
       <c r="B4">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C4">
-        <v>0.047</v>
+        <v>1.259</v>
       </c>
       <c r="D4">
-        <v>0.068</v>
+        <v>1.765</v>
       </c>
       <c r="E4">
-        <v>0.358</v>
+        <v>3.466</v>
       </c>
       <c r="F4">
-        <v>0.015</v>
+        <v>0.393</v>
       </c>
       <c r="G4">
-        <v>0.023</v>
+        <v>0.317</v>
       </c>
       <c r="H4">
-        <v>0.063</v>
+        <v>0.479</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>0.606</v>
       </c>
       <c r="J4">
-        <v>0.045</v>
+        <v>0.672</v>
       </c>
       <c r="S4" t="s">
         <v>22</v>
@@ -1123,34 +1123,34 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" s="2">
-        <v>46071</v>
+        <v>46110</v>
       </c>
       <c r="B5">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>1.111</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>1.392</v>
       </c>
       <c r="E5">
-        <v>0.221</v>
+        <v>1.261</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>0.402</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>0.262</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>0.403</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>0.446</v>
       </c>
       <c r="J5">
-        <v>0.031</v>
+        <v>0.61</v>
       </c>
       <c r="S5" t="s">
         <v>23</v>
@@ -1161,34 +1161,34 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6" s="2">
-        <v>46071</v>
+        <v>46110</v>
       </c>
       <c r="B6">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>0.904</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>1.067</v>
       </c>
       <c r="E6">
-        <v>0.218</v>
+        <v>1.045</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>0.271</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>0.262</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>0.358</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>0.294</v>
       </c>
       <c r="J6">
-        <v>0.031</v>
+        <v>0.439</v>
       </c>
       <c r="S6" t="s">
         <v>24</v>
@@ -1199,34 +1199,34 @@
     </row>
     <row r="7" spans="1:20">
       <c r="A7" s="2">
-        <v>46071</v>
+        <v>46110</v>
       </c>
       <c r="B7">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>0.586</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>0.742</v>
       </c>
       <c r="E7">
-        <v>0.216</v>
+        <v>0.805</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>0.253</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>0.227</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>0.312</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>0.227</v>
       </c>
       <c r="J7">
-        <v>0.031</v>
+        <v>0.311</v>
       </c>
       <c r="S7" t="s">
         <v>25</v>
@@ -1237,34 +1237,34 @@
     </row>
     <row r="8" spans="1:20">
       <c r="A8" s="2">
-        <v>46071</v>
+        <v>46110</v>
       </c>
       <c r="B8">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>0.465</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>0.546</v>
       </c>
       <c r="E8">
-        <v>0.214</v>
+        <v>0.829</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>0.224</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>0.162</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>0.237</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>0.183</v>
       </c>
       <c r="J8">
-        <v>0.031</v>
+        <v>0.248</v>
       </c>
       <c r="S8" t="s">
         <v>26</v>
@@ -1275,34 +1275,34 @@
     </row>
     <row r="9" spans="1:20">
       <c r="A9" s="2">
-        <v>46071</v>
+        <v>46110</v>
       </c>
       <c r="B9">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>0.255</v>
       </c>
       <c r="E9">
-        <v>0.214</v>
+        <v>0.485</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>0.105</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>0.096</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>0.151</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>0.094</v>
       </c>
       <c r="J9">
-        <v>0.031</v>
+        <v>0.11</v>
       </c>
       <c r="S9" t="s">
         <v>27</v>
@@ -1313,34 +1313,34 @@
     </row>
     <row r="10" spans="1:20">
       <c r="A10" s="2">
-        <v>46072</v>
+        <v>46110</v>
       </c>
       <c r="B10">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>0.116</v>
       </c>
       <c r="E10">
-        <v>0.021</v>
+        <v>0.174</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>0.026</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>0.038</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>0.053</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="J10">
-        <v>0.032</v>
+        <v>0.026</v>
       </c>
       <c r="S10" t="s">
         <v>28</v>
@@ -1351,19 +1351,19 @@
     </row>
     <row r="11" spans="1:20">
       <c r="A11" s="2">
-        <v>46072</v>
+        <v>46110</v>
       </c>
       <c r="B11">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>0.011</v>
       </c>
       <c r="D11">
         <v>0</v>
       </c>
       <c r="E11">
-        <v>0.021</v>
+        <v>0.012</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -1378,7 +1378,7 @@
         <v>0</v>
       </c>
       <c r="J11">
-        <v>0.032</v>
+        <v>0.019</v>
       </c>
       <c r="S11" t="s">
         <v>29</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="12" spans="1:20">
       <c r="A12" s="2">
-        <v>46072</v>
+        <v>46110</v>
       </c>
       <c r="B12">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -1401,7 +1401,7 @@
         <v>0</v>
       </c>
       <c r="E12">
-        <v>0.021</v>
+        <v>0</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -1416,7 +1416,7 @@
         <v>0</v>
       </c>
       <c r="J12">
-        <v>0.032</v>
+        <v>0.013</v>
       </c>
       <c r="S12" t="s">
         <v>30</v>
@@ -1427,10 +1427,10 @@
     </row>
     <row r="13" spans="1:20">
       <c r="A13" s="2">
-        <v>46072</v>
+        <v>46110</v>
       </c>
       <c r="B13">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -1439,7 +1439,7 @@
         <v>0</v>
       </c>
       <c r="E13">
-        <v>0.024</v>
+        <v>0</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -1454,7 +1454,7 @@
         <v>0</v>
       </c>
       <c r="J13">
-        <v>0.032</v>
+        <v>0.013</v>
       </c>
       <c r="S13" t="s">
         <v>31</v>
@@ -1465,10 +1465,10 @@
     </row>
     <row r="14" spans="1:20">
       <c r="A14" s="2">
-        <v>46072</v>
+        <v>46110</v>
       </c>
       <c r="B14">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -1477,7 +1477,7 @@
         <v>0</v>
       </c>
       <c r="E14">
-        <v>0.022</v>
+        <v>0</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -1492,7 +1492,7 @@
         <v>0</v>
       </c>
       <c r="J14">
-        <v>0.032</v>
+        <v>0.013</v>
       </c>
       <c r="S14" t="s">
         <v>32</v>
@@ -1503,10 +1503,10 @@
     </row>
     <row r="15" spans="1:20">
       <c r="A15" s="2">
-        <v>46072</v>
+        <v>46110</v>
       </c>
       <c r="B15">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -1515,7 +1515,7 @@
         <v>0</v>
       </c>
       <c r="E15">
-        <v>0.022</v>
+        <v>0</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -1530,7 +1530,7 @@
         <v>0</v>
       </c>
       <c r="J15">
-        <v>0.032</v>
+        <v>0.013</v>
       </c>
       <c r="S15" t="s">
         <v>33</v>
@@ -1541,10 +1541,10 @@
     </row>
     <row r="16" spans="1:20">
       <c r="A16" s="2">
-        <v>46072</v>
+        <v>46111</v>
       </c>
       <c r="B16">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -1553,7 +1553,7 @@
         <v>0</v>
       </c>
       <c r="E16">
-        <v>0.018</v>
+        <v>0</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -1568,7 +1568,7 @@
         <v>0</v>
       </c>
       <c r="J16">
-        <v>0.032</v>
+        <v>0.014</v>
       </c>
       <c r="S16" t="s">
         <v>34</v>
@@ -1579,10 +1579,10 @@
     </row>
     <row r="17" spans="1:20">
       <c r="A17" s="2">
-        <v>46072</v>
+        <v>46111</v>
       </c>
       <c r="B17">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -1591,7 +1591,7 @@
         <v>0</v>
       </c>
       <c r="E17">
-        <v>0.022</v>
+        <v>0</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -1606,7 +1606,7 @@
         <v>0</v>
       </c>
       <c r="J17">
-        <v>0.032</v>
+        <v>0.014</v>
       </c>
       <c r="S17" t="s">
         <v>35</v>
@@ -1617,34 +1617,34 @@
     </row>
     <row r="18" spans="1:20">
       <c r="A18" s="2">
-        <v>46072</v>
+        <v>46111</v>
       </c>
       <c r="B18">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C18">
-        <v>0.016</v>
+        <v>0</v>
       </c>
       <c r="D18">
-        <v>0.025</v>
+        <v>0</v>
       </c>
       <c r="E18">
-        <v>0.126</v>
+        <v>0</v>
       </c>
       <c r="F18">
-        <v>0.228</v>
+        <v>0</v>
       </c>
       <c r="G18">
-        <v>0.145</v>
+        <v>0</v>
       </c>
       <c r="H18">
-        <v>0.082</v>
+        <v>0</v>
       </c>
       <c r="I18">
-        <v>0.064</v>
+        <v>0</v>
       </c>
       <c r="J18">
-        <v>0.051</v>
+        <v>0.014</v>
       </c>
       <c r="S18" t="s">
         <v>36</v>
@@ -1655,34 +1655,34 @@
     </row>
     <row r="19" spans="1:20">
       <c r="A19" s="2">
-        <v>46072</v>
+        <v>46111</v>
       </c>
       <c r="B19">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C19">
-        <v>0.296</v>
+        <v>0</v>
       </c>
       <c r="D19">
-        <v>0.453</v>
+        <v>0</v>
       </c>
       <c r="E19">
-        <v>0.548</v>
+        <v>0</v>
       </c>
       <c r="F19">
-        <v>1.211</v>
+        <v>0</v>
       </c>
       <c r="G19">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="H19">
-        <v>0.666</v>
+        <v>0</v>
       </c>
       <c r="I19">
-        <v>0.368</v>
+        <v>0</v>
       </c>
       <c r="J19">
-        <v>0.35</v>
+        <v>0.014</v>
       </c>
       <c r="S19" t="s">
         <v>37</v>
@@ -1693,34 +1693,34 @@
     </row>
     <row r="20" spans="1:20">
       <c r="A20" s="2">
-        <v>46072</v>
+        <v>46111</v>
       </c>
       <c r="B20">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C20">
-        <v>1.035</v>
+        <v>0</v>
       </c>
       <c r="D20">
-        <v>1.429</v>
+        <v>0</v>
       </c>
       <c r="E20">
-        <v>1.297</v>
+        <v>0</v>
       </c>
       <c r="F20">
-        <v>1.765</v>
+        <v>0</v>
       </c>
       <c r="G20">
-        <v>2.266</v>
+        <v>0</v>
       </c>
       <c r="H20">
-        <v>0.995</v>
+        <v>0</v>
       </c>
       <c r="I20">
-        <v>0.925</v>
+        <v>0</v>
       </c>
       <c r="J20">
-        <v>0.829</v>
+        <v>0.014</v>
       </c>
       <c r="S20" t="s">
         <v>38</v>
@@ -1731,34 +1731,34 @@
     </row>
     <row r="21" spans="1:20">
       <c r="A21" s="2">
-        <v>46072</v>
+        <v>46111</v>
       </c>
       <c r="B21">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C21">
-        <v>1.718</v>
+        <v>0</v>
       </c>
       <c r="D21">
-        <v>2.146</v>
+        <v>0</v>
       </c>
       <c r="E21">
-        <v>1.679</v>
+        <v>0</v>
       </c>
       <c r="F21">
-        <v>1.816</v>
+        <v>0</v>
       </c>
       <c r="G21">
-        <v>2.769</v>
+        <v>0</v>
       </c>
       <c r="H21">
-        <v>1.333</v>
+        <v>0</v>
       </c>
       <c r="I21">
-        <v>1.348</v>
+        <v>0</v>
       </c>
       <c r="J21">
-        <v>0.956</v>
+        <v>0.014</v>
       </c>
       <c r="S21" t="s">
         <v>39</v>
@@ -1769,34 +1769,34 @@
     </row>
     <row r="22" spans="1:20">
       <c r="A22" s="2">
-        <v>46072</v>
+        <v>46111</v>
       </c>
       <c r="B22">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C22">
-        <v>1.813</v>
+        <v>0</v>
       </c>
       <c r="D22">
-        <v>2.192</v>
+        <v>0</v>
       </c>
       <c r="E22">
-        <v>2.891</v>
+        <v>0</v>
       </c>
       <c r="F22">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="G22">
-        <v>2.364</v>
+        <v>0</v>
       </c>
       <c r="H22">
-        <v>1.408</v>
+        <v>0</v>
       </c>
       <c r="I22">
-        <v>1.366</v>
+        <v>0</v>
       </c>
       <c r="J22">
-        <v>1.156</v>
+        <v>0.014</v>
       </c>
       <c r="S22" t="s">
         <v>40</v>
@@ -1807,34 +1807,34 @@
     </row>
     <row r="23" spans="1:20">
       <c r="A23" s="2">
-        <v>46072</v>
+        <v>46111</v>
       </c>
       <c r="B23">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C23">
-        <v>1.707</v>
+        <v>0.022</v>
       </c>
       <c r="D23">
-        <v>1.982</v>
+        <v>0.024</v>
       </c>
       <c r="E23">
-        <v>3.003</v>
+        <v>0.011</v>
       </c>
       <c r="F23">
-        <v>1.972</v>
+        <v>0.044</v>
       </c>
       <c r="G23">
-        <v>1.819</v>
+        <v>0.019</v>
       </c>
       <c r="H23">
-        <v>1.332</v>
+        <v>0.012</v>
       </c>
       <c r="I23">
-        <v>1.353</v>
+        <v>0.025</v>
       </c>
       <c r="J23">
-        <v>1.2</v>
+        <v>0.038</v>
       </c>
       <c r="S23" t="s">
         <v>41</v>
@@ -1845,34 +1845,34 @@
     </row>
     <row r="24" spans="1:20">
       <c r="A24" s="2">
-        <v>46072</v>
+        <v>46111</v>
       </c>
       <c r="B24">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C24">
-        <v>1.264</v>
+        <v>0.287</v>
       </c>
       <c r="D24">
-        <v>1.697</v>
+        <v>0.241</v>
       </c>
       <c r="E24">
-        <v>2.821</v>
+        <v>0.293</v>
       </c>
       <c r="F24">
-        <v>1.788</v>
+        <v>0.196</v>
       </c>
       <c r="G24">
-        <v>1.977</v>
+        <v>0.114</v>
       </c>
       <c r="H24">
-        <v>1.259</v>
+        <v>0.106</v>
       </c>
       <c r="I24">
-        <v>1.304</v>
+        <v>0.167</v>
       </c>
       <c r="J24">
-        <v>1.065</v>
+        <v>0.139</v>
       </c>
       <c r="S24" t="s">
         <v>42</v>
@@ -1883,34 +1883,34 @@
     </row>
     <row r="25" spans="1:20">
       <c r="A25" s="2">
-        <v>46072</v>
+        <v>46111</v>
       </c>
       <c r="B25">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C25">
-        <v>0.855</v>
+        <v>0.584</v>
       </c>
       <c r="D25">
-        <v>1.073</v>
+        <v>0.632</v>
       </c>
       <c r="E25">
-        <v>1.758</v>
+        <v>0.754</v>
       </c>
       <c r="F25">
-        <v>1.512</v>
+        <v>0.308</v>
       </c>
       <c r="G25">
-        <v>1.647</v>
+        <v>0.237</v>
       </c>
       <c r="H25">
-        <v>1.164</v>
+        <v>0.278</v>
       </c>
       <c r="I25">
-        <v>1.007</v>
+        <v>0.451</v>
       </c>
       <c r="J25">
-        <v>0.8159999999999999</v>
+        <v>0.336</v>
       </c>
       <c r="S25" t="s">
         <v>43</v>
@@ -1921,34 +1921,34 @@
     </row>
     <row r="26" spans="1:20">
       <c r="A26" s="2">
-        <v>46072</v>
+        <v>46111</v>
       </c>
       <c r="B26">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C26">
-        <v>0.439</v>
+        <v>0.895</v>
       </c>
       <c r="D26">
-        <v>0.653</v>
+        <v>1.017</v>
       </c>
       <c r="E26">
-        <v>1.497</v>
+        <v>0.795</v>
       </c>
       <c r="F26">
-        <v>0.317</v>
+        <v>0.528</v>
       </c>
       <c r="G26">
-        <v>0.855</v>
+        <v>0.345</v>
       </c>
       <c r="H26">
-        <v>0.727</v>
+        <v>0.637</v>
       </c>
       <c r="I26">
+        <v>0.701</v>
+      </c>
+      <c r="J26">
         <v>0.449</v>
-      </c>
-      <c r="J26">
-        <v>0.55</v>
       </c>
       <c r="S26" t="s">
         <v>44</v>
@@ -1959,34 +1959,34 @@
     </row>
     <row r="27" spans="1:20">
       <c r="A27" s="2">
-        <v>46072</v>
+        <v>46111</v>
       </c>
       <c r="B27">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C27">
-        <v>0.129</v>
+        <v>1.064</v>
       </c>
       <c r="D27">
-        <v>0.2</v>
+        <v>1.306</v>
       </c>
       <c r="E27">
-        <v>0.78</v>
+        <v>1.084</v>
       </c>
       <c r="F27">
-        <v>0.156</v>
+        <v>0.634</v>
       </c>
       <c r="G27">
-        <v>0.255</v>
+        <v>0.531</v>
       </c>
       <c r="H27">
-        <v>0.458</v>
+        <v>0.774</v>
       </c>
       <c r="I27">
-        <v>0.174</v>
+        <v>0.891</v>
       </c>
       <c r="J27">
-        <v>0.21</v>
+        <v>0.729</v>
       </c>
       <c r="S27" t="s">
         <v>45</v>
@@ -1997,34 +1997,34 @@
     </row>
     <row r="28" spans="1:20">
       <c r="A28" s="2">
-        <v>46072</v>
+        <v>46111</v>
       </c>
       <c r="B28">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C28">
-        <v>0.022</v>
+        <v>1.105</v>
       </c>
       <c r="D28">
-        <v>0.023</v>
+        <v>1.333</v>
       </c>
       <c r="E28">
-        <v>0.315</v>
+        <v>2.134</v>
       </c>
       <c r="F28">
-        <v>0.032</v>
+        <v>0.841</v>
       </c>
       <c r="G28">
-        <v>0.053</v>
+        <v>0.641</v>
       </c>
       <c r="H28">
-        <v>0.063</v>
+        <v>0.975</v>
       </c>
       <c r="I28">
-        <v>0.021</v>
+        <v>0.897</v>
       </c>
       <c r="J28">
-        <v>0.045</v>
+        <v>0.764</v>
       </c>
       <c r="S28" t="s">
         <v>46</v>
@@ -2035,34 +2035,34 @@
     </row>
     <row r="29" spans="1:20">
       <c r="A29" s="2">
-        <v>46072</v>
+        <v>46111</v>
       </c>
       <c r="B29">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C29">
-        <v>0</v>
+        <v>1.218</v>
       </c>
       <c r="D29">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="E29">
-        <v>0.205</v>
+        <v>1.732</v>
       </c>
       <c r="F29">
-        <v>0</v>
+        <v>0.89</v>
       </c>
       <c r="G29">
-        <v>0</v>
+        <v>0.541</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>1.013</v>
       </c>
       <c r="I29">
-        <v>0</v>
+        <v>0.789</v>
       </c>
       <c r="J29">
-        <v>0.031</v>
+        <v>0.801</v>
       </c>
       <c r="S29" t="s">
         <v>47</v>
@@ -2073,34 +2073,34 @@
     </row>
     <row r="30" spans="1:20">
       <c r="A30" s="2">
-        <v>46072</v>
+        <v>46111</v>
       </c>
       <c r="B30">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>1.322</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>1.365</v>
       </c>
       <c r="E30">
-        <v>0.201</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="F30">
-        <v>0</v>
+        <v>0.771</v>
       </c>
       <c r="G30">
-        <v>0</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>1.029</v>
       </c>
       <c r="I30">
-        <v>0</v>
+        <v>0.65</v>
       </c>
       <c r="J30">
-        <v>0.031</v>
+        <v>0.732</v>
       </c>
       <c r="S30" t="s">
         <v>48</v>
@@ -2111,34 +2111,34 @@
     </row>
     <row r="31" spans="1:20">
       <c r="A31" s="2">
-        <v>46072</v>
+        <v>46111</v>
       </c>
       <c r="B31">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>1.215</v>
       </c>
       <c r="D31">
-        <v>0</v>
+        <v>1.493</v>
       </c>
       <c r="E31">
-        <v>0.199</v>
+        <v>0.715</v>
       </c>
       <c r="F31">
-        <v>0</v>
+        <v>0.705</v>
       </c>
       <c r="G31">
-        <v>0</v>
+        <v>0.731</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>0.93</v>
       </c>
       <c r="I31">
-        <v>0</v>
+        <v>0.522</v>
       </c>
       <c r="J31">
-        <v>0.031</v>
+        <v>0.68</v>
       </c>
       <c r="S31" t="s">
         <v>49</v>
@@ -2149,34 +2149,34 @@
     </row>
     <row r="32" spans="1:20">
       <c r="A32" s="2">
-        <v>46072</v>
+        <v>46111</v>
       </c>
       <c r="B32">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>1.011</v>
       </c>
       <c r="D32">
-        <v>0</v>
+        <v>1.175</v>
       </c>
       <c r="E32">
-        <v>0.199</v>
+        <v>0.666</v>
       </c>
       <c r="F32">
-        <v>0</v>
+        <v>0.547</v>
       </c>
       <c r="G32">
-        <v>0</v>
+        <v>0.448</v>
       </c>
       <c r="H32">
-        <v>0</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="I32">
-        <v>0</v>
+        <v>0.366</v>
       </c>
       <c r="J32">
-        <v>0.031</v>
+        <v>0.373</v>
       </c>
       <c r="S32" t="s">
         <v>50</v>
@@ -2187,34 +2187,34 @@
     </row>
     <row r="33" spans="1:20">
       <c r="A33" s="2">
-        <v>46072</v>
+        <v>46111</v>
       </c>
       <c r="B33">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C33">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>0.669</v>
       </c>
       <c r="E33">
-        <v>0.205</v>
+        <v>0.452</v>
       </c>
       <c r="F33">
-        <v>0</v>
+        <v>0.241</v>
       </c>
       <c r="G33">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="H33">
-        <v>0</v>
+        <v>0.384</v>
       </c>
       <c r="I33">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="J33">
-        <v>0.031</v>
+        <v>0.24</v>
       </c>
       <c r="S33" t="s">
         <v>51</v>
@@ -2225,34 +2225,34 @@
     </row>
     <row r="34" spans="1:20">
       <c r="A34" s="2">
-        <v>46073</v>
+        <v>46111</v>
       </c>
       <c r="B34">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="C34">
-        <v>0</v>
+        <v>0.151</v>
       </c>
       <c r="D34">
-        <v>0</v>
+        <v>0.195</v>
       </c>
       <c r="E34">
-        <v>0.023</v>
+        <v>0.137</v>
       </c>
       <c r="F34">
-        <v>0</v>
+        <v>0.076</v>
       </c>
       <c r="G34">
-        <v>0</v>
+        <v>0.089</v>
       </c>
       <c r="H34">
-        <v>0</v>
+        <v>0.151</v>
       </c>
       <c r="I34">
-        <v>0</v>
+        <v>0.064</v>
       </c>
       <c r="J34">
-        <v>0.032</v>
+        <v>0.037</v>
       </c>
       <c r="S34" t="s">
         <v>52</v>
@@ -2263,34 +2263,34 @@
     </row>
     <row r="35" spans="1:20">
       <c r="A35" s="2">
-        <v>46073</v>
+        <v>46111</v>
       </c>
       <c r="B35">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="C35">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="D35">
-        <v>0</v>
+        <v>0.024</v>
       </c>
       <c r="E35">
-        <v>0.023</v>
+        <v>0.013</v>
       </c>
       <c r="F35">
-        <v>0</v>
+        <v>0.011</v>
       </c>
       <c r="G35">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H35">
-        <v>0</v>
+        <v>0.011</v>
       </c>
       <c r="I35">
         <v>0</v>
       </c>
       <c r="J35">
-        <v>0.032</v>
+        <v>0.019</v>
       </c>
       <c r="S35" t="s">
         <v>53</v>
@@ -2301,10 +2301,10 @@
     </row>
     <row r="36" spans="1:20">
       <c r="A36" s="2">
-        <v>46073</v>
+        <v>46111</v>
       </c>
       <c r="B36">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="C36">
         <v>0</v>
@@ -2313,7 +2313,7 @@
         <v>0</v>
       </c>
       <c r="E36">
-        <v>0.023</v>
+        <v>0</v>
       </c>
       <c r="F36">
         <v>0</v>
@@ -2328,7 +2328,7 @@
         <v>0</v>
       </c>
       <c r="J36">
-        <v>0.032</v>
+        <v>0.013</v>
       </c>
       <c r="S36" t="s">
         <v>54</v>
@@ -2339,10 +2339,10 @@
     </row>
     <row r="37" spans="1:20">
       <c r="A37" s="2">
-        <v>46073</v>
+        <v>46111</v>
       </c>
       <c r="B37">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="C37">
         <v>0</v>
@@ -2351,7 +2351,7 @@
         <v>0</v>
       </c>
       <c r="E37">
-        <v>0.023</v>
+        <v>0</v>
       </c>
       <c r="F37">
         <v>0</v>
@@ -2366,7 +2366,7 @@
         <v>0</v>
       </c>
       <c r="J37">
-        <v>0.032</v>
+        <v>0.013</v>
       </c>
       <c r="S37" t="s">
         <v>55</v>
@@ -2377,10 +2377,10 @@
     </row>
     <row r="38" spans="1:20">
       <c r="A38" s="2">
-        <v>46073</v>
+        <v>46111</v>
       </c>
       <c r="B38">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="C38">
         <v>0</v>
@@ -2389,7 +2389,7 @@
         <v>0</v>
       </c>
       <c r="E38">
-        <v>0.017</v>
+        <v>0</v>
       </c>
       <c r="F38">
         <v>0</v>
@@ -2404,7 +2404,7 @@
         <v>0</v>
       </c>
       <c r="J38">
-        <v>0.032</v>
+        <v>0.013</v>
       </c>
       <c r="S38" t="s">
         <v>56</v>
@@ -2415,10 +2415,10 @@
     </row>
     <row r="39" spans="1:20">
       <c r="A39" s="2">
-        <v>46073</v>
+        <v>46111</v>
       </c>
       <c r="B39">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="C39">
         <v>0</v>
@@ -2427,7 +2427,7 @@
         <v>0</v>
       </c>
       <c r="E39">
-        <v>0.017</v>
+        <v>0</v>
       </c>
       <c r="F39">
         <v>0</v>
@@ -2442,7 +2442,7 @@
         <v>0</v>
       </c>
       <c r="J39">
-        <v>0.032</v>
+        <v>0.013</v>
       </c>
       <c r="S39" t="s">
         <v>57</v>
@@ -2453,10 +2453,10 @@
     </row>
     <row r="40" spans="1:20">
       <c r="A40" s="2">
-        <v>46073</v>
+        <v>46112</v>
       </c>
       <c r="B40">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C40">
         <v>0</v>
@@ -2465,7 +2465,7 @@
         <v>0</v>
       </c>
       <c r="E40">
-        <v>0.017</v>
+        <v>0</v>
       </c>
       <c r="F40">
         <v>0</v>
@@ -2480,7 +2480,7 @@
         <v>0</v>
       </c>
       <c r="J40">
-        <v>0.032</v>
+        <v>0.014</v>
       </c>
       <c r="S40" t="s">
         <v>58</v>
@@ -2491,10 +2491,10 @@
     </row>
     <row r="41" spans="1:20">
       <c r="A41" s="2">
-        <v>46073</v>
+        <v>46112</v>
       </c>
       <c r="B41">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C41">
         <v>0</v>
@@ -2503,7 +2503,7 @@
         <v>0</v>
       </c>
       <c r="E41">
-        <v>0.017</v>
+        <v>0</v>
       </c>
       <c r="F41">
         <v>0</v>
@@ -2518,7 +2518,7 @@
         <v>0</v>
       </c>
       <c r="J41">
-        <v>0.032</v>
+        <v>0.014</v>
       </c>
       <c r="S41" t="s">
         <v>59</v>
@@ -2529,10 +2529,10 @@
     </row>
     <row r="42" spans="1:20">
       <c r="A42" s="2">
-        <v>46073</v>
+        <v>46112</v>
       </c>
       <c r="B42">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C42">
         <v>0</v>
@@ -2541,22 +2541,22 @@
         <v>0</v>
       </c>
       <c r="E42">
-        <v>0.08500000000000001</v>
+        <v>0</v>
       </c>
       <c r="F42">
-        <v>0.174</v>
+        <v>0</v>
       </c>
       <c r="G42">
-        <v>0.083</v>
+        <v>0</v>
       </c>
       <c r="H42">
-        <v>0.059</v>
+        <v>0</v>
       </c>
       <c r="I42">
-        <v>0.042</v>
+        <v>0</v>
       </c>
       <c r="J42">
-        <v>0.051</v>
+        <v>0.014</v>
       </c>
       <c r="S42" t="s">
         <v>60</v>
@@ -2567,34 +2567,34 @@
     </row>
     <row r="43" spans="1:20">
       <c r="A43" s="2">
-        <v>46073</v>
+        <v>46112</v>
       </c>
       <c r="B43">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C43">
-        <v>0.097</v>
+        <v>0</v>
       </c>
       <c r="D43">
-        <v>0.112</v>
+        <v>0</v>
       </c>
       <c r="E43">
-        <v>0.257</v>
+        <v>0</v>
       </c>
       <c r="F43">
-        <v>0.495</v>
+        <v>0</v>
       </c>
       <c r="G43">
-        <v>0.445</v>
+        <v>0</v>
       </c>
       <c r="H43">
-        <v>0.389</v>
+        <v>0</v>
       </c>
       <c r="I43">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="J43">
-        <v>0.073</v>
+        <v>0.014</v>
       </c>
       <c r="S43" t="s">
         <v>61</v>
@@ -2605,34 +2605,34 @@
     </row>
     <row r="44" spans="1:20">
       <c r="A44" s="2">
-        <v>46073</v>
+        <v>46112</v>
       </c>
       <c r="B44">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C44">
-        <v>0.281</v>
+        <v>0</v>
       </c>
       <c r="D44">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="E44">
-        <v>0.6889999999999999</v>
+        <v>0</v>
       </c>
       <c r="F44">
-        <v>1.132</v>
+        <v>0</v>
       </c>
       <c r="G44">
-        <v>1.536</v>
+        <v>0</v>
       </c>
       <c r="H44">
-        <v>0.732</v>
+        <v>0</v>
       </c>
       <c r="I44">
-        <v>0.527</v>
+        <v>0</v>
       </c>
       <c r="J44">
-        <v>0.348</v>
+        <v>0.014</v>
       </c>
       <c r="S44" t="s">
         <v>62</v>
@@ -2643,34 +2643,34 @@
     </row>
     <row r="45" spans="1:20">
       <c r="A45" s="2">
-        <v>46073</v>
+        <v>46112</v>
       </c>
       <c r="B45">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C45">
-        <v>0.39</v>
+        <v>0</v>
       </c>
       <c r="D45">
-        <v>0.553</v>
+        <v>0</v>
       </c>
       <c r="E45">
-        <v>0.909</v>
+        <v>0</v>
       </c>
       <c r="F45">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="G45">
-        <v>2.015</v>
+        <v>0</v>
       </c>
       <c r="H45">
-        <v>1.121</v>
+        <v>0</v>
       </c>
       <c r="I45">
-        <v>1.007</v>
+        <v>0</v>
       </c>
       <c r="J45">
-        <v>0.462</v>
+        <v>0.014</v>
       </c>
       <c r="S45" t="s">
         <v>63</v>
@@ -2681,34 +2681,34 @@
     </row>
     <row r="46" spans="1:20">
       <c r="A46" s="2">
-        <v>46073</v>
+        <v>46112</v>
       </c>
       <c r="B46">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C46">
-        <v>0.419</v>
+        <v>0</v>
       </c>
       <c r="D46">
-        <v>0.6840000000000001</v>
+        <v>0</v>
       </c>
       <c r="E46">
-        <v>0.965</v>
+        <v>0</v>
       </c>
       <c r="F46">
-        <v>1.679</v>
+        <v>0</v>
       </c>
       <c r="G46">
-        <v>2.148</v>
+        <v>0</v>
       </c>
       <c r="H46">
-        <v>1.212</v>
+        <v>0</v>
       </c>
       <c r="I46">
-        <v>1.151</v>
+        <v>0</v>
       </c>
       <c r="J46">
-        <v>0.596</v>
+        <v>0.014</v>
       </c>
       <c r="S46" t="s">
         <v>64</v>
@@ -2719,34 +2719,34 @@
     </row>
     <row r="47" spans="1:20">
       <c r="A47" s="2">
-        <v>46073</v>
+        <v>46112</v>
       </c>
       <c r="B47">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C47">
-        <v>0.572</v>
+        <v>0.017</v>
       </c>
       <c r="D47">
-        <v>0.746</v>
+        <v>0.019</v>
       </c>
       <c r="E47">
-        <v>0.748</v>
+        <v>0.011</v>
       </c>
       <c r="F47">
-        <v>1.609</v>
+        <v>0.145</v>
       </c>
       <c r="G47">
-        <v>2.085</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="H47">
-        <v>1.112</v>
+        <v>0.034</v>
       </c>
       <c r="I47">
-        <v>1.21</v>
+        <v>0.021</v>
       </c>
       <c r="J47">
-        <v>0.805</v>
+        <v>0.038</v>
       </c>
       <c r="S47" t="s">
         <v>65</v>
@@ -2757,34 +2757,34 @@
     </row>
     <row r="48" spans="1:20">
       <c r="A48" s="2">
-        <v>46073</v>
+        <v>46112</v>
       </c>
       <c r="B48">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C48">
-        <v>0.572</v>
+        <v>0.205</v>
       </c>
       <c r="D48">
-        <v>0.648</v>
+        <v>0.179</v>
       </c>
       <c r="E48">
-        <v>0.548</v>
+        <v>0.309</v>
       </c>
       <c r="F48">
-        <v>1.373</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="G48">
-        <v>1.767</v>
+        <v>0.372</v>
       </c>
       <c r="H48">
-        <v>0.9409999999999999</v>
+        <v>0.231</v>
       </c>
       <c r="I48">
-        <v>1.127</v>
+        <v>0.098</v>
       </c>
       <c r="J48">
-        <v>0.572</v>
+        <v>0.075</v>
       </c>
       <c r="S48" t="s">
         <v>66</v>
@@ -2795,34 +2795,34 @@
     </row>
     <row r="49" spans="1:20">
       <c r="A49" s="2">
-        <v>46073</v>
+        <v>46112</v>
       </c>
       <c r="B49">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C49">
-        <v>0.389</v>
+        <v>0.383</v>
       </c>
       <c r="D49">
-        <v>0.497</v>
+        <v>0.405</v>
       </c>
       <c r="E49">
-        <v>0.425</v>
+        <v>0.838</v>
       </c>
       <c r="F49">
-        <v>0.459</v>
+        <v>1.417</v>
       </c>
       <c r="G49">
-        <v>1.165</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H49">
-        <v>0.714</v>
+        <v>0.479</v>
       </c>
       <c r="I49">
-        <v>0.489</v>
+        <v>0.178</v>
       </c>
       <c r="J49">
-        <v>0.37</v>
+        <v>0.281</v>
       </c>
       <c r="S49" t="s">
         <v>67</v>
@@ -2833,34 +2833,34 @@
     </row>
     <row r="50" spans="1:20">
       <c r="A50" s="2">
-        <v>46073</v>
+        <v>46112</v>
       </c>
       <c r="B50">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C50">
-        <v>0.256</v>
+        <v>0.556</v>
       </c>
       <c r="D50">
-        <v>0.327</v>
+        <v>0.648</v>
       </c>
       <c r="E50">
-        <v>0.361</v>
+        <v>1.152</v>
       </c>
       <c r="F50">
-        <v>0.291</v>
+        <v>2.212</v>
       </c>
       <c r="G50">
-        <v>0.314</v>
+        <v>1.478</v>
       </c>
       <c r="H50">
-        <v>0.461</v>
+        <v>0.763</v>
       </c>
       <c r="I50">
-        <v>0.274</v>
+        <v>0.247</v>
       </c>
       <c r="J50">
-        <v>0.282</v>
+        <v>0.435</v>
       </c>
       <c r="S50" t="s">
         <v>68</v>
@@ -2871,34 +2871,34 @@
     </row>
     <row r="51" spans="1:20">
       <c r="A51" s="2">
-        <v>46073</v>
+        <v>46112</v>
       </c>
       <c r="B51">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C51">
-        <v>0.099</v>
+        <v>0.638</v>
       </c>
       <c r="D51">
-        <v>0.116</v>
+        <v>0.825</v>
       </c>
       <c r="E51">
-        <v>0.121</v>
+        <v>2.392</v>
       </c>
       <c r="F51">
-        <v>0.111</v>
+        <v>2.581</v>
       </c>
       <c r="G51">
-        <v>0.102</v>
+        <v>1.967</v>
       </c>
       <c r="H51">
-        <v>0.221</v>
+        <v>0.998</v>
       </c>
       <c r="I51">
-        <v>0.099</v>
+        <v>0.323</v>
       </c>
       <c r="J51">
-        <v>0.056</v>
+        <v>0.531</v>
       </c>
       <c r="S51" t="s">
         <v>69</v>
@@ -2909,34 +2909,34 @@
     </row>
     <row r="52" spans="1:20">
       <c r="A52" s="2">
-        <v>46073</v>
+        <v>46112</v>
       </c>
       <c r="B52">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C52">
-        <v>0.011</v>
+        <v>0.834</v>
       </c>
       <c r="D52">
-        <v>0.01</v>
+        <v>1.001</v>
       </c>
       <c r="E52">
-        <v>0</v>
+        <v>2.711</v>
       </c>
       <c r="F52">
-        <v>0.01</v>
+        <v>3.034</v>
       </c>
       <c r="G52">
-        <v>0.017</v>
+        <v>2.055</v>
       </c>
       <c r="H52">
-        <v>0.015</v>
+        <v>1.169</v>
       </c>
       <c r="I52">
-        <v>0</v>
+        <v>0.501</v>
       </c>
       <c r="J52">
-        <v>0.045</v>
+        <v>0.662</v>
       </c>
       <c r="S52" t="s">
         <v>70</v>
@@ -2947,34 +2947,34 @@
     </row>
     <row r="53" spans="1:20">
       <c r="A53" s="2">
-        <v>46073</v>
+        <v>46112</v>
       </c>
       <c r="B53">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C53">
-        <v>0</v>
+        <v>0.873</v>
       </c>
       <c r="D53">
-        <v>0</v>
+        <v>1.087</v>
       </c>
       <c r="E53">
-        <v>0</v>
+        <v>2.851</v>
       </c>
       <c r="F53">
-        <v>0</v>
+        <v>3.008</v>
       </c>
       <c r="G53">
-        <v>0</v>
+        <v>2.012</v>
       </c>
       <c r="H53">
-        <v>0</v>
+        <v>1.112</v>
       </c>
       <c r="I53">
-        <v>0</v>
+        <v>0.606</v>
       </c>
       <c r="J53">
-        <v>0.031</v>
+        <v>0.7</v>
       </c>
       <c r="S53" t="s">
         <v>71</v>
@@ -2985,34 +2985,34 @@
     </row>
     <row r="54" spans="1:20">
       <c r="A54" s="2">
-        <v>46073</v>
+        <v>46112</v>
       </c>
       <c r="B54">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C54">
-        <v>0</v>
+        <v>0.826</v>
       </c>
       <c r="D54">
-        <v>0</v>
+        <v>1.015</v>
       </c>
       <c r="E54">
-        <v>0</v>
+        <v>2.696</v>
       </c>
       <c r="F54">
-        <v>0</v>
+        <v>2.649</v>
       </c>
       <c r="G54">
-        <v>0</v>
+        <v>1.939</v>
       </c>
       <c r="H54">
-        <v>0</v>
+        <v>1.124</v>
       </c>
       <c r="I54">
-        <v>0</v>
+        <v>0.614</v>
       </c>
       <c r="J54">
-        <v>0.031</v>
+        <v>0.627</v>
       </c>
       <c r="S54" t="s">
         <v>72</v>
@@ -3023,34 +3023,34 @@
     </row>
     <row r="55" spans="1:20">
       <c r="A55" s="2">
-        <v>46073</v>
+        <v>46112</v>
       </c>
       <c r="B55">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C55">
-        <v>0</v>
+        <v>0.706</v>
       </c>
       <c r="D55">
-        <v>0</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="E55">
-        <v>0</v>
+        <v>1.606</v>
       </c>
       <c r="F55">
-        <v>0</v>
+        <v>2.081</v>
       </c>
       <c r="G55">
-        <v>0</v>
+        <v>1.504</v>
       </c>
       <c r="H55">
-        <v>0</v>
+        <v>0.958</v>
       </c>
       <c r="I55">
-        <v>0</v>
+        <v>0.606</v>
       </c>
       <c r="J55">
-        <v>0.031</v>
+        <v>0.495</v>
       </c>
       <c r="S55" t="s">
         <v>73</v>
@@ -3061,34 +3061,34 @@
     </row>
     <row r="56" spans="1:20">
       <c r="A56" s="2">
-        <v>46073</v>
+        <v>46112</v>
       </c>
       <c r="B56">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C56">
-        <v>0</v>
+        <v>0.532</v>
       </c>
       <c r="D56">
-        <v>0</v>
+        <v>0.637</v>
       </c>
       <c r="E56">
-        <v>0</v>
+        <v>1.105</v>
       </c>
       <c r="F56">
-        <v>0</v>
+        <v>0.953</v>
       </c>
       <c r="G56">
-        <v>0</v>
+        <v>0.879</v>
       </c>
       <c r="H56">
-        <v>0</v>
+        <v>0.737</v>
       </c>
       <c r="I56">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="J56">
-        <v>0.031</v>
+        <v>0.375</v>
       </c>
       <c r="S56" t="s">
         <v>74</v>
@@ -3099,34 +3099,34 @@
     </row>
     <row r="57" spans="1:20">
       <c r="A57" s="2">
-        <v>46073</v>
+        <v>46112</v>
       </c>
       <c r="B57">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C57">
-        <v>0</v>
+        <v>0.316</v>
       </c>
       <c r="D57">
-        <v>0</v>
+        <v>0.393</v>
       </c>
       <c r="E57">
-        <v>0</v>
+        <v>0.83</v>
       </c>
       <c r="F57">
-        <v>0</v>
+        <v>0.468</v>
       </c>
       <c r="G57">
-        <v>0</v>
+        <v>0.38</v>
       </c>
       <c r="H57">
-        <v>0</v>
+        <v>0.431</v>
       </c>
       <c r="I57">
-        <v>0</v>
+        <v>0.198</v>
       </c>
       <c r="J57">
-        <v>0.031</v>
+        <v>0.255</v>
       </c>
       <c r="S57" t="s">
         <v>75</v>
@@ -3137,34 +3137,34 @@
     </row>
     <row r="58" spans="1:20">
       <c r="A58" s="2">
-        <v>46074</v>
+        <v>46112</v>
       </c>
       <c r="B58">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="C58">
-        <v>0</v>
+        <v>0.115</v>
       </c>
       <c r="D58">
-        <v>0</v>
+        <v>0.146</v>
       </c>
       <c r="E58">
-        <v>0</v>
+        <v>0.308</v>
       </c>
       <c r="F58">
-        <v>0</v>
+        <v>0.144</v>
       </c>
       <c r="G58">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="H58">
-        <v>0</v>
+        <v>0.151</v>
       </c>
       <c r="I58">
-        <v>0</v>
+        <v>0.058</v>
       </c>
       <c r="J58">
-        <v>0.032</v>
+        <v>0.035</v>
       </c>
       <c r="S58" t="s">
         <v>76</v>
@@ -3175,25 +3175,25 @@
     </row>
     <row r="59" spans="1:20">
       <c r="A59" s="2">
-        <v>46074</v>
+        <v>46112</v>
       </c>
       <c r="B59">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="C59">
-        <v>0</v>
+        <v>0.012</v>
       </c>
       <c r="D59">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E59">
-        <v>0</v>
+        <v>0.032</v>
       </c>
       <c r="F59">
-        <v>0</v>
+        <v>0.011</v>
       </c>
       <c r="G59">
-        <v>0</v>
+        <v>0.012</v>
       </c>
       <c r="H59">
         <v>0</v>
@@ -3202,7 +3202,7 @@
         <v>0</v>
       </c>
       <c r="J59">
-        <v>0.032</v>
+        <v>0.019</v>
       </c>
       <c r="S59" t="s">
         <v>77</v>
@@ -3213,10 +3213,10 @@
     </row>
     <row r="60" spans="1:20">
       <c r="A60" s="2">
-        <v>46074</v>
+        <v>46112</v>
       </c>
       <c r="B60">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="C60">
         <v>0</v>
@@ -3240,7 +3240,7 @@
         <v>0</v>
       </c>
       <c r="J60">
-        <v>0.032</v>
+        <v>0.013</v>
       </c>
       <c r="S60" t="s">
         <v>78</v>
@@ -3251,10 +3251,10 @@
     </row>
     <row r="61" spans="1:20">
       <c r="A61" s="2">
-        <v>46074</v>
+        <v>46112</v>
       </c>
       <c r="B61">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="C61">
         <v>0</v>
@@ -3278,7 +3278,7 @@
         <v>0</v>
       </c>
       <c r="J61">
-        <v>0.032</v>
+        <v>0.013</v>
       </c>
       <c r="S61" t="s">
         <v>79</v>
@@ -3289,10 +3289,10 @@
     </row>
     <row r="62" spans="1:20">
       <c r="A62" s="2">
-        <v>46074</v>
+        <v>46112</v>
       </c>
       <c r="B62">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="C62">
         <v>0</v>
@@ -3316,7 +3316,7 @@
         <v>0</v>
       </c>
       <c r="J62">
-        <v>0.032</v>
+        <v>0.013</v>
       </c>
       <c r="S62" t="s">
         <v>80</v>
@@ -3327,10 +3327,10 @@
     </row>
     <row r="63" spans="1:20">
       <c r="A63" s="2">
-        <v>46074</v>
+        <v>46112</v>
       </c>
       <c r="B63">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="C63">
         <v>0</v>
@@ -3354,7 +3354,7 @@
         <v>0</v>
       </c>
       <c r="J63">
-        <v>0.032</v>
+        <v>0.013</v>
       </c>
       <c r="S63" t="s">
         <v>81</v>
@@ -3365,10 +3365,10 @@
     </row>
     <row r="64" spans="1:20">
       <c r="A64" s="2">
-        <v>46074</v>
+        <v>46113</v>
       </c>
       <c r="B64">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C64">
         <v>0</v>
@@ -3392,7 +3392,7 @@
         <v>0</v>
       </c>
       <c r="J64">
-        <v>0.032</v>
+        <v>0.014</v>
       </c>
       <c r="S64" t="s">
         <v>82</v>
@@ -3403,10 +3403,10 @@
     </row>
     <row r="65" spans="1:20">
       <c r="A65" s="2">
-        <v>46074</v>
+        <v>46113</v>
       </c>
       <c r="B65">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C65">
         <v>0</v>
@@ -3415,7 +3415,7 @@
         <v>0</v>
       </c>
       <c r="E65">
-        <v>0.025</v>
+        <v>0</v>
       </c>
       <c r="F65">
         <v>0</v>
@@ -3430,7 +3430,7 @@
         <v>0</v>
       </c>
       <c r="J65">
-        <v>0.032</v>
+        <v>0.014</v>
       </c>
       <c r="S65" t="s">
         <v>83</v>
@@ -3441,34 +3441,34 @@
     </row>
     <row r="66" spans="1:20">
       <c r="A66" s="2">
-        <v>46074</v>
+        <v>46113</v>
       </c>
       <c r="B66">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C66">
-        <v>0.023</v>
+        <v>0</v>
       </c>
       <c r="D66">
-        <v>0.023</v>
+        <v>0</v>
       </c>
       <c r="E66">
-        <v>0.097</v>
+        <v>0</v>
       </c>
       <c r="F66">
-        <v>0.079</v>
+        <v>0</v>
       </c>
       <c r="G66">
-        <v>0.055</v>
+        <v>0</v>
       </c>
       <c r="H66">
-        <v>0.043</v>
+        <v>0</v>
       </c>
       <c r="I66">
-        <v>0.034</v>
+        <v>0</v>
       </c>
       <c r="J66">
-        <v>0.051</v>
+        <v>0.014</v>
       </c>
       <c r="S66" t="s">
         <v>84</v>
@@ -3479,34 +3479,34 @@
     </row>
     <row r="67" spans="1:20">
       <c r="A67" s="2">
-        <v>46074</v>
+        <v>46113</v>
       </c>
       <c r="B67">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C67">
-        <v>0.334</v>
+        <v>0</v>
       </c>
       <c r="D67">
-        <v>0.368</v>
+        <v>0</v>
       </c>
       <c r="E67">
-        <v>0.235</v>
+        <v>0</v>
       </c>
       <c r="F67">
-        <v>0.238</v>
+        <v>0</v>
       </c>
       <c r="G67">
-        <v>0.274</v>
+        <v>0</v>
       </c>
       <c r="H67">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I67">
-        <v>0.194</v>
+        <v>0</v>
       </c>
       <c r="J67">
-        <v>0.294</v>
+        <v>0.014</v>
       </c>
       <c r="S67" t="s">
         <v>85</v>
@@ -3517,34 +3517,34 @@
     </row>
     <row r="68" spans="1:20">
       <c r="A68" s="2">
-        <v>46074</v>
+        <v>46113</v>
       </c>
       <c r="B68">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C68">
-        <v>0.928</v>
+        <v>0</v>
       </c>
       <c r="D68">
-        <v>1.021</v>
+        <v>0</v>
       </c>
       <c r="E68">
-        <v>0.65</v>
+        <v>0</v>
       </c>
       <c r="F68">
-        <v>0.398</v>
+        <v>0</v>
       </c>
       <c r="G68">
-        <v>0.419</v>
+        <v>0</v>
       </c>
       <c r="H68">
-        <v>0.597</v>
+        <v>0</v>
       </c>
       <c r="I68">
-        <v>0.321</v>
+        <v>0</v>
       </c>
       <c r="J68">
-        <v>0.609</v>
+        <v>0.014</v>
       </c>
       <c r="S68" t="s">
         <v>86</v>
@@ -3555,34 +3555,34 @@
     </row>
     <row r="69" spans="1:20">
       <c r="A69" s="2">
-        <v>46074</v>
+        <v>46113</v>
       </c>
       <c r="B69">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C69">
-        <v>1.367</v>
+        <v>0</v>
       </c>
       <c r="D69">
-        <v>1.903</v>
+        <v>0</v>
       </c>
       <c r="E69">
-        <v>0.99</v>
+        <v>0</v>
       </c>
       <c r="F69">
-        <v>0.607</v>
+        <v>0</v>
       </c>
       <c r="G69">
-        <v>0.845</v>
+        <v>0</v>
       </c>
       <c r="H69">
-        <v>0.802</v>
+        <v>0</v>
       </c>
       <c r="I69">
-        <v>0.614</v>
+        <v>0</v>
       </c>
       <c r="J69">
-        <v>0.837</v>
+        <v>0.014</v>
       </c>
       <c r="S69" t="s">
         <v>87</v>
@@ -3593,34 +3593,34 @@
     </row>
     <row r="70" spans="1:20">
       <c r="A70" s="2">
-        <v>46074</v>
+        <v>46113</v>
       </c>
       <c r="B70">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C70">
-        <v>1.657</v>
+        <v>0</v>
       </c>
       <c r="D70">
-        <v>2.252</v>
+        <v>0</v>
       </c>
       <c r="E70">
-        <v>1.266</v>
+        <v>0</v>
       </c>
       <c r="F70">
-        <v>0.588</v>
+        <v>0</v>
       </c>
       <c r="G70">
-        <v>0.9429999999999999</v>
+        <v>0</v>
       </c>
       <c r="H70">
-        <v>0.791</v>
+        <v>0</v>
       </c>
       <c r="I70">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="J70">
-        <v>0.966</v>
+        <v>0.014</v>
       </c>
       <c r="S70" t="s">
         <v>88</v>
@@ -3631,34 +3631,34 @@
     </row>
     <row r="71" spans="1:20">
       <c r="A71" s="2">
-        <v>46074</v>
+        <v>46113</v>
       </c>
       <c r="B71">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C71">
-        <v>1.845</v>
+        <v>0.046</v>
       </c>
       <c r="D71">
-        <v>2.283</v>
+        <v>0.046</v>
       </c>
       <c r="E71">
-        <v>1.239</v>
+        <v>0.024</v>
       </c>
       <c r="F71">
-        <v>0.592</v>
+        <v>0.118</v>
       </c>
       <c r="G71">
-        <v>1.003</v>
+        <v>0.064</v>
       </c>
       <c r="H71">
-        <v>0.907</v>
+        <v>0.053</v>
       </c>
       <c r="I71">
-        <v>1.047</v>
+        <v>0.034</v>
       </c>
       <c r="J71">
-        <v>0.965</v>
+        <v>0.038</v>
       </c>
       <c r="S71" t="s">
         <v>89</v>
@@ -3669,34 +3669,34 @@
     </row>
     <row r="72" spans="1:20">
       <c r="A72" s="2">
-        <v>46074</v>
+        <v>46113</v>
       </c>
       <c r="B72">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C72">
-        <v>1.656</v>
+        <v>0.529</v>
       </c>
       <c r="D72">
-        <v>2.164</v>
+        <v>0.436</v>
       </c>
       <c r="E72">
-        <v>1.218</v>
+        <v>0.325</v>
       </c>
       <c r="F72">
-        <v>0.518</v>
+        <v>0.337</v>
       </c>
       <c r="G72">
-        <v>0.944</v>
+        <v>0.218</v>
       </c>
       <c r="H72">
-        <v>0.725</v>
+        <v>0.236</v>
       </c>
       <c r="I72">
-        <v>1.034</v>
+        <v>0.193</v>
       </c>
       <c r="J72">
-        <v>0.8179999999999999</v>
+        <v>0.218</v>
       </c>
       <c r="S72" t="s">
         <v>90</v>
@@ -3707,34 +3707,34 @@
     </row>
     <row r="73" spans="1:20">
       <c r="A73" s="2">
-        <v>46074</v>
+        <v>46113</v>
       </c>
       <c r="B73">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C73">
-        <v>1.31</v>
+        <v>0.907</v>
       </c>
       <c r="D73">
-        <v>1.759</v>
+        <v>0.991</v>
       </c>
       <c r="E73">
-        <v>1.014</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="F73">
-        <v>0.466</v>
+        <v>0.453</v>
       </c>
       <c r="G73">
-        <v>0.833</v>
+        <v>0.241</v>
       </c>
       <c r="H73">
-        <v>0.705</v>
+        <v>0.656</v>
       </c>
       <c r="I73">
-        <v>0.481</v>
+        <v>0.424</v>
       </c>
       <c r="J73">
-        <v>0.806</v>
+        <v>0.594</v>
       </c>
       <c r="S73" t="s">
         <v>91</v>
@@ -3745,34 +3745,34 @@
     </row>
     <row r="74" spans="1:20">
       <c r="A74" s="2">
-        <v>46074</v>
+        <v>46113</v>
       </c>
       <c r="B74">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C74">
-        <v>0.9340000000000001</v>
+        <v>1.499</v>
       </c>
       <c r="D74">
-        <v>0.972</v>
+        <v>1.559</v>
       </c>
       <c r="E74">
-        <v>0.796</v>
+        <v>1.639</v>
       </c>
       <c r="F74">
-        <v>0.294</v>
+        <v>0.84</v>
       </c>
       <c r="G74">
-        <v>0.389</v>
+        <v>0.666</v>
       </c>
       <c r="H74">
-        <v>0.522</v>
+        <v>0.917</v>
       </c>
       <c r="I74">
-        <v>0.285</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="J74">
-        <v>0.539</v>
+        <v>0.886</v>
       </c>
       <c r="S74" t="s">
         <v>92</v>
@@ -3783,34 +3783,34 @@
     </row>
     <row r="75" spans="1:20">
       <c r="A75" s="2">
-        <v>46074</v>
+        <v>46113</v>
       </c>
       <c r="B75">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C75">
-        <v>0.266</v>
+        <v>1.899</v>
       </c>
       <c r="D75">
-        <v>0.405</v>
+        <v>2.335</v>
       </c>
       <c r="E75">
-        <v>0.462</v>
+        <v>2.247</v>
       </c>
       <c r="F75">
-        <v>0.133</v>
+        <v>1.849</v>
       </c>
       <c r="G75">
-        <v>0.221</v>
+        <v>0.789</v>
       </c>
       <c r="H75">
-        <v>0.304</v>
+        <v>1.032</v>
       </c>
       <c r="I75">
-        <v>0.142</v>
+        <v>1.013</v>
       </c>
       <c r="J75">
-        <v>0.273</v>
+        <v>0.887</v>
       </c>
       <c r="S75" t="s">
         <v>93</v>
@@ -3821,34 +3821,34 @@
     </row>
     <row r="76" spans="1:20">
       <c r="A76" s="2">
-        <v>46074</v>
+        <v>46113</v>
       </c>
       <c r="B76">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C76">
-        <v>0.04</v>
+        <v>1.953</v>
       </c>
       <c r="D76">
-        <v>0.053</v>
+        <v>2.494</v>
       </c>
       <c r="E76">
-        <v>0.237</v>
+        <v>2.968</v>
       </c>
       <c r="F76">
-        <v>0.015</v>
+        <v>2.108</v>
       </c>
       <c r="G76">
-        <v>0.027</v>
+        <v>1.234</v>
       </c>
       <c r="H76">
-        <v>0.023</v>
+        <v>1.092</v>
       </c>
       <c r="I76">
-        <v>0.015</v>
+        <v>1.341</v>
       </c>
       <c r="J76">
-        <v>0.045</v>
+        <v>1.042</v>
       </c>
       <c r="S76" t="s">
         <v>94</v>
@@ -3859,34 +3859,34 @@
     </row>
     <row r="77" spans="1:20">
       <c r="A77" s="2">
-        <v>46074</v>
+        <v>46113</v>
       </c>
       <c r="B77">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C77">
-        <v>0</v>
+        <v>1.976</v>
       </c>
       <c r="D77">
-        <v>0</v>
+        <v>2.518</v>
       </c>
       <c r="E77">
-        <v>0.195</v>
+        <v>3.04</v>
       </c>
       <c r="F77">
-        <v>0</v>
+        <v>2.121</v>
       </c>
       <c r="G77">
-        <v>0</v>
+        <v>1.237</v>
       </c>
       <c r="H77">
-        <v>0</v>
+        <v>1.094</v>
       </c>
       <c r="I77">
-        <v>0</v>
+        <v>1.462</v>
       </c>
       <c r="J77">
-        <v>0.031</v>
+        <v>1.08</v>
       </c>
       <c r="S77" t="s">
         <v>95</v>
@@ -3897,34 +3897,34 @@
     </row>
     <row r="78" spans="1:20">
       <c r="A78" s="2">
-        <v>46074</v>
+        <v>46113</v>
       </c>
       <c r="B78">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C78">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="D78">
-        <v>0</v>
+        <v>2.448</v>
       </c>
       <c r="E78">
-        <v>0.194</v>
+        <v>2.739</v>
       </c>
       <c r="F78">
-        <v>0</v>
+        <v>1.961</v>
       </c>
       <c r="G78">
-        <v>0</v>
+        <v>1.175</v>
       </c>
       <c r="H78">
-        <v>0</v>
+        <v>0.987</v>
       </c>
       <c r="I78">
-        <v>0</v>
+        <v>1.383</v>
       </c>
       <c r="J78">
-        <v>0.031</v>
+        <v>0.907</v>
       </c>
       <c r="S78" t="s">
         <v>96</v>
@@ -3935,34 +3935,34 @@
     </row>
     <row r="79" spans="1:20">
       <c r="A79" s="2">
-        <v>46074</v>
+        <v>46113</v>
       </c>
       <c r="B79">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C79">
-        <v>0</v>
+        <v>1.632</v>
       </c>
       <c r="D79">
-        <v>0</v>
+        <v>1.763</v>
       </c>
       <c r="E79">
-        <v>0.199</v>
+        <v>2.131</v>
       </c>
       <c r="F79">
-        <v>0</v>
+        <v>1.397</v>
       </c>
       <c r="G79">
-        <v>0</v>
+        <v>0.89</v>
       </c>
       <c r="H79">
-        <v>0</v>
+        <v>0.989</v>
       </c>
       <c r="I79">
-        <v>0</v>
+        <v>1.219</v>
       </c>
       <c r="J79">
-        <v>0.031</v>
+        <v>0.893</v>
       </c>
       <c r="S79" t="s">
         <v>97</v>
@@ -3973,34 +3973,34 @@
     </row>
     <row r="80" spans="1:20">
       <c r="A80" s="2">
-        <v>46074</v>
+        <v>46113</v>
       </c>
       <c r="B80">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C80">
-        <v>0</v>
+        <v>1.179</v>
       </c>
       <c r="D80">
-        <v>0</v>
+        <v>1.399</v>
       </c>
       <c r="E80">
-        <v>0.199</v>
+        <v>1.665</v>
       </c>
       <c r="F80">
-        <v>0</v>
+        <v>0.754</v>
       </c>
       <c r="G80">
-        <v>0</v>
+        <v>0.539</v>
       </c>
       <c r="H80">
-        <v>0</v>
+        <v>0.917</v>
       </c>
       <c r="I80">
-        <v>0</v>
+        <v>0.906</v>
       </c>
       <c r="J80">
-        <v>0.031</v>
+        <v>0.763</v>
       </c>
       <c r="S80" t="s">
         <v>98</v>
@@ -4011,34 +4011,34 @@
     </row>
     <row r="81" spans="1:20">
       <c r="A81" s="2">
-        <v>46074</v>
+        <v>46113</v>
       </c>
       <c r="B81">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C81">
-        <v>0</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="D81">
-        <v>0</v>
+        <v>0.838</v>
       </c>
       <c r="E81">
-        <v>0.199</v>
+        <v>1.13</v>
       </c>
       <c r="F81">
-        <v>0</v>
+        <v>0.366</v>
       </c>
       <c r="G81">
-        <v>0</v>
+        <v>0.239</v>
       </c>
       <c r="H81">
-        <v>0</v>
+        <v>0.461</v>
       </c>
       <c r="I81">
-        <v>0</v>
+        <v>0.533</v>
       </c>
       <c r="J81">
-        <v>0.031</v>
+        <v>0.312</v>
       </c>
       <c r="S81" t="s">
         <v>99</v>
@@ -4049,34 +4049,34 @@
     </row>
     <row r="82" spans="1:20">
       <c r="A82" s="2">
-        <v>46075</v>
+        <v>46113</v>
       </c>
       <c r="B82">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="C82">
-        <v>0</v>
+        <v>0.275</v>
       </c>
       <c r="D82">
-        <v>0</v>
+        <v>0.297</v>
       </c>
       <c r="E82">
-        <v>0.021</v>
+        <v>0.402</v>
       </c>
       <c r="F82">
-        <v>0</v>
+        <v>0.075</v>
       </c>
       <c r="G82">
-        <v>0</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="H82">
-        <v>0</v>
+        <v>0.145</v>
       </c>
       <c r="I82">
-        <v>0</v>
+        <v>0.116</v>
       </c>
       <c r="J82">
-        <v>0.032</v>
+        <v>0.156</v>
       </c>
       <c r="S82" t="s">
         <v>100</v>
@@ -4087,19 +4087,19 @@
     </row>
     <row r="83" spans="1:20">
       <c r="A83" s="2">
-        <v>46075</v>
+        <v>46113</v>
       </c>
       <c r="B83">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="C83">
-        <v>0</v>
+        <v>0.024</v>
       </c>
       <c r="D83">
-        <v>0</v>
+        <v>0.023</v>
       </c>
       <c r="E83">
-        <v>0.021</v>
+        <v>0.047</v>
       </c>
       <c r="F83">
         <v>0</v>
@@ -4114,7 +4114,7 @@
         <v>0</v>
       </c>
       <c r="J83">
-        <v>0.032</v>
+        <v>0.037</v>
       </c>
       <c r="S83" t="s">
         <v>101</v>
@@ -4125,10 +4125,10 @@
     </row>
     <row r="84" spans="1:20">
       <c r="A84" s="2">
-        <v>46075</v>
+        <v>46113</v>
       </c>
       <c r="B84">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="C84">
         <v>0</v>
@@ -4137,7 +4137,7 @@
         <v>0</v>
       </c>
       <c r="E84">
-        <v>0.021</v>
+        <v>0</v>
       </c>
       <c r="F84">
         <v>0</v>
@@ -4152,7 +4152,7 @@
         <v>0</v>
       </c>
       <c r="J84">
-        <v>0.032</v>
+        <v>0.031</v>
       </c>
       <c r="S84" t="s">
         <v>102</v>
@@ -4163,10 +4163,10 @@
     </row>
     <row r="85" spans="1:20">
       <c r="A85" s="2">
-        <v>46075</v>
+        <v>46113</v>
       </c>
       <c r="B85">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="C85">
         <v>0</v>
@@ -4175,7 +4175,7 @@
         <v>0</v>
       </c>
       <c r="E85">
-        <v>0.021</v>
+        <v>0.016</v>
       </c>
       <c r="F85">
         <v>0</v>
@@ -4190,7 +4190,7 @@
         <v>0</v>
       </c>
       <c r="J85">
-        <v>0.032</v>
+        <v>0.031</v>
       </c>
       <c r="S85" t="s">
         <v>103</v>
@@ -4201,10 +4201,10 @@
     </row>
     <row r="86" spans="1:20">
       <c r="A86" s="2">
-        <v>46075</v>
+        <v>46113</v>
       </c>
       <c r="B86">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="C86">
         <v>0</v>
@@ -4213,7 +4213,7 @@
         <v>0</v>
       </c>
       <c r="E86">
-        <v>0.029</v>
+        <v>0.018</v>
       </c>
       <c r="F86">
         <v>0</v>
@@ -4228,7 +4228,7 @@
         <v>0</v>
       </c>
       <c r="J86">
-        <v>0.032</v>
+        <v>0.031</v>
       </c>
       <c r="S86" t="s">
         <v>104</v>
@@ -4239,10 +4239,10 @@
     </row>
     <row r="87" spans="1:20">
       <c r="A87" s="2">
-        <v>46075</v>
+        <v>46113</v>
       </c>
       <c r="B87">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="C87">
         <v>0</v>
@@ -4251,7 +4251,7 @@
         <v>0</v>
       </c>
       <c r="E87">
-        <v>0.022</v>
+        <v>0</v>
       </c>
       <c r="F87">
         <v>0</v>
@@ -4266,7 +4266,7 @@
         <v>0</v>
       </c>
       <c r="J87">
-        <v>0.032</v>
+        <v>0.031</v>
       </c>
       <c r="S87" t="s">
         <v>105</v>
@@ -4277,10 +4277,10 @@
     </row>
     <row r="88" spans="1:20">
       <c r="A88" s="2">
-        <v>46075</v>
+        <v>46114</v>
       </c>
       <c r="B88">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C88">
         <v>0</v>
@@ -4289,7 +4289,7 @@
         <v>0</v>
       </c>
       <c r="E88">
-        <v>0.022</v>
+        <v>0</v>
       </c>
       <c r="F88">
         <v>0</v>
@@ -4315,10 +4315,10 @@
     </row>
     <row r="89" spans="1:20">
       <c r="A89" s="2">
-        <v>46075</v>
+        <v>46114</v>
       </c>
       <c r="B89">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C89">
         <v>0</v>
@@ -4327,7 +4327,7 @@
         <v>0</v>
       </c>
       <c r="E89">
-        <v>0.025</v>
+        <v>0</v>
       </c>
       <c r="F89">
         <v>0</v>
@@ -4353,34 +4353,34 @@
     </row>
     <row r="90" spans="1:20">
       <c r="A90" s="2">
-        <v>46075</v>
+        <v>46114</v>
       </c>
       <c r="B90">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C90">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="D90">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="E90">
-        <v>0.143</v>
+        <v>0</v>
       </c>
       <c r="F90">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="G90">
-        <v>0.095</v>
+        <v>0</v>
       </c>
       <c r="H90">
-        <v>0.063</v>
+        <v>0</v>
       </c>
       <c r="I90">
-        <v>0.034</v>
+        <v>0</v>
       </c>
       <c r="J90">
-        <v>0.051</v>
+        <v>0.032</v>
       </c>
       <c r="S90" t="s">
         <v>108</v>
@@ -4391,34 +4391,34 @@
     </row>
     <row r="91" spans="1:20">
       <c r="A91" s="2">
-        <v>46075</v>
+        <v>46114</v>
       </c>
       <c r="B91">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C91">
-        <v>0.109</v>
+        <v>0</v>
       </c>
       <c r="D91">
-        <v>0.151</v>
+        <v>0</v>
       </c>
       <c r="E91">
-        <v>0.533</v>
+        <v>0</v>
       </c>
       <c r="F91">
-        <v>0.458</v>
+        <v>0</v>
       </c>
       <c r="G91">
-        <v>0.551</v>
+        <v>0</v>
       </c>
       <c r="H91">
-        <v>0.506</v>
+        <v>0</v>
       </c>
       <c r="I91">
-        <v>0.185</v>
+        <v>0</v>
       </c>
       <c r="J91">
-        <v>0.152</v>
+        <v>0.032</v>
       </c>
       <c r="S91" t="s">
         <v>109</v>
@@ -4429,34 +4429,34 @@
     </row>
     <row r="92" spans="1:20">
       <c r="A92" s="2">
-        <v>46075</v>
+        <v>46114</v>
       </c>
       <c r="B92">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C92">
-        <v>0.301</v>
+        <v>0</v>
       </c>
       <c r="D92">
-        <v>0.374</v>
+        <v>0</v>
       </c>
       <c r="E92">
-        <v>0.918</v>
+        <v>0</v>
       </c>
       <c r="F92">
-        <v>1.038</v>
+        <v>0</v>
       </c>
       <c r="G92">
-        <v>0.879</v>
+        <v>0</v>
       </c>
       <c r="H92">
-        <v>0.96</v>
+        <v>0</v>
       </c>
       <c r="I92">
-        <v>0.453</v>
+        <v>0</v>
       </c>
       <c r="J92">
-        <v>0.37</v>
+        <v>0.032</v>
       </c>
       <c r="S92" t="s">
         <v>110</v>
@@ -4467,34 +4467,34 @@
     </row>
     <row r="93" spans="1:20">
       <c r="A93" s="2">
-        <v>46075</v>
+        <v>46114</v>
       </c>
       <c r="B93">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C93">
-        <v>0.534</v>
+        <v>0</v>
       </c>
       <c r="D93">
-        <v>0.612</v>
+        <v>0</v>
       </c>
       <c r="E93">
-        <v>1.302</v>
+        <v>0</v>
       </c>
       <c r="F93">
-        <v>1.642</v>
+        <v>0</v>
       </c>
       <c r="G93">
-        <v>1.805</v>
+        <v>0</v>
       </c>
       <c r="H93">
-        <v>1.211</v>
+        <v>0</v>
       </c>
       <c r="I93">
-        <v>0.97</v>
+        <v>0</v>
       </c>
       <c r="J93">
-        <v>0.574</v>
+        <v>0.032</v>
       </c>
       <c r="S93" t="s">
         <v>111</v>
@@ -4505,34 +4505,34 @@
     </row>
     <row r="94" spans="1:20">
       <c r="A94" s="2">
-        <v>46075</v>
+        <v>46114</v>
       </c>
       <c r="B94">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C94">
-        <v>0.552</v>
+        <v>0</v>
       </c>
       <c r="D94">
-        <v>0.765</v>
+        <v>0</v>
       </c>
       <c r="E94">
-        <v>2.517</v>
+        <v>0</v>
       </c>
       <c r="F94">
-        <v>1.641</v>
+        <v>0</v>
       </c>
       <c r="G94">
-        <v>2.252</v>
+        <v>0</v>
       </c>
       <c r="H94">
-        <v>1.308</v>
+        <v>0</v>
       </c>
       <c r="I94">
-        <v>1.142</v>
+        <v>0</v>
       </c>
       <c r="J94">
-        <v>0.608</v>
+        <v>0.032</v>
       </c>
       <c r="S94" t="s">
         <v>112</v>
@@ -4543,34 +4543,34 @@
     </row>
     <row r="95" spans="1:20">
       <c r="A95" s="2">
-        <v>46075</v>
+        <v>46114</v>
       </c>
       <c r="B95">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C95">
-        <v>0.588</v>
+        <v>0.048</v>
       </c>
       <c r="D95">
-        <v>0.769</v>
+        <v>0.047</v>
       </c>
       <c r="E95">
-        <v>2.744</v>
+        <v>0.012</v>
       </c>
       <c r="F95">
-        <v>1.778</v>
+        <v>0.081</v>
       </c>
       <c r="G95">
-        <v>2.226</v>
+        <v>0.041</v>
       </c>
       <c r="H95">
-        <v>1.298</v>
+        <v>0.016</v>
       </c>
       <c r="I95">
-        <v>1.2</v>
+        <v>0.025</v>
       </c>
       <c r="J95">
-        <v>0.608</v>
+        <v>0.051</v>
       </c>
       <c r="S95" t="s">
         <v>113</v>
@@ -4581,34 +4581,34 @@
     </row>
     <row r="96" spans="1:20">
       <c r="A96" s="2">
-        <v>46075</v>
+        <v>46114</v>
       </c>
       <c r="B96">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C96">
-        <v>0.574</v>
+        <v>0.538</v>
       </c>
       <c r="D96">
-        <v>0.68</v>
+        <v>0.653</v>
       </c>
       <c r="E96">
-        <v>2.6</v>
+        <v>0.196</v>
       </c>
       <c r="F96">
-        <v>1.729</v>
+        <v>0.36</v>
       </c>
       <c r="G96">
-        <v>1.975</v>
+        <v>0.232</v>
       </c>
       <c r="H96">
-        <v>1.218</v>
+        <v>0.172</v>
       </c>
       <c r="I96">
-        <v>1.189</v>
+        <v>0.188</v>
       </c>
       <c r="J96">
-        <v>0.432</v>
+        <v>0.218</v>
       </c>
       <c r="S96" t="s">
         <v>114</v>
@@ -4619,34 +4619,34 @@
     </row>
     <row r="97" spans="1:20">
       <c r="A97" s="2">
-        <v>46075</v>
+        <v>46114</v>
       </c>
       <c r="B97">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C97">
-        <v>0.457</v>
+        <v>1.169</v>
       </c>
       <c r="D97">
-        <v>0.61</v>
+        <v>1.3</v>
       </c>
       <c r="E97">
-        <v>2.331</v>
+        <v>0.641</v>
       </c>
       <c r="F97">
-        <v>1.529</v>
+        <v>0.701</v>
       </c>
       <c r="G97">
-        <v>1.733</v>
+        <v>0.339</v>
       </c>
       <c r="H97">
-        <v>1.155</v>
+        <v>0.393</v>
       </c>
       <c r="I97">
-        <v>1.034</v>
+        <v>0.418</v>
       </c>
       <c r="J97">
-        <v>0.37</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="S97" t="s">
         <v>115</v>
@@ -4657,34 +4657,34 @@
     </row>
     <row r="98" spans="1:20">
       <c r="A98" s="2">
-        <v>46075</v>
+        <v>46114</v>
       </c>
       <c r="B98">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C98">
-        <v>0.27</v>
+        <v>1.935</v>
       </c>
       <c r="D98">
-        <v>0.43</v>
+        <v>2.394</v>
       </c>
       <c r="E98">
-        <v>1.013</v>
+        <v>0.98</v>
       </c>
       <c r="F98">
-        <v>0.348</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="G98">
-        <v>0.903</v>
+        <v>0.539</v>
       </c>
       <c r="H98">
-        <v>0.8</v>
+        <v>0.723</v>
       </c>
       <c r="I98">
-        <v>0.509</v>
+        <v>0.663</v>
       </c>
       <c r="J98">
-        <v>0.288</v>
+        <v>0.886</v>
       </c>
       <c r="S98" t="s">
         <v>116</v>
@@ -4695,34 +4695,34 @@
     </row>
     <row r="99" spans="1:20">
       <c r="A99" s="2">
-        <v>46075</v>
+        <v>46114</v>
       </c>
       <c r="B99">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C99">
-        <v>0.114</v>
+        <v>2.526</v>
       </c>
       <c r="D99">
-        <v>0.205</v>
+        <v>2.842</v>
       </c>
       <c r="E99">
-        <v>0.452</v>
+        <v>1.499</v>
       </c>
       <c r="F99">
-        <v>0.155</v>
+        <v>0.859</v>
       </c>
       <c r="G99">
-        <v>0.257</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="H99">
-        <v>0.459</v>
+        <v>0.729</v>
       </c>
       <c r="I99">
-        <v>0.211</v>
+        <v>0.743</v>
       </c>
       <c r="J99">
-        <v>0.08500000000000001</v>
+        <v>0.904</v>
       </c>
       <c r="S99" t="s">
         <v>117</v>
@@ -4733,34 +4733,34 @@
     </row>
     <row r="100" spans="1:20">
       <c r="A100" s="2">
-        <v>46075</v>
+        <v>46114</v>
       </c>
       <c r="B100">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C100">
-        <v>0.017</v>
+        <v>2.525</v>
       </c>
       <c r="D100">
-        <v>0.024</v>
+        <v>3.042</v>
       </c>
       <c r="E100">
-        <v>0.119</v>
+        <v>1.558</v>
       </c>
       <c r="F100">
-        <v>0.034</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="G100">
-        <v>0.057</v>
+        <v>0.593</v>
       </c>
       <c r="H100">
-        <v>0.063</v>
+        <v>0.748</v>
       </c>
       <c r="I100">
-        <v>0.025</v>
+        <v>0.747</v>
       </c>
       <c r="J100">
-        <v>0.045</v>
+        <v>1.027</v>
       </c>
       <c r="S100" t="s">
         <v>118</v>
@@ -4771,34 +4771,34 @@
     </row>
     <row r="101" spans="1:20">
       <c r="A101" s="2">
-        <v>46075</v>
+        <v>46114</v>
       </c>
       <c r="B101">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C101">
-        <v>0</v>
+        <v>2.458</v>
       </c>
       <c r="D101">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E101">
-        <v>0</v>
+        <v>1.663</v>
       </c>
       <c r="F101">
-        <v>0</v>
+        <v>0.795</v>
       </c>
       <c r="G101">
-        <v>0</v>
+        <v>0.581</v>
       </c>
       <c r="H101">
-        <v>0</v>
+        <v>0.748</v>
       </c>
       <c r="I101">
-        <v>0</v>
+        <v>0.747</v>
       </c>
       <c r="J101">
-        <v>0.031</v>
+        <v>1.121</v>
       </c>
       <c r="S101" t="s">
         <v>119</v>
@@ -4809,34 +4809,34 @@
     </row>
     <row r="102" spans="1:20">
       <c r="A102" s="2">
-        <v>46075</v>
+        <v>46114</v>
       </c>
       <c r="B102">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C102">
-        <v>0</v>
+        <v>2.194</v>
       </c>
       <c r="D102">
-        <v>0</v>
+        <v>2.574</v>
       </c>
       <c r="E102">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="F102">
-        <v>0</v>
+        <v>0.735</v>
       </c>
       <c r="G102">
-        <v>0</v>
+        <v>0.532</v>
       </c>
       <c r="H102">
-        <v>0</v>
+        <v>0.729</v>
       </c>
       <c r="I102">
-        <v>0</v>
+        <v>0.665</v>
       </c>
       <c r="J102">
-        <v>0.031</v>
+        <v>1.061</v>
       </c>
       <c r="S102" t="s">
         <v>120</v>
@@ -4847,34 +4847,34 @@
     </row>
     <row r="103" spans="1:20">
       <c r="A103" s="2">
-        <v>46075</v>
+        <v>46114</v>
       </c>
       <c r="B103">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C103">
-        <v>0</v>
+        <v>1.894</v>
       </c>
       <c r="D103">
-        <v>0</v>
+        <v>2.117</v>
       </c>
       <c r="E103">
-        <v>0</v>
+        <v>1.155</v>
       </c>
       <c r="F103">
-        <v>0</v>
+        <v>0.611</v>
       </c>
       <c r="G103">
-        <v>0</v>
+        <v>0.381</v>
       </c>
       <c r="H103">
-        <v>0</v>
+        <v>0.632</v>
       </c>
       <c r="I103">
-        <v>0</v>
+        <v>0.571</v>
       </c>
       <c r="J103">
-        <v>0.031</v>
+        <v>0.893</v>
       </c>
       <c r="S103" t="s">
         <v>121</v>
@@ -4885,34 +4885,34 @@
     </row>
     <row r="104" spans="1:20">
       <c r="A104" s="2">
-        <v>46075</v>
+        <v>46114</v>
       </c>
       <c r="B104">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C104">
-        <v>0</v>
+        <v>1.479</v>
       </c>
       <c r="D104">
-        <v>0</v>
+        <v>1.534</v>
       </c>
       <c r="E104">
-        <v>0</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="F104">
-        <v>0</v>
+        <v>0.379</v>
       </c>
       <c r="G104">
-        <v>0</v>
+        <v>0.273</v>
       </c>
       <c r="H104">
-        <v>0</v>
+        <v>0.393</v>
       </c>
       <c r="I104">
-        <v>0</v>
+        <v>0.451</v>
       </c>
       <c r="J104">
-        <v>0.031</v>
+        <v>0.68</v>
       </c>
       <c r="S104" t="s">
         <v>122</v>
@@ -4923,34 +4923,34 @@
     </row>
     <row r="105" spans="1:20">
       <c r="A105" s="2">
-        <v>46075</v>
+        <v>46114</v>
       </c>
       <c r="B105">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C105">
-        <v>0</v>
+        <v>0.765</v>
       </c>
       <c r="D105">
-        <v>0</v>
+        <v>0.894</v>
       </c>
       <c r="E105">
-        <v>0.201</v>
+        <v>0.651</v>
       </c>
       <c r="F105">
-        <v>0</v>
+        <v>0.153</v>
       </c>
       <c r="G105">
-        <v>0</v>
+        <v>0.154</v>
       </c>
       <c r="H105">
-        <v>0</v>
+        <v>0.221</v>
       </c>
       <c r="I105">
-        <v>0</v>
+        <v>0.193</v>
       </c>
       <c r="J105">
-        <v>0.031</v>
+        <v>0.285</v>
       </c>
       <c r="S105" t="s">
         <v>123</v>
@@ -4961,34 +4961,34 @@
     </row>
     <row r="106" spans="1:20">
       <c r="A106" s="2">
-        <v>46076</v>
+        <v>46114</v>
       </c>
       <c r="B106">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="C106">
-        <v>0</v>
+        <v>0.278</v>
       </c>
       <c r="D106">
-        <v>0</v>
+        <v>0.347</v>
       </c>
       <c r="E106">
-        <v>0.046</v>
+        <v>0.189</v>
       </c>
       <c r="F106">
-        <v>0</v>
+        <v>0.047</v>
       </c>
       <c r="G106">
-        <v>0</v>
+        <v>0.059</v>
       </c>
       <c r="H106">
-        <v>0</v>
+        <v>0.104</v>
       </c>
       <c r="I106">
-        <v>0</v>
+        <v>0.064</v>
       </c>
       <c r="J106">
-        <v>0.032</v>
+        <v>0.053</v>
       </c>
       <c r="S106" t="s">
         <v>124</v>
@@ -4999,22 +4999,22 @@
     </row>
     <row r="107" spans="1:20">
       <c r="A107" s="2">
-        <v>46076</v>
+        <v>46114</v>
       </c>
       <c r="B107">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="C107">
-        <v>0</v>
+        <v>0.023</v>
       </c>
       <c r="D107">
-        <v>0</v>
+        <v>0.023</v>
       </c>
       <c r="E107">
         <v>0.024</v>
       </c>
       <c r="F107">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="G107">
         <v>0</v>
@@ -5026,7 +5026,7 @@
         <v>0</v>
       </c>
       <c r="J107">
-        <v>0.032</v>
+        <v>0.019</v>
       </c>
       <c r="S107" t="s">
         <v>125</v>
@@ -5037,10 +5037,10 @@
     </row>
     <row r="108" spans="1:20">
       <c r="A108" s="2">
-        <v>46076</v>
+        <v>46114</v>
       </c>
       <c r="B108">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="C108">
         <v>0</v>
@@ -5049,7 +5049,7 @@
         <v>0</v>
       </c>
       <c r="E108">
-        <v>0.024</v>
+        <v>0.011</v>
       </c>
       <c r="F108">
         <v>0</v>
@@ -5064,7 +5064,7 @@
         <v>0</v>
       </c>
       <c r="J108">
-        <v>0.032</v>
+        <v>0.013</v>
       </c>
       <c r="S108" t="s">
         <v>126</v>
@@ -5075,10 +5075,10 @@
     </row>
     <row r="109" spans="1:20">
       <c r="A109" s="2">
-        <v>46076</v>
+        <v>46114</v>
       </c>
       <c r="B109">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="C109">
         <v>0</v>
@@ -5087,7 +5087,7 @@
         <v>0</v>
       </c>
       <c r="E109">
-        <v>0.025</v>
+        <v>0.01</v>
       </c>
       <c r="F109">
         <v>0</v>
@@ -5102,7 +5102,7 @@
         <v>0</v>
       </c>
       <c r="J109">
-        <v>0.032</v>
+        <v>0.013</v>
       </c>
       <c r="S109" t="s">
         <v>127</v>
@@ -5113,10 +5113,10 @@
     </row>
     <row r="110" spans="1:20">
       <c r="A110" s="2">
-        <v>46076</v>
+        <v>46114</v>
       </c>
       <c r="B110">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="C110">
         <v>0</v>
@@ -5125,7 +5125,7 @@
         <v>0</v>
       </c>
       <c r="E110">
-        <v>0.022</v>
+        <v>0</v>
       </c>
       <c r="F110">
         <v>0</v>
@@ -5140,7 +5140,7 @@
         <v>0</v>
       </c>
       <c r="J110">
-        <v>0.032</v>
+        <v>0.013</v>
       </c>
       <c r="S110" t="s">
         <v>128</v>
@@ -5151,10 +5151,10 @@
     </row>
     <row r="111" spans="1:20">
       <c r="A111" s="2">
-        <v>46076</v>
+        <v>46114</v>
       </c>
       <c r="B111">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="C111">
         <v>0</v>
@@ -5163,7 +5163,7 @@
         <v>0</v>
       </c>
       <c r="E111">
-        <v>0.021</v>
+        <v>0</v>
       </c>
       <c r="F111">
         <v>0</v>
@@ -5178,7 +5178,7 @@
         <v>0</v>
       </c>
       <c r="J111">
-        <v>0.032</v>
+        <v>0.013</v>
       </c>
       <c r="S111" t="s">
         <v>129</v>
@@ -5189,10 +5189,10 @@
     </row>
     <row r="112" spans="1:20">
       <c r="A112" s="2">
-        <v>46076</v>
+        <v>46115</v>
       </c>
       <c r="B112">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C112">
         <v>0</v>
@@ -5201,7 +5201,7 @@
         <v>0</v>
       </c>
       <c r="E112">
-        <v>0.016</v>
+        <v>0</v>
       </c>
       <c r="F112">
         <v>0</v>
@@ -5216,7 +5216,7 @@
         <v>0</v>
       </c>
       <c r="J112">
-        <v>0.032</v>
+        <v>0.014</v>
       </c>
       <c r="S112" t="s">
         <v>130</v>
@@ -5227,10 +5227,10 @@
     </row>
     <row r="113" spans="1:20">
       <c r="A113" s="2">
-        <v>46076</v>
+        <v>46115</v>
       </c>
       <c r="B113">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C113">
         <v>0</v>
@@ -5239,7 +5239,7 @@
         <v>0</v>
       </c>
       <c r="E113">
-        <v>0.039</v>
+        <v>0</v>
       </c>
       <c r="F113">
         <v>0</v>
@@ -5265,34 +5265,34 @@
     </row>
     <row r="114" spans="1:20">
       <c r="A114" s="2">
-        <v>46076</v>
+        <v>46115</v>
       </c>
       <c r="B114">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C114">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="D114">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="E114">
-        <v>0.015</v>
+        <v>0</v>
       </c>
       <c r="F114">
-        <v>0.098</v>
+        <v>0</v>
       </c>
       <c r="G114">
-        <v>0.073</v>
+        <v>0</v>
       </c>
       <c r="H114">
-        <v>0.043</v>
+        <v>0</v>
       </c>
       <c r="I114">
-        <v>0.034</v>
+        <v>0</v>
       </c>
       <c r="J114">
-        <v>0.051</v>
+        <v>0.032</v>
       </c>
       <c r="S114" t="s">
         <v>132</v>
@@ -5303,34 +5303,34 @@
     </row>
     <row r="115" spans="1:20">
       <c r="A115" s="2">
-        <v>46076</v>
+        <v>46115</v>
       </c>
       <c r="B115">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C115">
-        <v>0.107</v>
+        <v>0</v>
       </c>
       <c r="D115">
-        <v>0.149</v>
+        <v>0</v>
       </c>
       <c r="E115">
-        <v>0.237</v>
+        <v>0</v>
       </c>
       <c r="F115">
-        <v>0.435</v>
+        <v>0</v>
       </c>
       <c r="G115">
-        <v>0.34</v>
+        <v>0</v>
       </c>
       <c r="H115">
-        <v>0.354</v>
+        <v>0</v>
       </c>
       <c r="I115">
-        <v>0.178</v>
+        <v>0</v>
       </c>
       <c r="J115">
-        <v>0.08799999999999999</v>
+        <v>0.032</v>
       </c>
       <c r="S115" t="s">
         <v>133</v>
@@ -5341,34 +5341,34 @@
     </row>
     <row r="116" spans="1:20">
       <c r="A116" s="2">
-        <v>46076</v>
+        <v>46115</v>
       </c>
       <c r="B116">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C116">
-        <v>0.273</v>
+        <v>0</v>
       </c>
       <c r="D116">
-        <v>0.384</v>
+        <v>0</v>
       </c>
       <c r="E116">
-        <v>0.584</v>
+        <v>0</v>
       </c>
       <c r="F116">
-        <v>0.64</v>
+        <v>0</v>
       </c>
       <c r="G116">
-        <v>0.783</v>
+        <v>0</v>
       </c>
       <c r="H116">
-        <v>0.72</v>
+        <v>0</v>
       </c>
       <c r="I116">
-        <v>0.402</v>
+        <v>0</v>
       </c>
       <c r="J116">
-        <v>0.336</v>
+        <v>0.032</v>
       </c>
       <c r="S116" t="s">
         <v>134</v>
@@ -5379,34 +5379,34 @@
     </row>
     <row r="117" spans="1:20">
       <c r="A117" s="2">
-        <v>46076</v>
+        <v>46115</v>
       </c>
       <c r="B117">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C117">
-        <v>0.39</v>
+        <v>0</v>
       </c>
       <c r="D117">
-        <v>0.462</v>
+        <v>0</v>
       </c>
       <c r="E117">
-        <v>0.847</v>
+        <v>0</v>
       </c>
       <c r="F117">
-        <v>0.623</v>
+        <v>0</v>
       </c>
       <c r="G117">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="H117">
-        <v>0.949</v>
+        <v>0</v>
       </c>
       <c r="I117">
-        <v>0.52</v>
+        <v>0</v>
       </c>
       <c r="J117">
-        <v>0.462</v>
+        <v>0.032</v>
       </c>
       <c r="S117" t="s">
         <v>135</v>
@@ -5417,34 +5417,34 @@
     </row>
     <row r="118" spans="1:20">
       <c r="A118" s="2">
-        <v>46076</v>
+        <v>46115</v>
       </c>
       <c r="B118">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C118">
-        <v>0.485</v>
+        <v>0</v>
       </c>
       <c r="D118">
-        <v>0.54</v>
+        <v>0</v>
       </c>
       <c r="E118">
-        <v>0.875</v>
+        <v>0</v>
       </c>
       <c r="F118">
-        <v>1.601</v>
+        <v>0</v>
       </c>
       <c r="G118">
-        <v>1.516</v>
+        <v>0</v>
       </c>
       <c r="H118">
-        <v>1.121</v>
+        <v>0</v>
       </c>
       <c r="I118">
-        <v>0.673</v>
+        <v>0</v>
       </c>
       <c r="J118">
-        <v>0.459</v>
+        <v>0.032</v>
       </c>
       <c r="S118" t="s">
         <v>136</v>
@@ -5455,34 +5455,34 @@
     </row>
     <row r="119" spans="1:20">
       <c r="A119" s="2">
-        <v>46076</v>
+        <v>46115</v>
       </c>
       <c r="B119">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C119">
-        <v>0.49</v>
+        <v>0.032</v>
       </c>
       <c r="D119">
-        <v>0.595</v>
+        <v>0.055</v>
       </c>
       <c r="E119">
-        <v>0.797</v>
+        <v>0.044</v>
       </c>
       <c r="F119">
-        <v>1.607</v>
+        <v>0.066</v>
       </c>
       <c r="G119">
-        <v>1.886</v>
+        <v>0.026</v>
       </c>
       <c r="H119">
-        <v>1.166</v>
+        <v>0.016</v>
       </c>
       <c r="I119">
-        <v>0.789</v>
+        <v>0.021</v>
       </c>
       <c r="J119">
-        <v>0.459</v>
+        <v>0.051</v>
       </c>
       <c r="S119" t="s">
         <v>137</v>
@@ -5493,34 +5493,34 @@
     </row>
     <row r="120" spans="1:20">
       <c r="A120" s="2">
-        <v>46076</v>
+        <v>46115</v>
       </c>
       <c r="B120">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C120">
-        <v>0.48</v>
+        <v>0.431</v>
       </c>
       <c r="D120">
-        <v>0.452</v>
+        <v>0.635</v>
       </c>
       <c r="E120">
-        <v>0.847</v>
+        <v>0.418</v>
       </c>
       <c r="F120">
-        <v>1.599</v>
+        <v>0.29</v>
       </c>
       <c r="G120">
-        <v>1.83</v>
+        <v>0.204</v>
       </c>
       <c r="H120">
-        <v>1.176</v>
+        <v>0.145</v>
       </c>
       <c r="I120">
-        <v>0.648</v>
+        <v>0.15</v>
       </c>
       <c r="J120">
-        <v>0.337</v>
+        <v>0.189</v>
       </c>
       <c r="S120" t="s">
         <v>138</v>
@@ -5531,34 +5531,34 @@
     </row>
     <row r="121" spans="1:20">
       <c r="A121" s="2">
-        <v>46076</v>
+        <v>46115</v>
       </c>
       <c r="B121">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C121">
-        <v>0.29</v>
+        <v>0.89</v>
       </c>
       <c r="D121">
-        <v>0.39</v>
+        <v>1.314</v>
       </c>
       <c r="E121">
-        <v>0.893</v>
+        <v>1.305</v>
       </c>
       <c r="F121">
-        <v>1.28</v>
+        <v>0.388</v>
       </c>
       <c r="G121">
-        <v>1.491</v>
+        <v>0.263</v>
       </c>
       <c r="H121">
-        <v>0.981</v>
+        <v>0.349</v>
       </c>
       <c r="I121">
-        <v>0.484</v>
+        <v>0.328</v>
       </c>
       <c r="J121">
-        <v>0.28</v>
+        <v>0.468</v>
       </c>
       <c r="S121" t="s">
         <v>139</v>
@@ -5569,34 +5569,34 @@
     </row>
     <row r="122" spans="1:20">
       <c r="A122" s="2">
-        <v>46076</v>
+        <v>46115</v>
       </c>
       <c r="B122">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C122">
-        <v>0.2</v>
+        <v>1.208</v>
       </c>
       <c r="D122">
-        <v>0.266</v>
+        <v>2.155</v>
       </c>
       <c r="E122">
-        <v>0.634</v>
+        <v>2.148</v>
       </c>
       <c r="F122">
-        <v>0.319</v>
+        <v>0.581</v>
       </c>
       <c r="G122">
-        <v>0.718</v>
+        <v>0.347</v>
       </c>
       <c r="H122">
-        <v>0.714</v>
+        <v>0.637</v>
       </c>
       <c r="I122">
-        <v>0.251</v>
+        <v>0.465</v>
       </c>
       <c r="J122">
-        <v>0.198</v>
+        <v>0.781</v>
       </c>
       <c r="S122" t="s">
         <v>140</v>
@@ -5607,34 +5607,34 @@
     </row>
     <row r="123" spans="1:20">
       <c r="A123" s="2">
-        <v>46076</v>
+        <v>46115</v>
       </c>
       <c r="B123">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C123">
-        <v>0.106</v>
+        <v>1.685</v>
       </c>
       <c r="D123">
-        <v>0.139</v>
+        <v>2.503</v>
       </c>
       <c r="E123">
-        <v>0.395</v>
+        <v>2.852</v>
       </c>
       <c r="F123">
-        <v>0.185</v>
+        <v>0.438</v>
       </c>
       <c r="G123">
-        <v>0.242</v>
+        <v>0.339</v>
       </c>
       <c r="H123">
-        <v>0.332</v>
+        <v>0.67</v>
       </c>
       <c r="I123">
-        <v>0.098</v>
+        <v>0.612</v>
       </c>
       <c r="J123">
-        <v>0.037</v>
+        <v>0.834</v>
       </c>
       <c r="S123" t="s">
         <v>141</v>
@@ -5645,34 +5645,34 @@
     </row>
     <row r="124" spans="1:20">
       <c r="A124" s="2">
-        <v>46076</v>
+        <v>46115</v>
       </c>
       <c r="B124">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C124">
-        <v>0.011</v>
+        <v>1.947</v>
       </c>
       <c r="D124">
-        <v>0.019</v>
+        <v>2.603</v>
       </c>
       <c r="E124">
-        <v>0.061</v>
+        <v>3.168</v>
       </c>
       <c r="F124">
-        <v>0.022</v>
+        <v>0.43</v>
       </c>
       <c r="G124">
-        <v>0.038</v>
+        <v>0.432</v>
       </c>
       <c r="H124">
-        <v>0.043</v>
+        <v>0.702</v>
       </c>
       <c r="I124">
-        <v>0</v>
+        <v>0.627</v>
       </c>
       <c r="J124">
-        <v>0.026</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="S124" t="s">
         <v>142</v>
@@ -5683,34 +5683,34 @@
     </row>
     <row r="125" spans="1:20">
       <c r="A125" s="2">
-        <v>46076</v>
+        <v>46115</v>
       </c>
       <c r="B125">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C125">
-        <v>0</v>
+        <v>1.922</v>
       </c>
       <c r="D125">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="E125">
-        <v>0</v>
+        <v>3.711</v>
       </c>
       <c r="F125">
-        <v>0</v>
+        <v>0.438</v>
       </c>
       <c r="G125">
-        <v>0</v>
+        <v>0.436</v>
       </c>
       <c r="H125">
-        <v>0</v>
+        <v>0.702</v>
       </c>
       <c r="I125">
-        <v>0</v>
+        <v>0.724</v>
       </c>
       <c r="J125">
-        <v>0.013</v>
+        <v>0.866</v>
       </c>
       <c r="S125" t="s">
         <v>143</v>
@@ -5721,34 +5721,34 @@
     </row>
     <row r="126" spans="1:20">
       <c r="A126" s="2">
-        <v>46076</v>
+        <v>46115</v>
       </c>
       <c r="B126">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C126">
-        <v>0</v>
+        <v>1.819</v>
       </c>
       <c r="D126">
-        <v>0</v>
+        <v>2.449</v>
       </c>
       <c r="E126">
-        <v>0</v>
+        <v>3.664</v>
       </c>
       <c r="F126">
-        <v>0</v>
+        <v>0.465</v>
       </c>
       <c r="G126">
-        <v>0</v>
+        <v>0.648</v>
       </c>
       <c r="H126">
-        <v>0</v>
+        <v>0.702</v>
       </c>
       <c r="I126">
-        <v>0</v>
+        <v>0.698</v>
       </c>
       <c r="J126">
-        <v>0.013</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="S126" t="s">
         <v>144</v>
@@ -5759,34 +5759,34 @@
     </row>
     <row r="127" spans="1:20">
       <c r="A127" s="2">
-        <v>46076</v>
+        <v>46115</v>
       </c>
       <c r="B127">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C127">
-        <v>0</v>
+        <v>1.566</v>
       </c>
       <c r="D127">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="E127">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="F127">
-        <v>0</v>
+        <v>0.462</v>
       </c>
       <c r="G127">
-        <v>0</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="H127">
-        <v>0</v>
+        <v>0.678</v>
       </c>
       <c r="I127">
-        <v>0</v>
+        <v>0.612</v>
       </c>
       <c r="J127">
-        <v>0.013</v>
+        <v>0.733</v>
       </c>
       <c r="S127" t="s">
         <v>145</v>
@@ -5797,34 +5797,34 @@
     </row>
     <row r="128" spans="1:20">
       <c r="A128" s="2">
-        <v>46076</v>
+        <v>46115</v>
       </c>
       <c r="B128">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C128">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="D128">
-        <v>0</v>
+        <v>1.523</v>
       </c>
       <c r="E128">
-        <v>0</v>
+        <v>2.784</v>
       </c>
       <c r="F128">
-        <v>0</v>
+        <v>0.418</v>
       </c>
       <c r="G128">
-        <v>0</v>
+        <v>0.477</v>
       </c>
       <c r="H128">
-        <v>0</v>
+        <v>0.645</v>
       </c>
       <c r="I128">
-        <v>0</v>
+        <v>0.391</v>
       </c>
       <c r="J128">
-        <v>0.013</v>
+        <v>0.488</v>
       </c>
       <c r="S128" t="s">
         <v>146</v>
@@ -5835,34 +5835,34 @@
     </row>
     <row r="129" spans="1:20">
       <c r="A129" s="2">
-        <v>46076</v>
+        <v>46115</v>
       </c>
       <c r="B129">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C129">
-        <v>0</v>
+        <v>0.788</v>
       </c>
       <c r="D129">
-        <v>0</v>
+        <v>0.923</v>
       </c>
       <c r="E129">
-        <v>0</v>
+        <v>1.623</v>
       </c>
       <c r="F129">
-        <v>0</v>
+        <v>0.189</v>
       </c>
       <c r="G129">
-        <v>0</v>
+        <v>0.195</v>
       </c>
       <c r="H129">
-        <v>0</v>
+        <v>0.334</v>
       </c>
       <c r="I129">
-        <v>0</v>
+        <v>0.193</v>
       </c>
       <c r="J129">
-        <v>0.013</v>
+        <v>0.263</v>
       </c>
       <c r="S129" t="s">
         <v>147</v>
@@ -5873,34 +5873,34 @@
     </row>
     <row r="130" spans="1:20">
       <c r="A130" s="2">
-        <v>46077</v>
+        <v>46115</v>
       </c>
       <c r="B130">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="C130">
-        <v>0</v>
+        <v>0.29</v>
       </c>
       <c r="D130">
-        <v>0</v>
+        <v>0.344</v>
       </c>
       <c r="E130">
-        <v>0</v>
+        <v>0.579</v>
       </c>
       <c r="F130">
-        <v>0</v>
+        <v>0.075</v>
       </c>
       <c r="G130">
-        <v>0</v>
+        <v>0.092</v>
       </c>
       <c r="H130">
-        <v>0</v>
+        <v>0.145</v>
       </c>
       <c r="I130">
-        <v>0</v>
+        <v>0.064</v>
       </c>
       <c r="J130">
-        <v>0.014</v>
+        <v>0.11</v>
       </c>
       <c r="S130" t="s">
         <v>148</v>
@@ -5911,22 +5911,22 @@
     </row>
     <row r="131" spans="1:20">
       <c r="A131" s="2">
-        <v>46077</v>
+        <v>46115</v>
       </c>
       <c r="B131">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="C131">
-        <v>0</v>
+        <v>0.026</v>
       </c>
       <c r="D131">
-        <v>0</v>
+        <v>0.023</v>
       </c>
       <c r="E131">
-        <v>0</v>
+        <v>0.064</v>
       </c>
       <c r="F131">
-        <v>0</v>
+        <v>0.012</v>
       </c>
       <c r="G131">
         <v>0</v>
@@ -5938,7 +5938,7 @@
         <v>0</v>
       </c>
       <c r="J131">
-        <v>0.014</v>
+        <v>0.019</v>
       </c>
       <c r="S131" t="s">
         <v>149</v>
@@ -5949,10 +5949,10 @@
     </row>
     <row r="132" spans="1:20">
       <c r="A132" s="2">
-        <v>46077</v>
+        <v>46115</v>
       </c>
       <c r="B132">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="C132">
         <v>0</v>
@@ -5976,7 +5976,7 @@
         <v>0</v>
       </c>
       <c r="J132">
-        <v>0.014</v>
+        <v>0.013</v>
       </c>
       <c r="S132" t="s">
         <v>150</v>
@@ -5987,10 +5987,10 @@
     </row>
     <row r="133" spans="1:20">
       <c r="A133" s="2">
-        <v>46077</v>
+        <v>46115</v>
       </c>
       <c r="B133">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="C133">
         <v>0</v>
@@ -6014,7 +6014,7 @@
         <v>0</v>
       </c>
       <c r="J133">
-        <v>0.014</v>
+        <v>0.013</v>
       </c>
       <c r="S133" t="s">
         <v>151</v>
@@ -6025,10 +6025,10 @@
     </row>
     <row r="134" spans="1:20">
       <c r="A134" s="2">
-        <v>46077</v>
+        <v>46115</v>
       </c>
       <c r="B134">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="C134">
         <v>0</v>
@@ -6052,7 +6052,7 @@
         <v>0</v>
       </c>
       <c r="J134">
-        <v>0.014</v>
+        <v>0.013</v>
       </c>
       <c r="S134" t="s">
         <v>152</v>
@@ -6063,10 +6063,10 @@
     </row>
     <row r="135" spans="1:20">
       <c r="A135" s="2">
-        <v>46077</v>
+        <v>46115</v>
       </c>
       <c r="B135">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="C135">
         <v>0</v>
@@ -6090,7 +6090,7 @@
         <v>0</v>
       </c>
       <c r="J135">
-        <v>0.014</v>
+        <v>0.013</v>
       </c>
       <c r="S135" t="s">
         <v>153</v>
@@ -6101,10 +6101,10 @@
     </row>
     <row r="136" spans="1:20">
       <c r="A136" s="2">
-        <v>46077</v>
+        <v>46116</v>
       </c>
       <c r="B136">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C136">
         <v>0</v>
@@ -6139,10 +6139,10 @@
     </row>
     <row r="137" spans="1:20">
       <c r="A137" s="2">
-        <v>46077</v>
+        <v>46116</v>
       </c>
       <c r="B137">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C137">
         <v>0</v>
@@ -6177,34 +6177,34 @@
     </row>
     <row r="138" spans="1:20">
       <c r="A138" s="2">
-        <v>46077</v>
+        <v>46116</v>
       </c>
       <c r="B138">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C138">
-        <v>0.015</v>
+        <v>0</v>
       </c>
       <c r="D138">
-        <v>0.012</v>
+        <v>0</v>
       </c>
       <c r="E138">
-        <v>0.015</v>
+        <v>0</v>
       </c>
       <c r="F138">
-        <v>0.105</v>
+        <v>0</v>
       </c>
       <c r="G138">
-        <v>0.073</v>
+        <v>0</v>
       </c>
       <c r="H138">
-        <v>0.053</v>
+        <v>0</v>
       </c>
       <c r="I138">
-        <v>0.042</v>
+        <v>0</v>
       </c>
       <c r="J138">
-        <v>0.038</v>
+        <v>0.014</v>
       </c>
       <c r="S138" t="s">
         <v>156</v>
@@ -6215,34 +6215,34 @@
     </row>
     <row r="139" spans="1:20">
       <c r="A139" s="2">
-        <v>46077</v>
+        <v>46116</v>
       </c>
       <c r="B139">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C139">
-        <v>0.208</v>
+        <v>0</v>
       </c>
       <c r="D139">
-        <v>0.219</v>
+        <v>0</v>
       </c>
       <c r="E139">
-        <v>0.267</v>
+        <v>0</v>
       </c>
       <c r="F139">
-        <v>0.468</v>
+        <v>0</v>
       </c>
       <c r="G139">
-        <v>0.357</v>
+        <v>0</v>
       </c>
       <c r="H139">
-        <v>0.341</v>
+        <v>0</v>
       </c>
       <c r="I139">
-        <v>0.213</v>
+        <v>0</v>
       </c>
       <c r="J139">
-        <v>0.15</v>
+        <v>0.014</v>
       </c>
       <c r="S139" t="s">
         <v>157</v>
@@ -6253,34 +6253,34 @@
     </row>
     <row r="140" spans="1:20">
       <c r="A140" s="2">
-        <v>46077</v>
+        <v>46116</v>
       </c>
       <c r="B140">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C140">
-        <v>0.448</v>
+        <v>0</v>
       </c>
       <c r="D140">
-        <v>0.601</v>
+        <v>0</v>
       </c>
       <c r="E140">
-        <v>0.708</v>
+        <v>0</v>
       </c>
       <c r="F140">
-        <v>0.708</v>
+        <v>0</v>
       </c>
       <c r="G140">
-        <v>0.74</v>
+        <v>0</v>
       </c>
       <c r="H140">
-        <v>0.777</v>
+        <v>0</v>
       </c>
       <c r="I140">
-        <v>0.474</v>
+        <v>0</v>
       </c>
       <c r="J140">
-        <v>0.334</v>
+        <v>0.014</v>
       </c>
       <c r="S140" t="s">
         <v>158</v>
@@ -6291,34 +6291,34 @@
     </row>
     <row r="141" spans="1:20">
       <c r="A141" s="2">
-        <v>46077</v>
+        <v>46116</v>
       </c>
       <c r="B141">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C141">
-        <v>0.6909999999999999</v>
+        <v>0</v>
       </c>
       <c r="D141">
-        <v>0.953</v>
+        <v>0</v>
       </c>
       <c r="E141">
-        <v>0.971</v>
+        <v>0</v>
       </c>
       <c r="F141">
-        <v>0.628</v>
+        <v>0</v>
       </c>
       <c r="G141">
-        <v>1.383</v>
+        <v>0</v>
       </c>
       <c r="H141">
-        <v>0.949</v>
+        <v>0</v>
       </c>
       <c r="I141">
-        <v>0.649</v>
+        <v>0</v>
       </c>
       <c r="J141">
-        <v>0.449</v>
+        <v>0.014</v>
       </c>
       <c r="S141" t="s">
         <v>159</v>
@@ -6329,34 +6329,34 @@
     </row>
     <row r="142" spans="1:20">
       <c r="A142" s="2">
-        <v>46077</v>
+        <v>46116</v>
       </c>
       <c r="B142">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C142">
-        <v>0.9399999999999999</v>
+        <v>0</v>
       </c>
       <c r="D142">
-        <v>1.127</v>
+        <v>0</v>
       </c>
       <c r="E142">
-        <v>1.369</v>
+        <v>0</v>
       </c>
       <c r="F142">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="G142">
-        <v>1.409</v>
+        <v>0</v>
       </c>
       <c r="H142">
-        <v>1.145</v>
+        <v>0</v>
       </c>
       <c r="I142">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="J142">
-        <v>0.538</v>
+        <v>0.014</v>
       </c>
       <c r="S142" t="s">
         <v>160</v>
@@ -6367,34 +6367,34 @@
     </row>
     <row r="143" spans="1:20">
       <c r="A143" s="2">
-        <v>46077</v>
+        <v>46116</v>
       </c>
       <c r="B143">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C143">
-        <v>1.206</v>
+        <v>0.036</v>
       </c>
       <c r="D143">
-        <v>1.36</v>
+        <v>0.035</v>
       </c>
       <c r="E143">
-        <v>1.467</v>
+        <v>0.055</v>
       </c>
       <c r="F143">
-        <v>1.534</v>
+        <v>0.128</v>
       </c>
       <c r="G143">
-        <v>1.536</v>
+        <v>0.065</v>
       </c>
       <c r="H143">
-        <v>1.142</v>
+        <v>0.041</v>
       </c>
       <c r="I143">
-        <v>1.01</v>
+        <v>0.064</v>
       </c>
       <c r="J143">
-        <v>0.525</v>
+        <v>0.038</v>
       </c>
       <c r="S143" t="s">
         <v>161</v>
@@ -6405,34 +6405,34 @@
     </row>
     <row r="144" spans="1:20">
       <c r="A144" s="2">
-        <v>46077</v>
+        <v>46116</v>
       </c>
       <c r="B144">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C144">
-        <v>1.053</v>
+        <v>0.468</v>
       </c>
       <c r="D144">
-        <v>1.543</v>
+        <v>0.405</v>
       </c>
       <c r="E144">
-        <v>1.447</v>
+        <v>0.597</v>
       </c>
       <c r="F144">
-        <v>1.356</v>
+        <v>0.642</v>
       </c>
       <c r="G144">
-        <v>1.346</v>
+        <v>0.307</v>
       </c>
       <c r="H144">
-        <v>1.126</v>
+        <v>0.221</v>
       </c>
       <c r="I144">
-        <v>0.724</v>
+        <v>0.295</v>
       </c>
       <c r="J144">
-        <v>0.397</v>
+        <v>0.281</v>
       </c>
       <c r="S144" t="s">
         <v>162</v>
@@ -6443,34 +6443,34 @@
     </row>
     <row r="145" spans="1:20">
       <c r="A145" s="2">
-        <v>46077</v>
+        <v>46116</v>
       </c>
       <c r="B145">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C145">
-        <v>0.918</v>
+        <v>0.915</v>
       </c>
       <c r="D145">
-        <v>1.303</v>
+        <v>0.946</v>
       </c>
       <c r="E145">
-        <v>1.236</v>
+        <v>1.612</v>
       </c>
       <c r="F145">
-        <v>0.589</v>
+        <v>1.492</v>
       </c>
       <c r="G145">
-        <v>1.144</v>
+        <v>0.644</v>
       </c>
       <c r="H145">
-        <v>1.001</v>
+        <v>0.716</v>
       </c>
       <c r="I145">
-        <v>0.5600000000000001</v>
+        <v>0.701</v>
       </c>
       <c r="J145">
-        <v>0.327</v>
+        <v>0.606</v>
       </c>
       <c r="S145" t="s">
         <v>163</v>
@@ -6481,34 +6481,34 @@
     </row>
     <row r="146" spans="1:20">
       <c r="A146" s="2">
-        <v>46077</v>
+        <v>46116</v>
       </c>
       <c r="B146">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C146">
-        <v>0.723</v>
+        <v>1.451</v>
       </c>
       <c r="D146">
-        <v>0.902</v>
+        <v>1.602</v>
       </c>
       <c r="E146">
-        <v>0.948</v>
+        <v>2.262</v>
       </c>
       <c r="F146">
-        <v>0.604</v>
+        <v>2.255</v>
       </c>
       <c r="G146">
-        <v>0.783</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="H146">
-        <v>0.716</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="I146">
-        <v>0.369</v>
+        <v>0.882</v>
       </c>
       <c r="J146">
-        <v>0.269</v>
+        <v>0.872</v>
       </c>
       <c r="S146" t="s">
         <v>164</v>
@@ -6519,34 +6519,34 @@
     </row>
     <row r="147" spans="1:20">
       <c r="A147" s="2">
-        <v>46077</v>
+        <v>46116</v>
       </c>
       <c r="B147">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C147">
-        <v>0.248</v>
+        <v>1.853</v>
       </c>
       <c r="D147">
-        <v>0.447</v>
+        <v>2.139</v>
       </c>
       <c r="E147">
-        <v>0.464</v>
+        <v>2.945</v>
       </c>
       <c r="F147">
-        <v>0.194</v>
+        <v>2.502</v>
       </c>
       <c r="G147">
-        <v>0.248</v>
+        <v>1.279</v>
       </c>
       <c r="H147">
-        <v>0.327</v>
+        <v>1.08</v>
       </c>
       <c r="I147">
-        <v>0.116</v>
+        <v>0.919</v>
       </c>
       <c r="J147">
-        <v>0.136</v>
+        <v>0.922</v>
       </c>
       <c r="S147" t="s">
         <v>165</v>
@@ -6557,34 +6557,34 @@
     </row>
     <row r="148" spans="1:20">
       <c r="A148" s="2">
-        <v>46077</v>
+        <v>46116</v>
       </c>
       <c r="B148">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C148">
-        <v>0.037</v>
+        <v>1.975</v>
       </c>
       <c r="D148">
-        <v>0.053</v>
+        <v>2.466</v>
       </c>
       <c r="E148">
-        <v>0.081</v>
+        <v>3.378</v>
       </c>
       <c r="F148">
-        <v>0.024</v>
+        <v>2.718</v>
       </c>
       <c r="G148">
-        <v>0.038</v>
+        <v>1.538</v>
       </c>
       <c r="H148">
-        <v>0.051</v>
+        <v>1.315</v>
       </c>
       <c r="I148">
-        <v>0</v>
+        <v>0.909</v>
       </c>
       <c r="J148">
-        <v>0.045</v>
+        <v>1.103</v>
       </c>
       <c r="S148" t="s">
         <v>166</v>
@@ -6595,34 +6595,34 @@
     </row>
     <row r="149" spans="1:20">
       <c r="A149" s="2">
-        <v>46077</v>
+        <v>46116</v>
       </c>
       <c r="B149">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C149">
-        <v>0</v>
+        <v>1.965</v>
       </c>
       <c r="D149">
-        <v>0</v>
+        <v>2.487</v>
       </c>
       <c r="E149">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="F149">
-        <v>0</v>
+        <v>2.785</v>
       </c>
       <c r="G149">
-        <v>0</v>
+        <v>1.497</v>
       </c>
       <c r="H149">
-        <v>0</v>
+        <v>1.462</v>
       </c>
       <c r="I149">
-        <v>0</v>
+        <v>0.773</v>
       </c>
       <c r="J149">
-        <v>0.031</v>
+        <v>1.088</v>
       </c>
       <c r="S149" t="s">
         <v>167</v>
@@ -6633,34 +6633,34 @@
     </row>
     <row r="150" spans="1:20">
       <c r="A150" s="2">
-        <v>46077</v>
+        <v>46116</v>
       </c>
       <c r="B150">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C150">
-        <v>0</v>
+        <v>1.961</v>
       </c>
       <c r="D150">
-        <v>0</v>
+        <v>2.477</v>
       </c>
       <c r="E150">
-        <v>0</v>
+        <v>3.399</v>
       </c>
       <c r="F150">
-        <v>0</v>
+        <v>2.569</v>
       </c>
       <c r="G150">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="H150">
-        <v>0</v>
+        <v>1.223</v>
       </c>
       <c r="I150">
-        <v>0</v>
+        <v>0.716</v>
       </c>
       <c r="J150">
-        <v>0.031</v>
+        <v>0.949</v>
       </c>
       <c r="S150" t="s">
         <v>168</v>
@@ -6671,34 +6671,34 @@
     </row>
     <row r="151" spans="1:20">
       <c r="A151" s="2">
-        <v>46077</v>
+        <v>46116</v>
       </c>
       <c r="B151">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C151">
-        <v>0</v>
+        <v>1.809</v>
       </c>
       <c r="D151">
-        <v>0</v>
+        <v>2.214</v>
       </c>
       <c r="E151">
-        <v>0</v>
+        <v>2.828</v>
       </c>
       <c r="F151">
-        <v>0</v>
+        <v>2.274</v>
       </c>
       <c r="G151">
-        <v>0</v>
+        <v>1.407</v>
       </c>
       <c r="H151">
-        <v>0</v>
+        <v>1.133</v>
       </c>
       <c r="I151">
-        <v>0</v>
+        <v>0.76</v>
       </c>
       <c r="J151">
-        <v>0.031</v>
+        <v>0.852</v>
       </c>
       <c r="S151" t="s">
         <v>169</v>
@@ -6709,34 +6709,34 @@
     </row>
     <row r="152" spans="1:20">
       <c r="A152" s="2">
-        <v>46077</v>
+        <v>46116</v>
       </c>
       <c r="B152">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C152">
-        <v>0</v>
+        <v>1.395</v>
       </c>
       <c r="D152">
-        <v>0</v>
+        <v>1.564</v>
       </c>
       <c r="E152">
-        <v>0</v>
+        <v>2.071</v>
       </c>
       <c r="F152">
-        <v>0</v>
+        <v>1.442</v>
       </c>
       <c r="G152">
-        <v>0</v>
+        <v>0.904</v>
       </c>
       <c r="H152">
-        <v>0</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="I152">
-        <v>0</v>
+        <v>0.572</v>
       </c>
       <c r="J152">
-        <v>0.031</v>
+        <v>0.728</v>
       </c>
       <c r="S152" t="s">
         <v>170</v>
@@ -6747,34 +6747,34 @@
     </row>
     <row r="153" spans="1:20">
       <c r="A153" s="2">
-        <v>46077</v>
+        <v>46116</v>
       </c>
       <c r="B153">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C153">
-        <v>0</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="D153">
-        <v>0</v>
+        <v>0.986</v>
       </c>
       <c r="E153">
-        <v>0.013</v>
+        <v>1.497</v>
       </c>
       <c r="F153">
-        <v>0</v>
+        <v>0.759</v>
       </c>
       <c r="G153">
-        <v>0</v>
+        <v>0.602</v>
       </c>
       <c r="H153">
-        <v>0</v>
+        <v>0.59</v>
       </c>
       <c r="I153">
-        <v>0</v>
+        <v>0.301</v>
       </c>
       <c r="J153">
-        <v>0.031</v>
+        <v>0.279</v>
       </c>
       <c r="S153" t="s">
         <v>171</v>
@@ -6785,34 +6785,34 @@
     </row>
     <row r="154" spans="1:20">
       <c r="A154" s="2">
-        <v>46078</v>
+        <v>46116</v>
       </c>
       <c r="B154">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="C154">
-        <v>0</v>
+        <v>0.285</v>
       </c>
       <c r="D154">
-        <v>0</v>
+        <v>0.392</v>
       </c>
       <c r="E154">
-        <v>0</v>
+        <v>0.586</v>
       </c>
       <c r="F154">
-        <v>0</v>
+        <v>0.164</v>
       </c>
       <c r="G154">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="H154">
-        <v>0</v>
+        <v>0.174</v>
       </c>
       <c r="I154">
-        <v>0</v>
+        <v>0.074</v>
       </c>
       <c r="J154">
-        <v>0.032</v>
+        <v>0.053</v>
       </c>
       <c r="S154" t="s">
         <v>172</v>
@@ -6823,34 +6823,34 @@
     </row>
     <row r="155" spans="1:20">
       <c r="A155" s="2">
-        <v>46078</v>
+        <v>46116</v>
       </c>
       <c r="B155">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="C155">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="D155">
-        <v>0</v>
+        <v>0.033</v>
       </c>
       <c r="E155">
-        <v>0.034</v>
+        <v>0.079</v>
       </c>
       <c r="F155">
-        <v>0</v>
+        <v>0.011</v>
       </c>
       <c r="G155">
-        <v>0</v>
+        <v>0.017</v>
       </c>
       <c r="H155">
-        <v>0</v>
+        <v>0.012</v>
       </c>
       <c r="I155">
         <v>0</v>
       </c>
       <c r="J155">
-        <v>0.032</v>
+        <v>0.019</v>
       </c>
       <c r="S155" t="s">
         <v>173</v>
@@ -6861,10 +6861,10 @@
     </row>
     <row r="156" spans="1:20">
       <c r="A156" s="2">
-        <v>46078</v>
+        <v>46116</v>
       </c>
       <c r="B156">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="C156">
         <v>0</v>
@@ -6873,7 +6873,7 @@
         <v>0</v>
       </c>
       <c r="E156">
-        <v>0.049</v>
+        <v>0</v>
       </c>
       <c r="F156">
         <v>0</v>
@@ -6888,7 +6888,7 @@
         <v>0</v>
       </c>
       <c r="J156">
-        <v>0.032</v>
+        <v>0.013</v>
       </c>
       <c r="S156" t="s">
         <v>174</v>
@@ -6899,10 +6899,10 @@
     </row>
     <row r="157" spans="1:20">
       <c r="A157" s="2">
-        <v>46078</v>
+        <v>46116</v>
       </c>
       <c r="B157">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="C157">
         <v>0</v>
@@ -6911,7 +6911,7 @@
         <v>0</v>
       </c>
       <c r="E157">
-        <v>0.028</v>
+        <v>0</v>
       </c>
       <c r="F157">
         <v>0</v>
@@ -6926,7 +6926,7 @@
         <v>0</v>
       </c>
       <c r="J157">
-        <v>0.032</v>
+        <v>0.013</v>
       </c>
       <c r="S157" t="s">
         <v>175</v>
@@ -6937,10 +6937,10 @@
     </row>
     <row r="158" spans="1:20">
       <c r="A158" s="2">
-        <v>46078</v>
+        <v>46116</v>
       </c>
       <c r="B158">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="C158">
         <v>0</v>
@@ -6949,7 +6949,7 @@
         <v>0</v>
       </c>
       <c r="E158">
-        <v>0.025</v>
+        <v>0</v>
       </c>
       <c r="F158">
         <v>0</v>
@@ -6964,7 +6964,7 @@
         <v>0</v>
       </c>
       <c r="J158">
-        <v>0.032</v>
+        <v>0.013</v>
       </c>
       <c r="S158" t="s">
         <v>176</v>
@@ -6975,10 +6975,10 @@
     </row>
     <row r="159" spans="1:20">
       <c r="A159" s="2">
-        <v>46078</v>
+        <v>46116</v>
       </c>
       <c r="B159">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="C159">
         <v>0</v>
@@ -6987,7 +6987,7 @@
         <v>0</v>
       </c>
       <c r="E159">
-        <v>0.021</v>
+        <v>0.018</v>
       </c>
       <c r="F159">
         <v>0</v>
@@ -7002,7 +7002,7 @@
         <v>0</v>
       </c>
       <c r="J159">
-        <v>0.032</v>
+        <v>0.013</v>
       </c>
       <c r="S159" t="s">
         <v>177</v>
@@ -7013,10 +7013,10 @@
     </row>
     <row r="160" spans="1:20">
       <c r="A160" s="2">
-        <v>46078</v>
+        <v>46117</v>
       </c>
       <c r="B160">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C160">
         <v>0</v>
@@ -7025,7 +7025,7 @@
         <v>0</v>
       </c>
       <c r="E160">
-        <v>0.026</v>
+        <v>0.02</v>
       </c>
       <c r="F160">
         <v>0</v>
@@ -7040,7 +7040,7 @@
         <v>0</v>
       </c>
       <c r="J160">
-        <v>0.032</v>
+        <v>0.014</v>
       </c>
       <c r="S160" t="s">
         <v>178</v>
@@ -7051,10 +7051,10 @@
     </row>
     <row r="161" spans="1:20">
       <c r="A161" s="2">
-        <v>46078</v>
+        <v>46117</v>
       </c>
       <c r="B161">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C161">
         <v>0</v>
@@ -7063,7 +7063,7 @@
         <v>0</v>
       </c>
       <c r="E161">
-        <v>0.026</v>
+        <v>0.013</v>
       </c>
       <c r="F161">
         <v>0</v>
@@ -7078,7 +7078,7 @@
         <v>0</v>
       </c>
       <c r="J161">
-        <v>0.032</v>
+        <v>0.014</v>
       </c>
       <c r="S161" t="s">
         <v>179</v>
@@ -7089,34 +7089,34 @@
     </row>
     <row r="162" spans="1:20">
       <c r="A162" s="2">
-        <v>46078</v>
+        <v>46117</v>
       </c>
       <c r="B162">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C162">
-        <v>0.027</v>
+        <v>0</v>
       </c>
       <c r="D162">
-        <v>0.036</v>
+        <v>0</v>
       </c>
       <c r="E162">
-        <v>0.146</v>
+        <v>0</v>
       </c>
       <c r="F162">
-        <v>0.192</v>
+        <v>0</v>
       </c>
       <c r="G162">
-        <v>0.115</v>
+        <v>0</v>
       </c>
       <c r="H162">
-        <v>0.063</v>
+        <v>0</v>
       </c>
       <c r="I162">
-        <v>0.058</v>
+        <v>0</v>
       </c>
       <c r="J162">
-        <v>0.051</v>
+        <v>0.014</v>
       </c>
       <c r="S162" t="s">
         <v>180</v>
@@ -7127,34 +7127,34 @@
     </row>
     <row r="163" spans="1:20">
       <c r="A163" s="2">
-        <v>46078</v>
+        <v>46117</v>
       </c>
       <c r="B163">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C163">
-        <v>0.426</v>
+        <v>0</v>
       </c>
       <c r="D163">
-        <v>0.455</v>
+        <v>0</v>
       </c>
       <c r="E163">
-        <v>0.574</v>
+        <v>0</v>
       </c>
       <c r="F163">
-        <v>0.645</v>
+        <v>0</v>
       </c>
       <c r="G163">
-        <v>0.387</v>
+        <v>0</v>
       </c>
       <c r="H163">
-        <v>0.465</v>
+        <v>0</v>
       </c>
       <c r="I163">
-        <v>0.264</v>
+        <v>0</v>
       </c>
       <c r="J163">
-        <v>0.35</v>
+        <v>0.014</v>
       </c>
       <c r="S163" t="s">
         <v>181</v>
@@ -7165,34 +7165,34 @@
     </row>
     <row r="164" spans="1:20">
       <c r="A164" s="2">
-        <v>46078</v>
+        <v>46117</v>
       </c>
       <c r="B164">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C164">
-        <v>1.082</v>
+        <v>0</v>
       </c>
       <c r="D164">
-        <v>1.225</v>
+        <v>0</v>
       </c>
       <c r="E164">
-        <v>1.303</v>
+        <v>0</v>
       </c>
       <c r="F164">
-        <v>1.112</v>
+        <v>0</v>
       </c>
       <c r="G164">
-        <v>1.396</v>
+        <v>0</v>
       </c>
       <c r="H164">
-        <v>0.734</v>
+        <v>0</v>
       </c>
       <c r="I164">
-        <v>0.5679999999999999</v>
+        <v>0</v>
       </c>
       <c r="J164">
-        <v>0.822</v>
+        <v>0.014</v>
       </c>
       <c r="S164" t="s">
         <v>182</v>
@@ -7203,34 +7203,34 @@
     </row>
     <row r="165" spans="1:20">
       <c r="A165" s="2">
-        <v>46078</v>
+        <v>46117</v>
       </c>
       <c r="B165">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C165">
-        <v>1.691</v>
+        <v>0</v>
       </c>
       <c r="D165">
-        <v>2.146</v>
+        <v>0</v>
       </c>
       <c r="E165">
-        <v>1.656</v>
+        <v>0</v>
       </c>
       <c r="F165">
-        <v>1.871</v>
+        <v>0</v>
       </c>
       <c r="G165">
-        <v>1.917</v>
+        <v>0</v>
       </c>
       <c r="H165">
-        <v>1.121</v>
+        <v>0</v>
       </c>
       <c r="I165">
-        <v>1.116</v>
+        <v>0</v>
       </c>
       <c r="J165">
-        <v>0.989</v>
+        <v>0.014</v>
       </c>
       <c r="S165" t="s">
         <v>183</v>
@@ -7241,34 +7241,34 @@
     </row>
     <row r="166" spans="1:20">
       <c r="A166" s="2">
-        <v>46078</v>
+        <v>46117</v>
       </c>
       <c r="B166">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C166">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="D166">
-        <v>2.627</v>
+        <v>0</v>
       </c>
       <c r="E166">
-        <v>2.861</v>
+        <v>0</v>
       </c>
       <c r="F166">
-        <v>1.814</v>
+        <v>0</v>
       </c>
       <c r="G166">
-        <v>2.125</v>
+        <v>0</v>
       </c>
       <c r="H166">
-        <v>1.244</v>
+        <v>0</v>
       </c>
       <c r="I166">
-        <v>1.332</v>
+        <v>0</v>
       </c>
       <c r="J166">
-        <v>1.288</v>
+        <v>0.014</v>
       </c>
       <c r="S166" t="s">
         <v>184</v>
@@ -7279,34 +7279,34 @@
     </row>
     <row r="167" spans="1:20">
       <c r="A167" s="2">
-        <v>46078</v>
+        <v>46117</v>
       </c>
       <c r="B167">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C167">
-        <v>2.459</v>
+        <v>0.037</v>
       </c>
       <c r="D167">
-        <v>2.885</v>
+        <v>0.036</v>
       </c>
       <c r="E167">
-        <v>3.092</v>
+        <v>0.102</v>
       </c>
       <c r="F167">
-        <v>1.735</v>
+        <v>0.301</v>
       </c>
       <c r="G167">
-        <v>2.2</v>
+        <v>0.113</v>
       </c>
       <c r="H167">
-        <v>1.233</v>
+        <v>0.106</v>
       </c>
       <c r="I167">
-        <v>1.332</v>
+        <v>0.064</v>
       </c>
       <c r="J167">
-        <v>1.273</v>
+        <v>0.038</v>
       </c>
       <c r="S167" t="s">
         <v>185</v>
@@ -7317,34 +7317,34 @@
     </row>
     <row r="168" spans="1:20">
       <c r="A168" s="2">
-        <v>46078</v>
+        <v>46117</v>
       </c>
       <c r="B168">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C168">
-        <v>2.531</v>
+        <v>0.375</v>
       </c>
       <c r="D168">
-        <v>2.974</v>
+        <v>0.409</v>
       </c>
       <c r="E168">
-        <v>3.157</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="F168">
-        <v>1.686</v>
+        <v>0.997</v>
       </c>
       <c r="G168">
-        <v>1.86</v>
+        <v>0.353</v>
       </c>
       <c r="H168">
-        <v>1.169</v>
+        <v>0.479</v>
       </c>
       <c r="I168">
-        <v>1.318</v>
+        <v>0.361</v>
       </c>
       <c r="J168">
-        <v>1.233</v>
+        <v>0.281</v>
       </c>
       <c r="S168" t="s">
         <v>186</v>
@@ -7355,34 +7355,34 @@
     </row>
     <row r="169" spans="1:20">
       <c r="A169" s="2">
-        <v>46078</v>
+        <v>46117</v>
       </c>
       <c r="B169">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C169">
-        <v>2.395</v>
+        <v>0.857</v>
       </c>
       <c r="D169">
-        <v>2.791</v>
+        <v>0.887</v>
       </c>
       <c r="E169">
-        <v>2.785</v>
+        <v>1.906</v>
       </c>
       <c r="F169">
-        <v>1.333</v>
+        <v>1.832</v>
       </c>
       <c r="G169">
-        <v>1.443</v>
+        <v>0.792</v>
       </c>
       <c r="H169">
-        <v>1.127</v>
+        <v>1.003</v>
       </c>
       <c r="I169">
-        <v>1.093</v>
+        <v>0.715</v>
       </c>
       <c r="J169">
-        <v>1.232</v>
+        <v>0.591</v>
       </c>
       <c r="S169" t="s">
         <v>187</v>
@@ -7393,34 +7393,34 @@
     </row>
     <row r="170" spans="1:20">
       <c r="A170" s="2">
-        <v>46078</v>
+        <v>46117</v>
       </c>
       <c r="B170">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C170">
-        <v>1.733</v>
+        <v>1.012</v>
       </c>
       <c r="D170">
-        <v>1.954</v>
+        <v>1.522</v>
       </c>
       <c r="E170">
-        <v>1.323</v>
+        <v>2.87</v>
       </c>
       <c r="F170">
-        <v>0.637</v>
+        <v>2.52</v>
       </c>
       <c r="G170">
-        <v>1.015</v>
+        <v>1.368</v>
       </c>
       <c r="H170">
-        <v>0.785</v>
+        <v>1.275</v>
       </c>
       <c r="I170">
-        <v>0.612</v>
+        <v>1.109</v>
       </c>
       <c r="J170">
-        <v>0.806</v>
+        <v>0.841</v>
       </c>
       <c r="S170" t="s">
         <v>188</v>

--- a/Forecast.xlsx
+++ b/Forecast.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="192">
   <si>
     <t>Data</t>
   </si>
@@ -76,517 +76,520 @@
     <t>Prediction_Motif</t>
   </si>
   <si>
+    <t>Prediction_Ferma</t>
+  </si>
+  <si>
     <t>Lookup</t>
   </si>
   <si>
     <t>Prediction_3D_Steel</t>
   </si>
   <si>
-    <t>21.04.202610</t>
-  </si>
-  <si>
-    <t>21.04.202611</t>
-  </si>
-  <si>
-    <t>21.04.202612</t>
-  </si>
-  <si>
-    <t>21.04.202613</t>
-  </si>
-  <si>
-    <t>21.04.202614</t>
-  </si>
-  <si>
-    <t>21.04.202615</t>
-  </si>
-  <si>
-    <t>21.04.202616</t>
-  </si>
-  <si>
-    <t>21.04.202617</t>
-  </si>
-  <si>
-    <t>21.04.202618</t>
-  </si>
-  <si>
-    <t>21.04.202619</t>
-  </si>
-  <si>
-    <t>21.04.202620</t>
-  </si>
-  <si>
-    <t>21.04.202621</t>
-  </si>
-  <si>
-    <t>21.04.202622</t>
-  </si>
-  <si>
-    <t>21.04.202623</t>
-  </si>
-  <si>
-    <t>21.04.202624</t>
-  </si>
-  <si>
-    <t>22.04.20261</t>
-  </si>
-  <si>
-    <t>22.04.20262</t>
-  </si>
-  <si>
-    <t>22.04.20263</t>
-  </si>
-  <si>
-    <t>22.04.20264</t>
-  </si>
-  <si>
-    <t>22.04.20265</t>
-  </si>
-  <si>
-    <t>22.04.20266</t>
-  </si>
-  <si>
-    <t>22.04.20267</t>
-  </si>
-  <si>
-    <t>22.04.20268</t>
-  </si>
-  <si>
-    <t>22.04.20269</t>
-  </si>
-  <si>
-    <t>22.04.202610</t>
-  </si>
-  <si>
-    <t>22.04.202611</t>
-  </si>
-  <si>
-    <t>22.04.202612</t>
-  </si>
-  <si>
-    <t>22.04.202613</t>
-  </si>
-  <si>
-    <t>22.04.202614</t>
-  </si>
-  <si>
-    <t>22.04.202615</t>
-  </si>
-  <si>
-    <t>22.04.202616</t>
-  </si>
-  <si>
-    <t>22.04.202617</t>
-  </si>
-  <si>
-    <t>22.04.202618</t>
-  </si>
-  <si>
-    <t>22.04.202619</t>
-  </si>
-  <si>
-    <t>22.04.202620</t>
-  </si>
-  <si>
-    <t>22.04.202621</t>
-  </si>
-  <si>
-    <t>22.04.202622</t>
-  </si>
-  <si>
-    <t>22.04.202623</t>
-  </si>
-  <si>
-    <t>22.04.202624</t>
-  </si>
-  <si>
-    <t>23.04.20261</t>
-  </si>
-  <si>
-    <t>23.04.20262</t>
-  </si>
-  <si>
-    <t>23.04.20263</t>
-  </si>
-  <si>
-    <t>23.04.20264</t>
-  </si>
-  <si>
-    <t>23.04.20265</t>
-  </si>
-  <si>
-    <t>23.04.20266</t>
-  </si>
-  <si>
-    <t>23.04.20267</t>
-  </si>
-  <si>
-    <t>23.04.20268</t>
-  </si>
-  <si>
-    <t>23.04.20269</t>
-  </si>
-  <si>
-    <t>23.04.202610</t>
-  </si>
-  <si>
-    <t>23.04.202611</t>
-  </si>
-  <si>
-    <t>23.04.202612</t>
-  </si>
-  <si>
-    <t>23.04.202613</t>
-  </si>
-  <si>
-    <t>23.04.202614</t>
-  </si>
-  <si>
-    <t>23.04.202615</t>
-  </si>
-  <si>
-    <t>23.04.202616</t>
-  </si>
-  <si>
-    <t>23.04.202617</t>
-  </si>
-  <si>
-    <t>23.04.202618</t>
-  </si>
-  <si>
-    <t>23.04.202619</t>
-  </si>
-  <si>
-    <t>23.04.202620</t>
-  </si>
-  <si>
-    <t>23.04.202621</t>
-  </si>
-  <si>
-    <t>23.04.202622</t>
-  </si>
-  <si>
-    <t>23.04.202623</t>
-  </si>
-  <si>
-    <t>23.04.202624</t>
-  </si>
-  <si>
-    <t>24.04.20261</t>
-  </si>
-  <si>
-    <t>24.04.20262</t>
-  </si>
-  <si>
-    <t>24.04.20263</t>
-  </si>
-  <si>
-    <t>24.04.20264</t>
-  </si>
-  <si>
-    <t>24.04.20265</t>
-  </si>
-  <si>
-    <t>24.04.20266</t>
-  </si>
-  <si>
-    <t>24.04.20267</t>
-  </si>
-  <si>
-    <t>24.04.20268</t>
-  </si>
-  <si>
-    <t>24.04.20269</t>
-  </si>
-  <si>
-    <t>24.04.202610</t>
-  </si>
-  <si>
-    <t>24.04.202611</t>
-  </si>
-  <si>
-    <t>24.04.202612</t>
-  </si>
-  <si>
-    <t>24.04.202613</t>
-  </si>
-  <si>
-    <t>24.04.202614</t>
-  </si>
-  <si>
-    <t>24.04.202615</t>
-  </si>
-  <si>
-    <t>24.04.202616</t>
-  </si>
-  <si>
-    <t>24.04.202617</t>
-  </si>
-  <si>
-    <t>24.04.202618</t>
-  </si>
-  <si>
-    <t>24.04.202619</t>
-  </si>
-  <si>
-    <t>24.04.202620</t>
-  </si>
-  <si>
-    <t>24.04.202621</t>
-  </si>
-  <si>
-    <t>24.04.202622</t>
-  </si>
-  <si>
-    <t>24.04.202623</t>
-  </si>
-  <si>
-    <t>24.04.202624</t>
-  </si>
-  <si>
-    <t>25.04.20261</t>
-  </si>
-  <si>
-    <t>25.04.20262</t>
-  </si>
-  <si>
-    <t>25.04.20263</t>
-  </si>
-  <si>
-    <t>25.04.20264</t>
-  </si>
-  <si>
-    <t>25.04.20265</t>
-  </si>
-  <si>
-    <t>25.04.20266</t>
-  </si>
-  <si>
-    <t>25.04.20267</t>
-  </si>
-  <si>
-    <t>25.04.20268</t>
-  </si>
-  <si>
-    <t>25.04.20269</t>
-  </si>
-  <si>
-    <t>25.04.202610</t>
-  </si>
-  <si>
-    <t>25.04.202611</t>
-  </si>
-  <si>
-    <t>25.04.202612</t>
-  </si>
-  <si>
-    <t>25.04.202613</t>
-  </si>
-  <si>
-    <t>25.04.202614</t>
-  </si>
-  <si>
-    <t>25.04.202615</t>
-  </si>
-  <si>
-    <t>25.04.202616</t>
-  </si>
-  <si>
-    <t>25.04.202617</t>
-  </si>
-  <si>
-    <t>25.04.202618</t>
-  </si>
-  <si>
-    <t>25.04.202619</t>
-  </si>
-  <si>
-    <t>25.04.202620</t>
-  </si>
-  <si>
-    <t>25.04.202621</t>
-  </si>
-  <si>
-    <t>25.04.202622</t>
-  </si>
-  <si>
-    <t>25.04.202623</t>
-  </si>
-  <si>
-    <t>25.04.202624</t>
-  </si>
-  <si>
-    <t>26.04.20261</t>
-  </si>
-  <si>
-    <t>26.04.20262</t>
-  </si>
-  <si>
-    <t>26.04.20263</t>
-  </si>
-  <si>
-    <t>26.04.20264</t>
-  </si>
-  <si>
-    <t>26.04.20265</t>
-  </si>
-  <si>
-    <t>26.04.20266</t>
-  </si>
-  <si>
-    <t>26.04.20267</t>
-  </si>
-  <si>
-    <t>26.04.20268</t>
-  </si>
-  <si>
-    <t>26.04.20269</t>
-  </si>
-  <si>
-    <t>26.04.202610</t>
-  </si>
-  <si>
-    <t>26.04.202611</t>
-  </si>
-  <si>
-    <t>26.04.202612</t>
-  </si>
-  <si>
-    <t>26.04.202613</t>
-  </si>
-  <si>
-    <t>26.04.202614</t>
-  </si>
-  <si>
-    <t>26.04.202615</t>
-  </si>
-  <si>
-    <t>26.04.202616</t>
-  </si>
-  <si>
-    <t>26.04.202617</t>
-  </si>
-  <si>
-    <t>26.04.202618</t>
-  </si>
-  <si>
-    <t>26.04.202619</t>
-  </si>
-  <si>
-    <t>26.04.202620</t>
-  </si>
-  <si>
-    <t>26.04.202621</t>
-  </si>
-  <si>
-    <t>26.04.202622</t>
-  </si>
-  <si>
-    <t>26.04.202623</t>
-  </si>
-  <si>
-    <t>26.04.202624</t>
-  </si>
-  <si>
-    <t>27.04.20261</t>
-  </si>
-  <si>
-    <t>27.04.20262</t>
-  </si>
-  <si>
-    <t>27.04.20263</t>
-  </si>
-  <si>
-    <t>27.04.20264</t>
-  </si>
-  <si>
-    <t>27.04.20265</t>
-  </si>
-  <si>
-    <t>27.04.20266</t>
-  </si>
-  <si>
-    <t>27.04.20267</t>
-  </si>
-  <si>
-    <t>27.04.20268</t>
-  </si>
-  <si>
-    <t>27.04.20269</t>
-  </si>
-  <si>
-    <t>27.04.202610</t>
-  </si>
-  <si>
-    <t>27.04.202611</t>
-  </si>
-  <si>
-    <t>27.04.202612</t>
-  </si>
-  <si>
-    <t>27.04.202613</t>
-  </si>
-  <si>
-    <t>27.04.202614</t>
-  </si>
-  <si>
-    <t>27.04.202615</t>
-  </si>
-  <si>
-    <t>27.04.202616</t>
-  </si>
-  <si>
-    <t>27.04.202617</t>
-  </si>
-  <si>
-    <t>27.04.202618</t>
-  </si>
-  <si>
-    <t>27.04.202619</t>
-  </si>
-  <si>
-    <t>27.04.202620</t>
-  </si>
-  <si>
-    <t>27.04.202621</t>
-  </si>
-  <si>
-    <t>27.04.202622</t>
-  </si>
-  <si>
-    <t>27.04.202623</t>
-  </si>
-  <si>
-    <t>27.04.202624</t>
-  </si>
-  <si>
-    <t>28.04.20261</t>
-  </si>
-  <si>
-    <t>28.04.20262</t>
-  </si>
-  <si>
-    <t>28.04.20263</t>
-  </si>
-  <si>
-    <t>28.04.20264</t>
-  </si>
-  <si>
-    <t>28.04.20265</t>
-  </si>
-  <si>
-    <t>28.04.20266</t>
-  </si>
-  <si>
-    <t>28.04.20267</t>
-  </si>
-  <si>
-    <t>28.04.20268</t>
-  </si>
-  <si>
-    <t>28.04.20269</t>
-  </si>
-  <si>
-    <t>28.04.202610</t>
+    <t>31.05.202610</t>
+  </si>
+  <si>
+    <t>31.05.202611</t>
+  </si>
+  <si>
+    <t>31.05.202612</t>
+  </si>
+  <si>
+    <t>31.05.202613</t>
+  </si>
+  <si>
+    <t>31.05.202614</t>
+  </si>
+  <si>
+    <t>31.05.202615</t>
+  </si>
+  <si>
+    <t>31.05.202616</t>
+  </si>
+  <si>
+    <t>31.05.202617</t>
+  </si>
+  <si>
+    <t>31.05.202618</t>
+  </si>
+  <si>
+    <t>31.05.202619</t>
+  </si>
+  <si>
+    <t>31.05.202620</t>
+  </si>
+  <si>
+    <t>31.05.202621</t>
+  </si>
+  <si>
+    <t>31.05.202622</t>
+  </si>
+  <si>
+    <t>31.05.202623</t>
+  </si>
+  <si>
+    <t>31.05.202624</t>
+  </si>
+  <si>
+    <t>01.06.20261</t>
+  </si>
+  <si>
+    <t>01.06.20262</t>
+  </si>
+  <si>
+    <t>01.06.20263</t>
+  </si>
+  <si>
+    <t>01.06.20264</t>
+  </si>
+  <si>
+    <t>01.06.20265</t>
+  </si>
+  <si>
+    <t>01.06.20266</t>
+  </si>
+  <si>
+    <t>01.06.20267</t>
+  </si>
+  <si>
+    <t>01.06.20268</t>
+  </si>
+  <si>
+    <t>01.06.20269</t>
+  </si>
+  <si>
+    <t>01.06.202610</t>
+  </si>
+  <si>
+    <t>01.06.202611</t>
+  </si>
+  <si>
+    <t>01.06.202612</t>
+  </si>
+  <si>
+    <t>01.06.202613</t>
+  </si>
+  <si>
+    <t>01.06.202614</t>
+  </si>
+  <si>
+    <t>01.06.202615</t>
+  </si>
+  <si>
+    <t>01.06.202616</t>
+  </si>
+  <si>
+    <t>01.06.202617</t>
+  </si>
+  <si>
+    <t>01.06.202618</t>
+  </si>
+  <si>
+    <t>01.06.202619</t>
+  </si>
+  <si>
+    <t>01.06.202620</t>
+  </si>
+  <si>
+    <t>01.06.202621</t>
+  </si>
+  <si>
+    <t>01.06.202622</t>
+  </si>
+  <si>
+    <t>01.06.202623</t>
+  </si>
+  <si>
+    <t>01.06.202624</t>
+  </si>
+  <si>
+    <t>02.06.20261</t>
+  </si>
+  <si>
+    <t>02.06.20262</t>
+  </si>
+  <si>
+    <t>02.06.20263</t>
+  </si>
+  <si>
+    <t>02.06.20264</t>
+  </si>
+  <si>
+    <t>02.06.20265</t>
+  </si>
+  <si>
+    <t>02.06.20266</t>
+  </si>
+  <si>
+    <t>02.06.20267</t>
+  </si>
+  <si>
+    <t>02.06.20268</t>
+  </si>
+  <si>
+    <t>02.06.20269</t>
+  </si>
+  <si>
+    <t>02.06.202610</t>
+  </si>
+  <si>
+    <t>02.06.202611</t>
+  </si>
+  <si>
+    <t>02.06.202612</t>
+  </si>
+  <si>
+    <t>02.06.202613</t>
+  </si>
+  <si>
+    <t>02.06.202614</t>
+  </si>
+  <si>
+    <t>02.06.202615</t>
+  </si>
+  <si>
+    <t>02.06.202616</t>
+  </si>
+  <si>
+    <t>02.06.202617</t>
+  </si>
+  <si>
+    <t>02.06.202618</t>
+  </si>
+  <si>
+    <t>02.06.202619</t>
+  </si>
+  <si>
+    <t>02.06.202620</t>
+  </si>
+  <si>
+    <t>02.06.202621</t>
+  </si>
+  <si>
+    <t>02.06.202622</t>
+  </si>
+  <si>
+    <t>02.06.202623</t>
+  </si>
+  <si>
+    <t>02.06.202624</t>
+  </si>
+  <si>
+    <t>03.06.20261</t>
+  </si>
+  <si>
+    <t>03.06.20262</t>
+  </si>
+  <si>
+    <t>03.06.20263</t>
+  </si>
+  <si>
+    <t>03.06.20264</t>
+  </si>
+  <si>
+    <t>03.06.20265</t>
+  </si>
+  <si>
+    <t>03.06.20266</t>
+  </si>
+  <si>
+    <t>03.06.20267</t>
+  </si>
+  <si>
+    <t>03.06.20268</t>
+  </si>
+  <si>
+    <t>03.06.20269</t>
+  </si>
+  <si>
+    <t>03.06.202610</t>
+  </si>
+  <si>
+    <t>03.06.202611</t>
+  </si>
+  <si>
+    <t>03.06.202612</t>
+  </si>
+  <si>
+    <t>03.06.202613</t>
+  </si>
+  <si>
+    <t>03.06.202614</t>
+  </si>
+  <si>
+    <t>03.06.202615</t>
+  </si>
+  <si>
+    <t>03.06.202616</t>
+  </si>
+  <si>
+    <t>03.06.202617</t>
+  </si>
+  <si>
+    <t>03.06.202618</t>
+  </si>
+  <si>
+    <t>03.06.202619</t>
+  </si>
+  <si>
+    <t>03.06.202620</t>
+  </si>
+  <si>
+    <t>03.06.202621</t>
+  </si>
+  <si>
+    <t>03.06.202622</t>
+  </si>
+  <si>
+    <t>03.06.202623</t>
+  </si>
+  <si>
+    <t>03.06.202624</t>
+  </si>
+  <si>
+    <t>04.06.20261</t>
+  </si>
+  <si>
+    <t>04.06.20262</t>
+  </si>
+  <si>
+    <t>04.06.20263</t>
+  </si>
+  <si>
+    <t>04.06.20264</t>
+  </si>
+  <si>
+    <t>04.06.20265</t>
+  </si>
+  <si>
+    <t>04.06.20266</t>
+  </si>
+  <si>
+    <t>04.06.20267</t>
+  </si>
+  <si>
+    <t>04.06.20268</t>
+  </si>
+  <si>
+    <t>04.06.20269</t>
+  </si>
+  <si>
+    <t>04.06.202610</t>
+  </si>
+  <si>
+    <t>04.06.202611</t>
+  </si>
+  <si>
+    <t>04.06.202612</t>
+  </si>
+  <si>
+    <t>04.06.202613</t>
+  </si>
+  <si>
+    <t>04.06.202614</t>
+  </si>
+  <si>
+    <t>04.06.202615</t>
+  </si>
+  <si>
+    <t>04.06.202616</t>
+  </si>
+  <si>
+    <t>04.06.202617</t>
+  </si>
+  <si>
+    <t>04.06.202618</t>
+  </si>
+  <si>
+    <t>04.06.202619</t>
+  </si>
+  <si>
+    <t>04.06.202620</t>
+  </si>
+  <si>
+    <t>04.06.202621</t>
+  </si>
+  <si>
+    <t>04.06.202622</t>
+  </si>
+  <si>
+    <t>04.06.202623</t>
+  </si>
+  <si>
+    <t>04.06.202624</t>
+  </si>
+  <si>
+    <t>05.06.20261</t>
+  </si>
+  <si>
+    <t>05.06.20262</t>
+  </si>
+  <si>
+    <t>05.06.20263</t>
+  </si>
+  <si>
+    <t>05.06.20264</t>
+  </si>
+  <si>
+    <t>05.06.20265</t>
+  </si>
+  <si>
+    <t>05.06.20266</t>
+  </si>
+  <si>
+    <t>05.06.20267</t>
+  </si>
+  <si>
+    <t>05.06.20268</t>
+  </si>
+  <si>
+    <t>05.06.20269</t>
+  </si>
+  <si>
+    <t>05.06.202610</t>
+  </si>
+  <si>
+    <t>05.06.202611</t>
+  </si>
+  <si>
+    <t>05.06.202612</t>
+  </si>
+  <si>
+    <t>05.06.202613</t>
+  </si>
+  <si>
+    <t>05.06.202614</t>
+  </si>
+  <si>
+    <t>05.06.202615</t>
+  </si>
+  <si>
+    <t>05.06.202616</t>
+  </si>
+  <si>
+    <t>05.06.202617</t>
+  </si>
+  <si>
+    <t>05.06.202618</t>
+  </si>
+  <si>
+    <t>05.06.202619</t>
+  </si>
+  <si>
+    <t>05.06.202620</t>
+  </si>
+  <si>
+    <t>05.06.202621</t>
+  </si>
+  <si>
+    <t>05.06.202622</t>
+  </si>
+  <si>
+    <t>05.06.202623</t>
+  </si>
+  <si>
+    <t>05.06.202624</t>
+  </si>
+  <si>
+    <t>06.06.20261</t>
+  </si>
+  <si>
+    <t>06.06.20262</t>
+  </si>
+  <si>
+    <t>06.06.20263</t>
+  </si>
+  <si>
+    <t>06.06.20264</t>
+  </si>
+  <si>
+    <t>06.06.20265</t>
+  </si>
+  <si>
+    <t>06.06.20266</t>
+  </si>
+  <si>
+    <t>06.06.20267</t>
+  </si>
+  <si>
+    <t>06.06.20268</t>
+  </si>
+  <si>
+    <t>06.06.20269</t>
+  </si>
+  <si>
+    <t>06.06.202610</t>
+  </si>
+  <si>
+    <t>06.06.202611</t>
+  </si>
+  <si>
+    <t>06.06.202612</t>
+  </si>
+  <si>
+    <t>06.06.202613</t>
+  </si>
+  <si>
+    <t>06.06.202614</t>
+  </si>
+  <si>
+    <t>06.06.202615</t>
+  </si>
+  <si>
+    <t>06.06.202616</t>
+  </si>
+  <si>
+    <t>06.06.202617</t>
+  </si>
+  <si>
+    <t>06.06.202618</t>
+  </si>
+  <si>
+    <t>06.06.202619</t>
+  </si>
+  <si>
+    <t>06.06.202620</t>
+  </si>
+  <si>
+    <t>06.06.202621</t>
+  </si>
+  <si>
+    <t>06.06.202622</t>
+  </si>
+  <si>
+    <t>06.06.202623</t>
+  </si>
+  <si>
+    <t>06.06.202624</t>
+  </si>
+  <si>
+    <t>07.06.20261</t>
+  </si>
+  <si>
+    <t>07.06.20262</t>
+  </si>
+  <si>
+    <t>07.06.20263</t>
+  </si>
+  <si>
+    <t>07.06.20264</t>
+  </si>
+  <si>
+    <t>07.06.20265</t>
+  </si>
+  <si>
+    <t>07.06.20266</t>
+  </si>
+  <si>
+    <t>07.06.20267</t>
+  </si>
+  <si>
+    <t>07.06.20268</t>
+  </si>
+  <si>
+    <t>07.06.20269</t>
+  </si>
+  <si>
+    <t>07.06.202610</t>
   </si>
 </sst>
 </file>
@@ -948,10 +951,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V170"/>
+  <dimension ref="A1:W170"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:22">
+    <row r="1" spans="1:23">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1018,10 +1021,13 @@
       <c r="V1" s="1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="2" spans="1:22">
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23">
       <c r="A2" s="2">
-        <v>46133</v>
+        <v>46173</v>
       </c>
       <c r="B2">
         <v>10</v>
@@ -1033,7 +1039,7 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>0.083</v>
+        <v>0.082</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -1050,16 +1056,16 @@
       <c r="J2">
         <v>0</v>
       </c>
-      <c r="U2" t="s">
-        <v>22</v>
-      </c>
-      <c r="V2">
+      <c r="V2" t="s">
+        <v>23</v>
+      </c>
+      <c r="W2">
         <v>0.034</v>
       </c>
     </row>
-    <row r="3" spans="1:22">
+    <row r="3" spans="1:23">
       <c r="A3" s="2">
-        <v>46133</v>
+        <v>46173</v>
       </c>
       <c r="B3">
         <v>11</v>
@@ -1071,7 +1077,7 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>0.08599999999999999</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -1088,396 +1094,396 @@
       <c r="J3">
         <v>0</v>
       </c>
-      <c r="U3" t="s">
-        <v>23</v>
-      </c>
-      <c r="V3">
+      <c r="V3" t="s">
+        <v>24</v>
+      </c>
+      <c r="W3">
         <v>0.034</v>
       </c>
     </row>
-    <row r="4" spans="1:22">
+    <row r="4" spans="1:23">
       <c r="A4" s="2">
-        <v>46133</v>
+        <v>46173</v>
       </c>
       <c r="B4">
         <v>12</v>
       </c>
       <c r="C4">
-        <v>2.224</v>
+        <v>2.055</v>
       </c>
       <c r="D4">
-        <v>2.93</v>
+        <v>2.708</v>
       </c>
       <c r="E4">
-        <v>2.239</v>
+        <v>4.099</v>
       </c>
       <c r="F4">
-        <v>2.071</v>
+        <v>3.481</v>
       </c>
       <c r="G4">
-        <v>1.15</v>
+        <v>1.626</v>
       </c>
       <c r="H4">
-        <v>0.917</v>
+        <v>1.423</v>
       </c>
       <c r="I4">
-        <v>0.612</v>
+        <v>0.451</v>
       </c>
       <c r="J4">
-        <v>1.117</v>
-      </c>
-      <c r="U4" t="s">
-        <v>24</v>
-      </c>
-      <c r="V4">
+        <v>1.069</v>
+      </c>
+      <c r="V4" t="s">
+        <v>25</v>
+      </c>
+      <c r="W4">
         <v>1.509</v>
       </c>
     </row>
-    <row r="5" spans="1:22">
+    <row r="5" spans="1:23">
       <c r="A5" s="2">
-        <v>46133</v>
+        <v>46173</v>
       </c>
       <c r="B5">
         <v>13</v>
       </c>
       <c r="C5">
-        <v>1.968</v>
+        <v>2.39</v>
       </c>
       <c r="D5">
-        <v>2.634</v>
+        <v>2.592</v>
       </c>
       <c r="E5">
-        <v>3.659</v>
+        <v>3.658</v>
       </c>
       <c r="F5">
-        <v>2.187</v>
+        <v>3.384</v>
       </c>
       <c r="G5">
-        <v>1.31</v>
+        <v>1.597</v>
       </c>
       <c r="H5">
-        <v>1.07</v>
+        <v>1.317</v>
       </c>
       <c r="I5">
-        <v>0.612</v>
+        <v>0.997</v>
       </c>
       <c r="J5">
-        <v>1.244</v>
-      </c>
-      <c r="U5" t="s">
-        <v>25</v>
-      </c>
-      <c r="V5">
+        <v>1.39</v>
+      </c>
+      <c r="V5" t="s">
+        <v>26</v>
+      </c>
+      <c r="W5">
         <v>1.714</v>
       </c>
     </row>
-    <row r="6" spans="1:22">
+    <row r="6" spans="1:23">
       <c r="A6" s="2">
-        <v>46133</v>
+        <v>46173</v>
       </c>
       <c r="B6">
         <v>14</v>
       </c>
       <c r="C6">
-        <v>2.07</v>
+        <v>2.833</v>
       </c>
       <c r="D6">
-        <v>2.621</v>
+        <v>3.177</v>
       </c>
       <c r="E6">
-        <v>3.964</v>
+        <v>3.568</v>
       </c>
       <c r="F6">
-        <v>2.154</v>
+        <v>3.231</v>
       </c>
       <c r="G6">
-        <v>1.323</v>
+        <v>1.546</v>
       </c>
       <c r="H6">
-        <v>1.065</v>
+        <v>1.36</v>
       </c>
       <c r="I6">
-        <v>0.515</v>
+        <v>1.225</v>
       </c>
       <c r="J6">
-        <v>0.947</v>
-      </c>
-      <c r="U6" t="s">
-        <v>26</v>
-      </c>
-      <c r="V6">
+        <v>1.275</v>
+      </c>
+      <c r="V6" t="s">
+        <v>27</v>
+      </c>
+      <c r="W6">
         <v>1.603</v>
       </c>
     </row>
-    <row r="7" spans="1:22">
+    <row r="7" spans="1:23">
       <c r="A7" s="2">
-        <v>46133</v>
+        <v>46173</v>
       </c>
       <c r="B7">
         <v>15</v>
       </c>
       <c r="C7">
-        <v>1.987</v>
+        <v>2.705</v>
       </c>
       <c r="D7">
-        <v>2.521</v>
+        <v>3.109</v>
       </c>
       <c r="E7">
-        <v>3.79</v>
+        <v>3.674</v>
       </c>
       <c r="F7">
-        <v>1.811</v>
+        <v>3.515</v>
       </c>
       <c r="G7">
-        <v>1.174</v>
+        <v>1.642</v>
       </c>
       <c r="H7">
-        <v>0.919</v>
+        <v>1.195</v>
       </c>
       <c r="I7">
-        <v>0.502</v>
+        <v>1.346</v>
       </c>
       <c r="J7">
-        <v>0.931</v>
-      </c>
-      <c r="U7" t="s">
-        <v>27</v>
-      </c>
-      <c r="V7">
+        <v>1.23</v>
+      </c>
+      <c r="V7" t="s">
+        <v>28</v>
+      </c>
+      <c r="W7">
         <v>1.468</v>
       </c>
     </row>
-    <row r="8" spans="1:22">
+    <row r="8" spans="1:23">
       <c r="A8" s="2">
-        <v>46133</v>
+        <v>46173</v>
       </c>
       <c r="B8">
         <v>16</v>
       </c>
       <c r="C8">
-        <v>1.894</v>
+        <v>2.305</v>
       </c>
       <c r="D8">
-        <v>2.388</v>
+        <v>2.719</v>
       </c>
       <c r="E8">
-        <v>3.643</v>
+        <v>3.588</v>
       </c>
       <c r="F8">
-        <v>1.446</v>
+        <v>2.935</v>
       </c>
       <c r="G8">
-        <v>0.855</v>
+        <v>1.342</v>
       </c>
       <c r="H8">
-        <v>0.9320000000000001</v>
+        <v>1.214</v>
       </c>
       <c r="I8">
-        <v>0.424</v>
+        <v>0.908</v>
       </c>
       <c r="J8">
-        <v>0.849</v>
-      </c>
-      <c r="U8" t="s">
-        <v>28</v>
-      </c>
-      <c r="V8">
+        <v>1.079</v>
+      </c>
+      <c r="V8" t="s">
+        <v>29</v>
+      </c>
+      <c r="W8">
         <v>1.235</v>
       </c>
     </row>
-    <row r="9" spans="1:22">
+    <row r="9" spans="1:23">
       <c r="A9" s="2">
-        <v>46133</v>
+        <v>46173</v>
       </c>
       <c r="B9">
         <v>17</v>
       </c>
       <c r="C9">
-        <v>1.587</v>
+        <v>1.945</v>
       </c>
       <c r="D9">
-        <v>1.796</v>
+        <v>2.57</v>
       </c>
       <c r="E9">
-        <v>3.004</v>
+        <v>3.001</v>
       </c>
       <c r="F9">
-        <v>0.897</v>
+        <v>2.197</v>
       </c>
       <c r="G9">
-        <v>0.776</v>
+        <v>1.092</v>
       </c>
       <c r="H9">
-        <v>0.732</v>
+        <v>1.076</v>
       </c>
       <c r="I9">
-        <v>0.329</v>
+        <v>0.824</v>
       </c>
       <c r="J9">
-        <v>0.655</v>
-      </c>
-      <c r="U9" t="s">
-        <v>29</v>
-      </c>
-      <c r="V9">
+        <v>0.847</v>
+      </c>
+      <c r="V9" t="s">
+        <v>30</v>
+      </c>
+      <c r="W9">
         <v>0.679</v>
       </c>
     </row>
-    <row r="10" spans="1:22">
+    <row r="10" spans="1:23">
       <c r="A10" s="2">
-        <v>46133</v>
+        <v>46173</v>
       </c>
       <c r="B10">
         <v>18</v>
       </c>
       <c r="C10">
-        <v>0.88</v>
+        <v>1.419</v>
       </c>
       <c r="D10">
-        <v>1.145</v>
+        <v>1.889</v>
       </c>
       <c r="E10">
-        <v>2.098</v>
+        <v>2.387</v>
       </c>
       <c r="F10">
-        <v>0.525</v>
+        <v>0.991</v>
       </c>
       <c r="G10">
-        <v>0.413</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="H10">
-        <v>0.457</v>
+        <v>0.831</v>
       </c>
       <c r="I10">
-        <v>0.257</v>
+        <v>0.754</v>
       </c>
       <c r="J10">
-        <v>0.285</v>
-      </c>
-      <c r="U10" t="s">
-        <v>30</v>
-      </c>
-      <c r="V10">
+        <v>0.447</v>
+      </c>
+      <c r="V10" t="s">
+        <v>31</v>
+      </c>
+      <c r="W10">
         <v>0.421</v>
       </c>
     </row>
-    <row r="11" spans="1:22">
+    <row r="11" spans="1:23">
       <c r="A11" s="2">
-        <v>46133</v>
+        <v>46173</v>
       </c>
       <c r="B11">
         <v>19</v>
       </c>
       <c r="C11">
-        <v>0.426</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="D11">
-        <v>0.494</v>
+        <v>0.97</v>
       </c>
       <c r="E11">
-        <v>1.023</v>
+        <v>1.378</v>
       </c>
       <c r="F11">
-        <v>0.173</v>
+        <v>0.586</v>
       </c>
       <c r="G11">
-        <v>0.164</v>
+        <v>0.432</v>
       </c>
       <c r="H11">
-        <v>0.213</v>
+        <v>0.569</v>
       </c>
       <c r="I11">
-        <v>0.125</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="J11">
-        <v>0.176</v>
-      </c>
-      <c r="U11" t="s">
-        <v>31</v>
-      </c>
-      <c r="V11">
+        <v>0.308</v>
+      </c>
+      <c r="V11" t="s">
+        <v>32</v>
+      </c>
+      <c r="W11">
         <v>0.044</v>
       </c>
     </row>
-    <row r="12" spans="1:22">
+    <row r="12" spans="1:23">
       <c r="A12" s="2">
-        <v>46133</v>
+        <v>46173</v>
       </c>
       <c r="B12">
         <v>20</v>
       </c>
       <c r="C12">
-        <v>0.08400000000000001</v>
+        <v>0.282</v>
       </c>
       <c r="D12">
-        <v>0.115</v>
+        <v>0.317</v>
       </c>
       <c r="E12">
-        <v>0.262</v>
+        <v>0.594</v>
       </c>
       <c r="F12">
-        <v>0.025</v>
+        <v>0.218</v>
       </c>
       <c r="G12">
-        <v>0.04</v>
+        <v>0.181</v>
       </c>
       <c r="H12">
-        <v>0.05</v>
+        <v>0.285</v>
       </c>
       <c r="I12">
-        <v>0.025</v>
+        <v>0.241</v>
       </c>
       <c r="J12">
-        <v>0.019</v>
-      </c>
-      <c r="U12" t="s">
-        <v>32</v>
-      </c>
-      <c r="V12">
+        <v>0.165</v>
+      </c>
+      <c r="V12" t="s">
+        <v>33</v>
+      </c>
+      <c r="W12">
         <v>0.049</v>
       </c>
     </row>
-    <row r="13" spans="1:22">
+    <row r="13" spans="1:23">
       <c r="A13" s="2">
-        <v>46133</v>
+        <v>46173</v>
       </c>
       <c r="B13">
         <v>21</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>0.057</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>0.038</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>0.041</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="J13">
-        <v>0.013</v>
-      </c>
-      <c r="U13" t="s">
-        <v>33</v>
-      </c>
-      <c r="V13">
+        <v>0.027</v>
+      </c>
+      <c r="V13" t="s">
+        <v>34</v>
+      </c>
+      <c r="W13">
         <v>0.04</v>
       </c>
     </row>
-    <row r="14" spans="1:22">
+    <row r="14" spans="1:23">
       <c r="A14" s="2">
-        <v>46133</v>
+        <v>46173</v>
       </c>
       <c r="B14">
         <v>22</v>
@@ -1506,16 +1512,16 @@
       <c r="J14">
         <v>0.013</v>
       </c>
-      <c r="U14" t="s">
-        <v>34</v>
-      </c>
-      <c r="V14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:22">
+      <c r="V14" t="s">
+        <v>35</v>
+      </c>
+      <c r="W14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23">
       <c r="A15" s="2">
-        <v>46133</v>
+        <v>46173</v>
       </c>
       <c r="B15">
         <v>23</v>
@@ -1544,16 +1550,16 @@
       <c r="J15">
         <v>0.013</v>
       </c>
-      <c r="U15" t="s">
-        <v>35</v>
-      </c>
-      <c r="V15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:22">
+      <c r="V15" t="s">
+        <v>36</v>
+      </c>
+      <c r="W15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23">
       <c r="A16" s="2">
-        <v>46133</v>
+        <v>46173</v>
       </c>
       <c r="B16">
         <v>24</v>
@@ -1582,16 +1588,16 @@
       <c r="J16">
         <v>0.013</v>
       </c>
-      <c r="U16" t="s">
-        <v>36</v>
-      </c>
-      <c r="V16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:22">
+      <c r="V16" t="s">
+        <v>37</v>
+      </c>
+      <c r="W16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23">
       <c r="A17" s="2">
-        <v>46134</v>
+        <v>46174</v>
       </c>
       <c r="B17">
         <v>1</v>
@@ -1620,16 +1626,16 @@
       <c r="J17">
         <v>0.014</v>
       </c>
-      <c r="U17" t="s">
-        <v>37</v>
-      </c>
-      <c r="V17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:22">
+      <c r="V17" t="s">
+        <v>38</v>
+      </c>
+      <c r="W17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23">
       <c r="A18" s="2">
-        <v>46134</v>
+        <v>46174</v>
       </c>
       <c r="B18">
         <v>2</v>
@@ -1658,16 +1664,16 @@
       <c r="J18">
         <v>0.014</v>
       </c>
-      <c r="U18" t="s">
-        <v>38</v>
-      </c>
-      <c r="V18">
+      <c r="V18" t="s">
+        <v>39</v>
+      </c>
+      <c r="W18">
         <v>0.014</v>
       </c>
     </row>
-    <row r="19" spans="1:22">
+    <row r="19" spans="1:23">
       <c r="A19" s="2">
-        <v>46134</v>
+        <v>46174</v>
       </c>
       <c r="B19">
         <v>3</v>
@@ -1696,16 +1702,16 @@
       <c r="J19">
         <v>0.014</v>
       </c>
-      <c r="U19" t="s">
-        <v>39</v>
-      </c>
-      <c r="V19">
+      <c r="V19" t="s">
+        <v>40</v>
+      </c>
+      <c r="W19">
         <v>0.014</v>
       </c>
     </row>
-    <row r="20" spans="1:22">
+    <row r="20" spans="1:23">
       <c r="A20" s="2">
-        <v>46134</v>
+        <v>46174</v>
       </c>
       <c r="B20">
         <v>4</v>
@@ -1734,16 +1740,16 @@
       <c r="J20">
         <v>0.014</v>
       </c>
-      <c r="U20" t="s">
-        <v>40</v>
-      </c>
-      <c r="V20">
+      <c r="V20" t="s">
+        <v>41</v>
+      </c>
+      <c r="W20">
         <v>0.014</v>
       </c>
     </row>
-    <row r="21" spans="1:22">
+    <row r="21" spans="1:23">
       <c r="A21" s="2">
-        <v>46134</v>
+        <v>46174</v>
       </c>
       <c r="B21">
         <v>5</v>
@@ -1772,16 +1778,16 @@
       <c r="J21">
         <v>0.014</v>
       </c>
-      <c r="U21" t="s">
-        <v>41</v>
-      </c>
-      <c r="V21">
+      <c r="V21" t="s">
+        <v>42</v>
+      </c>
+      <c r="W21">
         <v>0.014</v>
       </c>
     </row>
-    <row r="22" spans="1:22">
+    <row r="22" spans="1:23">
       <c r="A22" s="2">
-        <v>46134</v>
+        <v>46174</v>
       </c>
       <c r="B22">
         <v>6</v>
@@ -1796,7 +1802,7 @@
         <v>0</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>0.028</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -1808,550 +1814,550 @@
         <v>0</v>
       </c>
       <c r="J22">
+        <v>0.024</v>
+      </c>
+      <c r="V22" t="s">
+        <v>43</v>
+      </c>
+      <c r="W22">
         <v>0.014</v>
       </c>
-      <c r="U22" t="s">
-        <v>42</v>
-      </c>
-      <c r="V22">
-        <v>0.014</v>
-      </c>
-    </row>
-    <row r="23" spans="1:22">
+    </row>
+    <row r="23" spans="1:23">
       <c r="A23" s="2">
-        <v>46134</v>
+        <v>46174</v>
       </c>
       <c r="B23">
         <v>7</v>
       </c>
       <c r="C23">
-        <v>0.013</v>
+        <v>0.068</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>0.078</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>0.169</v>
       </c>
       <c r="F23">
-        <v>0.033</v>
+        <v>0.334</v>
       </c>
       <c r="G23">
-        <v>0.013</v>
+        <v>0.205</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>0.145</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>0.116</v>
       </c>
       <c r="J23">
-        <v>0.038</v>
-      </c>
-      <c r="U23" t="s">
-        <v>43</v>
-      </c>
-      <c r="V23">
+        <v>0.062</v>
+      </c>
+      <c r="V23" t="s">
+        <v>44</v>
+      </c>
+      <c r="W23">
         <v>0.014</v>
       </c>
     </row>
-    <row r="24" spans="1:22">
+    <row r="24" spans="1:23">
       <c r="A24" s="2">
-        <v>46134</v>
+        <v>46174</v>
       </c>
       <c r="B24">
         <v>8</v>
       </c>
       <c r="C24">
-        <v>0.242</v>
+        <v>0.283</v>
       </c>
       <c r="D24">
-        <v>0.239</v>
+        <v>0.361</v>
       </c>
       <c r="E24">
-        <v>0.188</v>
+        <v>0.699</v>
       </c>
       <c r="F24">
-        <v>0.23</v>
+        <v>1.07</v>
       </c>
       <c r="G24">
-        <v>0.121</v>
+        <v>0.413</v>
       </c>
       <c r="H24">
-        <v>0.145</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="I24">
-        <v>0.112</v>
+        <v>0.369</v>
       </c>
       <c r="J24">
-        <v>0.046</v>
-      </c>
-      <c r="U24" t="s">
-        <v>44</v>
-      </c>
-      <c r="V24">
+        <v>0.3</v>
+      </c>
+      <c r="V24" t="s">
+        <v>45</v>
+      </c>
+      <c r="W24">
         <v>0.041</v>
       </c>
     </row>
-    <row r="25" spans="1:22">
+    <row r="25" spans="1:23">
       <c r="A25" s="2">
-        <v>46134</v>
+        <v>46174</v>
       </c>
       <c r="B25">
         <v>9</v>
       </c>
       <c r="C25">
-        <v>0.772</v>
+        <v>0.642</v>
       </c>
       <c r="D25">
-        <v>0.764</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="E25">
-        <v>0.842</v>
+        <v>1.674</v>
       </c>
       <c r="F25">
-        <v>0.526</v>
+        <v>1.831</v>
       </c>
       <c r="G25">
-        <v>0.256</v>
+        <v>1.125</v>
       </c>
       <c r="H25">
-        <v>0.479</v>
+        <v>0.953</v>
       </c>
       <c r="I25">
-        <v>0.348</v>
+        <v>0.518</v>
       </c>
       <c r="J25">
-        <v>0.205</v>
-      </c>
-      <c r="U25" t="s">
-        <v>45</v>
-      </c>
-      <c r="V25">
+        <v>0.584</v>
+      </c>
+      <c r="V25" t="s">
+        <v>46</v>
+      </c>
+      <c r="W25">
         <v>0.06</v>
       </c>
     </row>
-    <row r="26" spans="1:22">
+    <row r="26" spans="1:23">
       <c r="A26" s="2">
-        <v>46134</v>
+        <v>46174</v>
       </c>
       <c r="B26">
         <v>10</v>
       </c>
       <c r="C26">
-        <v>1.524</v>
+        <v>0.744</v>
       </c>
       <c r="D26">
-        <v>1.69</v>
+        <v>0.838</v>
       </c>
       <c r="E26">
-        <v>1.577</v>
+        <v>2.584</v>
       </c>
       <c r="F26">
-        <v>0.782</v>
+        <v>2.644</v>
       </c>
       <c r="G26">
-        <v>0.385</v>
+        <v>1.855</v>
       </c>
       <c r="H26">
-        <v>0.969</v>
+        <v>1.255</v>
       </c>
       <c r="I26">
-        <v>0.572</v>
+        <v>0.628</v>
       </c>
       <c r="J26">
-        <v>0.454</v>
-      </c>
-      <c r="U26" t="s">
-        <v>46</v>
-      </c>
-      <c r="V26">
+        <v>0.856</v>
+      </c>
+      <c r="V26" t="s">
+        <v>47</v>
+      </c>
+      <c r="W26">
         <v>0.334</v>
       </c>
     </row>
-    <row r="27" spans="1:22">
+    <row r="27" spans="1:23">
       <c r="A27" s="2">
-        <v>46134</v>
+        <v>46174</v>
       </c>
       <c r="B27">
         <v>11</v>
       </c>
       <c r="C27">
-        <v>2.111</v>
+        <v>0.853</v>
       </c>
       <c r="D27">
-        <v>2.471</v>
+        <v>0.983</v>
       </c>
       <c r="E27">
-        <v>2.766</v>
+        <v>2.909</v>
       </c>
       <c r="F27">
-        <v>0.859</v>
+        <v>3.33</v>
       </c>
       <c r="G27">
-        <v>0.66</v>
+        <v>2.465</v>
       </c>
       <c r="H27">
-        <v>1.132</v>
+        <v>1.227</v>
       </c>
       <c r="I27">
-        <v>0.658</v>
+        <v>0.823</v>
       </c>
       <c r="J27">
-        <v>0.786</v>
-      </c>
-      <c r="U27" t="s">
-        <v>47</v>
-      </c>
-      <c r="V27">
+        <v>0.884</v>
+      </c>
+      <c r="V27" t="s">
+        <v>48</v>
+      </c>
+      <c r="W27">
         <v>1.057</v>
       </c>
     </row>
-    <row r="28" spans="1:22">
+    <row r="28" spans="1:23">
       <c r="A28" s="2">
-        <v>46134</v>
+        <v>46174</v>
       </c>
       <c r="B28">
         <v>12</v>
       </c>
       <c r="C28">
-        <v>2.502</v>
+        <v>0.792</v>
       </c>
       <c r="D28">
-        <v>2.943</v>
+        <v>1.009</v>
       </c>
       <c r="E28">
-        <v>3.31</v>
+        <v>3.328</v>
       </c>
       <c r="F28">
-        <v>0.718</v>
+        <v>2.601</v>
       </c>
       <c r="G28">
-        <v>0.823</v>
+        <v>2.659</v>
       </c>
       <c r="H28">
-        <v>1.245</v>
+        <v>1.188</v>
       </c>
       <c r="I28">
-        <v>0.79</v>
+        <v>0.859</v>
       </c>
       <c r="J28">
-        <v>0.885</v>
-      </c>
-      <c r="U28" t="s">
-        <v>48</v>
-      </c>
-      <c r="V28">
+        <v>0.829</v>
+      </c>
+      <c r="V28" t="s">
+        <v>49</v>
+      </c>
+      <c r="W28">
         <v>1.652</v>
       </c>
     </row>
-    <row r="29" spans="1:22">
+    <row r="29" spans="1:23">
       <c r="A29" s="2">
-        <v>46134</v>
+        <v>46174</v>
       </c>
       <c r="B29">
         <v>13</v>
       </c>
       <c r="C29">
-        <v>2.611</v>
+        <v>0.742</v>
       </c>
       <c r="D29">
-        <v>3.213</v>
+        <v>0.971</v>
       </c>
       <c r="E29">
-        <v>3.575</v>
+        <v>3.231</v>
       </c>
       <c r="F29">
-        <v>0.768</v>
+        <v>2.012</v>
       </c>
       <c r="G29">
-        <v>0.924</v>
+        <v>2.878</v>
       </c>
       <c r="H29">
-        <v>1.157</v>
+        <v>1.243</v>
       </c>
       <c r="I29">
-        <v>0.92</v>
+        <v>1.063</v>
       </c>
       <c r="J29">
-        <v>0.877</v>
-      </c>
-      <c r="U29" t="s">
-        <v>49</v>
-      </c>
-      <c r="V29">
+        <v>0.753</v>
+      </c>
+      <c r="V29" t="s">
+        <v>50</v>
+      </c>
+      <c r="W29">
         <v>2.17</v>
       </c>
     </row>
-    <row r="30" spans="1:22">
+    <row r="30" spans="1:23">
       <c r="A30" s="2">
-        <v>46134</v>
+        <v>46174</v>
       </c>
       <c r="B30">
         <v>14</v>
       </c>
       <c r="C30">
-        <v>2.417</v>
+        <v>0.705</v>
       </c>
       <c r="D30">
-        <v>2.923</v>
+        <v>0.927</v>
       </c>
       <c r="E30">
-        <v>3.6</v>
+        <v>3.201</v>
       </c>
       <c r="F30">
-        <v>1.654</v>
+        <v>3.462</v>
       </c>
       <c r="G30">
-        <v>0.8159999999999999</v>
+        <v>2.981</v>
       </c>
       <c r="H30">
-        <v>1.258</v>
+        <v>1.358</v>
       </c>
       <c r="I30">
-        <v>0.977</v>
+        <v>1.089</v>
       </c>
       <c r="J30">
-        <v>0.917</v>
-      </c>
-      <c r="U30" t="s">
-        <v>50</v>
-      </c>
-      <c r="V30">
+        <v>0.715</v>
+      </c>
+      <c r="V30" t="s">
+        <v>51</v>
+      </c>
+      <c r="W30">
         <v>1.983</v>
       </c>
     </row>
-    <row r="31" spans="1:22">
+    <row r="31" spans="1:23">
       <c r="A31" s="2">
-        <v>46134</v>
+        <v>46174</v>
       </c>
       <c r="B31">
         <v>15</v>
       </c>
       <c r="C31">
-        <v>2.118</v>
+        <v>0.673</v>
       </c>
       <c r="D31">
-        <v>3.003</v>
+        <v>0.917</v>
       </c>
       <c r="E31">
-        <v>3.63</v>
+        <v>3.103</v>
       </c>
       <c r="F31">
-        <v>1.907</v>
+        <v>3.283</v>
       </c>
       <c r="G31">
-        <v>1.153</v>
+        <v>2.753</v>
       </c>
       <c r="H31">
-        <v>1.258</v>
+        <v>1.284</v>
       </c>
       <c r="I31">
-        <v>0.882</v>
+        <v>0.895</v>
       </c>
       <c r="J31">
-        <v>0.9409999999999999</v>
-      </c>
-      <c r="U31" t="s">
-        <v>51</v>
-      </c>
-      <c r="V31">
+        <v>0.649</v>
+      </c>
+      <c r="V31" t="s">
+        <v>52</v>
+      </c>
+      <c r="W31">
         <v>1.764</v>
       </c>
     </row>
-    <row r="32" spans="1:22">
+    <row r="32" spans="1:23">
       <c r="A32" s="2">
-        <v>46134</v>
+        <v>46174</v>
       </c>
       <c r="B32">
         <v>16</v>
       </c>
       <c r="C32">
-        <v>1.922</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="D32">
-        <v>2.613</v>
+        <v>0.771</v>
       </c>
       <c r="E32">
-        <v>3.36</v>
+        <v>2.666</v>
       </c>
       <c r="F32">
-        <v>1.985</v>
+        <v>2.46</v>
       </c>
       <c r="G32">
-        <v>1.149</v>
+        <v>2.054</v>
       </c>
       <c r="H32">
-        <v>1.108</v>
+        <v>0.987</v>
       </c>
       <c r="I32">
-        <v>0.906</v>
+        <v>0.612</v>
       </c>
       <c r="J32">
-        <v>1.119</v>
-      </c>
-      <c r="U32" t="s">
-        <v>52</v>
-      </c>
-      <c r="V32">
+        <v>0.381</v>
+      </c>
+      <c r="V32" t="s">
+        <v>53</v>
+      </c>
+      <c r="W32">
         <v>1.184</v>
       </c>
     </row>
-    <row r="33" spans="1:22">
+    <row r="33" spans="1:23">
       <c r="A33" s="2">
-        <v>46134</v>
+        <v>46174</v>
       </c>
       <c r="B33">
         <v>17</v>
       </c>
       <c r="C33">
-        <v>1.893</v>
+        <v>0.466</v>
       </c>
       <c r="D33">
-        <v>2.343</v>
+        <v>0.625</v>
       </c>
       <c r="E33">
-        <v>2.602</v>
+        <v>1.806</v>
       </c>
       <c r="F33">
-        <v>1.448</v>
+        <v>1.554</v>
       </c>
       <c r="G33">
-        <v>0.9399999999999999</v>
+        <v>1.362</v>
       </c>
       <c r="H33">
-        <v>1.06</v>
+        <v>0.799</v>
       </c>
       <c r="I33">
-        <v>0.709</v>
+        <v>0.48</v>
       </c>
       <c r="J33">
-        <v>0.869</v>
-      </c>
-      <c r="U33" t="s">
-        <v>53</v>
-      </c>
-      <c r="V33">
+        <v>0.281</v>
+      </c>
+      <c r="V33" t="s">
+        <v>54</v>
+      </c>
+      <c r="W33">
         <v>0.583</v>
       </c>
     </row>
-    <row r="34" spans="1:22">
+    <row r="34" spans="1:23">
       <c r="A34" s="2">
-        <v>46134</v>
+        <v>46174</v>
       </c>
       <c r="B34">
         <v>18</v>
       </c>
       <c r="C34">
-        <v>1.341</v>
+        <v>0.348</v>
       </c>
       <c r="D34">
-        <v>1.599</v>
+        <v>0.454</v>
       </c>
       <c r="E34">
-        <v>1.587</v>
+        <v>1.424</v>
       </c>
       <c r="F34">
-        <v>0.619</v>
+        <v>1.056</v>
       </c>
       <c r="G34">
-        <v>0.655</v>
+        <v>0.835</v>
       </c>
       <c r="H34">
-        <v>0.822</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="I34">
-        <v>0.479</v>
+        <v>0.272</v>
       </c>
       <c r="J34">
-        <v>0.523</v>
-      </c>
-      <c r="U34" t="s">
-        <v>54</v>
-      </c>
-      <c r="V34">
+        <v>0.239</v>
+      </c>
+      <c r="V34" t="s">
+        <v>55</v>
+      </c>
+      <c r="W34">
         <v>0.427</v>
       </c>
     </row>
-    <row r="35" spans="1:22">
+    <row r="35" spans="1:23">
       <c r="A35" s="2">
-        <v>46134</v>
+        <v>46174</v>
       </c>
       <c r="B35">
         <v>19</v>
       </c>
       <c r="C35">
-        <v>0.615</v>
+        <v>0.152</v>
       </c>
       <c r="D35">
-        <v>0.712</v>
+        <v>0.228</v>
       </c>
       <c r="E35">
-        <v>0.828</v>
+        <v>0.752</v>
       </c>
       <c r="F35">
-        <v>0.202</v>
+        <v>0.505</v>
       </c>
       <c r="G35">
-        <v>0.192</v>
+        <v>0.407</v>
       </c>
       <c r="H35">
-        <v>0.388</v>
+        <v>0.423</v>
       </c>
       <c r="I35">
-        <v>0.208</v>
+        <v>0.15</v>
       </c>
       <c r="J35">
-        <v>0.268</v>
-      </c>
-      <c r="U35" t="s">
-        <v>55</v>
-      </c>
-      <c r="V35">
+        <v>0.11</v>
+      </c>
+      <c r="V35" t="s">
+        <v>56</v>
+      </c>
+      <c r="W35">
         <v>0.035</v>
       </c>
     </row>
-    <row r="36" spans="1:22">
+    <row r="36" spans="1:23">
       <c r="A36" s="2">
-        <v>46134</v>
+        <v>46174</v>
       </c>
       <c r="B36">
         <v>20</v>
       </c>
       <c r="C36">
-        <v>0.122</v>
+        <v>0.063</v>
       </c>
       <c r="D36">
-        <v>0.151</v>
+        <v>0.101</v>
       </c>
       <c r="E36">
-        <v>0.186</v>
+        <v>0.205</v>
       </c>
       <c r="F36">
-        <v>0.053</v>
+        <v>0.173</v>
       </c>
       <c r="G36">
-        <v>0.078</v>
+        <v>0.157</v>
       </c>
       <c r="H36">
-        <v>0.106</v>
+        <v>0.199</v>
       </c>
       <c r="I36">
         <v>0.064</v>
       </c>
       <c r="J36">
-        <v>0.045</v>
-      </c>
-      <c r="U36" t="s">
-        <v>56</v>
-      </c>
-      <c r="V36">
+        <v>0.027</v>
+      </c>
+      <c r="V36" t="s">
+        <v>57</v>
+      </c>
+      <c r="W36">
         <v>0.091</v>
       </c>
     </row>
-    <row r="37" spans="1:22">
+    <row r="37" spans="1:23">
       <c r="A37" s="2">
-        <v>46134</v>
+        <v>46174</v>
       </c>
       <c r="B37">
         <v>21</v>
@@ -2360,36 +2366,36 @@
         <v>0</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>0.023</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="F37">
-        <v>0</v>
+        <v>0.018</v>
       </c>
       <c r="G37">
-        <v>0</v>
+        <v>0.022</v>
       </c>
       <c r="H37">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="I37">
         <v>0</v>
       </c>
       <c r="J37">
-        <v>0.013</v>
-      </c>
-      <c r="U37" t="s">
-        <v>57</v>
-      </c>
-      <c r="V37">
+        <v>0.019</v>
+      </c>
+      <c r="V37" t="s">
+        <v>58</v>
+      </c>
+      <c r="W37">
         <v>0.091</v>
       </c>
     </row>
-    <row r="38" spans="1:22">
+    <row r="38" spans="1:23">
       <c r="A38" s="2">
-        <v>46134</v>
+        <v>46174</v>
       </c>
       <c r="B38">
         <v>22</v>
@@ -2401,7 +2407,7 @@
         <v>0</v>
       </c>
       <c r="E38">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="F38">
         <v>0</v>
@@ -2418,16 +2424,16 @@
       <c r="J38">
         <v>0.013</v>
       </c>
-      <c r="U38" t="s">
-        <v>58</v>
-      </c>
-      <c r="V38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:22">
+      <c r="V38" t="s">
+        <v>59</v>
+      </c>
+      <c r="W38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23">
       <c r="A39" s="2">
-        <v>46134</v>
+        <v>46174</v>
       </c>
       <c r="B39">
         <v>23</v>
@@ -2439,7 +2445,7 @@
         <v>0</v>
       </c>
       <c r="E39">
-        <v>0.015</v>
+        <v>0.01</v>
       </c>
       <c r="F39">
         <v>0</v>
@@ -2454,18 +2460,18 @@
         <v>0</v>
       </c>
       <c r="J39">
-        <v>0.031</v>
-      </c>
-      <c r="U39" t="s">
-        <v>59</v>
-      </c>
-      <c r="V39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:22">
+        <v>0.013</v>
+      </c>
+      <c r="V39" t="s">
+        <v>60</v>
+      </c>
+      <c r="W39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:23">
       <c r="A40" s="2">
-        <v>46134</v>
+        <v>46174</v>
       </c>
       <c r="B40">
         <v>24</v>
@@ -2492,18 +2498,18 @@
         <v>0</v>
       </c>
       <c r="J40">
-        <v>0.031</v>
-      </c>
-      <c r="U40" t="s">
-        <v>60</v>
-      </c>
-      <c r="V40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:22">
+        <v>0.013</v>
+      </c>
+      <c r="V40" t="s">
+        <v>61</v>
+      </c>
+      <c r="W40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23">
       <c r="A41" s="2">
-        <v>46135</v>
+        <v>46175</v>
       </c>
       <c r="B41">
         <v>1</v>
@@ -2530,18 +2536,18 @@
         <v>0</v>
       </c>
       <c r="J41">
-        <v>0.032</v>
-      </c>
-      <c r="U41" t="s">
-        <v>61</v>
-      </c>
-      <c r="V41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:22">
+        <v>0.014</v>
+      </c>
+      <c r="V41" t="s">
+        <v>62</v>
+      </c>
+      <c r="W41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23">
       <c r="A42" s="2">
-        <v>46135</v>
+        <v>46175</v>
       </c>
       <c r="B42">
         <v>2</v>
@@ -2568,18 +2574,18 @@
         <v>0</v>
       </c>
       <c r="J42">
-        <v>0.032</v>
-      </c>
-      <c r="U42" t="s">
-        <v>62</v>
-      </c>
-      <c r="V42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:22">
+        <v>0.014</v>
+      </c>
+      <c r="V42" t="s">
+        <v>63</v>
+      </c>
+      <c r="W42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:23">
       <c r="A43" s="2">
-        <v>46135</v>
+        <v>46175</v>
       </c>
       <c r="B43">
         <v>3</v>
@@ -2606,18 +2612,18 @@
         <v>0</v>
       </c>
       <c r="J43">
-        <v>0.032</v>
-      </c>
-      <c r="U43" t="s">
-        <v>63</v>
-      </c>
-      <c r="V43">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:22">
+        <v>0.014</v>
+      </c>
+      <c r="V43" t="s">
+        <v>64</v>
+      </c>
+      <c r="W43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23">
       <c r="A44" s="2">
-        <v>46135</v>
+        <v>46175</v>
       </c>
       <c r="B44">
         <v>4</v>
@@ -2644,18 +2650,18 @@
         <v>0</v>
       </c>
       <c r="J44">
-        <v>0.032</v>
-      </c>
-      <c r="U44" t="s">
-        <v>64</v>
-      </c>
-      <c r="V44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:22">
+        <v>0.014</v>
+      </c>
+      <c r="V44" t="s">
+        <v>65</v>
+      </c>
+      <c r="W44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:23">
       <c r="A45" s="2">
-        <v>46135</v>
+        <v>46175</v>
       </c>
       <c r="B45">
         <v>5</v>
@@ -2682,18 +2688,18 @@
         <v>0</v>
       </c>
       <c r="J45">
-        <v>0.032</v>
-      </c>
-      <c r="U45" t="s">
-        <v>65</v>
-      </c>
-      <c r="V45">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:22">
+        <v>0.014</v>
+      </c>
+      <c r="V45" t="s">
+        <v>66</v>
+      </c>
+      <c r="W45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23">
       <c r="A46" s="2">
-        <v>46135</v>
+        <v>46175</v>
       </c>
       <c r="B46">
         <v>6</v>
@@ -2705,10 +2711,10 @@
         <v>0</v>
       </c>
       <c r="E46">
-        <v>0.039</v>
+        <v>0</v>
       </c>
       <c r="F46">
-        <v>0</v>
+        <v>0.022</v>
       </c>
       <c r="G46">
         <v>0</v>
@@ -2720,588 +2726,588 @@
         <v>0</v>
       </c>
       <c r="J46">
-        <v>0.032</v>
-      </c>
-      <c r="U46" t="s">
-        <v>66</v>
-      </c>
-      <c r="V46">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:22">
+        <v>0.024</v>
+      </c>
+      <c r="V46" t="s">
+        <v>67</v>
+      </c>
+      <c r="W46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23">
       <c r="A47" s="2">
-        <v>46135</v>
+        <v>46175</v>
       </c>
       <c r="B47">
         <v>7</v>
       </c>
       <c r="C47">
-        <v>0.014</v>
+        <v>0.05</v>
       </c>
       <c r="D47">
-        <v>0.018</v>
+        <v>0.046</v>
       </c>
       <c r="E47">
+        <v>0.089</v>
+      </c>
+      <c r="F47">
+        <v>0.216</v>
+      </c>
+      <c r="G47">
+        <v>0.122</v>
+      </c>
+      <c r="H47">
         <v>0.053</v>
       </c>
-      <c r="F47">
-        <v>0.101</v>
-      </c>
-      <c r="G47">
-        <v>0.04</v>
-      </c>
-      <c r="H47">
-        <v>0.034</v>
-      </c>
       <c r="I47">
-        <v>0.034</v>
+        <v>0.025</v>
       </c>
       <c r="J47">
-        <v>0.051</v>
-      </c>
-      <c r="U47" t="s">
-        <v>67</v>
-      </c>
-      <c r="V47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:22">
+        <v>0.038</v>
+      </c>
+      <c r="V47" t="s">
+        <v>68</v>
+      </c>
+      <c r="W47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23">
       <c r="A48" s="2">
-        <v>46135</v>
+        <v>46175</v>
       </c>
       <c r="B48">
         <v>8</v>
       </c>
       <c r="C48">
-        <v>0.321</v>
+        <v>0.19</v>
       </c>
       <c r="D48">
-        <v>0.344</v>
+        <v>0.222</v>
       </c>
       <c r="E48">
-        <v>0.467</v>
+        <v>0.404</v>
       </c>
       <c r="F48">
-        <v>0.719</v>
+        <v>0.823</v>
       </c>
       <c r="G48">
-        <v>0.276</v>
+        <v>0.446</v>
       </c>
       <c r="H48">
-        <v>0.38</v>
+        <v>0.221</v>
       </c>
       <c r="I48">
-        <v>0.396</v>
+        <v>0.079</v>
       </c>
       <c r="J48">
-        <v>0.294</v>
-      </c>
-      <c r="U48" t="s">
-        <v>68</v>
-      </c>
-      <c r="V48">
+        <v>0.157</v>
+      </c>
+      <c r="V48" t="s">
+        <v>69</v>
+      </c>
+      <c r="W48">
         <v>0.033</v>
       </c>
     </row>
-    <row r="49" spans="1:22">
+    <row r="49" spans="1:23">
       <c r="A49" s="2">
-        <v>46135</v>
+        <v>46175</v>
       </c>
       <c r="B49">
         <v>9</v>
       </c>
       <c r="C49">
-        <v>0.791</v>
+        <v>0.386</v>
       </c>
       <c r="D49">
-        <v>1.196</v>
+        <v>0.418</v>
       </c>
       <c r="E49">
-        <v>1.797</v>
+        <v>0.881</v>
       </c>
       <c r="F49">
-        <v>2.007</v>
+        <v>1.365</v>
       </c>
       <c r="G49">
-        <v>0.785</v>
+        <v>0.705</v>
       </c>
       <c r="H49">
-        <v>0.929</v>
+        <v>0.551</v>
       </c>
       <c r="I49">
-        <v>0.954</v>
+        <v>0.142</v>
       </c>
       <c r="J49">
-        <v>0.633</v>
-      </c>
-      <c r="U49" t="s">
-        <v>69</v>
-      </c>
-      <c r="V49">
+        <v>0.306</v>
+      </c>
+      <c r="V49" t="s">
+        <v>70</v>
+      </c>
+      <c r="W49">
         <v>0.051</v>
       </c>
     </row>
-    <row r="50" spans="1:22">
+    <row r="50" spans="1:23">
       <c r="A50" s="2">
-        <v>46135</v>
+        <v>46175</v>
       </c>
       <c r="B50">
         <v>10</v>
       </c>
       <c r="C50">
-        <v>1.197</v>
+        <v>0.732</v>
       </c>
       <c r="D50">
-        <v>1.608</v>
+        <v>0.706</v>
       </c>
       <c r="E50">
-        <v>2.841</v>
+        <v>1.532</v>
       </c>
       <c r="F50">
-        <v>3.096</v>
+        <v>2.251</v>
       </c>
       <c r="G50">
-        <v>1.461</v>
+        <v>1.534</v>
       </c>
       <c r="H50">
-        <v>1.316</v>
+        <v>0.603</v>
       </c>
       <c r="I50">
-        <v>1.444</v>
+        <v>0.257</v>
       </c>
       <c r="J50">
-        <v>0.839</v>
-      </c>
-      <c r="U50" t="s">
-        <v>70</v>
-      </c>
-      <c r="V50">
+        <v>0.461</v>
+      </c>
+      <c r="V50" t="s">
+        <v>71</v>
+      </c>
+      <c r="W50">
         <v>0.28</v>
       </c>
     </row>
-    <row r="51" spans="1:22">
+    <row r="51" spans="1:23">
       <c r="A51" s="2">
-        <v>46135</v>
+        <v>46175</v>
       </c>
       <c r="B51">
         <v>11</v>
       </c>
       <c r="C51">
-        <v>1.558</v>
+        <v>1.102</v>
       </c>
       <c r="D51">
-        <v>1.982</v>
+        <v>1.141</v>
       </c>
       <c r="E51">
-        <v>3.83</v>
+        <v>1.962</v>
       </c>
       <c r="F51">
-        <v>3.5</v>
+        <v>2.516</v>
       </c>
       <c r="G51">
-        <v>1.53</v>
+        <v>1.783</v>
       </c>
       <c r="H51">
-        <v>1.336</v>
+        <v>0.678</v>
       </c>
       <c r="I51">
-        <v>1.604</v>
+        <v>0.349</v>
       </c>
       <c r="J51">
-        <v>1.179</v>
-      </c>
-      <c r="U51" t="s">
-        <v>71</v>
-      </c>
-      <c r="V51">
+        <v>0.554</v>
+      </c>
+      <c r="V51" t="s">
+        <v>72</v>
+      </c>
+      <c r="W51">
         <v>1.108</v>
       </c>
     </row>
-    <row r="52" spans="1:22">
+    <row r="52" spans="1:23">
       <c r="A52" s="2">
-        <v>46135</v>
+        <v>46175</v>
       </c>
       <c r="B52">
         <v>12</v>
       </c>
       <c r="C52">
-        <v>1.894</v>
+        <v>1.205</v>
       </c>
       <c r="D52">
-        <v>2.428</v>
+        <v>1.402</v>
       </c>
       <c r="E52">
-        <v>4.184</v>
+        <v>2.898</v>
       </c>
       <c r="F52">
-        <v>2.101</v>
+        <v>2.592</v>
       </c>
       <c r="G52">
-        <v>1.601</v>
+        <v>2.097</v>
       </c>
       <c r="H52">
-        <v>1.358</v>
+        <v>0.707</v>
       </c>
       <c r="I52">
-        <v>1.602</v>
+        <v>0.465</v>
       </c>
       <c r="J52">
-        <v>1.185</v>
-      </c>
-      <c r="U52" t="s">
-        <v>72</v>
-      </c>
-      <c r="V52">
+        <v>0.76</v>
+      </c>
+      <c r="V52" t="s">
+        <v>73</v>
+      </c>
+      <c r="W52">
         <v>1.505</v>
       </c>
     </row>
-    <row r="53" spans="1:22">
+    <row r="53" spans="1:23">
       <c r="A53" s="2">
-        <v>46135</v>
+        <v>46175</v>
       </c>
       <c r="B53">
         <v>13</v>
       </c>
       <c r="C53">
-        <v>1.99</v>
+        <v>1.319</v>
       </c>
       <c r="D53">
-        <v>2.461</v>
+        <v>1.831</v>
       </c>
       <c r="E53">
-        <v>4.285</v>
+        <v>3.577</v>
       </c>
       <c r="F53">
-        <v>3.517</v>
+        <v>2.486</v>
       </c>
       <c r="G53">
-        <v>1.675</v>
+        <v>2.095</v>
       </c>
       <c r="H53">
-        <v>1.308</v>
+        <v>1.101</v>
       </c>
       <c r="I53">
-        <v>1.604</v>
+        <v>0.633</v>
       </c>
       <c r="J53">
-        <v>1.163</v>
-      </c>
-      <c r="U53" t="s">
-        <v>73</v>
-      </c>
-      <c r="V53">
+        <v>1.007</v>
+      </c>
+      <c r="V53" t="s">
+        <v>74</v>
+      </c>
+      <c r="W53">
         <v>2.043</v>
       </c>
     </row>
-    <row r="54" spans="1:22">
+    <row r="54" spans="1:23">
       <c r="A54" s="2">
-        <v>46135</v>
+        <v>46175</v>
       </c>
       <c r="B54">
         <v>14</v>
       </c>
       <c r="C54">
-        <v>2.029</v>
+        <v>1.291</v>
       </c>
       <c r="D54">
-        <v>2.501</v>
+        <v>1.949</v>
       </c>
       <c r="E54">
-        <v>4.092</v>
+        <v>3.578</v>
       </c>
       <c r="F54">
-        <v>3.445</v>
+        <v>2.206</v>
       </c>
       <c r="G54">
-        <v>1.814</v>
+        <v>1.728</v>
       </c>
       <c r="H54">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="I54">
-        <v>1.604</v>
+        <v>0.821</v>
       </c>
       <c r="J54">
-        <v>1.219</v>
-      </c>
-      <c r="U54" t="s">
-        <v>74</v>
-      </c>
-      <c r="V54">
+        <v>0.977</v>
+      </c>
+      <c r="V54" t="s">
+        <v>75</v>
+      </c>
+      <c r="W54">
         <v>1.84</v>
       </c>
     </row>
-    <row r="55" spans="1:22">
+    <row r="55" spans="1:23">
       <c r="A55" s="2">
-        <v>46135</v>
+        <v>46175</v>
       </c>
       <c r="B55">
         <v>15</v>
       </c>
       <c r="C55">
-        <v>2</v>
+        <v>1.193</v>
       </c>
       <c r="D55">
-        <v>2.453</v>
+        <v>1.591</v>
       </c>
       <c r="E55">
-        <v>4.047</v>
+        <v>3.315</v>
       </c>
       <c r="F55">
-        <v>3.021</v>
+        <v>1.769</v>
       </c>
       <c r="G55">
-        <v>1.797</v>
+        <v>1.522</v>
       </c>
       <c r="H55">
-        <v>1.275</v>
+        <v>1.261</v>
       </c>
       <c r="I55">
-        <v>1.604</v>
+        <v>0.782</v>
       </c>
       <c r="J55">
-        <v>1.119</v>
-      </c>
-      <c r="U55" t="s">
-        <v>75</v>
-      </c>
-      <c r="V55">
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="V55" t="s">
+        <v>76</v>
+      </c>
+      <c r="W55">
         <v>1.826</v>
       </c>
     </row>
-    <row r="56" spans="1:22">
+    <row r="56" spans="1:23">
       <c r="A56" s="2">
-        <v>46135</v>
+        <v>46175</v>
       </c>
       <c r="B56">
         <v>16</v>
       </c>
       <c r="C56">
-        <v>1.859</v>
+        <v>0.913</v>
       </c>
       <c r="D56">
-        <v>2.119</v>
+        <v>1.162</v>
       </c>
       <c r="E56">
-        <v>3.897</v>
+        <v>2.5</v>
       </c>
       <c r="F56">
-        <v>2.477</v>
+        <v>1.725</v>
       </c>
       <c r="G56">
-        <v>1.813</v>
+        <v>1.527</v>
       </c>
       <c r="H56">
-        <v>1.256</v>
+        <v>1.15</v>
       </c>
       <c r="I56">
-        <v>1.574</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="J56">
-        <v>0.918</v>
-      </c>
-      <c r="U56" t="s">
-        <v>76</v>
-      </c>
-      <c r="V56">
+        <v>0.741</v>
+      </c>
+      <c r="V56" t="s">
+        <v>77</v>
+      </c>
+      <c r="W56">
         <v>1.02</v>
       </c>
     </row>
-    <row r="57" spans="1:22">
+    <row r="57" spans="1:23">
       <c r="A57" s="2">
-        <v>46135</v>
+        <v>46175</v>
       </c>
       <c r="B57">
         <v>17</v>
       </c>
       <c r="C57">
-        <v>1.337</v>
+        <v>1.028</v>
       </c>
       <c r="D57">
-        <v>1.586</v>
+        <v>1.079</v>
       </c>
       <c r="E57">
-        <v>3.054</v>
+        <v>2.397</v>
       </c>
       <c r="F57">
-        <v>2.053</v>
+        <v>1.425</v>
       </c>
       <c r="G57">
-        <v>1.355</v>
+        <v>1.323</v>
       </c>
       <c r="H57">
-        <v>1.212</v>
+        <v>0.954</v>
       </c>
       <c r="I57">
-        <v>0.955</v>
+        <v>0.645</v>
       </c>
       <c r="J57">
-        <v>0.8080000000000001</v>
-      </c>
-      <c r="U57" t="s">
-        <v>77</v>
-      </c>
-      <c r="V57">
+        <v>0.67</v>
+      </c>
+      <c r="V57" t="s">
+        <v>78</v>
+      </c>
+      <c r="W57">
         <v>0.508</v>
       </c>
     </row>
-    <row r="58" spans="1:22">
+    <row r="58" spans="1:23">
       <c r="A58" s="2">
-        <v>46135</v>
+        <v>46175</v>
       </c>
       <c r="B58">
         <v>18</v>
       </c>
       <c r="C58">
-        <v>0.766</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="D58">
-        <v>1.092</v>
+        <v>0.986</v>
       </c>
       <c r="E58">
-        <v>2.183</v>
+        <v>1.733</v>
       </c>
       <c r="F58">
-        <v>1.039</v>
+        <v>1.075</v>
       </c>
       <c r="G58">
-        <v>0.729</v>
+        <v>0.832</v>
       </c>
       <c r="H58">
-        <v>0.867</v>
+        <v>0.604</v>
       </c>
       <c r="I58">
-        <v>0.829</v>
+        <v>0.596</v>
       </c>
       <c r="J58">
-        <v>0.299</v>
-      </c>
-      <c r="U58" t="s">
-        <v>78</v>
-      </c>
-      <c r="V58">
+        <v>0.334</v>
+      </c>
+      <c r="V58" t="s">
+        <v>79</v>
+      </c>
+      <c r="W58">
         <v>0.422</v>
       </c>
     </row>
-    <row r="59" spans="1:22">
+    <row r="59" spans="1:23">
       <c r="A59" s="2">
-        <v>46135</v>
+        <v>46175</v>
       </c>
       <c r="B59">
         <v>19</v>
       </c>
       <c r="C59">
-        <v>0.387</v>
+        <v>0.421</v>
       </c>
       <c r="D59">
-        <v>0.443</v>
+        <v>0.527</v>
       </c>
       <c r="E59">
-        <v>1.036</v>
+        <v>1.255</v>
       </c>
       <c r="F59">
-        <v>0.344</v>
+        <v>0.633</v>
       </c>
       <c r="G59">
-        <v>0.283</v>
+        <v>0.516</v>
       </c>
       <c r="H59">
-        <v>0.584</v>
+        <v>0.459</v>
       </c>
       <c r="I59">
-        <v>0.472</v>
+        <v>0.347</v>
       </c>
       <c r="J59">
-        <v>0.176</v>
-      </c>
-      <c r="U59" t="s">
-        <v>79</v>
-      </c>
-      <c r="V59">
+        <v>0.248</v>
+      </c>
+      <c r="V59" t="s">
+        <v>80</v>
+      </c>
+      <c r="W59">
         <v>0.045</v>
       </c>
     </row>
-    <row r="60" spans="1:22">
+    <row r="60" spans="1:23">
       <c r="A60" s="2">
-        <v>46135</v>
+        <v>46175</v>
       </c>
       <c r="B60">
         <v>20</v>
       </c>
       <c r="C60">
-        <v>0.067</v>
+        <v>0.224</v>
       </c>
       <c r="D60">
-        <v>0.082</v>
+        <v>0.252</v>
       </c>
       <c r="E60">
-        <v>0.319</v>
+        <v>0.585</v>
       </c>
       <c r="F60">
-        <v>0.06</v>
+        <v>0.178</v>
       </c>
       <c r="G60">
-        <v>0.08500000000000001</v>
+        <v>0.185</v>
       </c>
       <c r="H60">
-        <v>0.106</v>
+        <v>0.199</v>
       </c>
       <c r="I60">
-        <v>0.064</v>
+        <v>0.107</v>
       </c>
       <c r="J60">
-        <v>0.019</v>
-      </c>
-      <c r="U60" t="s">
-        <v>80</v>
-      </c>
-      <c r="V60">
+        <v>0.11</v>
+      </c>
+      <c r="V60" t="s">
+        <v>81</v>
+      </c>
+      <c r="W60">
         <v>0.096</v>
       </c>
     </row>
-    <row r="61" spans="1:22">
+    <row r="61" spans="1:23">
       <c r="A61" s="2">
-        <v>46135</v>
+        <v>46175</v>
       </c>
       <c r="B61">
         <v>21</v>
       </c>
       <c r="C61">
-        <v>0</v>
+        <v>0.043</v>
       </c>
       <c r="D61">
-        <v>0</v>
+        <v>0.065</v>
       </c>
       <c r="E61">
-        <v>0.02</v>
+        <v>0.12</v>
       </c>
       <c r="F61">
-        <v>0</v>
+        <v>0.018</v>
       </c>
       <c r="G61">
-        <v>0</v>
+        <v>0.028</v>
       </c>
       <c r="H61">
-        <v>0</v>
+        <v>0.034</v>
       </c>
       <c r="I61">
         <v>0</v>
       </c>
       <c r="J61">
-        <v>0.013</v>
-      </c>
-      <c r="U61" t="s">
-        <v>81</v>
-      </c>
-      <c r="V61">
+        <v>0.019</v>
+      </c>
+      <c r="V61" t="s">
+        <v>82</v>
+      </c>
+      <c r="W61">
         <v>0.096</v>
       </c>
     </row>
-    <row r="62" spans="1:22">
+    <row r="62" spans="1:23">
       <c r="A62" s="2">
-        <v>46135</v>
+        <v>46175</v>
       </c>
       <c r="B62">
         <v>22</v>
@@ -3313,7 +3319,7 @@
         <v>0</v>
       </c>
       <c r="E62">
-        <v>0.012</v>
+        <v>0</v>
       </c>
       <c r="F62">
         <v>0</v>
@@ -3330,16 +3336,16 @@
       <c r="J62">
         <v>0.013</v>
       </c>
-      <c r="U62" t="s">
-        <v>82</v>
-      </c>
-      <c r="V62">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:22">
+      <c r="V62" t="s">
+        <v>83</v>
+      </c>
+      <c r="W62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:23">
       <c r="A63" s="2">
-        <v>46135</v>
+        <v>46175</v>
       </c>
       <c r="B63">
         <v>23</v>
@@ -3368,16 +3374,16 @@
       <c r="J63">
         <v>0.013</v>
       </c>
-      <c r="U63" t="s">
-        <v>83</v>
-      </c>
-      <c r="V63">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:22">
+      <c r="V63" t="s">
+        <v>84</v>
+      </c>
+      <c r="W63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:23">
       <c r="A64" s="2">
-        <v>46135</v>
+        <v>46175</v>
       </c>
       <c r="B64">
         <v>24</v>
@@ -3406,16 +3412,16 @@
       <c r="J64">
         <v>0.013</v>
       </c>
-      <c r="U64" t="s">
-        <v>84</v>
-      </c>
-      <c r="V64">
+      <c r="V64" t="s">
+        <v>85</v>
+      </c>
+      <c r="W64">
         <v>0.014</v>
       </c>
     </row>
-    <row r="65" spans="1:22">
+    <row r="65" spans="1:23">
       <c r="A65" s="2">
-        <v>46136</v>
+        <v>46176</v>
       </c>
       <c r="B65">
         <v>1</v>
@@ -3444,16 +3450,16 @@
       <c r="J65">
         <v>0.014</v>
       </c>
-      <c r="U65" t="s">
-        <v>85</v>
-      </c>
-      <c r="V65">
+      <c r="V65" t="s">
+        <v>86</v>
+      </c>
+      <c r="W65">
         <v>0.011</v>
       </c>
     </row>
-    <row r="66" spans="1:22">
+    <row r="66" spans="1:23">
       <c r="A66" s="2">
-        <v>46136</v>
+        <v>46176</v>
       </c>
       <c r="B66">
         <v>2</v>
@@ -3482,16 +3488,16 @@
       <c r="J66">
         <v>0.014</v>
       </c>
-      <c r="U66" t="s">
-        <v>86</v>
-      </c>
-      <c r="V66">
+      <c r="V66" t="s">
+        <v>87</v>
+      </c>
+      <c r="W66">
         <v>0.011</v>
       </c>
     </row>
-    <row r="67" spans="1:22">
+    <row r="67" spans="1:23">
       <c r="A67" s="2">
-        <v>46136</v>
+        <v>46176</v>
       </c>
       <c r="B67">
         <v>3</v>
@@ -3520,16 +3526,16 @@
       <c r="J67">
         <v>0.014</v>
       </c>
-      <c r="U67" t="s">
-        <v>87</v>
-      </c>
-      <c r="V67">
+      <c r="V67" t="s">
+        <v>88</v>
+      </c>
+      <c r="W67">
         <v>0.011</v>
       </c>
     </row>
-    <row r="68" spans="1:22">
+    <row r="68" spans="1:23">
       <c r="A68" s="2">
-        <v>46136</v>
+        <v>46176</v>
       </c>
       <c r="B68">
         <v>4</v>
@@ -3556,18 +3562,18 @@
         <v>0</v>
       </c>
       <c r="J68">
-        <v>0.032</v>
-      </c>
-      <c r="U68" t="s">
-        <v>88</v>
-      </c>
-      <c r="V68">
+        <v>0.014</v>
+      </c>
+      <c r="V68" t="s">
+        <v>89</v>
+      </c>
+      <c r="W68">
         <v>0.011</v>
       </c>
     </row>
-    <row r="69" spans="1:22">
+    <row r="69" spans="1:23">
       <c r="A69" s="2">
-        <v>46136</v>
+        <v>46176</v>
       </c>
       <c r="B69">
         <v>5</v>
@@ -3594,18 +3600,18 @@
         <v>0</v>
       </c>
       <c r="J69">
-        <v>0.032</v>
-      </c>
-      <c r="U69" t="s">
-        <v>89</v>
-      </c>
-      <c r="V69">
+        <v>0.014</v>
+      </c>
+      <c r="V69" t="s">
+        <v>90</v>
+      </c>
+      <c r="W69">
         <v>0.011</v>
       </c>
     </row>
-    <row r="70" spans="1:22">
+    <row r="70" spans="1:23">
       <c r="A70" s="2">
-        <v>46136</v>
+        <v>46176</v>
       </c>
       <c r="B70">
         <v>6</v>
@@ -3620,7 +3626,7 @@
         <v>0</v>
       </c>
       <c r="F70">
-        <v>0</v>
+        <v>0.028</v>
       </c>
       <c r="G70">
         <v>0</v>
@@ -3632,588 +3638,588 @@
         <v>0</v>
       </c>
       <c r="J70">
-        <v>0.032</v>
-      </c>
-      <c r="U70" t="s">
-        <v>90</v>
-      </c>
-      <c r="V70">
+        <v>0.038</v>
+      </c>
+      <c r="V70" t="s">
+        <v>91</v>
+      </c>
+      <c r="W70">
         <v>0.011</v>
       </c>
     </row>
-    <row r="71" spans="1:22">
+    <row r="71" spans="1:23">
       <c r="A71" s="2">
-        <v>46136</v>
+        <v>46176</v>
       </c>
       <c r="B71">
         <v>7</v>
       </c>
       <c r="C71">
-        <v>0.028</v>
+        <v>0.091</v>
       </c>
       <c r="D71">
-        <v>0.024</v>
+        <v>0.108</v>
       </c>
       <c r="E71">
-        <v>0.014</v>
+        <v>0.175</v>
       </c>
       <c r="F71">
-        <v>0.095</v>
+        <v>0.308</v>
       </c>
       <c r="G71">
-        <v>0.029</v>
+        <v>0.201</v>
       </c>
       <c r="H71">
-        <v>0.03</v>
+        <v>0.145</v>
       </c>
       <c r="I71">
-        <v>0.025</v>
+        <v>0.079</v>
       </c>
       <c r="J71">
-        <v>0.051</v>
-      </c>
-      <c r="U71" t="s">
-        <v>91</v>
-      </c>
-      <c r="V71">
+        <v>0.165</v>
+      </c>
+      <c r="V71" t="s">
+        <v>92</v>
+      </c>
+      <c r="W71">
         <v>0.011</v>
       </c>
     </row>
-    <row r="72" spans="1:22">
+    <row r="72" spans="1:23">
       <c r="A72" s="2">
-        <v>46136</v>
+        <v>46176</v>
       </c>
       <c r="B72">
         <v>8</v>
       </c>
       <c r="C72">
-        <v>0.404</v>
+        <v>0.405</v>
       </c>
       <c r="D72">
-        <v>0.398</v>
+        <v>0.414</v>
       </c>
       <c r="E72">
-        <v>0.34</v>
+        <v>0.717</v>
       </c>
       <c r="F72">
-        <v>0.611</v>
+        <v>1.207</v>
       </c>
       <c r="G72">
+        <v>0.605</v>
+      </c>
+      <c r="H72">
+        <v>0.439</v>
+      </c>
+      <c r="I72">
         <v>0.26</v>
       </c>
-      <c r="H72">
-        <v>0.302</v>
-      </c>
-      <c r="I72">
-        <v>0.226</v>
-      </c>
       <c r="J72">
-        <v>0.218</v>
-      </c>
-      <c r="U72" t="s">
-        <v>92</v>
-      </c>
-      <c r="V72">
+        <v>0.481</v>
+      </c>
+      <c r="V72" t="s">
+        <v>93</v>
+      </c>
+      <c r="W72">
         <v>0.038</v>
       </c>
     </row>
-    <row r="73" spans="1:22">
+    <row r="73" spans="1:23">
       <c r="A73" s="2">
-        <v>46136</v>
+        <v>46176</v>
       </c>
       <c r="B73">
         <v>9</v>
       </c>
       <c r="C73">
-        <v>1.082</v>
+        <v>0.98</v>
       </c>
       <c r="D73">
-        <v>1.325</v>
+        <v>1.077</v>
       </c>
       <c r="E73">
-        <v>1.616</v>
+        <v>1.73</v>
       </c>
       <c r="F73">
-        <v>1.769</v>
+        <v>2.232</v>
       </c>
       <c r="G73">
-        <v>0.641</v>
+        <v>1.286</v>
       </c>
       <c r="H73">
-        <v>0.793</v>
+        <v>0.754</v>
       </c>
       <c r="I73">
-        <v>0.68</v>
+        <v>0.516</v>
       </c>
       <c r="J73">
-        <v>0.607</v>
-      </c>
-      <c r="U73" t="s">
-        <v>93</v>
-      </c>
-      <c r="V73">
+        <v>0.863</v>
+      </c>
+      <c r="V73" t="s">
+        <v>94</v>
+      </c>
+      <c r="W73">
         <v>0.056</v>
       </c>
     </row>
-    <row r="74" spans="1:22">
+    <row r="74" spans="1:23">
       <c r="A74" s="2">
-        <v>46136</v>
+        <v>46176</v>
       </c>
       <c r="B74">
         <v>10</v>
       </c>
       <c r="C74">
-        <v>1.867</v>
+        <v>1.532</v>
       </c>
       <c r="D74">
-        <v>2.288</v>
+        <v>1.876</v>
       </c>
       <c r="E74">
-        <v>2.241</v>
+        <v>2.539</v>
       </c>
       <c r="F74">
-        <v>2.612</v>
+        <v>3.014</v>
       </c>
       <c r="G74">
-        <v>1.514</v>
+        <v>2.078</v>
       </c>
       <c r="H74">
-        <v>1.128</v>
+        <v>1.126</v>
       </c>
       <c r="I74">
-        <v>1.19</v>
+        <v>0.793</v>
       </c>
       <c r="J74">
-        <v>1.015</v>
-      </c>
-      <c r="U74" t="s">
-        <v>94</v>
-      </c>
-      <c r="V74">
+        <v>0.989</v>
+      </c>
+      <c r="V74" t="s">
+        <v>95</v>
+      </c>
+      <c r="W74">
         <v>0.29</v>
       </c>
     </row>
-    <row r="75" spans="1:22">
+    <row r="75" spans="1:23">
       <c r="A75" s="2">
-        <v>46136</v>
+        <v>46176</v>
       </c>
       <c r="B75">
         <v>11</v>
       </c>
       <c r="C75">
-        <v>2.068</v>
+        <v>2.061</v>
       </c>
       <c r="D75">
-        <v>2.45</v>
+        <v>2.358</v>
       </c>
       <c r="E75">
-        <v>3.647</v>
+        <v>3.091</v>
       </c>
       <c r="F75">
-        <v>3.252</v>
+        <v>3.233</v>
       </c>
       <c r="G75">
-        <v>1.64</v>
+        <v>2.424</v>
       </c>
       <c r="H75">
-        <v>1.341</v>
+        <v>1.332</v>
       </c>
       <c r="I75">
-        <v>1.576</v>
+        <v>0.899</v>
       </c>
       <c r="J75">
-        <v>1.239</v>
-      </c>
-      <c r="U75" t="s">
-        <v>95</v>
-      </c>
-      <c r="V75">
+        <v>1.418</v>
+      </c>
+      <c r="V75" t="s">
+        <v>96</v>
+      </c>
+      <c r="W75">
         <v>0.96</v>
       </c>
     </row>
-    <row r="76" spans="1:22">
+    <row r="76" spans="1:23">
       <c r="A76" s="2">
-        <v>46136</v>
+        <v>46176</v>
       </c>
       <c r="B76">
         <v>12</v>
       </c>
       <c r="C76">
-        <v>1.991</v>
+        <v>2.462</v>
       </c>
       <c r="D76">
-        <v>2.567</v>
+        <v>2.652</v>
       </c>
       <c r="E76">
-        <v>4.207</v>
+        <v>3.645</v>
       </c>
       <c r="F76">
-        <v>2.358</v>
+        <v>3.079</v>
       </c>
       <c r="G76">
-        <v>1.692</v>
+        <v>2.63</v>
       </c>
       <c r="H76">
-        <v>1.234</v>
+        <v>1.169</v>
       </c>
       <c r="I76">
-        <v>1.612</v>
+        <v>1.495</v>
       </c>
       <c r="J76">
-        <v>1.064</v>
-      </c>
-      <c r="U76" t="s">
-        <v>96</v>
-      </c>
-      <c r="V76">
+        <v>1.428</v>
+      </c>
+      <c r="V76" t="s">
+        <v>97</v>
+      </c>
+      <c r="W76">
         <v>1.436</v>
       </c>
     </row>
-    <row r="77" spans="1:22">
+    <row r="77" spans="1:23">
       <c r="A77" s="2">
-        <v>46136</v>
+        <v>46176</v>
       </c>
       <c r="B77">
         <v>13</v>
       </c>
       <c r="C77">
-        <v>1.887</v>
+        <v>2.819</v>
       </c>
       <c r="D77">
-        <v>2.427</v>
+        <v>3.044</v>
       </c>
       <c r="E77">
-        <v>4.175</v>
+        <v>3.664</v>
       </c>
       <c r="F77">
-        <v>2.187</v>
+        <v>1.446</v>
       </c>
       <c r="G77">
-        <v>1.68</v>
+        <v>3.001</v>
       </c>
       <c r="H77">
-        <v>1.339</v>
+        <v>1.095</v>
       </c>
       <c r="I77">
-        <v>1.612</v>
+        <v>1.563</v>
       </c>
       <c r="J77">
-        <v>1.052</v>
-      </c>
-      <c r="U77" t="s">
-        <v>97</v>
-      </c>
-      <c r="V77">
+        <v>1.445</v>
+      </c>
+      <c r="V77" t="s">
+        <v>98</v>
+      </c>
+      <c r="W77">
         <v>1.977</v>
       </c>
     </row>
-    <row r="78" spans="1:22">
+    <row r="78" spans="1:23">
       <c r="A78" s="2">
-        <v>46136</v>
+        <v>46176</v>
       </c>
       <c r="B78">
         <v>14</v>
       </c>
       <c r="C78">
-        <v>1.863</v>
+        <v>2.875</v>
       </c>
       <c r="D78">
-        <v>2.48</v>
+        <v>3.056</v>
       </c>
       <c r="E78">
-        <v>4.094</v>
+        <v>3.645</v>
       </c>
       <c r="F78">
-        <v>2.148</v>
+        <v>1.878</v>
       </c>
       <c r="G78">
-        <v>1.633</v>
+        <v>3.066</v>
       </c>
       <c r="H78">
-        <v>1.402</v>
+        <v>1.014</v>
       </c>
       <c r="I78">
-        <v>1.602</v>
+        <v>1.563</v>
       </c>
       <c r="J78">
-        <v>1.183</v>
-      </c>
-      <c r="U78" t="s">
-        <v>98</v>
-      </c>
-      <c r="V78">
+        <v>1.465</v>
+      </c>
+      <c r="V78" t="s">
+        <v>99</v>
+      </c>
+      <c r="W78">
         <v>1.827</v>
       </c>
     </row>
-    <row r="79" spans="1:22">
+    <row r="79" spans="1:23">
       <c r="A79" s="2">
-        <v>46136</v>
+        <v>46176</v>
       </c>
       <c r="B79">
         <v>15</v>
       </c>
       <c r="C79">
-        <v>1.904</v>
+        <v>2.691</v>
       </c>
       <c r="D79">
-        <v>2.451</v>
+        <v>3.06</v>
       </c>
       <c r="E79">
-        <v>3.965</v>
+        <v>3.7</v>
       </c>
       <c r="F79">
-        <v>3.169</v>
+        <v>3.171</v>
       </c>
       <c r="G79">
-        <v>1.544</v>
+        <v>3.134</v>
       </c>
       <c r="H79">
-        <v>1.477</v>
+        <v>0.99</v>
       </c>
       <c r="I79">
-        <v>1.576</v>
+        <v>1.563</v>
       </c>
       <c r="J79">
-        <v>1.153</v>
-      </c>
-      <c r="U79" t="s">
-        <v>99</v>
-      </c>
-      <c r="V79">
+        <v>1.282</v>
+      </c>
+      <c r="V79" t="s">
+        <v>100</v>
+      </c>
+      <c r="W79">
         <v>1.35</v>
       </c>
     </row>
-    <row r="80" spans="1:22">
+    <row r="80" spans="1:23">
       <c r="A80" s="2">
-        <v>46136</v>
+        <v>46176</v>
       </c>
       <c r="B80">
         <v>16</v>
       </c>
       <c r="C80">
-        <v>1.729</v>
+        <v>2.326</v>
       </c>
       <c r="D80">
-        <v>1.98</v>
+        <v>2.735</v>
       </c>
       <c r="E80">
-        <v>3.716</v>
+        <v>3.616</v>
       </c>
       <c r="F80">
-        <v>2.746</v>
+        <v>2.922</v>
       </c>
       <c r="G80">
-        <v>1.46</v>
+        <v>2.807</v>
       </c>
       <c r="H80">
-        <v>1.461</v>
+        <v>0.944</v>
       </c>
       <c r="I80">
-        <v>1.408</v>
+        <v>1.563</v>
       </c>
       <c r="J80">
-        <v>0.999</v>
-      </c>
-      <c r="U80" t="s">
-        <v>100</v>
-      </c>
-      <c r="V80">
+        <v>1.12</v>
+      </c>
+      <c r="V80" t="s">
+        <v>101</v>
+      </c>
+      <c r="W80">
         <v>0.888</v>
       </c>
     </row>
-    <row r="81" spans="1:22">
+    <row r="81" spans="1:23">
       <c r="A81" s="2">
-        <v>46136</v>
+        <v>46176</v>
       </c>
       <c r="B81">
         <v>17</v>
       </c>
       <c r="C81">
-        <v>1.516</v>
+        <v>1.916</v>
       </c>
       <c r="D81">
-        <v>1.706</v>
+        <v>2.313</v>
       </c>
       <c r="E81">
-        <v>2.964</v>
+        <v>2.851</v>
       </c>
       <c r="F81">
-        <v>2.179</v>
+        <v>2.466</v>
       </c>
       <c r="G81">
-        <v>1.374</v>
+        <v>2.196</v>
       </c>
       <c r="H81">
-        <v>1.148</v>
+        <v>1.098</v>
       </c>
       <c r="I81">
-        <v>0.994</v>
+        <v>1.225</v>
       </c>
       <c r="J81">
-        <v>0.797</v>
-      </c>
-      <c r="U81" t="s">
-        <v>101</v>
-      </c>
-      <c r="V81">
+        <v>0.976</v>
+      </c>
+      <c r="V81" t="s">
+        <v>102</v>
+      </c>
+      <c r="W81">
         <v>0.297</v>
       </c>
     </row>
-    <row r="82" spans="1:22">
+    <row r="82" spans="1:23">
       <c r="A82" s="2">
-        <v>46136</v>
+        <v>46176</v>
       </c>
       <c r="B82">
         <v>18</v>
       </c>
       <c r="C82">
-        <v>1.061</v>
+        <v>1.398</v>
       </c>
       <c r="D82">
-        <v>1.259</v>
+        <v>1.775</v>
       </c>
       <c r="E82">
-        <v>2.096</v>
+        <v>2.296</v>
       </c>
       <c r="F82">
-        <v>0.963</v>
+        <v>1.625</v>
       </c>
       <c r="G82">
-        <v>0.738</v>
+        <v>1.491</v>
       </c>
       <c r="H82">
-        <v>0.74</v>
+        <v>0.839</v>
       </c>
       <c r="I82">
-        <v>0.7</v>
+        <v>0.925</v>
       </c>
       <c r="J82">
-        <v>0.46</v>
-      </c>
-      <c r="U82" t="s">
-        <v>102</v>
-      </c>
-      <c r="V82">
+        <v>0.696</v>
+      </c>
+      <c r="V82" t="s">
+        <v>103</v>
+      </c>
+      <c r="W82">
         <v>0.132</v>
       </c>
     </row>
-    <row r="83" spans="1:22">
+    <row r="83" spans="1:23">
       <c r="A83" s="2">
-        <v>46136</v>
+        <v>46176</v>
       </c>
       <c r="B83">
         <v>19</v>
       </c>
       <c r="C83">
-        <v>0.454</v>
+        <v>0.822</v>
       </c>
       <c r="D83">
-        <v>0.53</v>
+        <v>0.917</v>
       </c>
       <c r="E83">
-        <v>0.977</v>
+        <v>1.354</v>
       </c>
       <c r="F83">
-        <v>0.343</v>
+        <v>0.748</v>
       </c>
       <c r="G83">
-        <v>0.243</v>
+        <v>0.806</v>
       </c>
       <c r="H83">
-        <v>0.358</v>
+        <v>0.533</v>
       </c>
       <c r="I83">
-        <v>0.295</v>
+        <v>0.627</v>
       </c>
       <c r="J83">
-        <v>0.265</v>
-      </c>
-      <c r="U83" t="s">
-        <v>103</v>
-      </c>
-      <c r="V83">
+        <v>0.296</v>
+      </c>
+      <c r="V83" t="s">
+        <v>104</v>
+      </c>
+      <c r="W83">
         <v>0.038</v>
       </c>
     </row>
-    <row r="84" spans="1:22">
+    <row r="84" spans="1:23">
       <c r="A84" s="2">
-        <v>46136</v>
+        <v>46176</v>
       </c>
       <c r="B84">
         <v>20</v>
       </c>
       <c r="C84">
-        <v>0.098</v>
+        <v>0.344</v>
       </c>
       <c r="D84">
-        <v>0.116</v>
+        <v>0.316</v>
       </c>
       <c r="E84">
-        <v>0.229</v>
+        <v>0.614</v>
       </c>
       <c r="F84">
-        <v>0.058</v>
+        <v>0.228</v>
       </c>
       <c r="G84">
-        <v>0.079</v>
+        <v>0.296</v>
       </c>
       <c r="H84">
-        <v>0.106</v>
+        <v>0.285</v>
       </c>
       <c r="I84">
-        <v>0.064</v>
+        <v>0.201</v>
       </c>
       <c r="J84">
-        <v>0.037</v>
-      </c>
-      <c r="U84" t="s">
-        <v>104</v>
-      </c>
-      <c r="V84">
+        <v>0.136</v>
+      </c>
+      <c r="V84" t="s">
+        <v>105</v>
+      </c>
+      <c r="W84">
         <v>0.094</v>
       </c>
     </row>
-    <row r="85" spans="1:22">
+    <row r="85" spans="1:23">
       <c r="A85" s="2">
-        <v>46136</v>
+        <v>46176</v>
       </c>
       <c r="B85">
         <v>21</v>
       </c>
       <c r="C85">
-        <v>0</v>
+        <v>0.056</v>
       </c>
       <c r="D85">
-        <v>0</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="E85">
-        <v>0.014</v>
+        <v>0.11</v>
       </c>
       <c r="F85">
-        <v>0</v>
+        <v>0.037</v>
       </c>
       <c r="G85">
-        <v>0</v>
+        <v>0.056</v>
       </c>
       <c r="H85">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="I85">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="J85">
-        <v>0.031</v>
-      </c>
-      <c r="U85" t="s">
-        <v>105</v>
-      </c>
-      <c r="V85">
+        <v>0.011</v>
+      </c>
+      <c r="V85" t="s">
+        <v>106</v>
+      </c>
+      <c r="W85">
         <v>0.094</v>
       </c>
     </row>
-    <row r="86" spans="1:22">
+    <row r="86" spans="1:23">
       <c r="A86" s="2">
-        <v>46136</v>
+        <v>46176</v>
       </c>
       <c r="B86">
         <v>22</v>
@@ -4240,18 +4246,18 @@
         <v>0</v>
       </c>
       <c r="J86">
-        <v>0.031</v>
-      </c>
-      <c r="U86" t="s">
-        <v>106</v>
-      </c>
-      <c r="V86">
+        <v>0.013</v>
+      </c>
+      <c r="V86" t="s">
+        <v>107</v>
+      </c>
+      <c r="W86">
         <v>0.011</v>
       </c>
     </row>
-    <row r="87" spans="1:22">
+    <row r="87" spans="1:23">
       <c r="A87" s="2">
-        <v>46136</v>
+        <v>46176</v>
       </c>
       <c r="B87">
         <v>23</v>
@@ -4278,18 +4284,18 @@
         <v>0</v>
       </c>
       <c r="J87">
-        <v>0.031</v>
-      </c>
-      <c r="U87" t="s">
-        <v>107</v>
-      </c>
-      <c r="V87">
+        <v>0.013</v>
+      </c>
+      <c r="V87" t="s">
+        <v>108</v>
+      </c>
+      <c r="W87">
         <v>0.011</v>
       </c>
     </row>
-    <row r="88" spans="1:22">
+    <row r="88" spans="1:23">
       <c r="A88" s="2">
-        <v>46136</v>
+        <v>46176</v>
       </c>
       <c r="B88">
         <v>24</v>
@@ -4316,18 +4322,18 @@
         <v>0</v>
       </c>
       <c r="J88">
-        <v>0.031</v>
-      </c>
-      <c r="U88" t="s">
-        <v>108</v>
-      </c>
-      <c r="V88">
+        <v>0.013</v>
+      </c>
+      <c r="V88" t="s">
+        <v>109</v>
+      </c>
+      <c r="W88">
         <v>0.011</v>
       </c>
     </row>
-    <row r="89" spans="1:22">
+    <row r="89" spans="1:23">
       <c r="A89" s="2">
-        <v>46137</v>
+        <v>46177</v>
       </c>
       <c r="B89">
         <v>1</v>
@@ -4354,18 +4360,18 @@
         <v>0</v>
       </c>
       <c r="J89">
-        <v>0.032</v>
-      </c>
-      <c r="U89" t="s">
-        <v>109</v>
-      </c>
-      <c r="V89">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="1:22">
+        <v>0.014</v>
+      </c>
+      <c r="V89" t="s">
+        <v>110</v>
+      </c>
+      <c r="W89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:23">
       <c r="A90" s="2">
-        <v>46137</v>
+        <v>46177</v>
       </c>
       <c r="B90">
         <v>2</v>
@@ -4392,18 +4398,18 @@
         <v>0</v>
       </c>
       <c r="J90">
-        <v>0.032</v>
-      </c>
-      <c r="U90" t="s">
-        <v>110</v>
-      </c>
-      <c r="V90">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="1:22">
+        <v>0.014</v>
+      </c>
+      <c r="V90" t="s">
+        <v>111</v>
+      </c>
+      <c r="W90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:23">
       <c r="A91" s="2">
-        <v>46137</v>
+        <v>46177</v>
       </c>
       <c r="B91">
         <v>3</v>
@@ -4430,18 +4436,18 @@
         <v>0</v>
       </c>
       <c r="J91">
-        <v>0.032</v>
-      </c>
-      <c r="U91" t="s">
-        <v>111</v>
-      </c>
-      <c r="V91">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="1:22">
+        <v>0.014</v>
+      </c>
+      <c r="V91" t="s">
+        <v>112</v>
+      </c>
+      <c r="W91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:23">
       <c r="A92" s="2">
-        <v>46137</v>
+        <v>46177</v>
       </c>
       <c r="B92">
         <v>4</v>
@@ -4468,18 +4474,18 @@
         <v>0</v>
       </c>
       <c r="J92">
-        <v>0.033</v>
-      </c>
-      <c r="U92" t="s">
-        <v>112</v>
-      </c>
-      <c r="V92">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="1:22">
+        <v>0.014</v>
+      </c>
+      <c r="V92" t="s">
+        <v>113</v>
+      </c>
+      <c r="W92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:23">
       <c r="A93" s="2">
-        <v>46137</v>
+        <v>46177</v>
       </c>
       <c r="B93">
         <v>5</v>
@@ -4506,18 +4512,18 @@
         <v>0</v>
       </c>
       <c r="J93">
-        <v>0.033</v>
-      </c>
-      <c r="U93" t="s">
-        <v>113</v>
-      </c>
-      <c r="V93">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="1:22">
+        <v>0.014</v>
+      </c>
+      <c r="V93" t="s">
+        <v>114</v>
+      </c>
+      <c r="W93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:23">
       <c r="A94" s="2">
-        <v>46137</v>
+        <v>46177</v>
       </c>
       <c r="B94">
         <v>6</v>
@@ -4532,10 +4538,10 @@
         <v>0</v>
       </c>
       <c r="F94">
-        <v>0</v>
+        <v>0.036</v>
       </c>
       <c r="G94">
-        <v>0</v>
+        <v>0.012</v>
       </c>
       <c r="H94">
         <v>0</v>
@@ -4544,588 +4550,588 @@
         <v>0</v>
       </c>
       <c r="J94">
-        <v>0.033</v>
-      </c>
-      <c r="U94" t="s">
-        <v>114</v>
-      </c>
-      <c r="V94">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="1:22">
+        <v>0.038</v>
+      </c>
+      <c r="V94" t="s">
+        <v>115</v>
+      </c>
+      <c r="W94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:23">
       <c r="A95" s="2">
-        <v>46137</v>
+        <v>46177</v>
       </c>
       <c r="B95">
         <v>7</v>
       </c>
       <c r="C95">
-        <v>0.015</v>
+        <v>0.105</v>
       </c>
       <c r="D95">
-        <v>0</v>
+        <v>0.107</v>
       </c>
       <c r="E95">
-        <v>0.022</v>
+        <v>0.161</v>
       </c>
       <c r="F95">
-        <v>0.137</v>
+        <v>0.334</v>
       </c>
       <c r="G95">
-        <v>0.05</v>
+        <v>0.204</v>
       </c>
       <c r="H95">
-        <v>0.034</v>
+        <v>0.172</v>
       </c>
       <c r="I95">
-        <v>0.034</v>
+        <v>0.107</v>
       </c>
       <c r="J95">
-        <v>0.052</v>
-      </c>
-      <c r="U95" t="s">
-        <v>115</v>
-      </c>
-      <c r="V95">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96" spans="1:22">
+        <v>0.161</v>
+      </c>
+      <c r="V95" t="s">
+        <v>116</v>
+      </c>
+      <c r="W95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:23">
       <c r="A96" s="2">
-        <v>46137</v>
+        <v>46177</v>
       </c>
       <c r="B96">
         <v>8</v>
       </c>
       <c r="C96">
-        <v>0.314</v>
+        <v>0.417</v>
       </c>
       <c r="D96">
-        <v>0.215</v>
+        <v>0.398</v>
       </c>
       <c r="E96">
-        <v>0.46</v>
+        <v>0.711</v>
       </c>
       <c r="F96">
-        <v>0.606</v>
+        <v>1.182</v>
       </c>
       <c r="G96">
-        <v>0.279</v>
+        <v>0.584</v>
       </c>
       <c r="H96">
-        <v>0.306</v>
+        <v>0.586</v>
       </c>
       <c r="I96">
-        <v>0.361</v>
+        <v>0.332</v>
       </c>
       <c r="J96">
-        <v>0.297</v>
-      </c>
-      <c r="U96" t="s">
-        <v>116</v>
-      </c>
-      <c r="V96">
+        <v>0.487</v>
+      </c>
+      <c r="V96" t="s">
+        <v>117</v>
+      </c>
+      <c r="W96">
         <v>0.192</v>
       </c>
     </row>
-    <row r="97" spans="1:22">
+    <row r="97" spans="1:23">
       <c r="A97" s="2">
-        <v>46137</v>
+        <v>46177</v>
       </c>
       <c r="B97">
         <v>9</v>
       </c>
       <c r="C97">
-        <v>0.882</v>
+        <v>0.928</v>
       </c>
       <c r="D97">
-        <v>0.784</v>
+        <v>1.07</v>
       </c>
       <c r="E97">
-        <v>1.589</v>
+        <v>1.497</v>
       </c>
       <c r="F97">
-        <v>2.052</v>
+        <v>2.172</v>
       </c>
       <c r="G97">
-        <v>0.745</v>
+        <v>1.356</v>
       </c>
       <c r="H97">
-        <v>0.925</v>
+        <v>1.019</v>
       </c>
       <c r="I97">
-        <v>0.825</v>
+        <v>0.642</v>
       </c>
       <c r="J97">
-        <v>0.819</v>
-      </c>
-      <c r="U97" t="s">
-        <v>117</v>
-      </c>
-      <c r="V97">
+        <v>0.921</v>
+      </c>
+      <c r="V97" t="s">
+        <v>118</v>
+      </c>
+      <c r="W97">
         <v>0.21</v>
       </c>
     </row>
-    <row r="98" spans="1:22">
+    <row r="98" spans="1:23">
       <c r="A98" s="2">
-        <v>46137</v>
+        <v>46177</v>
       </c>
       <c r="B98">
         <v>10</v>
       </c>
       <c r="C98">
-        <v>1.406</v>
+        <v>1.543</v>
       </c>
       <c r="D98">
-        <v>1.552</v>
+        <v>1.872</v>
       </c>
       <c r="E98">
-        <v>2.808</v>
+        <v>2.486</v>
       </c>
       <c r="F98">
-        <v>3.173</v>
+        <v>3.239</v>
       </c>
       <c r="G98">
-        <v>1.727</v>
+        <v>2.241</v>
       </c>
       <c r="H98">
-        <v>1.459</v>
+        <v>1.264</v>
       </c>
       <c r="I98">
-        <v>1.288</v>
+        <v>0.804</v>
       </c>
       <c r="J98">
-        <v>1.245</v>
-      </c>
-      <c r="U98" t="s">
-        <v>118</v>
-      </c>
-      <c r="V98">
+        <v>1.212</v>
+      </c>
+      <c r="V98" t="s">
+        <v>119</v>
+      </c>
+      <c r="W98">
         <v>0.501</v>
       </c>
     </row>
-    <row r="99" spans="1:22">
+    <row r="99" spans="1:23">
       <c r="A99" s="2">
-        <v>46137</v>
+        <v>46177</v>
       </c>
       <c r="B99">
         <v>11</v>
       </c>
       <c r="C99">
-        <v>1.84</v>
+        <v>2.028</v>
       </c>
       <c r="D99">
-        <v>2.255</v>
+        <v>2.355</v>
       </c>
       <c r="E99">
-        <v>3.798</v>
+        <v>2.985</v>
       </c>
       <c r="F99">
-        <v>3.698</v>
+        <v>3.294</v>
       </c>
       <c r="G99">
-        <v>1.659</v>
+        <v>2.714</v>
       </c>
       <c r="H99">
-        <v>1.397</v>
+        <v>1.191</v>
       </c>
       <c r="I99">
-        <v>1.507</v>
+        <v>1.326</v>
       </c>
       <c r="J99">
-        <v>1.546</v>
-      </c>
-      <c r="U99" t="s">
-        <v>119</v>
-      </c>
-      <c r="V99">
+        <v>1.35</v>
+      </c>
+      <c r="V99" t="s">
+        <v>120</v>
+      </c>
+      <c r="W99">
         <v>0.678</v>
       </c>
     </row>
-    <row r="100" spans="1:22">
+    <row r="100" spans="1:23">
       <c r="A100" s="2">
-        <v>46137</v>
+        <v>46177</v>
       </c>
       <c r="B100">
         <v>12</v>
       </c>
       <c r="C100">
-        <v>1.978</v>
+        <v>2.455</v>
       </c>
       <c r="D100">
-        <v>2.546</v>
+        <v>2.477</v>
       </c>
       <c r="E100">
-        <v>4.223</v>
+        <v>3.488</v>
       </c>
       <c r="F100">
-        <v>3.67</v>
+        <v>1.705</v>
       </c>
       <c r="G100">
-        <v>1.838</v>
+        <v>3.11</v>
       </c>
       <c r="H100">
-        <v>1.347</v>
+        <v>1.068</v>
       </c>
       <c r="I100">
-        <v>1.423</v>
+        <v>1.563</v>
       </c>
       <c r="J100">
-        <v>1.63</v>
-      </c>
-      <c r="U100" t="s">
-        <v>120</v>
-      </c>
-      <c r="V100">
+        <v>1.542</v>
+      </c>
+      <c r="V100" t="s">
+        <v>121</v>
+      </c>
+      <c r="W100">
         <v>1.135</v>
       </c>
     </row>
-    <row r="101" spans="1:22">
+    <row r="101" spans="1:23">
       <c r="A101" s="2">
-        <v>46137</v>
+        <v>46177</v>
       </c>
       <c r="B101">
         <v>13</v>
       </c>
       <c r="C101">
-        <v>1.958</v>
+        <v>2.47</v>
       </c>
       <c r="D101">
-        <v>2.677</v>
+        <v>2.685</v>
       </c>
       <c r="E101">
-        <v>4.185</v>
+        <v>3.625</v>
       </c>
       <c r="F101">
-        <v>4.255</v>
+        <v>1.624</v>
       </c>
       <c r="G101">
-        <v>2.215</v>
+        <v>3.25</v>
       </c>
       <c r="H101">
-        <v>1.315</v>
+        <v>1.068</v>
       </c>
       <c r="I101">
-        <v>1.513</v>
+        <v>1.563</v>
       </c>
       <c r="J101">
-        <v>1.558</v>
-      </c>
-      <c r="U101" t="s">
-        <v>121</v>
-      </c>
-      <c r="V101">
+        <v>1.557</v>
+      </c>
+      <c r="V101" t="s">
+        <v>122</v>
+      </c>
+      <c r="W101">
         <v>1.387</v>
       </c>
     </row>
-    <row r="102" spans="1:22">
+    <row r="102" spans="1:23">
       <c r="A102" s="2">
-        <v>46137</v>
+        <v>46177</v>
       </c>
       <c r="B102">
         <v>14</v>
       </c>
       <c r="C102">
-        <v>1.931</v>
+        <v>2.442</v>
       </c>
       <c r="D102">
-        <v>2.517</v>
+        <v>2.681</v>
       </c>
       <c r="E102">
-        <v>3.909</v>
+        <v>3.703</v>
       </c>
       <c r="F102">
-        <v>4.127</v>
+        <v>1.796</v>
       </c>
       <c r="G102">
-        <v>2.229</v>
+        <v>3.226</v>
       </c>
       <c r="H102">
-        <v>1.304</v>
+        <v>1.003</v>
       </c>
       <c r="I102">
-        <v>1.513</v>
+        <v>1.563</v>
       </c>
       <c r="J102">
-        <v>1.403</v>
-      </c>
-      <c r="U102" t="s">
-        <v>122</v>
-      </c>
-      <c r="V102">
+        <v>1.425</v>
+      </c>
+      <c r="V102" t="s">
+        <v>123</v>
+      </c>
+      <c r="W102">
         <v>1.534</v>
       </c>
     </row>
-    <row r="103" spans="1:22">
+    <row r="103" spans="1:23">
       <c r="A103" s="2">
-        <v>46137</v>
+        <v>46177</v>
       </c>
       <c r="B103">
         <v>15</v>
       </c>
       <c r="C103">
-        <v>1.939</v>
+        <v>2.15</v>
       </c>
       <c r="D103">
-        <v>2.473</v>
+        <v>2.501</v>
       </c>
       <c r="E103">
-        <v>3.919</v>
+        <v>3.582</v>
       </c>
       <c r="F103">
-        <v>4.115</v>
+        <v>2.776</v>
       </c>
       <c r="G103">
-        <v>1.945</v>
+        <v>2.995</v>
       </c>
       <c r="H103">
-        <v>0.866</v>
+        <v>1.02</v>
       </c>
       <c r="I103">
-        <v>1.567</v>
+        <v>1.563</v>
       </c>
       <c r="J103">
-        <v>1.151</v>
-      </c>
-      <c r="U103" t="s">
-        <v>123</v>
-      </c>
-      <c r="V103">
+        <v>1.385</v>
+      </c>
+      <c r="V103" t="s">
+        <v>124</v>
+      </c>
+      <c r="W103">
         <v>1.228</v>
       </c>
     </row>
-    <row r="104" spans="1:22">
+    <row r="104" spans="1:23">
       <c r="A104" s="2">
-        <v>46137</v>
+        <v>46177</v>
       </c>
       <c r="B104">
         <v>16</v>
       </c>
       <c r="C104">
-        <v>1.619</v>
+        <v>1.809</v>
       </c>
       <c r="D104">
-        <v>2.098</v>
+        <v>2.147</v>
       </c>
       <c r="E104">
-        <v>3.109</v>
+        <v>3.155</v>
       </c>
       <c r="F104">
-        <v>3.261</v>
+        <v>2.893</v>
       </c>
       <c r="G104">
-        <v>1.578</v>
+        <v>2.498</v>
       </c>
       <c r="H104">
-        <v>0.883</v>
+        <v>0.921</v>
       </c>
       <c r="I104">
-        <v>1.543</v>
+        <v>1.563</v>
       </c>
       <c r="J104">
-        <v>1.068</v>
-      </c>
-      <c r="U104" t="s">
-        <v>124</v>
-      </c>
-      <c r="V104">
+        <v>1.286</v>
+      </c>
+      <c r="V104" t="s">
+        <v>125</v>
+      </c>
+      <c r="W104">
         <v>0.991</v>
       </c>
     </row>
-    <row r="105" spans="1:22">
+    <row r="105" spans="1:23">
       <c r="A105" s="2">
-        <v>46137</v>
+        <v>46177</v>
       </c>
       <c r="B105">
         <v>17</v>
       </c>
       <c r="C105">
-        <v>1.317</v>
+        <v>1.677</v>
       </c>
       <c r="D105">
-        <v>1.558</v>
+        <v>1.955</v>
       </c>
       <c r="E105">
-        <v>2.414</v>
+        <v>2.759</v>
       </c>
       <c r="F105">
-        <v>2.179</v>
+        <v>2.31</v>
       </c>
       <c r="G105">
-        <v>1.336</v>
+        <v>2.026</v>
       </c>
       <c r="H105">
-        <v>0.982</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="I105">
-        <v>1.14</v>
+        <v>1.382</v>
       </c>
       <c r="J105">
-        <v>0.742</v>
-      </c>
-      <c r="U105" t="s">
-        <v>125</v>
-      </c>
-      <c r="V105">
+        <v>0.893</v>
+      </c>
+      <c r="V105" t="s">
+        <v>126</v>
+      </c>
+      <c r="W105">
         <v>0.369</v>
       </c>
     </row>
-    <row r="106" spans="1:22">
+    <row r="106" spans="1:23">
       <c r="A106" s="2">
-        <v>46137</v>
+        <v>46177</v>
       </c>
       <c r="B106">
         <v>18</v>
       </c>
       <c r="C106">
-        <v>0.857</v>
+        <v>1.124</v>
       </c>
       <c r="D106">
-        <v>1.06</v>
+        <v>1.277</v>
       </c>
       <c r="E106">
-        <v>1.525</v>
+        <v>1.86</v>
       </c>
       <c r="F106">
-        <v>0.8</v>
+        <v>1.241</v>
       </c>
       <c r="G106">
-        <v>0.784</v>
+        <v>1.241</v>
       </c>
       <c r="H106">
-        <v>0.984</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="I106">
-        <v>0.756</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="J106">
-        <v>0.392</v>
-      </c>
-      <c r="U106" t="s">
-        <v>126</v>
-      </c>
-      <c r="V106">
+        <v>0.401</v>
+      </c>
+      <c r="V106" t="s">
+        <v>127</v>
+      </c>
+      <c r="W106">
         <v>0.421</v>
       </c>
     </row>
-    <row r="107" spans="1:22">
+    <row r="107" spans="1:23">
       <c r="A107" s="2">
-        <v>46137</v>
+        <v>46177</v>
       </c>
       <c r="B107">
         <v>19</v>
       </c>
       <c r="C107">
-        <v>0.424</v>
+        <v>0.635</v>
       </c>
       <c r="D107">
-        <v>0.46</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="E107">
-        <v>0.764</v>
+        <v>1.27</v>
       </c>
       <c r="F107">
-        <v>0.373</v>
+        <v>0.746</v>
       </c>
       <c r="G107">
-        <v>0.297</v>
+        <v>0.714</v>
       </c>
       <c r="H107">
-        <v>0.457</v>
+        <v>0.442</v>
       </c>
       <c r="I107">
-        <v>0.361</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="J107">
-        <v>0.248</v>
-      </c>
-      <c r="U107" t="s">
-        <v>127</v>
-      </c>
-      <c r="V107">
+        <v>0.238</v>
+      </c>
+      <c r="V107" t="s">
+        <v>128</v>
+      </c>
+      <c r="W107">
         <v>0.126</v>
       </c>
     </row>
-    <row r="108" spans="1:22">
+    <row r="108" spans="1:23">
       <c r="A108" s="2">
-        <v>46137</v>
+        <v>46177</v>
       </c>
       <c r="B108">
         <v>20</v>
       </c>
       <c r="C108">
-        <v>0.06900000000000001</v>
+        <v>0.272</v>
       </c>
       <c r="D108">
-        <v>0.082</v>
+        <v>0.254</v>
       </c>
       <c r="E108">
-        <v>0.177</v>
+        <v>0.602</v>
       </c>
       <c r="F108">
-        <v>0.07199999999999999</v>
+        <v>0.215</v>
       </c>
       <c r="G108">
-        <v>0.08699999999999999</v>
+        <v>0.235</v>
       </c>
       <c r="H108">
-        <v>0.106</v>
+        <v>0.232</v>
       </c>
       <c r="I108">
-        <v>0.064</v>
+        <v>0.188</v>
       </c>
       <c r="J108">
-        <v>0.027</v>
-      </c>
-      <c r="U108" t="s">
-        <v>128</v>
-      </c>
-      <c r="V108">
+        <v>0.15</v>
+      </c>
+      <c r="V108" t="s">
+        <v>129</v>
+      </c>
+      <c r="W108">
         <v>0.181</v>
       </c>
     </row>
-    <row r="109" spans="1:22">
+    <row r="109" spans="1:23">
       <c r="A109" s="2">
-        <v>46137</v>
+        <v>46177</v>
       </c>
       <c r="B109">
         <v>21</v>
       </c>
       <c r="C109">
-        <v>0</v>
+        <v>0.046</v>
       </c>
       <c r="D109">
-        <v>0</v>
+        <v>0.065</v>
       </c>
       <c r="E109">
-        <v>0</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="F109">
-        <v>0</v>
+        <v>0.018</v>
       </c>
       <c r="G109">
-        <v>0</v>
+        <v>0.035</v>
       </c>
       <c r="H109">
-        <v>0</v>
+        <v>0.034</v>
       </c>
       <c r="I109">
-        <v>0</v>
+        <v>0.021</v>
       </c>
       <c r="J109">
-        <v>0.013</v>
-      </c>
-      <c r="U109" t="s">
-        <v>129</v>
-      </c>
-      <c r="V109">
+        <v>0.019</v>
+      </c>
+      <c r="V109" t="s">
+        <v>130</v>
+      </c>
+      <c r="W109">
         <v>0.181</v>
       </c>
     </row>
-    <row r="110" spans="1:22">
+    <row r="110" spans="1:23">
       <c r="A110" s="2">
-        <v>46137</v>
+        <v>46177</v>
       </c>
       <c r="B110">
         <v>22</v>
@@ -5154,16 +5160,16 @@
       <c r="J110">
         <v>0.013</v>
       </c>
-      <c r="U110" t="s">
-        <v>130</v>
-      </c>
-      <c r="V110">
+      <c r="V110" t="s">
+        <v>131</v>
+      </c>
+      <c r="W110">
         <v>0.109</v>
       </c>
     </row>
-    <row r="111" spans="1:22">
+    <row r="111" spans="1:23">
       <c r="A111" s="2">
-        <v>46137</v>
+        <v>46177</v>
       </c>
       <c r="B111">
         <v>23</v>
@@ -5192,16 +5198,16 @@
       <c r="J111">
         <v>0.013</v>
       </c>
-      <c r="U111" t="s">
-        <v>131</v>
-      </c>
-      <c r="V111">
+      <c r="V111" t="s">
+        <v>132</v>
+      </c>
+      <c r="W111">
         <v>0.011</v>
       </c>
     </row>
-    <row r="112" spans="1:22">
+    <row r="112" spans="1:23">
       <c r="A112" s="2">
-        <v>46137</v>
+        <v>46177</v>
       </c>
       <c r="B112">
         <v>24</v>
@@ -5230,16 +5236,16 @@
       <c r="J112">
         <v>0.013</v>
       </c>
-      <c r="U112" t="s">
-        <v>132</v>
-      </c>
-      <c r="V112">
+      <c r="V112" t="s">
+        <v>133</v>
+      </c>
+      <c r="W112">
         <v>0.011</v>
       </c>
     </row>
-    <row r="113" spans="1:22">
+    <row r="113" spans="1:23">
       <c r="A113" s="2">
-        <v>46138</v>
+        <v>46178</v>
       </c>
       <c r="B113">
         <v>1</v>
@@ -5251,7 +5257,7 @@
         <v>0</v>
       </c>
       <c r="E113">
-        <v>0.019</v>
+        <v>0</v>
       </c>
       <c r="F113">
         <v>0</v>
@@ -5268,16 +5274,16 @@
       <c r="J113">
         <v>0.014</v>
       </c>
-      <c r="U113" t="s">
-        <v>133</v>
-      </c>
-      <c r="V113">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="114" spans="1:22">
+      <c r="V113" t="s">
+        <v>134</v>
+      </c>
+      <c r="W113">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:23">
       <c r="A114" s="2">
-        <v>46138</v>
+        <v>46178</v>
       </c>
       <c r="B114">
         <v>2</v>
@@ -5306,16 +5312,16 @@
       <c r="J114">
         <v>0.014</v>
       </c>
-      <c r="U114" t="s">
-        <v>134</v>
-      </c>
-      <c r="V114">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115" spans="1:22">
+      <c r="V114" t="s">
+        <v>135</v>
+      </c>
+      <c r="W114">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:23">
       <c r="A115" s="2">
-        <v>46138</v>
+        <v>46178</v>
       </c>
       <c r="B115">
         <v>3</v>
@@ -5344,16 +5350,16 @@
       <c r="J115">
         <v>0.014</v>
       </c>
-      <c r="U115" t="s">
-        <v>135</v>
-      </c>
-      <c r="V115">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116" spans="1:22">
+      <c r="V115" t="s">
+        <v>136</v>
+      </c>
+      <c r="W115">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:23">
       <c r="A116" s="2">
-        <v>46138</v>
+        <v>46178</v>
       </c>
       <c r="B116">
         <v>4</v>
@@ -5382,16 +5388,16 @@
       <c r="J116">
         <v>0.014</v>
       </c>
-      <c r="U116" t="s">
-        <v>136</v>
-      </c>
-      <c r="V116">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117" spans="1:22">
+      <c r="V116" t="s">
+        <v>137</v>
+      </c>
+      <c r="W116">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:23">
       <c r="A117" s="2">
-        <v>46138</v>
+        <v>46178</v>
       </c>
       <c r="B117">
         <v>5</v>
@@ -5420,16 +5426,16 @@
       <c r="J117">
         <v>0.014</v>
       </c>
-      <c r="U117" t="s">
-        <v>137</v>
-      </c>
-      <c r="V117">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="118" spans="1:22">
+      <c r="V117" t="s">
+        <v>138</v>
+      </c>
+      <c r="W117">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:23">
       <c r="A118" s="2">
-        <v>46138</v>
+        <v>46178</v>
       </c>
       <c r="B118">
         <v>6</v>
@@ -5444,7 +5450,7 @@
         <v>0</v>
       </c>
       <c r="F118">
-        <v>0</v>
+        <v>0.028</v>
       </c>
       <c r="G118">
         <v>0</v>
@@ -5456,588 +5462,588 @@
         <v>0</v>
       </c>
       <c r="J118">
-        <v>0.014</v>
-      </c>
-      <c r="U118" t="s">
-        <v>138</v>
-      </c>
-      <c r="V118">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="119" spans="1:22">
+        <v>0.038</v>
+      </c>
+      <c r="V118" t="s">
+        <v>139</v>
+      </c>
+      <c r="W118">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:23">
       <c r="A119" s="2">
-        <v>46138</v>
+        <v>46178</v>
       </c>
       <c r="B119">
         <v>7</v>
       </c>
       <c r="C119">
-        <v>0.029</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="D119">
-        <v>0.024</v>
+        <v>0.102</v>
       </c>
       <c r="E119">
-        <v>0.021</v>
+        <v>0.174</v>
       </c>
       <c r="F119">
+        <v>0.312</v>
+      </c>
+      <c r="G119">
+        <v>0.166</v>
+      </c>
+      <c r="H119">
         <v>0.145</v>
       </c>
-      <c r="G119">
-        <v>0.058</v>
-      </c>
-      <c r="H119">
-        <v>0.034</v>
-      </c>
       <c r="I119">
-        <v>0.034</v>
+        <v>0.136</v>
       </c>
       <c r="J119">
-        <v>0.038</v>
-      </c>
-      <c r="U119" t="s">
-        <v>139</v>
-      </c>
-      <c r="V119">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="120" spans="1:22">
+        <v>0.172</v>
+      </c>
+      <c r="V119" t="s">
+        <v>140</v>
+      </c>
+      <c r="W119">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:23">
       <c r="A120" s="2">
-        <v>46138</v>
+        <v>46178</v>
       </c>
       <c r="B120">
         <v>8</v>
       </c>
       <c r="C120">
-        <v>0.37</v>
+        <v>0.424</v>
       </c>
       <c r="D120">
-        <v>0.393</v>
+        <v>0.4</v>
       </c>
       <c r="E120">
-        <v>0.375</v>
+        <v>0.713</v>
       </c>
       <c r="F120">
-        <v>0.738</v>
+        <v>1.084</v>
       </c>
       <c r="G120">
-        <v>0.342</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="H120">
-        <v>0.38</v>
+        <v>0.439</v>
       </c>
       <c r="I120">
-        <v>0.371</v>
+        <v>0.477</v>
       </c>
       <c r="J120">
-        <v>0.281</v>
-      </c>
-      <c r="U120" t="s">
-        <v>140</v>
-      </c>
-      <c r="V120">
+        <v>0.487</v>
+      </c>
+      <c r="V120" t="s">
+        <v>141</v>
+      </c>
+      <c r="W120">
         <v>0.192</v>
       </c>
     </row>
-    <row r="121" spans="1:22">
+    <row r="121" spans="1:23">
       <c r="A121" s="2">
-        <v>46138</v>
+        <v>46178</v>
       </c>
       <c r="B121">
         <v>9</v>
       </c>
       <c r="C121">
-        <v>1.048</v>
+        <v>0.978</v>
       </c>
       <c r="D121">
-        <v>1.19</v>
+        <v>1.062</v>
       </c>
       <c r="E121">
-        <v>1.483</v>
+        <v>1.734</v>
       </c>
       <c r="F121">
-        <v>2.081</v>
+        <v>2.042</v>
       </c>
       <c r="G121">
-        <v>0.6929999999999999</v>
+        <v>1.278</v>
       </c>
       <c r="H121">
-        <v>0.907</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="I121">
-        <v>0.836</v>
+        <v>0.793</v>
       </c>
       <c r="J121">
-        <v>0.806</v>
-      </c>
-      <c r="U121" t="s">
-        <v>141</v>
-      </c>
-      <c r="V121">
+        <v>0.921</v>
+      </c>
+      <c r="V121" t="s">
+        <v>142</v>
+      </c>
+      <c r="W121">
         <v>0.21</v>
       </c>
     </row>
-    <row r="122" spans="1:22">
+    <row r="122" spans="1:23">
       <c r="A122" s="2">
-        <v>46138</v>
+        <v>46178</v>
       </c>
       <c r="B122">
         <v>10</v>
       </c>
       <c r="C122">
-        <v>1.783</v>
+        <v>1.477</v>
       </c>
       <c r="D122">
-        <v>2.112</v>
+        <v>1.689</v>
       </c>
       <c r="E122">
-        <v>2.612</v>
+        <v>2.5</v>
       </c>
       <c r="F122">
-        <v>3.15</v>
+        <v>2.437</v>
       </c>
       <c r="G122">
-        <v>1.691</v>
+        <v>1.838</v>
       </c>
       <c r="H122">
-        <v>1.358</v>
+        <v>1.204</v>
       </c>
       <c r="I122">
-        <v>1.283</v>
+        <v>0.906</v>
       </c>
       <c r="J122">
-        <v>0.955</v>
-      </c>
-      <c r="U122" t="s">
-        <v>142</v>
-      </c>
-      <c r="V122">
+        <v>1.216</v>
+      </c>
+      <c r="V122" t="s">
+        <v>143</v>
+      </c>
+      <c r="W122">
         <v>0.501</v>
       </c>
     </row>
-    <row r="123" spans="1:22">
+    <row r="123" spans="1:23">
       <c r="A123" s="2">
-        <v>46138</v>
+        <v>46178</v>
       </c>
       <c r="B123">
         <v>11</v>
       </c>
       <c r="C123">
-        <v>2.024</v>
+        <v>1.879</v>
       </c>
       <c r="D123">
-        <v>2.454</v>
+        <v>2.064</v>
       </c>
       <c r="E123">
-        <v>3.653</v>
+        <v>3.137</v>
       </c>
       <c r="F123">
-        <v>3.615</v>
+        <v>3.285</v>
       </c>
       <c r="G123">
-        <v>1.602</v>
+        <v>2.483</v>
       </c>
       <c r="H123">
-        <v>1.459</v>
+        <v>1.212</v>
       </c>
       <c r="I123">
-        <v>1.554</v>
+        <v>1.512</v>
       </c>
       <c r="J123">
-        <v>1.337</v>
-      </c>
-      <c r="U123" t="s">
-        <v>143</v>
-      </c>
-      <c r="V123">
+        <v>1.559</v>
+      </c>
+      <c r="V123" t="s">
+        <v>144</v>
+      </c>
+      <c r="W123">
         <v>0.678</v>
       </c>
     </row>
-    <row r="124" spans="1:22">
+    <row r="124" spans="1:23">
       <c r="A124" s="2">
-        <v>46138</v>
+        <v>46178</v>
       </c>
       <c r="B124">
         <v>12</v>
       </c>
       <c r="C124">
-        <v>1.998</v>
+        <v>2.223</v>
       </c>
       <c r="D124">
-        <v>2.92</v>
+        <v>2.395</v>
       </c>
       <c r="E124">
-        <v>4.222</v>
+        <v>3.65</v>
       </c>
       <c r="F124">
-        <v>3.709</v>
+        <v>2.829</v>
       </c>
       <c r="G124">
-        <v>1.794</v>
+        <v>2.63</v>
       </c>
       <c r="H124">
-        <v>1.294</v>
+        <v>1.119</v>
       </c>
       <c r="I124">
         <v>1.563</v>
       </c>
       <c r="J124">
-        <v>1.582</v>
-      </c>
-      <c r="U124" t="s">
-        <v>144</v>
-      </c>
-      <c r="V124">
+        <v>1.53</v>
+      </c>
+      <c r="V124" t="s">
+        <v>145</v>
+      </c>
+      <c r="W124">
         <v>0.954</v>
       </c>
     </row>
-    <row r="125" spans="1:22">
+    <row r="125" spans="1:23">
       <c r="A125" s="2">
-        <v>46138</v>
+        <v>46178</v>
       </c>
       <c r="B125">
         <v>13</v>
       </c>
       <c r="C125">
-        <v>1.963</v>
+        <v>2.395</v>
       </c>
       <c r="D125">
-        <v>2.924</v>
+        <v>2.521</v>
       </c>
       <c r="E125">
-        <v>4.179</v>
+        <v>3.704</v>
       </c>
       <c r="F125">
-        <v>3.829</v>
+        <v>1.463</v>
       </c>
       <c r="G125">
-        <v>1.942</v>
+        <v>2.857</v>
       </c>
       <c r="H125">
-        <v>1.282</v>
+        <v>1.096</v>
       </c>
       <c r="I125">
         <v>1.563</v>
       </c>
       <c r="J125">
-        <v>1.543</v>
-      </c>
-      <c r="U125" t="s">
-        <v>145</v>
-      </c>
-      <c r="V125">
+        <v>1.66</v>
+      </c>
+      <c r="V125" t="s">
+        <v>146</v>
+      </c>
+      <c r="W125">
         <v>1.021</v>
       </c>
     </row>
-    <row r="126" spans="1:22">
+    <row r="126" spans="1:23">
       <c r="A126" s="2">
-        <v>46138</v>
+        <v>46178</v>
       </c>
       <c r="B126">
         <v>14</v>
       </c>
       <c r="C126">
-        <v>1.939</v>
+        <v>2.411</v>
       </c>
       <c r="D126">
-        <v>2.819</v>
+        <v>2.765</v>
       </c>
       <c r="E126">
-        <v>4.139</v>
+        <v>3.685</v>
       </c>
       <c r="F126">
-        <v>3.76</v>
+        <v>1.443</v>
       </c>
       <c r="G126">
-        <v>1.933</v>
+        <v>2.997</v>
       </c>
       <c r="H126">
-        <v>1.249</v>
+        <v>1.06</v>
       </c>
       <c r="I126">
         <v>1.563</v>
       </c>
       <c r="J126">
-        <v>1.417</v>
-      </c>
-      <c r="U126" t="s">
-        <v>146</v>
-      </c>
-      <c r="V126">
+        <v>1.586</v>
+      </c>
+      <c r="V126" t="s">
+        <v>147</v>
+      </c>
+      <c r="W126">
         <v>0.797</v>
       </c>
     </row>
-    <row r="127" spans="1:22">
+    <row r="127" spans="1:23">
       <c r="A127" s="2">
-        <v>46138</v>
+        <v>46178</v>
       </c>
       <c r="B127">
         <v>15</v>
       </c>
       <c r="C127">
-        <v>1.977</v>
+        <v>2.431</v>
       </c>
       <c r="D127">
-        <v>2.564</v>
+        <v>2.724</v>
       </c>
       <c r="E127">
-        <v>4.08</v>
+        <v>3.665</v>
       </c>
       <c r="F127">
-        <v>3.652</v>
+        <v>1.865</v>
       </c>
       <c r="G127">
-        <v>1.795</v>
+        <v>2.806</v>
       </c>
       <c r="H127">
-        <v>1.188</v>
+        <v>1.036</v>
       </c>
       <c r="I127">
-        <v>1.542</v>
+        <v>1.563</v>
       </c>
       <c r="J127">
-        <v>1.061</v>
-      </c>
-      <c r="U127" t="s">
-        <v>147</v>
-      </c>
-      <c r="V127">
+        <v>1.35</v>
+      </c>
+      <c r="V127" t="s">
+        <v>148</v>
+      </c>
+      <c r="W127">
         <v>0.505</v>
       </c>
     </row>
-    <row r="128" spans="1:22">
+    <row r="128" spans="1:23">
       <c r="A128" s="2">
-        <v>46138</v>
+        <v>46178</v>
       </c>
       <c r="B128">
         <v>16</v>
       </c>
       <c r="C128">
-        <v>1.942</v>
+        <v>1.983</v>
       </c>
       <c r="D128">
-        <v>2.406</v>
+        <v>2.482</v>
       </c>
       <c r="E128">
-        <v>4.31</v>
+        <v>3.666</v>
       </c>
       <c r="F128">
-        <v>3.109</v>
+        <v>2.807</v>
       </c>
       <c r="G128">
-        <v>1.619</v>
+        <v>2.562</v>
       </c>
       <c r="H128">
-        <v>1.205</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="I128">
-        <v>1.541</v>
+        <v>1.563</v>
       </c>
       <c r="J128">
-        <v>1.275</v>
-      </c>
-      <c r="U128" t="s">
-        <v>148</v>
-      </c>
-      <c r="V128">
+        <v>1.16</v>
+      </c>
+      <c r="V128" t="s">
+        <v>149</v>
+      </c>
+      <c r="W128">
         <v>0.505</v>
       </c>
     </row>
-    <row r="129" spans="1:22">
+    <row r="129" spans="1:23">
       <c r="A129" s="2">
-        <v>46138</v>
+        <v>46178</v>
       </c>
       <c r="B129">
         <v>17</v>
       </c>
       <c r="C129">
-        <v>1.588</v>
+        <v>1.7</v>
       </c>
       <c r="D129">
-        <v>1.891</v>
+        <v>2.005</v>
       </c>
       <c r="E129">
-        <v>4.036</v>
+        <v>2.861</v>
       </c>
       <c r="F129">
-        <v>2.495</v>
+        <v>2.469</v>
       </c>
       <c r="G129">
-        <v>1.379</v>
+        <v>2.107</v>
       </c>
       <c r="H129">
-        <v>1.335</v>
+        <v>0.964</v>
       </c>
       <c r="I129">
-        <v>1.027</v>
+        <v>1.543</v>
       </c>
       <c r="J129">
-        <v>0.849</v>
-      </c>
-      <c r="U129" t="s">
-        <v>149</v>
-      </c>
-      <c r="V129">
+        <v>0.974</v>
+      </c>
+      <c r="V129" t="s">
+        <v>150</v>
+      </c>
+      <c r="W129">
         <v>0.465</v>
       </c>
     </row>
-    <row r="130" spans="1:22">
+    <row r="130" spans="1:23">
       <c r="A130" s="2">
-        <v>46138</v>
+        <v>46178</v>
       </c>
       <c r="B130">
         <v>18</v>
       </c>
       <c r="C130">
-        <v>1.197</v>
+        <v>1.145</v>
       </c>
       <c r="D130">
-        <v>1.36</v>
+        <v>1.354</v>
       </c>
       <c r="E130">
-        <v>3.309</v>
+        <v>2.247</v>
       </c>
       <c r="F130">
-        <v>1.38</v>
+        <v>1.604</v>
       </c>
       <c r="G130">
-        <v>0.896</v>
+        <v>1.448</v>
       </c>
       <c r="H130">
-        <v>1.058</v>
+        <v>0.68</v>
       </c>
       <c r="I130">
-        <v>0.725</v>
+        <v>1.165</v>
       </c>
       <c r="J130">
-        <v>0.616</v>
-      </c>
-      <c r="U130" t="s">
-        <v>150</v>
-      </c>
-      <c r="V130">
+        <v>0.588</v>
+      </c>
+      <c r="V130" t="s">
+        <v>151</v>
+      </c>
+      <c r="W130">
         <v>0.242</v>
       </c>
     </row>
-    <row r="131" spans="1:22">
+    <row r="131" spans="1:23">
       <c r="A131" s="2">
-        <v>46138</v>
+        <v>46178</v>
       </c>
       <c r="B131">
         <v>19</v>
       </c>
       <c r="C131">
-        <v>0.465</v>
+        <v>0.618</v>
       </c>
       <c r="D131">
+        <v>0.713</v>
+      </c>
+      <c r="E131">
+        <v>1.34</v>
+      </c>
+      <c r="F131">
+        <v>0.792</v>
+      </c>
+      <c r="G131">
+        <v>0.8139999999999999</v>
+      </c>
+      <c r="H131">
         <v>0.541</v>
       </c>
-      <c r="E131">
-        <v>2.003</v>
-      </c>
-      <c r="F131">
-        <v>0.485</v>
-      </c>
-      <c r="G131">
-        <v>0.482</v>
-      </c>
-      <c r="H131">
-        <v>0.627</v>
-      </c>
       <c r="I131">
-        <v>0.472</v>
+        <v>0.643</v>
       </c>
       <c r="J131">
-        <v>0.288</v>
-      </c>
-      <c r="U131" t="s">
-        <v>151</v>
-      </c>
-      <c r="V131">
+        <v>0.275</v>
+      </c>
+      <c r="V131" t="s">
+        <v>152</v>
+      </c>
+      <c r="W131">
         <v>0.195</v>
       </c>
     </row>
-    <row r="132" spans="1:22">
+    <row r="132" spans="1:23">
       <c r="A132" s="2">
-        <v>46138</v>
+        <v>46178</v>
       </c>
       <c r="B132">
         <v>20</v>
       </c>
       <c r="C132">
-        <v>0.106</v>
+        <v>0.275</v>
       </c>
       <c r="D132">
-        <v>0.107</v>
+        <v>0.256</v>
       </c>
       <c r="E132">
-        <v>0.774</v>
+        <v>0.55</v>
       </c>
       <c r="F132">
-        <v>0.122</v>
+        <v>0.224</v>
       </c>
       <c r="G132">
+        <v>0.295</v>
+      </c>
+      <c r="H132">
+        <v>0.325</v>
+      </c>
+      <c r="I132">
+        <v>0.269</v>
+      </c>
+      <c r="J132">
         <v>0.129</v>
       </c>
-      <c r="H132">
-        <v>0.168</v>
-      </c>
-      <c r="I132">
-        <v>0.074</v>
-      </c>
-      <c r="J132">
-        <v>0.046</v>
-      </c>
-      <c r="U132" t="s">
-        <v>152</v>
-      </c>
-      <c r="V132">
+      <c r="V132" t="s">
+        <v>153</v>
+      </c>
+      <c r="W132">
         <v>0.25</v>
       </c>
     </row>
-    <row r="133" spans="1:22">
+    <row r="133" spans="1:23">
       <c r="A133" s="2">
-        <v>46138</v>
+        <v>46178</v>
       </c>
       <c r="B133">
         <v>21</v>
       </c>
       <c r="C133">
-        <v>0</v>
+        <v>0.046</v>
       </c>
       <c r="D133">
-        <v>0</v>
+        <v>0.051</v>
       </c>
       <c r="E133">
-        <v>0.316</v>
+        <v>0.099</v>
       </c>
       <c r="F133">
-        <v>0</v>
+        <v>0.037</v>
       </c>
       <c r="G133">
-        <v>0</v>
+        <v>0.056</v>
       </c>
       <c r="H133">
-        <v>0</v>
+        <v>0.053</v>
       </c>
       <c r="I133">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="J133">
-        <v>0.031</v>
-      </c>
-      <c r="U133" t="s">
-        <v>153</v>
-      </c>
-      <c r="V133">
+        <v>0</v>
+      </c>
+      <c r="V133" t="s">
+        <v>154</v>
+      </c>
+      <c r="W133">
         <v>0.25</v>
       </c>
     </row>
-    <row r="134" spans="1:22">
+    <row r="134" spans="1:23">
       <c r="A134" s="2">
-        <v>46138</v>
+        <v>46178</v>
       </c>
       <c r="B134">
         <v>22</v>
@@ -6049,7 +6055,7 @@
         <v>0</v>
       </c>
       <c r="E134">
-        <v>0.284</v>
+        <v>0</v>
       </c>
       <c r="F134">
         <v>0</v>
@@ -6064,18 +6070,18 @@
         <v>0</v>
       </c>
       <c r="J134">
-        <v>0.031</v>
-      </c>
-      <c r="U134" t="s">
-        <v>154</v>
-      </c>
-      <c r="V134">
+        <v>0.013</v>
+      </c>
+      <c r="V134" t="s">
+        <v>155</v>
+      </c>
+      <c r="W134">
         <v>0.109</v>
       </c>
     </row>
-    <row r="135" spans="1:22">
+    <row r="135" spans="1:23">
       <c r="A135" s="2">
-        <v>46138</v>
+        <v>46178</v>
       </c>
       <c r="B135">
         <v>23</v>
@@ -6087,7 +6093,7 @@
         <v>0</v>
       </c>
       <c r="E135">
-        <v>0.277</v>
+        <v>0</v>
       </c>
       <c r="F135">
         <v>0</v>
@@ -6102,18 +6108,18 @@
         <v>0</v>
       </c>
       <c r="J135">
-        <v>0.031</v>
-      </c>
-      <c r="U135" t="s">
-        <v>155</v>
-      </c>
-      <c r="V135">
+        <v>0.013</v>
+      </c>
+      <c r="V135" t="s">
+        <v>156</v>
+      </c>
+      <c r="W135">
         <v>0.112</v>
       </c>
     </row>
-    <row r="136" spans="1:22">
+    <row r="136" spans="1:23">
       <c r="A136" s="2">
-        <v>46138</v>
+        <v>46178</v>
       </c>
       <c r="B136">
         <v>24</v>
@@ -6125,7 +6131,7 @@
         <v>0</v>
       </c>
       <c r="E136">
-        <v>0.255</v>
+        <v>0</v>
       </c>
       <c r="F136">
         <v>0</v>
@@ -6140,18 +6146,18 @@
         <v>0</v>
       </c>
       <c r="J136">
-        <v>0.031</v>
-      </c>
-      <c r="U136" t="s">
-        <v>156</v>
-      </c>
-      <c r="V136">
+        <v>0.013</v>
+      </c>
+      <c r="V136" t="s">
+        <v>157</v>
+      </c>
+      <c r="W136">
         <v>0.112</v>
       </c>
     </row>
-    <row r="137" spans="1:22">
+    <row r="137" spans="1:23">
       <c r="A137" s="2">
-        <v>46139</v>
+        <v>46179</v>
       </c>
       <c r="B137">
         <v>1</v>
@@ -6163,7 +6169,7 @@
         <v>0</v>
       </c>
       <c r="E137">
-        <v>0.037</v>
+        <v>0</v>
       </c>
       <c r="F137">
         <v>0</v>
@@ -6178,18 +6184,18 @@
         <v>0</v>
       </c>
       <c r="J137">
-        <v>0.032</v>
-      </c>
-      <c r="U137" t="s">
-        <v>157</v>
-      </c>
-      <c r="V137">
+        <v>0.014</v>
+      </c>
+      <c r="V137" t="s">
+        <v>158</v>
+      </c>
+      <c r="W137">
         <v>0.01</v>
       </c>
     </row>
-    <row r="138" spans="1:22">
+    <row r="138" spans="1:23">
       <c r="A138" s="2">
-        <v>46139</v>
+        <v>46179</v>
       </c>
       <c r="B138">
         <v>2</v>
@@ -6201,7 +6207,7 @@
         <v>0</v>
       </c>
       <c r="E138">
-        <v>0.034</v>
+        <v>0</v>
       </c>
       <c r="F138">
         <v>0</v>
@@ -6216,18 +6222,18 @@
         <v>0</v>
       </c>
       <c r="J138">
-        <v>0.032</v>
-      </c>
-      <c r="U138" t="s">
-        <v>158</v>
-      </c>
-      <c r="V138">
+        <v>0.014</v>
+      </c>
+      <c r="V138" t="s">
+        <v>159</v>
+      </c>
+      <c r="W138">
         <v>0.01</v>
       </c>
     </row>
-    <row r="139" spans="1:22">
+    <row r="139" spans="1:23">
       <c r="A139" s="2">
-        <v>46139</v>
+        <v>46179</v>
       </c>
       <c r="B139">
         <v>3</v>
@@ -6239,7 +6245,7 @@
         <v>0</v>
       </c>
       <c r="E139">
-        <v>0.034</v>
+        <v>0</v>
       </c>
       <c r="F139">
         <v>0</v>
@@ -6254,18 +6260,18 @@
         <v>0</v>
       </c>
       <c r="J139">
-        <v>0.032</v>
-      </c>
-      <c r="U139" t="s">
-        <v>159</v>
-      </c>
-      <c r="V139">
+        <v>0.014</v>
+      </c>
+      <c r="V139" t="s">
+        <v>160</v>
+      </c>
+      <c r="W139">
         <v>0.015</v>
       </c>
     </row>
-    <row r="140" spans="1:22">
+    <row r="140" spans="1:23">
       <c r="A140" s="2">
-        <v>46139</v>
+        <v>46179</v>
       </c>
       <c r="B140">
         <v>4</v>
@@ -6277,7 +6283,7 @@
         <v>0</v>
       </c>
       <c r="E140">
-        <v>0.034</v>
+        <v>0</v>
       </c>
       <c r="F140">
         <v>0</v>
@@ -6292,18 +6298,18 @@
         <v>0</v>
       </c>
       <c r="J140">
-        <v>0.032</v>
-      </c>
-      <c r="U140" t="s">
-        <v>160</v>
-      </c>
-      <c r="V140">
+        <v>0.014</v>
+      </c>
+      <c r="V140" t="s">
+        <v>161</v>
+      </c>
+      <c r="W140">
         <v>0.015</v>
       </c>
     </row>
-    <row r="141" spans="1:22">
+    <row r="141" spans="1:23">
       <c r="A141" s="2">
-        <v>46139</v>
+        <v>46179</v>
       </c>
       <c r="B141">
         <v>5</v>
@@ -6315,7 +6321,7 @@
         <v>0</v>
       </c>
       <c r="E141">
-        <v>0.034</v>
+        <v>0</v>
       </c>
       <c r="F141">
         <v>0</v>
@@ -6330,18 +6336,18 @@
         <v>0</v>
       </c>
       <c r="J141">
-        <v>0.032</v>
-      </c>
-      <c r="U141" t="s">
-        <v>161</v>
-      </c>
-      <c r="V141">
+        <v>0.014</v>
+      </c>
+      <c r="V141" t="s">
+        <v>162</v>
+      </c>
+      <c r="W141">
         <v>0.015</v>
       </c>
     </row>
-    <row r="142" spans="1:22">
+    <row r="142" spans="1:23">
       <c r="A142" s="2">
-        <v>46139</v>
+        <v>46179</v>
       </c>
       <c r="B142">
         <v>6</v>
@@ -6353,13 +6359,13 @@
         <v>0</v>
       </c>
       <c r="E142">
-        <v>0.036</v>
+        <v>0</v>
       </c>
       <c r="F142">
-        <v>0</v>
+        <v>0.035</v>
       </c>
       <c r="G142">
-        <v>0</v>
+        <v>0.012</v>
       </c>
       <c r="H142">
         <v>0</v>
@@ -6368,588 +6374,588 @@
         <v>0</v>
       </c>
       <c r="J142">
-        <v>0.032</v>
-      </c>
-      <c r="U142" t="s">
-        <v>162</v>
-      </c>
-      <c r="V142">
+        <v>0.038</v>
+      </c>
+      <c r="V142" t="s">
+        <v>163</v>
+      </c>
+      <c r="W142">
         <v>0.015</v>
       </c>
     </row>
-    <row r="143" spans="1:22">
+    <row r="143" spans="1:23">
       <c r="A143" s="2">
-        <v>46139</v>
+        <v>46179</v>
       </c>
       <c r="B143">
         <v>7</v>
       </c>
       <c r="C143">
-        <v>0.03</v>
+        <v>0.075</v>
       </c>
       <c r="D143">
-        <v>0.024</v>
+        <v>0.104</v>
       </c>
       <c r="E143">
-        <v>0.051</v>
+        <v>0.173</v>
       </c>
       <c r="F143">
-        <v>0.163</v>
+        <v>0.331</v>
       </c>
       <c r="G143">
-        <v>0.058</v>
+        <v>0.196</v>
       </c>
       <c r="H143">
-        <v>0.041</v>
+        <v>0.145</v>
       </c>
       <c r="I143">
-        <v>0.042</v>
+        <v>0.144</v>
       </c>
       <c r="J143">
-        <v>0.051</v>
-      </c>
-      <c r="U143" t="s">
-        <v>163</v>
-      </c>
-      <c r="V143">
+        <v>0.104</v>
+      </c>
+      <c r="V143" t="s">
+        <v>164</v>
+      </c>
+      <c r="W143">
         <v>0.01</v>
       </c>
     </row>
-    <row r="144" spans="1:22">
+    <row r="144" spans="1:23">
       <c r="A144" s="2">
-        <v>46139</v>
+        <v>46179</v>
       </c>
       <c r="B144">
         <v>8</v>
       </c>
       <c r="C144">
-        <v>0.455</v>
+        <v>0.446</v>
       </c>
       <c r="D144">
-        <v>0.544</v>
+        <v>0.414</v>
       </c>
       <c r="E144">
-        <v>0.589</v>
+        <v>0.739</v>
       </c>
       <c r="F144">
-        <v>0.636</v>
+        <v>1.111</v>
       </c>
       <c r="G144">
-        <v>0.578</v>
+        <v>0.571</v>
       </c>
       <c r="H144">
-        <v>0.393</v>
+        <v>0.542</v>
       </c>
       <c r="I144">
-        <v>0.451</v>
+        <v>0.521</v>
       </c>
       <c r="J144">
-        <v>0.35</v>
-      </c>
-      <c r="U144" t="s">
-        <v>164</v>
-      </c>
-      <c r="V144">
+        <v>0.487</v>
+      </c>
+      <c r="V144" t="s">
+        <v>165</v>
+      </c>
+      <c r="W144">
         <v>0.038</v>
       </c>
     </row>
-    <row r="145" spans="1:22">
+    <row r="145" spans="1:23">
       <c r="A145" s="2">
-        <v>46139</v>
+        <v>46179</v>
       </c>
       <c r="B145">
         <v>9</v>
       </c>
       <c r="C145">
-        <v>1.222</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="D145">
-        <v>1.524</v>
+        <v>1.044</v>
       </c>
       <c r="E145">
-        <v>2.168</v>
+        <v>1.671</v>
       </c>
       <c r="F145">
-        <v>1.9</v>
+        <v>2.13</v>
       </c>
       <c r="G145">
-        <v>0.968</v>
+        <v>1.337</v>
       </c>
       <c r="H145">
-        <v>0.998</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="I145">
-        <v>0.9340000000000001</v>
+        <v>0.772</v>
       </c>
       <c r="J145">
-        <v>0.878</v>
-      </c>
-      <c r="U145" t="s">
-        <v>165</v>
-      </c>
-      <c r="V145">
+        <v>0.956</v>
+      </c>
+      <c r="V145" t="s">
+        <v>166</v>
+      </c>
+      <c r="W145">
         <v>0.056</v>
       </c>
     </row>
-    <row r="146" spans="1:22">
+    <row r="146" spans="1:23">
       <c r="A146" s="2">
-        <v>46139</v>
+        <v>46179</v>
       </c>
       <c r="B146">
         <v>10</v>
       </c>
       <c r="C146">
-        <v>2.16</v>
+        <v>1.612</v>
       </c>
       <c r="D146">
-        <v>2.545</v>
+        <v>1.786</v>
       </c>
       <c r="E146">
-        <v>3.235</v>
+        <v>2.518</v>
       </c>
       <c r="F146">
-        <v>2.605</v>
+        <v>3.183</v>
       </c>
       <c r="G146">
-        <v>1.818</v>
+        <v>2.209</v>
       </c>
       <c r="H146">
-        <v>1.493</v>
+        <v>1.188</v>
       </c>
       <c r="I146">
-        <v>1.536</v>
+        <v>1.213</v>
       </c>
       <c r="J146">
-        <v>1.266</v>
-      </c>
-      <c r="U146" t="s">
-        <v>166</v>
-      </c>
-      <c r="V146">
+        <v>1.264</v>
+      </c>
+      <c r="V146" t="s">
+        <v>167</v>
+      </c>
+      <c r="W146">
         <v>0.462</v>
       </c>
     </row>
-    <row r="147" spans="1:22">
+    <row r="147" spans="1:23">
       <c r="A147" s="2">
-        <v>46139</v>
+        <v>46179</v>
       </c>
       <c r="B147">
         <v>11</v>
       </c>
       <c r="C147">
-        <v>2.899</v>
+        <v>2.014</v>
       </c>
       <c r="D147">
-        <v>3.325</v>
+        <v>2.284</v>
       </c>
       <c r="E147">
-        <v>4.152</v>
+        <v>2.962</v>
       </c>
       <c r="F147">
-        <v>2.845</v>
+        <v>2.926</v>
       </c>
       <c r="G147">
-        <v>1.684</v>
+        <v>2.763</v>
       </c>
       <c r="H147">
-        <v>1.306</v>
+        <v>1.156</v>
       </c>
       <c r="I147">
-        <v>1.605</v>
+        <v>1.512</v>
       </c>
       <c r="J147">
-        <v>1.504</v>
-      </c>
-      <c r="U147" t="s">
-        <v>167</v>
-      </c>
-      <c r="V147">
+        <v>1.567</v>
+      </c>
+      <c r="V147" t="s">
+        <v>168</v>
+      </c>
+      <c r="W147">
         <v>0.314</v>
       </c>
     </row>
-    <row r="148" spans="1:22">
+    <row r="148" spans="1:23">
       <c r="A148" s="2">
-        <v>46139</v>
+        <v>46179</v>
       </c>
       <c r="B148">
         <v>12</v>
       </c>
       <c r="C148">
-        <v>3.232</v>
+        <v>2.365</v>
       </c>
       <c r="D148">
-        <v>3.629</v>
+        <v>2.536</v>
       </c>
       <c r="E148">
-        <v>4.404</v>
+        <v>3.46</v>
       </c>
       <c r="F148">
-        <v>3.437</v>
+        <v>1.854</v>
       </c>
       <c r="G148">
-        <v>1.739</v>
+        <v>3.102</v>
       </c>
       <c r="H148">
-        <v>0.993</v>
+        <v>1.074</v>
       </c>
       <c r="I148">
-        <v>1.598</v>
+        <v>1.563</v>
       </c>
       <c r="J148">
-        <v>1.593</v>
-      </c>
-      <c r="U148" t="s">
-        <v>168</v>
-      </c>
-      <c r="V148">
+        <v>1.533</v>
+      </c>
+      <c r="V148" t="s">
+        <v>169</v>
+      </c>
+      <c r="W148">
         <v>0.43</v>
       </c>
     </row>
-    <row r="149" spans="1:22">
+    <row r="149" spans="1:23">
       <c r="A149" s="2">
-        <v>46139</v>
+        <v>46179</v>
       </c>
       <c r="B149">
         <v>13</v>
       </c>
       <c r="C149">
-        <v>3.232</v>
+        <v>2.428</v>
       </c>
       <c r="D149">
-        <v>3.638</v>
+        <v>2.795</v>
       </c>
       <c r="E149">
-        <v>4.037</v>
+        <v>3.486</v>
       </c>
       <c r="F149">
-        <v>3.499</v>
+        <v>1.77</v>
       </c>
       <c r="G149">
-        <v>2.029</v>
+        <v>3.273</v>
       </c>
       <c r="H149">
-        <v>1.066</v>
+        <v>1.086</v>
       </c>
       <c r="I149">
-        <v>1.588</v>
+        <v>1.563</v>
       </c>
       <c r="J149">
-        <v>1.655</v>
-      </c>
-      <c r="U149" t="s">
-        <v>169</v>
-      </c>
-      <c r="V149">
+        <v>1.561</v>
+      </c>
+      <c r="V149" t="s">
+        <v>170</v>
+      </c>
+      <c r="W149">
         <v>0.734</v>
       </c>
     </row>
-    <row r="150" spans="1:22">
+    <row r="150" spans="1:23">
       <c r="A150" s="2">
-        <v>46139</v>
+        <v>46179</v>
       </c>
       <c r="B150">
         <v>14</v>
       </c>
       <c r="C150">
-        <v>3.158</v>
+        <v>2.376</v>
       </c>
       <c r="D150">
-        <v>3.556</v>
+        <v>2.833</v>
       </c>
       <c r="E150">
-        <v>3.826</v>
+        <v>3.451</v>
       </c>
       <c r="F150">
-        <v>3.568</v>
+        <v>3.256</v>
       </c>
       <c r="G150">
-        <v>2.173</v>
+        <v>3.326</v>
       </c>
       <c r="H150">
-        <v>1.089</v>
+        <v>1.06</v>
       </c>
       <c r="I150">
-        <v>1.588</v>
+        <v>1.563</v>
       </c>
       <c r="J150">
-        <v>1.464</v>
-      </c>
-      <c r="U150" t="s">
-        <v>170</v>
-      </c>
-      <c r="V150">
+        <v>1.52</v>
+      </c>
+      <c r="V150" t="s">
+        <v>171</v>
+      </c>
+      <c r="W150">
         <v>0.5669999999999999</v>
       </c>
     </row>
-    <row r="151" spans="1:22">
+    <row r="151" spans="1:23">
       <c r="A151" s="2">
-        <v>46139</v>
+        <v>46179</v>
       </c>
       <c r="B151">
         <v>15</v>
       </c>
       <c r="C151">
-        <v>3.133</v>
+        <v>2.269</v>
       </c>
       <c r="D151">
-        <v>3.592</v>
+        <v>2.632</v>
       </c>
       <c r="E151">
-        <v>3.971</v>
+        <v>3.548</v>
       </c>
       <c r="F151">
-        <v>3.524</v>
+        <v>3.378</v>
       </c>
       <c r="G151">
-        <v>1.766</v>
+        <v>3.313</v>
       </c>
       <c r="H151">
-        <v>1.011</v>
+        <v>1.02</v>
       </c>
       <c r="I151">
-        <v>1.579</v>
+        <v>1.563</v>
       </c>
       <c r="J151">
-        <v>1.567</v>
-      </c>
-      <c r="U151" t="s">
-        <v>171</v>
-      </c>
-      <c r="V151">
+        <v>1.368</v>
+      </c>
+      <c r="V151" t="s">
+        <v>172</v>
+      </c>
+      <c r="W151">
         <v>0.41</v>
       </c>
     </row>
-    <row r="152" spans="1:22">
+    <row r="152" spans="1:23">
       <c r="A152" s="2">
-        <v>46139</v>
+        <v>46179</v>
       </c>
       <c r="B152">
         <v>16</v>
       </c>
       <c r="C152">
-        <v>2.778</v>
+        <v>1.91</v>
       </c>
       <c r="D152">
-        <v>3.388</v>
+        <v>2.338</v>
       </c>
       <c r="E152">
-        <v>4.18</v>
+        <v>3.258</v>
       </c>
       <c r="F152">
-        <v>2.99</v>
+        <v>3.017</v>
       </c>
       <c r="G152">
-        <v>1.531</v>
+        <v>2.868</v>
       </c>
       <c r="H152">
-        <v>0.987</v>
+        <v>0.913</v>
       </c>
       <c r="I152">
-        <v>1.579</v>
+        <v>1.563</v>
       </c>
       <c r="J152">
-        <v>1.36</v>
-      </c>
-      <c r="U152" t="s">
-        <v>172</v>
-      </c>
-      <c r="V152">
+        <v>1.178</v>
+      </c>
+      <c r="V152" t="s">
+        <v>173</v>
+      </c>
+      <c r="W152">
         <v>0.289</v>
       </c>
     </row>
-    <row r="153" spans="1:22">
+    <row r="153" spans="1:23">
       <c r="A153" s="2">
-        <v>46139</v>
+        <v>46179</v>
       </c>
       <c r="B153">
         <v>17</v>
       </c>
       <c r="C153">
-        <v>2.192</v>
+        <v>1.651</v>
       </c>
       <c r="D153">
-        <v>2.772</v>
+        <v>1.93</v>
       </c>
       <c r="E153">
-        <v>3.837</v>
+        <v>2.684</v>
       </c>
       <c r="F153">
-        <v>2.263</v>
+        <v>2.507</v>
       </c>
       <c r="G153">
-        <v>1.645</v>
+        <v>2.231</v>
       </c>
       <c r="H153">
-        <v>1.081</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="I153">
-        <v>1.56</v>
+        <v>1.543</v>
       </c>
       <c r="J153">
-        <v>1.095</v>
-      </c>
-      <c r="U153" t="s">
-        <v>173</v>
-      </c>
-      <c r="V153">
+        <v>1.009</v>
+      </c>
+      <c r="V153" t="s">
+        <v>174</v>
+      </c>
+      <c r="W153">
         <v>0.336</v>
       </c>
     </row>
-    <row r="154" spans="1:22">
+    <row r="154" spans="1:23">
       <c r="A154" s="2">
-        <v>46139</v>
+        <v>46179</v>
       </c>
       <c r="B154">
         <v>18</v>
       </c>
       <c r="C154">
-        <v>1.444</v>
+        <v>1.065</v>
       </c>
       <c r="D154">
-        <v>1.97</v>
+        <v>1.353</v>
       </c>
       <c r="E154">
-        <v>3.14</v>
+        <v>2.197</v>
       </c>
       <c r="F154">
-        <v>1.049</v>
+        <v>1.66</v>
       </c>
       <c r="G154">
-        <v>0.953</v>
+        <v>1.476</v>
       </c>
       <c r="H154">
-        <v>1.03</v>
+        <v>0.68</v>
       </c>
       <c r="I154">
-        <v>1.175</v>
+        <v>1.148</v>
       </c>
       <c r="J154">
-        <v>0.625</v>
-      </c>
-      <c r="U154" t="s">
-        <v>174</v>
-      </c>
-      <c r="V154">
+        <v>0.596</v>
+      </c>
+      <c r="V154" t="s">
+        <v>175</v>
+      </c>
+      <c r="W154">
         <v>0.244</v>
       </c>
     </row>
-    <row r="155" spans="1:22">
+    <row r="155" spans="1:23">
       <c r="A155" s="2">
-        <v>46139</v>
+        <v>46179</v>
       </c>
       <c r="B155">
         <v>19</v>
       </c>
       <c r="C155">
-        <v>0.621</v>
+        <v>0.593</v>
       </c>
       <c r="D155">
-        <v>0.84</v>
+        <v>0.727</v>
       </c>
       <c r="E155">
-        <v>2.056</v>
+        <v>1.276</v>
       </c>
       <c r="F155">
-        <v>0.4</v>
+        <v>0.781</v>
       </c>
       <c r="G155">
-        <v>0.425</v>
+        <v>0.822</v>
       </c>
       <c r="H155">
-        <v>0.627</v>
+        <v>0.541</v>
       </c>
       <c r="I155">
-        <v>0.62</v>
+        <v>0.661</v>
       </c>
       <c r="J155">
-        <v>0.331</v>
-      </c>
-      <c r="U155" t="s">
-        <v>175</v>
-      </c>
-      <c r="V155">
+        <v>0.294</v>
+      </c>
+      <c r="V155" t="s">
+        <v>176</v>
+      </c>
+      <c r="W155">
         <v>0.197</v>
       </c>
     </row>
-    <row r="156" spans="1:22">
+    <row r="156" spans="1:23">
       <c r="A156" s="2">
-        <v>46139</v>
+        <v>46179</v>
       </c>
       <c r="B156">
         <v>20</v>
       </c>
       <c r="C156">
-        <v>0.136</v>
+        <v>0.301</v>
       </c>
       <c r="D156">
-        <v>0.157</v>
+        <v>0.256</v>
       </c>
       <c r="E156">
-        <v>0.6879999999999999</v>
+        <v>0.574</v>
       </c>
       <c r="F156">
-        <v>0.073</v>
+        <v>0.239</v>
       </c>
       <c r="G156">
-        <v>0.08799999999999999</v>
+        <v>0.294</v>
       </c>
       <c r="H156">
-        <v>0.145</v>
+        <v>0.338</v>
       </c>
       <c r="I156">
-        <v>0.112</v>
+        <v>0.328</v>
       </c>
       <c r="J156">
-        <v>0.064</v>
-      </c>
-      <c r="U156" t="s">
-        <v>176</v>
-      </c>
-      <c r="V156">
+        <v>0.119</v>
+      </c>
+      <c r="V156" t="s">
+        <v>177</v>
+      </c>
+      <c r="W156">
         <v>0.252</v>
       </c>
     </row>
-    <row r="157" spans="1:22">
+    <row r="157" spans="1:23">
       <c r="A157" s="2">
-        <v>46139</v>
+        <v>46179</v>
       </c>
       <c r="B157">
         <v>21</v>
       </c>
       <c r="C157">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="D157">
-        <v>0</v>
+        <v>0.065</v>
       </c>
       <c r="E157">
-        <v>0.299</v>
+        <v>0.106</v>
       </c>
       <c r="F157">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="G157">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="H157">
-        <v>0</v>
+        <v>0.053</v>
       </c>
       <c r="I157">
-        <v>0</v>
+        <v>0.042</v>
       </c>
       <c r="J157">
-        <v>0.031</v>
-      </c>
-      <c r="U157" t="s">
-        <v>177</v>
-      </c>
-      <c r="V157">
+        <v>0</v>
+      </c>
+      <c r="V157" t="s">
+        <v>178</v>
+      </c>
+      <c r="W157">
         <v>0.252</v>
       </c>
     </row>
-    <row r="158" spans="1:22">
+    <row r="158" spans="1:23">
       <c r="A158" s="2">
-        <v>46139</v>
+        <v>46179</v>
       </c>
       <c r="B158">
         <v>22</v>
@@ -6961,7 +6967,7 @@
         <v>0</v>
       </c>
       <c r="E158">
-        <v>0.295</v>
+        <v>0</v>
       </c>
       <c r="F158">
         <v>0</v>
@@ -6976,18 +6982,18 @@
         <v>0</v>
       </c>
       <c r="J158">
-        <v>0.031</v>
-      </c>
-      <c r="U158" t="s">
-        <v>178</v>
-      </c>
-      <c r="V158">
+        <v>0</v>
+      </c>
+      <c r="V158" t="s">
+        <v>179</v>
+      </c>
+      <c r="W158">
         <v>0.112</v>
       </c>
     </row>
-    <row r="159" spans="1:22">
+    <row r="159" spans="1:23">
       <c r="A159" s="2">
-        <v>46139</v>
+        <v>46179</v>
       </c>
       <c r="B159">
         <v>23</v>
@@ -6999,7 +7005,7 @@
         <v>0</v>
       </c>
       <c r="E159">
-        <v>0.273</v>
+        <v>0</v>
       </c>
       <c r="F159">
         <v>0</v>
@@ -7014,18 +7020,18 @@
         <v>0</v>
       </c>
       <c r="J159">
-        <v>0.031</v>
-      </c>
-      <c r="U159" t="s">
-        <v>179</v>
-      </c>
-      <c r="V159">
+        <v>0</v>
+      </c>
+      <c r="V159" t="s">
+        <v>180</v>
+      </c>
+      <c r="W159">
         <v>0.112</v>
       </c>
     </row>
-    <row r="160" spans="1:22">
+    <row r="160" spans="1:23">
       <c r="A160" s="2">
-        <v>46139</v>
+        <v>46179</v>
       </c>
       <c r="B160">
         <v>24</v>
@@ -7037,7 +7043,7 @@
         <v>0</v>
       </c>
       <c r="E160">
-        <v>0.243</v>
+        <v>0</v>
       </c>
       <c r="F160">
         <v>0</v>
@@ -7052,18 +7058,18 @@
         <v>0</v>
       </c>
       <c r="J160">
-        <v>0.031</v>
-      </c>
-      <c r="U160" t="s">
-        <v>180</v>
-      </c>
-      <c r="V160">
+        <v>0.013</v>
+      </c>
+      <c r="V160" t="s">
+        <v>181</v>
+      </c>
+      <c r="W160">
         <v>0.112</v>
       </c>
     </row>
-    <row r="161" spans="1:22">
+    <row r="161" spans="1:23">
       <c r="A161" s="2">
-        <v>46140</v>
+        <v>46180</v>
       </c>
       <c r="B161">
         <v>1</v>
@@ -7075,7 +7081,7 @@
         <v>0</v>
       </c>
       <c r="E161">
-        <v>0.035</v>
+        <v>0</v>
       </c>
       <c r="F161">
         <v>0</v>
@@ -7090,18 +7096,18 @@
         <v>0</v>
       </c>
       <c r="J161">
-        <v>0.032</v>
-      </c>
-      <c r="U161" t="s">
-        <v>181</v>
-      </c>
-      <c r="V161">
+        <v>0.014</v>
+      </c>
+      <c r="V161" t="s">
+        <v>182</v>
+      </c>
+      <c r="W161">
         <v>0.01</v>
       </c>
     </row>
-    <row r="162" spans="1:22">
+    <row r="162" spans="1:23">
       <c r="A162" s="2">
-        <v>46140</v>
+        <v>46180</v>
       </c>
       <c r="B162">
         <v>2</v>
@@ -7113,7 +7119,7 @@
         <v>0</v>
       </c>
       <c r="E162">
-        <v>0.034</v>
+        <v>0</v>
       </c>
       <c r="F162">
         <v>0</v>
@@ -7128,18 +7134,18 @@
         <v>0</v>
       </c>
       <c r="J162">
-        <v>0.032</v>
-      </c>
-      <c r="U162" t="s">
-        <v>182</v>
-      </c>
-      <c r="V162">
+        <v>0.014</v>
+      </c>
+      <c r="V162" t="s">
+        <v>183</v>
+      </c>
+      <c r="W162">
         <v>0.01</v>
       </c>
     </row>
-    <row r="163" spans="1:22">
+    <row r="163" spans="1:23">
       <c r="A163" s="2">
-        <v>46140</v>
+        <v>46180</v>
       </c>
       <c r="B163">
         <v>3</v>
@@ -7151,7 +7157,7 @@
         <v>0</v>
       </c>
       <c r="E163">
-        <v>0.034</v>
+        <v>0</v>
       </c>
       <c r="F163">
         <v>0</v>
@@ -7166,18 +7172,18 @@
         <v>0</v>
       </c>
       <c r="J163">
-        <v>0.032</v>
-      </c>
-      <c r="U163" t="s">
-        <v>183</v>
-      </c>
-      <c r="V163">
+        <v>0.014</v>
+      </c>
+      <c r="V163" t="s">
+        <v>184</v>
+      </c>
+      <c r="W163">
         <v>0.01</v>
       </c>
     </row>
-    <row r="164" spans="1:22">
+    <row r="164" spans="1:23">
       <c r="A164" s="2">
-        <v>46140</v>
+        <v>46180</v>
       </c>
       <c r="B164">
         <v>4</v>
@@ -7189,7 +7195,7 @@
         <v>0</v>
       </c>
       <c r="E164">
-        <v>0.035</v>
+        <v>0</v>
       </c>
       <c r="F164">
         <v>0</v>
@@ -7204,18 +7210,18 @@
         <v>0</v>
       </c>
       <c r="J164">
-        <v>0.032</v>
-      </c>
-      <c r="U164" t="s">
-        <v>184</v>
-      </c>
-      <c r="V164">
+        <v>0.014</v>
+      </c>
+      <c r="V164" t="s">
+        <v>185</v>
+      </c>
+      <c r="W164">
         <v>0.01</v>
       </c>
     </row>
-    <row r="165" spans="1:22">
+    <row r="165" spans="1:23">
       <c r="A165" s="2">
-        <v>46140</v>
+        <v>46180</v>
       </c>
       <c r="B165">
         <v>5</v>
@@ -7227,7 +7233,7 @@
         <v>0</v>
       </c>
       <c r="E165">
-        <v>0.035</v>
+        <v>0</v>
       </c>
       <c r="F165">
         <v>0</v>
@@ -7242,18 +7248,18 @@
         <v>0</v>
       </c>
       <c r="J165">
-        <v>0.032</v>
-      </c>
-      <c r="U165" t="s">
-        <v>185</v>
-      </c>
-      <c r="V165">
+        <v>0.014</v>
+      </c>
+      <c r="V165" t="s">
+        <v>186</v>
+      </c>
+      <c r="W165">
         <v>0.01</v>
       </c>
     </row>
-    <row r="166" spans="1:22">
+    <row r="166" spans="1:23">
       <c r="A166" s="2">
-        <v>46140</v>
+        <v>46180</v>
       </c>
       <c r="B166">
         <v>6</v>
@@ -7265,179 +7271,179 @@
         <v>0</v>
       </c>
       <c r="E166">
+        <v>0</v>
+      </c>
+      <c r="F166">
+        <v>0.035</v>
+      </c>
+      <c r="G166">
+        <v>0.012</v>
+      </c>
+      <c r="H166">
+        <v>0</v>
+      </c>
+      <c r="I166">
+        <v>0</v>
+      </c>
+      <c r="J166">
         <v>0.038</v>
       </c>
-      <c r="F166">
-        <v>0</v>
-      </c>
-      <c r="G166">
-        <v>0</v>
-      </c>
-      <c r="H166">
-        <v>0</v>
-      </c>
-      <c r="I166">
-        <v>0</v>
-      </c>
-      <c r="J166">
-        <v>0.032</v>
-      </c>
-      <c r="U166" t="s">
-        <v>186</v>
-      </c>
-      <c r="V166">
+      <c r="V166" t="s">
+        <v>187</v>
+      </c>
+      <c r="W166">
         <v>0.01</v>
       </c>
     </row>
-    <row r="167" spans="1:22">
+    <row r="167" spans="1:23">
       <c r="A167" s="2">
-        <v>46140</v>
+        <v>46180</v>
       </c>
       <c r="B167">
         <v>7</v>
       </c>
       <c r="C167">
-        <v>0.028</v>
+        <v>0.075</v>
       </c>
       <c r="D167">
-        <v>0.024</v>
+        <v>0.102</v>
       </c>
       <c r="E167">
-        <v>0.052</v>
+        <v>0.179</v>
       </c>
       <c r="F167">
-        <v>0.097</v>
+        <v>0.336</v>
       </c>
       <c r="G167">
-        <v>0.04</v>
+        <v>0.196</v>
       </c>
       <c r="H167">
-        <v>0.034</v>
+        <v>0.203</v>
       </c>
       <c r="I167">
-        <v>0.025</v>
+        <v>0.183</v>
       </c>
       <c r="J167">
-        <v>0.051</v>
-      </c>
-      <c r="U167" t="s">
-        <v>187</v>
-      </c>
-      <c r="V167">
+        <v>0.075</v>
+      </c>
+      <c r="V167" t="s">
+        <v>188</v>
+      </c>
+      <c r="W167">
         <v>0.01</v>
       </c>
     </row>
-    <row r="168" spans="1:22">
+    <row r="168" spans="1:23">
       <c r="A168" s="2">
-        <v>46140</v>
+        <v>46180</v>
       </c>
       <c r="B168">
         <v>8</v>
       </c>
       <c r="C168">
-        <v>0.42</v>
+        <v>0.451</v>
       </c>
       <c r="D168">
-        <v>0.433</v>
+        <v>0.431</v>
       </c>
       <c r="E168">
-        <v>0.432</v>
+        <v>0.747</v>
       </c>
       <c r="F168">
-        <v>0.581</v>
+        <v>1.134</v>
       </c>
       <c r="G168">
-        <v>0.343</v>
+        <v>0.591</v>
       </c>
       <c r="H168">
-        <v>0.347</v>
+        <v>0.582</v>
       </c>
       <c r="I168">
-        <v>0.2</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="J168">
-        <v>0.218</v>
-      </c>
-      <c r="U168" t="s">
-        <v>188</v>
-      </c>
-      <c r="V168">
+        <v>0.388</v>
+      </c>
+      <c r="V168" t="s">
+        <v>189</v>
+      </c>
+      <c r="W168">
         <v>0.194</v>
       </c>
     </row>
-    <row r="169" spans="1:22">
+    <row r="169" spans="1:23">
       <c r="A169" s="2">
-        <v>46140</v>
+        <v>46180</v>
       </c>
       <c r="B169">
         <v>9</v>
       </c>
       <c r="C169">
-        <v>1.064</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="D169">
-        <v>1.276</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="E169">
-        <v>1.931</v>
+        <v>1.803</v>
       </c>
       <c r="F169">
-        <v>1.33</v>
+        <v>2.045</v>
       </c>
       <c r="G169">
-        <v>0.719</v>
+        <v>1.394</v>
       </c>
       <c r="H169">
-        <v>0.9330000000000001</v>
+        <v>1.018</v>
       </c>
       <c r="I169">
-        <v>0.584</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="J169">
-        <v>0.595</v>
-      </c>
-      <c r="U169" t="s">
-        <v>189</v>
-      </c>
-      <c r="V169">
+        <v>0.663</v>
+      </c>
+      <c r="V169" t="s">
+        <v>190</v>
+      </c>
+      <c r="W169">
         <v>0.212</v>
       </c>
     </row>
-    <row r="170" spans="1:22">
+    <row r="170" spans="1:23">
       <c r="A170" s="2">
-        <v>46140</v>
+        <v>46180</v>
       </c>
       <c r="B170">
         <v>10</v>
       </c>
       <c r="C170">
-        <v>2.105</v>
+        <v>1.382</v>
       </c>
       <c r="D170">
-        <v>2.32</v>
+        <v>1.636</v>
       </c>
       <c r="E170">
-        <v>2.605</v>
+        <v>2.616</v>
       </c>
       <c r="F170">
-        <v>2.255</v>
+        <v>2.72</v>
       </c>
       <c r="G170">
-        <v>1.443</v>
+        <v>2.039</v>
       </c>
       <c r="H170">
-        <v>1.439</v>
+        <v>1.257</v>
       </c>
       <c r="I170">
-        <v>0.882</v>
+        <v>1.147</v>
       </c>
       <c r="J170">
-        <v>0.876</v>
-      </c>
-      <c r="U170" t="s">
-        <v>190</v>
-      </c>
-      <c r="V170">
+        <v>1.002</v>
+      </c>
+      <c r="V170" t="s">
+        <v>191</v>
+      </c>
+      <c r="W170">
         <v>1.081</v>
       </c>
     </row>

--- a/Forecast.xlsx
+++ b/Forecast.xlsx
@@ -85,511 +85,511 @@
     <t>Prediction_3D_Steel</t>
   </si>
   <si>
-    <t>31.05.202610</t>
-  </si>
-  <si>
-    <t>31.05.202611</t>
-  </si>
-  <si>
-    <t>31.05.202612</t>
-  </si>
-  <si>
-    <t>31.05.202613</t>
-  </si>
-  <si>
-    <t>31.05.202614</t>
-  </si>
-  <si>
-    <t>31.05.202615</t>
-  </si>
-  <si>
-    <t>31.05.202616</t>
-  </si>
-  <si>
-    <t>31.05.202617</t>
-  </si>
-  <si>
-    <t>31.05.202618</t>
-  </si>
-  <si>
-    <t>31.05.202619</t>
-  </si>
-  <si>
-    <t>31.05.202620</t>
-  </si>
-  <si>
-    <t>31.05.202621</t>
-  </si>
-  <si>
-    <t>31.05.202622</t>
-  </si>
-  <si>
-    <t>31.05.202623</t>
-  </si>
-  <si>
-    <t>31.05.202624</t>
-  </si>
-  <si>
-    <t>01.06.20261</t>
-  </si>
-  <si>
-    <t>01.06.20262</t>
-  </si>
-  <si>
-    <t>01.06.20263</t>
-  </si>
-  <si>
-    <t>01.06.20264</t>
-  </si>
-  <si>
-    <t>01.06.20265</t>
-  </si>
-  <si>
-    <t>01.06.20266</t>
-  </si>
-  <si>
-    <t>01.06.20267</t>
-  </si>
-  <si>
-    <t>01.06.20268</t>
-  </si>
-  <si>
-    <t>01.06.20269</t>
-  </si>
-  <si>
-    <t>01.06.202610</t>
-  </si>
-  <si>
-    <t>01.06.202611</t>
-  </si>
-  <si>
-    <t>01.06.202612</t>
-  </si>
-  <si>
-    <t>01.06.202613</t>
-  </si>
-  <si>
-    <t>01.06.202614</t>
-  </si>
-  <si>
-    <t>01.06.202615</t>
-  </si>
-  <si>
-    <t>01.06.202616</t>
-  </si>
-  <si>
-    <t>01.06.202617</t>
-  </si>
-  <si>
-    <t>01.06.202618</t>
-  </si>
-  <si>
-    <t>01.06.202619</t>
-  </si>
-  <si>
-    <t>01.06.202620</t>
-  </si>
-  <si>
-    <t>01.06.202621</t>
-  </si>
-  <si>
-    <t>01.06.202622</t>
-  </si>
-  <si>
-    <t>01.06.202623</t>
-  </si>
-  <si>
-    <t>01.06.202624</t>
-  </si>
-  <si>
-    <t>02.06.20261</t>
-  </si>
-  <si>
-    <t>02.06.20262</t>
-  </si>
-  <si>
-    <t>02.06.20263</t>
-  </si>
-  <si>
-    <t>02.06.20264</t>
-  </si>
-  <si>
-    <t>02.06.20265</t>
-  </si>
-  <si>
-    <t>02.06.20266</t>
-  </si>
-  <si>
-    <t>02.06.20267</t>
-  </si>
-  <si>
-    <t>02.06.20268</t>
-  </si>
-  <si>
-    <t>02.06.20269</t>
-  </si>
-  <si>
-    <t>02.06.202610</t>
-  </si>
-  <si>
-    <t>02.06.202611</t>
-  </si>
-  <si>
-    <t>02.06.202612</t>
-  </si>
-  <si>
-    <t>02.06.202613</t>
-  </si>
-  <si>
-    <t>02.06.202614</t>
-  </si>
-  <si>
-    <t>02.06.202615</t>
-  </si>
-  <si>
-    <t>02.06.202616</t>
-  </si>
-  <si>
-    <t>02.06.202617</t>
-  </si>
-  <si>
-    <t>02.06.202618</t>
-  </si>
-  <si>
-    <t>02.06.202619</t>
-  </si>
-  <si>
-    <t>02.06.202620</t>
-  </si>
-  <si>
-    <t>02.06.202621</t>
-  </si>
-  <si>
-    <t>02.06.202622</t>
-  </si>
-  <si>
-    <t>02.06.202623</t>
-  </si>
-  <si>
-    <t>02.06.202624</t>
-  </si>
-  <si>
-    <t>03.06.20261</t>
-  </si>
-  <si>
-    <t>03.06.20262</t>
-  </si>
-  <si>
-    <t>03.06.20263</t>
-  </si>
-  <si>
-    <t>03.06.20264</t>
-  </si>
-  <si>
-    <t>03.06.20265</t>
-  </si>
-  <si>
-    <t>03.06.20266</t>
-  </si>
-  <si>
-    <t>03.06.20267</t>
-  </si>
-  <si>
-    <t>03.06.20268</t>
-  </si>
-  <si>
-    <t>03.06.20269</t>
-  </si>
-  <si>
-    <t>03.06.202610</t>
-  </si>
-  <si>
-    <t>03.06.202611</t>
-  </si>
-  <si>
-    <t>03.06.202612</t>
-  </si>
-  <si>
-    <t>03.06.202613</t>
-  </si>
-  <si>
-    <t>03.06.202614</t>
-  </si>
-  <si>
-    <t>03.06.202615</t>
-  </si>
-  <si>
-    <t>03.06.202616</t>
-  </si>
-  <si>
-    <t>03.06.202617</t>
-  </si>
-  <si>
-    <t>03.06.202618</t>
-  </si>
-  <si>
-    <t>03.06.202619</t>
-  </si>
-  <si>
-    <t>03.06.202620</t>
-  </si>
-  <si>
-    <t>03.06.202621</t>
-  </si>
-  <si>
-    <t>03.06.202622</t>
-  </si>
-  <si>
-    <t>03.06.202623</t>
-  </si>
-  <si>
-    <t>03.06.202624</t>
-  </si>
-  <si>
-    <t>04.06.20261</t>
-  </si>
-  <si>
-    <t>04.06.20262</t>
-  </si>
-  <si>
-    <t>04.06.20263</t>
-  </si>
-  <si>
-    <t>04.06.20264</t>
-  </si>
-  <si>
-    <t>04.06.20265</t>
-  </si>
-  <si>
-    <t>04.06.20266</t>
-  </si>
-  <si>
-    <t>04.06.20267</t>
-  </si>
-  <si>
-    <t>04.06.20268</t>
-  </si>
-  <si>
-    <t>04.06.20269</t>
-  </si>
-  <si>
-    <t>04.06.202610</t>
-  </si>
-  <si>
-    <t>04.06.202611</t>
-  </si>
-  <si>
-    <t>04.06.202612</t>
-  </si>
-  <si>
-    <t>04.06.202613</t>
-  </si>
-  <si>
-    <t>04.06.202614</t>
-  </si>
-  <si>
-    <t>04.06.202615</t>
-  </si>
-  <si>
-    <t>04.06.202616</t>
-  </si>
-  <si>
-    <t>04.06.202617</t>
-  </si>
-  <si>
-    <t>04.06.202618</t>
-  </si>
-  <si>
-    <t>04.06.202619</t>
-  </si>
-  <si>
-    <t>04.06.202620</t>
-  </si>
-  <si>
-    <t>04.06.202621</t>
-  </si>
-  <si>
-    <t>04.06.202622</t>
-  </si>
-  <si>
-    <t>04.06.202623</t>
-  </si>
-  <si>
-    <t>04.06.202624</t>
-  </si>
-  <si>
-    <t>05.06.20261</t>
-  </si>
-  <si>
-    <t>05.06.20262</t>
-  </si>
-  <si>
-    <t>05.06.20263</t>
-  </si>
-  <si>
-    <t>05.06.20264</t>
-  </si>
-  <si>
-    <t>05.06.20265</t>
-  </si>
-  <si>
-    <t>05.06.20266</t>
-  </si>
-  <si>
-    <t>05.06.20267</t>
-  </si>
-  <si>
-    <t>05.06.20268</t>
-  </si>
-  <si>
-    <t>05.06.20269</t>
-  </si>
-  <si>
-    <t>05.06.202610</t>
-  </si>
-  <si>
-    <t>05.06.202611</t>
-  </si>
-  <si>
-    <t>05.06.202612</t>
-  </si>
-  <si>
-    <t>05.06.202613</t>
-  </si>
-  <si>
-    <t>05.06.202614</t>
-  </si>
-  <si>
-    <t>05.06.202615</t>
-  </si>
-  <si>
-    <t>05.06.202616</t>
-  </si>
-  <si>
-    <t>05.06.202617</t>
-  </si>
-  <si>
-    <t>05.06.202618</t>
-  </si>
-  <si>
-    <t>05.06.202619</t>
-  </si>
-  <si>
-    <t>05.06.202620</t>
-  </si>
-  <si>
-    <t>05.06.202621</t>
-  </si>
-  <si>
-    <t>05.06.202622</t>
-  </si>
-  <si>
-    <t>05.06.202623</t>
-  </si>
-  <si>
-    <t>05.06.202624</t>
-  </si>
-  <si>
-    <t>06.06.20261</t>
-  </si>
-  <si>
-    <t>06.06.20262</t>
-  </si>
-  <si>
-    <t>06.06.20263</t>
-  </si>
-  <si>
-    <t>06.06.20264</t>
-  </si>
-  <si>
-    <t>06.06.20265</t>
-  </si>
-  <si>
-    <t>06.06.20266</t>
-  </si>
-  <si>
-    <t>06.06.20267</t>
-  </si>
-  <si>
-    <t>06.06.20268</t>
-  </si>
-  <si>
-    <t>06.06.20269</t>
-  </si>
-  <si>
-    <t>06.06.202610</t>
-  </si>
-  <si>
-    <t>06.06.202611</t>
-  </si>
-  <si>
-    <t>06.06.202612</t>
-  </si>
-  <si>
-    <t>06.06.202613</t>
-  </si>
-  <si>
-    <t>06.06.202614</t>
-  </si>
-  <si>
-    <t>06.06.202615</t>
-  </si>
-  <si>
-    <t>06.06.202616</t>
-  </si>
-  <si>
-    <t>06.06.202617</t>
-  </si>
-  <si>
-    <t>06.06.202618</t>
-  </si>
-  <si>
-    <t>06.06.202619</t>
-  </si>
-  <si>
-    <t>06.06.202620</t>
-  </si>
-  <si>
-    <t>06.06.202621</t>
-  </si>
-  <si>
-    <t>06.06.202622</t>
-  </si>
-  <si>
-    <t>06.06.202623</t>
-  </si>
-  <si>
-    <t>06.06.202624</t>
-  </si>
-  <si>
-    <t>07.06.20261</t>
-  </si>
-  <si>
-    <t>07.06.20262</t>
-  </si>
-  <si>
-    <t>07.06.20263</t>
-  </si>
-  <si>
-    <t>07.06.20264</t>
-  </si>
-  <si>
-    <t>07.06.20265</t>
-  </si>
-  <si>
-    <t>07.06.20266</t>
-  </si>
-  <si>
-    <t>07.06.20267</t>
-  </si>
-  <si>
-    <t>07.06.20268</t>
-  </si>
-  <si>
-    <t>07.06.20269</t>
-  </si>
-  <si>
-    <t>07.06.202610</t>
+    <t>24.07.20267</t>
+  </si>
+  <si>
+    <t>24.07.20268</t>
+  </si>
+  <si>
+    <t>24.07.20269</t>
+  </si>
+  <si>
+    <t>24.07.202610</t>
+  </si>
+  <si>
+    <t>24.07.202611</t>
+  </si>
+  <si>
+    <t>24.07.202612</t>
+  </si>
+  <si>
+    <t>24.07.202613</t>
+  </si>
+  <si>
+    <t>24.07.202614</t>
+  </si>
+  <si>
+    <t>24.07.202615</t>
+  </si>
+  <si>
+    <t>24.07.202616</t>
+  </si>
+  <si>
+    <t>24.07.202617</t>
+  </si>
+  <si>
+    <t>24.07.202618</t>
+  </si>
+  <si>
+    <t>24.07.202619</t>
+  </si>
+  <si>
+    <t>24.07.202620</t>
+  </si>
+  <si>
+    <t>24.07.202621</t>
+  </si>
+  <si>
+    <t>24.07.202622</t>
+  </si>
+  <si>
+    <t>24.07.202623</t>
+  </si>
+  <si>
+    <t>24.07.202624</t>
+  </si>
+  <si>
+    <t>25.07.20261</t>
+  </si>
+  <si>
+    <t>25.07.20262</t>
+  </si>
+  <si>
+    <t>25.07.20263</t>
+  </si>
+  <si>
+    <t>25.07.20264</t>
+  </si>
+  <si>
+    <t>25.07.20265</t>
+  </si>
+  <si>
+    <t>25.07.20266</t>
+  </si>
+  <si>
+    <t>25.07.20267</t>
+  </si>
+  <si>
+    <t>25.07.20268</t>
+  </si>
+  <si>
+    <t>25.07.20269</t>
+  </si>
+  <si>
+    <t>25.07.202610</t>
+  </si>
+  <si>
+    <t>25.07.202611</t>
+  </si>
+  <si>
+    <t>25.07.202612</t>
+  </si>
+  <si>
+    <t>25.07.202613</t>
+  </si>
+  <si>
+    <t>25.07.202614</t>
+  </si>
+  <si>
+    <t>25.07.202615</t>
+  </si>
+  <si>
+    <t>25.07.202616</t>
+  </si>
+  <si>
+    <t>25.07.202617</t>
+  </si>
+  <si>
+    <t>25.07.202618</t>
+  </si>
+  <si>
+    <t>25.07.202619</t>
+  </si>
+  <si>
+    <t>25.07.202620</t>
+  </si>
+  <si>
+    <t>25.07.202621</t>
+  </si>
+  <si>
+    <t>25.07.202622</t>
+  </si>
+  <si>
+    <t>25.07.202623</t>
+  </si>
+  <si>
+    <t>25.07.202624</t>
+  </si>
+  <si>
+    <t>26.07.20261</t>
+  </si>
+  <si>
+    <t>26.07.20262</t>
+  </si>
+  <si>
+    <t>26.07.20263</t>
+  </si>
+  <si>
+    <t>26.07.20264</t>
+  </si>
+  <si>
+    <t>26.07.20265</t>
+  </si>
+  <si>
+    <t>26.07.20266</t>
+  </si>
+  <si>
+    <t>26.07.20267</t>
+  </si>
+  <si>
+    <t>26.07.20268</t>
+  </si>
+  <si>
+    <t>26.07.20269</t>
+  </si>
+  <si>
+    <t>26.07.202610</t>
+  </si>
+  <si>
+    <t>26.07.202611</t>
+  </si>
+  <si>
+    <t>26.07.202612</t>
+  </si>
+  <si>
+    <t>26.07.202613</t>
+  </si>
+  <si>
+    <t>26.07.202614</t>
+  </si>
+  <si>
+    <t>26.07.202615</t>
+  </si>
+  <si>
+    <t>26.07.202616</t>
+  </si>
+  <si>
+    <t>26.07.202617</t>
+  </si>
+  <si>
+    <t>26.07.202618</t>
+  </si>
+  <si>
+    <t>26.07.202619</t>
+  </si>
+  <si>
+    <t>26.07.202620</t>
+  </si>
+  <si>
+    <t>26.07.202621</t>
+  </si>
+  <si>
+    <t>26.07.202622</t>
+  </si>
+  <si>
+    <t>26.07.202623</t>
+  </si>
+  <si>
+    <t>26.07.202624</t>
+  </si>
+  <si>
+    <t>27.07.20261</t>
+  </si>
+  <si>
+    <t>27.07.20262</t>
+  </si>
+  <si>
+    <t>27.07.20263</t>
+  </si>
+  <si>
+    <t>27.07.20264</t>
+  </si>
+  <si>
+    <t>27.07.20265</t>
+  </si>
+  <si>
+    <t>27.07.20266</t>
+  </si>
+  <si>
+    <t>27.07.20267</t>
+  </si>
+  <si>
+    <t>27.07.20268</t>
+  </si>
+  <si>
+    <t>27.07.20269</t>
+  </si>
+  <si>
+    <t>27.07.202610</t>
+  </si>
+  <si>
+    <t>27.07.202611</t>
+  </si>
+  <si>
+    <t>27.07.202612</t>
+  </si>
+  <si>
+    <t>27.07.202613</t>
+  </si>
+  <si>
+    <t>27.07.202614</t>
+  </si>
+  <si>
+    <t>27.07.202615</t>
+  </si>
+  <si>
+    <t>27.07.202616</t>
+  </si>
+  <si>
+    <t>27.07.202617</t>
+  </si>
+  <si>
+    <t>27.07.202618</t>
+  </si>
+  <si>
+    <t>27.07.202619</t>
+  </si>
+  <si>
+    <t>27.07.202620</t>
+  </si>
+  <si>
+    <t>27.07.202621</t>
+  </si>
+  <si>
+    <t>27.07.202622</t>
+  </si>
+  <si>
+    <t>27.07.202623</t>
+  </si>
+  <si>
+    <t>27.07.202624</t>
+  </si>
+  <si>
+    <t>28.07.20261</t>
+  </si>
+  <si>
+    <t>28.07.20262</t>
+  </si>
+  <si>
+    <t>28.07.20263</t>
+  </si>
+  <si>
+    <t>28.07.20264</t>
+  </si>
+  <si>
+    <t>28.07.20265</t>
+  </si>
+  <si>
+    <t>28.07.20266</t>
+  </si>
+  <si>
+    <t>28.07.20267</t>
+  </si>
+  <si>
+    <t>28.07.20268</t>
+  </si>
+  <si>
+    <t>28.07.20269</t>
+  </si>
+  <si>
+    <t>28.07.202610</t>
+  </si>
+  <si>
+    <t>28.07.202611</t>
+  </si>
+  <si>
+    <t>28.07.202612</t>
+  </si>
+  <si>
+    <t>28.07.202613</t>
+  </si>
+  <si>
+    <t>28.07.202614</t>
+  </si>
+  <si>
+    <t>28.07.202615</t>
+  </si>
+  <si>
+    <t>28.07.202616</t>
+  </si>
+  <si>
+    <t>28.07.202617</t>
+  </si>
+  <si>
+    <t>28.07.202618</t>
+  </si>
+  <si>
+    <t>28.07.202619</t>
+  </si>
+  <si>
+    <t>28.07.202620</t>
+  </si>
+  <si>
+    <t>28.07.202621</t>
+  </si>
+  <si>
+    <t>28.07.202622</t>
+  </si>
+  <si>
+    <t>28.07.202623</t>
+  </si>
+  <si>
+    <t>28.07.202624</t>
+  </si>
+  <si>
+    <t>29.07.20261</t>
+  </si>
+  <si>
+    <t>29.07.20262</t>
+  </si>
+  <si>
+    <t>29.07.20263</t>
+  </si>
+  <si>
+    <t>29.07.20264</t>
+  </si>
+  <si>
+    <t>29.07.20265</t>
+  </si>
+  <si>
+    <t>29.07.20266</t>
+  </si>
+  <si>
+    <t>29.07.20267</t>
+  </si>
+  <si>
+    <t>29.07.20268</t>
+  </si>
+  <si>
+    <t>29.07.20269</t>
+  </si>
+  <si>
+    <t>29.07.202610</t>
+  </si>
+  <si>
+    <t>29.07.202611</t>
+  </si>
+  <si>
+    <t>29.07.202612</t>
+  </si>
+  <si>
+    <t>29.07.202613</t>
+  </si>
+  <si>
+    <t>29.07.202614</t>
+  </si>
+  <si>
+    <t>29.07.202615</t>
+  </si>
+  <si>
+    <t>29.07.202616</t>
+  </si>
+  <si>
+    <t>29.07.202617</t>
+  </si>
+  <si>
+    <t>29.07.202618</t>
+  </si>
+  <si>
+    <t>29.07.202619</t>
+  </si>
+  <si>
+    <t>29.07.202620</t>
+  </si>
+  <si>
+    <t>29.07.202621</t>
+  </si>
+  <si>
+    <t>29.07.202622</t>
+  </si>
+  <si>
+    <t>29.07.202623</t>
+  </si>
+  <si>
+    <t>29.07.202624</t>
+  </si>
+  <si>
+    <t>30.07.20261</t>
+  </si>
+  <si>
+    <t>30.07.20262</t>
+  </si>
+  <si>
+    <t>30.07.20263</t>
+  </si>
+  <si>
+    <t>30.07.20264</t>
+  </si>
+  <si>
+    <t>30.07.20265</t>
+  </si>
+  <si>
+    <t>30.07.20266</t>
+  </si>
+  <si>
+    <t>30.07.20267</t>
+  </si>
+  <si>
+    <t>30.07.20268</t>
+  </si>
+  <si>
+    <t>30.07.20269</t>
+  </si>
+  <si>
+    <t>30.07.202610</t>
+  </si>
+  <si>
+    <t>30.07.202611</t>
+  </si>
+  <si>
+    <t>30.07.202612</t>
+  </si>
+  <si>
+    <t>30.07.202613</t>
+  </si>
+  <si>
+    <t>30.07.202614</t>
+  </si>
+  <si>
+    <t>30.07.202615</t>
+  </si>
+  <si>
+    <t>30.07.202616</t>
+  </si>
+  <si>
+    <t>30.07.202617</t>
+  </si>
+  <si>
+    <t>30.07.202618</t>
+  </si>
+  <si>
+    <t>30.07.202619</t>
+  </si>
+  <si>
+    <t>30.07.202620</t>
+  </si>
+  <si>
+    <t>30.07.202621</t>
+  </si>
+  <si>
+    <t>30.07.202622</t>
+  </si>
+  <si>
+    <t>30.07.202623</t>
+  </si>
+  <si>
+    <t>30.07.202624</t>
+  </si>
+  <si>
+    <t>31.07.20261</t>
+  </si>
+  <si>
+    <t>31.07.20262</t>
+  </si>
+  <si>
+    <t>31.07.20263</t>
+  </si>
+  <si>
+    <t>31.07.20264</t>
+  </si>
+  <si>
+    <t>31.07.20265</t>
+  </si>
+  <si>
+    <t>31.07.20266</t>
+  </si>
+  <si>
+    <t>31.07.20267</t>
   </si>
 </sst>
 </file>
@@ -1027,10 +1027,10 @@
     </row>
     <row r="2" spans="1:23">
       <c r="A2" s="2">
-        <v>46173</v>
+        <v>46227</v>
       </c>
       <c r="B2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -1039,7 +1039,7 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>0.082</v>
+        <v>0.079</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -1065,10 +1065,10 @@
     </row>
     <row r="3" spans="1:23">
       <c r="A3" s="2">
-        <v>46173</v>
+        <v>46227</v>
       </c>
       <c r="B3">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -1077,7 +1077,7 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>0.08500000000000001</v>
+        <v>0.079</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -1103,34 +1103,34 @@
     </row>
     <row r="4" spans="1:23">
       <c r="A4" s="2">
-        <v>46173</v>
+        <v>46227</v>
       </c>
       <c r="B4">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C4">
-        <v>2.055</v>
+        <v>1.116</v>
       </c>
       <c r="D4">
-        <v>2.708</v>
+        <v>1.118</v>
       </c>
       <c r="E4">
-        <v>4.099</v>
+        <v>1.566</v>
       </c>
       <c r="F4">
-        <v>3.481</v>
+        <v>2.156</v>
       </c>
       <c r="G4">
-        <v>1.626</v>
+        <v>1.467</v>
       </c>
       <c r="H4">
-        <v>1.423</v>
+        <v>1.088</v>
       </c>
       <c r="I4">
-        <v>0.451</v>
+        <v>0.865</v>
       </c>
       <c r="J4">
-        <v>1.069</v>
+        <v>0.858</v>
       </c>
       <c r="V4" t="s">
         <v>25</v>
@@ -1141,34 +1141,34 @@
     </row>
     <row r="5" spans="1:23">
       <c r="A5" s="2">
-        <v>46173</v>
+        <v>46227</v>
       </c>
       <c r="B5">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C5">
-        <v>2.39</v>
+        <v>1.909</v>
       </c>
       <c r="D5">
-        <v>2.592</v>
+        <v>2.168</v>
       </c>
       <c r="E5">
-        <v>3.658</v>
+        <v>1.571</v>
       </c>
       <c r="F5">
-        <v>3.384</v>
+        <v>3.102</v>
       </c>
       <c r="G5">
-        <v>1.597</v>
+        <v>2.381</v>
       </c>
       <c r="H5">
-        <v>1.317</v>
+        <v>1.419</v>
       </c>
       <c r="I5">
-        <v>0.997</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="J5">
-        <v>1.39</v>
+        <v>0.998</v>
       </c>
       <c r="V5" t="s">
         <v>26</v>
@@ -1179,34 +1179,34 @@
     </row>
     <row r="6" spans="1:23">
       <c r="A6" s="2">
-        <v>46173</v>
+        <v>46227</v>
       </c>
       <c r="B6">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C6">
-        <v>2.833</v>
+        <v>2.225</v>
       </c>
       <c r="D6">
-        <v>3.177</v>
+        <v>2.727</v>
       </c>
       <c r="E6">
-        <v>3.568</v>
+        <v>2.272</v>
       </c>
       <c r="F6">
-        <v>3.231</v>
+        <v>3.387</v>
       </c>
       <c r="G6">
-        <v>1.546</v>
+        <v>2.907</v>
       </c>
       <c r="H6">
-        <v>1.36</v>
+        <v>1.356</v>
       </c>
       <c r="I6">
-        <v>1.225</v>
+        <v>1.416</v>
       </c>
       <c r="J6">
-        <v>1.275</v>
+        <v>1.035</v>
       </c>
       <c r="V6" t="s">
         <v>27</v>
@@ -1217,34 +1217,34 @@
     </row>
     <row r="7" spans="1:23">
       <c r="A7" s="2">
-        <v>46173</v>
+        <v>46227</v>
       </c>
       <c r="B7">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C7">
-        <v>2.705</v>
+        <v>2.444</v>
       </c>
       <c r="D7">
-        <v>3.109</v>
+        <v>2.851</v>
       </c>
       <c r="E7">
-        <v>3.674</v>
+        <v>3.287</v>
       </c>
       <c r="F7">
-        <v>3.515</v>
+        <v>3.337</v>
       </c>
       <c r="G7">
-        <v>1.642</v>
+        <v>2.889</v>
       </c>
       <c r="H7">
-        <v>1.195</v>
+        <v>1.276</v>
       </c>
       <c r="I7">
-        <v>1.346</v>
+        <v>1.481</v>
       </c>
       <c r="J7">
-        <v>1.23</v>
+        <v>0.996</v>
       </c>
       <c r="V7" t="s">
         <v>28</v>
@@ -1255,34 +1255,34 @@
     </row>
     <row r="8" spans="1:23">
       <c r="A8" s="2">
-        <v>46173</v>
+        <v>46227</v>
       </c>
       <c r="B8">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C8">
-        <v>2.305</v>
+        <v>2.401</v>
       </c>
       <c r="D8">
-        <v>2.719</v>
+        <v>2.883</v>
       </c>
       <c r="E8">
-        <v>3.588</v>
+        <v>3.675</v>
       </c>
       <c r="F8">
-        <v>2.935</v>
+        <v>3.273</v>
       </c>
       <c r="G8">
-        <v>1.342</v>
+        <v>2.841</v>
       </c>
       <c r="H8">
-        <v>1.214</v>
+        <v>1.119</v>
       </c>
       <c r="I8">
-        <v>0.908</v>
+        <v>1.465</v>
       </c>
       <c r="J8">
-        <v>1.079</v>
+        <v>1.114</v>
       </c>
       <c r="V8" t="s">
         <v>29</v>
@@ -1293,34 +1293,34 @@
     </row>
     <row r="9" spans="1:23">
       <c r="A9" s="2">
-        <v>46173</v>
+        <v>46227</v>
       </c>
       <c r="B9">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C9">
-        <v>1.945</v>
+        <v>2.375</v>
       </c>
       <c r="D9">
-        <v>2.57</v>
+        <v>2.789</v>
       </c>
       <c r="E9">
-        <v>3.001</v>
+        <v>3.676</v>
       </c>
       <c r="F9">
-        <v>2.197</v>
+        <v>3.242</v>
       </c>
       <c r="G9">
-        <v>1.092</v>
+        <v>2.798</v>
       </c>
       <c r="H9">
-        <v>1.076</v>
+        <v>1.119</v>
       </c>
       <c r="I9">
-        <v>0.824</v>
+        <v>1.502</v>
       </c>
       <c r="J9">
-        <v>0.847</v>
+        <v>1.221</v>
       </c>
       <c r="V9" t="s">
         <v>30</v>
@@ -1331,34 +1331,34 @@
     </row>
     <row r="10" spans="1:23">
       <c r="A10" s="2">
-        <v>46173</v>
+        <v>46227</v>
       </c>
       <c r="B10">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C10">
-        <v>1.419</v>
+        <v>2.132</v>
       </c>
       <c r="D10">
-        <v>1.889</v>
+        <v>2.722</v>
       </c>
       <c r="E10">
-        <v>2.387</v>
+        <v>3.643</v>
       </c>
       <c r="F10">
-        <v>0.991</v>
+        <v>3.025</v>
       </c>
       <c r="G10">
-        <v>0.5679999999999999</v>
+        <v>2.77</v>
       </c>
       <c r="H10">
-        <v>0.831</v>
+        <v>1.056</v>
       </c>
       <c r="I10">
-        <v>0.754</v>
+        <v>1.476</v>
       </c>
       <c r="J10">
-        <v>0.447</v>
+        <v>1.128</v>
       </c>
       <c r="V10" t="s">
         <v>31</v>
@@ -1369,34 +1369,34 @@
     </row>
     <row r="11" spans="1:23">
       <c r="A11" s="2">
-        <v>46173</v>
+        <v>46227</v>
       </c>
       <c r="B11">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C11">
-        <v>0.8159999999999999</v>
+        <v>1.857</v>
       </c>
       <c r="D11">
-        <v>0.97</v>
+        <v>2.403</v>
       </c>
       <c r="E11">
-        <v>1.378</v>
+        <v>3.561</v>
       </c>
       <c r="F11">
-        <v>0.586</v>
+        <v>2.595</v>
       </c>
       <c r="G11">
-        <v>0.432</v>
+        <v>2.365</v>
       </c>
       <c r="H11">
-        <v>0.569</v>
+        <v>1.146</v>
       </c>
       <c r="I11">
-        <v>0.5639999999999999</v>
+        <v>1.241</v>
       </c>
       <c r="J11">
-        <v>0.308</v>
+        <v>0.993</v>
       </c>
       <c r="V11" t="s">
         <v>32</v>
@@ -1407,34 +1407,34 @@
     </row>
     <row r="12" spans="1:23">
       <c r="A12" s="2">
-        <v>46173</v>
+        <v>46227</v>
       </c>
       <c r="B12">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C12">
-        <v>0.282</v>
+        <v>1.719</v>
       </c>
       <c r="D12">
-        <v>0.317</v>
+        <v>1.943</v>
       </c>
       <c r="E12">
-        <v>0.594</v>
+        <v>2.727</v>
       </c>
       <c r="F12">
-        <v>0.218</v>
+        <v>2.054</v>
       </c>
       <c r="G12">
-        <v>0.181</v>
+        <v>1.687</v>
       </c>
       <c r="H12">
-        <v>0.285</v>
+        <v>1.169</v>
       </c>
       <c r="I12">
-        <v>0.241</v>
+        <v>1.045</v>
       </c>
       <c r="J12">
-        <v>0.165</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="V12" t="s">
         <v>33</v>
@@ -1445,34 +1445,34 @@
     </row>
     <row r="13" spans="1:23">
       <c r="A13" s="2">
-        <v>46173</v>
+        <v>46227</v>
       </c>
       <c r="B13">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C13">
-        <v>0.057</v>
+        <v>1.145</v>
       </c>
       <c r="D13">
-        <v>0.08599999999999999</v>
+        <v>1.452</v>
       </c>
       <c r="E13">
-        <v>0.12</v>
+        <v>1.927</v>
       </c>
       <c r="F13">
-        <v>0.025</v>
+        <v>1.111</v>
       </c>
       <c r="G13">
-        <v>0.038</v>
+        <v>1.181</v>
       </c>
       <c r="H13">
-        <v>0.041</v>
+        <v>0.736</v>
       </c>
       <c r="I13">
-        <v>0.025</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="J13">
-        <v>0.027</v>
+        <v>0.359</v>
       </c>
       <c r="V13" t="s">
         <v>34</v>
@@ -1483,34 +1483,34 @@
     </row>
     <row r="14" spans="1:23">
       <c r="A14" s="2">
-        <v>46173</v>
+        <v>46227</v>
       </c>
       <c r="B14">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>0.648</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>0.747</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>1.385</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>0.554</v>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>0.361</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>0.485</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>0.464</v>
       </c>
       <c r="J14">
-        <v>0.013</v>
+        <v>0.206</v>
       </c>
       <c r="V14" t="s">
         <v>35</v>
@@ -1521,34 +1521,34 @@
     </row>
     <row r="15" spans="1:23">
       <c r="A15" s="2">
-        <v>46173</v>
+        <v>46227</v>
       </c>
       <c r="B15">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>0.306</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>0.301</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>0.65</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>0.153</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>0.147</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>0.199</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="J15">
-        <v>0.013</v>
+        <v>0.107</v>
       </c>
       <c r="V15" t="s">
         <v>36</v>
@@ -1559,34 +1559,34 @@
     </row>
     <row r="16" spans="1:23">
       <c r="A16" s="2">
-        <v>46173</v>
+        <v>46227</v>
       </c>
       <c r="B16">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>0.066</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>0.078</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>0.133</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>0.018</v>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>0.023</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>0.015</v>
       </c>
       <c r="J16">
-        <v>0.013</v>
+        <v>0.025</v>
       </c>
       <c r="V16" t="s">
         <v>37</v>
@@ -1597,10 +1597,10 @@
     </row>
     <row r="17" spans="1:23">
       <c r="A17" s="2">
-        <v>46174</v>
+        <v>46227</v>
       </c>
       <c r="B17">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -1624,7 +1624,7 @@
         <v>0</v>
       </c>
       <c r="J17">
-        <v>0.014</v>
+        <v>0.013</v>
       </c>
       <c r="V17" t="s">
         <v>38</v>
@@ -1635,10 +1635,10 @@
     </row>
     <row r="18" spans="1:23">
       <c r="A18" s="2">
-        <v>46174</v>
+        <v>46227</v>
       </c>
       <c r="B18">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -1662,7 +1662,7 @@
         <v>0</v>
       </c>
       <c r="J18">
-        <v>0.014</v>
+        <v>0.013</v>
       </c>
       <c r="V18" t="s">
         <v>39</v>
@@ -1673,10 +1673,10 @@
     </row>
     <row r="19" spans="1:23">
       <c r="A19" s="2">
-        <v>46174</v>
+        <v>46227</v>
       </c>
       <c r="B19">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -1700,7 +1700,7 @@
         <v>0</v>
       </c>
       <c r="J19">
-        <v>0.014</v>
+        <v>0.013</v>
       </c>
       <c r="V19" t="s">
         <v>40</v>
@@ -1711,10 +1711,10 @@
     </row>
     <row r="20" spans="1:23">
       <c r="A20" s="2">
-        <v>46174</v>
+        <v>46228</v>
       </c>
       <c r="B20">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -1749,10 +1749,10 @@
     </row>
     <row r="21" spans="1:23">
       <c r="A21" s="2">
-        <v>46174</v>
+        <v>46228</v>
       </c>
       <c r="B21">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -1787,10 +1787,10 @@
     </row>
     <row r="22" spans="1:23">
       <c r="A22" s="2">
-        <v>46174</v>
+        <v>46228</v>
       </c>
       <c r="B22">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -1802,7 +1802,7 @@
         <v>0</v>
       </c>
       <c r="F22">
-        <v>0.028</v>
+        <v>0</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -1814,7 +1814,7 @@
         <v>0</v>
       </c>
       <c r="J22">
-        <v>0.024</v>
+        <v>0.014</v>
       </c>
       <c r="V22" t="s">
         <v>43</v>
@@ -1825,34 +1825,34 @@
     </row>
     <row r="23" spans="1:23">
       <c r="A23" s="2">
-        <v>46174</v>
+        <v>46228</v>
       </c>
       <c r="B23">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C23">
-        <v>0.068</v>
+        <v>0</v>
       </c>
       <c r="D23">
-        <v>0.078</v>
+        <v>0</v>
       </c>
       <c r="E23">
-        <v>0.169</v>
+        <v>0</v>
       </c>
       <c r="F23">
-        <v>0.334</v>
+        <v>0</v>
       </c>
       <c r="G23">
-        <v>0.205</v>
+        <v>0</v>
       </c>
       <c r="H23">
-        <v>0.145</v>
+        <v>0</v>
       </c>
       <c r="I23">
-        <v>0.116</v>
+        <v>0</v>
       </c>
       <c r="J23">
-        <v>0.062</v>
+        <v>0.014</v>
       </c>
       <c r="V23" t="s">
         <v>44</v>
@@ -1863,34 +1863,34 @@
     </row>
     <row r="24" spans="1:23">
       <c r="A24" s="2">
-        <v>46174</v>
+        <v>46228</v>
       </c>
       <c r="B24">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C24">
-        <v>0.283</v>
+        <v>0</v>
       </c>
       <c r="D24">
-        <v>0.361</v>
+        <v>0</v>
       </c>
       <c r="E24">
-        <v>0.699</v>
+        <v>0</v>
       </c>
       <c r="F24">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="G24">
-        <v>0.413</v>
+        <v>0</v>
       </c>
       <c r="H24">
-        <v>0.5570000000000001</v>
+        <v>0</v>
       </c>
       <c r="I24">
-        <v>0.369</v>
+        <v>0</v>
       </c>
       <c r="J24">
-        <v>0.3</v>
+        <v>0.014</v>
       </c>
       <c r="V24" t="s">
         <v>45</v>
@@ -1901,34 +1901,34 @@
     </row>
     <row r="25" spans="1:23">
       <c r="A25" s="2">
-        <v>46174</v>
+        <v>46228</v>
       </c>
       <c r="B25">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C25">
-        <v>0.642</v>
+        <v>0</v>
       </c>
       <c r="D25">
-        <v>0.6889999999999999</v>
+        <v>0</v>
       </c>
       <c r="E25">
-        <v>1.674</v>
+        <v>0</v>
       </c>
       <c r="F25">
-        <v>1.831</v>
+        <v>0</v>
       </c>
       <c r="G25">
-        <v>1.125</v>
+        <v>0</v>
       </c>
       <c r="H25">
-        <v>0.953</v>
+        <v>0</v>
       </c>
       <c r="I25">
-        <v>0.518</v>
+        <v>0</v>
       </c>
       <c r="J25">
-        <v>0.584</v>
+        <v>0.014</v>
       </c>
       <c r="V25" t="s">
         <v>46</v>
@@ -1939,34 +1939,34 @@
     </row>
     <row r="26" spans="1:23">
       <c r="A26" s="2">
-        <v>46174</v>
+        <v>46228</v>
       </c>
       <c r="B26">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C26">
-        <v>0.744</v>
+        <v>0.059</v>
       </c>
       <c r="D26">
-        <v>0.838</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="E26">
-        <v>2.584</v>
+        <v>0.112</v>
       </c>
       <c r="F26">
-        <v>2.644</v>
+        <v>0.137</v>
       </c>
       <c r="G26">
-        <v>1.855</v>
+        <v>0.067</v>
       </c>
       <c r="H26">
-        <v>1.255</v>
+        <v>0.106</v>
       </c>
       <c r="I26">
-        <v>0.628</v>
+        <v>0.064</v>
       </c>
       <c r="J26">
-        <v>0.856</v>
+        <v>0.062</v>
       </c>
       <c r="V26" t="s">
         <v>47</v>
@@ -1977,34 +1977,34 @@
     </row>
     <row r="27" spans="1:23">
       <c r="A27" s="2">
-        <v>46174</v>
+        <v>46228</v>
       </c>
       <c r="B27">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C27">
-        <v>0.853</v>
+        <v>0.372</v>
       </c>
       <c r="D27">
-        <v>0.983</v>
+        <v>0.408</v>
       </c>
       <c r="E27">
-        <v>2.909</v>
+        <v>0.648</v>
       </c>
       <c r="F27">
-        <v>3.33</v>
+        <v>0.708</v>
       </c>
       <c r="G27">
-        <v>2.465</v>
+        <v>0.388</v>
       </c>
       <c r="H27">
-        <v>1.227</v>
+        <v>0.465</v>
       </c>
       <c r="I27">
-        <v>0.823</v>
+        <v>0.463</v>
       </c>
       <c r="J27">
-        <v>0.884</v>
+        <v>0.371</v>
       </c>
       <c r="V27" t="s">
         <v>48</v>
@@ -2015,34 +2015,34 @@
     </row>
     <row r="28" spans="1:23">
       <c r="A28" s="2">
-        <v>46174</v>
+        <v>46228</v>
       </c>
       <c r="B28">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C28">
-        <v>0.792</v>
+        <v>1.095</v>
       </c>
       <c r="D28">
-        <v>1.009</v>
+        <v>1.154</v>
       </c>
       <c r="E28">
-        <v>3.328</v>
+        <v>1.691</v>
       </c>
       <c r="F28">
-        <v>2.601</v>
+        <v>1.748</v>
       </c>
       <c r="G28">
-        <v>2.659</v>
+        <v>1.15</v>
       </c>
       <c r="H28">
-        <v>1.188</v>
+        <v>0.85</v>
       </c>
       <c r="I28">
-        <v>0.859</v>
+        <v>0.84</v>
       </c>
       <c r="J28">
-        <v>0.829</v>
+        <v>0.847</v>
       </c>
       <c r="V28" t="s">
         <v>49</v>
@@ -2053,34 +2053,34 @@
     </row>
     <row r="29" spans="1:23">
       <c r="A29" s="2">
-        <v>46174</v>
+        <v>46228</v>
       </c>
       <c r="B29">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C29">
-        <v>0.742</v>
+        <v>1.84</v>
       </c>
       <c r="D29">
-        <v>0.971</v>
+        <v>2.091</v>
       </c>
       <c r="E29">
-        <v>3.231</v>
+        <v>2.964</v>
       </c>
       <c r="F29">
-        <v>2.012</v>
+        <v>2.6</v>
       </c>
       <c r="G29">
-        <v>2.878</v>
+        <v>2.071</v>
       </c>
       <c r="H29">
-        <v>1.243</v>
+        <v>1.281</v>
       </c>
       <c r="I29">
-        <v>1.063</v>
+        <v>1.276</v>
       </c>
       <c r="J29">
-        <v>0.753</v>
+        <v>1.021</v>
       </c>
       <c r="V29" t="s">
         <v>50</v>
@@ -2091,34 +2091,34 @@
     </row>
     <row r="30" spans="1:23">
       <c r="A30" s="2">
-        <v>46174</v>
+        <v>46228</v>
       </c>
       <c r="B30">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C30">
-        <v>0.705</v>
+        <v>2.311</v>
       </c>
       <c r="D30">
-        <v>0.927</v>
+        <v>2.629</v>
       </c>
       <c r="E30">
-        <v>3.201</v>
+        <v>3.758</v>
       </c>
       <c r="F30">
-        <v>3.462</v>
+        <v>3.155</v>
       </c>
       <c r="G30">
-        <v>2.981</v>
+        <v>2.682</v>
       </c>
       <c r="H30">
-        <v>1.358</v>
+        <v>1.373</v>
       </c>
       <c r="I30">
+        <v>1.554</v>
+      </c>
+      <c r="J30">
         <v>1.089</v>
-      </c>
-      <c r="J30">
-        <v>0.715</v>
       </c>
       <c r="V30" t="s">
         <v>51</v>
@@ -2129,34 +2129,34 @@
     </row>
     <row r="31" spans="1:23">
       <c r="A31" s="2">
-        <v>46174</v>
+        <v>46228</v>
       </c>
       <c r="B31">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C31">
-        <v>0.673</v>
+        <v>2.444</v>
       </c>
       <c r="D31">
-        <v>0.917</v>
+        <v>2.816</v>
       </c>
       <c r="E31">
-        <v>3.103</v>
+        <v>3.734</v>
       </c>
       <c r="F31">
-        <v>3.283</v>
+        <v>3.339</v>
       </c>
       <c r="G31">
-        <v>2.753</v>
+        <v>2.854</v>
       </c>
       <c r="H31">
-        <v>1.284</v>
+        <v>1.242</v>
       </c>
       <c r="I31">
-        <v>0.895</v>
+        <v>1.563</v>
       </c>
       <c r="J31">
-        <v>0.649</v>
+        <v>1.285</v>
       </c>
       <c r="V31" t="s">
         <v>52</v>
@@ -2167,34 +2167,34 @@
     </row>
     <row r="32" spans="1:23">
       <c r="A32" s="2">
-        <v>46174</v>
+        <v>46228</v>
       </c>
       <c r="B32">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C32">
-        <v>0.5600000000000001</v>
+        <v>2.695</v>
       </c>
       <c r="D32">
-        <v>0.771</v>
+        <v>3.182</v>
       </c>
       <c r="E32">
-        <v>2.666</v>
+        <v>3.648</v>
       </c>
       <c r="F32">
-        <v>2.46</v>
+        <v>3.364</v>
       </c>
       <c r="G32">
-        <v>2.054</v>
+        <v>2.991</v>
       </c>
       <c r="H32">
-        <v>0.987</v>
+        <v>0.761</v>
       </c>
       <c r="I32">
-        <v>0.612</v>
+        <v>1.563</v>
       </c>
       <c r="J32">
-        <v>0.381</v>
+        <v>1.374</v>
       </c>
       <c r="V32" t="s">
         <v>53</v>
@@ -2205,34 +2205,34 @@
     </row>
     <row r="33" spans="1:23">
       <c r="A33" s="2">
-        <v>46174</v>
+        <v>46228</v>
       </c>
       <c r="B33">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C33">
-        <v>0.466</v>
+        <v>2.715</v>
       </c>
       <c r="D33">
-        <v>0.625</v>
+        <v>3.224</v>
       </c>
       <c r="E33">
-        <v>1.806</v>
+        <v>3.566</v>
       </c>
       <c r="F33">
-        <v>1.554</v>
+        <v>3.359</v>
       </c>
       <c r="G33">
-        <v>1.362</v>
+        <v>3.002</v>
       </c>
       <c r="H33">
-        <v>0.799</v>
+        <v>0.824</v>
       </c>
       <c r="I33">
-        <v>0.48</v>
+        <v>1.563</v>
       </c>
       <c r="J33">
-        <v>0.281</v>
+        <v>1.412</v>
       </c>
       <c r="V33" t="s">
         <v>54</v>
@@ -2243,34 +2243,34 @@
     </row>
     <row r="34" spans="1:23">
       <c r="A34" s="2">
-        <v>46174</v>
+        <v>46228</v>
       </c>
       <c r="B34">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C34">
-        <v>0.348</v>
+        <v>2.632</v>
       </c>
       <c r="D34">
-        <v>0.454</v>
+        <v>3.168</v>
       </c>
       <c r="E34">
-        <v>1.424</v>
+        <v>3.524</v>
       </c>
       <c r="F34">
-        <v>1.056</v>
+        <v>3.289</v>
       </c>
       <c r="G34">
-        <v>0.835</v>
+        <v>2.894</v>
       </c>
       <c r="H34">
-        <v>0.5590000000000001</v>
+        <v>0.73</v>
       </c>
       <c r="I34">
-        <v>0.272</v>
+        <v>1.537</v>
       </c>
       <c r="J34">
-        <v>0.239</v>
+        <v>1.345</v>
       </c>
       <c r="V34" t="s">
         <v>55</v>
@@ -2281,34 +2281,34 @@
     </row>
     <row r="35" spans="1:23">
       <c r="A35" s="2">
-        <v>46174</v>
+        <v>46228</v>
       </c>
       <c r="B35">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C35">
-        <v>0.152</v>
+        <v>2.204</v>
       </c>
       <c r="D35">
-        <v>0.228</v>
+        <v>2.899</v>
       </c>
       <c r="E35">
-        <v>0.752</v>
+        <v>3.515</v>
       </c>
       <c r="F35">
-        <v>0.505</v>
+        <v>2.958</v>
       </c>
       <c r="G35">
-        <v>0.407</v>
+        <v>2.657</v>
       </c>
       <c r="H35">
-        <v>0.423</v>
+        <v>0.893</v>
       </c>
       <c r="I35">
-        <v>0.15</v>
+        <v>1.518</v>
       </c>
       <c r="J35">
-        <v>0.11</v>
+        <v>1.174</v>
       </c>
       <c r="V35" t="s">
         <v>56</v>
@@ -2319,34 +2319,34 @@
     </row>
     <row r="36" spans="1:23">
       <c r="A36" s="2">
-        <v>46174</v>
+        <v>46228</v>
       </c>
       <c r="B36">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C36">
-        <v>0.063</v>
+        <v>1.96</v>
       </c>
       <c r="D36">
-        <v>0.101</v>
+        <v>2.611</v>
       </c>
       <c r="E36">
-        <v>0.205</v>
+        <v>3.068</v>
       </c>
       <c r="F36">
-        <v>0.173</v>
+        <v>2.355</v>
       </c>
       <c r="G36">
-        <v>0.157</v>
+        <v>2.228</v>
       </c>
       <c r="H36">
-        <v>0.199</v>
+        <v>0.98</v>
       </c>
       <c r="I36">
-        <v>0.064</v>
+        <v>1.177</v>
       </c>
       <c r="J36">
-        <v>0.027</v>
+        <v>0.924</v>
       </c>
       <c r="V36" t="s">
         <v>57</v>
@@ -2357,34 +2357,34 @@
     </row>
     <row r="37" spans="1:23">
       <c r="A37" s="2">
-        <v>46174</v>
+        <v>46228</v>
       </c>
       <c r="B37">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C37">
-        <v>0</v>
+        <v>1.367</v>
       </c>
       <c r="D37">
-        <v>0.023</v>
+        <v>1.877</v>
       </c>
       <c r="E37">
-        <v>0.03</v>
+        <v>2.388</v>
       </c>
       <c r="F37">
-        <v>0.018</v>
+        <v>1.584</v>
       </c>
       <c r="G37">
-        <v>0.022</v>
+        <v>1.662</v>
       </c>
       <c r="H37">
-        <v>0.02</v>
+        <v>0.955</v>
       </c>
       <c r="I37">
-        <v>0</v>
+        <v>0.851</v>
       </c>
       <c r="J37">
-        <v>0.019</v>
+        <v>0.655</v>
       </c>
       <c r="V37" t="s">
         <v>58</v>
@@ -2395,34 +2395,34 @@
     </row>
     <row r="38" spans="1:23">
       <c r="A38" s="2">
-        <v>46174</v>
+        <v>46228</v>
       </c>
       <c r="B38">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C38">
-        <v>0</v>
+        <v>0.863</v>
       </c>
       <c r="D38">
-        <v>0</v>
+        <v>0.963</v>
       </c>
       <c r="E38">
-        <v>0.01</v>
+        <v>1.49</v>
       </c>
       <c r="F38">
-        <v>0</v>
+        <v>0.728</v>
       </c>
       <c r="G38">
-        <v>0</v>
+        <v>0.913</v>
       </c>
       <c r="H38">
-        <v>0</v>
+        <v>0.68</v>
       </c>
       <c r="I38">
-        <v>0</v>
+        <v>0.635</v>
       </c>
       <c r="J38">
-        <v>0.013</v>
+        <v>0.371</v>
       </c>
       <c r="V38" t="s">
         <v>59</v>
@@ -2433,34 +2433,34 @@
     </row>
     <row r="39" spans="1:23">
       <c r="A39" s="2">
-        <v>46174</v>
+        <v>46228</v>
       </c>
       <c r="B39">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C39">
-        <v>0</v>
+        <v>0.282</v>
       </c>
       <c r="D39">
-        <v>0</v>
+        <v>0.317</v>
       </c>
       <c r="E39">
-        <v>0.01</v>
+        <v>0.666</v>
       </c>
       <c r="F39">
-        <v>0</v>
+        <v>0.215</v>
       </c>
       <c r="G39">
-        <v>0</v>
+        <v>0.29</v>
       </c>
       <c r="H39">
-        <v>0</v>
+        <v>0.353</v>
       </c>
       <c r="I39">
-        <v>0</v>
+        <v>0.328</v>
       </c>
       <c r="J39">
-        <v>0.013</v>
+        <v>0.114</v>
       </c>
       <c r="V39" t="s">
         <v>60</v>
@@ -2471,34 +2471,34 @@
     </row>
     <row r="40" spans="1:23">
       <c r="A40" s="2">
-        <v>46174</v>
+        <v>46228</v>
       </c>
       <c r="B40">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C40">
-        <v>0</v>
+        <v>0.052</v>
       </c>
       <c r="D40">
-        <v>0</v>
+        <v>0.093</v>
       </c>
       <c r="E40">
-        <v>0</v>
+        <v>0.147</v>
       </c>
       <c r="F40">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="G40">
-        <v>0</v>
+        <v>0.061</v>
       </c>
       <c r="H40">
-        <v>0</v>
+        <v>0.053</v>
       </c>
       <c r="I40">
-        <v>0</v>
+        <v>0.034</v>
       </c>
       <c r="J40">
-        <v>0.013</v>
+        <v>0</v>
       </c>
       <c r="V40" t="s">
         <v>61</v>
@@ -2509,10 +2509,10 @@
     </row>
     <row r="41" spans="1:23">
       <c r="A41" s="2">
-        <v>46175</v>
+        <v>46228</v>
       </c>
       <c r="B41">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="C41">
         <v>0</v>
@@ -2536,7 +2536,7 @@
         <v>0</v>
       </c>
       <c r="J41">
-        <v>0.014</v>
+        <v>0.019</v>
       </c>
       <c r="V41" t="s">
         <v>62</v>
@@ -2547,10 +2547,10 @@
     </row>
     <row r="42" spans="1:23">
       <c r="A42" s="2">
-        <v>46175</v>
+        <v>46228</v>
       </c>
       <c r="B42">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="C42">
         <v>0</v>
@@ -2574,7 +2574,7 @@
         <v>0</v>
       </c>
       <c r="J42">
-        <v>0.014</v>
+        <v>0.019</v>
       </c>
       <c r="V42" t="s">
         <v>63</v>
@@ -2585,10 +2585,10 @@
     </row>
     <row r="43" spans="1:23">
       <c r="A43" s="2">
-        <v>46175</v>
+        <v>46228</v>
       </c>
       <c r="B43">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="C43">
         <v>0</v>
@@ -2612,7 +2612,7 @@
         <v>0</v>
       </c>
       <c r="J43">
-        <v>0.014</v>
+        <v>0.019</v>
       </c>
       <c r="V43" t="s">
         <v>64</v>
@@ -2623,10 +2623,10 @@
     </row>
     <row r="44" spans="1:23">
       <c r="A44" s="2">
-        <v>46175</v>
+        <v>46229</v>
       </c>
       <c r="B44">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C44">
         <v>0</v>
@@ -2661,10 +2661,10 @@
     </row>
     <row r="45" spans="1:23">
       <c r="A45" s="2">
-        <v>46175</v>
+        <v>46229</v>
       </c>
       <c r="B45">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C45">
         <v>0</v>
@@ -2699,10 +2699,10 @@
     </row>
     <row r="46" spans="1:23">
       <c r="A46" s="2">
-        <v>46175</v>
+        <v>46229</v>
       </c>
       <c r="B46">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C46">
         <v>0</v>
@@ -2714,7 +2714,7 @@
         <v>0</v>
       </c>
       <c r="F46">
-        <v>0.022</v>
+        <v>0</v>
       </c>
       <c r="G46">
         <v>0</v>
@@ -2726,7 +2726,7 @@
         <v>0</v>
       </c>
       <c r="J46">
-        <v>0.024</v>
+        <v>0.014</v>
       </c>
       <c r="V46" t="s">
         <v>67</v>
@@ -2737,34 +2737,34 @@
     </row>
     <row r="47" spans="1:23">
       <c r="A47" s="2">
-        <v>46175</v>
+        <v>46229</v>
       </c>
       <c r="B47">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C47">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="D47">
-        <v>0.046</v>
+        <v>0</v>
       </c>
       <c r="E47">
-        <v>0.089</v>
+        <v>0</v>
       </c>
       <c r="F47">
-        <v>0.216</v>
+        <v>0</v>
       </c>
       <c r="G47">
-        <v>0.122</v>
+        <v>0</v>
       </c>
       <c r="H47">
-        <v>0.053</v>
+        <v>0</v>
       </c>
       <c r="I47">
-        <v>0.025</v>
+        <v>0</v>
       </c>
       <c r="J47">
-        <v>0.038</v>
+        <v>0.014</v>
       </c>
       <c r="V47" t="s">
         <v>68</v>
@@ -2775,34 +2775,34 @@
     </row>
     <row r="48" spans="1:23">
       <c r="A48" s="2">
-        <v>46175</v>
+        <v>46229</v>
       </c>
       <c r="B48">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C48">
-        <v>0.19</v>
+        <v>0</v>
       </c>
       <c r="D48">
-        <v>0.222</v>
+        <v>0</v>
       </c>
       <c r="E48">
-        <v>0.404</v>
+        <v>0</v>
       </c>
       <c r="F48">
-        <v>0.823</v>
+        <v>0</v>
       </c>
       <c r="G48">
-        <v>0.446</v>
+        <v>0</v>
       </c>
       <c r="H48">
-        <v>0.221</v>
+        <v>0</v>
       </c>
       <c r="I48">
-        <v>0.079</v>
+        <v>0</v>
       </c>
       <c r="J48">
-        <v>0.157</v>
+        <v>0.014</v>
       </c>
       <c r="V48" t="s">
         <v>69</v>
@@ -2813,34 +2813,34 @@
     </row>
     <row r="49" spans="1:23">
       <c r="A49" s="2">
-        <v>46175</v>
+        <v>46229</v>
       </c>
       <c r="B49">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C49">
-        <v>0.386</v>
+        <v>0</v>
       </c>
       <c r="D49">
-        <v>0.418</v>
+        <v>0</v>
       </c>
       <c r="E49">
-        <v>0.881</v>
+        <v>0</v>
       </c>
       <c r="F49">
-        <v>1.365</v>
+        <v>0</v>
       </c>
       <c r="G49">
-        <v>0.705</v>
+        <v>0</v>
       </c>
       <c r="H49">
-        <v>0.551</v>
+        <v>0</v>
       </c>
       <c r="I49">
-        <v>0.142</v>
+        <v>0</v>
       </c>
       <c r="J49">
-        <v>0.306</v>
+        <v>0.014</v>
       </c>
       <c r="V49" t="s">
         <v>70</v>
@@ -2851,34 +2851,34 @@
     </row>
     <row r="50" spans="1:23">
       <c r="A50" s="2">
-        <v>46175</v>
+        <v>46229</v>
       </c>
       <c r="B50">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C50">
-        <v>0.732</v>
+        <v>0.057</v>
       </c>
       <c r="D50">
-        <v>0.706</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="E50">
-        <v>1.532</v>
+        <v>0.097</v>
       </c>
       <c r="F50">
-        <v>2.251</v>
+        <v>0.279</v>
       </c>
       <c r="G50">
-        <v>1.534</v>
+        <v>0.13</v>
       </c>
       <c r="H50">
-        <v>0.603</v>
+        <v>0.106</v>
       </c>
       <c r="I50">
-        <v>0.257</v>
+        <v>0.112</v>
       </c>
       <c r="J50">
-        <v>0.461</v>
+        <v>0.075</v>
       </c>
       <c r="V50" t="s">
         <v>71</v>
@@ -2889,34 +2889,34 @@
     </row>
     <row r="51" spans="1:23">
       <c r="A51" s="2">
-        <v>46175</v>
+        <v>46229</v>
       </c>
       <c r="B51">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C51">
-        <v>1.102</v>
+        <v>0.393</v>
       </c>
       <c r="D51">
-        <v>1.141</v>
+        <v>0.413</v>
       </c>
       <c r="E51">
-        <v>1.962</v>
+        <v>0.658</v>
       </c>
       <c r="F51">
-        <v>2.516</v>
+        <v>0.991</v>
       </c>
       <c r="G51">
-        <v>1.783</v>
+        <v>0.604</v>
       </c>
       <c r="H51">
-        <v>0.678</v>
+        <v>0.591</v>
       </c>
       <c r="I51">
-        <v>0.349</v>
+        <v>0.526</v>
       </c>
       <c r="J51">
-        <v>0.554</v>
+        <v>0.481</v>
       </c>
       <c r="V51" t="s">
         <v>72</v>
@@ -2927,34 +2927,34 @@
     </row>
     <row r="52" spans="1:23">
       <c r="A52" s="2">
-        <v>46175</v>
+        <v>46229</v>
       </c>
       <c r="B52">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C52">
-        <v>1.205</v>
+        <v>1.136</v>
       </c>
       <c r="D52">
-        <v>1.402</v>
+        <v>1.158</v>
       </c>
       <c r="E52">
-        <v>2.898</v>
+        <v>1.724</v>
       </c>
       <c r="F52">
-        <v>2.592</v>
+        <v>2.233</v>
       </c>
       <c r="G52">
-        <v>2.097</v>
+        <v>1.653</v>
       </c>
       <c r="H52">
-        <v>0.707</v>
+        <v>1.066</v>
       </c>
       <c r="I52">
-        <v>0.465</v>
+        <v>0.971</v>
       </c>
       <c r="J52">
-        <v>0.76</v>
+        <v>0.822</v>
       </c>
       <c r="V52" t="s">
         <v>73</v>
@@ -2965,34 +2965,34 @@
     </row>
     <row r="53" spans="1:23">
       <c r="A53" s="2">
-        <v>46175</v>
+        <v>46229</v>
       </c>
       <c r="B53">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C53">
-        <v>1.319</v>
+        <v>1.825</v>
       </c>
       <c r="D53">
-        <v>1.831</v>
+        <v>2.079</v>
       </c>
       <c r="E53">
-        <v>3.577</v>
+        <v>2.812</v>
       </c>
       <c r="F53">
-        <v>2.486</v>
+        <v>3.133</v>
       </c>
       <c r="G53">
-        <v>2.095</v>
+        <v>2.407</v>
       </c>
       <c r="H53">
-        <v>1.101</v>
+        <v>1.399</v>
       </c>
       <c r="I53">
-        <v>0.633</v>
+        <v>1.424</v>
       </c>
       <c r="J53">
-        <v>1.007</v>
+        <v>1.117</v>
       </c>
       <c r="V53" t="s">
         <v>74</v>
@@ -3003,34 +3003,34 @@
     </row>
     <row r="54" spans="1:23">
       <c r="A54" s="2">
-        <v>46175</v>
+        <v>46229</v>
       </c>
       <c r="B54">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C54">
-        <v>1.291</v>
+        <v>2.494</v>
       </c>
       <c r="D54">
-        <v>1.949</v>
+        <v>2.848</v>
       </c>
       <c r="E54">
-        <v>3.578</v>
+        <v>3.785</v>
       </c>
       <c r="F54">
-        <v>2.206</v>
+        <v>3.67</v>
       </c>
       <c r="G54">
-        <v>1.728</v>
+        <v>2.952</v>
       </c>
       <c r="H54">
-        <v>1.32</v>
+        <v>1.171</v>
       </c>
       <c r="I54">
-        <v>0.821</v>
+        <v>1.554</v>
       </c>
       <c r="J54">
-        <v>0.977</v>
+        <v>1.493</v>
       </c>
       <c r="V54" t="s">
         <v>75</v>
@@ -3041,34 +3041,34 @@
     </row>
     <row r="55" spans="1:23">
       <c r="A55" s="2">
-        <v>46175</v>
+        <v>46229</v>
       </c>
       <c r="B55">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C55">
-        <v>1.193</v>
+        <v>2.878</v>
       </c>
       <c r="D55">
-        <v>1.591</v>
+        <v>3.166</v>
       </c>
       <c r="E55">
-        <v>3.315</v>
+        <v>3.919</v>
       </c>
       <c r="F55">
-        <v>1.769</v>
+        <v>3.834</v>
       </c>
       <c r="G55">
-        <v>1.522</v>
+        <v>3.206</v>
       </c>
       <c r="H55">
-        <v>1.261</v>
+        <v>0.855</v>
       </c>
       <c r="I55">
-        <v>0.782</v>
+        <v>1.481</v>
       </c>
       <c r="J55">
-        <v>0.9350000000000001</v>
+        <v>1.435</v>
       </c>
       <c r="V55" t="s">
         <v>76</v>
@@ -3079,34 +3079,34 @@
     </row>
     <row r="56" spans="1:23">
       <c r="A56" s="2">
-        <v>46175</v>
+        <v>46229</v>
       </c>
       <c r="B56">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C56">
-        <v>0.913</v>
+        <v>3.069</v>
       </c>
       <c r="D56">
-        <v>1.162</v>
+        <v>3.379</v>
       </c>
       <c r="E56">
-        <v>2.5</v>
+        <v>3.827</v>
       </c>
       <c r="F56">
-        <v>1.725</v>
+        <v>3.859</v>
       </c>
       <c r="G56">
-        <v>1.527</v>
+        <v>3.34</v>
       </c>
       <c r="H56">
-        <v>1.15</v>
+        <v>0.9370000000000001</v>
       </c>
       <c r="I56">
-        <v>0.6870000000000001</v>
+        <v>1.465</v>
       </c>
       <c r="J56">
-        <v>0.741</v>
+        <v>1.64</v>
       </c>
       <c r="V56" t="s">
         <v>77</v>
@@ -3117,34 +3117,34 @@
     </row>
     <row r="57" spans="1:23">
       <c r="A57" s="2">
-        <v>46175</v>
+        <v>46229</v>
       </c>
       <c r="B57">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C57">
-        <v>1.028</v>
+        <v>3.015</v>
       </c>
       <c r="D57">
-        <v>1.079</v>
+        <v>3.392</v>
       </c>
       <c r="E57">
-        <v>2.397</v>
+        <v>3.761</v>
       </c>
       <c r="F57">
-        <v>1.425</v>
+        <v>3.768</v>
       </c>
       <c r="G57">
-        <v>1.323</v>
+        <v>3.32</v>
       </c>
       <c r="H57">
-        <v>0.954</v>
+        <v>1.04</v>
       </c>
       <c r="I57">
-        <v>0.645</v>
+        <v>1.502</v>
       </c>
       <c r="J57">
-        <v>0.67</v>
+        <v>1.692</v>
       </c>
       <c r="V57" t="s">
         <v>78</v>
@@ -3155,34 +3155,34 @@
     </row>
     <row r="58" spans="1:23">
       <c r="A58" s="2">
-        <v>46175</v>
+        <v>46229</v>
       </c>
       <c r="B58">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C58">
-        <v>0.8110000000000001</v>
+        <v>2.845</v>
       </c>
       <c r="D58">
-        <v>0.986</v>
+        <v>3.292</v>
       </c>
       <c r="E58">
-        <v>1.733</v>
+        <v>3.743</v>
       </c>
       <c r="F58">
-        <v>1.075</v>
+        <v>3.547</v>
       </c>
       <c r="G58">
-        <v>0.832</v>
+        <v>3.207</v>
       </c>
       <c r="H58">
-        <v>0.604</v>
+        <v>0.869</v>
       </c>
       <c r="I58">
-        <v>0.596</v>
+        <v>1.502</v>
       </c>
       <c r="J58">
-        <v>0.334</v>
+        <v>1.494</v>
       </c>
       <c r="V58" t="s">
         <v>79</v>
@@ -3193,34 +3193,34 @@
     </row>
     <row r="59" spans="1:23">
       <c r="A59" s="2">
-        <v>46175</v>
+        <v>46229</v>
       </c>
       <c r="B59">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C59">
-        <v>0.421</v>
+        <v>2.56</v>
       </c>
       <c r="D59">
-        <v>0.527</v>
+        <v>3.173</v>
       </c>
       <c r="E59">
-        <v>1.255</v>
+        <v>3.696</v>
       </c>
       <c r="F59">
-        <v>0.633</v>
+        <v>3.097</v>
       </c>
       <c r="G59">
-        <v>0.516</v>
+        <v>2.906</v>
       </c>
       <c r="H59">
-        <v>0.459</v>
+        <v>0.913</v>
       </c>
       <c r="I59">
-        <v>0.347</v>
+        <v>1.502</v>
       </c>
       <c r="J59">
-        <v>0.248</v>
+        <v>1.473</v>
       </c>
       <c r="V59" t="s">
         <v>80</v>
@@ -3231,34 +3231,34 @@
     </row>
     <row r="60" spans="1:23">
       <c r="A60" s="2">
-        <v>46175</v>
+        <v>46229</v>
       </c>
       <c r="B60">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C60">
-        <v>0.224</v>
+        <v>1.954</v>
       </c>
       <c r="D60">
-        <v>0.252</v>
+        <v>2.789</v>
       </c>
       <c r="E60">
-        <v>0.585</v>
+        <v>3.35</v>
       </c>
       <c r="F60">
-        <v>0.178</v>
+        <v>2.413</v>
       </c>
       <c r="G60">
-        <v>0.185</v>
+        <v>2.302</v>
       </c>
       <c r="H60">
-        <v>0.199</v>
+        <v>1.045</v>
       </c>
       <c r="I60">
-        <v>0.107</v>
+        <v>1.502</v>
       </c>
       <c r="J60">
-        <v>0.11</v>
+        <v>1.166</v>
       </c>
       <c r="V60" t="s">
         <v>81</v>
@@ -3269,34 +3269,34 @@
     </row>
     <row r="61" spans="1:23">
       <c r="A61" s="2">
-        <v>46175</v>
+        <v>46229</v>
       </c>
       <c r="B61">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C61">
-        <v>0.043</v>
+        <v>1.336</v>
       </c>
       <c r="D61">
-        <v>0.065</v>
+        <v>1.912</v>
       </c>
       <c r="E61">
-        <v>0.12</v>
+        <v>2.607</v>
       </c>
       <c r="F61">
-        <v>0.018</v>
+        <v>1.615</v>
       </c>
       <c r="G61">
-        <v>0.028</v>
+        <v>1.744</v>
       </c>
       <c r="H61">
-        <v>0.034</v>
+        <v>0.979</v>
       </c>
       <c r="I61">
-        <v>0</v>
+        <v>1.124</v>
       </c>
       <c r="J61">
-        <v>0.019</v>
+        <v>0.847</v>
       </c>
       <c r="V61" t="s">
         <v>82</v>
@@ -3307,34 +3307,34 @@
     </row>
     <row r="62" spans="1:23">
       <c r="A62" s="2">
-        <v>46175</v>
+        <v>46229</v>
       </c>
       <c r="B62">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C62">
-        <v>0</v>
+        <v>0.832</v>
       </c>
       <c r="D62">
-        <v>0</v>
+        <v>1.029</v>
       </c>
       <c r="E62">
-        <v>0</v>
+        <v>1.573</v>
       </c>
       <c r="F62">
-        <v>0</v>
+        <v>0.788</v>
       </c>
       <c r="G62">
-        <v>0</v>
+        <v>0.996</v>
       </c>
       <c r="H62">
-        <v>0</v>
+        <v>0.726</v>
       </c>
       <c r="I62">
-        <v>0</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="J62">
-        <v>0.013</v>
+        <v>0.466</v>
       </c>
       <c r="V62" t="s">
         <v>83</v>
@@ -3345,34 +3345,34 @@
     </row>
     <row r="63" spans="1:23">
       <c r="A63" s="2">
-        <v>46175</v>
+        <v>46229</v>
       </c>
       <c r="B63">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C63">
-        <v>0</v>
+        <v>0.301</v>
       </c>
       <c r="D63">
-        <v>0</v>
+        <v>0.301</v>
       </c>
       <c r="E63">
-        <v>0</v>
+        <v>0.542</v>
       </c>
       <c r="F63">
-        <v>0</v>
+        <v>0.234</v>
       </c>
       <c r="G63">
-        <v>0</v>
+        <v>0.291</v>
       </c>
       <c r="H63">
-        <v>0</v>
+        <v>0.382</v>
       </c>
       <c r="I63">
-        <v>0</v>
+        <v>0.379</v>
       </c>
       <c r="J63">
-        <v>0.013</v>
+        <v>0.11</v>
       </c>
       <c r="V63" t="s">
         <v>84</v>
@@ -3383,34 +3383,34 @@
     </row>
     <row r="64" spans="1:23">
       <c r="A64" s="2">
-        <v>46175</v>
+        <v>46229</v>
       </c>
       <c r="B64">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C64">
-        <v>0</v>
+        <v>0.051</v>
       </c>
       <c r="D64">
-        <v>0</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="E64">
-        <v>0</v>
+        <v>0.148</v>
       </c>
       <c r="F64">
-        <v>0</v>
+        <v>0.041</v>
       </c>
       <c r="G64">
-        <v>0</v>
+        <v>0.061</v>
       </c>
       <c r="H64">
-        <v>0</v>
+        <v>0.053</v>
       </c>
       <c r="I64">
-        <v>0</v>
+        <v>0.042</v>
       </c>
       <c r="J64">
-        <v>0.013</v>
+        <v>0</v>
       </c>
       <c r="V64" t="s">
         <v>85</v>
@@ -3421,10 +3421,10 @@
     </row>
     <row r="65" spans="1:23">
       <c r="A65" s="2">
-        <v>46176</v>
+        <v>46229</v>
       </c>
       <c r="B65">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="C65">
         <v>0</v>
@@ -3433,7 +3433,7 @@
         <v>0</v>
       </c>
       <c r="E65">
-        <v>0</v>
+        <v>0.029</v>
       </c>
       <c r="F65">
         <v>0</v>
@@ -3448,7 +3448,7 @@
         <v>0</v>
       </c>
       <c r="J65">
-        <v>0.014</v>
+        <v>0</v>
       </c>
       <c r="V65" t="s">
         <v>86</v>
@@ -3459,10 +3459,10 @@
     </row>
     <row r="66" spans="1:23">
       <c r="A66" s="2">
-        <v>46176</v>
+        <v>46229</v>
       </c>
       <c r="B66">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="C66">
         <v>0</v>
@@ -3471,7 +3471,7 @@
         <v>0</v>
       </c>
       <c r="E66">
-        <v>0</v>
+        <v>0.054</v>
       </c>
       <c r="F66">
         <v>0</v>
@@ -3486,7 +3486,7 @@
         <v>0</v>
       </c>
       <c r="J66">
-        <v>0.014</v>
+        <v>0.018</v>
       </c>
       <c r="V66" t="s">
         <v>87</v>
@@ -3497,10 +3497,10 @@
     </row>
     <row r="67" spans="1:23">
       <c r="A67" s="2">
-        <v>46176</v>
+        <v>46229</v>
       </c>
       <c r="B67">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="C67">
         <v>0</v>
@@ -3509,7 +3509,7 @@
         <v>0</v>
       </c>
       <c r="E67">
-        <v>0</v>
+        <v>0.034</v>
       </c>
       <c r="F67">
         <v>0</v>
@@ -3524,7 +3524,7 @@
         <v>0</v>
       </c>
       <c r="J67">
-        <v>0.014</v>
+        <v>0</v>
       </c>
       <c r="V67" t="s">
         <v>88</v>
@@ -3535,10 +3535,10 @@
     </row>
     <row r="68" spans="1:23">
       <c r="A68" s="2">
-        <v>46176</v>
+        <v>46230</v>
       </c>
       <c r="B68">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C68">
         <v>0</v>
@@ -3547,7 +3547,7 @@
         <v>0</v>
       </c>
       <c r="E68">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="F68">
         <v>0</v>
@@ -3562,7 +3562,7 @@
         <v>0</v>
       </c>
       <c r="J68">
-        <v>0.014</v>
+        <v>0.02</v>
       </c>
       <c r="V68" t="s">
         <v>89</v>
@@ -3573,10 +3573,10 @@
     </row>
     <row r="69" spans="1:23">
       <c r="A69" s="2">
-        <v>46176</v>
+        <v>46230</v>
       </c>
       <c r="B69">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C69">
         <v>0</v>
@@ -3585,7 +3585,7 @@
         <v>0</v>
       </c>
       <c r="E69">
-        <v>0</v>
+        <v>0.095</v>
       </c>
       <c r="F69">
         <v>0</v>
@@ -3600,7 +3600,7 @@
         <v>0</v>
       </c>
       <c r="J69">
-        <v>0.014</v>
+        <v>0.02</v>
       </c>
       <c r="V69" t="s">
         <v>90</v>
@@ -3611,10 +3611,10 @@
     </row>
     <row r="70" spans="1:23">
       <c r="A70" s="2">
-        <v>46176</v>
+        <v>46230</v>
       </c>
       <c r="B70">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C70">
         <v>0</v>
@@ -3623,10 +3623,10 @@
         <v>0</v>
       </c>
       <c r="E70">
-        <v>0</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="F70">
-        <v>0.028</v>
+        <v>0</v>
       </c>
       <c r="G70">
         <v>0</v>
@@ -3638,7 +3638,7 @@
         <v>0</v>
       </c>
       <c r="J70">
-        <v>0.038</v>
+        <v>0.02</v>
       </c>
       <c r="V70" t="s">
         <v>91</v>
@@ -3649,34 +3649,34 @@
     </row>
     <row r="71" spans="1:23">
       <c r="A71" s="2">
-        <v>46176</v>
+        <v>46230</v>
       </c>
       <c r="B71">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C71">
-        <v>0.091</v>
+        <v>0</v>
       </c>
       <c r="D71">
-        <v>0.108</v>
+        <v>0</v>
       </c>
       <c r="E71">
-        <v>0.175</v>
+        <v>0.082</v>
       </c>
       <c r="F71">
-        <v>0.308</v>
+        <v>0</v>
       </c>
       <c r="G71">
-        <v>0.201</v>
+        <v>0</v>
       </c>
       <c r="H71">
-        <v>0.145</v>
+        <v>0</v>
       </c>
       <c r="I71">
-        <v>0.079</v>
+        <v>0</v>
       </c>
       <c r="J71">
-        <v>0.165</v>
+        <v>0.014</v>
       </c>
       <c r="V71" t="s">
         <v>92</v>
@@ -3687,34 +3687,34 @@
     </row>
     <row r="72" spans="1:23">
       <c r="A72" s="2">
-        <v>46176</v>
+        <v>46230</v>
       </c>
       <c r="B72">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C72">
-        <v>0.405</v>
+        <v>0</v>
       </c>
       <c r="D72">
-        <v>0.414</v>
+        <v>0</v>
       </c>
       <c r="E72">
-        <v>0.717</v>
+        <v>0</v>
       </c>
       <c r="F72">
-        <v>1.207</v>
+        <v>0</v>
       </c>
       <c r="G72">
-        <v>0.605</v>
+        <v>0</v>
       </c>
       <c r="H72">
-        <v>0.439</v>
+        <v>0</v>
       </c>
       <c r="I72">
-        <v>0.26</v>
+        <v>0</v>
       </c>
       <c r="J72">
-        <v>0.481</v>
+        <v>0.014</v>
       </c>
       <c r="V72" t="s">
         <v>93</v>
@@ -3725,34 +3725,34 @@
     </row>
     <row r="73" spans="1:23">
       <c r="A73" s="2">
-        <v>46176</v>
+        <v>46230</v>
       </c>
       <c r="B73">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C73">
-        <v>0.98</v>
+        <v>0</v>
       </c>
       <c r="D73">
-        <v>1.077</v>
+        <v>0</v>
       </c>
       <c r="E73">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="F73">
-        <v>2.232</v>
+        <v>0</v>
       </c>
       <c r="G73">
-        <v>1.286</v>
+        <v>0</v>
       </c>
       <c r="H73">
-        <v>0.754</v>
+        <v>0</v>
       </c>
       <c r="I73">
-        <v>0.516</v>
+        <v>0</v>
       </c>
       <c r="J73">
-        <v>0.863</v>
+        <v>0.014</v>
       </c>
       <c r="V73" t="s">
         <v>94</v>
@@ -3763,34 +3763,34 @@
     </row>
     <row r="74" spans="1:23">
       <c r="A74" s="2">
-        <v>46176</v>
+        <v>46230</v>
       </c>
       <c r="B74">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C74">
-        <v>1.532</v>
+        <v>0.034</v>
       </c>
       <c r="D74">
-        <v>1.876</v>
+        <v>0.041</v>
       </c>
       <c r="E74">
-        <v>2.539</v>
+        <v>0.044</v>
       </c>
       <c r="F74">
-        <v>3.014</v>
+        <v>0.173</v>
       </c>
       <c r="G74">
-        <v>2.078</v>
+        <v>0.077</v>
       </c>
       <c r="H74">
-        <v>1.126</v>
+        <v>0.053</v>
       </c>
       <c r="I74">
-        <v>0.793</v>
+        <v>0.064</v>
       </c>
       <c r="J74">
-        <v>0.989</v>
+        <v>0.038</v>
       </c>
       <c r="V74" t="s">
         <v>95</v>
@@ -3801,34 +3801,34 @@
     </row>
     <row r="75" spans="1:23">
       <c r="A75" s="2">
-        <v>46176</v>
+        <v>46230</v>
       </c>
       <c r="B75">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C75">
-        <v>2.061</v>
+        <v>0.306</v>
       </c>
       <c r="D75">
-        <v>2.358</v>
+        <v>0.324</v>
       </c>
       <c r="E75">
-        <v>3.091</v>
+        <v>0.391</v>
       </c>
       <c r="F75">
-        <v>3.233</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="G75">
-        <v>2.424</v>
+        <v>0.345</v>
       </c>
       <c r="H75">
-        <v>1.332</v>
+        <v>0.236</v>
       </c>
       <c r="I75">
-        <v>0.899</v>
+        <v>0.361</v>
       </c>
       <c r="J75">
-        <v>1.418</v>
+        <v>0.195</v>
       </c>
       <c r="V75" t="s">
         <v>96</v>
@@ -3839,34 +3839,34 @@
     </row>
     <row r="76" spans="1:23">
       <c r="A76" s="2">
-        <v>46176</v>
+        <v>46230</v>
       </c>
       <c r="B76">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C76">
-        <v>2.462</v>
+        <v>0.755</v>
       </c>
       <c r="D76">
-        <v>2.652</v>
+        <v>0.726</v>
       </c>
       <c r="E76">
-        <v>3.645</v>
+        <v>1.125</v>
       </c>
       <c r="F76">
-        <v>3.079</v>
+        <v>1.22</v>
       </c>
       <c r="G76">
-        <v>2.63</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="H76">
-        <v>1.169</v>
+        <v>0.604</v>
       </c>
       <c r="I76">
-        <v>1.495</v>
+        <v>0.635</v>
       </c>
       <c r="J76">
-        <v>1.428</v>
+        <v>0.526</v>
       </c>
       <c r="V76" t="s">
         <v>97</v>
@@ -3877,34 +3877,34 @@
     </row>
     <row r="77" spans="1:23">
       <c r="A77" s="2">
-        <v>46176</v>
+        <v>46230</v>
       </c>
       <c r="B77">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C77">
-        <v>2.819</v>
+        <v>1.128</v>
       </c>
       <c r="D77">
-        <v>3.044</v>
+        <v>1.391</v>
       </c>
       <c r="E77">
-        <v>3.664</v>
+        <v>1.853</v>
       </c>
       <c r="F77">
-        <v>1.446</v>
+        <v>2.301</v>
       </c>
       <c r="G77">
-        <v>3.001</v>
+        <v>1.776</v>
       </c>
       <c r="H77">
-        <v>1.095</v>
+        <v>0.996</v>
       </c>
       <c r="I77">
-        <v>1.563</v>
+        <v>0.945</v>
       </c>
       <c r="J77">
-        <v>1.445</v>
+        <v>0.845</v>
       </c>
       <c r="V77" t="s">
         <v>98</v>
@@ -3915,34 +3915,34 @@
     </row>
     <row r="78" spans="1:23">
       <c r="A78" s="2">
-        <v>46176</v>
+        <v>46230</v>
       </c>
       <c r="B78">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C78">
-        <v>2.875</v>
+        <v>1.64</v>
       </c>
       <c r="D78">
-        <v>3.056</v>
+        <v>2.017</v>
       </c>
       <c r="E78">
-        <v>3.645</v>
+        <v>2.647</v>
       </c>
       <c r="F78">
-        <v>1.878</v>
+        <v>2.96</v>
       </c>
       <c r="G78">
-        <v>3.066</v>
+        <v>2.478</v>
       </c>
       <c r="H78">
-        <v>1.014</v>
+        <v>1.33</v>
       </c>
       <c r="I78">
-        <v>1.563</v>
+        <v>1.453</v>
       </c>
       <c r="J78">
-        <v>1.465</v>
+        <v>1.023</v>
       </c>
       <c r="V78" t="s">
         <v>99</v>
@@ -3953,34 +3953,34 @@
     </row>
     <row r="79" spans="1:23">
       <c r="A79" s="2">
-        <v>46176</v>
+        <v>46230</v>
       </c>
       <c r="B79">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C79">
-        <v>2.691</v>
+        <v>1.791</v>
       </c>
       <c r="D79">
-        <v>3.06</v>
+        <v>2.201</v>
       </c>
       <c r="E79">
-        <v>3.7</v>
+        <v>3.449</v>
       </c>
       <c r="F79">
-        <v>3.171</v>
+        <v>2.845</v>
       </c>
       <c r="G79">
-        <v>3.134</v>
+        <v>2.622</v>
       </c>
       <c r="H79">
-        <v>0.99</v>
+        <v>0.96</v>
       </c>
       <c r="I79">
-        <v>1.563</v>
+        <v>1.4</v>
       </c>
       <c r="J79">
-        <v>1.282</v>
+        <v>1.277</v>
       </c>
       <c r="V79" t="s">
         <v>100</v>
@@ -3991,34 +3991,34 @@
     </row>
     <row r="80" spans="1:23">
       <c r="A80" s="2">
-        <v>46176</v>
+        <v>46230</v>
       </c>
       <c r="B80">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C80">
-        <v>2.326</v>
+        <v>2.071</v>
       </c>
       <c r="D80">
-        <v>2.735</v>
+        <v>2.432</v>
       </c>
       <c r="E80">
-        <v>3.616</v>
+        <v>3.748</v>
       </c>
       <c r="F80">
-        <v>2.922</v>
+        <v>2.964</v>
       </c>
       <c r="G80">
-        <v>2.807</v>
+        <v>2.704</v>
       </c>
       <c r="H80">
-        <v>0.944</v>
+        <v>1.08</v>
       </c>
       <c r="I80">
-        <v>1.563</v>
+        <v>1.419</v>
       </c>
       <c r="J80">
-        <v>1.12</v>
+        <v>1.415</v>
       </c>
       <c r="V80" t="s">
         <v>101</v>
@@ -4029,34 +4029,34 @@
     </row>
     <row r="81" spans="1:23">
       <c r="A81" s="2">
-        <v>46176</v>
+        <v>46230</v>
       </c>
       <c r="B81">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C81">
-        <v>1.916</v>
+        <v>2.281</v>
       </c>
       <c r="D81">
-        <v>2.313</v>
+        <v>2.622</v>
       </c>
       <c r="E81">
-        <v>2.851</v>
+        <v>3.608</v>
       </c>
       <c r="F81">
-        <v>2.466</v>
+        <v>3.283</v>
       </c>
       <c r="G81">
-        <v>2.196</v>
+        <v>3.037</v>
       </c>
       <c r="H81">
-        <v>1.098</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="I81">
-        <v>1.225</v>
+        <v>1.502</v>
       </c>
       <c r="J81">
-        <v>0.976</v>
+        <v>1.377</v>
       </c>
       <c r="V81" t="s">
         <v>102</v>
@@ -4067,34 +4067,34 @@
     </row>
     <row r="82" spans="1:23">
       <c r="A82" s="2">
-        <v>46176</v>
+        <v>46230</v>
       </c>
       <c r="B82">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C82">
-        <v>1.398</v>
+        <v>1.894</v>
       </c>
       <c r="D82">
-        <v>1.775</v>
+        <v>2.199</v>
       </c>
       <c r="E82">
-        <v>2.296</v>
+        <v>3.428</v>
       </c>
       <c r="F82">
-        <v>1.625</v>
+        <v>3.29</v>
       </c>
       <c r="G82">
-        <v>1.491</v>
+        <v>3.001</v>
       </c>
       <c r="H82">
-        <v>0.839</v>
+        <v>1.024</v>
       </c>
       <c r="I82">
-        <v>0.925</v>
+        <v>1.502</v>
       </c>
       <c r="J82">
-        <v>0.696</v>
+        <v>1.259</v>
       </c>
       <c r="V82" t="s">
         <v>103</v>
@@ -4105,34 +4105,34 @@
     </row>
     <row r="83" spans="1:23">
       <c r="A83" s="2">
-        <v>46176</v>
+        <v>46230</v>
       </c>
       <c r="B83">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C83">
-        <v>0.822</v>
+        <v>1.555</v>
       </c>
       <c r="D83">
-        <v>0.917</v>
+        <v>1.91</v>
       </c>
       <c r="E83">
-        <v>1.354</v>
+        <v>3.151</v>
       </c>
       <c r="F83">
-        <v>0.748</v>
+        <v>2.887</v>
       </c>
       <c r="G83">
-        <v>0.806</v>
+        <v>2.772</v>
       </c>
       <c r="H83">
-        <v>0.533</v>
+        <v>0.965</v>
       </c>
       <c r="I83">
-        <v>0.627</v>
+        <v>1.502</v>
       </c>
       <c r="J83">
-        <v>0.296</v>
+        <v>1.019</v>
       </c>
       <c r="V83" t="s">
         <v>104</v>
@@ -4143,34 +4143,34 @@
     </row>
     <row r="84" spans="1:23">
       <c r="A84" s="2">
-        <v>46176</v>
+        <v>46230</v>
       </c>
       <c r="B84">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C84">
-        <v>0.344</v>
+        <v>1.299</v>
       </c>
       <c r="D84">
-        <v>0.316</v>
+        <v>1.345</v>
       </c>
       <c r="E84">
-        <v>0.614</v>
+        <v>2.462</v>
       </c>
       <c r="F84">
-        <v>0.228</v>
+        <v>2.159</v>
       </c>
       <c r="G84">
-        <v>0.296</v>
+        <v>2.18</v>
       </c>
       <c r="H84">
-        <v>0.285</v>
+        <v>1.001</v>
       </c>
       <c r="I84">
-        <v>0.201</v>
+        <v>1.341</v>
       </c>
       <c r="J84">
-        <v>0.136</v>
+        <v>0.697</v>
       </c>
       <c r="V84" t="s">
         <v>105</v>
@@ -4181,34 +4181,34 @@
     </row>
     <row r="85" spans="1:23">
       <c r="A85" s="2">
-        <v>46176</v>
+        <v>46230</v>
       </c>
       <c r="B85">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C85">
-        <v>0.056</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="D85">
-        <v>0.08699999999999999</v>
+        <v>0.986</v>
       </c>
       <c r="E85">
-        <v>0.11</v>
+        <v>1.777</v>
       </c>
       <c r="F85">
-        <v>0.037</v>
+        <v>1.469</v>
       </c>
       <c r="G85">
-        <v>0.056</v>
+        <v>1.422</v>
       </c>
       <c r="H85">
-        <v>0.05</v>
+        <v>0.903</v>
       </c>
       <c r="I85">
-        <v>0.025</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="J85">
-        <v>0.011</v>
+        <v>0.299</v>
       </c>
       <c r="V85" t="s">
         <v>106</v>
@@ -4219,34 +4219,34 @@
     </row>
     <row r="86" spans="1:23">
       <c r="A86" s="2">
-        <v>46176</v>
+        <v>46230</v>
       </c>
       <c r="B86">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C86">
-        <v>0</v>
+        <v>0.498</v>
       </c>
       <c r="D86">
-        <v>0</v>
+        <v>0.509</v>
       </c>
       <c r="E86">
-        <v>0</v>
+        <v>1.253</v>
       </c>
       <c r="F86">
-        <v>0</v>
+        <v>0.461</v>
       </c>
       <c r="G86">
-        <v>0</v>
+        <v>0.594</v>
       </c>
       <c r="H86">
-        <v>0</v>
+        <v>0.46</v>
       </c>
       <c r="I86">
-        <v>0</v>
+        <v>0.588</v>
       </c>
       <c r="J86">
-        <v>0.013</v>
+        <v>0.231</v>
       </c>
       <c r="V86" t="s">
         <v>107</v>
@@ -4257,34 +4257,34 @@
     </row>
     <row r="87" spans="1:23">
       <c r="A87" s="2">
-        <v>46176</v>
+        <v>46230</v>
       </c>
       <c r="B87">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C87">
-        <v>0</v>
+        <v>0.219</v>
       </c>
       <c r="D87">
-        <v>0</v>
+        <v>0.225</v>
       </c>
       <c r="E87">
-        <v>0</v>
+        <v>0.522</v>
       </c>
       <c r="F87">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="G87">
-        <v>0</v>
+        <v>0.225</v>
       </c>
       <c r="H87">
-        <v>0</v>
+        <v>0.174</v>
       </c>
       <c r="I87">
-        <v>0</v>
+        <v>0.201</v>
       </c>
       <c r="J87">
-        <v>0.013</v>
+        <v>0.055</v>
       </c>
       <c r="V87" t="s">
         <v>108</v>
@@ -4295,34 +4295,34 @@
     </row>
     <row r="88" spans="1:23">
       <c r="A88" s="2">
-        <v>46176</v>
+        <v>46230</v>
       </c>
       <c r="B88">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C88">
-        <v>0</v>
+        <v>0.036</v>
       </c>
       <c r="D88">
-        <v>0</v>
+        <v>0.043</v>
       </c>
       <c r="E88">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="F88">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="G88">
-        <v>0</v>
+        <v>0.029</v>
       </c>
       <c r="H88">
-        <v>0</v>
+        <v>0.016</v>
       </c>
       <c r="I88">
-        <v>0</v>
+        <v>0.021</v>
       </c>
       <c r="J88">
-        <v>0.013</v>
+        <v>0</v>
       </c>
       <c r="V88" t="s">
         <v>109</v>
@@ -4333,10 +4333,10 @@
     </row>
     <row r="89" spans="1:23">
       <c r="A89" s="2">
-        <v>46177</v>
+        <v>46230</v>
       </c>
       <c r="B89">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="C89">
         <v>0</v>
@@ -4360,7 +4360,7 @@
         <v>0</v>
       </c>
       <c r="J89">
-        <v>0.014</v>
+        <v>0</v>
       </c>
       <c r="V89" t="s">
         <v>110</v>
@@ -4371,10 +4371,10 @@
     </row>
     <row r="90" spans="1:23">
       <c r="A90" s="2">
-        <v>46177</v>
+        <v>46230</v>
       </c>
       <c r="B90">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="C90">
         <v>0</v>
@@ -4398,7 +4398,7 @@
         <v>0</v>
       </c>
       <c r="J90">
-        <v>0.014</v>
+        <v>0.013</v>
       </c>
       <c r="V90" t="s">
         <v>111</v>
@@ -4409,10 +4409,10 @@
     </row>
     <row r="91" spans="1:23">
       <c r="A91" s="2">
-        <v>46177</v>
+        <v>46230</v>
       </c>
       <c r="B91">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="C91">
         <v>0</v>
@@ -4436,7 +4436,7 @@
         <v>0</v>
       </c>
       <c r="J91">
-        <v>0.014</v>
+        <v>0.013</v>
       </c>
       <c r="V91" t="s">
         <v>112</v>
@@ -4447,10 +4447,10 @@
     </row>
     <row r="92" spans="1:23">
       <c r="A92" s="2">
-        <v>46177</v>
+        <v>46231</v>
       </c>
       <c r="B92">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C92">
         <v>0</v>
@@ -4485,10 +4485,10 @@
     </row>
     <row r="93" spans="1:23">
       <c r="A93" s="2">
-        <v>46177</v>
+        <v>46231</v>
       </c>
       <c r="B93">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C93">
         <v>0</v>
@@ -4523,10 +4523,10 @@
     </row>
     <row r="94" spans="1:23">
       <c r="A94" s="2">
-        <v>46177</v>
+        <v>46231</v>
       </c>
       <c r="B94">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C94">
         <v>0</v>
@@ -4538,10 +4538,10 @@
         <v>0</v>
       </c>
       <c r="F94">
-        <v>0.036</v>
+        <v>0</v>
       </c>
       <c r="G94">
-        <v>0.012</v>
+        <v>0</v>
       </c>
       <c r="H94">
         <v>0</v>
@@ -4550,7 +4550,7 @@
         <v>0</v>
       </c>
       <c r="J94">
-        <v>0.038</v>
+        <v>0.014</v>
       </c>
       <c r="V94" t="s">
         <v>115</v>
@@ -4561,34 +4561,34 @@
     </row>
     <row r="95" spans="1:23">
       <c r="A95" s="2">
-        <v>46177</v>
+        <v>46231</v>
       </c>
       <c r="B95">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C95">
-        <v>0.105</v>
+        <v>0</v>
       </c>
       <c r="D95">
-        <v>0.107</v>
+        <v>0</v>
       </c>
       <c r="E95">
-        <v>0.161</v>
+        <v>0</v>
       </c>
       <c r="F95">
-        <v>0.334</v>
+        <v>0</v>
       </c>
       <c r="G95">
-        <v>0.204</v>
+        <v>0</v>
       </c>
       <c r="H95">
-        <v>0.172</v>
+        <v>0</v>
       </c>
       <c r="I95">
-        <v>0.107</v>
+        <v>0</v>
       </c>
       <c r="J95">
-        <v>0.161</v>
+        <v>0.014</v>
       </c>
       <c r="V95" t="s">
         <v>116</v>
@@ -4599,34 +4599,34 @@
     </row>
     <row r="96" spans="1:23">
       <c r="A96" s="2">
-        <v>46177</v>
+        <v>46231</v>
       </c>
       <c r="B96">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C96">
-        <v>0.417</v>
+        <v>0</v>
       </c>
       <c r="D96">
-        <v>0.398</v>
+        <v>0</v>
       </c>
       <c r="E96">
-        <v>0.711</v>
+        <v>0</v>
       </c>
       <c r="F96">
-        <v>1.182</v>
+        <v>0</v>
       </c>
       <c r="G96">
-        <v>0.584</v>
+        <v>0</v>
       </c>
       <c r="H96">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="I96">
-        <v>0.332</v>
+        <v>0</v>
       </c>
       <c r="J96">
-        <v>0.487</v>
+        <v>0.014</v>
       </c>
       <c r="V96" t="s">
         <v>117</v>
@@ -4637,34 +4637,34 @@
     </row>
     <row r="97" spans="1:23">
       <c r="A97" s="2">
-        <v>46177</v>
+        <v>46231</v>
       </c>
       <c r="B97">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C97">
-        <v>0.928</v>
+        <v>0</v>
       </c>
       <c r="D97">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="E97">
-        <v>1.497</v>
+        <v>0</v>
       </c>
       <c r="F97">
-        <v>2.172</v>
+        <v>0</v>
       </c>
       <c r="G97">
-        <v>1.356</v>
+        <v>0</v>
       </c>
       <c r="H97">
-        <v>1.019</v>
+        <v>0</v>
       </c>
       <c r="I97">
-        <v>0.642</v>
+        <v>0</v>
       </c>
       <c r="J97">
-        <v>0.921</v>
+        <v>0.014</v>
       </c>
       <c r="V97" t="s">
         <v>118</v>
@@ -4675,34 +4675,34 @@
     </row>
     <row r="98" spans="1:23">
       <c r="A98" s="2">
-        <v>46177</v>
+        <v>46231</v>
       </c>
       <c r="B98">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C98">
-        <v>1.543</v>
+        <v>0.035</v>
       </c>
       <c r="D98">
-        <v>1.872</v>
+        <v>0.044</v>
       </c>
       <c r="E98">
-        <v>2.486</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="F98">
-        <v>3.239</v>
+        <v>0.239</v>
       </c>
       <c r="G98">
-        <v>2.241</v>
+        <v>0.108</v>
       </c>
       <c r="H98">
-        <v>1.264</v>
+        <v>0.106</v>
       </c>
       <c r="I98">
-        <v>0.804</v>
+        <v>0.064</v>
       </c>
       <c r="J98">
-        <v>1.212</v>
+        <v>0.038</v>
       </c>
       <c r="V98" t="s">
         <v>119</v>
@@ -4713,34 +4713,34 @@
     </row>
     <row r="99" spans="1:23">
       <c r="A99" s="2">
-        <v>46177</v>
+        <v>46231</v>
       </c>
       <c r="B99">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C99">
-        <v>2.028</v>
+        <v>0.248</v>
       </c>
       <c r="D99">
-        <v>2.355</v>
+        <v>0.305</v>
       </c>
       <c r="E99">
-        <v>2.985</v>
+        <v>0.584</v>
       </c>
       <c r="F99">
-        <v>3.294</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="G99">
-        <v>2.714</v>
+        <v>0.505</v>
       </c>
       <c r="H99">
-        <v>1.191</v>
+        <v>0.442</v>
       </c>
       <c r="I99">
-        <v>1.326</v>
+        <v>0.361</v>
       </c>
       <c r="J99">
-        <v>1.35</v>
+        <v>0.294</v>
       </c>
       <c r="V99" t="s">
         <v>120</v>
@@ -4751,34 +4751,34 @@
     </row>
     <row r="100" spans="1:23">
       <c r="A100" s="2">
-        <v>46177</v>
+        <v>46231</v>
       </c>
       <c r="B100">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C100">
-        <v>2.455</v>
+        <v>0.757</v>
       </c>
       <c r="D100">
-        <v>2.477</v>
+        <v>0.848</v>
       </c>
       <c r="E100">
-        <v>3.488</v>
+        <v>1.586</v>
       </c>
       <c r="F100">
-        <v>1.705</v>
+        <v>1.925</v>
       </c>
       <c r="G100">
-        <v>3.11</v>
+        <v>1.337</v>
       </c>
       <c r="H100">
-        <v>1.068</v>
+        <v>0.968</v>
       </c>
       <c r="I100">
-        <v>1.563</v>
+        <v>0.667</v>
       </c>
       <c r="J100">
-        <v>1.542</v>
+        <v>0.618</v>
       </c>
       <c r="V100" t="s">
         <v>121</v>
@@ -4789,34 +4789,34 @@
     </row>
     <row r="101" spans="1:23">
       <c r="A101" s="2">
-        <v>46177</v>
+        <v>46231</v>
       </c>
       <c r="B101">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C101">
-        <v>2.47</v>
+        <v>1.254</v>
       </c>
       <c r="D101">
-        <v>2.685</v>
+        <v>1.398</v>
       </c>
       <c r="E101">
-        <v>3.625</v>
+        <v>2.584</v>
       </c>
       <c r="F101">
-        <v>1.624</v>
+        <v>2.561</v>
       </c>
       <c r="G101">
-        <v>3.25</v>
+        <v>2.046</v>
       </c>
       <c r="H101">
-        <v>1.068</v>
+        <v>1.303</v>
       </c>
       <c r="I101">
-        <v>1.563</v>
+        <v>1.017</v>
       </c>
       <c r="J101">
-        <v>1.557</v>
+        <v>0.883</v>
       </c>
       <c r="V101" t="s">
         <v>122</v>
@@ -4827,34 +4827,34 @@
     </row>
     <row r="102" spans="1:23">
       <c r="A102" s="2">
-        <v>46177</v>
+        <v>46231</v>
       </c>
       <c r="B102">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C102">
-        <v>2.442</v>
+        <v>1.613</v>
       </c>
       <c r="D102">
-        <v>2.681</v>
+        <v>1.997</v>
       </c>
       <c r="E102">
-        <v>3.703</v>
+        <v>3.414</v>
       </c>
       <c r="F102">
-        <v>1.796</v>
+        <v>3.282</v>
       </c>
       <c r="G102">
-        <v>3.226</v>
+        <v>2.764</v>
       </c>
       <c r="H102">
-        <v>1.003</v>
+        <v>1.117</v>
       </c>
       <c r="I102">
-        <v>1.563</v>
+        <v>1.554</v>
       </c>
       <c r="J102">
-        <v>1.425</v>
+        <v>0.962</v>
       </c>
       <c r="V102" t="s">
         <v>123</v>
@@ -4865,34 +4865,34 @@
     </row>
     <row r="103" spans="1:23">
       <c r="A103" s="2">
-        <v>46177</v>
+        <v>46231</v>
       </c>
       <c r="B103">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C103">
-        <v>2.15</v>
+        <v>1.842</v>
       </c>
       <c r="D103">
-        <v>2.501</v>
+        <v>2.298</v>
       </c>
       <c r="E103">
-        <v>3.582</v>
+        <v>3.639</v>
       </c>
       <c r="F103">
-        <v>2.776</v>
+        <v>3.536</v>
       </c>
       <c r="G103">
-        <v>2.995</v>
+        <v>3.088</v>
       </c>
       <c r="H103">
-        <v>1.02</v>
+        <v>1.145</v>
       </c>
       <c r="I103">
-        <v>1.563</v>
+        <v>1.481</v>
       </c>
       <c r="J103">
-        <v>1.385</v>
+        <v>1.104</v>
       </c>
       <c r="V103" t="s">
         <v>124</v>
@@ -4903,34 +4903,34 @@
     </row>
     <row r="104" spans="1:23">
       <c r="A104" s="2">
-        <v>46177</v>
+        <v>46231</v>
       </c>
       <c r="B104">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C104">
-        <v>1.809</v>
+        <v>2.238</v>
       </c>
       <c r="D104">
-        <v>2.147</v>
+        <v>2.638</v>
       </c>
       <c r="E104">
-        <v>3.155</v>
+        <v>3.402</v>
       </c>
       <c r="F104">
-        <v>2.893</v>
+        <v>3.675</v>
       </c>
       <c r="G104">
-        <v>2.498</v>
+        <v>3.221</v>
       </c>
       <c r="H104">
-        <v>0.921</v>
+        <v>1.422</v>
       </c>
       <c r="I104">
-        <v>1.563</v>
+        <v>1.481</v>
       </c>
       <c r="J104">
-        <v>1.286</v>
+        <v>1.21</v>
       </c>
       <c r="V104" t="s">
         <v>125</v>
@@ -4941,34 +4941,34 @@
     </row>
     <row r="105" spans="1:23">
       <c r="A105" s="2">
-        <v>46177</v>
+        <v>46231</v>
       </c>
       <c r="B105">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C105">
-        <v>1.677</v>
+        <v>2.484</v>
       </c>
       <c r="D105">
-        <v>1.955</v>
+        <v>2.88</v>
       </c>
       <c r="E105">
-        <v>2.759</v>
+        <v>3.342</v>
       </c>
       <c r="F105">
-        <v>2.31</v>
+        <v>3.695</v>
       </c>
       <c r="G105">
-        <v>2.026</v>
+        <v>3.268</v>
       </c>
       <c r="H105">
-        <v>0.9409999999999999</v>
+        <v>0.901</v>
       </c>
       <c r="I105">
-        <v>1.382</v>
+        <v>1.502</v>
       </c>
       <c r="J105">
-        <v>0.893</v>
+        <v>1.37</v>
       </c>
       <c r="V105" t="s">
         <v>126</v>
@@ -4979,34 +4979,34 @@
     </row>
     <row r="106" spans="1:23">
       <c r="A106" s="2">
-        <v>46177</v>
+        <v>46231</v>
       </c>
       <c r="B106">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C106">
-        <v>1.124</v>
+        <v>2.615</v>
       </c>
       <c r="D106">
-        <v>1.277</v>
+        <v>2.917</v>
       </c>
       <c r="E106">
-        <v>1.86</v>
+        <v>3.516</v>
       </c>
       <c r="F106">
-        <v>1.241</v>
+        <v>3.361</v>
       </c>
       <c r="G106">
-        <v>1.241</v>
+        <v>3.158</v>
       </c>
       <c r="H106">
-        <v>0.6909999999999999</v>
+        <v>1.056</v>
       </c>
       <c r="I106">
-        <v>0.9350000000000001</v>
+        <v>1.502</v>
       </c>
       <c r="J106">
-        <v>0.401</v>
+        <v>1.284</v>
       </c>
       <c r="V106" t="s">
         <v>127</v>
@@ -5017,34 +5017,34 @@
     </row>
     <row r="107" spans="1:23">
       <c r="A107" s="2">
-        <v>46177</v>
+        <v>46231</v>
       </c>
       <c r="B107">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C107">
-        <v>0.635</v>
+        <v>2.181</v>
       </c>
       <c r="D107">
-        <v>0.6870000000000001</v>
+        <v>2.81</v>
       </c>
       <c r="E107">
-        <v>1.27</v>
+        <v>3.326</v>
       </c>
       <c r="F107">
-        <v>0.746</v>
+        <v>2.812</v>
       </c>
       <c r="G107">
-        <v>0.714</v>
+        <v>2.754</v>
       </c>
       <c r="H107">
-        <v>0.442</v>
+        <v>1.135</v>
       </c>
       <c r="I107">
-        <v>0.5639999999999999</v>
+        <v>1.502</v>
       </c>
       <c r="J107">
-        <v>0.238</v>
+        <v>1.161</v>
       </c>
       <c r="V107" t="s">
         <v>128</v>
@@ -5055,34 +5055,34 @@
     </row>
     <row r="108" spans="1:23">
       <c r="A108" s="2">
-        <v>46177</v>
+        <v>46231</v>
       </c>
       <c r="B108">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C108">
-        <v>0.272</v>
+        <v>1.918</v>
       </c>
       <c r="D108">
-        <v>0.254</v>
+        <v>2.479</v>
       </c>
       <c r="E108">
-        <v>0.602</v>
+        <v>3.028</v>
       </c>
       <c r="F108">
-        <v>0.215</v>
+        <v>2.144</v>
       </c>
       <c r="G108">
-        <v>0.235</v>
+        <v>2.148</v>
       </c>
       <c r="H108">
-        <v>0.232</v>
+        <v>1.141</v>
       </c>
       <c r="I108">
-        <v>0.188</v>
+        <v>1.186</v>
       </c>
       <c r="J108">
-        <v>0.15</v>
+        <v>0.82</v>
       </c>
       <c r="V108" t="s">
         <v>129</v>
@@ -5093,34 +5093,34 @@
     </row>
     <row r="109" spans="1:23">
       <c r="A109" s="2">
-        <v>46177</v>
+        <v>46231</v>
       </c>
       <c r="B109">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C109">
-        <v>0.046</v>
+        <v>1.393</v>
       </c>
       <c r="D109">
-        <v>0.065</v>
+        <v>1.783</v>
       </c>
       <c r="E109">
-        <v>0.08799999999999999</v>
+        <v>2.245</v>
       </c>
       <c r="F109">
-        <v>0.018</v>
+        <v>1.522</v>
       </c>
       <c r="G109">
-        <v>0.035</v>
+        <v>1.53</v>
       </c>
       <c r="H109">
-        <v>0.034</v>
+        <v>0.964</v>
       </c>
       <c r="I109">
-        <v>0.021</v>
+        <v>0.855</v>
       </c>
       <c r="J109">
-        <v>0.019</v>
+        <v>0.549</v>
       </c>
       <c r="V109" t="s">
         <v>130</v>
@@ -5131,34 +5131,34 @@
     </row>
     <row r="110" spans="1:23">
       <c r="A110" s="2">
-        <v>46177</v>
+        <v>46231</v>
       </c>
       <c r="B110">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C110">
-        <v>0</v>
+        <v>0.777</v>
       </c>
       <c r="D110">
-        <v>0</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="E110">
-        <v>0</v>
+        <v>1.288</v>
       </c>
       <c r="F110">
-        <v>0</v>
+        <v>0.499</v>
       </c>
       <c r="G110">
-        <v>0</v>
+        <v>0.671</v>
       </c>
       <c r="H110">
-        <v>0</v>
+        <v>0.484</v>
       </c>
       <c r="I110">
-        <v>0</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="J110">
-        <v>0.013</v>
+        <v>0.255</v>
       </c>
       <c r="V110" t="s">
         <v>131</v>
@@ -5169,34 +5169,34 @@
     </row>
     <row r="111" spans="1:23">
       <c r="A111" s="2">
-        <v>46177</v>
+        <v>46231</v>
       </c>
       <c r="B111">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C111">
-        <v>0</v>
+        <v>0.245</v>
       </c>
       <c r="D111">
-        <v>0</v>
+        <v>0.295</v>
       </c>
       <c r="E111">
-        <v>0</v>
+        <v>0.549</v>
       </c>
       <c r="F111">
-        <v>0</v>
+        <v>0.206</v>
       </c>
       <c r="G111">
-        <v>0</v>
+        <v>0.252</v>
       </c>
       <c r="H111">
-        <v>0</v>
+        <v>0.232</v>
       </c>
       <c r="I111">
-        <v>0</v>
+        <v>0.197</v>
       </c>
       <c r="J111">
-        <v>0.013</v>
+        <v>0.109</v>
       </c>
       <c r="V111" t="s">
         <v>132</v>
@@ -5207,34 +5207,34 @@
     </row>
     <row r="112" spans="1:23">
       <c r="A112" s="2">
-        <v>46177</v>
+        <v>46231</v>
       </c>
       <c r="B112">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C112">
-        <v>0</v>
+        <v>0.039</v>
       </c>
       <c r="D112">
-        <v>0</v>
+        <v>0.074</v>
       </c>
       <c r="E112">
-        <v>0</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="F112">
-        <v>0</v>
+        <v>0.024</v>
       </c>
       <c r="G112">
-        <v>0</v>
+        <v>0.031</v>
       </c>
       <c r="H112">
-        <v>0</v>
+        <v>0.034</v>
       </c>
       <c r="I112">
-        <v>0</v>
+        <v>0.021</v>
       </c>
       <c r="J112">
-        <v>0.013</v>
+        <v>0</v>
       </c>
       <c r="V112" t="s">
         <v>133</v>
@@ -5245,10 +5245,10 @@
     </row>
     <row r="113" spans="1:23">
       <c r="A113" s="2">
-        <v>46178</v>
+        <v>46231</v>
       </c>
       <c r="B113">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="C113">
         <v>0</v>
@@ -5257,7 +5257,7 @@
         <v>0</v>
       </c>
       <c r="E113">
-        <v>0</v>
+        <v>0.014</v>
       </c>
       <c r="F113">
         <v>0</v>
@@ -5272,7 +5272,7 @@
         <v>0</v>
       </c>
       <c r="J113">
-        <v>0.014</v>
+        <v>0.013</v>
       </c>
       <c r="V113" t="s">
         <v>134</v>
@@ -5283,10 +5283,10 @@
     </row>
     <row r="114" spans="1:23">
       <c r="A114" s="2">
-        <v>46178</v>
+        <v>46231</v>
       </c>
       <c r="B114">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="C114">
         <v>0</v>
@@ -5310,7 +5310,7 @@
         <v>0</v>
       </c>
       <c r="J114">
-        <v>0.014</v>
+        <v>0.019</v>
       </c>
       <c r="V114" t="s">
         <v>135</v>
@@ -5321,10 +5321,10 @@
     </row>
     <row r="115" spans="1:23">
       <c r="A115" s="2">
-        <v>46178</v>
+        <v>46231</v>
       </c>
       <c r="B115">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="C115">
         <v>0</v>
@@ -5348,7 +5348,7 @@
         <v>0</v>
       </c>
       <c r="J115">
-        <v>0.014</v>
+        <v>0.019</v>
       </c>
       <c r="V115" t="s">
         <v>136</v>
@@ -5359,10 +5359,10 @@
     </row>
     <row r="116" spans="1:23">
       <c r="A116" s="2">
-        <v>46178</v>
+        <v>46232</v>
       </c>
       <c r="B116">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C116">
         <v>0</v>
@@ -5397,10 +5397,10 @@
     </row>
     <row r="117" spans="1:23">
       <c r="A117" s="2">
-        <v>46178</v>
+        <v>46232</v>
       </c>
       <c r="B117">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C117">
         <v>0</v>
@@ -5435,10 +5435,10 @@
     </row>
     <row r="118" spans="1:23">
       <c r="A118" s="2">
-        <v>46178</v>
+        <v>46232</v>
       </c>
       <c r="B118">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C118">
         <v>0</v>
@@ -5450,7 +5450,7 @@
         <v>0</v>
       </c>
       <c r="F118">
-        <v>0.028</v>
+        <v>0</v>
       </c>
       <c r="G118">
         <v>0</v>
@@ -5462,7 +5462,7 @@
         <v>0</v>
       </c>
       <c r="J118">
-        <v>0.038</v>
+        <v>0.014</v>
       </c>
       <c r="V118" t="s">
         <v>139</v>
@@ -5473,34 +5473,34 @@
     </row>
     <row r="119" spans="1:23">
       <c r="A119" s="2">
-        <v>46178</v>
+        <v>46232</v>
       </c>
       <c r="B119">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C119">
-        <v>0.07199999999999999</v>
+        <v>0</v>
       </c>
       <c r="D119">
-        <v>0.102</v>
+        <v>0</v>
       </c>
       <c r="E119">
-        <v>0.174</v>
+        <v>0</v>
       </c>
       <c r="F119">
-        <v>0.312</v>
+        <v>0</v>
       </c>
       <c r="G119">
-        <v>0.166</v>
+        <v>0</v>
       </c>
       <c r="H119">
-        <v>0.145</v>
+        <v>0</v>
       </c>
       <c r="I119">
-        <v>0.136</v>
+        <v>0</v>
       </c>
       <c r="J119">
-        <v>0.172</v>
+        <v>0.015</v>
       </c>
       <c r="V119" t="s">
         <v>140</v>
@@ -5511,34 +5511,34 @@
     </row>
     <row r="120" spans="1:23">
       <c r="A120" s="2">
-        <v>46178</v>
+        <v>46232</v>
       </c>
       <c r="B120">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C120">
-        <v>0.424</v>
+        <v>0</v>
       </c>
       <c r="D120">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="E120">
-        <v>0.713</v>
+        <v>0</v>
       </c>
       <c r="F120">
-        <v>1.084</v>
+        <v>0</v>
       </c>
       <c r="G120">
-        <v>0.5669999999999999</v>
+        <v>0</v>
       </c>
       <c r="H120">
-        <v>0.439</v>
+        <v>0</v>
       </c>
       <c r="I120">
-        <v>0.477</v>
+        <v>0</v>
       </c>
       <c r="J120">
-        <v>0.487</v>
+        <v>0.015</v>
       </c>
       <c r="V120" t="s">
         <v>141</v>
@@ -5549,34 +5549,34 @@
     </row>
     <row r="121" spans="1:23">
       <c r="A121" s="2">
-        <v>46178</v>
+        <v>46232</v>
       </c>
       <c r="B121">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C121">
-        <v>0.978</v>
+        <v>0</v>
       </c>
       <c r="D121">
-        <v>1.062</v>
+        <v>0</v>
       </c>
       <c r="E121">
-        <v>1.734</v>
+        <v>0</v>
       </c>
       <c r="F121">
-        <v>2.042</v>
+        <v>0</v>
       </c>
       <c r="G121">
-        <v>1.278</v>
+        <v>0</v>
       </c>
       <c r="H121">
-        <v>0.6870000000000001</v>
+        <v>0</v>
       </c>
       <c r="I121">
-        <v>0.793</v>
+        <v>0</v>
       </c>
       <c r="J121">
-        <v>0.921</v>
+        <v>0.015</v>
       </c>
       <c r="V121" t="s">
         <v>142</v>
@@ -5587,34 +5587,34 @@
     </row>
     <row r="122" spans="1:23">
       <c r="A122" s="2">
-        <v>46178</v>
+        <v>46232</v>
       </c>
       <c r="B122">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C122">
-        <v>1.477</v>
+        <v>0.045</v>
       </c>
       <c r="D122">
-        <v>1.689</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="E122">
-        <v>2.5</v>
+        <v>0.077</v>
       </c>
       <c r="F122">
-        <v>2.437</v>
+        <v>0.198</v>
       </c>
       <c r="G122">
-        <v>1.838</v>
+        <v>0.107</v>
       </c>
       <c r="H122">
-        <v>1.204</v>
+        <v>0.073</v>
       </c>
       <c r="I122">
-        <v>0.906</v>
+        <v>0.074</v>
       </c>
       <c r="J122">
-        <v>1.216</v>
+        <v>0.059</v>
       </c>
       <c r="V122" t="s">
         <v>143</v>
@@ -5625,34 +5625,34 @@
     </row>
     <row r="123" spans="1:23">
       <c r="A123" s="2">
-        <v>46178</v>
+        <v>46232</v>
       </c>
       <c r="B123">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C123">
-        <v>1.879</v>
+        <v>0.342</v>
       </c>
       <c r="D123">
-        <v>2.064</v>
+        <v>0.396</v>
       </c>
       <c r="E123">
-        <v>3.137</v>
+        <v>0.553</v>
       </c>
       <c r="F123">
-        <v>3.285</v>
+        <v>0.865</v>
       </c>
       <c r="G123">
-        <v>2.483</v>
+        <v>0.49</v>
       </c>
       <c r="H123">
-        <v>1.212</v>
+        <v>0.366</v>
       </c>
       <c r="I123">
-        <v>1.512</v>
+        <v>0.443</v>
       </c>
       <c r="J123">
-        <v>1.559</v>
+        <v>0.398</v>
       </c>
       <c r="V123" t="s">
         <v>144</v>
@@ -5663,34 +5663,34 @@
     </row>
     <row r="124" spans="1:23">
       <c r="A124" s="2">
-        <v>46178</v>
+        <v>46232</v>
       </c>
       <c r="B124">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C124">
-        <v>2.223</v>
+        <v>1.056</v>
       </c>
       <c r="D124">
-        <v>2.395</v>
+        <v>1.064</v>
       </c>
       <c r="E124">
-        <v>3.65</v>
+        <v>1.399</v>
       </c>
       <c r="F124">
-        <v>2.829</v>
+        <v>1.933</v>
       </c>
       <c r="G124">
-        <v>2.63</v>
+        <v>1.356</v>
       </c>
       <c r="H124">
-        <v>1.119</v>
+        <v>0.758</v>
       </c>
       <c r="I124">
-        <v>1.563</v>
+        <v>0.856</v>
       </c>
       <c r="J124">
-        <v>1.53</v>
+        <v>0.866</v>
       </c>
       <c r="V124" t="s">
         <v>145</v>
@@ -5701,34 +5701,34 @@
     </row>
     <row r="125" spans="1:23">
       <c r="A125" s="2">
-        <v>46178</v>
+        <v>46232</v>
       </c>
       <c r="B125">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C125">
-        <v>2.395</v>
+        <v>1.812</v>
       </c>
       <c r="D125">
-        <v>2.521</v>
+        <v>2.05</v>
       </c>
       <c r="E125">
-        <v>3.704</v>
+        <v>2.412</v>
       </c>
       <c r="F125">
-        <v>1.463</v>
+        <v>2.857</v>
       </c>
       <c r="G125">
-        <v>2.857</v>
+        <v>2.251</v>
       </c>
       <c r="H125">
-        <v>1.096</v>
+        <v>1.267</v>
       </c>
       <c r="I125">
-        <v>1.563</v>
+        <v>1.074</v>
       </c>
       <c r="J125">
-        <v>1.66</v>
+        <v>1.083</v>
       </c>
       <c r="V125" t="s">
         <v>146</v>
@@ -5739,34 +5739,34 @@
     </row>
     <row r="126" spans="1:23">
       <c r="A126" s="2">
-        <v>46178</v>
+        <v>46232</v>
       </c>
       <c r="B126">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C126">
-        <v>2.411</v>
+        <v>2.454</v>
       </c>
       <c r="D126">
-        <v>2.765</v>
+        <v>2.75</v>
       </c>
       <c r="E126">
-        <v>3.685</v>
+        <v>3.156</v>
       </c>
       <c r="F126">
-        <v>1.443</v>
+        <v>3.398</v>
       </c>
       <c r="G126">
-        <v>2.997</v>
+        <v>2.78</v>
       </c>
       <c r="H126">
-        <v>1.06</v>
+        <v>1.349</v>
       </c>
       <c r="I126">
-        <v>1.563</v>
+        <v>1.472</v>
       </c>
       <c r="J126">
-        <v>1.586</v>
+        <v>1.46</v>
       </c>
       <c r="V126" t="s">
         <v>147</v>
@@ -5777,34 +5777,34 @@
     </row>
     <row r="127" spans="1:23">
       <c r="A127" s="2">
-        <v>46178</v>
+        <v>46232</v>
       </c>
       <c r="B127">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C127">
-        <v>2.431</v>
+        <v>2.842</v>
       </c>
       <c r="D127">
-        <v>2.724</v>
+        <v>3.174</v>
       </c>
       <c r="E127">
-        <v>3.665</v>
+        <v>3.588</v>
       </c>
       <c r="F127">
-        <v>1.865</v>
+        <v>3.732</v>
       </c>
       <c r="G127">
-        <v>2.806</v>
+        <v>3.15</v>
       </c>
       <c r="H127">
-        <v>1.036</v>
+        <v>0.903</v>
       </c>
       <c r="I127">
-        <v>1.563</v>
+        <v>1.465</v>
       </c>
       <c r="J127">
-        <v>1.35</v>
+        <v>1.394</v>
       </c>
       <c r="V127" t="s">
         <v>148</v>
@@ -5815,34 +5815,34 @@
     </row>
     <row r="128" spans="1:23">
       <c r="A128" s="2">
-        <v>46178</v>
+        <v>46232</v>
       </c>
       <c r="B128">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C128">
-        <v>1.983</v>
+        <v>3.097</v>
       </c>
       <c r="D128">
-        <v>2.482</v>
+        <v>3.331</v>
       </c>
       <c r="E128">
-        <v>3.666</v>
+        <v>3.699</v>
       </c>
       <c r="F128">
-        <v>2.807</v>
+        <v>3.802</v>
       </c>
       <c r="G128">
-        <v>2.562</v>
+        <v>3.295</v>
       </c>
       <c r="H128">
-        <v>0.9320000000000001</v>
+        <v>1.155</v>
       </c>
       <c r="I128">
-        <v>1.563</v>
+        <v>1.445</v>
       </c>
       <c r="J128">
-        <v>1.16</v>
+        <v>1.499</v>
       </c>
       <c r="V128" t="s">
         <v>149</v>
@@ -5853,34 +5853,34 @@
     </row>
     <row r="129" spans="1:23">
       <c r="A129" s="2">
-        <v>46178</v>
+        <v>46232</v>
       </c>
       <c r="B129">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C129">
-        <v>1.7</v>
+        <v>3.142</v>
       </c>
       <c r="D129">
-        <v>2.005</v>
+        <v>3.41</v>
       </c>
       <c r="E129">
-        <v>2.861</v>
+        <v>3.281</v>
       </c>
       <c r="F129">
-        <v>2.469</v>
+        <v>3.728</v>
       </c>
       <c r="G129">
-        <v>2.107</v>
+        <v>3.281</v>
       </c>
       <c r="H129">
-        <v>0.964</v>
+        <v>0.877</v>
       </c>
       <c r="I129">
-        <v>1.543</v>
+        <v>1.502</v>
       </c>
       <c r="J129">
-        <v>0.974</v>
+        <v>1.391</v>
       </c>
       <c r="V129" t="s">
         <v>150</v>
@@ -5891,34 +5891,34 @@
     </row>
     <row r="130" spans="1:23">
       <c r="A130" s="2">
-        <v>46178</v>
+        <v>46232</v>
       </c>
       <c r="B130">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C130">
-        <v>1.145</v>
+        <v>3.013</v>
       </c>
       <c r="D130">
-        <v>1.354</v>
+        <v>3.292</v>
       </c>
       <c r="E130">
-        <v>2.247</v>
+        <v>3.44</v>
       </c>
       <c r="F130">
-        <v>1.604</v>
+        <v>3.602</v>
       </c>
       <c r="G130">
-        <v>1.448</v>
+        <v>3.144</v>
       </c>
       <c r="H130">
-        <v>0.68</v>
+        <v>0.851</v>
       </c>
       <c r="I130">
-        <v>1.165</v>
+        <v>1.502</v>
       </c>
       <c r="J130">
-        <v>0.588</v>
+        <v>1.382</v>
       </c>
       <c r="V130" t="s">
         <v>151</v>
@@ -5929,34 +5929,34 @@
     </row>
     <row r="131" spans="1:23">
       <c r="A131" s="2">
-        <v>46178</v>
+        <v>46232</v>
       </c>
       <c r="B131">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C131">
-        <v>0.618</v>
+        <v>2.734</v>
       </c>
       <c r="D131">
-        <v>0.713</v>
+        <v>3.187</v>
       </c>
       <c r="E131">
-        <v>1.34</v>
+        <v>3.651</v>
       </c>
       <c r="F131">
-        <v>0.792</v>
+        <v>3.115</v>
       </c>
       <c r="G131">
-        <v>0.8139999999999999</v>
+        <v>2.849</v>
       </c>
       <c r="H131">
-        <v>0.541</v>
+        <v>0.778</v>
       </c>
       <c r="I131">
-        <v>0.643</v>
+        <v>1.502</v>
       </c>
       <c r="J131">
-        <v>0.275</v>
+        <v>1.172</v>
       </c>
       <c r="V131" t="s">
         <v>152</v>
@@ -5967,34 +5967,34 @@
     </row>
     <row r="132" spans="1:23">
       <c r="A132" s="2">
-        <v>46178</v>
+        <v>46232</v>
       </c>
       <c r="B132">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C132">
-        <v>0.275</v>
+        <v>2.187</v>
       </c>
       <c r="D132">
-        <v>0.256</v>
+        <v>2.688</v>
       </c>
       <c r="E132">
-        <v>0.55</v>
+        <v>3.206</v>
       </c>
       <c r="F132">
-        <v>0.224</v>
+        <v>2.309</v>
       </c>
       <c r="G132">
-        <v>0.295</v>
+        <v>2.217</v>
       </c>
       <c r="H132">
-        <v>0.325</v>
+        <v>0.888</v>
       </c>
       <c r="I132">
-        <v>0.269</v>
+        <v>1.169</v>
       </c>
       <c r="J132">
-        <v>0.129</v>
+        <v>1.017</v>
       </c>
       <c r="V132" t="s">
         <v>153</v>
@@ -6005,34 +6005,34 @@
     </row>
     <row r="133" spans="1:23">
       <c r="A133" s="2">
-        <v>46178</v>
+        <v>46232</v>
       </c>
       <c r="B133">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C133">
-        <v>0.046</v>
+        <v>1.564</v>
       </c>
       <c r="D133">
-        <v>0.051</v>
+        <v>1.851</v>
       </c>
       <c r="E133">
-        <v>0.099</v>
+        <v>2.392</v>
       </c>
       <c r="F133">
-        <v>0.037</v>
+        <v>1.559</v>
       </c>
       <c r="G133">
-        <v>0.056</v>
+        <v>1.546</v>
       </c>
       <c r="H133">
-        <v>0.053</v>
+        <v>0.793</v>
       </c>
       <c r="I133">
-        <v>0.025</v>
+        <v>1.038</v>
       </c>
       <c r="J133">
-        <v>0</v>
+        <v>0.66</v>
       </c>
       <c r="V133" t="s">
         <v>154</v>
@@ -6043,34 +6043,34 @@
     </row>
     <row r="134" spans="1:23">
       <c r="A134" s="2">
-        <v>46178</v>
+        <v>46232</v>
       </c>
       <c r="B134">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C134">
-        <v>0</v>
+        <v>0.83</v>
       </c>
       <c r="D134">
-        <v>0</v>
+        <v>0.959</v>
       </c>
       <c r="E134">
-        <v>0</v>
+        <v>1.422</v>
       </c>
       <c r="F134">
-        <v>0</v>
+        <v>0.676</v>
       </c>
       <c r="G134">
-        <v>0</v>
+        <v>0.885</v>
       </c>
       <c r="H134">
-        <v>0</v>
+        <v>0.655</v>
       </c>
       <c r="I134">
-        <v>0</v>
+        <v>0.665</v>
       </c>
       <c r="J134">
-        <v>0.013</v>
+        <v>0.262</v>
       </c>
       <c r="V134" t="s">
         <v>155</v>
@@ -6081,34 +6081,34 @@
     </row>
     <row r="135" spans="1:23">
       <c r="A135" s="2">
-        <v>46178</v>
+        <v>46232</v>
       </c>
       <c r="B135">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C135">
-        <v>0</v>
+        <v>0.206</v>
       </c>
       <c r="D135">
-        <v>0</v>
+        <v>0.302</v>
       </c>
       <c r="E135">
-        <v>0</v>
+        <v>0.524</v>
       </c>
       <c r="F135">
-        <v>0</v>
+        <v>0.193</v>
       </c>
       <c r="G135">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="H135">
-        <v>0</v>
+        <v>0.328</v>
       </c>
       <c r="I135">
-        <v>0</v>
+        <v>0.208</v>
       </c>
       <c r="J135">
-        <v>0.013</v>
+        <v>0.11</v>
       </c>
       <c r="V135" t="s">
         <v>156</v>
@@ -6119,34 +6119,34 @@
     </row>
     <row r="136" spans="1:23">
       <c r="A136" s="2">
-        <v>46178</v>
+        <v>46232</v>
       </c>
       <c r="B136">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C136">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="D136">
-        <v>0</v>
+        <v>0.074</v>
       </c>
       <c r="E136">
-        <v>0</v>
+        <v>0.106</v>
       </c>
       <c r="F136">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="G136">
-        <v>0</v>
+        <v>0.042</v>
       </c>
       <c r="H136">
-        <v>0</v>
+        <v>0.044</v>
       </c>
       <c r="I136">
-        <v>0</v>
+        <v>0.021</v>
       </c>
       <c r="J136">
-        <v>0.013</v>
+        <v>0</v>
       </c>
       <c r="V136" t="s">
         <v>157</v>
@@ -6157,10 +6157,10 @@
     </row>
     <row r="137" spans="1:23">
       <c r="A137" s="2">
-        <v>46179</v>
+        <v>46232</v>
       </c>
       <c r="B137">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="C137">
         <v>0</v>
@@ -6169,7 +6169,7 @@
         <v>0</v>
       </c>
       <c r="E137">
-        <v>0</v>
+        <v>0.012</v>
       </c>
       <c r="F137">
         <v>0</v>
@@ -6195,10 +6195,10 @@
     </row>
     <row r="138" spans="1:23">
       <c r="A138" s="2">
-        <v>46179</v>
+        <v>46232</v>
       </c>
       <c r="B138">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="C138">
         <v>0</v>
@@ -6233,10 +6233,10 @@
     </row>
     <row r="139" spans="1:23">
       <c r="A139" s="2">
-        <v>46179</v>
+        <v>46232</v>
       </c>
       <c r="B139">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="C139">
         <v>0</v>
@@ -6271,10 +6271,10 @@
     </row>
     <row r="140" spans="1:23">
       <c r="A140" s="2">
-        <v>46179</v>
+        <v>46233</v>
       </c>
       <c r="B140">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C140">
         <v>0</v>
@@ -6298,7 +6298,7 @@
         <v>0</v>
       </c>
       <c r="J140">
-        <v>0.014</v>
+        <v>0.021</v>
       </c>
       <c r="V140" t="s">
         <v>161</v>
@@ -6309,10 +6309,10 @@
     </row>
     <row r="141" spans="1:23">
       <c r="A141" s="2">
-        <v>46179</v>
+        <v>46233</v>
       </c>
       <c r="B141">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C141">
         <v>0</v>
@@ -6336,7 +6336,7 @@
         <v>0</v>
       </c>
       <c r="J141">
-        <v>0.014</v>
+        <v>0.015</v>
       </c>
       <c r="V141" t="s">
         <v>162</v>
@@ -6347,10 +6347,10 @@
     </row>
     <row r="142" spans="1:23">
       <c r="A142" s="2">
-        <v>46179</v>
+        <v>46233</v>
       </c>
       <c r="B142">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C142">
         <v>0</v>
@@ -6362,10 +6362,10 @@
         <v>0</v>
       </c>
       <c r="F142">
-        <v>0.035</v>
+        <v>0</v>
       </c>
       <c r="G142">
-        <v>0.012</v>
+        <v>0</v>
       </c>
       <c r="H142">
         <v>0</v>
@@ -6374,7 +6374,7 @@
         <v>0</v>
       </c>
       <c r="J142">
-        <v>0.038</v>
+        <v>0.015</v>
       </c>
       <c r="V142" t="s">
         <v>163</v>
@@ -6385,34 +6385,34 @@
     </row>
     <row r="143" spans="1:23">
       <c r="A143" s="2">
-        <v>46179</v>
+        <v>46233</v>
       </c>
       <c r="B143">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C143">
-        <v>0.075</v>
+        <v>0</v>
       </c>
       <c r="D143">
-        <v>0.104</v>
+        <v>0</v>
       </c>
       <c r="E143">
-        <v>0.173</v>
+        <v>0</v>
       </c>
       <c r="F143">
-        <v>0.331</v>
+        <v>0</v>
       </c>
       <c r="G143">
-        <v>0.196</v>
+        <v>0</v>
       </c>
       <c r="H143">
-        <v>0.145</v>
+        <v>0</v>
       </c>
       <c r="I143">
-        <v>0.144</v>
+        <v>0</v>
       </c>
       <c r="J143">
-        <v>0.104</v>
+        <v>0.015</v>
       </c>
       <c r="V143" t="s">
         <v>164</v>
@@ -6423,34 +6423,34 @@
     </row>
     <row r="144" spans="1:23">
       <c r="A144" s="2">
-        <v>46179</v>
+        <v>46233</v>
       </c>
       <c r="B144">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C144">
-        <v>0.446</v>
+        <v>0</v>
       </c>
       <c r="D144">
-        <v>0.414</v>
+        <v>0</v>
       </c>
       <c r="E144">
-        <v>0.739</v>
+        <v>0</v>
       </c>
       <c r="F144">
-        <v>1.111</v>
+        <v>0</v>
       </c>
       <c r="G144">
-        <v>0.571</v>
+        <v>0</v>
       </c>
       <c r="H144">
-        <v>0.542</v>
+        <v>0</v>
       </c>
       <c r="I144">
-        <v>0.521</v>
+        <v>0</v>
       </c>
       <c r="J144">
-        <v>0.487</v>
+        <v>0.015</v>
       </c>
       <c r="V144" t="s">
         <v>165</v>
@@ -6461,34 +6461,34 @@
     </row>
     <row r="145" spans="1:23">
       <c r="A145" s="2">
-        <v>46179</v>
+        <v>46233</v>
       </c>
       <c r="B145">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C145">
-        <v>0.9330000000000001</v>
+        <v>0</v>
       </c>
       <c r="D145">
-        <v>1.044</v>
+        <v>0</v>
       </c>
       <c r="E145">
-        <v>1.671</v>
+        <v>0</v>
       </c>
       <c r="F145">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="G145">
-        <v>1.337</v>
+        <v>0</v>
       </c>
       <c r="H145">
-        <v>0.8070000000000001</v>
+        <v>0</v>
       </c>
       <c r="I145">
-        <v>0.772</v>
+        <v>0</v>
       </c>
       <c r="J145">
-        <v>0.956</v>
+        <v>0.015</v>
       </c>
       <c r="V145" t="s">
         <v>166</v>
@@ -6499,34 +6499,34 @@
     </row>
     <row r="146" spans="1:23">
       <c r="A146" s="2">
-        <v>46179</v>
+        <v>46233</v>
       </c>
       <c r="B146">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C146">
-        <v>1.612</v>
+        <v>0.047</v>
       </c>
       <c r="D146">
-        <v>1.786</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="E146">
-        <v>2.518</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F146">
-        <v>3.183</v>
+        <v>0.236</v>
       </c>
       <c r="G146">
-        <v>2.209</v>
+        <v>0.11</v>
       </c>
       <c r="H146">
-        <v>1.188</v>
+        <v>0.104</v>
       </c>
       <c r="I146">
-        <v>1.213</v>
+        <v>0.074</v>
       </c>
       <c r="J146">
-        <v>1.264</v>
+        <v>0.062</v>
       </c>
       <c r="V146" t="s">
         <v>167</v>
@@ -6537,34 +6537,34 @@
     </row>
     <row r="147" spans="1:23">
       <c r="A147" s="2">
-        <v>46179</v>
+        <v>46233</v>
       </c>
       <c r="B147">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C147">
-        <v>2.014</v>
+        <v>0.376</v>
       </c>
       <c r="D147">
-        <v>2.284</v>
+        <v>0.397</v>
       </c>
       <c r="E147">
-        <v>2.962</v>
+        <v>0.532</v>
       </c>
       <c r="F147">
-        <v>2.926</v>
+        <v>0.916</v>
       </c>
       <c r="G147">
-        <v>2.763</v>
+        <v>0.506</v>
       </c>
       <c r="H147">
-        <v>1.156</v>
+        <v>0.431</v>
       </c>
       <c r="I147">
-        <v>1.512</v>
+        <v>0.443</v>
       </c>
       <c r="J147">
-        <v>1.567</v>
+        <v>0.42</v>
       </c>
       <c r="V147" t="s">
         <v>168</v>
@@ -6575,34 +6575,34 @@
     </row>
     <row r="148" spans="1:23">
       <c r="A148" s="2">
-        <v>46179</v>
+        <v>46233</v>
       </c>
       <c r="B148">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C148">
-        <v>2.365</v>
+        <v>1.035</v>
       </c>
       <c r="D148">
-        <v>2.536</v>
+        <v>1.057</v>
       </c>
       <c r="E148">
-        <v>3.46</v>
+        <v>1.522</v>
       </c>
       <c r="F148">
-        <v>1.854</v>
+        <v>2.056</v>
       </c>
       <c r="G148">
-        <v>3.102</v>
+        <v>1.49</v>
       </c>
       <c r="H148">
-        <v>1.074</v>
+        <v>0.841</v>
       </c>
       <c r="I148">
-        <v>1.563</v>
+        <v>0.906</v>
       </c>
       <c r="J148">
-        <v>1.533</v>
+        <v>0.773</v>
       </c>
       <c r="V148" t="s">
         <v>169</v>
@@ -6613,34 +6613,34 @@
     </row>
     <row r="149" spans="1:23">
       <c r="A149" s="2">
-        <v>46179</v>
+        <v>46233</v>
       </c>
       <c r="B149">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C149">
-        <v>2.428</v>
+        <v>1.74</v>
       </c>
       <c r="D149">
-        <v>2.795</v>
+        <v>2.028</v>
       </c>
       <c r="E149">
-        <v>3.486</v>
+        <v>2.443</v>
       </c>
       <c r="F149">
-        <v>1.77</v>
+        <v>2.961</v>
       </c>
       <c r="G149">
-        <v>3.273</v>
+        <v>2.337</v>
       </c>
       <c r="H149">
-        <v>1.086</v>
+        <v>1.279</v>
       </c>
       <c r="I149">
-        <v>1.563</v>
+        <v>1.252</v>
       </c>
       <c r="J149">
-        <v>1.561</v>
+        <v>1.08</v>
       </c>
       <c r="V149" t="s">
         <v>170</v>
@@ -6651,34 +6651,34 @@
     </row>
     <row r="150" spans="1:23">
       <c r="A150" s="2">
-        <v>46179</v>
+        <v>46233</v>
       </c>
       <c r="B150">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C150">
-        <v>2.376</v>
+        <v>2.336</v>
       </c>
       <c r="D150">
-        <v>2.833</v>
+        <v>2.563</v>
       </c>
       <c r="E150">
-        <v>3.451</v>
+        <v>3.614</v>
       </c>
       <c r="F150">
-        <v>3.256</v>
+        <v>3.805</v>
       </c>
       <c r="G150">
-        <v>3.326</v>
+        <v>3.051</v>
       </c>
       <c r="H150">
-        <v>1.06</v>
+        <v>0.897</v>
       </c>
       <c r="I150">
-        <v>1.563</v>
+        <v>1.437</v>
       </c>
       <c r="J150">
-        <v>1.52</v>
+        <v>1.432</v>
       </c>
       <c r="V150" t="s">
         <v>171</v>
@@ -6689,34 +6689,34 @@
     </row>
     <row r="151" spans="1:23">
       <c r="A151" s="2">
-        <v>46179</v>
+        <v>46233</v>
       </c>
       <c r="B151">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C151">
-        <v>2.269</v>
+        <v>2.639</v>
       </c>
       <c r="D151">
-        <v>2.632</v>
+        <v>3.059</v>
       </c>
       <c r="E151">
-        <v>3.548</v>
+        <v>3.923</v>
       </c>
       <c r="F151">
-        <v>3.378</v>
+        <v>4.173</v>
       </c>
       <c r="G151">
-        <v>3.313</v>
+        <v>3.425</v>
       </c>
       <c r="H151">
-        <v>1.02</v>
+        <v>0.879</v>
       </c>
       <c r="I151">
-        <v>1.563</v>
+        <v>1.445</v>
       </c>
       <c r="J151">
-        <v>1.368</v>
+        <v>1.494</v>
       </c>
       <c r="V151" t="s">
         <v>172</v>
@@ -6727,34 +6727,34 @@
     </row>
     <row r="152" spans="1:23">
       <c r="A152" s="2">
-        <v>46179</v>
+        <v>46233</v>
       </c>
       <c r="B152">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C152">
-        <v>1.91</v>
+        <v>2.851</v>
       </c>
       <c r="D152">
-        <v>2.338</v>
+        <v>3.032</v>
       </c>
       <c r="E152">
-        <v>3.258</v>
+        <v>3.583</v>
       </c>
       <c r="F152">
-        <v>3.017</v>
+        <v>4.198</v>
       </c>
       <c r="G152">
-        <v>2.868</v>
+        <v>3.575</v>
       </c>
       <c r="H152">
-        <v>0.913</v>
+        <v>1.436</v>
       </c>
       <c r="I152">
-        <v>1.563</v>
+        <v>1.445</v>
       </c>
       <c r="J152">
-        <v>1.178</v>
+        <v>1.556</v>
       </c>
       <c r="V152" t="s">
         <v>173</v>
@@ -6765,34 +6765,34 @@
     </row>
     <row r="153" spans="1:23">
       <c r="A153" s="2">
-        <v>46179</v>
+        <v>46233</v>
       </c>
       <c r="B153">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C153">
-        <v>1.651</v>
+        <v>2.955</v>
       </c>
       <c r="D153">
-        <v>1.93</v>
+        <v>3.058</v>
       </c>
       <c r="E153">
-        <v>2.684</v>
+        <v>3.733</v>
       </c>
       <c r="F153">
-        <v>2.507</v>
+        <v>4.196</v>
       </c>
       <c r="G153">
-        <v>2.231</v>
+        <v>3.576</v>
       </c>
       <c r="H153">
-        <v>0.9379999999999999</v>
+        <v>0.951</v>
       </c>
       <c r="I153">
-        <v>1.543</v>
+        <v>1.502</v>
       </c>
       <c r="J153">
-        <v>1.009</v>
+        <v>1.467</v>
       </c>
       <c r="V153" t="s">
         <v>174</v>
@@ -6803,34 +6803,34 @@
     </row>
     <row r="154" spans="1:23">
       <c r="A154" s="2">
-        <v>46179</v>
+        <v>46233</v>
       </c>
       <c r="B154">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C154">
-        <v>1.065</v>
+        <v>2.786</v>
       </c>
       <c r="D154">
-        <v>1.353</v>
+        <v>3.102</v>
       </c>
       <c r="E154">
-        <v>2.197</v>
+        <v>3.644</v>
       </c>
       <c r="F154">
-        <v>1.66</v>
+        <v>4.001</v>
       </c>
       <c r="G154">
-        <v>1.476</v>
+        <v>3.513</v>
       </c>
       <c r="H154">
-        <v>0.68</v>
+        <v>0.906</v>
       </c>
       <c r="I154">
-        <v>1.148</v>
+        <v>1.502</v>
       </c>
       <c r="J154">
-        <v>0.596</v>
+        <v>1.41</v>
       </c>
       <c r="V154" t="s">
         <v>175</v>
@@ -6841,34 +6841,34 @@
     </row>
     <row r="155" spans="1:23">
       <c r="A155" s="2">
-        <v>46179</v>
+        <v>46233</v>
       </c>
       <c r="B155">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C155">
-        <v>0.593</v>
+        <v>2.474</v>
       </c>
       <c r="D155">
-        <v>0.727</v>
+        <v>3.005</v>
       </c>
       <c r="E155">
-        <v>1.276</v>
+        <v>3.636</v>
       </c>
       <c r="F155">
-        <v>0.781</v>
+        <v>3.447</v>
       </c>
       <c r="G155">
-        <v>0.822</v>
+        <v>3.166</v>
       </c>
       <c r="H155">
-        <v>0.541</v>
+        <v>0.99</v>
       </c>
       <c r="I155">
-        <v>0.661</v>
+        <v>1.502</v>
       </c>
       <c r="J155">
-        <v>0.294</v>
+        <v>1.22</v>
       </c>
       <c r="V155" t="s">
         <v>176</v>
@@ -6879,34 +6879,34 @@
     </row>
     <row r="156" spans="1:23">
       <c r="A156" s="2">
-        <v>46179</v>
+        <v>46233</v>
       </c>
       <c r="B156">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C156">
-        <v>0.301</v>
+        <v>2.016</v>
       </c>
       <c r="D156">
-        <v>0.256</v>
+        <v>2.593</v>
       </c>
       <c r="E156">
-        <v>0.574</v>
+        <v>3.154</v>
       </c>
       <c r="F156">
-        <v>0.239</v>
+        <v>2.567</v>
       </c>
       <c r="G156">
-        <v>0.294</v>
+        <v>2.581</v>
       </c>
       <c r="H156">
-        <v>0.338</v>
+        <v>1.044</v>
       </c>
       <c r="I156">
-        <v>0.328</v>
+        <v>1.502</v>
       </c>
       <c r="J156">
-        <v>0.119</v>
+        <v>0.979</v>
       </c>
       <c r="V156" t="s">
         <v>177</v>
@@ -6917,34 +6917,34 @@
     </row>
     <row r="157" spans="1:23">
       <c r="A157" s="2">
-        <v>46179</v>
+        <v>46233</v>
       </c>
       <c r="B157">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C157">
-        <v>0.05</v>
+        <v>1.473</v>
       </c>
       <c r="D157">
-        <v>0.065</v>
+        <v>1.76</v>
       </c>
       <c r="E157">
-        <v>0.106</v>
+        <v>2.317</v>
       </c>
       <c r="F157">
-        <v>0.04</v>
+        <v>1.599</v>
       </c>
       <c r="G157">
-        <v>0.06</v>
+        <v>1.676</v>
       </c>
       <c r="H157">
-        <v>0.053</v>
+        <v>0.919</v>
       </c>
       <c r="I157">
-        <v>0.042</v>
+        <v>1.087</v>
       </c>
       <c r="J157">
-        <v>0</v>
+        <v>0.638</v>
       </c>
       <c r="V157" t="s">
         <v>178</v>
@@ -6955,34 +6955,34 @@
     </row>
     <row r="158" spans="1:23">
       <c r="A158" s="2">
-        <v>46179</v>
+        <v>46233</v>
       </c>
       <c r="B158">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C158">
-        <v>0</v>
+        <v>0.773</v>
       </c>
       <c r="D158">
-        <v>0</v>
+        <v>0.921</v>
       </c>
       <c r="E158">
-        <v>0</v>
+        <v>1.384</v>
       </c>
       <c r="F158">
-        <v>0</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="G158">
-        <v>0</v>
+        <v>0.951</v>
       </c>
       <c r="H158">
-        <v>0</v>
+        <v>0.675</v>
       </c>
       <c r="I158">
-        <v>0</v>
+        <v>0.518</v>
       </c>
       <c r="J158">
-        <v>0</v>
+        <v>0.263</v>
       </c>
       <c r="V158" t="s">
         <v>179</v>
@@ -6993,34 +6993,34 @@
     </row>
     <row r="159" spans="1:23">
       <c r="A159" s="2">
-        <v>46179</v>
+        <v>46233</v>
       </c>
       <c r="B159">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C159">
-        <v>0</v>
+        <v>0.215</v>
       </c>
       <c r="D159">
-        <v>0</v>
+        <v>0.286</v>
       </c>
       <c r="E159">
-        <v>0</v>
+        <v>0.477</v>
       </c>
       <c r="F159">
-        <v>0</v>
+        <v>0.195</v>
       </c>
       <c r="G159">
-        <v>0</v>
+        <v>0.236</v>
       </c>
       <c r="H159">
-        <v>0</v>
+        <v>0.304</v>
       </c>
       <c r="I159">
-        <v>0</v>
+        <v>0.328</v>
       </c>
       <c r="J159">
-        <v>0</v>
+        <v>0.121</v>
       </c>
       <c r="V159" t="s">
         <v>180</v>
@@ -7031,34 +7031,34 @@
     </row>
     <row r="160" spans="1:23">
       <c r="A160" s="2">
-        <v>46179</v>
+        <v>46233</v>
       </c>
       <c r="B160">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C160">
-        <v>0</v>
+        <v>0.042</v>
       </c>
       <c r="D160">
-        <v>0</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="E160">
-        <v>0</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="F160">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="G160">
-        <v>0</v>
+        <v>0.042</v>
       </c>
       <c r="H160">
-        <v>0</v>
+        <v>0.041</v>
       </c>
       <c r="I160">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="J160">
-        <v>0.013</v>
+        <v>0</v>
       </c>
       <c r="V160" t="s">
         <v>181</v>
@@ -7069,10 +7069,10 @@
     </row>
     <row r="161" spans="1:23">
       <c r="A161" s="2">
-        <v>46180</v>
+        <v>46233</v>
       </c>
       <c r="B161">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="C161">
         <v>0</v>
@@ -7096,7 +7096,7 @@
         <v>0</v>
       </c>
       <c r="J161">
-        <v>0.014</v>
+        <v>0</v>
       </c>
       <c r="V161" t="s">
         <v>182</v>
@@ -7107,10 +7107,10 @@
     </row>
     <row r="162" spans="1:23">
       <c r="A162" s="2">
-        <v>46180</v>
+        <v>46233</v>
       </c>
       <c r="B162">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="C162">
         <v>0</v>
@@ -7119,7 +7119,7 @@
         <v>0</v>
       </c>
       <c r="E162">
-        <v>0</v>
+        <v>0.011</v>
       </c>
       <c r="F162">
         <v>0</v>
@@ -7145,10 +7145,10 @@
     </row>
     <row r="163" spans="1:23">
       <c r="A163" s="2">
-        <v>46180</v>
+        <v>46233</v>
       </c>
       <c r="B163">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="C163">
         <v>0</v>
@@ -7183,10 +7183,10 @@
     </row>
     <row r="164" spans="1:23">
       <c r="A164" s="2">
-        <v>46180</v>
+        <v>46234</v>
       </c>
       <c r="B164">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C164">
         <v>0</v>
@@ -7210,7 +7210,7 @@
         <v>0</v>
       </c>
       <c r="J164">
-        <v>0.014</v>
+        <v>0.015</v>
       </c>
       <c r="V164" t="s">
         <v>185</v>
@@ -7221,10 +7221,10 @@
     </row>
     <row r="165" spans="1:23">
       <c r="A165" s="2">
-        <v>46180</v>
+        <v>46234</v>
       </c>
       <c r="B165">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C165">
         <v>0</v>
@@ -7248,7 +7248,7 @@
         <v>0</v>
       </c>
       <c r="J165">
-        <v>0.014</v>
+        <v>0.015</v>
       </c>
       <c r="V165" t="s">
         <v>186</v>
@@ -7259,10 +7259,10 @@
     </row>
     <row r="166" spans="1:23">
       <c r="A166" s="2">
-        <v>46180</v>
+        <v>46234</v>
       </c>
       <c r="B166">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C166">
         <v>0</v>
@@ -7274,10 +7274,10 @@
         <v>0</v>
       </c>
       <c r="F166">
-        <v>0.035</v>
+        <v>0</v>
       </c>
       <c r="G166">
-        <v>0.012</v>
+        <v>0</v>
       </c>
       <c r="H166">
         <v>0</v>
@@ -7286,7 +7286,7 @@
         <v>0</v>
       </c>
       <c r="J166">
-        <v>0.038</v>
+        <v>0.015</v>
       </c>
       <c r="V166" t="s">
         <v>187</v>
@@ -7297,34 +7297,34 @@
     </row>
     <row r="167" spans="1:23">
       <c r="A167" s="2">
-        <v>46180</v>
+        <v>46234</v>
       </c>
       <c r="B167">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C167">
-        <v>0.075</v>
+        <v>0</v>
       </c>
       <c r="D167">
-        <v>0.102</v>
+        <v>0</v>
       </c>
       <c r="E167">
-        <v>0.179</v>
+        <v>0</v>
       </c>
       <c r="F167">
-        <v>0.336</v>
+        <v>0</v>
       </c>
       <c r="G167">
-        <v>0.196</v>
+        <v>0</v>
       </c>
       <c r="H167">
-        <v>0.203</v>
+        <v>0</v>
       </c>
       <c r="I167">
-        <v>0.183</v>
+        <v>0</v>
       </c>
       <c r="J167">
-        <v>0.075</v>
+        <v>0.015</v>
       </c>
       <c r="V167" t="s">
         <v>188</v>
@@ -7335,34 +7335,34 @@
     </row>
     <row r="168" spans="1:23">
       <c r="A168" s="2">
-        <v>46180</v>
+        <v>46234</v>
       </c>
       <c r="B168">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C168">
-        <v>0.451</v>
+        <v>0</v>
       </c>
       <c r="D168">
-        <v>0.431</v>
+        <v>0</v>
       </c>
       <c r="E168">
-        <v>0.747</v>
+        <v>0</v>
       </c>
       <c r="F168">
-        <v>1.134</v>
+        <v>0</v>
       </c>
       <c r="G168">
-        <v>0.591</v>
+        <v>0</v>
       </c>
       <c r="H168">
-        <v>0.582</v>
+        <v>0</v>
       </c>
       <c r="I168">
-        <v>0.5649999999999999</v>
+        <v>0</v>
       </c>
       <c r="J168">
-        <v>0.388</v>
+        <v>0.015</v>
       </c>
       <c r="V168" t="s">
         <v>189</v>
@@ -7373,34 +7373,34 @@
     </row>
     <row r="169" spans="1:23">
       <c r="A169" s="2">
-        <v>46180</v>
+        <v>46234</v>
       </c>
       <c r="B169">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C169">
-        <v>0.8120000000000001</v>
+        <v>0</v>
       </c>
       <c r="D169">
-        <v>0.9429999999999999</v>
+        <v>0</v>
       </c>
       <c r="E169">
-        <v>1.803</v>
+        <v>0</v>
       </c>
       <c r="F169">
-        <v>2.045</v>
+        <v>0</v>
       </c>
       <c r="G169">
-        <v>1.394</v>
+        <v>0</v>
       </c>
       <c r="H169">
-        <v>1.018</v>
+        <v>0</v>
       </c>
       <c r="I169">
-        <v>0.8179999999999999</v>
+        <v>0</v>
       </c>
       <c r="J169">
-        <v>0.663</v>
+        <v>0.015</v>
       </c>
       <c r="V169" t="s">
         <v>190</v>
@@ -7411,34 +7411,34 @@
     </row>
     <row r="170" spans="1:23">
       <c r="A170" s="2">
-        <v>46180</v>
+        <v>46234</v>
       </c>
       <c r="B170">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C170">
-        <v>1.382</v>
+        <v>0.043</v>
       </c>
       <c r="D170">
-        <v>1.636</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="E170">
-        <v>2.616</v>
+        <v>0.066</v>
       </c>
       <c r="F170">
-        <v>2.72</v>
+        <v>0.235</v>
       </c>
       <c r="G170">
-        <v>2.039</v>
+        <v>0.106</v>
       </c>
       <c r="H170">
-        <v>1.257</v>
+        <v>0.079</v>
       </c>
       <c r="I170">
-        <v>1.147</v>
+        <v>0.064</v>
       </c>
       <c r="J170">
-        <v>1.002</v>
+        <v>0.039</v>
       </c>
       <c r="V170" t="s">
         <v>191</v>

--- a/Forecast.xlsx
+++ b/Forecast.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="193">
   <si>
     <t>Data</t>
   </si>
@@ -79,27 +79,15 @@
     <t>Prediction_Ferma</t>
   </si>
   <si>
+    <t>Prediction_HNG</t>
+  </si>
+  <si>
     <t>Lookup</t>
   </si>
   <si>
     <t>Prediction_3D_Steel</t>
   </si>
   <si>
-    <t>24.07.20267</t>
-  </si>
-  <si>
-    <t>24.07.20268</t>
-  </si>
-  <si>
-    <t>24.07.20269</t>
-  </si>
-  <si>
-    <t>24.07.202610</t>
-  </si>
-  <si>
-    <t>24.07.202611</t>
-  </si>
-  <si>
     <t>24.07.202612</t>
   </si>
   <si>
@@ -590,6 +578,21 @@
   </si>
   <si>
     <t>31.07.20267</t>
+  </si>
+  <si>
+    <t>31.07.20268</t>
+  </si>
+  <si>
+    <t>31.07.20269</t>
+  </si>
+  <si>
+    <t>31.07.202610</t>
+  </si>
+  <si>
+    <t>31.07.202611</t>
+  </si>
+  <si>
+    <t>31.07.202612</t>
   </si>
 </sst>
 </file>
@@ -951,10 +954,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W170"/>
+  <dimension ref="A1:X170"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:23">
+    <row r="1" spans="1:24">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1024,13 +1027,16 @@
       <c r="W1" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="2" spans="1:23">
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24">
       <c r="A2" s="2">
         <v>46227</v>
       </c>
       <c r="B2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -1039,7 +1045,7 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>0.079</v>
+        <v>0.105</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -1056,19 +1062,19 @@
       <c r="J2">
         <v>0</v>
       </c>
-      <c r="V2" t="s">
-        <v>23</v>
-      </c>
-      <c r="W2">
+      <c r="W2" t="s">
+        <v>24</v>
+      </c>
+      <c r="X2">
         <v>0.034</v>
       </c>
     </row>
-    <row r="3" spans="1:23">
+    <row r="3" spans="1:24">
       <c r="A3" s="2">
         <v>46227</v>
       </c>
       <c r="B3">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -1077,7 +1083,7 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>0.079</v>
+        <v>0.104</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -1094,513 +1100,513 @@
       <c r="J3">
         <v>0</v>
       </c>
-      <c r="V3" t="s">
-        <v>24</v>
-      </c>
-      <c r="W3">
+      <c r="W3" t="s">
+        <v>25</v>
+      </c>
+      <c r="X3">
         <v>0.034</v>
       </c>
     </row>
-    <row r="4" spans="1:23">
+    <row r="4" spans="1:24">
       <c r="A4" s="2">
         <v>46227</v>
       </c>
       <c r="B4">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C4">
-        <v>1.116</v>
+        <v>2.235</v>
       </c>
       <c r="D4">
-        <v>1.118</v>
+        <v>2.703</v>
       </c>
       <c r="E4">
-        <v>1.566</v>
+        <v>3.668</v>
       </c>
       <c r="F4">
-        <v>2.156</v>
+        <v>0.838</v>
       </c>
       <c r="G4">
-        <v>1.467</v>
+        <v>1.139</v>
       </c>
       <c r="H4">
-        <v>1.088</v>
+        <v>1.085</v>
       </c>
       <c r="I4">
-        <v>0.865</v>
+        <v>1.537</v>
       </c>
       <c r="J4">
-        <v>0.858</v>
-      </c>
-      <c r="V4" t="s">
-        <v>25</v>
-      </c>
-      <c r="W4">
+        <v>1.419</v>
+      </c>
+      <c r="W4" t="s">
+        <v>26</v>
+      </c>
+      <c r="X4">
         <v>1.509</v>
       </c>
     </row>
-    <row r="5" spans="1:23">
+    <row r="5" spans="1:24">
       <c r="A5" s="2">
         <v>46227</v>
       </c>
       <c r="B5">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C5">
-        <v>1.909</v>
+        <v>1.846</v>
       </c>
       <c r="D5">
-        <v>2.168</v>
+        <v>2.576</v>
       </c>
       <c r="E5">
-        <v>1.571</v>
+        <v>3.629</v>
       </c>
       <c r="F5">
-        <v>3.102</v>
+        <v>2.798</v>
       </c>
       <c r="G5">
-        <v>2.381</v>
+        <v>2.709</v>
       </c>
       <c r="H5">
-        <v>1.419</v>
+        <v>1.068</v>
       </c>
       <c r="I5">
-        <v>0.9409999999999999</v>
+        <v>1.537</v>
       </c>
       <c r="J5">
-        <v>0.998</v>
-      </c>
-      <c r="V5" t="s">
-        <v>26</v>
-      </c>
-      <c r="W5">
+        <v>1.282</v>
+      </c>
+      <c r="W5" t="s">
+        <v>27</v>
+      </c>
+      <c r="X5">
         <v>1.714</v>
       </c>
     </row>
-    <row r="6" spans="1:23">
+    <row r="6" spans="1:24">
       <c r="A6" s="2">
         <v>46227</v>
       </c>
       <c r="B6">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C6">
-        <v>2.225</v>
+        <v>1.81</v>
       </c>
       <c r="D6">
-        <v>2.727</v>
+        <v>2.369</v>
       </c>
       <c r="E6">
-        <v>2.272</v>
+        <v>3.578</v>
       </c>
       <c r="F6">
-        <v>3.387</v>
+        <v>2.597</v>
       </c>
       <c r="G6">
-        <v>2.907</v>
+        <v>2.367</v>
       </c>
       <c r="H6">
-        <v>1.356</v>
+        <v>1.117</v>
       </c>
       <c r="I6">
-        <v>1.416</v>
+        <v>1.361</v>
       </c>
       <c r="J6">
-        <v>1.035</v>
-      </c>
-      <c r="V6" t="s">
-        <v>27</v>
-      </c>
-      <c r="W6">
+        <v>1.067</v>
+      </c>
+      <c r="W6" t="s">
+        <v>28</v>
+      </c>
+      <c r="X6">
         <v>1.603</v>
       </c>
     </row>
-    <row r="7" spans="1:23">
+    <row r="7" spans="1:24">
       <c r="A7" s="2">
         <v>46227</v>
       </c>
       <c r="B7">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C7">
-        <v>2.444</v>
+        <v>1.721</v>
       </c>
       <c r="D7">
-        <v>2.851</v>
+        <v>2.071</v>
       </c>
       <c r="E7">
-        <v>3.287</v>
+        <v>2.762</v>
       </c>
       <c r="F7">
-        <v>3.337</v>
+        <v>2.067</v>
       </c>
       <c r="G7">
-        <v>2.889</v>
+        <v>1.672</v>
       </c>
       <c r="H7">
-        <v>1.276</v>
+        <v>1.148</v>
       </c>
       <c r="I7">
-        <v>1.481</v>
+        <v>1.068</v>
       </c>
       <c r="J7">
-        <v>0.996</v>
-      </c>
-      <c r="V7" t="s">
-        <v>28</v>
-      </c>
-      <c r="W7">
+        <v>0.723</v>
+      </c>
+      <c r="W7" t="s">
+        <v>29</v>
+      </c>
+      <c r="X7">
         <v>1.468</v>
       </c>
     </row>
-    <row r="8" spans="1:23">
+    <row r="8" spans="1:24">
       <c r="A8" s="2">
         <v>46227</v>
       </c>
       <c r="B8">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C8">
-        <v>2.401</v>
+        <v>1.186</v>
       </c>
       <c r="D8">
-        <v>2.883</v>
+        <v>1.452</v>
       </c>
       <c r="E8">
-        <v>3.675</v>
+        <v>2.108</v>
       </c>
       <c r="F8">
-        <v>3.273</v>
+        <v>1.069</v>
       </c>
       <c r="G8">
-        <v>2.841</v>
+        <v>0.856</v>
       </c>
       <c r="H8">
-        <v>1.119</v>
+        <v>0.736</v>
       </c>
       <c r="I8">
-        <v>1.465</v>
+        <v>0.754</v>
       </c>
       <c r="J8">
-        <v>1.114</v>
-      </c>
-      <c r="V8" t="s">
-        <v>29</v>
-      </c>
-      <c r="W8">
+        <v>0.34</v>
+      </c>
+      <c r="W8" t="s">
+        <v>30</v>
+      </c>
+      <c r="X8">
         <v>1.235</v>
       </c>
     </row>
-    <row r="9" spans="1:23">
+    <row r="9" spans="1:24">
       <c r="A9" s="2">
         <v>46227</v>
       </c>
       <c r="B9">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C9">
-        <v>2.375</v>
+        <v>0.593</v>
       </c>
       <c r="D9">
-        <v>2.789</v>
+        <v>0.805</v>
       </c>
       <c r="E9">
-        <v>3.676</v>
+        <v>1.471</v>
       </c>
       <c r="F9">
-        <v>3.242</v>
+        <v>0.517</v>
       </c>
       <c r="G9">
-        <v>2.798</v>
+        <v>0.328</v>
       </c>
       <c r="H9">
-        <v>1.119</v>
+        <v>0.448</v>
       </c>
       <c r="I9">
-        <v>1.502</v>
+        <v>0.535</v>
       </c>
       <c r="J9">
-        <v>1.221</v>
-      </c>
-      <c r="V9" t="s">
-        <v>30</v>
-      </c>
-      <c r="W9">
+        <v>0.215</v>
+      </c>
+      <c r="W9" t="s">
+        <v>31</v>
+      </c>
+      <c r="X9">
         <v>0.679</v>
       </c>
     </row>
-    <row r="10" spans="1:23">
+    <row r="10" spans="1:24">
       <c r="A10" s="2">
         <v>46227</v>
       </c>
       <c r="B10">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C10">
-        <v>2.132</v>
+        <v>0.302</v>
       </c>
       <c r="D10">
-        <v>2.722</v>
+        <v>0.296</v>
       </c>
       <c r="E10">
-        <v>3.643</v>
+        <v>0.641</v>
       </c>
       <c r="F10">
-        <v>3.025</v>
+        <v>0.129</v>
       </c>
       <c r="G10">
-        <v>2.77</v>
+        <v>0.133</v>
       </c>
       <c r="H10">
-        <v>1.056</v>
+        <v>0.172</v>
       </c>
       <c r="I10">
-        <v>1.476</v>
+        <v>0.15</v>
       </c>
       <c r="J10">
-        <v>1.128</v>
-      </c>
-      <c r="V10" t="s">
-        <v>31</v>
-      </c>
-      <c r="W10">
+        <v>0.103</v>
+      </c>
+      <c r="W10" t="s">
+        <v>32</v>
+      </c>
+      <c r="X10">
         <v>0.421</v>
       </c>
     </row>
-    <row r="11" spans="1:23">
+    <row r="11" spans="1:24">
       <c r="A11" s="2">
         <v>46227</v>
       </c>
       <c r="B11">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C11">
-        <v>1.857</v>
+        <v>0.05</v>
       </c>
       <c r="D11">
-        <v>2.403</v>
+        <v>0.077</v>
       </c>
       <c r="E11">
-        <v>3.561</v>
+        <v>0.109</v>
       </c>
       <c r="F11">
-        <v>2.595</v>
+        <v>0.012</v>
       </c>
       <c r="G11">
-        <v>2.365</v>
+        <v>0.016</v>
       </c>
       <c r="H11">
-        <v>1.146</v>
+        <v>0.016</v>
       </c>
       <c r="I11">
-        <v>1.241</v>
+        <v>0.021</v>
       </c>
       <c r="J11">
-        <v>0.993</v>
-      </c>
-      <c r="V11" t="s">
-        <v>32</v>
-      </c>
-      <c r="W11">
+        <v>0.025</v>
+      </c>
+      <c r="W11" t="s">
+        <v>33</v>
+      </c>
+      <c r="X11">
         <v>0.044</v>
       </c>
     </row>
-    <row r="12" spans="1:23">
+    <row r="12" spans="1:24">
       <c r="A12" s="2">
         <v>46227</v>
       </c>
       <c r="B12">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C12">
-        <v>1.719</v>
+        <v>0</v>
       </c>
       <c r="D12">
-        <v>1.943</v>
+        <v>0</v>
       </c>
       <c r="E12">
-        <v>2.727</v>
+        <v>0</v>
       </c>
       <c r="F12">
-        <v>2.054</v>
+        <v>0</v>
       </c>
       <c r="G12">
-        <v>1.687</v>
+        <v>0</v>
       </c>
       <c r="H12">
-        <v>1.169</v>
+        <v>0</v>
       </c>
       <c r="I12">
-        <v>1.045</v>
+        <v>0</v>
       </c>
       <c r="J12">
-        <v>0.8120000000000001</v>
-      </c>
-      <c r="V12" t="s">
-        <v>33</v>
-      </c>
-      <c r="W12">
+        <v>0.013</v>
+      </c>
+      <c r="W12" t="s">
+        <v>34</v>
+      </c>
+      <c r="X12">
         <v>0.049</v>
       </c>
     </row>
-    <row r="13" spans="1:23">
+    <row r="13" spans="1:24">
       <c r="A13" s="2">
         <v>46227</v>
       </c>
       <c r="B13">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C13">
-        <v>1.145</v>
+        <v>0</v>
       </c>
       <c r="D13">
-        <v>1.452</v>
+        <v>0</v>
       </c>
       <c r="E13">
-        <v>1.927</v>
+        <v>0</v>
       </c>
       <c r="F13">
-        <v>1.111</v>
+        <v>0</v>
       </c>
       <c r="G13">
-        <v>1.181</v>
+        <v>0</v>
       </c>
       <c r="H13">
-        <v>0.736</v>
+        <v>0</v>
       </c>
       <c r="I13">
-        <v>0.6870000000000001</v>
+        <v>0</v>
       </c>
       <c r="J13">
-        <v>0.359</v>
-      </c>
-      <c r="V13" t="s">
-        <v>34</v>
-      </c>
-      <c r="W13">
+        <v>0.013</v>
+      </c>
+      <c r="W13" t="s">
+        <v>35</v>
+      </c>
+      <c r="X13">
         <v>0.04</v>
       </c>
     </row>
-    <row r="14" spans="1:23">
+    <row r="14" spans="1:24">
       <c r="A14" s="2">
         <v>46227</v>
       </c>
       <c r="B14">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C14">
-        <v>0.648</v>
+        <v>0</v>
       </c>
       <c r="D14">
-        <v>0.747</v>
+        <v>0</v>
       </c>
       <c r="E14">
-        <v>1.385</v>
+        <v>0</v>
       </c>
       <c r="F14">
-        <v>0.554</v>
+        <v>0</v>
       </c>
       <c r="G14">
-        <v>0.361</v>
+        <v>0</v>
       </c>
       <c r="H14">
-        <v>0.485</v>
+        <v>0</v>
       </c>
       <c r="I14">
-        <v>0.464</v>
+        <v>0</v>
       </c>
       <c r="J14">
-        <v>0.206</v>
-      </c>
-      <c r="V14" t="s">
-        <v>35</v>
-      </c>
-      <c r="W14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:23">
+        <v>0.013</v>
+      </c>
+      <c r="W14" t="s">
+        <v>36</v>
+      </c>
+      <c r="X14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24">
       <c r="A15" s="2">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="B15">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="C15">
-        <v>0.306</v>
+        <v>0</v>
       </c>
       <c r="D15">
-        <v>0.301</v>
+        <v>0</v>
       </c>
       <c r="E15">
-        <v>0.65</v>
+        <v>0</v>
       </c>
       <c r="F15">
-        <v>0.153</v>
+        <v>0</v>
       </c>
       <c r="G15">
-        <v>0.147</v>
+        <v>0</v>
       </c>
       <c r="H15">
-        <v>0.199</v>
+        <v>0</v>
       </c>
       <c r="I15">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="J15">
-        <v>0.107</v>
-      </c>
-      <c r="V15" t="s">
-        <v>36</v>
-      </c>
-      <c r="W15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:23">
+        <v>0.014</v>
+      </c>
+      <c r="W15" t="s">
+        <v>37</v>
+      </c>
+      <c r="X15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24">
       <c r="A16" s="2">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="B16">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="C16">
-        <v>0.066</v>
+        <v>0</v>
       </c>
       <c r="D16">
-        <v>0.078</v>
+        <v>0</v>
       </c>
       <c r="E16">
-        <v>0.133</v>
+        <v>0</v>
       </c>
       <c r="F16">
-        <v>0.018</v>
+        <v>0</v>
       </c>
       <c r="G16">
-        <v>0.023</v>
+        <v>0</v>
       </c>
       <c r="H16">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="I16">
-        <v>0.015</v>
+        <v>0</v>
       </c>
       <c r="J16">
-        <v>0.025</v>
-      </c>
-      <c r="V16" t="s">
-        <v>37</v>
-      </c>
-      <c r="W16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:23">
+        <v>0.014</v>
+      </c>
+      <c r="W16" t="s">
+        <v>38</v>
+      </c>
+      <c r="X16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:24">
       <c r="A17" s="2">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="B17">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -1624,21 +1630,21 @@
         <v>0</v>
       </c>
       <c r="J17">
-        <v>0.013</v>
-      </c>
-      <c r="V17" t="s">
-        <v>38</v>
-      </c>
-      <c r="W17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:23">
+        <v>0.014</v>
+      </c>
+      <c r="W17" t="s">
+        <v>39</v>
+      </c>
+      <c r="X17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:24">
       <c r="A18" s="2">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="B18">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -1662,21 +1668,21 @@
         <v>0</v>
       </c>
       <c r="J18">
-        <v>0.013</v>
-      </c>
-      <c r="V18" t="s">
-        <v>39</v>
-      </c>
-      <c r="W18">
         <v>0.014</v>
       </c>
-    </row>
-    <row r="19" spans="1:23">
+      <c r="W18" t="s">
+        <v>40</v>
+      </c>
+      <c r="X18">
+        <v>0.014</v>
+      </c>
+    </row>
+    <row r="19" spans="1:24">
       <c r="A19" s="2">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="B19">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -1700,21 +1706,21 @@
         <v>0</v>
       </c>
       <c r="J19">
-        <v>0.013</v>
-      </c>
-      <c r="V19" t="s">
-        <v>40</v>
-      </c>
-      <c r="W19">
         <v>0.014</v>
       </c>
-    </row>
-    <row r="20" spans="1:23">
+      <c r="W19" t="s">
+        <v>41</v>
+      </c>
+      <c r="X19">
+        <v>0.014</v>
+      </c>
+    </row>
+    <row r="20" spans="1:24">
       <c r="A20" s="2">
         <v>46228</v>
       </c>
       <c r="B20">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -1740,779 +1746,779 @@
       <c r="J20">
         <v>0.014</v>
       </c>
-      <c r="V20" t="s">
-        <v>41</v>
-      </c>
-      <c r="W20">
+      <c r="W20" t="s">
+        <v>42</v>
+      </c>
+      <c r="X20">
         <v>0.014</v>
       </c>
     </row>
-    <row r="21" spans="1:23">
+    <row r="21" spans="1:24">
       <c r="A21" s="2">
         <v>46228</v>
       </c>
       <c r="B21">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>0.055</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>0.112</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>0.079</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="J21">
+        <v>0.062</v>
+      </c>
+      <c r="W21" t="s">
+        <v>43</v>
+      </c>
+      <c r="X21">
         <v>0.014</v>
       </c>
-      <c r="V21" t="s">
-        <v>42</v>
-      </c>
-      <c r="W21">
-        <v>0.014</v>
-      </c>
-    </row>
-    <row r="22" spans="1:23">
+    </row>
+    <row r="22" spans="1:24">
       <c r="A22" s="2">
         <v>46228</v>
       </c>
       <c r="B22">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>0.371</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>0.401</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>0.648</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>0.794</v>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>0.357</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>0.385</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>0.477</v>
       </c>
       <c r="J22">
+        <v>0.349</v>
+      </c>
+      <c r="W22" t="s">
+        <v>44</v>
+      </c>
+      <c r="X22">
         <v>0.014</v>
       </c>
-      <c r="V22" t="s">
-        <v>43</v>
-      </c>
-      <c r="W22">
-        <v>0.014</v>
-      </c>
-    </row>
-    <row r="23" spans="1:23">
+    </row>
+    <row r="23" spans="1:24">
       <c r="A23" s="2">
         <v>46228</v>
       </c>
       <c r="B23">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>1.094</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>1.687</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>1.885</v>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>1.324</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>0.827</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>0.888</v>
       </c>
       <c r="J23">
+        <v>0.847</v>
+      </c>
+      <c r="W23" t="s">
+        <v>45</v>
+      </c>
+      <c r="X23">
         <v>0.014</v>
       </c>
-      <c r="V23" t="s">
-        <v>44</v>
-      </c>
-      <c r="W23">
-        <v>0.014</v>
-      </c>
-    </row>
-    <row r="24" spans="1:23">
+    </row>
+    <row r="24" spans="1:24">
       <c r="A24" s="2">
         <v>46228</v>
       </c>
       <c r="B24">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>1.863</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>2.086</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>2.964</v>
       </c>
       <c r="F24">
-        <v>0</v>
+        <v>2.698</v>
       </c>
       <c r="G24">
-        <v>0</v>
+        <v>2.053</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>1.206</v>
       </c>
       <c r="I24">
-        <v>0</v>
+        <v>1.222</v>
       </c>
       <c r="J24">
-        <v>0.014</v>
-      </c>
-      <c r="V24" t="s">
-        <v>45</v>
-      </c>
-      <c r="W24">
+        <v>1.021</v>
+      </c>
+      <c r="W24" t="s">
+        <v>46</v>
+      </c>
+      <c r="X24">
         <v>0.041</v>
       </c>
     </row>
-    <row r="25" spans="1:23">
+    <row r="25" spans="1:24">
       <c r="A25" s="2">
         <v>46228</v>
       </c>
       <c r="B25">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>2.277</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>2.574</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>3.751</v>
       </c>
       <c r="F25">
-        <v>0</v>
+        <v>3.192</v>
       </c>
       <c r="G25">
-        <v>0</v>
+        <v>2.697</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>1.385</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>1.554</v>
       </c>
       <c r="J25">
-        <v>0.014</v>
-      </c>
-      <c r="V25" t="s">
-        <v>46</v>
-      </c>
-      <c r="W25">
+        <v>1.096</v>
+      </c>
+      <c r="W25" t="s">
+        <v>47</v>
+      </c>
+      <c r="X25">
         <v>0.06</v>
       </c>
     </row>
-    <row r="26" spans="1:23">
+    <row r="26" spans="1:24">
       <c r="A26" s="2">
         <v>46228</v>
       </c>
       <c r="B26">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C26">
-        <v>0.059</v>
+        <v>2.426</v>
       </c>
       <c r="D26">
-        <v>0.08400000000000001</v>
+        <v>2.799</v>
       </c>
       <c r="E26">
-        <v>0.112</v>
+        <v>3.811</v>
       </c>
       <c r="F26">
-        <v>0.137</v>
+        <v>3.414</v>
       </c>
       <c r="G26">
-        <v>0.067</v>
+        <v>3.017</v>
       </c>
       <c r="H26">
-        <v>0.106</v>
+        <v>1.393</v>
       </c>
       <c r="I26">
-        <v>0.064</v>
+        <v>1.563</v>
       </c>
       <c r="J26">
-        <v>0.062</v>
-      </c>
-      <c r="V26" t="s">
-        <v>47</v>
-      </c>
-      <c r="W26">
+        <v>1.352</v>
+      </c>
+      <c r="W26" t="s">
+        <v>48</v>
+      </c>
+      <c r="X26">
         <v>0.334</v>
       </c>
     </row>
-    <row r="27" spans="1:23">
+    <row r="27" spans="1:24">
       <c r="A27" s="2">
         <v>46228</v>
       </c>
       <c r="B27">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C27">
-        <v>0.372</v>
+        <v>2.655</v>
       </c>
       <c r="D27">
-        <v>0.408</v>
+        <v>2.972</v>
       </c>
       <c r="E27">
-        <v>0.648</v>
+        <v>3.7</v>
       </c>
       <c r="F27">
-        <v>0.708</v>
+        <v>3.471</v>
       </c>
       <c r="G27">
-        <v>0.388</v>
+        <v>3.073</v>
       </c>
       <c r="H27">
-        <v>0.465</v>
+        <v>0.84</v>
       </c>
       <c r="I27">
-        <v>0.463</v>
+        <v>1.563</v>
       </c>
       <c r="J27">
-        <v>0.371</v>
-      </c>
-      <c r="V27" t="s">
-        <v>48</v>
-      </c>
-      <c r="W27">
+        <v>1.374</v>
+      </c>
+      <c r="W27" t="s">
+        <v>49</v>
+      </c>
+      <c r="X27">
         <v>1.057</v>
       </c>
     </row>
-    <row r="28" spans="1:23">
+    <row r="28" spans="1:24">
       <c r="A28" s="2">
         <v>46228</v>
       </c>
       <c r="B28">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C28">
-        <v>1.095</v>
+        <v>2.7</v>
       </c>
       <c r="D28">
-        <v>1.154</v>
+        <v>3.19</v>
       </c>
       <c r="E28">
-        <v>1.691</v>
+        <v>3.493</v>
       </c>
       <c r="F28">
-        <v>1.748</v>
+        <v>3.374</v>
       </c>
       <c r="G28">
-        <v>1.15</v>
+        <v>3.105</v>
       </c>
       <c r="H28">
-        <v>0.85</v>
+        <v>0.835</v>
       </c>
       <c r="I28">
-        <v>0.84</v>
+        <v>1.563</v>
       </c>
       <c r="J28">
-        <v>0.847</v>
-      </c>
-      <c r="V28" t="s">
-        <v>49</v>
-      </c>
-      <c r="W28">
+        <v>1.345</v>
+      </c>
+      <c r="W28" t="s">
+        <v>50</v>
+      </c>
+      <c r="X28">
         <v>1.652</v>
       </c>
     </row>
-    <row r="29" spans="1:23">
+    <row r="29" spans="1:24">
       <c r="A29" s="2">
         <v>46228</v>
       </c>
       <c r="B29">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C29">
-        <v>1.84</v>
+        <v>2.641</v>
       </c>
       <c r="D29">
-        <v>2.091</v>
+        <v>3.018</v>
       </c>
       <c r="E29">
-        <v>2.964</v>
+        <v>3.58</v>
       </c>
       <c r="F29">
-        <v>2.6</v>
+        <v>3.298</v>
       </c>
       <c r="G29">
-        <v>2.071</v>
+        <v>3.019</v>
       </c>
       <c r="H29">
-        <v>1.281</v>
+        <v>0.756</v>
       </c>
       <c r="I29">
-        <v>1.276</v>
+        <v>1.563</v>
       </c>
       <c r="J29">
-        <v>1.021</v>
-      </c>
-      <c r="V29" t="s">
-        <v>50</v>
-      </c>
-      <c r="W29">
+        <v>1.349</v>
+      </c>
+      <c r="W29" t="s">
+        <v>51</v>
+      </c>
+      <c r="X29">
         <v>2.17</v>
       </c>
     </row>
-    <row r="30" spans="1:23">
+    <row r="30" spans="1:24">
       <c r="A30" s="2">
         <v>46228</v>
       </c>
       <c r="B30">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C30">
-        <v>2.311</v>
+        <v>2.206</v>
       </c>
       <c r="D30">
-        <v>2.629</v>
+        <v>2.907</v>
       </c>
       <c r="E30">
-        <v>3.758</v>
+        <v>3.429</v>
       </c>
       <c r="F30">
-        <v>3.155</v>
+        <v>2.95</v>
       </c>
       <c r="G30">
-        <v>2.682</v>
+        <v>2.668</v>
       </c>
       <c r="H30">
-        <v>1.373</v>
+        <v>0.792</v>
       </c>
       <c r="I30">
-        <v>1.554</v>
+        <v>1.537</v>
       </c>
       <c r="J30">
-        <v>1.089</v>
-      </c>
-      <c r="V30" t="s">
-        <v>51</v>
-      </c>
-      <c r="W30">
+        <v>1.092</v>
+      </c>
+      <c r="W30" t="s">
+        <v>52</v>
+      </c>
+      <c r="X30">
         <v>1.983</v>
       </c>
     </row>
-    <row r="31" spans="1:23">
+    <row r="31" spans="1:24">
       <c r="A31" s="2">
         <v>46228</v>
       </c>
       <c r="B31">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C31">
-        <v>2.444</v>
+        <v>1.918</v>
       </c>
       <c r="D31">
-        <v>2.816</v>
+        <v>2.432</v>
       </c>
       <c r="E31">
-        <v>3.734</v>
+        <v>3.137</v>
       </c>
       <c r="F31">
-        <v>3.339</v>
+        <v>2.389</v>
       </c>
       <c r="G31">
-        <v>2.854</v>
+        <v>2.24</v>
       </c>
       <c r="H31">
-        <v>1.242</v>
+        <v>0.863</v>
       </c>
       <c r="I31">
-        <v>1.563</v>
+        <v>1.23</v>
       </c>
       <c r="J31">
-        <v>1.285</v>
-      </c>
-      <c r="V31" t="s">
-        <v>52</v>
-      </c>
-      <c r="W31">
+        <v>0.924</v>
+      </c>
+      <c r="W31" t="s">
+        <v>53</v>
+      </c>
+      <c r="X31">
         <v>1.764</v>
       </c>
     </row>
-    <row r="32" spans="1:23">
+    <row r="32" spans="1:24">
       <c r="A32" s="2">
         <v>46228</v>
       </c>
       <c r="B32">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C32">
-        <v>2.695</v>
+        <v>1.351</v>
       </c>
       <c r="D32">
-        <v>3.182</v>
+        <v>1.847</v>
       </c>
       <c r="E32">
-        <v>3.648</v>
+        <v>2.536</v>
       </c>
       <c r="F32">
-        <v>3.364</v>
+        <v>1.619</v>
       </c>
       <c r="G32">
-        <v>2.991</v>
+        <v>1.665</v>
       </c>
       <c r="H32">
-        <v>0.761</v>
+        <v>0.911</v>
       </c>
       <c r="I32">
-        <v>1.563</v>
+        <v>0.954</v>
       </c>
       <c r="J32">
-        <v>1.374</v>
-      </c>
-      <c r="V32" t="s">
-        <v>53</v>
-      </c>
-      <c r="W32">
+        <v>0.672</v>
+      </c>
+      <c r="W32" t="s">
+        <v>54</v>
+      </c>
+      <c r="X32">
         <v>1.184</v>
       </c>
     </row>
-    <row r="33" spans="1:23">
+    <row r="33" spans="1:24">
       <c r="A33" s="2">
         <v>46228</v>
       </c>
       <c r="B33">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C33">
-        <v>2.715</v>
+        <v>0.757</v>
       </c>
       <c r="D33">
-        <v>3.224</v>
+        <v>0.964</v>
       </c>
       <c r="E33">
-        <v>3.566</v>
+        <v>1.413</v>
       </c>
       <c r="F33">
-        <v>3.359</v>
+        <v>0.701</v>
       </c>
       <c r="G33">
-        <v>3.002</v>
+        <v>0.927</v>
       </c>
       <c r="H33">
-        <v>0.824</v>
+        <v>0.68</v>
       </c>
       <c r="I33">
-        <v>1.563</v>
+        <v>0.635</v>
       </c>
       <c r="J33">
-        <v>1.412</v>
-      </c>
-      <c r="V33" t="s">
-        <v>54</v>
-      </c>
-      <c r="W33">
+        <v>0.371</v>
+      </c>
+      <c r="W33" t="s">
+        <v>55</v>
+      </c>
+      <c r="X33">
         <v>0.583</v>
       </c>
     </row>
-    <row r="34" spans="1:23">
+    <row r="34" spans="1:24">
       <c r="A34" s="2">
         <v>46228</v>
       </c>
       <c r="B34">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C34">
-        <v>2.632</v>
+        <v>0.262</v>
       </c>
       <c r="D34">
-        <v>3.168</v>
+        <v>0.324</v>
       </c>
       <c r="E34">
-        <v>3.524</v>
+        <v>0.672</v>
       </c>
       <c r="F34">
-        <v>3.289</v>
+        <v>0.228</v>
       </c>
       <c r="G34">
-        <v>2.894</v>
+        <v>0.281</v>
       </c>
       <c r="H34">
-        <v>0.73</v>
+        <v>0.351</v>
       </c>
       <c r="I34">
-        <v>1.537</v>
+        <v>0.328</v>
       </c>
       <c r="J34">
-        <v>1.345</v>
-      </c>
-      <c r="V34" t="s">
-        <v>55</v>
-      </c>
-      <c r="W34">
+        <v>0.129</v>
+      </c>
+      <c r="W34" t="s">
+        <v>56</v>
+      </c>
+      <c r="X34">
         <v>0.427</v>
       </c>
     </row>
-    <row r="35" spans="1:23">
+    <row r="35" spans="1:24">
       <c r="A35" s="2">
         <v>46228</v>
       </c>
       <c r="B35">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C35">
-        <v>2.204</v>
+        <v>0.06</v>
       </c>
       <c r="D35">
-        <v>2.899</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="E35">
-        <v>3.515</v>
+        <v>0.134</v>
       </c>
       <c r="F35">
-        <v>2.958</v>
+        <v>0.038</v>
       </c>
       <c r="G35">
-        <v>2.657</v>
+        <v>0.061</v>
       </c>
       <c r="H35">
-        <v>0.893</v>
+        <v>0.053</v>
       </c>
       <c r="I35">
-        <v>1.518</v>
+        <v>0.034</v>
       </c>
       <c r="J35">
-        <v>1.174</v>
-      </c>
-      <c r="V35" t="s">
-        <v>56</v>
-      </c>
-      <c r="W35">
+        <v>0</v>
+      </c>
+      <c r="W35" t="s">
+        <v>57</v>
+      </c>
+      <c r="X35">
         <v>0.035</v>
       </c>
     </row>
-    <row r="36" spans="1:23">
+    <row r="36" spans="1:24">
       <c r="A36" s="2">
         <v>46228</v>
       </c>
       <c r="B36">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C36">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="D36">
-        <v>2.611</v>
+        <v>0</v>
       </c>
       <c r="E36">
-        <v>3.068</v>
+        <v>0.014</v>
       </c>
       <c r="F36">
-        <v>2.355</v>
+        <v>0</v>
       </c>
       <c r="G36">
-        <v>2.228</v>
+        <v>0</v>
       </c>
       <c r="H36">
-        <v>0.98</v>
+        <v>0</v>
       </c>
       <c r="I36">
-        <v>1.177</v>
+        <v>0</v>
       </c>
       <c r="J36">
-        <v>0.924</v>
-      </c>
-      <c r="V36" t="s">
-        <v>57</v>
-      </c>
-      <c r="W36">
+        <v>0.019</v>
+      </c>
+      <c r="W36" t="s">
+        <v>58</v>
+      </c>
+      <c r="X36">
         <v>0.091</v>
       </c>
     </row>
-    <row r="37" spans="1:23">
+    <row r="37" spans="1:24">
       <c r="A37" s="2">
         <v>46228</v>
       </c>
       <c r="B37">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C37">
-        <v>1.367</v>
+        <v>0</v>
       </c>
       <c r="D37">
-        <v>1.877</v>
+        <v>0</v>
       </c>
       <c r="E37">
-        <v>2.388</v>
+        <v>0</v>
       </c>
       <c r="F37">
-        <v>1.584</v>
+        <v>0</v>
       </c>
       <c r="G37">
-        <v>1.662</v>
+        <v>0</v>
       </c>
       <c r="H37">
-        <v>0.955</v>
+        <v>0</v>
       </c>
       <c r="I37">
-        <v>0.851</v>
+        <v>0</v>
       </c>
       <c r="J37">
-        <v>0.655</v>
-      </c>
-      <c r="V37" t="s">
-        <v>58</v>
-      </c>
-      <c r="W37">
+        <v>0.013</v>
+      </c>
+      <c r="W37" t="s">
+        <v>59</v>
+      </c>
+      <c r="X37">
         <v>0.091</v>
       </c>
     </row>
-    <row r="38" spans="1:23">
+    <row r="38" spans="1:24">
       <c r="A38" s="2">
         <v>46228</v>
       </c>
       <c r="B38">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C38">
-        <v>0.863</v>
+        <v>0</v>
       </c>
       <c r="D38">
-        <v>0.963</v>
+        <v>0</v>
       </c>
       <c r="E38">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="F38">
-        <v>0.728</v>
+        <v>0</v>
       </c>
       <c r="G38">
-        <v>0.913</v>
+        <v>0</v>
       </c>
       <c r="H38">
-        <v>0.68</v>
+        <v>0</v>
       </c>
       <c r="I38">
-        <v>0.635</v>
+        <v>0</v>
       </c>
       <c r="J38">
-        <v>0.371</v>
-      </c>
-      <c r="V38" t="s">
-        <v>59</v>
-      </c>
-      <c r="W38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:23">
+        <v>0.013</v>
+      </c>
+      <c r="W38" t="s">
+        <v>60</v>
+      </c>
+      <c r="X38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:24">
       <c r="A39" s="2">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="B39">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="C39">
-        <v>0.282</v>
+        <v>0</v>
       </c>
       <c r="D39">
-        <v>0.317</v>
+        <v>0</v>
       </c>
       <c r="E39">
-        <v>0.666</v>
+        <v>0</v>
       </c>
       <c r="F39">
-        <v>0.215</v>
+        <v>0</v>
       </c>
       <c r="G39">
-        <v>0.29</v>
+        <v>0</v>
       </c>
       <c r="H39">
-        <v>0.353</v>
+        <v>0</v>
       </c>
       <c r="I39">
-        <v>0.328</v>
+        <v>0</v>
       </c>
       <c r="J39">
-        <v>0.114</v>
-      </c>
-      <c r="V39" t="s">
-        <v>60</v>
-      </c>
-      <c r="W39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:23">
+        <v>0.014</v>
+      </c>
+      <c r="W39" t="s">
+        <v>61</v>
+      </c>
+      <c r="X39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:24">
       <c r="A40" s="2">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="B40">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="C40">
-        <v>0.052</v>
+        <v>0</v>
       </c>
       <c r="D40">
-        <v>0.093</v>
+        <v>0</v>
       </c>
       <c r="E40">
-        <v>0.147</v>
+        <v>0</v>
       </c>
       <c r="F40">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="G40">
-        <v>0.061</v>
+        <v>0</v>
       </c>
       <c r="H40">
-        <v>0.053</v>
+        <v>0</v>
       </c>
       <c r="I40">
-        <v>0.034</v>
+        <v>0</v>
       </c>
       <c r="J40">
-        <v>0</v>
-      </c>
-      <c r="V40" t="s">
-        <v>61</v>
-      </c>
-      <c r="W40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:23">
+        <v>0.014</v>
+      </c>
+      <c r="W40" t="s">
+        <v>62</v>
+      </c>
+      <c r="X40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:24">
       <c r="A41" s="2">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="B41">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="C41">
         <v>0</v>
@@ -2536,21 +2542,21 @@
         <v>0</v>
       </c>
       <c r="J41">
-        <v>0.019</v>
-      </c>
-      <c r="V41" t="s">
-        <v>62</v>
-      </c>
-      <c r="W41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:23">
+        <v>0.014</v>
+      </c>
+      <c r="W41" t="s">
+        <v>63</v>
+      </c>
+      <c r="X41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:24">
       <c r="A42" s="2">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="B42">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="C42">
         <v>0</v>
@@ -2574,21 +2580,21 @@
         <v>0</v>
       </c>
       <c r="J42">
-        <v>0.019</v>
-      </c>
-      <c r="V42" t="s">
-        <v>63</v>
-      </c>
-      <c r="W42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:23">
+        <v>0.014</v>
+      </c>
+      <c r="W42" t="s">
+        <v>64</v>
+      </c>
+      <c r="X42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:24">
       <c r="A43" s="2">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="B43">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="C43">
         <v>0</v>
@@ -2612,21 +2618,21 @@
         <v>0</v>
       </c>
       <c r="J43">
-        <v>0.019</v>
-      </c>
-      <c r="V43" t="s">
-        <v>64</v>
-      </c>
-      <c r="W43">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:23">
+        <v>0.014</v>
+      </c>
+      <c r="W43" t="s">
+        <v>65</v>
+      </c>
+      <c r="X43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:24">
       <c r="A44" s="2">
         <v>46229</v>
       </c>
       <c r="B44">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C44">
         <v>0</v>
@@ -2652,779 +2658,779 @@
       <c r="J44">
         <v>0.014</v>
       </c>
-      <c r="V44" t="s">
-        <v>65</v>
-      </c>
-      <c r="W44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:23">
+      <c r="W44" t="s">
+        <v>66</v>
+      </c>
+      <c r="X44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:24">
       <c r="A45" s="2">
         <v>46229</v>
       </c>
       <c r="B45">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C45">
-        <v>0</v>
+        <v>0.056</v>
       </c>
       <c r="D45">
-        <v>0</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="E45">
-        <v>0</v>
+        <v>0.099</v>
       </c>
       <c r="F45">
-        <v>0</v>
+        <v>0.281</v>
       </c>
       <c r="G45">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="H45">
-        <v>0</v>
+        <v>0.106</v>
       </c>
       <c r="I45">
-        <v>0</v>
+        <v>0.112</v>
       </c>
       <c r="J45">
-        <v>0.014</v>
-      </c>
-      <c r="V45" t="s">
-        <v>66</v>
-      </c>
-      <c r="W45">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:23">
+        <v>0.075</v>
+      </c>
+      <c r="W45" t="s">
+        <v>67</v>
+      </c>
+      <c r="X45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:24">
       <c r="A46" s="2">
         <v>46229</v>
       </c>
       <c r="B46">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C46">
-        <v>0</v>
+        <v>0.356</v>
       </c>
       <c r="D46">
-        <v>0</v>
+        <v>0.421</v>
       </c>
       <c r="E46">
-        <v>0</v>
+        <v>0.659</v>
       </c>
       <c r="F46">
-        <v>0</v>
+        <v>1.001</v>
       </c>
       <c r="G46">
-        <v>0</v>
+        <v>0.594</v>
       </c>
       <c r="H46">
-        <v>0</v>
+        <v>0.623</v>
       </c>
       <c r="I46">
-        <v>0</v>
+        <v>0.526</v>
       </c>
       <c r="J46">
-        <v>0.014</v>
-      </c>
-      <c r="V46" t="s">
-        <v>67</v>
-      </c>
-      <c r="W46">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:23">
+        <v>0.481</v>
+      </c>
+      <c r="W46" t="s">
+        <v>68</v>
+      </c>
+      <c r="X46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:24">
       <c r="A47" s="2">
         <v>46229</v>
       </c>
       <c r="B47">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C47">
-        <v>0</v>
+        <v>1.113</v>
       </c>
       <c r="D47">
-        <v>0</v>
+        <v>1.158</v>
       </c>
       <c r="E47">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="F47">
-        <v>0</v>
+        <v>2.189</v>
       </c>
       <c r="G47">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="H47">
-        <v>0</v>
+        <v>1.156</v>
       </c>
       <c r="I47">
-        <v>0</v>
+        <v>0.971</v>
       </c>
       <c r="J47">
-        <v>0.014</v>
-      </c>
-      <c r="V47" t="s">
-        <v>68</v>
-      </c>
-      <c r="W47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:23">
+        <v>0.83</v>
+      </c>
+      <c r="W47" t="s">
+        <v>69</v>
+      </c>
+      <c r="X47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:24">
       <c r="A48" s="2">
         <v>46229</v>
       </c>
       <c r="B48">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C48">
-        <v>0</v>
+        <v>1.864</v>
       </c>
       <c r="D48">
-        <v>0</v>
+        <v>2.092</v>
       </c>
       <c r="E48">
-        <v>0</v>
+        <v>2.725</v>
       </c>
       <c r="F48">
-        <v>0</v>
+        <v>3.143</v>
       </c>
       <c r="G48">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="H48">
-        <v>0</v>
+        <v>1.384</v>
       </c>
       <c r="I48">
-        <v>0</v>
+        <v>1.418</v>
       </c>
       <c r="J48">
-        <v>0.014</v>
-      </c>
-      <c r="V48" t="s">
-        <v>69</v>
-      </c>
-      <c r="W48">
+        <v>1.118</v>
+      </c>
+      <c r="W48" t="s">
+        <v>70</v>
+      </c>
+      <c r="X48">
         <v>0.033</v>
       </c>
     </row>
-    <row r="49" spans="1:23">
+    <row r="49" spans="1:24">
       <c r="A49" s="2">
         <v>46229</v>
       </c>
       <c r="B49">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C49">
-        <v>0</v>
+        <v>2.487</v>
       </c>
       <c r="D49">
-        <v>0</v>
+        <v>2.873</v>
       </c>
       <c r="E49">
-        <v>0</v>
+        <v>3.713</v>
       </c>
       <c r="F49">
-        <v>0</v>
+        <v>3.679</v>
       </c>
       <c r="G49">
-        <v>0</v>
+        <v>2.952</v>
       </c>
       <c r="H49">
-        <v>0</v>
+        <v>1.171</v>
       </c>
       <c r="I49">
-        <v>0</v>
+        <v>1.554</v>
       </c>
       <c r="J49">
-        <v>0.014</v>
-      </c>
-      <c r="V49" t="s">
-        <v>70</v>
-      </c>
-      <c r="W49">
+        <v>1.487</v>
+      </c>
+      <c r="W49" t="s">
+        <v>71</v>
+      </c>
+      <c r="X49">
         <v>0.051</v>
       </c>
     </row>
-    <row r="50" spans="1:23">
+    <row r="50" spans="1:24">
       <c r="A50" s="2">
         <v>46229</v>
       </c>
       <c r="B50">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C50">
-        <v>0.057</v>
+        <v>2.846</v>
       </c>
       <c r="D50">
-        <v>0.08500000000000001</v>
+        <v>3.189</v>
       </c>
       <c r="E50">
-        <v>0.097</v>
+        <v>3.812</v>
       </c>
       <c r="F50">
-        <v>0.279</v>
+        <v>3.82</v>
       </c>
       <c r="G50">
-        <v>0.13</v>
+        <v>3.206</v>
       </c>
       <c r="H50">
-        <v>0.106</v>
+        <v>0.855</v>
       </c>
       <c r="I50">
-        <v>0.112</v>
+        <v>1.563</v>
       </c>
       <c r="J50">
-        <v>0.075</v>
-      </c>
-      <c r="V50" t="s">
-        <v>71</v>
-      </c>
-      <c r="W50">
+        <v>1.435</v>
+      </c>
+      <c r="W50" t="s">
+        <v>72</v>
+      </c>
+      <c r="X50">
         <v>0.28</v>
       </c>
     </row>
-    <row r="51" spans="1:23">
+    <row r="51" spans="1:24">
       <c r="A51" s="2">
         <v>46229</v>
       </c>
       <c r="B51">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C51">
-        <v>0.393</v>
+        <v>3.02</v>
       </c>
       <c r="D51">
-        <v>0.413</v>
+        <v>3.381</v>
       </c>
       <c r="E51">
-        <v>0.658</v>
+        <v>3.837</v>
       </c>
       <c r="F51">
-        <v>0.991</v>
+        <v>3.86</v>
       </c>
       <c r="G51">
-        <v>0.604</v>
+        <v>3.34</v>
       </c>
       <c r="H51">
-        <v>0.591</v>
+        <v>0.9370000000000001</v>
       </c>
       <c r="I51">
-        <v>0.526</v>
+        <v>1.465</v>
       </c>
       <c r="J51">
-        <v>0.481</v>
-      </c>
-      <c r="V51" t="s">
-        <v>72</v>
-      </c>
-      <c r="W51">
+        <v>1.595</v>
+      </c>
+      <c r="W51" t="s">
+        <v>73</v>
+      </c>
+      <c r="X51">
         <v>1.108</v>
       </c>
     </row>
-    <row r="52" spans="1:23">
+    <row r="52" spans="1:24">
       <c r="A52" s="2">
         <v>46229</v>
       </c>
       <c r="B52">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C52">
-        <v>1.136</v>
+        <v>2.996</v>
       </c>
       <c r="D52">
-        <v>1.158</v>
+        <v>3.4</v>
       </c>
       <c r="E52">
-        <v>1.724</v>
+        <v>3.775</v>
       </c>
       <c r="F52">
-        <v>2.233</v>
+        <v>3.726</v>
       </c>
       <c r="G52">
-        <v>1.653</v>
+        <v>3.3</v>
       </c>
       <c r="H52">
-        <v>1.066</v>
+        <v>0.944</v>
       </c>
       <c r="I52">
-        <v>0.971</v>
+        <v>1.502</v>
       </c>
       <c r="J52">
-        <v>0.822</v>
-      </c>
-      <c r="V52" t="s">
-        <v>73</v>
-      </c>
-      <c r="W52">
+        <v>1.656</v>
+      </c>
+      <c r="W52" t="s">
+        <v>74</v>
+      </c>
+      <c r="X52">
         <v>1.505</v>
       </c>
     </row>
-    <row r="53" spans="1:23">
+    <row r="53" spans="1:24">
       <c r="A53" s="2">
         <v>46229</v>
       </c>
       <c r="B53">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C53">
-        <v>1.825</v>
+        <v>2.903</v>
       </c>
       <c r="D53">
-        <v>2.079</v>
+        <v>3.291</v>
       </c>
       <c r="E53">
-        <v>2.812</v>
+        <v>3.743</v>
       </c>
       <c r="F53">
-        <v>3.133</v>
+        <v>3.397</v>
       </c>
       <c r="G53">
-        <v>2.407</v>
+        <v>3.241</v>
       </c>
       <c r="H53">
-        <v>1.399</v>
+        <v>0.854</v>
       </c>
       <c r="I53">
-        <v>1.424</v>
+        <v>1.502</v>
       </c>
       <c r="J53">
-        <v>1.117</v>
-      </c>
-      <c r="V53" t="s">
-        <v>74</v>
-      </c>
-      <c r="W53">
+        <v>1.596</v>
+      </c>
+      <c r="W53" t="s">
+        <v>75</v>
+      </c>
+      <c r="X53">
         <v>2.043</v>
       </c>
     </row>
-    <row r="54" spans="1:23">
+    <row r="54" spans="1:24">
       <c r="A54" s="2">
         <v>46229</v>
       </c>
       <c r="B54">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C54">
-        <v>2.494</v>
+        <v>2.593</v>
       </c>
       <c r="D54">
-        <v>2.848</v>
+        <v>3.171</v>
       </c>
       <c r="E54">
-        <v>3.785</v>
+        <v>3.696</v>
       </c>
       <c r="F54">
-        <v>3.67</v>
+        <v>3.082</v>
       </c>
       <c r="G54">
-        <v>2.952</v>
+        <v>2.914</v>
       </c>
       <c r="H54">
-        <v>1.171</v>
+        <v>0.869</v>
       </c>
       <c r="I54">
-        <v>1.554</v>
+        <v>1.502</v>
       </c>
       <c r="J54">
-        <v>1.493</v>
-      </c>
-      <c r="V54" t="s">
-        <v>75</v>
-      </c>
-      <c r="W54">
+        <v>1.455</v>
+      </c>
+      <c r="W54" t="s">
+        <v>76</v>
+      </c>
+      <c r="X54">
         <v>1.84</v>
       </c>
     </row>
-    <row r="55" spans="1:23">
+    <row r="55" spans="1:24">
       <c r="A55" s="2">
         <v>46229</v>
       </c>
       <c r="B55">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C55">
-        <v>2.878</v>
+        <v>2.003</v>
       </c>
       <c r="D55">
-        <v>3.166</v>
+        <v>2.779</v>
       </c>
       <c r="E55">
-        <v>3.919</v>
+        <v>3.35</v>
       </c>
       <c r="F55">
-        <v>3.834</v>
+        <v>2.427</v>
       </c>
       <c r="G55">
-        <v>3.206</v>
+        <v>2.265</v>
       </c>
       <c r="H55">
-        <v>0.855</v>
+        <v>1.003</v>
       </c>
       <c r="I55">
-        <v>1.481</v>
+        <v>1.502</v>
       </c>
       <c r="J55">
-        <v>1.435</v>
-      </c>
-      <c r="V55" t="s">
-        <v>76</v>
-      </c>
-      <c r="W55">
+        <v>1.12</v>
+      </c>
+      <c r="W55" t="s">
+        <v>77</v>
+      </c>
+      <c r="X55">
         <v>1.826</v>
       </c>
     </row>
-    <row r="56" spans="1:23">
+    <row r="56" spans="1:24">
       <c r="A56" s="2">
         <v>46229</v>
       </c>
       <c r="B56">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C56">
-        <v>3.069</v>
+        <v>1.337</v>
       </c>
       <c r="D56">
-        <v>3.379</v>
+        <v>1.896</v>
       </c>
       <c r="E56">
-        <v>3.827</v>
+        <v>2.54</v>
       </c>
       <c r="F56">
-        <v>3.859</v>
+        <v>1.633</v>
       </c>
       <c r="G56">
-        <v>3.34</v>
+        <v>1.806</v>
       </c>
       <c r="H56">
-        <v>0.9370000000000001</v>
+        <v>0.925</v>
       </c>
       <c r="I56">
-        <v>1.465</v>
+        <v>1.094</v>
       </c>
       <c r="J56">
-        <v>1.64</v>
-      </c>
-      <c r="V56" t="s">
-        <v>77</v>
-      </c>
-      <c r="W56">
+        <v>0.797</v>
+      </c>
+      <c r="W56" t="s">
+        <v>78</v>
+      </c>
+      <c r="X56">
         <v>1.02</v>
       </c>
     </row>
-    <row r="57" spans="1:23">
+    <row r="57" spans="1:24">
       <c r="A57" s="2">
         <v>46229</v>
       </c>
       <c r="B57">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C57">
-        <v>3.015</v>
+        <v>0.827</v>
       </c>
       <c r="D57">
-        <v>3.392</v>
+        <v>0.985</v>
       </c>
       <c r="E57">
-        <v>3.761</v>
+        <v>1.544</v>
       </c>
       <c r="F57">
-        <v>3.768</v>
+        <v>0.79</v>
       </c>
       <c r="G57">
-        <v>3.32</v>
+        <v>0.989</v>
       </c>
       <c r="H57">
-        <v>1.04</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="I57">
-        <v>1.502</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="J57">
-        <v>1.692</v>
-      </c>
-      <c r="V57" t="s">
-        <v>78</v>
-      </c>
-      <c r="W57">
+        <v>0.426</v>
+      </c>
+      <c r="W57" t="s">
+        <v>79</v>
+      </c>
+      <c r="X57">
         <v>0.508</v>
       </c>
     </row>
-    <row r="58" spans="1:23">
+    <row r="58" spans="1:24">
       <c r="A58" s="2">
         <v>46229</v>
       </c>
       <c r="B58">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C58">
-        <v>2.845</v>
+        <v>0.274</v>
       </c>
       <c r="D58">
-        <v>3.292</v>
+        <v>0.305</v>
       </c>
       <c r="E58">
-        <v>3.743</v>
+        <v>0.525</v>
       </c>
       <c r="F58">
-        <v>3.547</v>
+        <v>0.234</v>
       </c>
       <c r="G58">
-        <v>3.207</v>
+        <v>0.287</v>
       </c>
       <c r="H58">
-        <v>0.869</v>
+        <v>0.382</v>
       </c>
       <c r="I58">
-        <v>1.502</v>
+        <v>0.361</v>
       </c>
       <c r="J58">
-        <v>1.494</v>
-      </c>
-      <c r="V58" t="s">
-        <v>79</v>
-      </c>
-      <c r="W58">
+        <v>0.11</v>
+      </c>
+      <c r="W58" t="s">
+        <v>80</v>
+      </c>
+      <c r="X58">
         <v>0.422</v>
       </c>
     </row>
-    <row r="59" spans="1:23">
+    <row r="59" spans="1:24">
       <c r="A59" s="2">
         <v>46229</v>
       </c>
       <c r="B59">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C59">
-        <v>2.56</v>
+        <v>0.051</v>
       </c>
       <c r="D59">
-        <v>3.173</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="E59">
-        <v>3.696</v>
+        <v>0.109</v>
       </c>
       <c r="F59">
-        <v>3.097</v>
+        <v>0.041</v>
       </c>
       <c r="G59">
-        <v>2.906</v>
+        <v>0.061</v>
       </c>
       <c r="H59">
-        <v>0.913</v>
+        <v>0.053</v>
       </c>
       <c r="I59">
-        <v>1.502</v>
+        <v>0.042</v>
       </c>
       <c r="J59">
-        <v>1.473</v>
-      </c>
-      <c r="V59" t="s">
-        <v>80</v>
-      </c>
-      <c r="W59">
+        <v>0</v>
+      </c>
+      <c r="W59" t="s">
+        <v>81</v>
+      </c>
+      <c r="X59">
         <v>0.045</v>
       </c>
     </row>
-    <row r="60" spans="1:23">
+    <row r="60" spans="1:24">
       <c r="A60" s="2">
         <v>46229</v>
       </c>
       <c r="B60">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C60">
-        <v>1.954</v>
+        <v>0</v>
       </c>
       <c r="D60">
-        <v>2.789</v>
+        <v>0</v>
       </c>
       <c r="E60">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="F60">
-        <v>2.413</v>
+        <v>0</v>
       </c>
       <c r="G60">
-        <v>2.302</v>
+        <v>0</v>
       </c>
       <c r="H60">
-        <v>1.045</v>
+        <v>0</v>
       </c>
       <c r="I60">
-        <v>1.502</v>
+        <v>0</v>
       </c>
       <c r="J60">
-        <v>1.166</v>
-      </c>
-      <c r="V60" t="s">
-        <v>81</v>
-      </c>
-      <c r="W60">
+        <v>0</v>
+      </c>
+      <c r="W60" t="s">
+        <v>82</v>
+      </c>
+      <c r="X60">
         <v>0.096</v>
       </c>
     </row>
-    <row r="61" spans="1:23">
+    <row r="61" spans="1:24">
       <c r="A61" s="2">
         <v>46229</v>
       </c>
       <c r="B61">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C61">
-        <v>1.336</v>
+        <v>0</v>
       </c>
       <c r="D61">
-        <v>1.912</v>
+        <v>0</v>
       </c>
       <c r="E61">
-        <v>2.607</v>
+        <v>0.023</v>
       </c>
       <c r="F61">
-        <v>1.615</v>
+        <v>0</v>
       </c>
       <c r="G61">
-        <v>1.744</v>
+        <v>0</v>
       </c>
       <c r="H61">
-        <v>0.979</v>
+        <v>0</v>
       </c>
       <c r="I61">
-        <v>1.124</v>
+        <v>0</v>
       </c>
       <c r="J61">
-        <v>0.847</v>
-      </c>
-      <c r="V61" t="s">
-        <v>82</v>
-      </c>
-      <c r="W61">
+        <v>0</v>
+      </c>
+      <c r="W61" t="s">
+        <v>83</v>
+      </c>
+      <c r="X61">
         <v>0.096</v>
       </c>
     </row>
-    <row r="62" spans="1:23">
+    <row r="62" spans="1:24">
       <c r="A62" s="2">
         <v>46229</v>
       </c>
       <c r="B62">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C62">
-        <v>0.832</v>
+        <v>0</v>
       </c>
       <c r="D62">
-        <v>1.029</v>
+        <v>0</v>
       </c>
       <c r="E62">
-        <v>1.573</v>
+        <v>0.022</v>
       </c>
       <c r="F62">
-        <v>0.788</v>
+        <v>0</v>
       </c>
       <c r="G62">
-        <v>0.996</v>
+        <v>0</v>
       </c>
       <c r="H62">
-        <v>0.726</v>
+        <v>0</v>
       </c>
       <c r="I62">
-        <v>0.6870000000000001</v>
+        <v>0</v>
       </c>
       <c r="J62">
-        <v>0.466</v>
-      </c>
-      <c r="V62" t="s">
-        <v>83</v>
-      </c>
-      <c r="W62">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:23">
+        <v>0.019</v>
+      </c>
+      <c r="W62" t="s">
+        <v>84</v>
+      </c>
+      <c r="X62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:24">
       <c r="A63" s="2">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="B63">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="C63">
-        <v>0.301</v>
+        <v>0</v>
       </c>
       <c r="D63">
-        <v>0.301</v>
+        <v>0</v>
       </c>
       <c r="E63">
-        <v>0.542</v>
+        <v>0.065</v>
       </c>
       <c r="F63">
-        <v>0.234</v>
+        <v>0</v>
       </c>
       <c r="G63">
-        <v>0.291</v>
+        <v>0</v>
       </c>
       <c r="H63">
-        <v>0.382</v>
+        <v>0</v>
       </c>
       <c r="I63">
-        <v>0.379</v>
+        <v>0</v>
       </c>
       <c r="J63">
-        <v>0.11</v>
-      </c>
-      <c r="V63" t="s">
-        <v>84</v>
-      </c>
-      <c r="W63">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:23">
+        <v>0.02</v>
+      </c>
+      <c r="W63" t="s">
+        <v>85</v>
+      </c>
+      <c r="X63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:24">
       <c r="A64" s="2">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="B64">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="C64">
-        <v>0.051</v>
+        <v>0</v>
       </c>
       <c r="D64">
-        <v>0.08500000000000001</v>
+        <v>0</v>
       </c>
       <c r="E64">
-        <v>0.148</v>
+        <v>0.082</v>
       </c>
       <c r="F64">
-        <v>0.041</v>
+        <v>0</v>
       </c>
       <c r="G64">
-        <v>0.061</v>
+        <v>0</v>
       </c>
       <c r="H64">
-        <v>0.053</v>
+        <v>0</v>
       </c>
       <c r="I64">
-        <v>0.042</v>
+        <v>0</v>
       </c>
       <c r="J64">
-        <v>0</v>
-      </c>
-      <c r="V64" t="s">
-        <v>85</v>
-      </c>
-      <c r="W64">
+        <v>0.02</v>
+      </c>
+      <c r="W64" t="s">
+        <v>86</v>
+      </c>
+      <c r="X64">
         <v>0.014</v>
       </c>
     </row>
-    <row r="65" spans="1:23">
+    <row r="65" spans="1:24">
       <c r="A65" s="2">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="B65">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="C65">
         <v>0</v>
@@ -3433,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="E65">
-        <v>0.029</v>
+        <v>0</v>
       </c>
       <c r="F65">
         <v>0</v>
@@ -3448,21 +3454,21 @@
         <v>0</v>
       </c>
       <c r="J65">
-        <v>0</v>
-      </c>
-      <c r="V65" t="s">
-        <v>86</v>
-      </c>
-      <c r="W65">
+        <v>0.02</v>
+      </c>
+      <c r="W65" t="s">
+        <v>87</v>
+      </c>
+      <c r="X65">
         <v>0.011</v>
       </c>
     </row>
-    <row r="66" spans="1:23">
+    <row r="66" spans="1:24">
       <c r="A66" s="2">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="B66">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="C66">
         <v>0</v>
@@ -3471,7 +3477,7 @@
         <v>0</v>
       </c>
       <c r="E66">
-        <v>0.054</v>
+        <v>0</v>
       </c>
       <c r="F66">
         <v>0</v>
@@ -3486,21 +3492,21 @@
         <v>0</v>
       </c>
       <c r="J66">
-        <v>0.018</v>
-      </c>
-      <c r="V66" t="s">
-        <v>87</v>
-      </c>
-      <c r="W66">
+        <v>0.02</v>
+      </c>
+      <c r="W66" t="s">
+        <v>88</v>
+      </c>
+      <c r="X66">
         <v>0.011</v>
       </c>
     </row>
-    <row r="67" spans="1:23">
+    <row r="67" spans="1:24">
       <c r="A67" s="2">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="B67">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="C67">
         <v>0</v>
@@ -3509,7 +3515,7 @@
         <v>0</v>
       </c>
       <c r="E67">
-        <v>0.034</v>
+        <v>0</v>
       </c>
       <c r="F67">
         <v>0</v>
@@ -3524,21 +3530,21 @@
         <v>0</v>
       </c>
       <c r="J67">
-        <v>0</v>
-      </c>
-      <c r="V67" t="s">
-        <v>88</v>
-      </c>
-      <c r="W67">
+        <v>0.02</v>
+      </c>
+      <c r="W67" t="s">
+        <v>89</v>
+      </c>
+      <c r="X67">
         <v>0.011</v>
       </c>
     </row>
-    <row r="68" spans="1:23">
+    <row r="68" spans="1:24">
       <c r="A68" s="2">
         <v>46230</v>
       </c>
       <c r="B68">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C68">
         <v>0</v>
@@ -3547,7 +3553,7 @@
         <v>0</v>
       </c>
       <c r="E68">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="F68">
         <v>0</v>
@@ -3562,781 +3568,781 @@
         <v>0</v>
       </c>
       <c r="J68">
-        <v>0.02</v>
-      </c>
-      <c r="V68" t="s">
-        <v>89</v>
-      </c>
-      <c r="W68">
+        <v>0.014</v>
+      </c>
+      <c r="W68" t="s">
+        <v>90</v>
+      </c>
+      <c r="X68">
         <v>0.011</v>
       </c>
     </row>
-    <row r="69" spans="1:23">
+    <row r="69" spans="1:24">
       <c r="A69" s="2">
         <v>46230</v>
       </c>
       <c r="B69">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C69">
-        <v>0</v>
+        <v>0.042</v>
       </c>
       <c r="D69">
-        <v>0</v>
+        <v>0.044</v>
       </c>
       <c r="E69">
-        <v>0.095</v>
+        <v>0.034</v>
       </c>
       <c r="F69">
-        <v>0</v>
+        <v>0.175</v>
       </c>
       <c r="G69">
-        <v>0</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="H69">
-        <v>0</v>
+        <v>0.053</v>
       </c>
       <c r="I69">
-        <v>0</v>
+        <v>0.064</v>
       </c>
       <c r="J69">
-        <v>0.02</v>
-      </c>
-      <c r="V69" t="s">
-        <v>90</v>
-      </c>
-      <c r="W69">
+        <v>0.038</v>
+      </c>
+      <c r="W69" t="s">
+        <v>91</v>
+      </c>
+      <c r="X69">
         <v>0.011</v>
       </c>
     </row>
-    <row r="70" spans="1:23">
+    <row r="70" spans="1:24">
       <c r="A70" s="2">
         <v>46230</v>
       </c>
       <c r="B70">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C70">
-        <v>0</v>
+        <v>0.305</v>
       </c>
       <c r="D70">
-        <v>0</v>
+        <v>0.342</v>
       </c>
       <c r="E70">
-        <v>0.08599999999999999</v>
+        <v>0.347</v>
       </c>
       <c r="F70">
-        <v>0</v>
+        <v>0.631</v>
       </c>
       <c r="G70">
-        <v>0</v>
+        <v>0.362</v>
       </c>
       <c r="H70">
-        <v>0</v>
+        <v>0.236</v>
       </c>
       <c r="I70">
-        <v>0</v>
+        <v>0.361</v>
       </c>
       <c r="J70">
-        <v>0.02</v>
-      </c>
-      <c r="V70" t="s">
-        <v>91</v>
-      </c>
-      <c r="W70">
+        <v>0.195</v>
+      </c>
+      <c r="W70" t="s">
+        <v>92</v>
+      </c>
+      <c r="X70">
         <v>0.011</v>
       </c>
     </row>
-    <row r="71" spans="1:23">
+    <row r="71" spans="1:24">
       <c r="A71" s="2">
         <v>46230</v>
       </c>
       <c r="B71">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C71">
-        <v>0</v>
+        <v>0.77</v>
       </c>
       <c r="D71">
-        <v>0</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="E71">
-        <v>0.082</v>
+        <v>1.089</v>
       </c>
       <c r="F71">
-        <v>0</v>
+        <v>1.251</v>
       </c>
       <c r="G71">
-        <v>0</v>
+        <v>0.714</v>
       </c>
       <c r="H71">
-        <v>0</v>
+        <v>0.632</v>
       </c>
       <c r="I71">
-        <v>0</v>
+        <v>0.635</v>
       </c>
       <c r="J71">
-        <v>0.014</v>
-      </c>
-      <c r="V71" t="s">
-        <v>92</v>
-      </c>
-      <c r="W71">
+        <v>0.526</v>
+      </c>
+      <c r="W71" t="s">
+        <v>93</v>
+      </c>
+      <c r="X71">
         <v>0.011</v>
       </c>
     </row>
-    <row r="72" spans="1:23">
+    <row r="72" spans="1:24">
       <c r="A72" s="2">
         <v>46230</v>
       </c>
       <c r="B72">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C72">
-        <v>0</v>
+        <v>1.175</v>
       </c>
       <c r="D72">
-        <v>0</v>
+        <v>1.462</v>
       </c>
       <c r="E72">
-        <v>0</v>
+        <v>1.873</v>
       </c>
       <c r="F72">
-        <v>0</v>
+        <v>2.328</v>
       </c>
       <c r="G72">
-        <v>0</v>
+        <v>1.884</v>
       </c>
       <c r="H72">
-        <v>0</v>
+        <v>1.031</v>
       </c>
       <c r="I72">
-        <v>0</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="J72">
-        <v>0.014</v>
-      </c>
-      <c r="V72" t="s">
-        <v>93</v>
-      </c>
-      <c r="W72">
+        <v>0.874</v>
+      </c>
+      <c r="W72" t="s">
+        <v>94</v>
+      </c>
+      <c r="X72">
         <v>0.038</v>
       </c>
     </row>
-    <row r="73" spans="1:23">
+    <row r="73" spans="1:24">
       <c r="A73" s="2">
         <v>46230</v>
       </c>
       <c r="B73">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C73">
-        <v>0</v>
+        <v>1.715</v>
       </c>
       <c r="D73">
-        <v>0</v>
+        <v>2.083</v>
       </c>
       <c r="E73">
-        <v>0</v>
+        <v>2.724</v>
       </c>
       <c r="F73">
-        <v>0</v>
+        <v>2.951</v>
       </c>
       <c r="G73">
-        <v>0</v>
+        <v>2.637</v>
       </c>
       <c r="H73">
-        <v>0</v>
+        <v>0.918</v>
       </c>
       <c r="I73">
-        <v>0</v>
+        <v>1.437</v>
       </c>
       <c r="J73">
-        <v>0.014</v>
-      </c>
-      <c r="V73" t="s">
-        <v>94</v>
-      </c>
-      <c r="W73">
+        <v>1.092</v>
+      </c>
+      <c r="W73" t="s">
+        <v>95</v>
+      </c>
+      <c r="X73">
         <v>0.056</v>
       </c>
     </row>
-    <row r="74" spans="1:23">
+    <row r="74" spans="1:24">
       <c r="A74" s="2">
         <v>46230</v>
       </c>
       <c r="B74">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C74">
-        <v>0.034</v>
+        <v>1.832</v>
       </c>
       <c r="D74">
-        <v>0.041</v>
+        <v>2.244</v>
       </c>
       <c r="E74">
-        <v>0.044</v>
+        <v>3.127</v>
       </c>
       <c r="F74">
-        <v>0.173</v>
+        <v>2.831</v>
       </c>
       <c r="G74">
-        <v>0.077</v>
+        <v>2.624</v>
       </c>
       <c r="H74">
-        <v>0.053</v>
+        <v>1.372</v>
       </c>
       <c r="I74">
-        <v>0.064</v>
+        <v>1.445</v>
       </c>
       <c r="J74">
-        <v>0.038</v>
-      </c>
-      <c r="V74" t="s">
-        <v>95</v>
-      </c>
-      <c r="W74">
+        <v>1.22</v>
+      </c>
+      <c r="W74" t="s">
+        <v>96</v>
+      </c>
+      <c r="X74">
         <v>0.29</v>
       </c>
     </row>
-    <row r="75" spans="1:23">
+    <row r="75" spans="1:24">
       <c r="A75" s="2">
         <v>46230</v>
       </c>
       <c r="B75">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C75">
-        <v>0.306</v>
+        <v>2.281</v>
       </c>
       <c r="D75">
-        <v>0.324</v>
+        <v>2.453</v>
       </c>
       <c r="E75">
-        <v>0.391</v>
+        <v>3.658</v>
       </c>
       <c r="F75">
-        <v>0.5679999999999999</v>
+        <v>2.771</v>
       </c>
       <c r="G75">
-        <v>0.345</v>
+        <v>2.699</v>
       </c>
       <c r="H75">
-        <v>0.236</v>
+        <v>1.103</v>
       </c>
       <c r="I75">
-        <v>0.361</v>
+        <v>1.419</v>
       </c>
       <c r="J75">
-        <v>0.195</v>
-      </c>
-      <c r="V75" t="s">
-        <v>96</v>
-      </c>
-      <c r="W75">
+        <v>1.359</v>
+      </c>
+      <c r="W75" t="s">
+        <v>97</v>
+      </c>
+      <c r="X75">
         <v>0.96</v>
       </c>
     </row>
-    <row r="76" spans="1:23">
+    <row r="76" spans="1:24">
       <c r="A76" s="2">
         <v>46230</v>
       </c>
       <c r="B76">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C76">
-        <v>0.755</v>
+        <v>2.505</v>
       </c>
       <c r="D76">
-        <v>0.726</v>
+        <v>2.621</v>
       </c>
       <c r="E76">
-        <v>1.125</v>
+        <v>3.855</v>
       </c>
       <c r="F76">
-        <v>1.22</v>
+        <v>3.255</v>
       </c>
       <c r="G76">
-        <v>0.6870000000000001</v>
+        <v>2.862</v>
       </c>
       <c r="H76">
-        <v>0.604</v>
+        <v>1.093</v>
       </c>
       <c r="I76">
-        <v>0.635</v>
+        <v>1.502</v>
       </c>
       <c r="J76">
-        <v>0.526</v>
-      </c>
-      <c r="V76" t="s">
-        <v>97</v>
-      </c>
-      <c r="W76">
+        <v>1.206</v>
+      </c>
+      <c r="W76" t="s">
+        <v>98</v>
+      </c>
+      <c r="X76">
         <v>1.436</v>
       </c>
     </row>
-    <row r="77" spans="1:23">
+    <row r="77" spans="1:24">
       <c r="A77" s="2">
         <v>46230</v>
       </c>
       <c r="B77">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C77">
-        <v>1.128</v>
+        <v>2.144</v>
       </c>
       <c r="D77">
-        <v>1.391</v>
+        <v>2.372</v>
       </c>
       <c r="E77">
-        <v>1.853</v>
+        <v>3.571</v>
       </c>
       <c r="F77">
-        <v>2.301</v>
+        <v>3.195</v>
       </c>
       <c r="G77">
-        <v>1.776</v>
+        <v>2.881</v>
       </c>
       <c r="H77">
-        <v>0.996</v>
+        <v>0.922</v>
       </c>
       <c r="I77">
-        <v>0.945</v>
+        <v>1.502</v>
       </c>
       <c r="J77">
-        <v>0.845</v>
-      </c>
-      <c r="V77" t="s">
-        <v>98</v>
-      </c>
-      <c r="W77">
+        <v>1.249</v>
+      </c>
+      <c r="W77" t="s">
+        <v>99</v>
+      </c>
+      <c r="X77">
         <v>1.977</v>
       </c>
     </row>
-    <row r="78" spans="1:23">
+    <row r="78" spans="1:24">
       <c r="A78" s="2">
         <v>46230</v>
       </c>
       <c r="B78">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C78">
-        <v>1.64</v>
+        <v>1.685</v>
       </c>
       <c r="D78">
-        <v>2.017</v>
+        <v>1.891</v>
       </c>
       <c r="E78">
-        <v>2.647</v>
+        <v>3.144</v>
       </c>
       <c r="F78">
-        <v>2.96</v>
+        <v>2.558</v>
       </c>
       <c r="G78">
-        <v>2.478</v>
+        <v>2.581</v>
       </c>
       <c r="H78">
-        <v>1.33</v>
+        <v>0.824</v>
       </c>
       <c r="I78">
-        <v>1.453</v>
+        <v>1.502</v>
       </c>
       <c r="J78">
-        <v>1.023</v>
-      </c>
-      <c r="V78" t="s">
-        <v>99</v>
-      </c>
-      <c r="W78">
+        <v>1.11</v>
+      </c>
+      <c r="W78" t="s">
+        <v>100</v>
+      </c>
+      <c r="X78">
         <v>1.827</v>
       </c>
     </row>
-    <row r="79" spans="1:23">
+    <row r="79" spans="1:24">
       <c r="A79" s="2">
         <v>46230</v>
       </c>
       <c r="B79">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C79">
-        <v>1.791</v>
+        <v>1.483</v>
       </c>
       <c r="D79">
-        <v>2.201</v>
+        <v>1.662</v>
       </c>
       <c r="E79">
-        <v>3.449</v>
+        <v>2.529</v>
       </c>
       <c r="F79">
-        <v>2.845</v>
+        <v>2.078</v>
       </c>
       <c r="G79">
-        <v>2.622</v>
+        <v>2.1</v>
       </c>
       <c r="H79">
-        <v>0.96</v>
+        <v>1.039</v>
       </c>
       <c r="I79">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="J79">
-        <v>1.277</v>
-      </c>
-      <c r="V79" t="s">
-        <v>100</v>
-      </c>
-      <c r="W79">
+        <v>0.784</v>
+      </c>
+      <c r="W79" t="s">
+        <v>101</v>
+      </c>
+      <c r="X79">
         <v>1.35</v>
       </c>
     </row>
-    <row r="80" spans="1:23">
+    <row r="80" spans="1:24">
       <c r="A80" s="2">
         <v>46230</v>
       </c>
       <c r="B80">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C80">
-        <v>2.071</v>
+        <v>1.014</v>
       </c>
       <c r="D80">
-        <v>2.432</v>
+        <v>1.054</v>
       </c>
       <c r="E80">
-        <v>3.748</v>
+        <v>1.811</v>
       </c>
       <c r="F80">
-        <v>2.964</v>
+        <v>1.483</v>
       </c>
       <c r="G80">
-        <v>2.704</v>
+        <v>1.395</v>
       </c>
       <c r="H80">
-        <v>1.08</v>
+        <v>0.875</v>
       </c>
       <c r="I80">
-        <v>1.419</v>
+        <v>0.961</v>
       </c>
       <c r="J80">
-        <v>1.415</v>
-      </c>
-      <c r="V80" t="s">
-        <v>101</v>
-      </c>
-      <c r="W80">
+        <v>0.327</v>
+      </c>
+      <c r="W80" t="s">
+        <v>102</v>
+      </c>
+      <c r="X80">
         <v>0.888</v>
       </c>
     </row>
-    <row r="81" spans="1:23">
+    <row r="81" spans="1:24">
       <c r="A81" s="2">
         <v>46230</v>
       </c>
       <c r="B81">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C81">
-        <v>2.281</v>
+        <v>0.491</v>
       </c>
       <c r="D81">
-        <v>2.622</v>
+        <v>0.514</v>
       </c>
       <c r="E81">
-        <v>3.608</v>
+        <v>1.301</v>
       </c>
       <c r="F81">
-        <v>3.283</v>
+        <v>0.461</v>
       </c>
       <c r="G81">
-        <v>3.037</v>
+        <v>0.622</v>
       </c>
       <c r="H81">
-        <v>0.9350000000000001</v>
+        <v>0.446</v>
       </c>
       <c r="I81">
-        <v>1.502</v>
+        <v>0.588</v>
       </c>
       <c r="J81">
-        <v>1.377</v>
-      </c>
-      <c r="V81" t="s">
-        <v>102</v>
-      </c>
-      <c r="W81">
+        <v>0.219</v>
+      </c>
+      <c r="W81" t="s">
+        <v>103</v>
+      </c>
+      <c r="X81">
         <v>0.297</v>
       </c>
     </row>
-    <row r="82" spans="1:23">
+    <row r="82" spans="1:24">
       <c r="A82" s="2">
         <v>46230</v>
       </c>
       <c r="B82">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C82">
-        <v>1.894</v>
+        <v>0.229</v>
       </c>
       <c r="D82">
-        <v>2.199</v>
+        <v>0.245</v>
       </c>
       <c r="E82">
-        <v>3.428</v>
+        <v>0.539</v>
       </c>
       <c r="F82">
-        <v>3.29</v>
+        <v>0.17</v>
       </c>
       <c r="G82">
-        <v>3.001</v>
+        <v>0.225</v>
       </c>
       <c r="H82">
-        <v>1.024</v>
+        <v>0.217</v>
       </c>
       <c r="I82">
-        <v>1.502</v>
+        <v>0.201</v>
       </c>
       <c r="J82">
-        <v>1.259</v>
-      </c>
-      <c r="V82" t="s">
-        <v>103</v>
-      </c>
-      <c r="W82">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="W82" t="s">
+        <v>104</v>
+      </c>
+      <c r="X82">
         <v>0.132</v>
       </c>
     </row>
-    <row r="83" spans="1:23">
+    <row r="83" spans="1:24">
       <c r="A83" s="2">
         <v>46230</v>
       </c>
       <c r="B83">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C83">
-        <v>1.555</v>
+        <v>0.029</v>
       </c>
       <c r="D83">
-        <v>1.91</v>
+        <v>0.043</v>
       </c>
       <c r="E83">
-        <v>3.151</v>
+        <v>0.098</v>
       </c>
       <c r="F83">
-        <v>2.887</v>
+        <v>0.02</v>
       </c>
       <c r="G83">
-        <v>2.772</v>
+        <v>0.029</v>
       </c>
       <c r="H83">
-        <v>0.965</v>
+        <v>0.03</v>
       </c>
       <c r="I83">
-        <v>1.502</v>
+        <v>0.021</v>
       </c>
       <c r="J83">
-        <v>1.019</v>
-      </c>
-      <c r="V83" t="s">
-        <v>104</v>
-      </c>
-      <c r="W83">
+        <v>0</v>
+      </c>
+      <c r="W83" t="s">
+        <v>105</v>
+      </c>
+      <c r="X83">
         <v>0.038</v>
       </c>
     </row>
-    <row r="84" spans="1:23">
+    <row r="84" spans="1:24">
       <c r="A84" s="2">
         <v>46230</v>
       </c>
       <c r="B84">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C84">
-        <v>1.299</v>
+        <v>0</v>
       </c>
       <c r="D84">
-        <v>1.345</v>
+        <v>0</v>
       </c>
       <c r="E84">
-        <v>2.462</v>
+        <v>0</v>
       </c>
       <c r="F84">
-        <v>2.159</v>
+        <v>0</v>
       </c>
       <c r="G84">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="H84">
-        <v>1.001</v>
+        <v>0</v>
       </c>
       <c r="I84">
-        <v>1.341</v>
+        <v>0</v>
       </c>
       <c r="J84">
-        <v>0.697</v>
-      </c>
-      <c r="V84" t="s">
-        <v>105</v>
-      </c>
-      <c r="W84">
+        <v>0.013</v>
+      </c>
+      <c r="W84" t="s">
+        <v>106</v>
+      </c>
+      <c r="X84">
         <v>0.094</v>
       </c>
     </row>
-    <row r="85" spans="1:23">
+    <row r="85" spans="1:24">
       <c r="A85" s="2">
         <v>46230</v>
       </c>
       <c r="B85">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C85">
-        <v>0.8129999999999999</v>
+        <v>0</v>
       </c>
       <c r="D85">
-        <v>0.986</v>
+        <v>0</v>
       </c>
       <c r="E85">
-        <v>1.777</v>
+        <v>0</v>
       </c>
       <c r="F85">
-        <v>1.469</v>
+        <v>0</v>
       </c>
       <c r="G85">
-        <v>1.422</v>
+        <v>0</v>
       </c>
       <c r="H85">
-        <v>0.903</v>
+        <v>0</v>
       </c>
       <c r="I85">
-        <v>0.9419999999999999</v>
+        <v>0</v>
       </c>
       <c r="J85">
-        <v>0.299</v>
-      </c>
-      <c r="V85" t="s">
-        <v>106</v>
-      </c>
-      <c r="W85">
+        <v>0.013</v>
+      </c>
+      <c r="W85" t="s">
+        <v>107</v>
+      </c>
+      <c r="X85">
         <v>0.094</v>
       </c>
     </row>
-    <row r="86" spans="1:23">
+    <row r="86" spans="1:24">
       <c r="A86" s="2">
         <v>46230</v>
       </c>
       <c r="B86">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C86">
-        <v>0.498</v>
+        <v>0</v>
       </c>
       <c r="D86">
-        <v>0.509</v>
+        <v>0</v>
       </c>
       <c r="E86">
-        <v>1.253</v>
+        <v>0</v>
       </c>
       <c r="F86">
-        <v>0.461</v>
+        <v>0</v>
       </c>
       <c r="G86">
-        <v>0.594</v>
+        <v>0</v>
       </c>
       <c r="H86">
-        <v>0.46</v>
+        <v>0</v>
       </c>
       <c r="I86">
-        <v>0.588</v>
+        <v>0</v>
       </c>
       <c r="J86">
-        <v>0.231</v>
-      </c>
-      <c r="V86" t="s">
-        <v>107</v>
-      </c>
-      <c r="W86">
+        <v>0.013</v>
+      </c>
+      <c r="W86" t="s">
+        <v>108</v>
+      </c>
+      <c r="X86">
         <v>0.011</v>
       </c>
     </row>
-    <row r="87" spans="1:23">
+    <row r="87" spans="1:24">
       <c r="A87" s="2">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B87">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="C87">
-        <v>0.219</v>
+        <v>0</v>
       </c>
       <c r="D87">
-        <v>0.225</v>
+        <v>0</v>
       </c>
       <c r="E87">
-        <v>0.522</v>
+        <v>0</v>
       </c>
       <c r="F87">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="G87">
-        <v>0.225</v>
+        <v>0</v>
       </c>
       <c r="H87">
-        <v>0.174</v>
+        <v>0</v>
       </c>
       <c r="I87">
-        <v>0.201</v>
+        <v>0</v>
       </c>
       <c r="J87">
-        <v>0.055</v>
-      </c>
-      <c r="V87" t="s">
-        <v>108</v>
-      </c>
-      <c r="W87">
+        <v>0.014</v>
+      </c>
+      <c r="W87" t="s">
+        <v>109</v>
+      </c>
+      <c r="X87">
         <v>0.011</v>
       </c>
     </row>
-    <row r="88" spans="1:23">
+    <row r="88" spans="1:24">
       <c r="A88" s="2">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B88">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="C88">
-        <v>0.036</v>
+        <v>0</v>
       </c>
       <c r="D88">
-        <v>0.043</v>
+        <v>0</v>
       </c>
       <c r="E88">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="F88">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="G88">
-        <v>0.029</v>
+        <v>0</v>
       </c>
       <c r="H88">
-        <v>0.016</v>
+        <v>0</v>
       </c>
       <c r="I88">
-        <v>0.021</v>
+        <v>0</v>
       </c>
       <c r="J88">
-        <v>0</v>
-      </c>
-      <c r="V88" t="s">
-        <v>109</v>
-      </c>
-      <c r="W88">
+        <v>0.014</v>
+      </c>
+      <c r="W88" t="s">
+        <v>110</v>
+      </c>
+      <c r="X88">
         <v>0.011</v>
       </c>
     </row>
-    <row r="89" spans="1:23">
+    <row r="89" spans="1:24">
       <c r="A89" s="2">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B89">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="C89">
         <v>0</v>
@@ -4360,21 +4366,21 @@
         <v>0</v>
       </c>
       <c r="J89">
-        <v>0</v>
-      </c>
-      <c r="V89" t="s">
-        <v>110</v>
-      </c>
-      <c r="W89">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="1:23">
+        <v>0.014</v>
+      </c>
+      <c r="W89" t="s">
+        <v>111</v>
+      </c>
+      <c r="X89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:24">
       <c r="A90" s="2">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B90">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="C90">
         <v>0</v>
@@ -4398,21 +4404,21 @@
         <v>0</v>
       </c>
       <c r="J90">
-        <v>0.013</v>
-      </c>
-      <c r="V90" t="s">
-        <v>111</v>
-      </c>
-      <c r="W90">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="1:23">
+        <v>0.014</v>
+      </c>
+      <c r="W90" t="s">
+        <v>112</v>
+      </c>
+      <c r="X90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:24">
       <c r="A91" s="2">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B91">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="C91">
         <v>0</v>
@@ -4436,21 +4442,21 @@
         <v>0</v>
       </c>
       <c r="J91">
-        <v>0.013</v>
-      </c>
-      <c r="V91" t="s">
-        <v>112</v>
-      </c>
-      <c r="W91">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="1:23">
+        <v>0.014</v>
+      </c>
+      <c r="W91" t="s">
+        <v>113</v>
+      </c>
+      <c r="X91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:24">
       <c r="A92" s="2">
         <v>46231</v>
       </c>
       <c r="B92">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C92">
         <v>0</v>
@@ -4476,779 +4482,779 @@
       <c r="J92">
         <v>0.014</v>
       </c>
-      <c r="V92" t="s">
-        <v>113</v>
-      </c>
-      <c r="W92">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="1:23">
+      <c r="W92" t="s">
+        <v>114</v>
+      </c>
+      <c r="X92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:24">
       <c r="A93" s="2">
         <v>46231</v>
       </c>
       <c r="B93">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C93">
-        <v>0</v>
+        <v>0.046</v>
       </c>
       <c r="D93">
-        <v>0</v>
+        <v>0.065</v>
       </c>
       <c r="E93">
-        <v>0</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="F93">
-        <v>0</v>
+        <v>0.197</v>
       </c>
       <c r="G93">
-        <v>0</v>
+        <v>0.098</v>
       </c>
       <c r="H93">
-        <v>0</v>
+        <v>0.106</v>
       </c>
       <c r="I93">
-        <v>0</v>
+        <v>0.064</v>
       </c>
       <c r="J93">
-        <v>0.014</v>
-      </c>
-      <c r="V93" t="s">
-        <v>114</v>
-      </c>
-      <c r="W93">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="1:23">
+        <v>0.038</v>
+      </c>
+      <c r="W93" t="s">
+        <v>115</v>
+      </c>
+      <c r="X93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:24">
       <c r="A94" s="2">
         <v>46231</v>
       </c>
       <c r="B94">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C94">
-        <v>0</v>
+        <v>0.352</v>
       </c>
       <c r="D94">
-        <v>0</v>
+        <v>0.458</v>
       </c>
       <c r="E94">
-        <v>0</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="F94">
-        <v>0</v>
+        <v>0.771</v>
       </c>
       <c r="G94">
-        <v>0</v>
+        <v>0.49</v>
       </c>
       <c r="H94">
-        <v>0</v>
+        <v>0.442</v>
       </c>
       <c r="I94">
-        <v>0</v>
+        <v>0.328</v>
       </c>
       <c r="J94">
-        <v>0.014</v>
-      </c>
-      <c r="V94" t="s">
-        <v>115</v>
-      </c>
-      <c r="W94">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="1:23">
+        <v>0.349</v>
+      </c>
+      <c r="W94" t="s">
+        <v>116</v>
+      </c>
+      <c r="X94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:24">
       <c r="A95" s="2">
         <v>46231</v>
       </c>
       <c r="B95">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C95">
-        <v>0</v>
+        <v>0.861</v>
       </c>
       <c r="D95">
-        <v>0</v>
+        <v>0.973</v>
       </c>
       <c r="E95">
-        <v>0</v>
+        <v>1.511</v>
       </c>
       <c r="F95">
-        <v>0</v>
+        <v>1.765</v>
       </c>
       <c r="G95">
-        <v>0</v>
+        <v>1.323</v>
       </c>
       <c r="H95">
-        <v>0</v>
+        <v>0.743</v>
       </c>
       <c r="I95">
-        <v>0</v>
+        <v>0.635</v>
       </c>
       <c r="J95">
-        <v>0.014</v>
-      </c>
-      <c r="V95" t="s">
-        <v>116</v>
-      </c>
-      <c r="W95">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96" spans="1:23">
+        <v>0.866</v>
+      </c>
+      <c r="W95" t="s">
+        <v>117</v>
+      </c>
+      <c r="X95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:24">
       <c r="A96" s="2">
         <v>46231</v>
       </c>
       <c r="B96">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C96">
-        <v>0</v>
+        <v>1.462</v>
       </c>
       <c r="D96">
-        <v>0</v>
+        <v>1.697</v>
       </c>
       <c r="E96">
-        <v>0</v>
+        <v>2.372</v>
       </c>
       <c r="F96">
-        <v>0</v>
+        <v>2.559</v>
       </c>
       <c r="G96">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="H96">
-        <v>0</v>
+        <v>1.341</v>
       </c>
       <c r="I96">
-        <v>0</v>
+        <v>0.959</v>
       </c>
       <c r="J96">
-        <v>0.014</v>
-      </c>
-      <c r="V96" t="s">
-        <v>117</v>
-      </c>
-      <c r="W96">
+        <v>0.883</v>
+      </c>
+      <c r="W96" t="s">
+        <v>118</v>
+      </c>
+      <c r="X96">
         <v>0.192</v>
       </c>
     </row>
-    <row r="97" spans="1:23">
+    <row r="97" spans="1:24">
       <c r="A97" s="2">
         <v>46231</v>
       </c>
       <c r="B97">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C97">
-        <v>0</v>
+        <v>2.023</v>
       </c>
       <c r="D97">
-        <v>0</v>
+        <v>2.451</v>
       </c>
       <c r="E97">
-        <v>0</v>
+        <v>3.295</v>
       </c>
       <c r="F97">
-        <v>0</v>
+        <v>3.095</v>
       </c>
       <c r="G97">
-        <v>0</v>
+        <v>2.775</v>
       </c>
       <c r="H97">
-        <v>0</v>
+        <v>1.117</v>
       </c>
       <c r="I97">
-        <v>0</v>
+        <v>1.535</v>
       </c>
       <c r="J97">
-        <v>0.014</v>
-      </c>
-      <c r="V97" t="s">
-        <v>118</v>
-      </c>
-      <c r="W97">
+        <v>1.038</v>
+      </c>
+      <c r="W97" t="s">
+        <v>119</v>
+      </c>
+      <c r="X97">
         <v>0.21</v>
       </c>
     </row>
-    <row r="98" spans="1:23">
+    <row r="98" spans="1:24">
       <c r="A98" s="2">
         <v>46231</v>
       </c>
       <c r="B98">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C98">
-        <v>0.035</v>
+        <v>2.305</v>
       </c>
       <c r="D98">
-        <v>0.044</v>
+        <v>2.804</v>
       </c>
       <c r="E98">
-        <v>0.08699999999999999</v>
+        <v>3.626</v>
       </c>
       <c r="F98">
-        <v>0.239</v>
+        <v>3.409</v>
       </c>
       <c r="G98">
-        <v>0.108</v>
+        <v>3.137</v>
       </c>
       <c r="H98">
-        <v>0.106</v>
+        <v>1.182</v>
       </c>
       <c r="I98">
-        <v>0.064</v>
+        <v>1.563</v>
       </c>
       <c r="J98">
-        <v>0.038</v>
-      </c>
-      <c r="V98" t="s">
-        <v>119</v>
-      </c>
-      <c r="W98">
+        <v>1.21</v>
+      </c>
+      <c r="W98" t="s">
+        <v>120</v>
+      </c>
+      <c r="X98">
         <v>0.501</v>
       </c>
     </row>
-    <row r="99" spans="1:23">
+    <row r="99" spans="1:24">
       <c r="A99" s="2">
         <v>46231</v>
       </c>
       <c r="B99">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C99">
-        <v>0.248</v>
+        <v>2.65</v>
       </c>
       <c r="D99">
-        <v>0.305</v>
+        <v>3.146</v>
       </c>
       <c r="E99">
-        <v>0.584</v>
+        <v>3.48</v>
       </c>
       <c r="F99">
-        <v>0.9320000000000001</v>
+        <v>3.64</v>
       </c>
       <c r="G99">
-        <v>0.505</v>
+        <v>3.163</v>
       </c>
       <c r="H99">
-        <v>0.442</v>
+        <v>1.452</v>
       </c>
       <c r="I99">
-        <v>0.361</v>
+        <v>1.465</v>
       </c>
       <c r="J99">
-        <v>0.294</v>
-      </c>
-      <c r="V99" t="s">
-        <v>120</v>
-      </c>
-      <c r="W99">
+        <v>1.47</v>
+      </c>
+      <c r="W99" t="s">
+        <v>121</v>
+      </c>
+      <c r="X99">
         <v>0.678</v>
       </c>
     </row>
-    <row r="100" spans="1:23">
+    <row r="100" spans="1:24">
       <c r="A100" s="2">
         <v>46231</v>
       </c>
       <c r="B100">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C100">
-        <v>0.757</v>
+        <v>2.822</v>
       </c>
       <c r="D100">
-        <v>0.848</v>
+        <v>3.291</v>
       </c>
       <c r="E100">
-        <v>1.586</v>
+        <v>3.594</v>
       </c>
       <c r="F100">
-        <v>1.925</v>
+        <v>3.679</v>
       </c>
       <c r="G100">
-        <v>1.337</v>
+        <v>3.298</v>
       </c>
       <c r="H100">
-        <v>0.968</v>
+        <v>1.006</v>
       </c>
       <c r="I100">
-        <v>0.667</v>
+        <v>1.502</v>
       </c>
       <c r="J100">
-        <v>0.618</v>
-      </c>
-      <c r="V100" t="s">
-        <v>121</v>
-      </c>
-      <c r="W100">
+        <v>1.484</v>
+      </c>
+      <c r="W100" t="s">
+        <v>122</v>
+      </c>
+      <c r="X100">
         <v>1.135</v>
       </c>
     </row>
-    <row r="101" spans="1:23">
+    <row r="101" spans="1:24">
       <c r="A101" s="2">
         <v>46231</v>
       </c>
       <c r="B101">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C101">
-        <v>1.254</v>
+        <v>2.76</v>
       </c>
       <c r="D101">
-        <v>1.398</v>
+        <v>3.199</v>
       </c>
       <c r="E101">
-        <v>2.584</v>
+        <v>3.322</v>
       </c>
       <c r="F101">
-        <v>2.561</v>
+        <v>3.524</v>
       </c>
       <c r="G101">
-        <v>2.046</v>
+        <v>3.162</v>
       </c>
       <c r="H101">
-        <v>1.303</v>
+        <v>0.953</v>
       </c>
       <c r="I101">
-        <v>1.017</v>
+        <v>1.502</v>
       </c>
       <c r="J101">
-        <v>0.883</v>
-      </c>
-      <c r="V101" t="s">
-        <v>122</v>
-      </c>
-      <c r="W101">
+        <v>1.341</v>
+      </c>
+      <c r="W101" t="s">
+        <v>123</v>
+      </c>
+      <c r="X101">
         <v>1.387</v>
       </c>
     </row>
-    <row r="102" spans="1:23">
+    <row r="102" spans="1:24">
       <c r="A102" s="2">
         <v>46231</v>
       </c>
       <c r="B102">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C102">
-        <v>1.613</v>
+        <v>2.574</v>
       </c>
       <c r="D102">
-        <v>1.997</v>
+        <v>3.013</v>
       </c>
       <c r="E102">
-        <v>3.414</v>
+        <v>3.461</v>
       </c>
       <c r="F102">
-        <v>3.282</v>
+        <v>2.924</v>
       </c>
       <c r="G102">
-        <v>2.764</v>
+        <v>2.805</v>
       </c>
       <c r="H102">
-        <v>1.117</v>
+        <v>0.998</v>
       </c>
       <c r="I102">
-        <v>1.554</v>
+        <v>1.502</v>
       </c>
       <c r="J102">
-        <v>0.962</v>
-      </c>
-      <c r="V102" t="s">
-        <v>123</v>
-      </c>
-      <c r="W102">
+        <v>1.22</v>
+      </c>
+      <c r="W102" t="s">
+        <v>124</v>
+      </c>
+      <c r="X102">
         <v>1.534</v>
       </c>
     </row>
-    <row r="103" spans="1:23">
+    <row r="103" spans="1:24">
       <c r="A103" s="2">
         <v>46231</v>
       </c>
       <c r="B103">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C103">
-        <v>1.842</v>
+        <v>2.049</v>
       </c>
       <c r="D103">
-        <v>2.298</v>
+        <v>2.626</v>
       </c>
       <c r="E103">
-        <v>3.639</v>
+        <v>3.197</v>
       </c>
       <c r="F103">
-        <v>3.536</v>
+        <v>2.215</v>
       </c>
       <c r="G103">
-        <v>3.088</v>
+        <v>2.218</v>
       </c>
       <c r="H103">
-        <v>1.145</v>
+        <v>1.141</v>
       </c>
       <c r="I103">
-        <v>1.481</v>
+        <v>1.221</v>
       </c>
       <c r="J103">
-        <v>1.104</v>
-      </c>
-      <c r="V103" t="s">
-        <v>124</v>
-      </c>
-      <c r="W103">
+        <v>0.996</v>
+      </c>
+      <c r="W103" t="s">
+        <v>125</v>
+      </c>
+      <c r="X103">
         <v>1.228</v>
       </c>
     </row>
-    <row r="104" spans="1:23">
+    <row r="104" spans="1:24">
       <c r="A104" s="2">
         <v>46231</v>
       </c>
       <c r="B104">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C104">
-        <v>2.238</v>
+        <v>1.483</v>
       </c>
       <c r="D104">
-        <v>2.638</v>
+        <v>1.85</v>
       </c>
       <c r="E104">
-        <v>3.402</v>
+        <v>2.197</v>
       </c>
       <c r="F104">
-        <v>3.675</v>
+        <v>1.528</v>
       </c>
       <c r="G104">
-        <v>3.221</v>
+        <v>1.471</v>
       </c>
       <c r="H104">
-        <v>1.422</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="I104">
-        <v>1.481</v>
+        <v>0.892</v>
       </c>
       <c r="J104">
-        <v>1.21</v>
-      </c>
-      <c r="V104" t="s">
-        <v>125</v>
-      </c>
-      <c r="W104">
+        <v>0.657</v>
+      </c>
+      <c r="W104" t="s">
+        <v>126</v>
+      </c>
+      <c r="X104">
         <v>0.991</v>
       </c>
     </row>
-    <row r="105" spans="1:23">
+    <row r="105" spans="1:24">
       <c r="A105" s="2">
         <v>46231</v>
       </c>
       <c r="B105">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C105">
-        <v>2.484</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="D105">
-        <v>2.88</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E105">
-        <v>3.342</v>
+        <v>1.372</v>
       </c>
       <c r="F105">
-        <v>3.695</v>
+        <v>0.619</v>
       </c>
       <c r="G105">
-        <v>3.268</v>
+        <v>0.653</v>
       </c>
       <c r="H105">
-        <v>0.901</v>
+        <v>0.507</v>
       </c>
       <c r="I105">
-        <v>1.502</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="J105">
-        <v>1.37</v>
-      </c>
-      <c r="V105" t="s">
-        <v>126</v>
-      </c>
-      <c r="W105">
+        <v>0.284</v>
+      </c>
+      <c r="W105" t="s">
+        <v>127</v>
+      </c>
+      <c r="X105">
         <v>0.369</v>
       </c>
     </row>
-    <row r="106" spans="1:23">
+    <row r="106" spans="1:24">
       <c r="A106" s="2">
         <v>46231</v>
       </c>
       <c r="B106">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C106">
-        <v>2.615</v>
+        <v>0.24</v>
       </c>
       <c r="D106">
-        <v>2.917</v>
+        <v>0.302</v>
       </c>
       <c r="E106">
-        <v>3.516</v>
+        <v>0.523</v>
       </c>
       <c r="F106">
-        <v>3.361</v>
+        <v>0.198</v>
       </c>
       <c r="G106">
-        <v>3.158</v>
+        <v>0.253</v>
       </c>
       <c r="H106">
-        <v>1.056</v>
+        <v>0.281</v>
       </c>
       <c r="I106">
-        <v>1.502</v>
+        <v>0.201</v>
       </c>
       <c r="J106">
-        <v>1.284</v>
-      </c>
-      <c r="V106" t="s">
-        <v>127</v>
-      </c>
-      <c r="W106">
+        <v>0.116</v>
+      </c>
+      <c r="W106" t="s">
+        <v>128</v>
+      </c>
+      <c r="X106">
         <v>0.421</v>
       </c>
     </row>
-    <row r="107" spans="1:23">
+    <row r="107" spans="1:24">
       <c r="A107" s="2">
         <v>46231</v>
       </c>
       <c r="B107">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C107">
-        <v>2.181</v>
+        <v>0.041</v>
       </c>
       <c r="D107">
-        <v>2.81</v>
+        <v>0.074</v>
       </c>
       <c r="E107">
-        <v>3.326</v>
+        <v>0.101</v>
       </c>
       <c r="F107">
-        <v>2.812</v>
+        <v>0.026</v>
       </c>
       <c r="G107">
-        <v>2.754</v>
+        <v>0.042</v>
       </c>
       <c r="H107">
-        <v>1.135</v>
+        <v>0.034</v>
       </c>
       <c r="I107">
-        <v>1.502</v>
+        <v>0.021</v>
       </c>
       <c r="J107">
-        <v>1.161</v>
-      </c>
-      <c r="V107" t="s">
-        <v>128</v>
-      </c>
-      <c r="W107">
+        <v>0</v>
+      </c>
+      <c r="W107" t="s">
+        <v>129</v>
+      </c>
+      <c r="X107">
         <v>0.126</v>
       </c>
     </row>
-    <row r="108" spans="1:23">
+    <row r="108" spans="1:24">
       <c r="A108" s="2">
         <v>46231</v>
       </c>
       <c r="B108">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C108">
-        <v>1.918</v>
+        <v>0</v>
       </c>
       <c r="D108">
-        <v>2.479</v>
+        <v>0</v>
       </c>
       <c r="E108">
-        <v>3.028</v>
+        <v>0</v>
       </c>
       <c r="F108">
-        <v>2.144</v>
+        <v>0</v>
       </c>
       <c r="G108">
-        <v>2.148</v>
+        <v>0</v>
       </c>
       <c r="H108">
-        <v>1.141</v>
+        <v>0</v>
       </c>
       <c r="I108">
-        <v>1.186</v>
+        <v>0</v>
       </c>
       <c r="J108">
-        <v>0.82</v>
-      </c>
-      <c r="V108" t="s">
-        <v>129</v>
-      </c>
-      <c r="W108">
+        <v>0</v>
+      </c>
+      <c r="W108" t="s">
+        <v>130</v>
+      </c>
+      <c r="X108">
         <v>0.181</v>
       </c>
     </row>
-    <row r="109" spans="1:23">
+    <row r="109" spans="1:24">
       <c r="A109" s="2">
         <v>46231</v>
       </c>
       <c r="B109">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C109">
-        <v>1.393</v>
+        <v>0</v>
       </c>
       <c r="D109">
-        <v>1.783</v>
+        <v>0</v>
       </c>
       <c r="E109">
-        <v>2.245</v>
+        <v>0</v>
       </c>
       <c r="F109">
-        <v>1.522</v>
+        <v>0</v>
       </c>
       <c r="G109">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="H109">
-        <v>0.964</v>
+        <v>0</v>
       </c>
       <c r="I109">
-        <v>0.855</v>
+        <v>0</v>
       </c>
       <c r="J109">
-        <v>0.549</v>
-      </c>
-      <c r="V109" t="s">
-        <v>130</v>
-      </c>
-      <c r="W109">
+        <v>0.019</v>
+      </c>
+      <c r="W109" t="s">
+        <v>131</v>
+      </c>
+      <c r="X109">
         <v>0.181</v>
       </c>
     </row>
-    <row r="110" spans="1:23">
+    <row r="110" spans="1:24">
       <c r="A110" s="2">
         <v>46231</v>
       </c>
       <c r="B110">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C110">
-        <v>0.777</v>
+        <v>0</v>
       </c>
       <c r="D110">
-        <v>0.9389999999999999</v>
+        <v>0</v>
       </c>
       <c r="E110">
-        <v>1.288</v>
+        <v>0</v>
       </c>
       <c r="F110">
-        <v>0.499</v>
+        <v>0</v>
       </c>
       <c r="G110">
-        <v>0.671</v>
+        <v>0</v>
       </c>
       <c r="H110">
-        <v>0.484</v>
+        <v>0</v>
       </c>
       <c r="I110">
-        <v>0.5629999999999999</v>
+        <v>0</v>
       </c>
       <c r="J110">
-        <v>0.255</v>
-      </c>
-      <c r="V110" t="s">
-        <v>131</v>
-      </c>
-      <c r="W110">
+        <v>0.019</v>
+      </c>
+      <c r="W110" t="s">
+        <v>132</v>
+      </c>
+      <c r="X110">
         <v>0.109</v>
       </c>
     </row>
-    <row r="111" spans="1:23">
+    <row r="111" spans="1:24">
       <c r="A111" s="2">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B111">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="C111">
-        <v>0.245</v>
+        <v>0</v>
       </c>
       <c r="D111">
-        <v>0.295</v>
+        <v>0</v>
       </c>
       <c r="E111">
-        <v>0.549</v>
+        <v>0</v>
       </c>
       <c r="F111">
-        <v>0.206</v>
+        <v>0</v>
       </c>
       <c r="G111">
-        <v>0.252</v>
+        <v>0</v>
       </c>
       <c r="H111">
-        <v>0.232</v>
+        <v>0</v>
       </c>
       <c r="I111">
-        <v>0.197</v>
+        <v>0</v>
       </c>
       <c r="J111">
-        <v>0.109</v>
-      </c>
-      <c r="V111" t="s">
-        <v>132</v>
-      </c>
-      <c r="W111">
+        <v>0.02</v>
+      </c>
+      <c r="W111" t="s">
+        <v>133</v>
+      </c>
+      <c r="X111">
         <v>0.011</v>
       </c>
     </row>
-    <row r="112" spans="1:23">
+    <row r="112" spans="1:24">
       <c r="A112" s="2">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B112">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="C112">
-        <v>0.039</v>
+        <v>0</v>
       </c>
       <c r="D112">
-        <v>0.074</v>
+        <v>0</v>
       </c>
       <c r="E112">
-        <v>0.08799999999999999</v>
+        <v>0</v>
       </c>
       <c r="F112">
-        <v>0.024</v>
+        <v>0</v>
       </c>
       <c r="G112">
-        <v>0.031</v>
+        <v>0</v>
       </c>
       <c r="H112">
-        <v>0.034</v>
+        <v>0</v>
       </c>
       <c r="I112">
-        <v>0.021</v>
+        <v>0</v>
       </c>
       <c r="J112">
-        <v>0</v>
-      </c>
-      <c r="V112" t="s">
-        <v>133</v>
-      </c>
-      <c r="W112">
+        <v>0.02</v>
+      </c>
+      <c r="W112" t="s">
+        <v>134</v>
+      </c>
+      <c r="X112">
         <v>0.011</v>
       </c>
     </row>
-    <row r="113" spans="1:23">
+    <row r="113" spans="1:24">
       <c r="A113" s="2">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B113">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="C113">
         <v>0</v>
@@ -5257,36 +5263,36 @@
         <v>0</v>
       </c>
       <c r="E113">
+        <v>0</v>
+      </c>
+      <c r="F113">
+        <v>0</v>
+      </c>
+      <c r="G113">
+        <v>0</v>
+      </c>
+      <c r="H113">
+        <v>0</v>
+      </c>
+      <c r="I113">
+        <v>0</v>
+      </c>
+      <c r="J113">
         <v>0.014</v>
       </c>
-      <c r="F113">
-        <v>0</v>
-      </c>
-      <c r="G113">
-        <v>0</v>
-      </c>
-      <c r="H113">
-        <v>0</v>
-      </c>
-      <c r="I113">
-        <v>0</v>
-      </c>
-      <c r="J113">
-        <v>0.013</v>
-      </c>
-      <c r="V113" t="s">
-        <v>134</v>
-      </c>
-      <c r="W113">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="114" spans="1:23">
+      <c r="W113" t="s">
+        <v>135</v>
+      </c>
+      <c r="X113">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:24">
       <c r="A114" s="2">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B114">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="C114">
         <v>0</v>
@@ -5310,21 +5316,21 @@
         <v>0</v>
       </c>
       <c r="J114">
-        <v>0.019</v>
-      </c>
-      <c r="V114" t="s">
-        <v>135</v>
-      </c>
-      <c r="W114">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115" spans="1:23">
+        <v>0.015</v>
+      </c>
+      <c r="W114" t="s">
+        <v>136</v>
+      </c>
+      <c r="X114">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:24">
       <c r="A115" s="2">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B115">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="C115">
         <v>0</v>
@@ -5348,21 +5354,21 @@
         <v>0</v>
       </c>
       <c r="J115">
-        <v>0.019</v>
-      </c>
-      <c r="V115" t="s">
-        <v>136</v>
-      </c>
-      <c r="W115">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116" spans="1:23">
+        <v>0.015</v>
+      </c>
+      <c r="W115" t="s">
+        <v>137</v>
+      </c>
+      <c r="X115">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:24">
       <c r="A116" s="2">
         <v>46232</v>
       </c>
       <c r="B116">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C116">
         <v>0</v>
@@ -5386,781 +5392,781 @@
         <v>0</v>
       </c>
       <c r="J116">
-        <v>0.014</v>
-      </c>
-      <c r="V116" t="s">
-        <v>137</v>
-      </c>
-      <c r="W116">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117" spans="1:23">
+        <v>0.015</v>
+      </c>
+      <c r="W116" t="s">
+        <v>138</v>
+      </c>
+      <c r="X116">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:24">
       <c r="A117" s="2">
         <v>46232</v>
       </c>
       <c r="B117">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C117">
-        <v>0</v>
+        <v>0.046</v>
       </c>
       <c r="D117">
-        <v>0</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="E117">
-        <v>0</v>
+        <v>0.078</v>
       </c>
       <c r="F117">
-        <v>0</v>
+        <v>0.228</v>
       </c>
       <c r="G117">
-        <v>0</v>
+        <v>0.106</v>
       </c>
       <c r="H117">
-        <v>0</v>
+        <v>0.106</v>
       </c>
       <c r="I117">
-        <v>0</v>
+        <v>0.074</v>
       </c>
       <c r="J117">
-        <v>0.014</v>
-      </c>
-      <c r="V117" t="s">
-        <v>138</v>
-      </c>
-      <c r="W117">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="118" spans="1:23">
+        <v>0.059</v>
+      </c>
+      <c r="W117" t="s">
+        <v>139</v>
+      </c>
+      <c r="X117">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:24">
       <c r="A118" s="2">
         <v>46232</v>
       </c>
       <c r="B118">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C118">
-        <v>0</v>
+        <v>0.351</v>
       </c>
       <c r="D118">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="E118">
-        <v>0</v>
+        <v>0.552</v>
       </c>
       <c r="F118">
-        <v>0</v>
+        <v>0.906</v>
       </c>
       <c r="G118">
-        <v>0</v>
+        <v>0.499</v>
       </c>
       <c r="H118">
-        <v>0</v>
+        <v>0.469</v>
       </c>
       <c r="I118">
-        <v>0</v>
+        <v>0.443</v>
       </c>
       <c r="J118">
-        <v>0.014</v>
-      </c>
-      <c r="V118" t="s">
-        <v>139</v>
-      </c>
-      <c r="W118">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="119" spans="1:23">
+        <v>0.347</v>
+      </c>
+      <c r="W118" t="s">
+        <v>140</v>
+      </c>
+      <c r="X118">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:24">
       <c r="A119" s="2">
         <v>46232</v>
       </c>
       <c r="B119">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C119">
-        <v>0</v>
+        <v>1.069</v>
       </c>
       <c r="D119">
-        <v>0</v>
+        <v>1.065</v>
       </c>
       <c r="E119">
-        <v>0</v>
+        <v>1.434</v>
       </c>
       <c r="F119">
-        <v>0</v>
+        <v>2.051</v>
       </c>
       <c r="G119">
-        <v>0</v>
+        <v>1.491</v>
       </c>
       <c r="H119">
-        <v>0</v>
+        <v>0.868</v>
       </c>
       <c r="I119">
-        <v>0</v>
+        <v>0.909</v>
       </c>
       <c r="J119">
-        <v>0.015</v>
-      </c>
-      <c r="V119" t="s">
-        <v>140</v>
-      </c>
-      <c r="W119">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="120" spans="1:23">
+        <v>0.829</v>
+      </c>
+      <c r="W119" t="s">
+        <v>141</v>
+      </c>
+      <c r="X119">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:24">
       <c r="A120" s="2">
         <v>46232</v>
       </c>
       <c r="B120">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C120">
-        <v>0</v>
+        <v>1.792</v>
       </c>
       <c r="D120">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="E120">
-        <v>0</v>
+        <v>2.441</v>
       </c>
       <c r="F120">
-        <v>0</v>
+        <v>2.944</v>
       </c>
       <c r="G120">
-        <v>0</v>
+        <v>2.316</v>
       </c>
       <c r="H120">
-        <v>0</v>
+        <v>1.271</v>
       </c>
       <c r="I120">
-        <v>0</v>
+        <v>1.181</v>
       </c>
       <c r="J120">
-        <v>0.015</v>
-      </c>
-      <c r="V120" t="s">
-        <v>141</v>
-      </c>
-      <c r="W120">
+        <v>1.089</v>
+      </c>
+      <c r="W120" t="s">
+        <v>142</v>
+      </c>
+      <c r="X120">
         <v>0.192</v>
       </c>
     </row>
-    <row r="121" spans="1:23">
+    <row r="121" spans="1:24">
       <c r="A121" s="2">
         <v>46232</v>
       </c>
       <c r="B121">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C121">
-        <v>0</v>
+        <v>2.456</v>
       </c>
       <c r="D121">
-        <v>0</v>
+        <v>2.742</v>
       </c>
       <c r="E121">
-        <v>0</v>
+        <v>3.097</v>
       </c>
       <c r="F121">
-        <v>0</v>
+        <v>3.562</v>
       </c>
       <c r="G121">
-        <v>0</v>
+        <v>2.974</v>
       </c>
       <c r="H121">
-        <v>0</v>
+        <v>0.803</v>
       </c>
       <c r="I121">
-        <v>0</v>
+        <v>1.472</v>
       </c>
       <c r="J121">
-        <v>0.015</v>
-      </c>
-      <c r="V121" t="s">
-        <v>142</v>
-      </c>
-      <c r="W121">
+        <v>1.434</v>
+      </c>
+      <c r="W121" t="s">
+        <v>143</v>
+      </c>
+      <c r="X121">
         <v>0.21</v>
       </c>
     </row>
-    <row r="122" spans="1:23">
+    <row r="122" spans="1:24">
       <c r="A122" s="2">
         <v>46232</v>
       </c>
       <c r="B122">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C122">
-        <v>0.045</v>
+        <v>2.851</v>
       </c>
       <c r="D122">
-        <v>0.07099999999999999</v>
+        <v>3.175</v>
       </c>
       <c r="E122">
-        <v>0.077</v>
+        <v>3.369</v>
       </c>
       <c r="F122">
-        <v>0.198</v>
+        <v>4.13</v>
       </c>
       <c r="G122">
-        <v>0.107</v>
+        <v>3.416</v>
       </c>
       <c r="H122">
-        <v>0.073</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="I122">
-        <v>0.074</v>
+        <v>1.465</v>
       </c>
       <c r="J122">
-        <v>0.059</v>
-      </c>
-      <c r="V122" t="s">
-        <v>143</v>
-      </c>
-      <c r="W122">
+        <v>1.388</v>
+      </c>
+      <c r="W122" t="s">
+        <v>144</v>
+      </c>
+      <c r="X122">
         <v>0.501</v>
       </c>
     </row>
-    <row r="123" spans="1:23">
+    <row r="123" spans="1:24">
       <c r="A123" s="2">
         <v>46232</v>
       </c>
       <c r="B123">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C123">
-        <v>0.342</v>
+        <v>3.098</v>
       </c>
       <c r="D123">
-        <v>0.396</v>
+        <v>3.331</v>
       </c>
       <c r="E123">
-        <v>0.553</v>
+        <v>3.541</v>
       </c>
       <c r="F123">
-        <v>0.865</v>
+        <v>4.182</v>
       </c>
       <c r="G123">
-        <v>0.49</v>
+        <v>3.549</v>
       </c>
       <c r="H123">
-        <v>0.366</v>
+        <v>1.242</v>
       </c>
       <c r="I123">
-        <v>0.443</v>
+        <v>1.445</v>
       </c>
       <c r="J123">
-        <v>0.398</v>
-      </c>
-      <c r="V123" t="s">
-        <v>144</v>
-      </c>
-      <c r="W123">
+        <v>1.526</v>
+      </c>
+      <c r="W123" t="s">
+        <v>145</v>
+      </c>
+      <c r="X123">
         <v>0.678</v>
       </c>
     </row>
-    <row r="124" spans="1:23">
+    <row r="124" spans="1:24">
       <c r="A124" s="2">
         <v>46232</v>
       </c>
       <c r="B124">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C124">
-        <v>1.056</v>
+        <v>3.143</v>
       </c>
       <c r="D124">
-        <v>1.064</v>
+        <v>3.409</v>
       </c>
       <c r="E124">
-        <v>1.399</v>
+        <v>3.41</v>
       </c>
       <c r="F124">
-        <v>1.933</v>
+        <v>4.205</v>
       </c>
       <c r="G124">
-        <v>1.356</v>
+        <v>3.575</v>
       </c>
       <c r="H124">
-        <v>0.758</v>
+        <v>0.835</v>
       </c>
       <c r="I124">
-        <v>0.856</v>
+        <v>1.502</v>
       </c>
       <c r="J124">
-        <v>0.866</v>
-      </c>
-      <c r="V124" t="s">
-        <v>145</v>
-      </c>
-      <c r="W124">
+        <v>1.433</v>
+      </c>
+      <c r="W124" t="s">
+        <v>146</v>
+      </c>
+      <c r="X124">
         <v>0.954</v>
       </c>
     </row>
-    <row r="125" spans="1:23">
+    <row r="125" spans="1:24">
       <c r="A125" s="2">
         <v>46232</v>
       </c>
       <c r="B125">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C125">
-        <v>1.812</v>
+        <v>3.018</v>
       </c>
       <c r="D125">
-        <v>2.05</v>
+        <v>3.293</v>
       </c>
       <c r="E125">
-        <v>2.412</v>
+        <v>3.382</v>
       </c>
       <c r="F125">
-        <v>2.857</v>
+        <v>3.982</v>
       </c>
       <c r="G125">
-        <v>2.251</v>
+        <v>3.522</v>
       </c>
       <c r="H125">
-        <v>1.267</v>
+        <v>0.833</v>
       </c>
       <c r="I125">
-        <v>1.074</v>
+        <v>1.502</v>
       </c>
       <c r="J125">
-        <v>1.083</v>
-      </c>
-      <c r="V125" t="s">
-        <v>146</v>
-      </c>
-      <c r="W125">
+        <v>1.365</v>
+      </c>
+      <c r="W125" t="s">
+        <v>147</v>
+      </c>
+      <c r="X125">
         <v>1.021</v>
       </c>
     </row>
-    <row r="126" spans="1:23">
+    <row r="126" spans="1:24">
       <c r="A126" s="2">
         <v>46232</v>
       </c>
       <c r="B126">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C126">
-        <v>2.454</v>
+        <v>2.732</v>
       </c>
       <c r="D126">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="E126">
-        <v>3.156</v>
+        <v>3.416</v>
       </c>
       <c r="F126">
-        <v>3.398</v>
+        <v>3.391</v>
       </c>
       <c r="G126">
-        <v>2.78</v>
+        <v>3.165</v>
       </c>
       <c r="H126">
-        <v>1.349</v>
+        <v>0.744</v>
       </c>
       <c r="I126">
-        <v>1.472</v>
+        <v>1.502</v>
       </c>
       <c r="J126">
-        <v>1.46</v>
-      </c>
-      <c r="V126" t="s">
-        <v>147</v>
-      </c>
-      <c r="W126">
+        <v>1.172</v>
+      </c>
+      <c r="W126" t="s">
+        <v>148</v>
+      </c>
+      <c r="X126">
         <v>0.797</v>
       </c>
     </row>
-    <row r="127" spans="1:23">
+    <row r="127" spans="1:24">
       <c r="A127" s="2">
         <v>46232</v>
       </c>
       <c r="B127">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C127">
-        <v>2.842</v>
+        <v>2.189</v>
       </c>
       <c r="D127">
-        <v>3.174</v>
+        <v>2.693</v>
       </c>
       <c r="E127">
-        <v>3.588</v>
+        <v>2.964</v>
       </c>
       <c r="F127">
-        <v>3.732</v>
+        <v>2.556</v>
       </c>
       <c r="G127">
-        <v>3.15</v>
+        <v>2.581</v>
       </c>
       <c r="H127">
-        <v>0.903</v>
+        <v>0.843</v>
       </c>
       <c r="I127">
-        <v>1.465</v>
+        <v>1.502</v>
       </c>
       <c r="J127">
-        <v>1.394</v>
-      </c>
-      <c r="V127" t="s">
-        <v>148</v>
-      </c>
-      <c r="W127">
+        <v>1.017</v>
+      </c>
+      <c r="W127" t="s">
+        <v>149</v>
+      </c>
+      <c r="X127">
         <v>0.505</v>
       </c>
     </row>
-    <row r="128" spans="1:23">
+    <row r="128" spans="1:24">
       <c r="A128" s="2">
         <v>46232</v>
       </c>
       <c r="B128">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C128">
-        <v>3.097</v>
+        <v>1.575</v>
       </c>
       <c r="D128">
-        <v>3.331</v>
+        <v>1.806</v>
       </c>
       <c r="E128">
-        <v>3.699</v>
+        <v>2.229</v>
       </c>
       <c r="F128">
-        <v>3.802</v>
+        <v>1.604</v>
       </c>
       <c r="G128">
-        <v>3.295</v>
+        <v>1.734</v>
       </c>
       <c r="H128">
-        <v>1.155</v>
+        <v>0.793</v>
       </c>
       <c r="I128">
-        <v>1.445</v>
+        <v>1.09</v>
       </c>
       <c r="J128">
-        <v>1.499</v>
-      </c>
-      <c r="V128" t="s">
-        <v>149</v>
-      </c>
-      <c r="W128">
+        <v>0.66</v>
+      </c>
+      <c r="W128" t="s">
+        <v>150</v>
+      </c>
+      <c r="X128">
         <v>0.505</v>
       </c>
     </row>
-    <row r="129" spans="1:23">
+    <row r="129" spans="1:24">
       <c r="A129" s="2">
         <v>46232</v>
       </c>
       <c r="B129">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C129">
-        <v>3.142</v>
+        <v>0.827</v>
       </c>
       <c r="D129">
-        <v>3.41</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="E129">
-        <v>3.281</v>
+        <v>1.36</v>
       </c>
       <c r="F129">
-        <v>3.728</v>
+        <v>0.679</v>
       </c>
       <c r="G129">
-        <v>3.281</v>
+        <v>0.899</v>
       </c>
       <c r="H129">
-        <v>0.877</v>
+        <v>0.655</v>
       </c>
       <c r="I129">
-        <v>1.502</v>
+        <v>0.652</v>
       </c>
       <c r="J129">
-        <v>1.391</v>
-      </c>
-      <c r="V129" t="s">
-        <v>150</v>
-      </c>
-      <c r="W129">
+        <v>0.262</v>
+      </c>
+      <c r="W129" t="s">
+        <v>151</v>
+      </c>
+      <c r="X129">
         <v>0.465</v>
       </c>
     </row>
-    <row r="130" spans="1:23">
+    <row r="130" spans="1:24">
       <c r="A130" s="2">
         <v>46232</v>
       </c>
       <c r="B130">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C130">
-        <v>3.013</v>
+        <v>0.205</v>
       </c>
       <c r="D130">
-        <v>3.292</v>
+        <v>0.302</v>
       </c>
       <c r="E130">
-        <v>3.44</v>
+        <v>0.519</v>
       </c>
       <c r="F130">
-        <v>3.602</v>
+        <v>0.193</v>
       </c>
       <c r="G130">
-        <v>3.144</v>
+        <v>0.25</v>
       </c>
       <c r="H130">
-        <v>0.851</v>
+        <v>0.326</v>
       </c>
       <c r="I130">
-        <v>1.502</v>
+        <v>0.301</v>
       </c>
       <c r="J130">
-        <v>1.382</v>
-      </c>
-      <c r="V130" t="s">
-        <v>151</v>
-      </c>
-      <c r="W130">
+        <v>0.093</v>
+      </c>
+      <c r="W130" t="s">
+        <v>152</v>
+      </c>
+      <c r="X130">
         <v>0.242</v>
       </c>
     </row>
-    <row r="131" spans="1:23">
+    <row r="131" spans="1:24">
       <c r="A131" s="2">
         <v>46232</v>
       </c>
       <c r="B131">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C131">
-        <v>2.734</v>
+        <v>0.04</v>
       </c>
       <c r="D131">
-        <v>3.187</v>
+        <v>0.074</v>
       </c>
       <c r="E131">
-        <v>3.651</v>
+        <v>0.092</v>
       </c>
       <c r="F131">
-        <v>3.115</v>
+        <v>0.025</v>
       </c>
       <c r="G131">
-        <v>2.849</v>
+        <v>0.042</v>
       </c>
       <c r="H131">
-        <v>0.778</v>
+        <v>0.044</v>
       </c>
       <c r="I131">
-        <v>1.502</v>
+        <v>0.025</v>
       </c>
       <c r="J131">
-        <v>1.172</v>
-      </c>
-      <c r="V131" t="s">
-        <v>152</v>
-      </c>
-      <c r="W131">
+        <v>0</v>
+      </c>
+      <c r="W131" t="s">
+        <v>153</v>
+      </c>
+      <c r="X131">
         <v>0.195</v>
       </c>
     </row>
-    <row r="132" spans="1:23">
+    <row r="132" spans="1:24">
       <c r="A132" s="2">
         <v>46232</v>
       </c>
       <c r="B132">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C132">
-        <v>2.187</v>
+        <v>0</v>
       </c>
       <c r="D132">
-        <v>2.688</v>
+        <v>0</v>
       </c>
       <c r="E132">
-        <v>3.206</v>
+        <v>0</v>
       </c>
       <c r="F132">
-        <v>2.309</v>
+        <v>0</v>
       </c>
       <c r="G132">
-        <v>2.217</v>
+        <v>0</v>
       </c>
       <c r="H132">
-        <v>0.888</v>
+        <v>0</v>
       </c>
       <c r="I132">
-        <v>1.169</v>
+        <v>0</v>
       </c>
       <c r="J132">
-        <v>1.017</v>
-      </c>
-      <c r="V132" t="s">
-        <v>153</v>
-      </c>
-      <c r="W132">
+        <v>0.012</v>
+      </c>
+      <c r="W132" t="s">
+        <v>154</v>
+      </c>
+      <c r="X132">
         <v>0.25</v>
       </c>
     </row>
-    <row r="133" spans="1:23">
+    <row r="133" spans="1:24">
       <c r="A133" s="2">
         <v>46232</v>
       </c>
       <c r="B133">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C133">
-        <v>1.564</v>
+        <v>0</v>
       </c>
       <c r="D133">
-        <v>1.851</v>
+        <v>0</v>
       </c>
       <c r="E133">
-        <v>2.392</v>
+        <v>0.015</v>
       </c>
       <c r="F133">
-        <v>1.559</v>
+        <v>0</v>
       </c>
       <c r="G133">
-        <v>1.546</v>
+        <v>0</v>
       </c>
       <c r="H133">
-        <v>0.793</v>
+        <v>0</v>
       </c>
       <c r="I133">
-        <v>1.038</v>
+        <v>0</v>
       </c>
       <c r="J133">
-        <v>0.66</v>
-      </c>
-      <c r="V133" t="s">
-        <v>154</v>
-      </c>
-      <c r="W133">
+        <v>0.014</v>
+      </c>
+      <c r="W133" t="s">
+        <v>155</v>
+      </c>
+      <c r="X133">
         <v>0.25</v>
       </c>
     </row>
-    <row r="134" spans="1:23">
+    <row r="134" spans="1:24">
       <c r="A134" s="2">
         <v>46232</v>
       </c>
       <c r="B134">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C134">
-        <v>0.83</v>
+        <v>0</v>
       </c>
       <c r="D134">
-        <v>0.959</v>
+        <v>0</v>
       </c>
       <c r="E134">
-        <v>1.422</v>
+        <v>0</v>
       </c>
       <c r="F134">
-        <v>0.676</v>
+        <v>0</v>
       </c>
       <c r="G134">
-        <v>0.885</v>
+        <v>0</v>
       </c>
       <c r="H134">
-        <v>0.655</v>
+        <v>0</v>
       </c>
       <c r="I134">
-        <v>0.665</v>
+        <v>0</v>
       </c>
       <c r="J134">
-        <v>0.262</v>
-      </c>
-      <c r="V134" t="s">
-        <v>155</v>
-      </c>
-      <c r="W134">
+        <v>0.019</v>
+      </c>
+      <c r="W134" t="s">
+        <v>156</v>
+      </c>
+      <c r="X134">
         <v>0.109</v>
       </c>
     </row>
-    <row r="135" spans="1:23">
+    <row r="135" spans="1:24">
       <c r="A135" s="2">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B135">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="C135">
-        <v>0.206</v>
+        <v>0</v>
       </c>
       <c r="D135">
-        <v>0.302</v>
+        <v>0</v>
       </c>
       <c r="E135">
-        <v>0.524</v>
+        <v>0</v>
       </c>
       <c r="F135">
-        <v>0.193</v>
+        <v>0</v>
       </c>
       <c r="G135">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="H135">
-        <v>0.328</v>
+        <v>0</v>
       </c>
       <c r="I135">
-        <v>0.208</v>
+        <v>0</v>
       </c>
       <c r="J135">
-        <v>0.11</v>
-      </c>
-      <c r="V135" t="s">
-        <v>156</v>
-      </c>
-      <c r="W135">
+        <v>0</v>
+      </c>
+      <c r="W135" t="s">
+        <v>157</v>
+      </c>
+      <c r="X135">
         <v>0.112</v>
       </c>
     </row>
-    <row r="136" spans="1:23">
+    <row r="136" spans="1:24">
       <c r="A136" s="2">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B136">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="C136">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="D136">
-        <v>0.074</v>
+        <v>0</v>
       </c>
       <c r="E136">
-        <v>0.106</v>
+        <v>0</v>
       </c>
       <c r="F136">
-        <v>0.025</v>
+        <v>0</v>
       </c>
       <c r="G136">
-        <v>0.042</v>
+        <v>0</v>
       </c>
       <c r="H136">
-        <v>0.044</v>
+        <v>0</v>
       </c>
       <c r="I136">
-        <v>0.021</v>
+        <v>0</v>
       </c>
       <c r="J136">
-        <v>0</v>
-      </c>
-      <c r="V136" t="s">
-        <v>157</v>
-      </c>
-      <c r="W136">
+        <v>0.015</v>
+      </c>
+      <c r="W136" t="s">
+        <v>158</v>
+      </c>
+      <c r="X136">
         <v>0.112</v>
       </c>
     </row>
-    <row r="137" spans="1:23">
+    <row r="137" spans="1:24">
       <c r="A137" s="2">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B137">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="C137">
         <v>0</v>
@@ -6169,7 +6175,7 @@
         <v>0</v>
       </c>
       <c r="E137">
-        <v>0.012</v>
+        <v>0</v>
       </c>
       <c r="F137">
         <v>0</v>
@@ -6184,21 +6190,21 @@
         <v>0</v>
       </c>
       <c r="J137">
-        <v>0.014</v>
-      </c>
-      <c r="V137" t="s">
-        <v>158</v>
-      </c>
-      <c r="W137">
+        <v>0.015</v>
+      </c>
+      <c r="W137" t="s">
+        <v>159</v>
+      </c>
+      <c r="X137">
         <v>0.01</v>
       </c>
     </row>
-    <row r="138" spans="1:23">
+    <row r="138" spans="1:24">
       <c r="A138" s="2">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B138">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="C138">
         <v>0</v>
@@ -6222,21 +6228,21 @@
         <v>0</v>
       </c>
       <c r="J138">
-        <v>0.014</v>
-      </c>
-      <c r="V138" t="s">
-        <v>159</v>
-      </c>
-      <c r="W138">
+        <v>0.015</v>
+      </c>
+      <c r="W138" t="s">
+        <v>160</v>
+      </c>
+      <c r="X138">
         <v>0.01</v>
       </c>
     </row>
-    <row r="139" spans="1:23">
+    <row r="139" spans="1:24">
       <c r="A139" s="2">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B139">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="C139">
         <v>0</v>
@@ -6260,21 +6266,21 @@
         <v>0</v>
       </c>
       <c r="J139">
-        <v>0.014</v>
-      </c>
-      <c r="V139" t="s">
-        <v>160</v>
-      </c>
-      <c r="W139">
         <v>0.015</v>
       </c>
-    </row>
-    <row r="140" spans="1:23">
+      <c r="W139" t="s">
+        <v>161</v>
+      </c>
+      <c r="X139">
+        <v>0.015</v>
+      </c>
+    </row>
+    <row r="140" spans="1:24">
       <c r="A140" s="2">
         <v>46233</v>
       </c>
       <c r="B140">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C140">
         <v>0</v>
@@ -6298,781 +6304,781 @@
         <v>0</v>
       </c>
       <c r="J140">
-        <v>0.021</v>
-      </c>
-      <c r="V140" t="s">
-        <v>161</v>
-      </c>
-      <c r="W140">
         <v>0.015</v>
       </c>
-    </row>
-    <row r="141" spans="1:23">
+      <c r="W140" t="s">
+        <v>162</v>
+      </c>
+      <c r="X140">
+        <v>0.015</v>
+      </c>
+    </row>
+    <row r="141" spans="1:24">
       <c r="A141" s="2">
         <v>46233</v>
       </c>
       <c r="B141">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C141">
-        <v>0</v>
+        <v>0.046</v>
       </c>
       <c r="D141">
-        <v>0</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="E141">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F141">
-        <v>0</v>
+        <v>0.228</v>
       </c>
       <c r="G141">
-        <v>0</v>
+        <v>0.106</v>
       </c>
       <c r="H141">
-        <v>0</v>
+        <v>0.106</v>
       </c>
       <c r="I141">
-        <v>0</v>
+        <v>0.074</v>
       </c>
       <c r="J141">
+        <v>0.059</v>
+      </c>
+      <c r="W141" t="s">
+        <v>163</v>
+      </c>
+      <c r="X141">
         <v>0.015</v>
       </c>
-      <c r="V141" t="s">
-        <v>162</v>
-      </c>
-      <c r="W141">
-        <v>0.015</v>
-      </c>
-    </row>
-    <row r="142" spans="1:23">
+    </row>
+    <row r="142" spans="1:24">
       <c r="A142" s="2">
         <v>46233</v>
       </c>
       <c r="B142">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C142">
-        <v>0</v>
+        <v>0.365</v>
       </c>
       <c r="D142">
-        <v>0</v>
+        <v>0.401</v>
       </c>
       <c r="E142">
-        <v>0</v>
+        <v>0.537</v>
       </c>
       <c r="F142">
-        <v>0</v>
+        <v>0.923</v>
       </c>
       <c r="G142">
-        <v>0</v>
+        <v>0.519</v>
       </c>
       <c r="H142">
-        <v>0</v>
+        <v>0.46</v>
       </c>
       <c r="I142">
-        <v>0</v>
+        <v>0.443</v>
       </c>
       <c r="J142">
+        <v>0.453</v>
+      </c>
+      <c r="W142" t="s">
+        <v>164</v>
+      </c>
+      <c r="X142">
         <v>0.015</v>
       </c>
-      <c r="V142" t="s">
-        <v>163</v>
-      </c>
-      <c r="W142">
-        <v>0.015</v>
-      </c>
-    </row>
-    <row r="143" spans="1:23">
+    </row>
+    <row r="143" spans="1:24">
       <c r="A143" s="2">
         <v>46233</v>
       </c>
       <c r="B143">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C143">
-        <v>0</v>
+        <v>1.037</v>
       </c>
       <c r="D143">
-        <v>0</v>
+        <v>1.063</v>
       </c>
       <c r="E143">
-        <v>0</v>
+        <v>1.585</v>
       </c>
       <c r="F143">
-        <v>0</v>
+        <v>2.083</v>
       </c>
       <c r="G143">
-        <v>0</v>
+        <v>1.448</v>
       </c>
       <c r="H143">
-        <v>0</v>
+        <v>0.803</v>
       </c>
       <c r="I143">
-        <v>0</v>
+        <v>0.899</v>
       </c>
       <c r="J143">
-        <v>0.015</v>
-      </c>
-      <c r="V143" t="s">
-        <v>164</v>
-      </c>
-      <c r="W143">
+        <v>0.7</v>
+      </c>
+      <c r="W143" t="s">
+        <v>165</v>
+      </c>
+      <c r="X143">
         <v>0.01</v>
       </c>
     </row>
-    <row r="144" spans="1:23">
+    <row r="144" spans="1:24">
       <c r="A144" s="2">
         <v>46233</v>
       </c>
       <c r="B144">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C144">
-        <v>0</v>
+        <v>1.786</v>
       </c>
       <c r="D144">
-        <v>0</v>
+        <v>2.049</v>
       </c>
       <c r="E144">
-        <v>0</v>
+        <v>2.461</v>
       </c>
       <c r="F144">
-        <v>0</v>
+        <v>2.982</v>
       </c>
       <c r="G144">
-        <v>0</v>
+        <v>2.359</v>
       </c>
       <c r="H144">
-        <v>0</v>
+        <v>1.263</v>
       </c>
       <c r="I144">
-        <v>0</v>
+        <v>1.227</v>
       </c>
       <c r="J144">
-        <v>0.015</v>
-      </c>
-      <c r="V144" t="s">
-        <v>165</v>
-      </c>
-      <c r="W144">
+        <v>1.002</v>
+      </c>
+      <c r="W144" t="s">
+        <v>166</v>
+      </c>
+      <c r="X144">
         <v>0.038</v>
       </c>
     </row>
-    <row r="145" spans="1:23">
+    <row r="145" spans="1:24">
       <c r="A145" s="2">
         <v>46233</v>
       </c>
       <c r="B145">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C145">
-        <v>0</v>
+        <v>2.343</v>
       </c>
       <c r="D145">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="E145">
-        <v>0</v>
+        <v>3.597</v>
       </c>
       <c r="F145">
-        <v>0</v>
+        <v>3.743</v>
       </c>
       <c r="G145">
-        <v>0</v>
+        <v>3.047</v>
       </c>
       <c r="H145">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="I145">
-        <v>0</v>
+        <v>1.472</v>
       </c>
       <c r="J145">
-        <v>0.015</v>
-      </c>
-      <c r="V145" t="s">
-        <v>166</v>
-      </c>
-      <c r="W145">
+        <v>1.451</v>
+      </c>
+      <c r="W145" t="s">
+        <v>167</v>
+      </c>
+      <c r="X145">
         <v>0.056</v>
       </c>
     </row>
-    <row r="146" spans="1:23">
+    <row r="146" spans="1:24">
       <c r="A146" s="2">
         <v>46233</v>
       </c>
       <c r="B146">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C146">
-        <v>0.047</v>
+        <v>2.64</v>
       </c>
       <c r="D146">
-        <v>0.07099999999999999</v>
+        <v>3.073</v>
       </c>
       <c r="E146">
-        <v>0.07000000000000001</v>
+        <v>3.917</v>
       </c>
       <c r="F146">
-        <v>0.236</v>
+        <v>3.921</v>
       </c>
       <c r="G146">
-        <v>0.11</v>
+        <v>3.271</v>
       </c>
       <c r="H146">
-        <v>0.104</v>
+        <v>1.253</v>
       </c>
       <c r="I146">
-        <v>0.074</v>
+        <v>1.465</v>
       </c>
       <c r="J146">
-        <v>0.062</v>
-      </c>
-      <c r="V146" t="s">
-        <v>167</v>
-      </c>
-      <c r="W146">
+        <v>1.632</v>
+      </c>
+      <c r="W146" t="s">
+        <v>168</v>
+      </c>
+      <c r="X146">
         <v>0.462</v>
       </c>
     </row>
-    <row r="147" spans="1:23">
+    <row r="147" spans="1:24">
       <c r="A147" s="2">
         <v>46233</v>
       </c>
       <c r="B147">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C147">
-        <v>0.376</v>
+        <v>2.874</v>
       </c>
       <c r="D147">
-        <v>0.397</v>
+        <v>3.044</v>
       </c>
       <c r="E147">
-        <v>0.532</v>
+        <v>3.548</v>
       </c>
       <c r="F147">
-        <v>0.916</v>
+        <v>3.832</v>
       </c>
       <c r="G147">
-        <v>0.506</v>
+        <v>3.325</v>
       </c>
       <c r="H147">
-        <v>0.431</v>
+        <v>1.407</v>
       </c>
       <c r="I147">
-        <v>0.443</v>
+        <v>1.445</v>
       </c>
       <c r="J147">
-        <v>0.42</v>
-      </c>
-      <c r="V147" t="s">
-        <v>168</v>
-      </c>
-      <c r="W147">
+        <v>1.607</v>
+      </c>
+      <c r="W147" t="s">
+        <v>169</v>
+      </c>
+      <c r="X147">
         <v>0.314</v>
       </c>
     </row>
-    <row r="148" spans="1:23">
+    <row r="148" spans="1:24">
       <c r="A148" s="2">
         <v>46233</v>
       </c>
       <c r="B148">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C148">
-        <v>1.035</v>
+        <v>3.058</v>
       </c>
       <c r="D148">
-        <v>1.057</v>
+        <v>3.273</v>
       </c>
       <c r="E148">
-        <v>1.522</v>
+        <v>3.636</v>
       </c>
       <c r="F148">
-        <v>2.056</v>
+        <v>3.81</v>
       </c>
       <c r="G148">
-        <v>1.49</v>
+        <v>3.351</v>
       </c>
       <c r="H148">
-        <v>0.841</v>
+        <v>0.835</v>
       </c>
       <c r="I148">
-        <v>0.906</v>
+        <v>1.502</v>
       </c>
       <c r="J148">
-        <v>0.773</v>
-      </c>
-      <c r="V148" t="s">
-        <v>169</v>
-      </c>
-      <c r="W148">
+        <v>1.463</v>
+      </c>
+      <c r="W148" t="s">
+        <v>170</v>
+      </c>
+      <c r="X148">
         <v>0.43</v>
       </c>
     </row>
-    <row r="149" spans="1:23">
+    <row r="149" spans="1:24">
       <c r="A149" s="2">
         <v>46233</v>
       </c>
       <c r="B149">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C149">
-        <v>1.74</v>
+        <v>3.031</v>
       </c>
       <c r="D149">
-        <v>2.028</v>
+        <v>3.158</v>
       </c>
       <c r="E149">
-        <v>2.443</v>
+        <v>3.648</v>
       </c>
       <c r="F149">
-        <v>2.961</v>
+        <v>3.631</v>
       </c>
       <c r="G149">
-        <v>2.337</v>
+        <v>3.321</v>
       </c>
       <c r="H149">
-        <v>1.279</v>
+        <v>0.763</v>
       </c>
       <c r="I149">
-        <v>1.252</v>
+        <v>1.502</v>
       </c>
       <c r="J149">
-        <v>1.08</v>
-      </c>
-      <c r="V149" t="s">
-        <v>170</v>
-      </c>
-      <c r="W149">
+        <v>1.43</v>
+      </c>
+      <c r="W149" t="s">
+        <v>171</v>
+      </c>
+      <c r="X149">
         <v>0.734</v>
       </c>
     </row>
-    <row r="150" spans="1:23">
+    <row r="150" spans="1:24">
       <c r="A150" s="2">
         <v>46233</v>
       </c>
       <c r="B150">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C150">
-        <v>2.336</v>
+        <v>2.562</v>
       </c>
       <c r="D150">
-        <v>2.563</v>
+        <v>3.04</v>
       </c>
       <c r="E150">
-        <v>3.614</v>
+        <v>3.715</v>
       </c>
       <c r="F150">
-        <v>3.805</v>
+        <v>3.174</v>
       </c>
       <c r="G150">
-        <v>3.051</v>
+        <v>2.983</v>
       </c>
       <c r="H150">
-        <v>0.897</v>
+        <v>0.839</v>
       </c>
       <c r="I150">
-        <v>1.437</v>
+        <v>1.502</v>
       </c>
       <c r="J150">
-        <v>1.432</v>
-      </c>
-      <c r="V150" t="s">
-        <v>171</v>
-      </c>
-      <c r="W150">
+        <v>1.156</v>
+      </c>
+      <c r="W150" t="s">
+        <v>172</v>
+      </c>
+      <c r="X150">
         <v>0.5669999999999999</v>
       </c>
     </row>
-    <row r="151" spans="1:23">
+    <row r="151" spans="1:24">
       <c r="A151" s="2">
         <v>46233</v>
       </c>
       <c r="B151">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C151">
-        <v>2.639</v>
+        <v>1.98</v>
       </c>
       <c r="D151">
-        <v>3.059</v>
+        <v>2.683</v>
       </c>
       <c r="E151">
-        <v>3.923</v>
+        <v>3.19</v>
       </c>
       <c r="F151">
-        <v>4.173</v>
+        <v>2.415</v>
       </c>
       <c r="G151">
-        <v>3.425</v>
+        <v>2.35</v>
       </c>
       <c r="H151">
-        <v>0.879</v>
+        <v>0.992</v>
       </c>
       <c r="I151">
-        <v>1.445</v>
+        <v>1.483</v>
       </c>
       <c r="J151">
-        <v>1.494</v>
-      </c>
-      <c r="V151" t="s">
-        <v>172</v>
-      </c>
-      <c r="W151">
+        <v>1.017</v>
+      </c>
+      <c r="W151" t="s">
+        <v>173</v>
+      </c>
+      <c r="X151">
         <v>0.41</v>
       </c>
     </row>
-    <row r="152" spans="1:23">
+    <row r="152" spans="1:24">
       <c r="A152" s="2">
         <v>46233</v>
       </c>
       <c r="B152">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C152">
-        <v>2.851</v>
+        <v>1.378</v>
       </c>
       <c r="D152">
-        <v>3.032</v>
+        <v>1.819</v>
       </c>
       <c r="E152">
-        <v>3.583</v>
+        <v>2.298</v>
       </c>
       <c r="F152">
-        <v>4.198</v>
+        <v>1.593</v>
       </c>
       <c r="G152">
-        <v>3.575</v>
+        <v>1.59</v>
       </c>
       <c r="H152">
-        <v>1.436</v>
+        <v>0.944</v>
       </c>
       <c r="I152">
-        <v>1.445</v>
+        <v>1.09</v>
       </c>
       <c r="J152">
-        <v>1.556</v>
-      </c>
-      <c r="V152" t="s">
-        <v>173</v>
-      </c>
-      <c r="W152">
+        <v>0.68</v>
+      </c>
+      <c r="W152" t="s">
+        <v>174</v>
+      </c>
+      <c r="X152">
         <v>0.289</v>
       </c>
     </row>
-    <row r="153" spans="1:23">
+    <row r="153" spans="1:24">
       <c r="A153" s="2">
         <v>46233</v>
       </c>
       <c r="B153">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C153">
-        <v>2.955</v>
+        <v>0.747</v>
       </c>
       <c r="D153">
-        <v>3.058</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="E153">
-        <v>3.733</v>
+        <v>1.391</v>
       </c>
       <c r="F153">
-        <v>4.196</v>
+        <v>0.677</v>
       </c>
       <c r="G153">
-        <v>3.576</v>
+        <v>0.825</v>
       </c>
       <c r="H153">
-        <v>0.951</v>
+        <v>0.655</v>
       </c>
       <c r="I153">
-        <v>1.502</v>
+        <v>0.652</v>
       </c>
       <c r="J153">
-        <v>1.467</v>
-      </c>
-      <c r="V153" t="s">
-        <v>174</v>
-      </c>
-      <c r="W153">
+        <v>0.262</v>
+      </c>
+      <c r="W153" t="s">
+        <v>175</v>
+      </c>
+      <c r="X153">
         <v>0.336</v>
       </c>
     </row>
-    <row r="154" spans="1:23">
+    <row r="154" spans="1:24">
       <c r="A154" s="2">
         <v>46233</v>
       </c>
       <c r="B154">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C154">
-        <v>2.786</v>
+        <v>0.248</v>
       </c>
       <c r="D154">
-        <v>3.102</v>
+        <v>0.303</v>
       </c>
       <c r="E154">
-        <v>3.644</v>
+        <v>0.481</v>
       </c>
       <c r="F154">
-        <v>4.001</v>
+        <v>0.195</v>
       </c>
       <c r="G154">
-        <v>3.513</v>
+        <v>0.25</v>
       </c>
       <c r="H154">
-        <v>0.906</v>
+        <v>0.326</v>
       </c>
       <c r="I154">
-        <v>1.502</v>
+        <v>0.328</v>
       </c>
       <c r="J154">
-        <v>1.41</v>
-      </c>
-      <c r="V154" t="s">
-        <v>175</v>
-      </c>
-      <c r="W154">
+        <v>0.121</v>
+      </c>
+      <c r="W154" t="s">
+        <v>176</v>
+      </c>
+      <c r="X154">
         <v>0.244</v>
       </c>
     </row>
-    <row r="155" spans="1:23">
+    <row r="155" spans="1:24">
       <c r="A155" s="2">
         <v>46233</v>
       </c>
       <c r="B155">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C155">
-        <v>2.474</v>
+        <v>0.048</v>
       </c>
       <c r="D155">
-        <v>3.005</v>
+        <v>0.074</v>
       </c>
       <c r="E155">
-        <v>3.636</v>
+        <v>0.094</v>
       </c>
       <c r="F155">
-        <v>3.447</v>
+        <v>0.026</v>
       </c>
       <c r="G155">
-        <v>3.166</v>
+        <v>0.042</v>
       </c>
       <c r="H155">
-        <v>0.99</v>
+        <v>0.044</v>
       </c>
       <c r="I155">
-        <v>1.502</v>
+        <v>0.025</v>
       </c>
       <c r="J155">
-        <v>1.22</v>
-      </c>
-      <c r="V155" t="s">
-        <v>176</v>
-      </c>
-      <c r="W155">
+        <v>0</v>
+      </c>
+      <c r="W155" t="s">
+        <v>177</v>
+      </c>
+      <c r="X155">
         <v>0.197</v>
       </c>
     </row>
-    <row r="156" spans="1:23">
+    <row r="156" spans="1:24">
       <c r="A156" s="2">
         <v>46233</v>
       </c>
       <c r="B156">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C156">
-        <v>2.016</v>
+        <v>0</v>
       </c>
       <c r="D156">
-        <v>2.593</v>
+        <v>0</v>
       </c>
       <c r="E156">
-        <v>3.154</v>
+        <v>0</v>
       </c>
       <c r="F156">
-        <v>2.567</v>
+        <v>0</v>
       </c>
       <c r="G156">
-        <v>2.581</v>
+        <v>0</v>
       </c>
       <c r="H156">
-        <v>1.044</v>
+        <v>0</v>
       </c>
       <c r="I156">
-        <v>1.502</v>
+        <v>0</v>
       </c>
       <c r="J156">
-        <v>0.979</v>
-      </c>
-      <c r="V156" t="s">
-        <v>177</v>
-      </c>
-      <c r="W156">
+        <v>0</v>
+      </c>
+      <c r="W156" t="s">
+        <v>178</v>
+      </c>
+      <c r="X156">
         <v>0.252</v>
       </c>
     </row>
-    <row r="157" spans="1:23">
+    <row r="157" spans="1:24">
       <c r="A157" s="2">
         <v>46233</v>
       </c>
       <c r="B157">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C157">
-        <v>1.473</v>
+        <v>0</v>
       </c>
       <c r="D157">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="E157">
-        <v>2.317</v>
+        <v>0</v>
       </c>
       <c r="F157">
-        <v>1.599</v>
+        <v>0</v>
       </c>
       <c r="G157">
-        <v>1.676</v>
+        <v>0</v>
       </c>
       <c r="H157">
-        <v>0.919</v>
+        <v>0</v>
       </c>
       <c r="I157">
-        <v>1.087</v>
+        <v>0</v>
       </c>
       <c r="J157">
-        <v>0.638</v>
-      </c>
-      <c r="V157" t="s">
-        <v>178</v>
-      </c>
-      <c r="W157">
+        <v>0</v>
+      </c>
+      <c r="W157" t="s">
+        <v>179</v>
+      </c>
+      <c r="X157">
         <v>0.252</v>
       </c>
     </row>
-    <row r="158" spans="1:23">
+    <row r="158" spans="1:24">
       <c r="A158" s="2">
         <v>46233</v>
       </c>
       <c r="B158">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C158">
-        <v>0.773</v>
+        <v>0</v>
       </c>
       <c r="D158">
-        <v>0.921</v>
+        <v>0</v>
       </c>
       <c r="E158">
-        <v>1.384</v>
+        <v>0</v>
       </c>
       <c r="F158">
-        <v>0.6929999999999999</v>
+        <v>0</v>
       </c>
       <c r="G158">
-        <v>0.951</v>
+        <v>0</v>
       </c>
       <c r="H158">
-        <v>0.675</v>
+        <v>0</v>
       </c>
       <c r="I158">
-        <v>0.518</v>
+        <v>0</v>
       </c>
       <c r="J158">
-        <v>0.263</v>
-      </c>
-      <c r="V158" t="s">
-        <v>179</v>
-      </c>
-      <c r="W158">
+        <v>0.014</v>
+      </c>
+      <c r="W158" t="s">
+        <v>180</v>
+      </c>
+      <c r="X158">
         <v>0.112</v>
       </c>
     </row>
-    <row r="159" spans="1:23">
+    <row r="159" spans="1:24">
       <c r="A159" s="2">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B159">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="C159">
-        <v>0.215</v>
+        <v>0</v>
       </c>
       <c r="D159">
-        <v>0.286</v>
+        <v>0</v>
       </c>
       <c r="E159">
-        <v>0.477</v>
+        <v>0</v>
       </c>
       <c r="F159">
-        <v>0.195</v>
+        <v>0</v>
       </c>
       <c r="G159">
-        <v>0.236</v>
+        <v>0</v>
       </c>
       <c r="H159">
-        <v>0.304</v>
+        <v>0</v>
       </c>
       <c r="I159">
-        <v>0.328</v>
+        <v>0</v>
       </c>
       <c r="J159">
-        <v>0.121</v>
-      </c>
-      <c r="V159" t="s">
-        <v>180</v>
-      </c>
-      <c r="W159">
+        <v>0.015</v>
+      </c>
+      <c r="W159" t="s">
+        <v>181</v>
+      </c>
+      <c r="X159">
         <v>0.112</v>
       </c>
     </row>
-    <row r="160" spans="1:23">
+    <row r="160" spans="1:24">
       <c r="A160" s="2">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B160">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="C160">
-        <v>0.042</v>
+        <v>0</v>
       </c>
       <c r="D160">
-        <v>0.07199999999999999</v>
+        <v>0</v>
       </c>
       <c r="E160">
-        <v>0.08799999999999999</v>
+        <v>0</v>
       </c>
       <c r="F160">
-        <v>0.025</v>
+        <v>0</v>
       </c>
       <c r="G160">
-        <v>0.042</v>
+        <v>0</v>
       </c>
       <c r="H160">
-        <v>0.041</v>
+        <v>0</v>
       </c>
       <c r="I160">
-        <v>0.025</v>
+        <v>0</v>
       </c>
       <c r="J160">
         <v>0</v>
       </c>
-      <c r="V160" t="s">
-        <v>181</v>
-      </c>
-      <c r="W160">
+      <c r="W160" t="s">
+        <v>182</v>
+      </c>
+      <c r="X160">
         <v>0.112</v>
       </c>
     </row>
-    <row r="161" spans="1:23">
+    <row r="161" spans="1:24">
       <c r="A161" s="2">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B161">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="C161">
         <v>0</v>
@@ -7096,21 +7102,21 @@
         <v>0</v>
       </c>
       <c r="J161">
-        <v>0</v>
-      </c>
-      <c r="V161" t="s">
-        <v>182</v>
-      </c>
-      <c r="W161">
+        <v>0.015</v>
+      </c>
+      <c r="W161" t="s">
+        <v>183</v>
+      </c>
+      <c r="X161">
         <v>0.01</v>
       </c>
     </row>
-    <row r="162" spans="1:23">
+    <row r="162" spans="1:24">
       <c r="A162" s="2">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B162">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="C162">
         <v>0</v>
@@ -7119,7 +7125,7 @@
         <v>0</v>
       </c>
       <c r="E162">
-        <v>0.011</v>
+        <v>0</v>
       </c>
       <c r="F162">
         <v>0</v>
@@ -7134,21 +7140,21 @@
         <v>0</v>
       </c>
       <c r="J162">
-        <v>0.014</v>
-      </c>
-      <c r="V162" t="s">
-        <v>183</v>
-      </c>
-      <c r="W162">
+        <v>0.015</v>
+      </c>
+      <c r="W162" t="s">
+        <v>184</v>
+      </c>
+      <c r="X162">
         <v>0.01</v>
       </c>
     </row>
-    <row r="163" spans="1:23">
+    <row r="163" spans="1:24">
       <c r="A163" s="2">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B163">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="C163">
         <v>0</v>
@@ -7172,21 +7178,21 @@
         <v>0</v>
       </c>
       <c r="J163">
-        <v>0.014</v>
-      </c>
-      <c r="V163" t="s">
-        <v>184</v>
-      </c>
-      <c r="W163">
+        <v>0.015</v>
+      </c>
+      <c r="W163" t="s">
+        <v>185</v>
+      </c>
+      <c r="X163">
         <v>0.01</v>
       </c>
     </row>
-    <row r="164" spans="1:23">
+    <row r="164" spans="1:24">
       <c r="A164" s="2">
         <v>46234</v>
       </c>
       <c r="B164">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C164">
         <v>0</v>
@@ -7212,238 +7218,238 @@
       <c r="J164">
         <v>0.015</v>
       </c>
-      <c r="V164" t="s">
-        <v>185</v>
-      </c>
-      <c r="W164">
+      <c r="W164" t="s">
+        <v>186</v>
+      </c>
+      <c r="X164">
         <v>0.01</v>
       </c>
     </row>
-    <row r="165" spans="1:23">
+    <row r="165" spans="1:24">
       <c r="A165" s="2">
         <v>46234</v>
       </c>
       <c r="B165">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C165">
-        <v>0</v>
+        <v>0.039</v>
       </c>
       <c r="D165">
-        <v>0</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="E165">
-        <v>0</v>
+        <v>0.066</v>
       </c>
       <c r="F165">
-        <v>0</v>
+        <v>0.242</v>
       </c>
       <c r="G165">
-        <v>0</v>
+        <v>0.106</v>
       </c>
       <c r="H165">
-        <v>0</v>
+        <v>0.104</v>
       </c>
       <c r="I165">
-        <v>0</v>
+        <v>0.064</v>
       </c>
       <c r="J165">
-        <v>0.015</v>
-      </c>
-      <c r="V165" t="s">
-        <v>186</v>
-      </c>
-      <c r="W165">
+        <v>0.039</v>
+      </c>
+      <c r="W165" t="s">
+        <v>187</v>
+      </c>
+      <c r="X165">
         <v>0.01</v>
       </c>
     </row>
-    <row r="166" spans="1:23">
+    <row r="166" spans="1:24">
       <c r="A166" s="2">
         <v>46234</v>
       </c>
       <c r="B166">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C166">
-        <v>0</v>
+        <v>0.36</v>
       </c>
       <c r="D166">
-        <v>0</v>
+        <v>0.399</v>
       </c>
       <c r="E166">
-        <v>0</v>
+        <v>0.536</v>
       </c>
       <c r="F166">
-        <v>0</v>
+        <v>0.93</v>
       </c>
       <c r="G166">
-        <v>0</v>
+        <v>0.497</v>
       </c>
       <c r="H166">
-        <v>0</v>
+        <v>0.414</v>
       </c>
       <c r="I166">
-        <v>0</v>
+        <v>0.443</v>
       </c>
       <c r="J166">
-        <v>0.015</v>
-      </c>
-      <c r="V166" t="s">
-        <v>187</v>
-      </c>
-      <c r="W166">
+        <v>0.387</v>
+      </c>
+      <c r="W166" t="s">
+        <v>188</v>
+      </c>
+      <c r="X166">
         <v>0.01</v>
       </c>
     </row>
-    <row r="167" spans="1:23">
+    <row r="167" spans="1:24">
       <c r="A167" s="2">
         <v>46234</v>
       </c>
       <c r="B167">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C167">
-        <v>0</v>
+        <v>0.994</v>
       </c>
       <c r="D167">
-        <v>0</v>
+        <v>1.013</v>
       </c>
       <c r="E167">
-        <v>0</v>
+        <v>1.503</v>
       </c>
       <c r="F167">
-        <v>0</v>
+        <v>2.097</v>
       </c>
       <c r="G167">
-        <v>0</v>
+        <v>1.444</v>
       </c>
       <c r="H167">
-        <v>0</v>
+        <v>0.786</v>
       </c>
       <c r="I167">
-        <v>0</v>
+        <v>0.888</v>
       </c>
       <c r="J167">
-        <v>0.015</v>
-      </c>
-      <c r="V167" t="s">
-        <v>188</v>
-      </c>
-      <c r="W167">
+        <v>0.737</v>
+      </c>
+      <c r="W167" t="s">
+        <v>189</v>
+      </c>
+      <c r="X167">
         <v>0.01</v>
       </c>
     </row>
-    <row r="168" spans="1:23">
+    <row r="168" spans="1:24">
       <c r="A168" s="2">
         <v>46234</v>
       </c>
       <c r="B168">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C168">
-        <v>0</v>
+        <v>1.729</v>
       </c>
       <c r="D168">
-        <v>0</v>
+        <v>1.858</v>
       </c>
       <c r="E168">
-        <v>0</v>
+        <v>2.327</v>
       </c>
       <c r="F168">
-        <v>0</v>
+        <v>3.079</v>
       </c>
       <c r="G168">
-        <v>0</v>
+        <v>2.386</v>
       </c>
       <c r="H168">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="I168">
-        <v>0</v>
+        <v>1.143</v>
       </c>
       <c r="J168">
-        <v>0.015</v>
-      </c>
-      <c r="V168" t="s">
-        <v>189</v>
-      </c>
-      <c r="W168">
+        <v>1.084</v>
+      </c>
+      <c r="W168" t="s">
+        <v>190</v>
+      </c>
+      <c r="X168">
         <v>0.194</v>
       </c>
     </row>
-    <row r="169" spans="1:23">
+    <row r="169" spans="1:24">
       <c r="A169" s="2">
         <v>46234</v>
       </c>
       <c r="B169">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C169">
-        <v>0</v>
+        <v>2.347</v>
       </c>
       <c r="D169">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="E169">
-        <v>0</v>
+        <v>3.424</v>
       </c>
       <c r="F169">
-        <v>0</v>
+        <v>3.803</v>
       </c>
       <c r="G169">
-        <v>0</v>
+        <v>3.035</v>
       </c>
       <c r="H169">
-        <v>0</v>
+        <v>0.824</v>
       </c>
       <c r="I169">
-        <v>0</v>
+        <v>1.472</v>
       </c>
       <c r="J169">
-        <v>0.015</v>
-      </c>
-      <c r="V169" t="s">
-        <v>190</v>
-      </c>
-      <c r="W169">
+        <v>1.455</v>
+      </c>
+      <c r="W169" t="s">
+        <v>191</v>
+      </c>
+      <c r="X169">
         <v>0.212</v>
       </c>
     </row>
-    <row r="170" spans="1:23">
+    <row r="170" spans="1:24">
       <c r="A170" s="2">
         <v>46234</v>
       </c>
       <c r="B170">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C170">
-        <v>0.043</v>
+        <v>2.688</v>
       </c>
       <c r="D170">
-        <v>0.07099999999999999</v>
+        <v>2.811</v>
       </c>
       <c r="E170">
-        <v>0.066</v>
+        <v>3.782</v>
       </c>
       <c r="F170">
-        <v>0.235</v>
+        <v>4.146</v>
       </c>
       <c r="G170">
-        <v>0.106</v>
+        <v>3.425</v>
       </c>
       <c r="H170">
-        <v>0.079</v>
+        <v>1.217</v>
       </c>
       <c r="I170">
-        <v>0.064</v>
+        <v>1.445</v>
       </c>
       <c r="J170">
-        <v>0.039</v>
-      </c>
-      <c r="V170" t="s">
-        <v>191</v>
-      </c>
-      <c r="W170">
+        <v>1.547</v>
+      </c>
+      <c r="W170" t="s">
+        <v>192</v>
+      </c>
+      <c r="X170">
         <v>1.081</v>
       </c>
     </row>

--- a/Forecast.xlsx
+++ b/Forecast.xlsx
@@ -88,511 +88,511 @@
     <t>Prediction_3D_Steel</t>
   </si>
   <si>
-    <t>24.07.202612</t>
-  </si>
-  <si>
-    <t>24.07.202613</t>
-  </si>
-  <si>
-    <t>24.07.202614</t>
-  </si>
-  <si>
-    <t>24.07.202615</t>
-  </si>
-  <si>
-    <t>24.07.202616</t>
-  </si>
-  <si>
-    <t>24.07.202617</t>
-  </si>
-  <si>
-    <t>24.07.202618</t>
-  </si>
-  <si>
-    <t>24.07.202619</t>
-  </si>
-  <si>
-    <t>24.07.202620</t>
-  </si>
-  <si>
-    <t>24.07.202621</t>
-  </si>
-  <si>
-    <t>24.07.202622</t>
-  </si>
-  <si>
-    <t>24.07.202623</t>
-  </si>
-  <si>
-    <t>24.07.202624</t>
-  </si>
-  <si>
-    <t>25.07.20261</t>
-  </si>
-  <si>
-    <t>25.07.20262</t>
-  </si>
-  <si>
-    <t>25.07.20263</t>
-  </si>
-  <si>
-    <t>25.07.20264</t>
-  </si>
-  <si>
-    <t>25.07.20265</t>
-  </si>
-  <si>
-    <t>25.07.20266</t>
-  </si>
-  <si>
-    <t>25.07.20267</t>
-  </si>
-  <si>
-    <t>25.07.20268</t>
-  </si>
-  <si>
-    <t>25.07.20269</t>
-  </si>
-  <si>
-    <t>25.07.202610</t>
-  </si>
-  <si>
-    <t>25.07.202611</t>
-  </si>
-  <si>
-    <t>25.07.202612</t>
-  </si>
-  <si>
-    <t>25.07.202613</t>
-  </si>
-  <si>
-    <t>25.07.202614</t>
-  </si>
-  <si>
-    <t>25.07.202615</t>
-  </si>
-  <si>
-    <t>25.07.202616</t>
-  </si>
-  <si>
-    <t>25.07.202617</t>
-  </si>
-  <si>
-    <t>25.07.202618</t>
-  </si>
-  <si>
-    <t>25.07.202619</t>
-  </si>
-  <si>
-    <t>25.07.202620</t>
-  </si>
-  <si>
-    <t>25.07.202621</t>
-  </si>
-  <si>
-    <t>25.07.202622</t>
-  </si>
-  <si>
-    <t>25.07.202623</t>
-  </si>
-  <si>
-    <t>25.07.202624</t>
-  </si>
-  <si>
-    <t>26.07.20261</t>
-  </si>
-  <si>
-    <t>26.07.20262</t>
-  </si>
-  <si>
-    <t>26.07.20263</t>
-  </si>
-  <si>
-    <t>26.07.20264</t>
-  </si>
-  <si>
-    <t>26.07.20265</t>
-  </si>
-  <si>
-    <t>26.07.20266</t>
-  </si>
-  <si>
-    <t>26.07.20267</t>
-  </si>
-  <si>
-    <t>26.07.20268</t>
-  </si>
-  <si>
-    <t>26.07.20269</t>
-  </si>
-  <si>
-    <t>26.07.202610</t>
-  </si>
-  <si>
-    <t>26.07.202611</t>
-  </si>
-  <si>
-    <t>26.07.202612</t>
-  </si>
-  <si>
-    <t>26.07.202613</t>
-  </si>
-  <si>
-    <t>26.07.202614</t>
-  </si>
-  <si>
-    <t>26.07.202615</t>
-  </si>
-  <si>
-    <t>26.07.202616</t>
-  </si>
-  <si>
-    <t>26.07.202617</t>
-  </si>
-  <si>
-    <t>26.07.202618</t>
-  </si>
-  <si>
-    <t>26.07.202619</t>
-  </si>
-  <si>
-    <t>26.07.202620</t>
-  </si>
-  <si>
-    <t>26.07.202621</t>
-  </si>
-  <si>
-    <t>26.07.202622</t>
-  </si>
-  <si>
-    <t>26.07.202623</t>
-  </si>
-  <si>
-    <t>26.07.202624</t>
-  </si>
-  <si>
-    <t>27.07.20261</t>
-  </si>
-  <si>
-    <t>27.07.20262</t>
-  </si>
-  <si>
-    <t>27.07.20263</t>
-  </si>
-  <si>
-    <t>27.07.20264</t>
-  </si>
-  <si>
-    <t>27.07.20265</t>
-  </si>
-  <si>
-    <t>27.07.20266</t>
-  </si>
-  <si>
-    <t>27.07.20267</t>
-  </si>
-  <si>
-    <t>27.07.20268</t>
-  </si>
-  <si>
-    <t>27.07.20269</t>
-  </si>
-  <si>
-    <t>27.07.202610</t>
-  </si>
-  <si>
-    <t>27.07.202611</t>
-  </si>
-  <si>
-    <t>27.07.202612</t>
-  </si>
-  <si>
-    <t>27.07.202613</t>
-  </si>
-  <si>
-    <t>27.07.202614</t>
-  </si>
-  <si>
-    <t>27.07.202615</t>
-  </si>
-  <si>
-    <t>27.07.202616</t>
-  </si>
-  <si>
-    <t>27.07.202617</t>
-  </si>
-  <si>
-    <t>27.07.202618</t>
-  </si>
-  <si>
-    <t>27.07.202619</t>
-  </si>
-  <si>
-    <t>27.07.202620</t>
-  </si>
-  <si>
-    <t>27.07.202621</t>
-  </si>
-  <si>
-    <t>27.07.202622</t>
-  </si>
-  <si>
-    <t>27.07.202623</t>
-  </si>
-  <si>
-    <t>27.07.202624</t>
-  </si>
-  <si>
-    <t>28.07.20261</t>
-  </si>
-  <si>
-    <t>28.07.20262</t>
-  </si>
-  <si>
-    <t>28.07.20263</t>
-  </si>
-  <si>
-    <t>28.07.20264</t>
-  </si>
-  <si>
-    <t>28.07.20265</t>
-  </si>
-  <si>
-    <t>28.07.20266</t>
-  </si>
-  <si>
-    <t>28.07.20267</t>
-  </si>
-  <si>
-    <t>28.07.20268</t>
-  </si>
-  <si>
-    <t>28.07.20269</t>
-  </si>
-  <si>
-    <t>28.07.202610</t>
-  </si>
-  <si>
-    <t>28.07.202611</t>
-  </si>
-  <si>
-    <t>28.07.202612</t>
-  </si>
-  <si>
-    <t>28.07.202613</t>
-  </si>
-  <si>
-    <t>28.07.202614</t>
-  </si>
-  <si>
-    <t>28.07.202615</t>
-  </si>
-  <si>
-    <t>28.07.202616</t>
-  </si>
-  <si>
-    <t>28.07.202617</t>
-  </si>
-  <si>
-    <t>28.07.202618</t>
-  </si>
-  <si>
-    <t>28.07.202619</t>
-  </si>
-  <si>
-    <t>28.07.202620</t>
-  </si>
-  <si>
-    <t>28.07.202621</t>
-  </si>
-  <si>
-    <t>28.07.202622</t>
-  </si>
-  <si>
-    <t>28.07.202623</t>
-  </si>
-  <si>
-    <t>28.07.202624</t>
-  </si>
-  <si>
-    <t>29.07.20261</t>
-  </si>
-  <si>
-    <t>29.07.20262</t>
-  </si>
-  <si>
-    <t>29.07.20263</t>
-  </si>
-  <si>
-    <t>29.07.20264</t>
-  </si>
-  <si>
-    <t>29.07.20265</t>
-  </si>
-  <si>
-    <t>29.07.20266</t>
-  </si>
-  <si>
-    <t>29.07.20267</t>
-  </si>
-  <si>
-    <t>29.07.20268</t>
-  </si>
-  <si>
-    <t>29.07.20269</t>
-  </si>
-  <si>
-    <t>29.07.202610</t>
-  </si>
-  <si>
-    <t>29.07.202611</t>
-  </si>
-  <si>
-    <t>29.07.202612</t>
-  </si>
-  <si>
-    <t>29.07.202613</t>
-  </si>
-  <si>
-    <t>29.07.202614</t>
-  </si>
-  <si>
-    <t>29.07.202615</t>
-  </si>
-  <si>
-    <t>29.07.202616</t>
-  </si>
-  <si>
-    <t>29.07.202617</t>
-  </si>
-  <si>
-    <t>29.07.202618</t>
-  </si>
-  <si>
-    <t>29.07.202619</t>
-  </si>
-  <si>
-    <t>29.07.202620</t>
-  </si>
-  <si>
-    <t>29.07.202621</t>
-  </si>
-  <si>
-    <t>29.07.202622</t>
-  </si>
-  <si>
-    <t>29.07.202623</t>
-  </si>
-  <si>
-    <t>29.07.202624</t>
-  </si>
-  <si>
-    <t>30.07.20261</t>
-  </si>
-  <si>
-    <t>30.07.20262</t>
-  </si>
-  <si>
-    <t>30.07.20263</t>
-  </si>
-  <si>
-    <t>30.07.20264</t>
-  </si>
-  <si>
-    <t>30.07.20265</t>
-  </si>
-  <si>
-    <t>30.07.20266</t>
-  </si>
-  <si>
-    <t>30.07.20267</t>
-  </si>
-  <si>
-    <t>30.07.20268</t>
-  </si>
-  <si>
-    <t>30.07.20269</t>
-  </si>
-  <si>
-    <t>30.07.202610</t>
-  </si>
-  <si>
-    <t>30.07.202611</t>
-  </si>
-  <si>
-    <t>30.07.202612</t>
-  </si>
-  <si>
-    <t>30.07.202613</t>
-  </si>
-  <si>
-    <t>30.07.202614</t>
-  </si>
-  <si>
-    <t>30.07.202615</t>
-  </si>
-  <si>
-    <t>30.07.202616</t>
-  </si>
-  <si>
-    <t>30.07.202617</t>
-  </si>
-  <si>
-    <t>30.07.202618</t>
-  </si>
-  <si>
-    <t>30.07.202619</t>
-  </si>
-  <si>
-    <t>30.07.202620</t>
-  </si>
-  <si>
-    <t>30.07.202621</t>
-  </si>
-  <si>
-    <t>30.07.202622</t>
-  </si>
-  <si>
-    <t>30.07.202623</t>
-  </si>
-  <si>
-    <t>30.07.202624</t>
-  </si>
-  <si>
-    <t>31.07.20261</t>
-  </si>
-  <si>
-    <t>31.07.20262</t>
-  </si>
-  <si>
-    <t>31.07.20263</t>
-  </si>
-  <si>
-    <t>31.07.20264</t>
-  </si>
-  <si>
-    <t>31.07.20265</t>
-  </si>
-  <si>
-    <t>31.07.20266</t>
-  </si>
-  <si>
-    <t>31.07.20267</t>
-  </si>
-  <si>
-    <t>31.07.20268</t>
-  </si>
-  <si>
-    <t>31.07.20269</t>
-  </si>
-  <si>
-    <t>31.07.202610</t>
-  </si>
-  <si>
-    <t>31.07.202611</t>
-  </si>
-  <si>
-    <t>31.07.202612</t>
+    <t>11.08.202614</t>
+  </si>
+  <si>
+    <t>11.08.202615</t>
+  </si>
+  <si>
+    <t>11.08.202616</t>
+  </si>
+  <si>
+    <t>11.08.202617</t>
+  </si>
+  <si>
+    <t>11.08.202618</t>
+  </si>
+  <si>
+    <t>11.08.202619</t>
+  </si>
+  <si>
+    <t>11.08.202620</t>
+  </si>
+  <si>
+    <t>11.08.202621</t>
+  </si>
+  <si>
+    <t>11.08.202622</t>
+  </si>
+  <si>
+    <t>11.08.202623</t>
+  </si>
+  <si>
+    <t>11.08.202624</t>
+  </si>
+  <si>
+    <t>12.08.20261</t>
+  </si>
+  <si>
+    <t>12.08.20262</t>
+  </si>
+  <si>
+    <t>12.08.20263</t>
+  </si>
+  <si>
+    <t>12.08.20264</t>
+  </si>
+  <si>
+    <t>12.08.20265</t>
+  </si>
+  <si>
+    <t>12.08.20266</t>
+  </si>
+  <si>
+    <t>12.08.20267</t>
+  </si>
+  <si>
+    <t>12.08.20268</t>
+  </si>
+  <si>
+    <t>12.08.20269</t>
+  </si>
+  <si>
+    <t>12.08.202610</t>
+  </si>
+  <si>
+    <t>12.08.202611</t>
+  </si>
+  <si>
+    <t>12.08.202612</t>
+  </si>
+  <si>
+    <t>12.08.202613</t>
+  </si>
+  <si>
+    <t>12.08.202614</t>
+  </si>
+  <si>
+    <t>12.08.202615</t>
+  </si>
+  <si>
+    <t>12.08.202616</t>
+  </si>
+  <si>
+    <t>12.08.202617</t>
+  </si>
+  <si>
+    <t>12.08.202618</t>
+  </si>
+  <si>
+    <t>12.08.202619</t>
+  </si>
+  <si>
+    <t>12.08.202620</t>
+  </si>
+  <si>
+    <t>12.08.202621</t>
+  </si>
+  <si>
+    <t>12.08.202622</t>
+  </si>
+  <si>
+    <t>12.08.202623</t>
+  </si>
+  <si>
+    <t>12.08.202624</t>
+  </si>
+  <si>
+    <t>13.08.20261</t>
+  </si>
+  <si>
+    <t>13.08.20262</t>
+  </si>
+  <si>
+    <t>13.08.20263</t>
+  </si>
+  <si>
+    <t>13.08.20264</t>
+  </si>
+  <si>
+    <t>13.08.20265</t>
+  </si>
+  <si>
+    <t>13.08.20266</t>
+  </si>
+  <si>
+    <t>13.08.20267</t>
+  </si>
+  <si>
+    <t>13.08.20268</t>
+  </si>
+  <si>
+    <t>13.08.20269</t>
+  </si>
+  <si>
+    <t>13.08.202610</t>
+  </si>
+  <si>
+    <t>13.08.202611</t>
+  </si>
+  <si>
+    <t>13.08.202612</t>
+  </si>
+  <si>
+    <t>13.08.202613</t>
+  </si>
+  <si>
+    <t>13.08.202614</t>
+  </si>
+  <si>
+    <t>13.08.202615</t>
+  </si>
+  <si>
+    <t>13.08.202616</t>
+  </si>
+  <si>
+    <t>13.08.202617</t>
+  </si>
+  <si>
+    <t>13.08.202618</t>
+  </si>
+  <si>
+    <t>13.08.202619</t>
+  </si>
+  <si>
+    <t>13.08.202620</t>
+  </si>
+  <si>
+    <t>13.08.202621</t>
+  </si>
+  <si>
+    <t>13.08.202622</t>
+  </si>
+  <si>
+    <t>13.08.202623</t>
+  </si>
+  <si>
+    <t>13.08.202624</t>
+  </si>
+  <si>
+    <t>14.08.20261</t>
+  </si>
+  <si>
+    <t>14.08.20262</t>
+  </si>
+  <si>
+    <t>14.08.20263</t>
+  </si>
+  <si>
+    <t>14.08.20264</t>
+  </si>
+  <si>
+    <t>14.08.20265</t>
+  </si>
+  <si>
+    <t>14.08.20266</t>
+  </si>
+  <si>
+    <t>14.08.20267</t>
+  </si>
+  <si>
+    <t>14.08.20268</t>
+  </si>
+  <si>
+    <t>14.08.20269</t>
+  </si>
+  <si>
+    <t>14.08.202610</t>
+  </si>
+  <si>
+    <t>14.08.202611</t>
+  </si>
+  <si>
+    <t>14.08.202612</t>
+  </si>
+  <si>
+    <t>14.08.202613</t>
+  </si>
+  <si>
+    <t>14.08.202614</t>
+  </si>
+  <si>
+    <t>14.08.202615</t>
+  </si>
+  <si>
+    <t>14.08.202616</t>
+  </si>
+  <si>
+    <t>14.08.202617</t>
+  </si>
+  <si>
+    <t>14.08.202618</t>
+  </si>
+  <si>
+    <t>14.08.202619</t>
+  </si>
+  <si>
+    <t>14.08.202620</t>
+  </si>
+  <si>
+    <t>14.08.202621</t>
+  </si>
+  <si>
+    <t>14.08.202622</t>
+  </si>
+  <si>
+    <t>14.08.202623</t>
+  </si>
+  <si>
+    <t>14.08.202624</t>
+  </si>
+  <si>
+    <t>15.08.20261</t>
+  </si>
+  <si>
+    <t>15.08.20262</t>
+  </si>
+  <si>
+    <t>15.08.20263</t>
+  </si>
+  <si>
+    <t>15.08.20264</t>
+  </si>
+  <si>
+    <t>15.08.20265</t>
+  </si>
+  <si>
+    <t>15.08.20266</t>
+  </si>
+  <si>
+    <t>15.08.20267</t>
+  </si>
+  <si>
+    <t>15.08.20268</t>
+  </si>
+  <si>
+    <t>15.08.20269</t>
+  </si>
+  <si>
+    <t>15.08.202610</t>
+  </si>
+  <si>
+    <t>15.08.202611</t>
+  </si>
+  <si>
+    <t>15.08.202612</t>
+  </si>
+  <si>
+    <t>15.08.202613</t>
+  </si>
+  <si>
+    <t>15.08.202614</t>
+  </si>
+  <si>
+    <t>15.08.202615</t>
+  </si>
+  <si>
+    <t>15.08.202616</t>
+  </si>
+  <si>
+    <t>15.08.202617</t>
+  </si>
+  <si>
+    <t>15.08.202618</t>
+  </si>
+  <si>
+    <t>15.08.202619</t>
+  </si>
+  <si>
+    <t>15.08.202620</t>
+  </si>
+  <si>
+    <t>15.08.202621</t>
+  </si>
+  <si>
+    <t>15.08.202622</t>
+  </si>
+  <si>
+    <t>15.08.202623</t>
+  </si>
+  <si>
+    <t>15.08.202624</t>
+  </si>
+  <si>
+    <t>16.08.20261</t>
+  </si>
+  <si>
+    <t>16.08.20262</t>
+  </si>
+  <si>
+    <t>16.08.20263</t>
+  </si>
+  <si>
+    <t>16.08.20264</t>
+  </si>
+  <si>
+    <t>16.08.20265</t>
+  </si>
+  <si>
+    <t>16.08.20266</t>
+  </si>
+  <si>
+    <t>16.08.20267</t>
+  </si>
+  <si>
+    <t>16.08.20268</t>
+  </si>
+  <si>
+    <t>16.08.20269</t>
+  </si>
+  <si>
+    <t>16.08.202610</t>
+  </si>
+  <si>
+    <t>16.08.202611</t>
+  </si>
+  <si>
+    <t>16.08.202612</t>
+  </si>
+  <si>
+    <t>16.08.202613</t>
+  </si>
+  <si>
+    <t>16.08.202614</t>
+  </si>
+  <si>
+    <t>16.08.202615</t>
+  </si>
+  <si>
+    <t>16.08.202616</t>
+  </si>
+  <si>
+    <t>16.08.202617</t>
+  </si>
+  <si>
+    <t>16.08.202618</t>
+  </si>
+  <si>
+    <t>16.08.202619</t>
+  </si>
+  <si>
+    <t>16.08.202620</t>
+  </si>
+  <si>
+    <t>16.08.202621</t>
+  </si>
+  <si>
+    <t>16.08.202622</t>
+  </si>
+  <si>
+    <t>16.08.202623</t>
+  </si>
+  <si>
+    <t>16.08.202624</t>
+  </si>
+  <si>
+    <t>17.08.20261</t>
+  </si>
+  <si>
+    <t>17.08.20262</t>
+  </si>
+  <si>
+    <t>17.08.20263</t>
+  </si>
+  <si>
+    <t>17.08.20264</t>
+  </si>
+  <si>
+    <t>17.08.20265</t>
+  </si>
+  <si>
+    <t>17.08.20266</t>
+  </si>
+  <si>
+    <t>17.08.20267</t>
+  </si>
+  <si>
+    <t>17.08.20268</t>
+  </si>
+  <si>
+    <t>17.08.20269</t>
+  </si>
+  <si>
+    <t>17.08.202610</t>
+  </si>
+  <si>
+    <t>17.08.202611</t>
+  </si>
+  <si>
+    <t>17.08.202612</t>
+  </si>
+  <si>
+    <t>17.08.202613</t>
+  </si>
+  <si>
+    <t>17.08.202614</t>
+  </si>
+  <si>
+    <t>17.08.202615</t>
+  </si>
+  <si>
+    <t>17.08.202616</t>
+  </si>
+  <si>
+    <t>17.08.202617</t>
+  </si>
+  <si>
+    <t>17.08.202618</t>
+  </si>
+  <si>
+    <t>17.08.202619</t>
+  </si>
+  <si>
+    <t>17.08.202620</t>
+  </si>
+  <si>
+    <t>17.08.202621</t>
+  </si>
+  <si>
+    <t>17.08.202622</t>
+  </si>
+  <si>
+    <t>17.08.202623</t>
+  </si>
+  <si>
+    <t>17.08.202624</t>
+  </si>
+  <si>
+    <t>18.08.20261</t>
+  </si>
+  <si>
+    <t>18.08.20262</t>
+  </si>
+  <si>
+    <t>18.08.20263</t>
+  </si>
+  <si>
+    <t>18.08.20264</t>
+  </si>
+  <si>
+    <t>18.08.20265</t>
+  </si>
+  <si>
+    <t>18.08.20266</t>
+  </si>
+  <si>
+    <t>18.08.20267</t>
+  </si>
+  <si>
+    <t>18.08.20268</t>
+  </si>
+  <si>
+    <t>18.08.20269</t>
+  </si>
+  <si>
+    <t>18.08.202610</t>
+  </si>
+  <si>
+    <t>18.08.202611</t>
+  </si>
+  <si>
+    <t>18.08.202612</t>
+  </si>
+  <si>
+    <t>18.08.202613</t>
+  </si>
+  <si>
+    <t>18.08.202614</t>
   </si>
 </sst>
 </file>
@@ -1033,10 +1033,10 @@
     </row>
     <row r="2" spans="1:24">
       <c r="A2" s="2">
-        <v>46227</v>
+        <v>46245</v>
       </c>
       <c r="B2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -1045,7 +1045,7 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>0.105</v>
+        <v>0.104</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -1071,10 +1071,10 @@
     </row>
     <row r="3" spans="1:24">
       <c r="A3" s="2">
-        <v>46227</v>
+        <v>46245</v>
       </c>
       <c r="B3">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -1098,7 +1098,7 @@
         <v>0</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>0.037</v>
       </c>
       <c r="W3" t="s">
         <v>25</v>
@@ -1109,34 +1109,34 @@
     </row>
     <row r="4" spans="1:24">
       <c r="A4" s="2">
-        <v>46227</v>
+        <v>46245</v>
       </c>
       <c r="B4">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C4">
-        <v>2.235</v>
+        <v>2.668</v>
       </c>
       <c r="D4">
-        <v>2.703</v>
+        <v>2.869</v>
       </c>
       <c r="E4">
-        <v>3.668</v>
+        <v>3.841</v>
       </c>
       <c r="F4">
-        <v>0.838</v>
+        <v>2.947</v>
       </c>
       <c r="G4">
-        <v>1.139</v>
+        <v>2.73</v>
       </c>
       <c r="H4">
-        <v>1.085</v>
+        <v>0.833</v>
       </c>
       <c r="I4">
-        <v>1.537</v>
+        <v>1.502</v>
       </c>
       <c r="J4">
-        <v>1.419</v>
+        <v>1.318</v>
       </c>
       <c r="W4" t="s">
         <v>26</v>
@@ -1147,34 +1147,34 @@
     </row>
     <row r="5" spans="1:24">
       <c r="A5" s="2">
-        <v>46227</v>
+        <v>46245</v>
       </c>
       <c r="B5">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C5">
-        <v>1.846</v>
+        <v>2.021</v>
       </c>
       <c r="D5">
-        <v>2.576</v>
+        <v>2.596</v>
       </c>
       <c r="E5">
-        <v>3.629</v>
+        <v>3.389</v>
       </c>
       <c r="F5">
-        <v>2.798</v>
+        <v>2.22</v>
       </c>
       <c r="G5">
-        <v>2.709</v>
+        <v>2.34</v>
       </c>
       <c r="H5">
-        <v>1.068</v>
+        <v>0.927</v>
       </c>
       <c r="I5">
-        <v>1.537</v>
+        <v>1.483</v>
       </c>
       <c r="J5">
-        <v>1.282</v>
+        <v>1.002</v>
       </c>
       <c r="W5" t="s">
         <v>27</v>
@@ -1185,34 +1185,34 @@
     </row>
     <row r="6" spans="1:24">
       <c r="A6" s="2">
-        <v>46227</v>
+        <v>46245</v>
       </c>
       <c r="B6">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C6">
-        <v>1.81</v>
+        <v>1.268</v>
       </c>
       <c r="D6">
-        <v>2.369</v>
+        <v>1.669</v>
       </c>
       <c r="E6">
-        <v>3.578</v>
+        <v>2.38</v>
       </c>
       <c r="F6">
-        <v>2.597</v>
+        <v>1.455</v>
       </c>
       <c r="G6">
-        <v>2.367</v>
+        <v>1.679</v>
       </c>
       <c r="H6">
-        <v>1.117</v>
+        <v>0.848</v>
       </c>
       <c r="I6">
-        <v>1.361</v>
+        <v>1.087</v>
       </c>
       <c r="J6">
-        <v>1.067</v>
+        <v>0.754</v>
       </c>
       <c r="W6" t="s">
         <v>28</v>
@@ -1223,34 +1223,34 @@
     </row>
     <row r="7" spans="1:24">
       <c r="A7" s="2">
-        <v>46227</v>
+        <v>46245</v>
       </c>
       <c r="B7">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C7">
-        <v>1.721</v>
+        <v>0.613</v>
       </c>
       <c r="D7">
-        <v>2.071</v>
+        <v>0.858</v>
       </c>
       <c r="E7">
-        <v>2.762</v>
+        <v>1.388</v>
       </c>
       <c r="F7">
-        <v>2.067</v>
+        <v>0.632</v>
       </c>
       <c r="G7">
-        <v>1.672</v>
+        <v>0.915</v>
       </c>
       <c r="H7">
-        <v>1.148</v>
+        <v>0.627</v>
       </c>
       <c r="I7">
-        <v>1.068</v>
+        <v>0.542</v>
       </c>
       <c r="J7">
-        <v>0.723</v>
+        <v>0.301</v>
       </c>
       <c r="W7" t="s">
         <v>29</v>
@@ -1261,34 +1261,34 @@
     </row>
     <row r="8" spans="1:24">
       <c r="A8" s="2">
-        <v>46227</v>
+        <v>46245</v>
       </c>
       <c r="B8">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C8">
-        <v>1.186</v>
+        <v>0.182</v>
       </c>
       <c r="D8">
-        <v>1.452</v>
+        <v>0.239</v>
       </c>
       <c r="E8">
-        <v>2.108</v>
+        <v>0.483</v>
       </c>
       <c r="F8">
-        <v>1.069</v>
+        <v>0.191</v>
       </c>
       <c r="G8">
-        <v>0.856</v>
+        <v>0.268</v>
       </c>
       <c r="H8">
-        <v>0.736</v>
+        <v>0.258</v>
       </c>
       <c r="I8">
-        <v>0.754</v>
+        <v>0.201</v>
       </c>
       <c r="J8">
-        <v>0.34</v>
+        <v>0.096</v>
       </c>
       <c r="W8" t="s">
         <v>30</v>
@@ -1299,34 +1299,34 @@
     </row>
     <row r="9" spans="1:24">
       <c r="A9" s="2">
-        <v>46227</v>
+        <v>46245</v>
       </c>
       <c r="B9">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C9">
-        <v>0.593</v>
+        <v>0.021</v>
       </c>
       <c r="D9">
-        <v>0.805</v>
+        <v>0.022</v>
       </c>
       <c r="E9">
-        <v>1.471</v>
+        <v>0.048</v>
       </c>
       <c r="F9">
-        <v>0.517</v>
+        <v>0.011</v>
       </c>
       <c r="G9">
-        <v>0.328</v>
+        <v>0.014</v>
       </c>
       <c r="H9">
-        <v>0.448</v>
+        <v>0.012</v>
       </c>
       <c r="I9">
-        <v>0.535</v>
+        <v>0</v>
       </c>
       <c r="J9">
-        <v>0.215</v>
+        <v>0</v>
       </c>
       <c r="W9" t="s">
         <v>31</v>
@@ -1337,34 +1337,34 @@
     </row>
     <row r="10" spans="1:24">
       <c r="A10" s="2">
-        <v>46227</v>
+        <v>46245</v>
       </c>
       <c r="B10">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C10">
-        <v>0.302</v>
+        <v>0</v>
       </c>
       <c r="D10">
-        <v>0.296</v>
+        <v>0</v>
       </c>
       <c r="E10">
-        <v>0.641</v>
+        <v>0</v>
       </c>
       <c r="F10">
-        <v>0.129</v>
+        <v>0</v>
       </c>
       <c r="G10">
-        <v>0.133</v>
+        <v>0</v>
       </c>
       <c r="H10">
-        <v>0.172</v>
+        <v>0</v>
       </c>
       <c r="I10">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="J10">
-        <v>0.103</v>
+        <v>0</v>
       </c>
       <c r="W10" t="s">
         <v>32</v>
@@ -1375,34 +1375,34 @@
     </row>
     <row r="11" spans="1:24">
       <c r="A11" s="2">
-        <v>46227</v>
+        <v>46245</v>
       </c>
       <c r="B11">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C11">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="D11">
-        <v>0.077</v>
+        <v>0</v>
       </c>
       <c r="E11">
-        <v>0.109</v>
+        <v>0</v>
       </c>
       <c r="F11">
-        <v>0.012</v>
+        <v>0</v>
       </c>
       <c r="G11">
-        <v>0.016</v>
+        <v>0</v>
       </c>
       <c r="H11">
-        <v>0.016</v>
+        <v>0</v>
       </c>
       <c r="I11">
-        <v>0.021</v>
+        <v>0</v>
       </c>
       <c r="J11">
-        <v>0.025</v>
+        <v>0</v>
       </c>
       <c r="W11" t="s">
         <v>33</v>
@@ -1413,10 +1413,10 @@
     </row>
     <row r="12" spans="1:24">
       <c r="A12" s="2">
-        <v>46227</v>
+        <v>46245</v>
       </c>
       <c r="B12">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -1440,7 +1440,7 @@
         <v>0</v>
       </c>
       <c r="J12">
-        <v>0.013</v>
+        <v>0</v>
       </c>
       <c r="W12" t="s">
         <v>34</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="13" spans="1:24">
       <c r="A13" s="2">
-        <v>46227</v>
+        <v>46246</v>
       </c>
       <c r="B13">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -1463,7 +1463,7 @@
         <v>0</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -1478,7 +1478,7 @@
         <v>0</v>
       </c>
       <c r="J13">
-        <v>0.013</v>
+        <v>0.014</v>
       </c>
       <c r="W13" t="s">
         <v>35</v>
@@ -1489,10 +1489,10 @@
     </row>
     <row r="14" spans="1:24">
       <c r="A14" s="2">
-        <v>46227</v>
+        <v>46246</v>
       </c>
       <c r="B14">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -1501,7 +1501,7 @@
         <v>0</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>0.015</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -1516,7 +1516,7 @@
         <v>0</v>
       </c>
       <c r="J14">
-        <v>0.013</v>
+        <v>0</v>
       </c>
       <c r="W14" t="s">
         <v>36</v>
@@ -1527,10 +1527,10 @@
     </row>
     <row r="15" spans="1:24">
       <c r="A15" s="2">
-        <v>46228</v>
+        <v>46246</v>
       </c>
       <c r="B15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -1539,7 +1539,7 @@
         <v>0</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>0.015</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -1554,7 +1554,7 @@
         <v>0</v>
       </c>
       <c r="J15">
-        <v>0.014</v>
+        <v>0</v>
       </c>
       <c r="W15" t="s">
         <v>37</v>
@@ -1565,10 +1565,10 @@
     </row>
     <row r="16" spans="1:24">
       <c r="A16" s="2">
-        <v>46228</v>
+        <v>46246</v>
       </c>
       <c r="B16">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -1577,7 +1577,7 @@
         <v>0</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>0.024</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -1603,10 +1603,10 @@
     </row>
     <row r="17" spans="1:24">
       <c r="A17" s="2">
-        <v>46228</v>
+        <v>46246</v>
       </c>
       <c r="B17">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -1615,7 +1615,7 @@
         <v>0</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>0.077</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -1641,10 +1641,10 @@
     </row>
     <row r="18" spans="1:24">
       <c r="A18" s="2">
-        <v>46228</v>
+        <v>46246</v>
       </c>
       <c r="B18">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -1653,7 +1653,7 @@
         <v>0</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>0.066</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -1668,7 +1668,7 @@
         <v>0</v>
       </c>
       <c r="J18">
-        <v>0.014</v>
+        <v>0.02</v>
       </c>
       <c r="W18" t="s">
         <v>40</v>
@@ -1679,34 +1679,34 @@
     </row>
     <row r="19" spans="1:24">
       <c r="A19" s="2">
-        <v>46228</v>
+        <v>46246</v>
       </c>
       <c r="B19">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>0.018</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>0.024</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>0.068</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>0.147</v>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>0.064</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>0.044</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>0.044</v>
       </c>
       <c r="J19">
-        <v>0.014</v>
+        <v>0.03</v>
       </c>
       <c r="W19" t="s">
         <v>41</v>
@@ -1717,34 +1717,34 @@
     </row>
     <row r="20" spans="1:24">
       <c r="A20" s="2">
-        <v>46228</v>
+        <v>46246</v>
       </c>
       <c r="B20">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>0.256</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>0.355</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>0.476</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>0.776</v>
       </c>
       <c r="G20">
-        <v>0</v>
+        <v>0.525</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>0.368</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>0.388</v>
       </c>
       <c r="J20">
-        <v>0.014</v>
+        <v>0.308</v>
       </c>
       <c r="W20" t="s">
         <v>42</v>
@@ -1755,34 +1755,34 @@
     </row>
     <row r="21" spans="1:24">
       <c r="A21" s="2">
-        <v>46228</v>
+        <v>46246</v>
       </c>
       <c r="B21">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C21">
-        <v>0.055</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="D21">
-        <v>0.08400000000000001</v>
+        <v>0.903</v>
       </c>
       <c r="E21">
-        <v>0.112</v>
+        <v>1.424</v>
       </c>
       <c r="F21">
-        <v>0.18</v>
+        <v>1.958</v>
       </c>
       <c r="G21">
-        <v>0.08699999999999999</v>
+        <v>1.403</v>
       </c>
       <c r="H21">
-        <v>0.079</v>
+        <v>0.727</v>
       </c>
       <c r="I21">
-        <v>0.08400000000000001</v>
+        <v>0.787</v>
       </c>
       <c r="J21">
-        <v>0.062</v>
+        <v>0.842</v>
       </c>
       <c r="W21" t="s">
         <v>43</v>
@@ -1793,34 +1793,34 @@
     </row>
     <row r="22" spans="1:24">
       <c r="A22" s="2">
-        <v>46228</v>
+        <v>46246</v>
       </c>
       <c r="B22">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C22">
-        <v>0.371</v>
+        <v>1.686</v>
       </c>
       <c r="D22">
-        <v>0.401</v>
+        <v>1.752</v>
       </c>
       <c r="E22">
-        <v>0.648</v>
+        <v>2.482</v>
       </c>
       <c r="F22">
-        <v>0.794</v>
+        <v>2.881</v>
       </c>
       <c r="G22">
-        <v>0.357</v>
+        <v>2.323</v>
       </c>
       <c r="H22">
-        <v>0.385</v>
+        <v>1.071</v>
       </c>
       <c r="I22">
-        <v>0.477</v>
+        <v>1.047</v>
       </c>
       <c r="J22">
-        <v>0.349</v>
+        <v>1.017</v>
       </c>
       <c r="W22" t="s">
         <v>44</v>
@@ -1831,34 +1831,34 @@
     </row>
     <row r="23" spans="1:24">
       <c r="A23" s="2">
-        <v>46228</v>
+        <v>46246</v>
       </c>
       <c r="B23">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C23">
-        <v>1.094</v>
+        <v>2.328</v>
       </c>
       <c r="D23">
-        <v>1.12</v>
+        <v>2.388</v>
       </c>
       <c r="E23">
-        <v>1.687</v>
+        <v>3.428</v>
       </c>
       <c r="F23">
-        <v>1.885</v>
+        <v>3.609</v>
       </c>
       <c r="G23">
-        <v>1.324</v>
+        <v>2.896</v>
       </c>
       <c r="H23">
-        <v>0.827</v>
+        <v>1.303</v>
       </c>
       <c r="I23">
-        <v>0.888</v>
+        <v>1.457</v>
       </c>
       <c r="J23">
-        <v>0.847</v>
+        <v>1.331</v>
       </c>
       <c r="W23" t="s">
         <v>45</v>
@@ -1869,34 +1869,34 @@
     </row>
     <row r="24" spans="1:24">
       <c r="A24" s="2">
-        <v>46228</v>
+        <v>46246</v>
       </c>
       <c r="B24">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C24">
-        <v>1.863</v>
+        <v>2.829</v>
       </c>
       <c r="D24">
-        <v>2.086</v>
+        <v>2.853</v>
       </c>
       <c r="E24">
-        <v>2.964</v>
+        <v>3.81</v>
       </c>
       <c r="F24">
-        <v>2.698</v>
+        <v>4.043</v>
       </c>
       <c r="G24">
-        <v>2.053</v>
+        <v>3.413</v>
       </c>
       <c r="H24">
-        <v>1.206</v>
+        <v>1.462</v>
       </c>
       <c r="I24">
-        <v>1.222</v>
+        <v>1.445</v>
       </c>
       <c r="J24">
-        <v>1.021</v>
+        <v>1.536</v>
       </c>
       <c r="W24" t="s">
         <v>46</v>
@@ -1907,34 +1907,34 @@
     </row>
     <row r="25" spans="1:24">
       <c r="A25" s="2">
-        <v>46228</v>
+        <v>46246</v>
       </c>
       <c r="B25">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C25">
-        <v>2.277</v>
+        <v>3.033</v>
       </c>
       <c r="D25">
-        <v>2.574</v>
+        <v>3.173</v>
       </c>
       <c r="E25">
-        <v>3.751</v>
+        <v>3.7</v>
       </c>
       <c r="F25">
-        <v>3.192</v>
+        <v>4.147</v>
       </c>
       <c r="G25">
-        <v>2.697</v>
+        <v>3.552</v>
       </c>
       <c r="H25">
-        <v>1.385</v>
+        <v>1.491</v>
       </c>
       <c r="I25">
-        <v>1.554</v>
+        <v>1.445</v>
       </c>
       <c r="J25">
-        <v>1.096</v>
+        <v>1.611</v>
       </c>
       <c r="W25" t="s">
         <v>47</v>
@@ -1945,34 +1945,34 @@
     </row>
     <row r="26" spans="1:24">
       <c r="A26" s="2">
-        <v>46228</v>
+        <v>46246</v>
       </c>
       <c r="B26">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C26">
-        <v>2.426</v>
+        <v>3.102</v>
       </c>
       <c r="D26">
-        <v>2.799</v>
+        <v>3.033</v>
       </c>
       <c r="E26">
-        <v>3.811</v>
+        <v>3.615</v>
       </c>
       <c r="F26">
-        <v>3.414</v>
+        <v>4.054</v>
       </c>
       <c r="G26">
-        <v>3.017</v>
+        <v>3.552</v>
       </c>
       <c r="H26">
-        <v>1.393</v>
+        <v>0.854</v>
       </c>
       <c r="I26">
-        <v>1.563</v>
+        <v>1.502</v>
       </c>
       <c r="J26">
-        <v>1.352</v>
+        <v>1.482</v>
       </c>
       <c r="W26" t="s">
         <v>48</v>
@@ -1983,34 +1983,34 @@
     </row>
     <row r="27" spans="1:24">
       <c r="A27" s="2">
-        <v>46228</v>
+        <v>46246</v>
       </c>
       <c r="B27">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C27">
-        <v>2.655</v>
+        <v>2.719</v>
       </c>
       <c r="D27">
-        <v>2.972</v>
+        <v>2.79</v>
       </c>
       <c r="E27">
-        <v>3.7</v>
+        <v>3.607</v>
       </c>
       <c r="F27">
-        <v>3.471</v>
+        <v>3.9</v>
       </c>
       <c r="G27">
-        <v>3.073</v>
+        <v>3.413</v>
       </c>
       <c r="H27">
-        <v>0.84</v>
+        <v>0.831</v>
       </c>
       <c r="I27">
-        <v>1.563</v>
+        <v>1.502</v>
       </c>
       <c r="J27">
-        <v>1.374</v>
+        <v>1.334</v>
       </c>
       <c r="W27" t="s">
         <v>49</v>
@@ -2021,34 +2021,34 @@
     </row>
     <row r="28" spans="1:24">
       <c r="A28" s="2">
-        <v>46228</v>
+        <v>46246</v>
       </c>
       <c r="B28">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C28">
-        <v>2.7</v>
+        <v>2.38</v>
       </c>
       <c r="D28">
-        <v>3.19</v>
+        <v>2.674</v>
       </c>
       <c r="E28">
-        <v>3.493</v>
+        <v>3.668</v>
       </c>
       <c r="F28">
-        <v>3.374</v>
+        <v>3.329</v>
       </c>
       <c r="G28">
-        <v>3.105</v>
+        <v>3.097</v>
       </c>
       <c r="H28">
-        <v>0.835</v>
+        <v>0.806</v>
       </c>
       <c r="I28">
-        <v>1.563</v>
+        <v>1.502</v>
       </c>
       <c r="J28">
-        <v>1.345</v>
+        <v>1.222</v>
       </c>
       <c r="W28" t="s">
         <v>50</v>
@@ -2059,34 +2059,34 @@
     </row>
     <row r="29" spans="1:24">
       <c r="A29" s="2">
-        <v>46228</v>
+        <v>46246</v>
       </c>
       <c r="B29">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C29">
-        <v>2.641</v>
+        <v>2.04</v>
       </c>
       <c r="D29">
-        <v>3.018</v>
+        <v>2.382</v>
       </c>
       <c r="E29">
-        <v>3.58</v>
+        <v>3.189</v>
       </c>
       <c r="F29">
-        <v>3.298</v>
+        <v>2.399</v>
       </c>
       <c r="G29">
-        <v>3.019</v>
+        <v>2.525</v>
       </c>
       <c r="H29">
-        <v>0.756</v>
+        <v>0.791</v>
       </c>
       <c r="I29">
-        <v>1.563</v>
+        <v>1.169</v>
       </c>
       <c r="J29">
-        <v>1.349</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="W29" t="s">
         <v>51</v>
@@ -2097,34 +2097,34 @@
     </row>
     <row r="30" spans="1:24">
       <c r="A30" s="2">
-        <v>46228</v>
+        <v>46246</v>
       </c>
       <c r="B30">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C30">
-        <v>2.206</v>
+        <v>1.363</v>
       </c>
       <c r="D30">
-        <v>2.907</v>
+        <v>1.764</v>
       </c>
       <c r="E30">
-        <v>3.429</v>
+        <v>2.22</v>
       </c>
       <c r="F30">
-        <v>2.95</v>
+        <v>1.454</v>
       </c>
       <c r="G30">
-        <v>2.668</v>
+        <v>1.655</v>
       </c>
       <c r="H30">
-        <v>0.792</v>
+        <v>0.649</v>
       </c>
       <c r="I30">
-        <v>1.537</v>
+        <v>0.966</v>
       </c>
       <c r="J30">
-        <v>1.092</v>
+        <v>0.333</v>
       </c>
       <c r="W30" t="s">
         <v>52</v>
@@ -2135,34 +2135,34 @@
     </row>
     <row r="31" spans="1:24">
       <c r="A31" s="2">
-        <v>46228</v>
+        <v>46246</v>
       </c>
       <c r="B31">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C31">
-        <v>1.918</v>
+        <v>0.754</v>
       </c>
       <c r="D31">
-        <v>2.432</v>
+        <v>0.955</v>
       </c>
       <c r="E31">
-        <v>3.137</v>
+        <v>1.234</v>
       </c>
       <c r="F31">
-        <v>2.389</v>
+        <v>0.542</v>
       </c>
       <c r="G31">
-        <v>2.24</v>
+        <v>0.792</v>
       </c>
       <c r="H31">
-        <v>0.863</v>
+        <v>0.455</v>
       </c>
       <c r="I31">
-        <v>1.23</v>
+        <v>0.491</v>
       </c>
       <c r="J31">
-        <v>0.924</v>
+        <v>0.217</v>
       </c>
       <c r="W31" t="s">
         <v>53</v>
@@ -2173,34 +2173,34 @@
     </row>
     <row r="32" spans="1:24">
       <c r="A32" s="2">
-        <v>46228</v>
+        <v>46246</v>
       </c>
       <c r="B32">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C32">
-        <v>1.351</v>
+        <v>0.204</v>
       </c>
       <c r="D32">
-        <v>1.847</v>
+        <v>0.275</v>
       </c>
       <c r="E32">
-        <v>2.536</v>
+        <v>0.472</v>
       </c>
       <c r="F32">
-        <v>1.619</v>
+        <v>0.172</v>
       </c>
       <c r="G32">
-        <v>1.665</v>
+        <v>0.248</v>
       </c>
       <c r="H32">
-        <v>0.911</v>
+        <v>0.227</v>
       </c>
       <c r="I32">
-        <v>0.954</v>
+        <v>0.112</v>
       </c>
       <c r="J32">
-        <v>0.672</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="W32" t="s">
         <v>54</v>
@@ -2211,34 +2211,34 @@
     </row>
     <row r="33" spans="1:24">
       <c r="A33" s="2">
-        <v>46228</v>
+        <v>46246</v>
       </c>
       <c r="B33">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C33">
-        <v>0.757</v>
+        <v>0.021</v>
       </c>
       <c r="D33">
-        <v>0.964</v>
+        <v>0.023</v>
       </c>
       <c r="E33">
-        <v>1.413</v>
+        <v>0.063</v>
       </c>
       <c r="F33">
-        <v>0.701</v>
+        <v>0.011</v>
       </c>
       <c r="G33">
-        <v>0.927</v>
+        <v>0.011</v>
       </c>
       <c r="H33">
-        <v>0.68</v>
+        <v>0</v>
       </c>
       <c r="I33">
-        <v>0.635</v>
+        <v>0</v>
       </c>
       <c r="J33">
-        <v>0.371</v>
+        <v>0</v>
       </c>
       <c r="W33" t="s">
         <v>55</v>
@@ -2249,34 +2249,34 @@
     </row>
     <row r="34" spans="1:24">
       <c r="A34" s="2">
-        <v>46228</v>
+        <v>46246</v>
       </c>
       <c r="B34">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C34">
-        <v>0.262</v>
+        <v>0</v>
       </c>
       <c r="D34">
-        <v>0.324</v>
+        <v>0</v>
       </c>
       <c r="E34">
-        <v>0.672</v>
+        <v>0.061</v>
       </c>
       <c r="F34">
-        <v>0.228</v>
+        <v>0</v>
       </c>
       <c r="G34">
-        <v>0.281</v>
+        <v>0</v>
       </c>
       <c r="H34">
-        <v>0.351</v>
+        <v>0</v>
       </c>
       <c r="I34">
-        <v>0.328</v>
+        <v>0</v>
       </c>
       <c r="J34">
-        <v>0.129</v>
+        <v>0.013</v>
       </c>
       <c r="W34" t="s">
         <v>56</v>
@@ -2287,34 +2287,34 @@
     </row>
     <row r="35" spans="1:24">
       <c r="A35" s="2">
-        <v>46228</v>
+        <v>46246</v>
       </c>
       <c r="B35">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C35">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="D35">
-        <v>0.08799999999999999</v>
+        <v>0</v>
       </c>
       <c r="E35">
-        <v>0.134</v>
+        <v>0.079</v>
       </c>
       <c r="F35">
-        <v>0.038</v>
+        <v>0</v>
       </c>
       <c r="G35">
-        <v>0.061</v>
+        <v>0</v>
       </c>
       <c r="H35">
-        <v>0.053</v>
+        <v>0</v>
       </c>
       <c r="I35">
-        <v>0.034</v>
+        <v>0</v>
       </c>
       <c r="J35">
-        <v>0</v>
+        <v>0.013</v>
       </c>
       <c r="W35" t="s">
         <v>57</v>
@@ -2325,10 +2325,10 @@
     </row>
     <row r="36" spans="1:24">
       <c r="A36" s="2">
-        <v>46228</v>
+        <v>46246</v>
       </c>
       <c r="B36">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C36">
         <v>0</v>
@@ -2337,7 +2337,7 @@
         <v>0</v>
       </c>
       <c r="E36">
-        <v>0.014</v>
+        <v>0.098</v>
       </c>
       <c r="F36">
         <v>0</v>
@@ -2352,7 +2352,7 @@
         <v>0</v>
       </c>
       <c r="J36">
-        <v>0.019</v>
+        <v>0.013</v>
       </c>
       <c r="W36" t="s">
         <v>58</v>
@@ -2363,10 +2363,10 @@
     </row>
     <row r="37" spans="1:24">
       <c r="A37" s="2">
-        <v>46228</v>
+        <v>46247</v>
       </c>
       <c r="B37">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="C37">
         <v>0</v>
@@ -2375,7 +2375,7 @@
         <v>0</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>0.161</v>
       </c>
       <c r="F37">
         <v>0</v>
@@ -2390,7 +2390,7 @@
         <v>0</v>
       </c>
       <c r="J37">
-        <v>0.013</v>
+        <v>0.014</v>
       </c>
       <c r="W37" t="s">
         <v>59</v>
@@ -2401,10 +2401,10 @@
     </row>
     <row r="38" spans="1:24">
       <c r="A38" s="2">
-        <v>46228</v>
+        <v>46247</v>
       </c>
       <c r="B38">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="C38">
         <v>0</v>
@@ -2413,7 +2413,7 @@
         <v>0</v>
       </c>
       <c r="E38">
-        <v>0</v>
+        <v>0.147</v>
       </c>
       <c r="F38">
         <v>0</v>
@@ -2428,7 +2428,7 @@
         <v>0</v>
       </c>
       <c r="J38">
-        <v>0.013</v>
+        <v>0.02</v>
       </c>
       <c r="W38" t="s">
         <v>60</v>
@@ -2439,10 +2439,10 @@
     </row>
     <row r="39" spans="1:24">
       <c r="A39" s="2">
-        <v>46229</v>
+        <v>46247</v>
       </c>
       <c r="B39">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C39">
         <v>0</v>
@@ -2451,7 +2451,7 @@
         <v>0</v>
       </c>
       <c r="E39">
-        <v>0</v>
+        <v>0.128</v>
       </c>
       <c r="F39">
         <v>0</v>
@@ -2466,7 +2466,7 @@
         <v>0</v>
       </c>
       <c r="J39">
-        <v>0.014</v>
+        <v>0.02</v>
       </c>
       <c r="W39" t="s">
         <v>61</v>
@@ -2477,10 +2477,10 @@
     </row>
     <row r="40" spans="1:24">
       <c r="A40" s="2">
-        <v>46229</v>
+        <v>46247</v>
       </c>
       <c r="B40">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C40">
         <v>0</v>
@@ -2489,7 +2489,7 @@
         <v>0</v>
       </c>
       <c r="E40">
-        <v>0</v>
+        <v>0.092</v>
       </c>
       <c r="F40">
         <v>0</v>
@@ -2504,7 +2504,7 @@
         <v>0</v>
       </c>
       <c r="J40">
-        <v>0.014</v>
+        <v>0.02</v>
       </c>
       <c r="W40" t="s">
         <v>62</v>
@@ -2515,10 +2515,10 @@
     </row>
     <row r="41" spans="1:24">
       <c r="A41" s="2">
-        <v>46229</v>
+        <v>46247</v>
       </c>
       <c r="B41">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C41">
         <v>0</v>
@@ -2527,7 +2527,7 @@
         <v>0</v>
       </c>
       <c r="E41">
-        <v>0</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="F41">
         <v>0</v>
@@ -2542,7 +2542,7 @@
         <v>0</v>
       </c>
       <c r="J41">
-        <v>0.014</v>
+        <v>0.02</v>
       </c>
       <c r="W41" t="s">
         <v>63</v>
@@ -2553,10 +2553,10 @@
     </row>
     <row r="42" spans="1:24">
       <c r="A42" s="2">
-        <v>46229</v>
+        <v>46247</v>
       </c>
       <c r="B42">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C42">
         <v>0</v>
@@ -2580,7 +2580,7 @@
         <v>0</v>
       </c>
       <c r="J42">
-        <v>0.014</v>
+        <v>0.02</v>
       </c>
       <c r="W42" t="s">
         <v>64</v>
@@ -2591,34 +2591,34 @@
     </row>
     <row r="43" spans="1:24">
       <c r="A43" s="2">
-        <v>46229</v>
+        <v>46247</v>
       </c>
       <c r="B43">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C43">
-        <v>0</v>
+        <v>0.024</v>
       </c>
       <c r="D43">
-        <v>0</v>
+        <v>0.023</v>
       </c>
       <c r="E43">
-        <v>0</v>
+        <v>0.016</v>
       </c>
       <c r="F43">
-        <v>0</v>
+        <v>0.098</v>
       </c>
       <c r="G43">
-        <v>0</v>
+        <v>0.046</v>
       </c>
       <c r="H43">
-        <v>0</v>
+        <v>0.012</v>
       </c>
       <c r="I43">
-        <v>0</v>
+        <v>0.021</v>
       </c>
       <c r="J43">
-        <v>0.014</v>
+        <v>0.044</v>
       </c>
       <c r="W43" t="s">
         <v>65</v>
@@ -2629,34 +2629,34 @@
     </row>
     <row r="44" spans="1:24">
       <c r="A44" s="2">
-        <v>46229</v>
+        <v>46247</v>
       </c>
       <c r="B44">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C44">
-        <v>0</v>
+        <v>0.303</v>
       </c>
       <c r="D44">
-        <v>0</v>
+        <v>0.318</v>
       </c>
       <c r="E44">
-        <v>0</v>
+        <v>0.197</v>
       </c>
       <c r="F44">
-        <v>0</v>
+        <v>0.634</v>
       </c>
       <c r="G44">
-        <v>0</v>
+        <v>0.319</v>
       </c>
       <c r="H44">
-        <v>0</v>
+        <v>0.145</v>
       </c>
       <c r="I44">
-        <v>0</v>
+        <v>0.191</v>
       </c>
       <c r="J44">
-        <v>0.014</v>
+        <v>0.194</v>
       </c>
       <c r="W44" t="s">
         <v>66</v>
@@ -2667,34 +2667,34 @@
     </row>
     <row r="45" spans="1:24">
       <c r="A45" s="2">
-        <v>46229</v>
+        <v>46247</v>
       </c>
       <c r="B45">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C45">
-        <v>0.056</v>
+        <v>1.001</v>
       </c>
       <c r="D45">
-        <v>0.08500000000000001</v>
+        <v>0.999</v>
       </c>
       <c r="E45">
-        <v>0.099</v>
+        <v>0.523</v>
       </c>
       <c r="F45">
-        <v>0.281</v>
+        <v>1.401</v>
       </c>
       <c r="G45">
-        <v>0.13</v>
+        <v>0.789</v>
       </c>
       <c r="H45">
-        <v>0.106</v>
+        <v>0.393</v>
       </c>
       <c r="I45">
-        <v>0.112</v>
+        <v>0.513</v>
       </c>
       <c r="J45">
-        <v>0.075</v>
+        <v>0.622</v>
       </c>
       <c r="W45" t="s">
         <v>67</v>
@@ -2705,34 +2705,34 @@
     </row>
     <row r="46" spans="1:24">
       <c r="A46" s="2">
-        <v>46229</v>
+        <v>46247</v>
       </c>
       <c r="B46">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C46">
-        <v>0.356</v>
+        <v>1.634</v>
       </c>
       <c r="D46">
-        <v>0.421</v>
+        <v>1.696</v>
       </c>
       <c r="E46">
-        <v>0.659</v>
+        <v>0.958</v>
       </c>
       <c r="F46">
-        <v>1.001</v>
+        <v>2.008</v>
       </c>
       <c r="G46">
-        <v>0.594</v>
+        <v>1.636</v>
       </c>
       <c r="H46">
-        <v>0.623</v>
+        <v>0.649</v>
       </c>
       <c r="I46">
-        <v>0.526</v>
+        <v>0.578</v>
       </c>
       <c r="J46">
-        <v>0.481</v>
+        <v>0.944</v>
       </c>
       <c r="W46" t="s">
         <v>68</v>
@@ -2743,34 +2743,34 @@
     </row>
     <row r="47" spans="1:24">
       <c r="A47" s="2">
-        <v>46229</v>
+        <v>46247</v>
       </c>
       <c r="B47">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C47">
-        <v>1.113</v>
+        <v>2.017</v>
       </c>
       <c r="D47">
-        <v>1.158</v>
+        <v>2.348</v>
       </c>
       <c r="E47">
-        <v>1.74</v>
+        <v>1.314</v>
       </c>
       <c r="F47">
-        <v>2.189</v>
+        <v>2.329</v>
       </c>
       <c r="G47">
-        <v>1.58</v>
+        <v>1.879</v>
       </c>
       <c r="H47">
-        <v>1.156</v>
+        <v>0.903</v>
       </c>
       <c r="I47">
-        <v>0.971</v>
+        <v>0.882</v>
       </c>
       <c r="J47">
-        <v>0.83</v>
+        <v>1.132</v>
       </c>
       <c r="W47" t="s">
         <v>69</v>
@@ -2781,34 +2781,34 @@
     </row>
     <row r="48" spans="1:24">
       <c r="A48" s="2">
-        <v>46229</v>
+        <v>46247</v>
       </c>
       <c r="B48">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C48">
-        <v>1.864</v>
+        <v>2.325</v>
       </c>
       <c r="D48">
-        <v>2.092</v>
+        <v>2.801</v>
       </c>
       <c r="E48">
-        <v>2.725</v>
+        <v>1.581</v>
       </c>
       <c r="F48">
-        <v>3.143</v>
+        <v>2.802</v>
       </c>
       <c r="G48">
-        <v>2.42</v>
+        <v>2.352</v>
       </c>
       <c r="H48">
-        <v>1.384</v>
+        <v>1.201</v>
       </c>
       <c r="I48">
-        <v>1.418</v>
+        <v>1.396</v>
       </c>
       <c r="J48">
-        <v>1.118</v>
+        <v>1.243</v>
       </c>
       <c r="W48" t="s">
         <v>70</v>
@@ -2819,34 +2819,34 @@
     </row>
     <row r="49" spans="1:24">
       <c r="A49" s="2">
-        <v>46229</v>
+        <v>46247</v>
       </c>
       <c r="B49">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C49">
-        <v>2.487</v>
+        <v>2.607</v>
       </c>
       <c r="D49">
-        <v>2.873</v>
+        <v>3.074</v>
       </c>
       <c r="E49">
-        <v>3.713</v>
+        <v>1.592</v>
       </c>
       <c r="F49">
-        <v>3.679</v>
+        <v>2.826</v>
       </c>
       <c r="G49">
-        <v>2.952</v>
+        <v>2.654</v>
       </c>
       <c r="H49">
-        <v>1.171</v>
+        <v>1.329</v>
       </c>
       <c r="I49">
-        <v>1.554</v>
+        <v>1.396</v>
       </c>
       <c r="J49">
-        <v>1.487</v>
+        <v>1.422</v>
       </c>
       <c r="W49" t="s">
         <v>71</v>
@@ -2857,34 +2857,34 @@
     </row>
     <row r="50" spans="1:24">
       <c r="A50" s="2">
-        <v>46229</v>
+        <v>46247</v>
       </c>
       <c r="B50">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C50">
-        <v>2.846</v>
+        <v>2.584</v>
       </c>
       <c r="D50">
-        <v>3.189</v>
+        <v>3.113</v>
       </c>
       <c r="E50">
-        <v>3.812</v>
+        <v>1.756</v>
       </c>
       <c r="F50">
-        <v>3.82</v>
+        <v>3.088</v>
       </c>
       <c r="G50">
-        <v>3.206</v>
+        <v>2.779</v>
       </c>
       <c r="H50">
-        <v>0.855</v>
+        <v>1.148</v>
       </c>
       <c r="I50">
-        <v>1.563</v>
+        <v>1.452</v>
       </c>
       <c r="J50">
-        <v>1.435</v>
+        <v>1.418</v>
       </c>
       <c r="W50" t="s">
         <v>72</v>
@@ -2895,34 +2895,34 @@
     </row>
     <row r="51" spans="1:24">
       <c r="A51" s="2">
-        <v>46229</v>
+        <v>46247</v>
       </c>
       <c r="B51">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C51">
-        <v>3.02</v>
+        <v>2.514</v>
       </c>
       <c r="D51">
-        <v>3.381</v>
+        <v>2.937</v>
       </c>
       <c r="E51">
-        <v>3.837</v>
+        <v>2.314</v>
       </c>
       <c r="F51">
-        <v>3.86</v>
+        <v>3.093</v>
       </c>
       <c r="G51">
-        <v>3.34</v>
+        <v>2.761</v>
       </c>
       <c r="H51">
-        <v>0.9370000000000001</v>
+        <v>1.152</v>
       </c>
       <c r="I51">
-        <v>1.465</v>
+        <v>1.506</v>
       </c>
       <c r="J51">
-        <v>1.595</v>
+        <v>1.316</v>
       </c>
       <c r="W51" t="s">
         <v>73</v>
@@ -2933,34 +2933,34 @@
     </row>
     <row r="52" spans="1:24">
       <c r="A52" s="2">
-        <v>46229</v>
+        <v>46247</v>
       </c>
       <c r="B52">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C52">
-        <v>2.996</v>
+        <v>2.118</v>
       </c>
       <c r="D52">
-        <v>3.4</v>
+        <v>2.688</v>
       </c>
       <c r="E52">
-        <v>3.775</v>
+        <v>2.604</v>
       </c>
       <c r="F52">
-        <v>3.726</v>
+        <v>2.722</v>
       </c>
       <c r="G52">
-        <v>3.3</v>
+        <v>2.52</v>
       </c>
       <c r="H52">
-        <v>0.944</v>
+        <v>1.126</v>
       </c>
       <c r="I52">
-        <v>1.502</v>
+        <v>1.506</v>
       </c>
       <c r="J52">
-        <v>1.656</v>
+        <v>1.207</v>
       </c>
       <c r="W52" t="s">
         <v>74</v>
@@ -2971,34 +2971,34 @@
     </row>
     <row r="53" spans="1:24">
       <c r="A53" s="2">
-        <v>46229</v>
+        <v>46247</v>
       </c>
       <c r="B53">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C53">
-        <v>2.903</v>
+        <v>1.582</v>
       </c>
       <c r="D53">
-        <v>3.291</v>
+        <v>2.146</v>
       </c>
       <c r="E53">
-        <v>3.743</v>
+        <v>2.485</v>
       </c>
       <c r="F53">
-        <v>3.397</v>
+        <v>2.082</v>
       </c>
       <c r="G53">
-        <v>3.241</v>
+        <v>2.09</v>
       </c>
       <c r="H53">
-        <v>0.854</v>
+        <v>1.079</v>
       </c>
       <c r="I53">
-        <v>1.502</v>
+        <v>1.487</v>
       </c>
       <c r="J53">
-        <v>1.596</v>
+        <v>0.82</v>
       </c>
       <c r="W53" t="s">
         <v>75</v>
@@ -3009,34 +3009,34 @@
     </row>
     <row r="54" spans="1:24">
       <c r="A54" s="2">
-        <v>46229</v>
+        <v>46247</v>
       </c>
       <c r="B54">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C54">
-        <v>2.593</v>
+        <v>1.096</v>
       </c>
       <c r="D54">
-        <v>3.171</v>
+        <v>1.349</v>
       </c>
       <c r="E54">
-        <v>3.696</v>
+        <v>1.826</v>
       </c>
       <c r="F54">
-        <v>3.082</v>
+        <v>1.458</v>
       </c>
       <c r="G54">
-        <v>2.914</v>
+        <v>1.563</v>
       </c>
       <c r="H54">
-        <v>0.869</v>
+        <v>0.826</v>
       </c>
       <c r="I54">
-        <v>1.502</v>
+        <v>1.091</v>
       </c>
       <c r="J54">
-        <v>1.455</v>
+        <v>0.333</v>
       </c>
       <c r="W54" t="s">
         <v>76</v>
@@ -3047,34 +3047,34 @@
     </row>
     <row r="55" spans="1:24">
       <c r="A55" s="2">
-        <v>46229</v>
+        <v>46247</v>
       </c>
       <c r="B55">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C55">
-        <v>2.003</v>
+        <v>0.586</v>
       </c>
       <c r="D55">
-        <v>2.779</v>
+        <v>0.656</v>
       </c>
       <c r="E55">
-        <v>3.35</v>
+        <v>1.114</v>
       </c>
       <c r="F55">
-        <v>2.427</v>
+        <v>0.543</v>
       </c>
       <c r="G55">
-        <v>2.265</v>
+        <v>0.869</v>
       </c>
       <c r="H55">
-        <v>1.003</v>
+        <v>0.532</v>
       </c>
       <c r="I55">
-        <v>1.502</v>
+        <v>0.542</v>
       </c>
       <c r="J55">
-        <v>1.12</v>
+        <v>0.208</v>
       </c>
       <c r="W55" t="s">
         <v>77</v>
@@ -3085,34 +3085,34 @@
     </row>
     <row r="56" spans="1:24">
       <c r="A56" s="2">
-        <v>46229</v>
+        <v>46247</v>
       </c>
       <c r="B56">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C56">
-        <v>1.337</v>
+        <v>0.204</v>
       </c>
       <c r="D56">
-        <v>1.896</v>
+        <v>0.179</v>
       </c>
       <c r="E56">
-        <v>2.54</v>
+        <v>0.392</v>
       </c>
       <c r="F56">
-        <v>1.633</v>
+        <v>0.171</v>
       </c>
       <c r="G56">
-        <v>1.806</v>
+        <v>0.242</v>
       </c>
       <c r="H56">
-        <v>0.925</v>
+        <v>0.213</v>
       </c>
       <c r="I56">
-        <v>1.094</v>
+        <v>0.197</v>
       </c>
       <c r="J56">
-        <v>0.797</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="W56" t="s">
         <v>78</v>
@@ -3123,34 +3123,34 @@
     </row>
     <row r="57" spans="1:24">
       <c r="A57" s="2">
-        <v>46229</v>
+        <v>46247</v>
       </c>
       <c r="B57">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C57">
-        <v>0.827</v>
+        <v>0.023</v>
       </c>
       <c r="D57">
-        <v>0.985</v>
+        <v>0.018</v>
       </c>
       <c r="E57">
-        <v>1.544</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="F57">
-        <v>0.79</v>
+        <v>0.011</v>
       </c>
       <c r="G57">
-        <v>0.989</v>
+        <v>0.011</v>
       </c>
       <c r="H57">
-        <v>0.6919999999999999</v>
+        <v>0</v>
       </c>
       <c r="I57">
-        <v>0.6870000000000001</v>
+        <v>0</v>
       </c>
       <c r="J57">
-        <v>0.426</v>
+        <v>0</v>
       </c>
       <c r="W57" t="s">
         <v>79</v>
@@ -3161,34 +3161,34 @@
     </row>
     <row r="58" spans="1:24">
       <c r="A58" s="2">
-        <v>46229</v>
+        <v>46247</v>
       </c>
       <c r="B58">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C58">
-        <v>0.274</v>
+        <v>0</v>
       </c>
       <c r="D58">
-        <v>0.305</v>
+        <v>0</v>
       </c>
       <c r="E58">
-        <v>0.525</v>
+        <v>0.078</v>
       </c>
       <c r="F58">
-        <v>0.234</v>
+        <v>0</v>
       </c>
       <c r="G58">
-        <v>0.287</v>
+        <v>0</v>
       </c>
       <c r="H58">
-        <v>0.382</v>
+        <v>0</v>
       </c>
       <c r="I58">
-        <v>0.361</v>
+        <v>0</v>
       </c>
       <c r="J58">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="W58" t="s">
         <v>80</v>
@@ -3199,31 +3199,31 @@
     </row>
     <row r="59" spans="1:24">
       <c r="A59" s="2">
-        <v>46229</v>
+        <v>46247</v>
       </c>
       <c r="B59">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C59">
-        <v>0.051</v>
+        <v>0</v>
       </c>
       <c r="D59">
-        <v>0.08400000000000001</v>
+        <v>0</v>
       </c>
       <c r="E59">
-        <v>0.109</v>
+        <v>0.064</v>
       </c>
       <c r="F59">
-        <v>0.041</v>
+        <v>0</v>
       </c>
       <c r="G59">
-        <v>0.061</v>
+        <v>0</v>
       </c>
       <c r="H59">
-        <v>0.053</v>
+        <v>0</v>
       </c>
       <c r="I59">
-        <v>0.042</v>
+        <v>0</v>
       </c>
       <c r="J59">
         <v>0</v>
@@ -3237,10 +3237,10 @@
     </row>
     <row r="60" spans="1:24">
       <c r="A60" s="2">
-        <v>46229</v>
+        <v>46247</v>
       </c>
       <c r="B60">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C60">
         <v>0</v>
@@ -3249,7 +3249,7 @@
         <v>0</v>
       </c>
       <c r="E60">
-        <v>0</v>
+        <v>0.029</v>
       </c>
       <c r="F60">
         <v>0</v>
@@ -3275,10 +3275,10 @@
     </row>
     <row r="61" spans="1:24">
       <c r="A61" s="2">
-        <v>46229</v>
+        <v>46248</v>
       </c>
       <c r="B61">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="C61">
         <v>0</v>
@@ -3287,7 +3287,7 @@
         <v>0</v>
       </c>
       <c r="E61">
-        <v>0.023</v>
+        <v>0.11</v>
       </c>
       <c r="F61">
         <v>0</v>
@@ -3313,10 +3313,10 @@
     </row>
     <row r="62" spans="1:24">
       <c r="A62" s="2">
-        <v>46229</v>
+        <v>46248</v>
       </c>
       <c r="B62">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="C62">
         <v>0</v>
@@ -3325,7 +3325,7 @@
         <v>0</v>
       </c>
       <c r="E62">
-        <v>0.022</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="F62">
         <v>0</v>
@@ -3340,7 +3340,7 @@
         <v>0</v>
       </c>
       <c r="J62">
-        <v>0.019</v>
+        <v>0</v>
       </c>
       <c r="W62" t="s">
         <v>84</v>
@@ -3351,10 +3351,10 @@
     </row>
     <row r="63" spans="1:24">
       <c r="A63" s="2">
-        <v>46230</v>
+        <v>46248</v>
       </c>
       <c r="B63">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C63">
         <v>0</v>
@@ -3363,7 +3363,7 @@
         <v>0</v>
       </c>
       <c r="E63">
-        <v>0.065</v>
+        <v>0.031</v>
       </c>
       <c r="F63">
         <v>0</v>
@@ -3389,10 +3389,10 @@
     </row>
     <row r="64" spans="1:24">
       <c r="A64" s="2">
-        <v>46230</v>
+        <v>46248</v>
       </c>
       <c r="B64">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C64">
         <v>0</v>
@@ -3401,7 +3401,7 @@
         <v>0</v>
       </c>
       <c r="E64">
-        <v>0.082</v>
+        <v>0.042</v>
       </c>
       <c r="F64">
         <v>0</v>
@@ -3427,10 +3427,10 @@
     </row>
     <row r="65" spans="1:24">
       <c r="A65" s="2">
-        <v>46230</v>
+        <v>46248</v>
       </c>
       <c r="B65">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C65">
         <v>0</v>
@@ -3465,10 +3465,10 @@
     </row>
     <row r="66" spans="1:24">
       <c r="A66" s="2">
-        <v>46230</v>
+        <v>46248</v>
       </c>
       <c r="B66">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C66">
         <v>0</v>
@@ -3477,7 +3477,7 @@
         <v>0</v>
       </c>
       <c r="E66">
-        <v>0</v>
+        <v>0.011</v>
       </c>
       <c r="F66">
         <v>0</v>
@@ -3503,34 +3503,34 @@
     </row>
     <row r="67" spans="1:24">
       <c r="A67" s="2">
-        <v>46230</v>
+        <v>46248</v>
       </c>
       <c r="B67">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C67">
-        <v>0</v>
+        <v>0.022</v>
       </c>
       <c r="D67">
-        <v>0</v>
+        <v>0.023</v>
       </c>
       <c r="E67">
-        <v>0</v>
+        <v>0.016</v>
       </c>
       <c r="F67">
-        <v>0</v>
+        <v>0.156</v>
       </c>
       <c r="G67">
-        <v>0</v>
+        <v>0.063</v>
       </c>
       <c r="H67">
-        <v>0</v>
+        <v>0.034</v>
       </c>
       <c r="I67">
-        <v>0</v>
+        <v>0.044</v>
       </c>
       <c r="J67">
-        <v>0.02</v>
+        <v>0.044</v>
       </c>
       <c r="W67" t="s">
         <v>89</v>
@@ -3541,34 +3541,34 @@
     </row>
     <row r="68" spans="1:24">
       <c r="A68" s="2">
-        <v>46230</v>
+        <v>46248</v>
       </c>
       <c r="B68">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C68">
-        <v>0</v>
+        <v>0.285</v>
       </c>
       <c r="D68">
-        <v>0</v>
+        <v>0.322</v>
       </c>
       <c r="E68">
-        <v>0</v>
+        <v>0.298</v>
       </c>
       <c r="F68">
-        <v>0</v>
+        <v>0.856</v>
       </c>
       <c r="G68">
-        <v>0</v>
+        <v>0.587</v>
       </c>
       <c r="H68">
-        <v>0</v>
+        <v>0.236</v>
       </c>
       <c r="I68">
-        <v>0</v>
+        <v>0.428</v>
       </c>
       <c r="J68">
-        <v>0.014</v>
+        <v>0.3</v>
       </c>
       <c r="W68" t="s">
         <v>90</v>
@@ -3579,34 +3579,34 @@
     </row>
     <row r="69" spans="1:24">
       <c r="A69" s="2">
-        <v>46230</v>
+        <v>46248</v>
       </c>
       <c r="B69">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C69">
-        <v>0.042</v>
+        <v>0.918</v>
       </c>
       <c r="D69">
-        <v>0.044</v>
+        <v>1.176</v>
       </c>
       <c r="E69">
-        <v>0.034</v>
+        <v>0.993</v>
       </c>
       <c r="F69">
-        <v>0.175</v>
+        <v>2.047</v>
       </c>
       <c r="G69">
-        <v>0.08500000000000001</v>
+        <v>1.519</v>
       </c>
       <c r="H69">
-        <v>0.053</v>
+        <v>0.76</v>
       </c>
       <c r="I69">
-        <v>0.064</v>
+        <v>0.587</v>
       </c>
       <c r="J69">
-        <v>0.038</v>
+        <v>0.883</v>
       </c>
       <c r="W69" t="s">
         <v>91</v>
@@ -3617,34 +3617,34 @@
     </row>
     <row r="70" spans="1:24">
       <c r="A70" s="2">
-        <v>46230</v>
+        <v>46248</v>
       </c>
       <c r="B70">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C70">
-        <v>0.305</v>
+        <v>1.602</v>
       </c>
       <c r="D70">
-        <v>0.342</v>
+        <v>1.816</v>
       </c>
       <c r="E70">
-        <v>0.347</v>
+        <v>2.014</v>
       </c>
       <c r="F70">
-        <v>0.631</v>
+        <v>2.925</v>
       </c>
       <c r="G70">
-        <v>0.362</v>
+        <v>2.376</v>
       </c>
       <c r="H70">
-        <v>0.236</v>
+        <v>0.905</v>
       </c>
       <c r="I70">
-        <v>0.361</v>
+        <v>1.033</v>
       </c>
       <c r="J70">
-        <v>0.195</v>
+        <v>1.096</v>
       </c>
       <c r="W70" t="s">
         <v>92</v>
@@ -3655,34 +3655,34 @@
     </row>
     <row r="71" spans="1:24">
       <c r="A71" s="2">
-        <v>46230</v>
+        <v>46248</v>
       </c>
       <c r="B71">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C71">
-        <v>0.77</v>
+        <v>2.025</v>
       </c>
       <c r="D71">
-        <v>0.8139999999999999</v>
+        <v>2.291</v>
       </c>
       <c r="E71">
-        <v>1.089</v>
+        <v>3.055</v>
       </c>
       <c r="F71">
-        <v>1.251</v>
+        <v>3.79</v>
       </c>
       <c r="G71">
-        <v>0.714</v>
+        <v>3.011</v>
       </c>
       <c r="H71">
-        <v>0.632</v>
+        <v>0.837</v>
       </c>
       <c r="I71">
-        <v>0.635</v>
+        <v>1.387</v>
       </c>
       <c r="J71">
-        <v>0.526</v>
+        <v>1.45</v>
       </c>
       <c r="W71" t="s">
         <v>93</v>
@@ -3693,34 +3693,34 @@
     </row>
     <row r="72" spans="1:24">
       <c r="A72" s="2">
-        <v>46230</v>
+        <v>46248</v>
       </c>
       <c r="B72">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C72">
-        <v>1.175</v>
+        <v>2.372</v>
       </c>
       <c r="D72">
-        <v>1.462</v>
+        <v>2.783</v>
       </c>
       <c r="E72">
-        <v>1.873</v>
+        <v>3.669</v>
       </c>
       <c r="F72">
-        <v>2.328</v>
+        <v>4.182</v>
       </c>
       <c r="G72">
-        <v>1.884</v>
+        <v>3.514</v>
       </c>
       <c r="H72">
-        <v>1.031</v>
+        <v>1.16</v>
       </c>
       <c r="I72">
-        <v>0.9330000000000001</v>
+        <v>1.396</v>
       </c>
       <c r="J72">
-        <v>0.874</v>
+        <v>1.571</v>
       </c>
       <c r="W72" t="s">
         <v>94</v>
@@ -3731,34 +3731,34 @@
     </row>
     <row r="73" spans="1:24">
       <c r="A73" s="2">
-        <v>46230</v>
+        <v>46248</v>
       </c>
       <c r="B73">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C73">
-        <v>1.715</v>
+        <v>2.694</v>
       </c>
       <c r="D73">
-        <v>2.083</v>
+        <v>3.071</v>
       </c>
       <c r="E73">
-        <v>2.724</v>
+        <v>3.808</v>
       </c>
       <c r="F73">
-        <v>2.951</v>
+        <v>4.246</v>
       </c>
       <c r="G73">
-        <v>2.637</v>
+        <v>3.604</v>
       </c>
       <c r="H73">
-        <v>0.918</v>
+        <v>1.428</v>
       </c>
       <c r="I73">
-        <v>1.437</v>
+        <v>1.396</v>
       </c>
       <c r="J73">
-        <v>1.092</v>
+        <v>1.637</v>
       </c>
       <c r="W73" t="s">
         <v>95</v>
@@ -3769,34 +3769,34 @@
     </row>
     <row r="74" spans="1:24">
       <c r="A74" s="2">
-        <v>46230</v>
+        <v>46248</v>
       </c>
       <c r="B74">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C74">
-        <v>1.832</v>
+        <v>2.6</v>
       </c>
       <c r="D74">
-        <v>2.244</v>
+        <v>3.215</v>
       </c>
       <c r="E74">
-        <v>3.127</v>
+        <v>3.576</v>
       </c>
       <c r="F74">
-        <v>2.831</v>
+        <v>4.229</v>
       </c>
       <c r="G74">
-        <v>2.624</v>
+        <v>3.583</v>
       </c>
       <c r="H74">
-        <v>1.372</v>
+        <v>0.911</v>
       </c>
       <c r="I74">
-        <v>1.445</v>
+        <v>1.452</v>
       </c>
       <c r="J74">
-        <v>1.22</v>
+        <v>1.567</v>
       </c>
       <c r="W74" t="s">
         <v>96</v>
@@ -3807,34 +3807,34 @@
     </row>
     <row r="75" spans="1:24">
       <c r="A75" s="2">
-        <v>46230</v>
+        <v>46248</v>
       </c>
       <c r="B75">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C75">
-        <v>2.281</v>
+        <v>2.622</v>
       </c>
       <c r="D75">
-        <v>2.453</v>
+        <v>3.193</v>
       </c>
       <c r="E75">
-        <v>3.658</v>
+        <v>3.667</v>
       </c>
       <c r="F75">
-        <v>2.771</v>
+        <v>3.65</v>
       </c>
       <c r="G75">
-        <v>2.699</v>
+        <v>3.222</v>
       </c>
       <c r="H75">
-        <v>1.103</v>
+        <v>0.949</v>
       </c>
       <c r="I75">
+        <v>1.506</v>
+      </c>
+      <c r="J75">
         <v>1.419</v>
-      </c>
-      <c r="J75">
-        <v>1.359</v>
       </c>
       <c r="W75" t="s">
         <v>97</v>
@@ -3845,34 +3845,34 @@
     </row>
     <row r="76" spans="1:24">
       <c r="A76" s="2">
-        <v>46230</v>
+        <v>46248</v>
       </c>
       <c r="B76">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C76">
-        <v>2.505</v>
+        <v>2.449</v>
       </c>
       <c r="D76">
-        <v>2.621</v>
+        <v>2.975</v>
       </c>
       <c r="E76">
-        <v>3.855</v>
+        <v>3.796</v>
       </c>
       <c r="F76">
-        <v>3.255</v>
+        <v>3.01</v>
       </c>
       <c r="G76">
-        <v>2.862</v>
+        <v>2.787</v>
       </c>
       <c r="H76">
-        <v>1.093</v>
+        <v>1.003</v>
       </c>
       <c r="I76">
-        <v>1.502</v>
+        <v>1.461</v>
       </c>
       <c r="J76">
-        <v>1.206</v>
+        <v>1.239</v>
       </c>
       <c r="W76" t="s">
         <v>98</v>
@@ -3883,34 +3883,34 @@
     </row>
     <row r="77" spans="1:24">
       <c r="A77" s="2">
-        <v>46230</v>
+        <v>46248</v>
       </c>
       <c r="B77">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C77">
-        <v>2.144</v>
+        <v>2.081</v>
       </c>
       <c r="D77">
-        <v>2.372</v>
+        <v>2.65</v>
       </c>
       <c r="E77">
-        <v>3.571</v>
+        <v>3.391</v>
       </c>
       <c r="F77">
-        <v>3.195</v>
+        <v>2.004</v>
       </c>
       <c r="G77">
-        <v>2.881</v>
+        <v>2.065</v>
       </c>
       <c r="H77">
-        <v>0.922</v>
+        <v>1.032</v>
       </c>
       <c r="I77">
-        <v>1.502</v>
+        <v>0.767</v>
       </c>
       <c r="J77">
-        <v>1.249</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="W77" t="s">
         <v>99</v>
@@ -3921,34 +3921,34 @@
     </row>
     <row r="78" spans="1:24">
       <c r="A78" s="2">
-        <v>46230</v>
+        <v>46248</v>
       </c>
       <c r="B78">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C78">
-        <v>1.685</v>
+        <v>1.445</v>
       </c>
       <c r="D78">
-        <v>1.891</v>
+        <v>1.877</v>
       </c>
       <c r="E78">
-        <v>3.144</v>
+        <v>2.415</v>
       </c>
       <c r="F78">
-        <v>2.558</v>
+        <v>1.34</v>
       </c>
       <c r="G78">
-        <v>2.581</v>
+        <v>1.552</v>
       </c>
       <c r="H78">
-        <v>0.824</v>
+        <v>0.923</v>
       </c>
       <c r="I78">
-        <v>1.502</v>
+        <v>0.551</v>
       </c>
       <c r="J78">
-        <v>1.11</v>
+        <v>0.507</v>
       </c>
       <c r="W78" t="s">
         <v>100</v>
@@ -3959,34 +3959,34 @@
     </row>
     <row r="79" spans="1:24">
       <c r="A79" s="2">
-        <v>46230</v>
+        <v>46248</v>
       </c>
       <c r="B79">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C79">
-        <v>1.483</v>
+        <v>0.74</v>
       </c>
       <c r="D79">
-        <v>1.662</v>
+        <v>0.875</v>
       </c>
       <c r="E79">
-        <v>2.529</v>
+        <v>1.347</v>
       </c>
       <c r="F79">
-        <v>2.078</v>
+        <v>0.468</v>
       </c>
       <c r="G79">
-        <v>2.1</v>
+        <v>0.65</v>
       </c>
       <c r="H79">
-        <v>1.039</v>
+        <v>0.537</v>
       </c>
       <c r="I79">
-        <v>1.39</v>
+        <v>0.52</v>
       </c>
       <c r="J79">
-        <v>0.784</v>
+        <v>0.325</v>
       </c>
       <c r="W79" t="s">
         <v>101</v>
@@ -3997,34 +3997,34 @@
     </row>
     <row r="80" spans="1:24">
       <c r="A80" s="2">
-        <v>46230</v>
+        <v>46248</v>
       </c>
       <c r="B80">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C80">
-        <v>1.014</v>
+        <v>0.172</v>
       </c>
       <c r="D80">
-        <v>1.054</v>
+        <v>0.272</v>
       </c>
       <c r="E80">
-        <v>1.811</v>
+        <v>0.517</v>
       </c>
       <c r="F80">
-        <v>1.483</v>
+        <v>0.139</v>
       </c>
       <c r="G80">
-        <v>1.395</v>
+        <v>0.192</v>
       </c>
       <c r="H80">
-        <v>0.875</v>
+        <v>0.213</v>
       </c>
       <c r="I80">
-        <v>0.961</v>
+        <v>0.116</v>
       </c>
       <c r="J80">
-        <v>0.327</v>
+        <v>0.107</v>
       </c>
       <c r="W80" t="s">
         <v>102</v>
@@ -4035,34 +4035,34 @@
     </row>
     <row r="81" spans="1:24">
       <c r="A81" s="2">
-        <v>46230</v>
+        <v>46248</v>
       </c>
       <c r="B81">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C81">
-        <v>0.491</v>
+        <v>0.02</v>
       </c>
       <c r="D81">
-        <v>0.514</v>
+        <v>0.022</v>
       </c>
       <c r="E81">
-        <v>1.301</v>
+        <v>0.056</v>
       </c>
       <c r="F81">
-        <v>0.461</v>
+        <v>0</v>
       </c>
       <c r="G81">
-        <v>0.622</v>
+        <v>0</v>
       </c>
       <c r="H81">
-        <v>0.446</v>
+        <v>0</v>
       </c>
       <c r="I81">
-        <v>0.588</v>
+        <v>0</v>
       </c>
       <c r="J81">
-        <v>0.219</v>
+        <v>0</v>
       </c>
       <c r="W81" t="s">
         <v>103</v>
@@ -4073,34 +4073,34 @@
     </row>
     <row r="82" spans="1:24">
       <c r="A82" s="2">
-        <v>46230</v>
+        <v>46248</v>
       </c>
       <c r="B82">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C82">
-        <v>0.229</v>
+        <v>0</v>
       </c>
       <c r="D82">
-        <v>0.245</v>
+        <v>0</v>
       </c>
       <c r="E82">
-        <v>0.539</v>
+        <v>0.027</v>
       </c>
       <c r="F82">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="G82">
-        <v>0.225</v>
+        <v>0</v>
       </c>
       <c r="H82">
-        <v>0.217</v>
+        <v>0</v>
       </c>
       <c r="I82">
-        <v>0.201</v>
+        <v>0</v>
       </c>
       <c r="J82">
-        <v>0.08799999999999999</v>
+        <v>0</v>
       </c>
       <c r="W82" t="s">
         <v>104</v>
@@ -4111,31 +4111,31 @@
     </row>
     <row r="83" spans="1:24">
       <c r="A83" s="2">
-        <v>46230</v>
+        <v>46248</v>
       </c>
       <c r="B83">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C83">
-        <v>0.029</v>
+        <v>0</v>
       </c>
       <c r="D83">
-        <v>0.043</v>
+        <v>0</v>
       </c>
       <c r="E83">
-        <v>0.098</v>
+        <v>0.018</v>
       </c>
       <c r="F83">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="G83">
-        <v>0.029</v>
+        <v>0</v>
       </c>
       <c r="H83">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="I83">
-        <v>0.021</v>
+        <v>0</v>
       </c>
       <c r="J83">
         <v>0</v>
@@ -4149,10 +4149,10 @@
     </row>
     <row r="84" spans="1:24">
       <c r="A84" s="2">
-        <v>46230</v>
+        <v>46248</v>
       </c>
       <c r="B84">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C84">
         <v>0</v>
@@ -4161,7 +4161,7 @@
         <v>0</v>
       </c>
       <c r="E84">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="F84">
         <v>0</v>
@@ -4176,7 +4176,7 @@
         <v>0</v>
       </c>
       <c r="J84">
-        <v>0.013</v>
+        <v>0</v>
       </c>
       <c r="W84" t="s">
         <v>106</v>
@@ -4187,10 +4187,10 @@
     </row>
     <row r="85" spans="1:24">
       <c r="A85" s="2">
-        <v>46230</v>
+        <v>46249</v>
       </c>
       <c r="B85">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="C85">
         <v>0</v>
@@ -4199,7 +4199,7 @@
         <v>0</v>
       </c>
       <c r="E85">
-        <v>0</v>
+        <v>0.059</v>
       </c>
       <c r="F85">
         <v>0</v>
@@ -4214,7 +4214,7 @@
         <v>0</v>
       </c>
       <c r="J85">
-        <v>0.013</v>
+        <v>0.019</v>
       </c>
       <c r="W85" t="s">
         <v>107</v>
@@ -4225,10 +4225,10 @@
     </row>
     <row r="86" spans="1:24">
       <c r="A86" s="2">
-        <v>46230</v>
+        <v>46249</v>
       </c>
       <c r="B86">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="C86">
         <v>0</v>
@@ -4237,7 +4237,7 @@
         <v>0</v>
       </c>
       <c r="E86">
-        <v>0</v>
+        <v>0.058</v>
       </c>
       <c r="F86">
         <v>0</v>
@@ -4252,7 +4252,7 @@
         <v>0</v>
       </c>
       <c r="J86">
-        <v>0.013</v>
+        <v>0</v>
       </c>
       <c r="W86" t="s">
         <v>108</v>
@@ -4263,10 +4263,10 @@
     </row>
     <row r="87" spans="1:24">
       <c r="A87" s="2">
-        <v>46231</v>
+        <v>46249</v>
       </c>
       <c r="B87">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C87">
         <v>0</v>
@@ -4275,7 +4275,7 @@
         <v>0</v>
       </c>
       <c r="E87">
-        <v>0</v>
+        <v>0.053</v>
       </c>
       <c r="F87">
         <v>0</v>
@@ -4290,7 +4290,7 @@
         <v>0</v>
       </c>
       <c r="J87">
-        <v>0.014</v>
+        <v>0</v>
       </c>
       <c r="W87" t="s">
         <v>109</v>
@@ -4301,10 +4301,10 @@
     </row>
     <row r="88" spans="1:24">
       <c r="A88" s="2">
-        <v>46231</v>
+        <v>46249</v>
       </c>
       <c r="B88">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C88">
         <v>0</v>
@@ -4313,7 +4313,7 @@
         <v>0</v>
       </c>
       <c r="E88">
-        <v>0</v>
+        <v>0.045</v>
       </c>
       <c r="F88">
         <v>0</v>
@@ -4328,7 +4328,7 @@
         <v>0</v>
       </c>
       <c r="J88">
-        <v>0.014</v>
+        <v>0</v>
       </c>
       <c r="W88" t="s">
         <v>110</v>
@@ -4339,10 +4339,10 @@
     </row>
     <row r="89" spans="1:24">
       <c r="A89" s="2">
-        <v>46231</v>
+        <v>46249</v>
       </c>
       <c r="B89">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C89">
         <v>0</v>
@@ -4351,7 +4351,7 @@
         <v>0</v>
       </c>
       <c r="E89">
-        <v>0</v>
+        <v>0.014</v>
       </c>
       <c r="F89">
         <v>0</v>
@@ -4366,7 +4366,7 @@
         <v>0</v>
       </c>
       <c r="J89">
-        <v>0.014</v>
+        <v>0</v>
       </c>
       <c r="W89" t="s">
         <v>111</v>
@@ -4377,10 +4377,10 @@
     </row>
     <row r="90" spans="1:24">
       <c r="A90" s="2">
-        <v>46231</v>
+        <v>46249</v>
       </c>
       <c r="B90">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C90">
         <v>0</v>
@@ -4404,7 +4404,7 @@
         <v>0</v>
       </c>
       <c r="J90">
-        <v>0.014</v>
+        <v>0.021</v>
       </c>
       <c r="W90" t="s">
         <v>112</v>
@@ -4415,34 +4415,34 @@
     </row>
     <row r="91" spans="1:24">
       <c r="A91" s="2">
-        <v>46231</v>
+        <v>46249</v>
       </c>
       <c r="B91">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C91">
-        <v>0</v>
+        <v>0.024</v>
       </c>
       <c r="D91">
-        <v>0</v>
+        <v>0.023</v>
       </c>
       <c r="E91">
-        <v>0</v>
+        <v>0.018</v>
       </c>
       <c r="F91">
-        <v>0</v>
+        <v>0.155</v>
       </c>
       <c r="G91">
-        <v>0</v>
+        <v>0.063</v>
       </c>
       <c r="H91">
-        <v>0</v>
+        <v>0.044</v>
       </c>
       <c r="I91">
-        <v>0</v>
+        <v>0.044</v>
       </c>
       <c r="J91">
-        <v>0.014</v>
+        <v>0</v>
       </c>
       <c r="W91" t="s">
         <v>113</v>
@@ -4453,34 +4453,34 @@
     </row>
     <row r="92" spans="1:24">
       <c r="A92" s="2">
-        <v>46231</v>
+        <v>46249</v>
       </c>
       <c r="B92">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C92">
-        <v>0</v>
+        <v>0.276</v>
       </c>
       <c r="D92">
-        <v>0</v>
+        <v>0.422</v>
       </c>
       <c r="E92">
-        <v>0</v>
+        <v>0.492</v>
       </c>
       <c r="F92">
-        <v>0</v>
+        <v>0.971</v>
       </c>
       <c r="G92">
-        <v>0</v>
+        <v>0.596</v>
       </c>
       <c r="H92">
-        <v>0</v>
+        <v>0.397</v>
       </c>
       <c r="I92">
-        <v>0</v>
+        <v>0.472</v>
       </c>
       <c r="J92">
-        <v>0.014</v>
+        <v>0.312</v>
       </c>
       <c r="W92" t="s">
         <v>114</v>
@@ -4491,34 +4491,34 @@
     </row>
     <row r="93" spans="1:24">
       <c r="A93" s="2">
-        <v>46231</v>
+        <v>46249</v>
       </c>
       <c r="B93">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C93">
-        <v>0.046</v>
+        <v>1.006</v>
       </c>
       <c r="D93">
-        <v>0.065</v>
+        <v>1.119</v>
       </c>
       <c r="E93">
-        <v>0.06900000000000001</v>
+        <v>1.525</v>
       </c>
       <c r="F93">
-        <v>0.197</v>
+        <v>2.129</v>
       </c>
       <c r="G93">
-        <v>0.098</v>
+        <v>1.476</v>
       </c>
       <c r="H93">
-        <v>0.106</v>
+        <v>0.915</v>
       </c>
       <c r="I93">
-        <v>0.064</v>
+        <v>0.928</v>
       </c>
       <c r="J93">
-        <v>0.038</v>
+        <v>0.863</v>
       </c>
       <c r="W93" t="s">
         <v>115</v>
@@ -4529,34 +4529,34 @@
     </row>
     <row r="94" spans="1:24">
       <c r="A94" s="2">
-        <v>46231</v>
+        <v>46249</v>
       </c>
       <c r="B94">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C94">
-        <v>0.352</v>
+        <v>1.668</v>
       </c>
       <c r="D94">
-        <v>0.458</v>
+        <v>2.076</v>
       </c>
       <c r="E94">
-        <v>0.5669999999999999</v>
+        <v>2.684</v>
       </c>
       <c r="F94">
-        <v>0.771</v>
+        <v>3.064</v>
       </c>
       <c r="G94">
-        <v>0.49</v>
+        <v>2.397</v>
       </c>
       <c r="H94">
-        <v>0.442</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="I94">
-        <v>0.328</v>
+        <v>1.163</v>
       </c>
       <c r="J94">
-        <v>0.349</v>
+        <v>1.208</v>
       </c>
       <c r="W94" t="s">
         <v>116</v>
@@ -4567,34 +4567,34 @@
     </row>
     <row r="95" spans="1:24">
       <c r="A95" s="2">
-        <v>46231</v>
+        <v>46249</v>
       </c>
       <c r="B95">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C95">
-        <v>0.861</v>
+        <v>2.317</v>
       </c>
       <c r="D95">
-        <v>0.973</v>
+        <v>2.791</v>
       </c>
       <c r="E95">
-        <v>1.511</v>
+        <v>3.76</v>
       </c>
       <c r="F95">
-        <v>1.765</v>
+        <v>3.85</v>
       </c>
       <c r="G95">
-        <v>1.323</v>
+        <v>3.042</v>
       </c>
       <c r="H95">
-        <v>0.743</v>
+        <v>0.793</v>
       </c>
       <c r="I95">
-        <v>0.635</v>
+        <v>1.437</v>
       </c>
       <c r="J95">
-        <v>0.866</v>
+        <v>1.473</v>
       </c>
       <c r="W95" t="s">
         <v>117</v>
@@ -4605,34 +4605,34 @@
     </row>
     <row r="96" spans="1:24">
       <c r="A96" s="2">
-        <v>46231</v>
+        <v>46249</v>
       </c>
       <c r="B96">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C96">
-        <v>1.462</v>
+        <v>2.652</v>
       </c>
       <c r="D96">
-        <v>1.697</v>
+        <v>3.042</v>
       </c>
       <c r="E96">
-        <v>2.372</v>
+        <v>3.995</v>
       </c>
       <c r="F96">
-        <v>2.559</v>
+        <v>4.164</v>
       </c>
       <c r="G96">
-        <v>1.99</v>
+        <v>3.476</v>
       </c>
       <c r="H96">
-        <v>1.341</v>
+        <v>0.783</v>
       </c>
       <c r="I96">
-        <v>0.959</v>
+        <v>1.396</v>
       </c>
       <c r="J96">
-        <v>0.883</v>
+        <v>1.621</v>
       </c>
       <c r="W96" t="s">
         <v>118</v>
@@ -4643,34 +4643,34 @@
     </row>
     <row r="97" spans="1:24">
       <c r="A97" s="2">
-        <v>46231</v>
+        <v>46249</v>
       </c>
       <c r="B97">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C97">
-        <v>2.023</v>
+        <v>2.828</v>
       </c>
       <c r="D97">
-        <v>2.451</v>
+        <v>3.171</v>
       </c>
       <c r="E97">
-        <v>3.295</v>
+        <v>3.889</v>
       </c>
       <c r="F97">
-        <v>3.095</v>
+        <v>4.251</v>
       </c>
       <c r="G97">
-        <v>2.775</v>
+        <v>3.641</v>
       </c>
       <c r="H97">
-        <v>1.117</v>
+        <v>1.441</v>
       </c>
       <c r="I97">
-        <v>1.535</v>
+        <v>1.396</v>
       </c>
       <c r="J97">
-        <v>1.038</v>
+        <v>1.586</v>
       </c>
       <c r="W97" t="s">
         <v>119</v>
@@ -4681,34 +4681,34 @@
     </row>
     <row r="98" spans="1:24">
       <c r="A98" s="2">
-        <v>46231</v>
+        <v>46249</v>
       </c>
       <c r="B98">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C98">
-        <v>2.305</v>
+        <v>3.109</v>
       </c>
       <c r="D98">
-        <v>2.804</v>
+        <v>3.106</v>
       </c>
       <c r="E98">
-        <v>3.626</v>
+        <v>3.821</v>
       </c>
       <c r="F98">
-        <v>3.409</v>
+        <v>4.251</v>
       </c>
       <c r="G98">
-        <v>3.137</v>
+        <v>3.621</v>
       </c>
       <c r="H98">
-        <v>1.182</v>
+        <v>0.911</v>
       </c>
       <c r="I98">
-        <v>1.563</v>
+        <v>1.363</v>
       </c>
       <c r="J98">
-        <v>1.21</v>
+        <v>1.621</v>
       </c>
       <c r="W98" t="s">
         <v>120</v>
@@ -4719,34 +4719,34 @@
     </row>
     <row r="99" spans="1:24">
       <c r="A99" s="2">
-        <v>46231</v>
+        <v>46249</v>
       </c>
       <c r="B99">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C99">
-        <v>2.65</v>
+        <v>3.026</v>
       </c>
       <c r="D99">
-        <v>3.146</v>
+        <v>3.124</v>
       </c>
       <c r="E99">
-        <v>3.48</v>
+        <v>3.788</v>
       </c>
       <c r="F99">
-        <v>3.64</v>
+        <v>4.044</v>
       </c>
       <c r="G99">
-        <v>3.163</v>
+        <v>3.531</v>
       </c>
       <c r="H99">
-        <v>1.452</v>
+        <v>0.895</v>
       </c>
       <c r="I99">
-        <v>1.465</v>
+        <v>1.417</v>
       </c>
       <c r="J99">
-        <v>1.47</v>
+        <v>1.501</v>
       </c>
       <c r="W99" t="s">
         <v>121</v>
@@ -4757,34 +4757,34 @@
     </row>
     <row r="100" spans="1:24">
       <c r="A100" s="2">
-        <v>46231</v>
+        <v>46249</v>
       </c>
       <c r="B100">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C100">
-        <v>2.822</v>
+        <v>2.643</v>
       </c>
       <c r="D100">
-        <v>3.291</v>
+        <v>2.998</v>
       </c>
       <c r="E100">
-        <v>3.594</v>
+        <v>3.906</v>
       </c>
       <c r="F100">
-        <v>3.679</v>
+        <v>3.175</v>
       </c>
       <c r="G100">
-        <v>3.298</v>
+        <v>2.88</v>
       </c>
       <c r="H100">
-        <v>1.006</v>
+        <v>1.013</v>
       </c>
       <c r="I100">
-        <v>1.502</v>
+        <v>1.334</v>
       </c>
       <c r="J100">
-        <v>1.484</v>
+        <v>1.318</v>
       </c>
       <c r="W100" t="s">
         <v>122</v>
@@ -4795,34 +4795,34 @@
     </row>
     <row r="101" spans="1:24">
       <c r="A101" s="2">
-        <v>46231</v>
+        <v>46249</v>
       </c>
       <c r="B101">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C101">
-        <v>2.76</v>
+        <v>2.085</v>
       </c>
       <c r="D101">
-        <v>3.199</v>
+        <v>2.67</v>
       </c>
       <c r="E101">
-        <v>3.322</v>
+        <v>3.552</v>
       </c>
       <c r="F101">
-        <v>3.524</v>
+        <v>2.048</v>
       </c>
       <c r="G101">
-        <v>3.162</v>
+        <v>2.104</v>
       </c>
       <c r="H101">
-        <v>0.953</v>
+        <v>1.021</v>
       </c>
       <c r="I101">
-        <v>1.502</v>
+        <v>1.314</v>
       </c>
       <c r="J101">
-        <v>1.341</v>
+        <v>1.07</v>
       </c>
       <c r="W101" t="s">
         <v>123</v>
@@ -4833,34 +4833,34 @@
     </row>
     <row r="102" spans="1:24">
       <c r="A102" s="2">
-        <v>46231</v>
+        <v>46249</v>
       </c>
       <c r="B102">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C102">
-        <v>2.574</v>
+        <v>1.488</v>
       </c>
       <c r="D102">
-        <v>3.013</v>
+        <v>1.86</v>
       </c>
       <c r="E102">
-        <v>3.461</v>
+        <v>2.56</v>
       </c>
       <c r="F102">
-        <v>2.924</v>
+        <v>1.43</v>
       </c>
       <c r="G102">
-        <v>2.805</v>
+        <v>1.529</v>
       </c>
       <c r="H102">
-        <v>0.998</v>
+        <v>0.928</v>
       </c>
       <c r="I102">
-        <v>1.502</v>
+        <v>0.924</v>
       </c>
       <c r="J102">
-        <v>1.22</v>
+        <v>0.776</v>
       </c>
       <c r="W102" t="s">
         <v>124</v>
@@ -4871,34 +4871,34 @@
     </row>
     <row r="103" spans="1:24">
       <c r="A103" s="2">
-        <v>46231</v>
+        <v>46249</v>
       </c>
       <c r="B103">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C103">
-        <v>2.049</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="D103">
-        <v>2.626</v>
+        <v>0.86</v>
       </c>
       <c r="E103">
-        <v>3.197</v>
+        <v>1.25</v>
       </c>
       <c r="F103">
-        <v>2.215</v>
+        <v>0.455</v>
       </c>
       <c r="G103">
-        <v>2.218</v>
+        <v>0.785</v>
       </c>
       <c r="H103">
-        <v>1.141</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="I103">
-        <v>1.221</v>
+        <v>0.547</v>
       </c>
       <c r="J103">
-        <v>0.996</v>
+        <v>0.463</v>
       </c>
       <c r="W103" t="s">
         <v>125</v>
@@ -4909,34 +4909,34 @@
     </row>
     <row r="104" spans="1:24">
       <c r="A104" s="2">
-        <v>46231</v>
+        <v>46249</v>
       </c>
       <c r="B104">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C104">
-        <v>1.483</v>
+        <v>0.149</v>
       </c>
       <c r="D104">
-        <v>1.85</v>
+        <v>0.233</v>
       </c>
       <c r="E104">
-        <v>2.197</v>
+        <v>0.457</v>
       </c>
       <c r="F104">
-        <v>1.528</v>
+        <v>0.139</v>
       </c>
       <c r="G104">
-        <v>1.471</v>
+        <v>0.187</v>
       </c>
       <c r="H104">
-        <v>0.9409999999999999</v>
+        <v>0.217</v>
       </c>
       <c r="I104">
-        <v>0.892</v>
+        <v>0.15</v>
       </c>
       <c r="J104">
-        <v>0.657</v>
+        <v>0.111</v>
       </c>
       <c r="W104" t="s">
         <v>126</v>
@@ -4947,34 +4947,34 @@
     </row>
     <row r="105" spans="1:24">
       <c r="A105" s="2">
-        <v>46231</v>
+        <v>46249</v>
       </c>
       <c r="B105">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C105">
-        <v>0.8120000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="D105">
-        <v>0.9399999999999999</v>
+        <v>0.021</v>
       </c>
       <c r="E105">
-        <v>1.372</v>
+        <v>0.033</v>
       </c>
       <c r="F105">
-        <v>0.619</v>
+        <v>0</v>
       </c>
       <c r="G105">
-        <v>0.653</v>
+        <v>0</v>
       </c>
       <c r="H105">
-        <v>0.507</v>
+        <v>0</v>
       </c>
       <c r="I105">
-        <v>0.5639999999999999</v>
+        <v>0</v>
       </c>
       <c r="J105">
-        <v>0.284</v>
+        <v>0</v>
       </c>
       <c r="W105" t="s">
         <v>127</v>
@@ -4985,34 +4985,34 @@
     </row>
     <row r="106" spans="1:24">
       <c r="A106" s="2">
-        <v>46231</v>
+        <v>46249</v>
       </c>
       <c r="B106">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C106">
-        <v>0.24</v>
+        <v>0</v>
       </c>
       <c r="D106">
-        <v>0.302</v>
+        <v>0</v>
       </c>
       <c r="E106">
-        <v>0.523</v>
+        <v>0.024</v>
       </c>
       <c r="F106">
-        <v>0.198</v>
+        <v>0</v>
       </c>
       <c r="G106">
-        <v>0.253</v>
+        <v>0</v>
       </c>
       <c r="H106">
-        <v>0.281</v>
+        <v>0</v>
       </c>
       <c r="I106">
-        <v>0.201</v>
+        <v>0</v>
       </c>
       <c r="J106">
-        <v>0.116</v>
+        <v>0</v>
       </c>
       <c r="W106" t="s">
         <v>128</v>
@@ -5023,31 +5023,31 @@
     </row>
     <row r="107" spans="1:24">
       <c r="A107" s="2">
-        <v>46231</v>
+        <v>46249</v>
       </c>
       <c r="B107">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C107">
-        <v>0.041</v>
+        <v>0</v>
       </c>
       <c r="D107">
-        <v>0.074</v>
+        <v>0</v>
       </c>
       <c r="E107">
-        <v>0.101</v>
+        <v>0.037</v>
       </c>
       <c r="F107">
-        <v>0.026</v>
+        <v>0</v>
       </c>
       <c r="G107">
-        <v>0.042</v>
+        <v>0</v>
       </c>
       <c r="H107">
-        <v>0.034</v>
+        <v>0</v>
       </c>
       <c r="I107">
-        <v>0.021</v>
+        <v>0</v>
       </c>
       <c r="J107">
         <v>0</v>
@@ -5061,10 +5061,10 @@
     </row>
     <row r="108" spans="1:24">
       <c r="A108" s="2">
-        <v>46231</v>
+        <v>46249</v>
       </c>
       <c r="B108">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C108">
         <v>0</v>
@@ -5073,7 +5073,7 @@
         <v>0</v>
       </c>
       <c r="E108">
-        <v>0</v>
+        <v>0.026</v>
       </c>
       <c r="F108">
         <v>0</v>
@@ -5088,7 +5088,7 @@
         <v>0</v>
       </c>
       <c r="J108">
-        <v>0</v>
+        <v>0.018</v>
       </c>
       <c r="W108" t="s">
         <v>130</v>
@@ -5099,10 +5099,10 @@
     </row>
     <row r="109" spans="1:24">
       <c r="A109" s="2">
-        <v>46231</v>
+        <v>46250</v>
       </c>
       <c r="B109">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="C109">
         <v>0</v>
@@ -5111,7 +5111,7 @@
         <v>0</v>
       </c>
       <c r="E109">
-        <v>0</v>
+        <v>0.046</v>
       </c>
       <c r="F109">
         <v>0</v>
@@ -5126,7 +5126,7 @@
         <v>0</v>
       </c>
       <c r="J109">
-        <v>0.019</v>
+        <v>0</v>
       </c>
       <c r="W109" t="s">
         <v>131</v>
@@ -5137,10 +5137,10 @@
     </row>
     <row r="110" spans="1:24">
       <c r="A110" s="2">
-        <v>46231</v>
+        <v>46250</v>
       </c>
       <c r="B110">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="C110">
         <v>0</v>
@@ -5149,7 +5149,7 @@
         <v>0</v>
       </c>
       <c r="E110">
-        <v>0</v>
+        <v>0.046</v>
       </c>
       <c r="F110">
         <v>0</v>
@@ -5164,7 +5164,7 @@
         <v>0</v>
       </c>
       <c r="J110">
-        <v>0.019</v>
+        <v>0</v>
       </c>
       <c r="W110" t="s">
         <v>132</v>
@@ -5175,10 +5175,10 @@
     </row>
     <row r="111" spans="1:24">
       <c r="A111" s="2">
-        <v>46232</v>
+        <v>46250</v>
       </c>
       <c r="B111">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C111">
         <v>0</v>
@@ -5187,7 +5187,7 @@
         <v>0</v>
       </c>
       <c r="E111">
-        <v>0</v>
+        <v>0.047</v>
       </c>
       <c r="F111">
         <v>0</v>
@@ -5202,7 +5202,7 @@
         <v>0</v>
       </c>
       <c r="J111">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="W111" t="s">
         <v>133</v>
@@ -5213,10 +5213,10 @@
     </row>
     <row r="112" spans="1:24">
       <c r="A112" s="2">
-        <v>46232</v>
+        <v>46250</v>
       </c>
       <c r="B112">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C112">
         <v>0</v>
@@ -5225,7 +5225,7 @@
         <v>0</v>
       </c>
       <c r="E112">
-        <v>0</v>
+        <v>0.047</v>
       </c>
       <c r="F112">
         <v>0</v>
@@ -5240,7 +5240,7 @@
         <v>0</v>
       </c>
       <c r="J112">
-        <v>0.02</v>
+        <v>0.021</v>
       </c>
       <c r="W112" t="s">
         <v>134</v>
@@ -5251,10 +5251,10 @@
     </row>
     <row r="113" spans="1:24">
       <c r="A113" s="2">
-        <v>46232</v>
+        <v>46250</v>
       </c>
       <c r="B113">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C113">
         <v>0</v>
@@ -5263,7 +5263,7 @@
         <v>0</v>
       </c>
       <c r="E113">
-        <v>0</v>
+        <v>0.059</v>
       </c>
       <c r="F113">
         <v>0</v>
@@ -5278,7 +5278,7 @@
         <v>0</v>
       </c>
       <c r="J113">
-        <v>0.014</v>
+        <v>0.021</v>
       </c>
       <c r="W113" t="s">
         <v>135</v>
@@ -5289,10 +5289,10 @@
     </row>
     <row r="114" spans="1:24">
       <c r="A114" s="2">
-        <v>46232</v>
+        <v>46250</v>
       </c>
       <c r="B114">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C114">
         <v>0</v>
@@ -5301,7 +5301,7 @@
         <v>0</v>
       </c>
       <c r="E114">
-        <v>0</v>
+        <v>0.062</v>
       </c>
       <c r="F114">
         <v>0</v>
@@ -5327,34 +5327,34 @@
     </row>
     <row r="115" spans="1:24">
       <c r="A115" s="2">
-        <v>46232</v>
+        <v>46250</v>
       </c>
       <c r="B115">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C115">
-        <v>0</v>
+        <v>0.024</v>
       </c>
       <c r="D115">
-        <v>0</v>
+        <v>0.022</v>
       </c>
       <c r="E115">
-        <v>0</v>
+        <v>0.076</v>
       </c>
       <c r="F115">
-        <v>0</v>
+        <v>0.136</v>
       </c>
       <c r="G115">
-        <v>0</v>
+        <v>0.052</v>
       </c>
       <c r="H115">
-        <v>0</v>
+        <v>0.034</v>
       </c>
       <c r="I115">
-        <v>0</v>
+        <v>0.034</v>
       </c>
       <c r="J115">
-        <v>0.015</v>
+        <v>0.039</v>
       </c>
       <c r="W115" t="s">
         <v>137</v>
@@ -5365,34 +5365,34 @@
     </row>
     <row r="116" spans="1:24">
       <c r="A116" s="2">
-        <v>46232</v>
+        <v>46250</v>
       </c>
       <c r="B116">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C116">
-        <v>0</v>
+        <v>0.238</v>
       </c>
       <c r="D116">
-        <v>0</v>
+        <v>0.315</v>
       </c>
       <c r="E116">
-        <v>0</v>
+        <v>0.498</v>
       </c>
       <c r="F116">
-        <v>0</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="G116">
-        <v>0</v>
+        <v>0.456</v>
       </c>
       <c r="H116">
-        <v>0</v>
+        <v>0.306</v>
       </c>
       <c r="I116">
-        <v>0</v>
+        <v>0.361</v>
       </c>
       <c r="J116">
-        <v>0.015</v>
+        <v>0.236</v>
       </c>
       <c r="W116" t="s">
         <v>138</v>
@@ -5403,34 +5403,34 @@
     </row>
     <row r="117" spans="1:24">
       <c r="A117" s="2">
-        <v>46232</v>
+        <v>46250</v>
       </c>
       <c r="B117">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C117">
-        <v>0.046</v>
+        <v>1.008</v>
       </c>
       <c r="D117">
-        <v>0.07099999999999999</v>
+        <v>1.047</v>
       </c>
       <c r="E117">
-        <v>0.078</v>
+        <v>1.518</v>
       </c>
       <c r="F117">
-        <v>0.228</v>
+        <v>1.908</v>
       </c>
       <c r="G117">
-        <v>0.106</v>
+        <v>1.465</v>
       </c>
       <c r="H117">
-        <v>0.106</v>
+        <v>0.896</v>
       </c>
       <c r="I117">
-        <v>0.074</v>
+        <v>0.839</v>
       </c>
       <c r="J117">
-        <v>0.059</v>
+        <v>0.772</v>
       </c>
       <c r="W117" t="s">
         <v>139</v>
@@ -5441,34 +5441,34 @@
     </row>
     <row r="118" spans="1:24">
       <c r="A118" s="2">
-        <v>46232</v>
+        <v>46250</v>
       </c>
       <c r="B118">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C118">
-        <v>0.351</v>
+        <v>1.721</v>
       </c>
       <c r="D118">
-        <v>0.4</v>
+        <v>2.048</v>
       </c>
       <c r="E118">
-        <v>0.552</v>
+        <v>2.674</v>
       </c>
       <c r="F118">
-        <v>0.906</v>
+        <v>2.901</v>
       </c>
       <c r="G118">
-        <v>0.499</v>
+        <v>2.246</v>
       </c>
       <c r="H118">
-        <v>0.469</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="I118">
-        <v>0.443</v>
+        <v>1.149</v>
       </c>
       <c r="J118">
-        <v>0.347</v>
+        <v>1.011</v>
       </c>
       <c r="W118" t="s">
         <v>140</v>
@@ -5479,34 +5479,34 @@
     </row>
     <row r="119" spans="1:24">
       <c r="A119" s="2">
-        <v>46232</v>
+        <v>46250</v>
       </c>
       <c r="B119">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C119">
-        <v>1.069</v>
+        <v>2.386</v>
       </c>
       <c r="D119">
-        <v>1.065</v>
+        <v>2.749</v>
       </c>
       <c r="E119">
-        <v>1.434</v>
+        <v>3.596</v>
       </c>
       <c r="F119">
-        <v>2.051</v>
+        <v>3.737</v>
       </c>
       <c r="G119">
-        <v>1.491</v>
+        <v>2.879</v>
       </c>
       <c r="H119">
-        <v>0.868</v>
+        <v>0.786</v>
       </c>
       <c r="I119">
-        <v>0.909</v>
+        <v>1.437</v>
       </c>
       <c r="J119">
-        <v>0.829</v>
+        <v>1.308</v>
       </c>
       <c r="W119" t="s">
         <v>141</v>
@@ -5517,34 +5517,34 @@
     </row>
     <row r="120" spans="1:24">
       <c r="A120" s="2">
-        <v>46232</v>
+        <v>46250</v>
       </c>
       <c r="B120">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C120">
-        <v>1.792</v>
+        <v>2.863</v>
       </c>
       <c r="D120">
-        <v>2.05</v>
+        <v>3.081</v>
       </c>
       <c r="E120">
-        <v>2.441</v>
+        <v>4.035</v>
       </c>
       <c r="F120">
-        <v>2.944</v>
+        <v>4.096</v>
       </c>
       <c r="G120">
-        <v>2.316</v>
+        <v>3.381</v>
       </c>
       <c r="H120">
-        <v>1.271</v>
+        <v>1.176</v>
       </c>
       <c r="I120">
-        <v>1.181</v>
+        <v>1.445</v>
       </c>
       <c r="J120">
-        <v>1.089</v>
+        <v>1.475</v>
       </c>
       <c r="W120" t="s">
         <v>142</v>
@@ -5555,34 +5555,34 @@
     </row>
     <row r="121" spans="1:24">
       <c r="A121" s="2">
-        <v>46232</v>
+        <v>46250</v>
       </c>
       <c r="B121">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C121">
-        <v>2.456</v>
+        <v>3.08</v>
       </c>
       <c r="D121">
-        <v>2.742</v>
+        <v>3.088</v>
       </c>
       <c r="E121">
-        <v>3.097</v>
+        <v>3.91</v>
       </c>
       <c r="F121">
-        <v>3.562</v>
+        <v>4.188</v>
       </c>
       <c r="G121">
-        <v>2.974</v>
+        <v>3.578</v>
       </c>
       <c r="H121">
-        <v>0.803</v>
+        <v>1.458</v>
       </c>
       <c r="I121">
-        <v>1.472</v>
+        <v>1.445</v>
       </c>
       <c r="J121">
-        <v>1.434</v>
+        <v>1.631</v>
       </c>
       <c r="W121" t="s">
         <v>143</v>
@@ -5593,34 +5593,34 @@
     </row>
     <row r="122" spans="1:24">
       <c r="A122" s="2">
-        <v>46232</v>
+        <v>46250</v>
       </c>
       <c r="B122">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C122">
-        <v>2.851</v>
+        <v>3.141</v>
       </c>
       <c r="D122">
-        <v>3.175</v>
+        <v>3.097</v>
       </c>
       <c r="E122">
-        <v>3.369</v>
+        <v>3.856</v>
       </c>
       <c r="F122">
-        <v>4.13</v>
+        <v>4.198</v>
       </c>
       <c r="G122">
-        <v>3.416</v>
+        <v>3.594</v>
       </c>
       <c r="H122">
-        <v>0.8139999999999999</v>
+        <v>0.978</v>
       </c>
       <c r="I122">
-        <v>1.465</v>
+        <v>1.502</v>
       </c>
       <c r="J122">
-        <v>1.388</v>
+        <v>1.57</v>
       </c>
       <c r="W122" t="s">
         <v>144</v>
@@ -5631,34 +5631,34 @@
     </row>
     <row r="123" spans="1:24">
       <c r="A123" s="2">
-        <v>46232</v>
+        <v>46250</v>
       </c>
       <c r="B123">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C123">
-        <v>3.098</v>
+        <v>3.006</v>
       </c>
       <c r="D123">
-        <v>3.331</v>
+        <v>3.116</v>
       </c>
       <c r="E123">
-        <v>3.541</v>
+        <v>3.881</v>
       </c>
       <c r="F123">
-        <v>4.182</v>
+        <v>4.018</v>
       </c>
       <c r="G123">
-        <v>3.549</v>
+        <v>3.461</v>
       </c>
       <c r="H123">
-        <v>1.242</v>
+        <v>1.054</v>
       </c>
       <c r="I123">
-        <v>1.445</v>
+        <v>1.502</v>
       </c>
       <c r="J123">
-        <v>1.526</v>
+        <v>1.548</v>
       </c>
       <c r="W123" t="s">
         <v>145</v>
@@ -5669,34 +5669,34 @@
     </row>
     <row r="124" spans="1:24">
       <c r="A124" s="2">
-        <v>46232</v>
+        <v>46250</v>
       </c>
       <c r="B124">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C124">
-        <v>3.143</v>
+        <v>2.646</v>
       </c>
       <c r="D124">
-        <v>3.409</v>
+        <v>2.996</v>
       </c>
       <c r="E124">
-        <v>3.41</v>
+        <v>3.888</v>
       </c>
       <c r="F124">
-        <v>4.205</v>
+        <v>3.393</v>
       </c>
       <c r="G124">
-        <v>3.575</v>
+        <v>3.12</v>
       </c>
       <c r="H124">
-        <v>0.835</v>
+        <v>1.109</v>
       </c>
       <c r="I124">
-        <v>1.502</v>
+        <v>1.506</v>
       </c>
       <c r="J124">
-        <v>1.433</v>
+        <v>1.285</v>
       </c>
       <c r="W124" t="s">
         <v>146</v>
@@ -5707,34 +5707,34 @@
     </row>
     <row r="125" spans="1:24">
       <c r="A125" s="2">
-        <v>46232</v>
+        <v>46250</v>
       </c>
       <c r="B125">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C125">
-        <v>3.018</v>
+        <v>2.076</v>
       </c>
       <c r="D125">
-        <v>3.293</v>
+        <v>2.659</v>
       </c>
       <c r="E125">
-        <v>3.382</v>
+        <v>3.473</v>
       </c>
       <c r="F125">
-        <v>3.982</v>
+        <v>2.416</v>
       </c>
       <c r="G125">
-        <v>3.522</v>
+        <v>2.556</v>
       </c>
       <c r="H125">
-        <v>0.833</v>
+        <v>1.137</v>
       </c>
       <c r="I125">
-        <v>1.502</v>
+        <v>1.487</v>
       </c>
       <c r="J125">
-        <v>1.365</v>
+        <v>1.07</v>
       </c>
       <c r="W125" t="s">
         <v>147</v>
@@ -5745,34 +5745,34 @@
     </row>
     <row r="126" spans="1:24">
       <c r="A126" s="2">
-        <v>46232</v>
+        <v>46250</v>
       </c>
       <c r="B126">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C126">
-        <v>2.732</v>
+        <v>1.488</v>
       </c>
       <c r="D126">
-        <v>3.2</v>
+        <v>1.821</v>
       </c>
       <c r="E126">
-        <v>3.416</v>
+        <v>2.476</v>
       </c>
       <c r="F126">
-        <v>3.391</v>
+        <v>1.489</v>
       </c>
       <c r="G126">
-        <v>3.165</v>
+        <v>1.74</v>
       </c>
       <c r="H126">
-        <v>0.744</v>
+        <v>0.996</v>
       </c>
       <c r="I126">
-        <v>1.502</v>
+        <v>1.049</v>
       </c>
       <c r="J126">
-        <v>1.172</v>
+        <v>0.695</v>
       </c>
       <c r="W126" t="s">
         <v>148</v>
@@ -5783,34 +5783,34 @@
     </row>
     <row r="127" spans="1:24">
       <c r="A127" s="2">
-        <v>46232</v>
+        <v>46250</v>
       </c>
       <c r="B127">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C127">
-        <v>2.189</v>
+        <v>0.637</v>
       </c>
       <c r="D127">
-        <v>2.693</v>
+        <v>0.83</v>
       </c>
       <c r="E127">
-        <v>2.964</v>
+        <v>1.264</v>
       </c>
       <c r="F127">
-        <v>2.556</v>
+        <v>0.55</v>
       </c>
       <c r="G127">
-        <v>2.581</v>
+        <v>1.014</v>
       </c>
       <c r="H127">
-        <v>0.843</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="I127">
-        <v>1.502</v>
+        <v>0.57</v>
       </c>
       <c r="J127">
-        <v>1.017</v>
+        <v>0.445</v>
       </c>
       <c r="W127" t="s">
         <v>149</v>
@@ -5821,34 +5821,34 @@
     </row>
     <row r="128" spans="1:24">
       <c r="A128" s="2">
-        <v>46232</v>
+        <v>46250</v>
       </c>
       <c r="B128">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C128">
-        <v>1.575</v>
+        <v>0.16</v>
       </c>
       <c r="D128">
-        <v>1.806</v>
+        <v>0.234</v>
       </c>
       <c r="E128">
-        <v>2.229</v>
+        <v>0.457</v>
       </c>
       <c r="F128">
-        <v>1.604</v>
+        <v>0.165</v>
       </c>
       <c r="G128">
-        <v>1.734</v>
+        <v>0.216</v>
       </c>
       <c r="H128">
-        <v>0.793</v>
+        <v>0.217</v>
       </c>
       <c r="I128">
-        <v>1.09</v>
+        <v>0.15</v>
       </c>
       <c r="J128">
-        <v>0.66</v>
+        <v>0.089</v>
       </c>
       <c r="W128" t="s">
         <v>150</v>
@@ -5859,34 +5859,34 @@
     </row>
     <row r="129" spans="1:24">
       <c r="A129" s="2">
-        <v>46232</v>
+        <v>46250</v>
       </c>
       <c r="B129">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C129">
-        <v>0.827</v>
+        <v>0.014</v>
       </c>
       <c r="D129">
-        <v>0.9340000000000001</v>
+        <v>0.022</v>
       </c>
       <c r="E129">
-        <v>1.36</v>
+        <v>0.032</v>
       </c>
       <c r="F129">
-        <v>0.679</v>
+        <v>0</v>
       </c>
       <c r="G129">
-        <v>0.899</v>
+        <v>0</v>
       </c>
       <c r="H129">
-        <v>0.655</v>
+        <v>0</v>
       </c>
       <c r="I129">
-        <v>0.652</v>
+        <v>0</v>
       </c>
       <c r="J129">
-        <v>0.262</v>
+        <v>0</v>
       </c>
       <c r="W129" t="s">
         <v>151</v>
@@ -5897,34 +5897,34 @@
     </row>
     <row r="130" spans="1:24">
       <c r="A130" s="2">
-        <v>46232</v>
+        <v>46250</v>
       </c>
       <c r="B130">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C130">
-        <v>0.205</v>
+        <v>0</v>
       </c>
       <c r="D130">
-        <v>0.302</v>
+        <v>0</v>
       </c>
       <c r="E130">
-        <v>0.519</v>
+        <v>0.018</v>
       </c>
       <c r="F130">
-        <v>0.193</v>
+        <v>0</v>
       </c>
       <c r="G130">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="H130">
-        <v>0.326</v>
+        <v>0</v>
       </c>
       <c r="I130">
-        <v>0.301</v>
+        <v>0</v>
       </c>
       <c r="J130">
-        <v>0.093</v>
+        <v>0</v>
       </c>
       <c r="W130" t="s">
         <v>152</v>
@@ -5935,31 +5935,31 @@
     </row>
     <row r="131" spans="1:24">
       <c r="A131" s="2">
-        <v>46232</v>
+        <v>46250</v>
       </c>
       <c r="B131">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C131">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="D131">
-        <v>0.074</v>
+        <v>0</v>
       </c>
       <c r="E131">
-        <v>0.092</v>
+        <v>0.024</v>
       </c>
       <c r="F131">
-        <v>0.025</v>
+        <v>0</v>
       </c>
       <c r="G131">
-        <v>0.042</v>
+        <v>0</v>
       </c>
       <c r="H131">
-        <v>0.044</v>
+        <v>0</v>
       </c>
       <c r="I131">
-        <v>0.025</v>
+        <v>0</v>
       </c>
       <c r="J131">
         <v>0</v>
@@ -5973,10 +5973,10 @@
     </row>
     <row r="132" spans="1:24">
       <c r="A132" s="2">
-        <v>46232</v>
+        <v>46250</v>
       </c>
       <c r="B132">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C132">
         <v>0</v>
@@ -5985,7 +5985,7 @@
         <v>0</v>
       </c>
       <c r="E132">
-        <v>0</v>
+        <v>0.024</v>
       </c>
       <c r="F132">
         <v>0</v>
@@ -6000,7 +6000,7 @@
         <v>0</v>
       </c>
       <c r="J132">
-        <v>0.012</v>
+        <v>0</v>
       </c>
       <c r="W132" t="s">
         <v>154</v>
@@ -6011,10 +6011,10 @@
     </row>
     <row r="133" spans="1:24">
       <c r="A133" s="2">
-        <v>46232</v>
+        <v>46251</v>
       </c>
       <c r="B133">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="C133">
         <v>0</v>
@@ -6023,7 +6023,7 @@
         <v>0</v>
       </c>
       <c r="E133">
-        <v>0.015</v>
+        <v>0.025</v>
       </c>
       <c r="F133">
         <v>0</v>
@@ -6038,7 +6038,7 @@
         <v>0</v>
       </c>
       <c r="J133">
-        <v>0.014</v>
+        <v>0</v>
       </c>
       <c r="W133" t="s">
         <v>155</v>
@@ -6049,10 +6049,10 @@
     </row>
     <row r="134" spans="1:24">
       <c r="A134" s="2">
-        <v>46232</v>
+        <v>46251</v>
       </c>
       <c r="B134">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="C134">
         <v>0</v>
@@ -6061,7 +6061,7 @@
         <v>0</v>
       </c>
       <c r="E134">
-        <v>0</v>
+        <v>0.063</v>
       </c>
       <c r="F134">
         <v>0</v>
@@ -6076,7 +6076,7 @@
         <v>0</v>
       </c>
       <c r="J134">
-        <v>0.019</v>
+        <v>0</v>
       </c>
       <c r="W134" t="s">
         <v>156</v>
@@ -6087,10 +6087,10 @@
     </row>
     <row r="135" spans="1:24">
       <c r="A135" s="2">
-        <v>46233</v>
+        <v>46251</v>
       </c>
       <c r="B135">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C135">
         <v>0</v>
@@ -6099,7 +6099,7 @@
         <v>0</v>
       </c>
       <c r="E135">
-        <v>0</v>
+        <v>0.045</v>
       </c>
       <c r="F135">
         <v>0</v>
@@ -6125,10 +6125,10 @@
     </row>
     <row r="136" spans="1:24">
       <c r="A136" s="2">
-        <v>46233</v>
+        <v>46251</v>
       </c>
       <c r="B136">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C136">
         <v>0</v>
@@ -6137,7 +6137,7 @@
         <v>0</v>
       </c>
       <c r="E136">
-        <v>0</v>
+        <v>0.049</v>
       </c>
       <c r="F136">
         <v>0</v>
@@ -6152,7 +6152,7 @@
         <v>0</v>
       </c>
       <c r="J136">
-        <v>0.015</v>
+        <v>0</v>
       </c>
       <c r="W136" t="s">
         <v>158</v>
@@ -6163,10 +6163,10 @@
     </row>
     <row r="137" spans="1:24">
       <c r="A137" s="2">
-        <v>46233</v>
+        <v>46251</v>
       </c>
       <c r="B137">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C137">
         <v>0</v>
@@ -6175,7 +6175,7 @@
         <v>0</v>
       </c>
       <c r="E137">
-        <v>0</v>
+        <v>0.047</v>
       </c>
       <c r="F137">
         <v>0</v>
@@ -6190,7 +6190,7 @@
         <v>0</v>
       </c>
       <c r="J137">
-        <v>0.015</v>
+        <v>0.021</v>
       </c>
       <c r="W137" t="s">
         <v>159</v>
@@ -6201,10 +6201,10 @@
     </row>
     <row r="138" spans="1:24">
       <c r="A138" s="2">
-        <v>46233</v>
+        <v>46251</v>
       </c>
       <c r="B138">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C138">
         <v>0</v>
@@ -6213,7 +6213,7 @@
         <v>0</v>
       </c>
       <c r="E138">
-        <v>0</v>
+        <v>0.048</v>
       </c>
       <c r="F138">
         <v>0</v>
@@ -6239,34 +6239,34 @@
     </row>
     <row r="139" spans="1:24">
       <c r="A139" s="2">
-        <v>46233</v>
+        <v>46251</v>
       </c>
       <c r="B139">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C139">
-        <v>0</v>
+        <v>0.024</v>
       </c>
       <c r="D139">
-        <v>0</v>
+        <v>0.022</v>
       </c>
       <c r="E139">
-        <v>0</v>
+        <v>0.059</v>
       </c>
       <c r="F139">
-        <v>0</v>
+        <v>0.136</v>
       </c>
       <c r="G139">
-        <v>0</v>
+        <v>0.052</v>
       </c>
       <c r="H139">
-        <v>0</v>
+        <v>0.034</v>
       </c>
       <c r="I139">
-        <v>0</v>
+        <v>0.034</v>
       </c>
       <c r="J139">
-        <v>0.015</v>
+        <v>0.045</v>
       </c>
       <c r="W139" t="s">
         <v>161</v>
@@ -6277,34 +6277,34 @@
     </row>
     <row r="140" spans="1:24">
       <c r="A140" s="2">
-        <v>46233</v>
+        <v>46251</v>
       </c>
       <c r="B140">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C140">
-        <v>0</v>
+        <v>0.251</v>
       </c>
       <c r="D140">
-        <v>0</v>
+        <v>0.315</v>
       </c>
       <c r="E140">
-        <v>0</v>
+        <v>0.483</v>
       </c>
       <c r="F140">
-        <v>0</v>
+        <v>0.753</v>
       </c>
       <c r="G140">
-        <v>0</v>
+        <v>0.455</v>
       </c>
       <c r="H140">
-        <v>0</v>
+        <v>0.347</v>
       </c>
       <c r="I140">
-        <v>0</v>
+        <v>0.361</v>
       </c>
       <c r="J140">
-        <v>0.015</v>
+        <v>0.265</v>
       </c>
       <c r="W140" t="s">
         <v>162</v>
@@ -6315,34 +6315,34 @@
     </row>
     <row r="141" spans="1:24">
       <c r="A141" s="2">
-        <v>46233</v>
+        <v>46251</v>
       </c>
       <c r="B141">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C141">
-        <v>0.046</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="D141">
-        <v>0.07099999999999999</v>
+        <v>0.957</v>
       </c>
       <c r="E141">
-        <v>0.07000000000000001</v>
+        <v>1.44</v>
       </c>
       <c r="F141">
-        <v>0.228</v>
+        <v>1.952</v>
       </c>
       <c r="G141">
-        <v>0.106</v>
+        <v>1.341</v>
       </c>
       <c r="H141">
-        <v>0.106</v>
+        <v>0.889</v>
       </c>
       <c r="I141">
-        <v>0.074</v>
+        <v>0.894</v>
       </c>
       <c r="J141">
-        <v>0.059</v>
+        <v>0.785</v>
       </c>
       <c r="W141" t="s">
         <v>163</v>
@@ -6353,34 +6353,34 @@
     </row>
     <row r="142" spans="1:24">
       <c r="A142" s="2">
-        <v>46233</v>
+        <v>46251</v>
       </c>
       <c r="B142">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C142">
-        <v>0.365</v>
+        <v>1.705</v>
       </c>
       <c r="D142">
-        <v>0.401</v>
+        <v>1.965</v>
       </c>
       <c r="E142">
-        <v>0.537</v>
+        <v>2.596</v>
       </c>
       <c r="F142">
-        <v>0.923</v>
+        <v>2.887</v>
       </c>
       <c r="G142">
-        <v>0.519</v>
+        <v>2.296</v>
       </c>
       <c r="H142">
-        <v>0.46</v>
+        <v>0.93</v>
       </c>
       <c r="I142">
-        <v>0.443</v>
+        <v>1.163</v>
       </c>
       <c r="J142">
-        <v>0.453</v>
+        <v>1.086</v>
       </c>
       <c r="W142" t="s">
         <v>164</v>
@@ -6391,34 +6391,34 @@
     </row>
     <row r="143" spans="1:24">
       <c r="A143" s="2">
-        <v>46233</v>
+        <v>46251</v>
       </c>
       <c r="B143">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C143">
-        <v>1.037</v>
+        <v>2.32</v>
       </c>
       <c r="D143">
-        <v>1.063</v>
+        <v>2.745</v>
       </c>
       <c r="E143">
-        <v>1.585</v>
+        <v>3.576</v>
       </c>
       <c r="F143">
-        <v>2.083</v>
+        <v>3.727</v>
       </c>
       <c r="G143">
-        <v>1.448</v>
+        <v>2.918</v>
       </c>
       <c r="H143">
-        <v>0.803</v>
+        <v>1.204</v>
       </c>
       <c r="I143">
-        <v>0.899</v>
+        <v>1.437</v>
       </c>
       <c r="J143">
-        <v>0.7</v>
+        <v>1.348</v>
       </c>
       <c r="W143" t="s">
         <v>165</v>
@@ -6429,34 +6429,34 @@
     </row>
     <row r="144" spans="1:24">
       <c r="A144" s="2">
-        <v>46233</v>
+        <v>46251</v>
       </c>
       <c r="B144">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C144">
-        <v>1.786</v>
+        <v>2.772</v>
       </c>
       <c r="D144">
-        <v>2.049</v>
+        <v>2.961</v>
       </c>
       <c r="E144">
-        <v>2.461</v>
+        <v>3.972</v>
       </c>
       <c r="F144">
-        <v>2.982</v>
+        <v>4.095</v>
       </c>
       <c r="G144">
-        <v>2.359</v>
+        <v>3.404</v>
       </c>
       <c r="H144">
-        <v>1.263</v>
+        <v>1.469</v>
       </c>
       <c r="I144">
-        <v>1.227</v>
+        <v>1.445</v>
       </c>
       <c r="J144">
-        <v>1.002</v>
+        <v>1.475</v>
       </c>
       <c r="W144" t="s">
         <v>166</v>
@@ -6467,34 +6467,34 @@
     </row>
     <row r="145" spans="1:24">
       <c r="A145" s="2">
-        <v>46233</v>
+        <v>46251</v>
       </c>
       <c r="B145">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C145">
-        <v>2.343</v>
+        <v>3.079</v>
       </c>
       <c r="D145">
-        <v>2.6</v>
+        <v>3.088</v>
       </c>
       <c r="E145">
-        <v>3.597</v>
+        <v>3.911</v>
       </c>
       <c r="F145">
-        <v>3.743</v>
+        <v>4.186</v>
       </c>
       <c r="G145">
-        <v>3.047</v>
+        <v>3.543</v>
       </c>
       <c r="H145">
-        <v>0.8</v>
+        <v>1.495</v>
       </c>
       <c r="I145">
-        <v>1.472</v>
+        <v>1.445</v>
       </c>
       <c r="J145">
-        <v>1.451</v>
+        <v>1.519</v>
       </c>
       <c r="W145" t="s">
         <v>167</v>
@@ -6505,34 +6505,34 @@
     </row>
     <row r="146" spans="1:24">
       <c r="A146" s="2">
-        <v>46233</v>
+        <v>46251</v>
       </c>
       <c r="B146">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C146">
-        <v>2.64</v>
+        <v>3.136</v>
       </c>
       <c r="D146">
-        <v>3.073</v>
+        <v>3.097</v>
       </c>
       <c r="E146">
-        <v>3.917</v>
+        <v>3.847</v>
       </c>
       <c r="F146">
-        <v>3.921</v>
+        <v>4.184</v>
       </c>
       <c r="G146">
-        <v>3.271</v>
+        <v>3.594</v>
       </c>
       <c r="H146">
-        <v>1.253</v>
+        <v>1.094</v>
       </c>
       <c r="I146">
-        <v>1.465</v>
+        <v>1.502</v>
       </c>
       <c r="J146">
-        <v>1.632</v>
+        <v>1.57</v>
       </c>
       <c r="W146" t="s">
         <v>168</v>
@@ -6543,34 +6543,34 @@
     </row>
     <row r="147" spans="1:24">
       <c r="A147" s="2">
-        <v>46233</v>
+        <v>46251</v>
       </c>
       <c r="B147">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C147">
-        <v>2.874</v>
+        <v>2.981</v>
       </c>
       <c r="D147">
-        <v>3.044</v>
+        <v>3.129</v>
       </c>
       <c r="E147">
-        <v>3.548</v>
+        <v>3.853</v>
       </c>
       <c r="F147">
-        <v>3.832</v>
+        <v>4.008</v>
       </c>
       <c r="G147">
-        <v>3.325</v>
+        <v>3.526</v>
       </c>
       <c r="H147">
-        <v>1.407</v>
+        <v>0.93</v>
       </c>
       <c r="I147">
-        <v>1.445</v>
+        <v>1.502</v>
       </c>
       <c r="J147">
-        <v>1.607</v>
+        <v>1.548</v>
       </c>
       <c r="W147" t="s">
         <v>169</v>
@@ -6581,34 +6581,34 @@
     </row>
     <row r="148" spans="1:24">
       <c r="A148" s="2">
-        <v>46233</v>
+        <v>46251</v>
       </c>
       <c r="B148">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C148">
-        <v>3.058</v>
+        <v>2.62</v>
       </c>
       <c r="D148">
-        <v>3.273</v>
+        <v>2.996</v>
       </c>
       <c r="E148">
-        <v>3.636</v>
+        <v>3.873</v>
       </c>
       <c r="F148">
-        <v>3.81</v>
+        <v>3.413</v>
       </c>
       <c r="G148">
-        <v>3.351</v>
+        <v>3.173</v>
       </c>
       <c r="H148">
-        <v>0.835</v>
+        <v>0.769</v>
       </c>
       <c r="I148">
-        <v>1.502</v>
+        <v>1.506</v>
       </c>
       <c r="J148">
-        <v>1.463</v>
+        <v>1.285</v>
       </c>
       <c r="W148" t="s">
         <v>170</v>
@@ -6619,34 +6619,34 @@
     </row>
     <row r="149" spans="1:24">
       <c r="A149" s="2">
-        <v>46233</v>
+        <v>46251</v>
       </c>
       <c r="B149">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C149">
-        <v>3.031</v>
+        <v>2.04</v>
       </c>
       <c r="D149">
-        <v>3.158</v>
+        <v>2.677</v>
       </c>
       <c r="E149">
-        <v>3.648</v>
+        <v>3.502</v>
       </c>
       <c r="F149">
-        <v>3.631</v>
+        <v>2.407</v>
       </c>
       <c r="G149">
-        <v>3.321</v>
+        <v>2.564</v>
       </c>
       <c r="H149">
-        <v>0.763</v>
+        <v>0.779</v>
       </c>
       <c r="I149">
-        <v>1.502</v>
+        <v>1.487</v>
       </c>
       <c r="J149">
-        <v>1.43</v>
+        <v>1.07</v>
       </c>
       <c r="W149" t="s">
         <v>171</v>
@@ -6657,34 +6657,34 @@
     </row>
     <row r="150" spans="1:24">
       <c r="A150" s="2">
-        <v>46233</v>
+        <v>46251</v>
       </c>
       <c r="B150">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C150">
-        <v>2.562</v>
+        <v>1.483</v>
       </c>
       <c r="D150">
-        <v>3.04</v>
+        <v>1.821</v>
       </c>
       <c r="E150">
-        <v>3.715</v>
+        <v>2.525</v>
       </c>
       <c r="F150">
-        <v>3.174</v>
+        <v>1.502</v>
       </c>
       <c r="G150">
-        <v>2.983</v>
+        <v>1.812</v>
       </c>
       <c r="H150">
-        <v>0.839</v>
+        <v>0.665</v>
       </c>
       <c r="I150">
-        <v>1.502</v>
+        <v>0.799</v>
       </c>
       <c r="J150">
-        <v>1.156</v>
+        <v>0.707</v>
       </c>
       <c r="W150" t="s">
         <v>172</v>
@@ -6695,34 +6695,34 @@
     </row>
     <row r="151" spans="1:24">
       <c r="A151" s="2">
-        <v>46233</v>
+        <v>46251</v>
       </c>
       <c r="B151">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C151">
-        <v>1.98</v>
+        <v>0.641</v>
       </c>
       <c r="D151">
-        <v>2.683</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="E151">
-        <v>3.19</v>
+        <v>1.316</v>
       </c>
       <c r="F151">
-        <v>2.415</v>
+        <v>0.533</v>
       </c>
       <c r="G151">
-        <v>2.35</v>
+        <v>1.014</v>
       </c>
       <c r="H151">
-        <v>0.992</v>
+        <v>0.537</v>
       </c>
       <c r="I151">
-        <v>1.483</v>
+        <v>0.547</v>
       </c>
       <c r="J151">
-        <v>1.017</v>
+        <v>0.389</v>
       </c>
       <c r="W151" t="s">
         <v>173</v>
@@ -6733,34 +6733,34 @@
     </row>
     <row r="152" spans="1:24">
       <c r="A152" s="2">
-        <v>46233</v>
+        <v>46251</v>
       </c>
       <c r="B152">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C152">
-        <v>1.378</v>
+        <v>0.151</v>
       </c>
       <c r="D152">
-        <v>1.819</v>
+        <v>0.207</v>
       </c>
       <c r="E152">
-        <v>2.298</v>
+        <v>0.452</v>
       </c>
       <c r="F152">
-        <v>1.593</v>
+        <v>0.161</v>
       </c>
       <c r="G152">
-        <v>1.59</v>
+        <v>0.21</v>
       </c>
       <c r="H152">
-        <v>0.944</v>
+        <v>0.213</v>
       </c>
       <c r="I152">
-        <v>1.09</v>
+        <v>0.15</v>
       </c>
       <c r="J152">
-        <v>0.68</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="W152" t="s">
         <v>174</v>
@@ -6771,34 +6771,34 @@
     </row>
     <row r="153" spans="1:24">
       <c r="A153" s="2">
-        <v>46233</v>
+        <v>46251</v>
       </c>
       <c r="B153">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C153">
-        <v>0.747</v>
+        <v>0.011</v>
       </c>
       <c r="D153">
-        <v>0.9419999999999999</v>
+        <v>0.016</v>
       </c>
       <c r="E153">
-        <v>1.391</v>
+        <v>0.032</v>
       </c>
       <c r="F153">
-        <v>0.677</v>
+        <v>0</v>
       </c>
       <c r="G153">
-        <v>0.825</v>
+        <v>0</v>
       </c>
       <c r="H153">
-        <v>0.655</v>
+        <v>0</v>
       </c>
       <c r="I153">
-        <v>0.652</v>
+        <v>0</v>
       </c>
       <c r="J153">
-        <v>0.262</v>
+        <v>0</v>
       </c>
       <c r="W153" t="s">
         <v>175</v>
@@ -6809,34 +6809,34 @@
     </row>
     <row r="154" spans="1:24">
       <c r="A154" s="2">
-        <v>46233</v>
+        <v>46251</v>
       </c>
       <c r="B154">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C154">
-        <v>0.248</v>
+        <v>0</v>
       </c>
       <c r="D154">
-        <v>0.303</v>
+        <v>0</v>
       </c>
       <c r="E154">
-        <v>0.481</v>
+        <v>0.016</v>
       </c>
       <c r="F154">
-        <v>0.195</v>
+        <v>0</v>
       </c>
       <c r="G154">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="H154">
-        <v>0.326</v>
+        <v>0</v>
       </c>
       <c r="I154">
-        <v>0.328</v>
+        <v>0</v>
       </c>
       <c r="J154">
-        <v>0.121</v>
+        <v>0</v>
       </c>
       <c r="W154" t="s">
         <v>176</v>
@@ -6847,31 +6847,31 @@
     </row>
     <row r="155" spans="1:24">
       <c r="A155" s="2">
-        <v>46233</v>
+        <v>46251</v>
       </c>
       <c r="B155">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C155">
-        <v>0.048</v>
+        <v>0</v>
       </c>
       <c r="D155">
-        <v>0.074</v>
+        <v>0</v>
       </c>
       <c r="E155">
-        <v>0.094</v>
+        <v>0.017</v>
       </c>
       <c r="F155">
-        <v>0.026</v>
+        <v>0</v>
       </c>
       <c r="G155">
-        <v>0.042</v>
+        <v>0</v>
       </c>
       <c r="H155">
-        <v>0.044</v>
+        <v>0</v>
       </c>
       <c r="I155">
-        <v>0.025</v>
+        <v>0</v>
       </c>
       <c r="J155">
         <v>0</v>
@@ -6885,10 +6885,10 @@
     </row>
     <row r="156" spans="1:24">
       <c r="A156" s="2">
-        <v>46233</v>
+        <v>46251</v>
       </c>
       <c r="B156">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C156">
         <v>0</v>
@@ -6897,7 +6897,7 @@
         <v>0</v>
       </c>
       <c r="E156">
-        <v>0</v>
+        <v>0.018</v>
       </c>
       <c r="F156">
         <v>0</v>
@@ -6923,10 +6923,10 @@
     </row>
     <row r="157" spans="1:24">
       <c r="A157" s="2">
-        <v>46233</v>
+        <v>46252</v>
       </c>
       <c r="B157">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="C157">
         <v>0</v>
@@ -6935,7 +6935,7 @@
         <v>0</v>
       </c>
       <c r="E157">
-        <v>0</v>
+        <v>0.041</v>
       </c>
       <c r="F157">
         <v>0</v>
@@ -6950,7 +6950,7 @@
         <v>0</v>
       </c>
       <c r="J157">
-        <v>0</v>
+        <v>0.014</v>
       </c>
       <c r="W157" t="s">
         <v>179</v>
@@ -6961,10 +6961,10 @@
     </row>
     <row r="158" spans="1:24">
       <c r="A158" s="2">
-        <v>46233</v>
+        <v>46252</v>
       </c>
       <c r="B158">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="C158">
         <v>0</v>
@@ -6973,7 +6973,7 @@
         <v>0</v>
       </c>
       <c r="E158">
-        <v>0</v>
+        <v>0.045</v>
       </c>
       <c r="F158">
         <v>0</v>
@@ -6999,10 +6999,10 @@
     </row>
     <row r="159" spans="1:24">
       <c r="A159" s="2">
-        <v>46234</v>
+        <v>46252</v>
       </c>
       <c r="B159">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C159">
         <v>0</v>
@@ -7011,7 +7011,7 @@
         <v>0</v>
       </c>
       <c r="E159">
-        <v>0</v>
+        <v>0.032</v>
       </c>
       <c r="F159">
         <v>0</v>
@@ -7026,7 +7026,7 @@
         <v>0</v>
       </c>
       <c r="J159">
-        <v>0.015</v>
+        <v>0.02</v>
       </c>
       <c r="W159" t="s">
         <v>181</v>
@@ -7037,10 +7037,10 @@
     </row>
     <row r="160" spans="1:24">
       <c r="A160" s="2">
-        <v>46234</v>
+        <v>46252</v>
       </c>
       <c r="B160">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C160">
         <v>0</v>
@@ -7049,7 +7049,7 @@
         <v>0</v>
       </c>
       <c r="E160">
-        <v>0</v>
+        <v>0.033</v>
       </c>
       <c r="F160">
         <v>0</v>
@@ -7064,7 +7064,7 @@
         <v>0</v>
       </c>
       <c r="J160">
-        <v>0</v>
+        <v>0.021</v>
       </c>
       <c r="W160" t="s">
         <v>182</v>
@@ -7075,10 +7075,10 @@
     </row>
     <row r="161" spans="1:24">
       <c r="A161" s="2">
-        <v>46234</v>
+        <v>46252</v>
       </c>
       <c r="B161">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C161">
         <v>0</v>
@@ -7087,7 +7087,7 @@
         <v>0</v>
       </c>
       <c r="E161">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="F161">
         <v>0</v>
@@ -7102,7 +7102,7 @@
         <v>0</v>
       </c>
       <c r="J161">
-        <v>0.015</v>
+        <v>0.021</v>
       </c>
       <c r="W161" t="s">
         <v>183</v>
@@ -7113,10 +7113,10 @@
     </row>
     <row r="162" spans="1:24">
       <c r="A162" s="2">
-        <v>46234</v>
+        <v>46252</v>
       </c>
       <c r="B162">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C162">
         <v>0</v>
@@ -7125,7 +7125,7 @@
         <v>0</v>
       </c>
       <c r="E162">
-        <v>0</v>
+        <v>0.049</v>
       </c>
       <c r="F162">
         <v>0</v>
@@ -7151,34 +7151,34 @@
     </row>
     <row r="163" spans="1:24">
       <c r="A163" s="2">
-        <v>46234</v>
+        <v>46252</v>
       </c>
       <c r="B163">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C163">
-        <v>0</v>
+        <v>0.016</v>
       </c>
       <c r="D163">
-        <v>0</v>
+        <v>0.017</v>
       </c>
       <c r="E163">
-        <v>0</v>
+        <v>0.031</v>
       </c>
       <c r="F163">
-        <v>0</v>
+        <v>0.099</v>
       </c>
       <c r="G163">
-        <v>0</v>
+        <v>0.043</v>
       </c>
       <c r="H163">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="I163">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="J163">
-        <v>0.015</v>
+        <v>0</v>
       </c>
       <c r="W163" t="s">
         <v>185</v>
@@ -7189,34 +7189,34 @@
     </row>
     <row r="164" spans="1:24">
       <c r="A164" s="2">
-        <v>46234</v>
+        <v>46252</v>
       </c>
       <c r="B164">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C164">
-        <v>0</v>
+        <v>0.229</v>
       </c>
       <c r="D164">
-        <v>0</v>
+        <v>0.28</v>
       </c>
       <c r="E164">
-        <v>0</v>
+        <v>0.388</v>
       </c>
       <c r="F164">
-        <v>0</v>
+        <v>0.68</v>
       </c>
       <c r="G164">
-        <v>0</v>
+        <v>0.463</v>
       </c>
       <c r="H164">
-        <v>0</v>
+        <v>0.306</v>
       </c>
       <c r="I164">
-        <v>0</v>
+        <v>0.335</v>
       </c>
       <c r="J164">
-        <v>0.015</v>
+        <v>0.233</v>
       </c>
       <c r="W164" t="s">
         <v>186</v>
@@ -7227,34 +7227,34 @@
     </row>
     <row r="165" spans="1:24">
       <c r="A165" s="2">
-        <v>46234</v>
+        <v>46252</v>
       </c>
       <c r="B165">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C165">
-        <v>0.039</v>
+        <v>0.918</v>
       </c>
       <c r="D165">
-        <v>0.06900000000000001</v>
+        <v>1.038</v>
       </c>
       <c r="E165">
-        <v>0.066</v>
+        <v>1.477</v>
       </c>
       <c r="F165">
-        <v>0.242</v>
+        <v>1.769</v>
       </c>
       <c r="G165">
-        <v>0.106</v>
+        <v>1.344</v>
       </c>
       <c r="H165">
-        <v>0.104</v>
+        <v>0.881</v>
       </c>
       <c r="I165">
-        <v>0.064</v>
+        <v>0.603</v>
       </c>
       <c r="J165">
-        <v>0.039</v>
+        <v>0.797</v>
       </c>
       <c r="W165" t="s">
         <v>187</v>
@@ -7265,34 +7265,34 @@
     </row>
     <row r="166" spans="1:24">
       <c r="A166" s="2">
-        <v>46234</v>
+        <v>46252</v>
       </c>
       <c r="B166">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C166">
-        <v>0.36</v>
+        <v>1.721</v>
       </c>
       <c r="D166">
-        <v>0.399</v>
+        <v>1.843</v>
       </c>
       <c r="E166">
-        <v>0.536</v>
+        <v>2.519</v>
       </c>
       <c r="F166">
+        <v>2.681</v>
+      </c>
+      <c r="G166">
+        <v>2.228</v>
+      </c>
+      <c r="H166">
         <v>0.93</v>
       </c>
-      <c r="G166">
-        <v>0.497</v>
-      </c>
-      <c r="H166">
-        <v>0.414</v>
-      </c>
       <c r="I166">
-        <v>0.443</v>
+        <v>1.071</v>
       </c>
       <c r="J166">
-        <v>0.387</v>
+        <v>0.949</v>
       </c>
       <c r="W166" t="s">
         <v>188</v>
@@ -7303,34 +7303,34 @@
     </row>
     <row r="167" spans="1:24">
       <c r="A167" s="2">
-        <v>46234</v>
+        <v>46252</v>
       </c>
       <c r="B167">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C167">
-        <v>0.994</v>
+        <v>2.313</v>
       </c>
       <c r="D167">
-        <v>1.013</v>
+        <v>2.743</v>
       </c>
       <c r="E167">
-        <v>1.503</v>
+        <v>3.563</v>
       </c>
       <c r="F167">
-        <v>2.097</v>
+        <v>3.677</v>
       </c>
       <c r="G167">
-        <v>1.444</v>
+        <v>2.893</v>
       </c>
       <c r="H167">
-        <v>0.786</v>
+        <v>1.448</v>
       </c>
       <c r="I167">
-        <v>0.888</v>
+        <v>1.437</v>
       </c>
       <c r="J167">
-        <v>0.737</v>
+        <v>1.386</v>
       </c>
       <c r="W167" t="s">
         <v>189</v>
@@ -7341,34 +7341,34 @@
     </row>
     <row r="168" spans="1:24">
       <c r="A168" s="2">
-        <v>46234</v>
+        <v>46252</v>
       </c>
       <c r="B168">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C168">
-        <v>1.729</v>
+        <v>2.814</v>
       </c>
       <c r="D168">
-        <v>1.858</v>
+        <v>2.967</v>
       </c>
       <c r="E168">
-        <v>2.327</v>
+        <v>3.971</v>
       </c>
       <c r="F168">
-        <v>3.079</v>
+        <v>4.136</v>
       </c>
       <c r="G168">
-        <v>2.386</v>
+        <v>3.482</v>
       </c>
       <c r="H168">
-        <v>1.28</v>
+        <v>1.49</v>
       </c>
       <c r="I168">
-        <v>1.143</v>
+        <v>1.445</v>
       </c>
       <c r="J168">
-        <v>1.084</v>
+        <v>1.582</v>
       </c>
       <c r="W168" t="s">
         <v>190</v>
@@ -7379,34 +7379,34 @@
     </row>
     <row r="169" spans="1:24">
       <c r="A169" s="2">
-        <v>46234</v>
+        <v>46252</v>
       </c>
       <c r="B169">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C169">
-        <v>2.347</v>
+        <v>3.052</v>
       </c>
       <c r="D169">
-        <v>2.52</v>
+        <v>3.053</v>
       </c>
       <c r="E169">
-        <v>3.424</v>
+        <v>3.921</v>
       </c>
       <c r="F169">
-        <v>3.803</v>
+        <v>4.206</v>
       </c>
       <c r="G169">
-        <v>3.035</v>
+        <v>3.583</v>
       </c>
       <c r="H169">
-        <v>0.824</v>
+        <v>1.5</v>
       </c>
       <c r="I169">
-        <v>1.472</v>
+        <v>1.396</v>
       </c>
       <c r="J169">
-        <v>1.455</v>
+        <v>1.665</v>
       </c>
       <c r="W169" t="s">
         <v>191</v>
@@ -7417,34 +7417,34 @@
     </row>
     <row r="170" spans="1:24">
       <c r="A170" s="2">
-        <v>46234</v>
+        <v>46252</v>
       </c>
       <c r="B170">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C170">
-        <v>2.688</v>
+        <v>3.124</v>
       </c>
       <c r="D170">
-        <v>2.811</v>
+        <v>3.097</v>
       </c>
       <c r="E170">
-        <v>3.782</v>
+        <v>3.81</v>
       </c>
       <c r="F170">
-        <v>4.146</v>
+        <v>4.138</v>
       </c>
       <c r="G170">
-        <v>3.425</v>
+        <v>3.538</v>
       </c>
       <c r="H170">
-        <v>1.217</v>
+        <v>0.835</v>
       </c>
       <c r="I170">
-        <v>1.445</v>
+        <v>1.452</v>
       </c>
       <c r="J170">
-        <v>1.547</v>
+        <v>1.617</v>
       </c>
       <c r="W170" t="s">
         <v>192</v>

--- a/Forecast.xlsx
+++ b/Forecast.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="195">
   <si>
     <t>Data</t>
   </si>
@@ -82,517 +82,523 @@
     <t>Prediction_HNG</t>
   </si>
   <si>
+    <t>Prediction_Start_Fotovoltaice</t>
+  </si>
+  <si>
+    <t>Prediction_AnaSun</t>
+  </si>
+  <si>
     <t>Lookup</t>
   </si>
   <si>
     <t>Prediction_3D_Steel</t>
   </si>
   <si>
-    <t>11.08.202614</t>
-  </si>
-  <si>
-    <t>11.08.202615</t>
-  </si>
-  <si>
-    <t>11.08.202616</t>
-  </si>
-  <si>
-    <t>11.08.202617</t>
-  </si>
-  <si>
-    <t>11.08.202618</t>
-  </si>
-  <si>
-    <t>11.08.202619</t>
-  </si>
-  <si>
-    <t>11.08.202620</t>
-  </si>
-  <si>
-    <t>11.08.202621</t>
-  </si>
-  <si>
-    <t>11.08.202622</t>
-  </si>
-  <si>
-    <t>11.08.202623</t>
-  </si>
-  <si>
-    <t>11.08.202624</t>
-  </si>
-  <si>
-    <t>12.08.20261</t>
-  </si>
-  <si>
-    <t>12.08.20262</t>
-  </si>
-  <si>
-    <t>12.08.20263</t>
-  </si>
-  <si>
-    <t>12.08.20264</t>
-  </si>
-  <si>
-    <t>12.08.20265</t>
-  </si>
-  <si>
-    <t>12.08.20266</t>
-  </si>
-  <si>
-    <t>12.08.20267</t>
-  </si>
-  <si>
-    <t>12.08.20268</t>
-  </si>
-  <si>
-    <t>12.08.20269</t>
-  </si>
-  <si>
-    <t>12.08.202610</t>
-  </si>
-  <si>
-    <t>12.08.202611</t>
-  </si>
-  <si>
-    <t>12.08.202612</t>
-  </si>
-  <si>
-    <t>12.08.202613</t>
-  </si>
-  <si>
-    <t>12.08.202614</t>
-  </si>
-  <si>
-    <t>12.08.202615</t>
-  </si>
-  <si>
-    <t>12.08.202616</t>
-  </si>
-  <si>
-    <t>12.08.202617</t>
-  </si>
-  <si>
-    <t>12.08.202618</t>
-  </si>
-  <si>
-    <t>12.08.202619</t>
-  </si>
-  <si>
-    <t>12.08.202620</t>
-  </si>
-  <si>
-    <t>12.08.202621</t>
-  </si>
-  <si>
-    <t>12.08.202622</t>
-  </si>
-  <si>
-    <t>12.08.202623</t>
-  </si>
-  <si>
-    <t>12.08.202624</t>
-  </si>
-  <si>
-    <t>13.08.20261</t>
-  </si>
-  <si>
-    <t>13.08.20262</t>
-  </si>
-  <si>
-    <t>13.08.20263</t>
-  </si>
-  <si>
-    <t>13.08.20264</t>
-  </si>
-  <si>
-    <t>13.08.20265</t>
-  </si>
-  <si>
-    <t>13.08.20266</t>
-  </si>
-  <si>
-    <t>13.08.20267</t>
-  </si>
-  <si>
-    <t>13.08.20268</t>
-  </si>
-  <si>
-    <t>13.08.20269</t>
-  </si>
-  <si>
-    <t>13.08.202610</t>
-  </si>
-  <si>
-    <t>13.08.202611</t>
-  </si>
-  <si>
-    <t>13.08.202612</t>
-  </si>
-  <si>
-    <t>13.08.202613</t>
-  </si>
-  <si>
-    <t>13.08.202614</t>
-  </si>
-  <si>
-    <t>13.08.202615</t>
-  </si>
-  <si>
-    <t>13.08.202616</t>
-  </si>
-  <si>
-    <t>13.08.202617</t>
-  </si>
-  <si>
-    <t>13.08.202618</t>
-  </si>
-  <si>
-    <t>13.08.202619</t>
-  </si>
-  <si>
-    <t>13.08.202620</t>
-  </si>
-  <si>
-    <t>13.08.202621</t>
-  </si>
-  <si>
-    <t>13.08.202622</t>
-  </si>
-  <si>
-    <t>13.08.202623</t>
-  </si>
-  <si>
-    <t>13.08.202624</t>
-  </si>
-  <si>
-    <t>14.08.20261</t>
-  </si>
-  <si>
-    <t>14.08.20262</t>
-  </si>
-  <si>
-    <t>14.08.20263</t>
-  </si>
-  <si>
-    <t>14.08.20264</t>
-  </si>
-  <si>
-    <t>14.08.20265</t>
-  </si>
-  <si>
-    <t>14.08.20266</t>
-  </si>
-  <si>
-    <t>14.08.20267</t>
-  </si>
-  <si>
-    <t>14.08.20268</t>
-  </si>
-  <si>
-    <t>14.08.20269</t>
-  </si>
-  <si>
-    <t>14.08.202610</t>
-  </si>
-  <si>
-    <t>14.08.202611</t>
-  </si>
-  <si>
-    <t>14.08.202612</t>
-  </si>
-  <si>
-    <t>14.08.202613</t>
-  </si>
-  <si>
-    <t>14.08.202614</t>
-  </si>
-  <si>
-    <t>14.08.202615</t>
-  </si>
-  <si>
-    <t>14.08.202616</t>
-  </si>
-  <si>
-    <t>14.08.202617</t>
-  </si>
-  <si>
-    <t>14.08.202618</t>
-  </si>
-  <si>
-    <t>14.08.202619</t>
-  </si>
-  <si>
-    <t>14.08.202620</t>
-  </si>
-  <si>
-    <t>14.08.202621</t>
-  </si>
-  <si>
-    <t>14.08.202622</t>
-  </si>
-  <si>
-    <t>14.08.202623</t>
-  </si>
-  <si>
-    <t>14.08.202624</t>
-  </si>
-  <si>
-    <t>15.08.20261</t>
-  </si>
-  <si>
-    <t>15.08.20262</t>
-  </si>
-  <si>
-    <t>15.08.20263</t>
-  </si>
-  <si>
-    <t>15.08.20264</t>
-  </si>
-  <si>
-    <t>15.08.20265</t>
-  </si>
-  <si>
-    <t>15.08.20266</t>
-  </si>
-  <si>
-    <t>15.08.20267</t>
-  </si>
-  <si>
-    <t>15.08.20268</t>
-  </si>
-  <si>
-    <t>15.08.20269</t>
-  </si>
-  <si>
-    <t>15.08.202610</t>
-  </si>
-  <si>
-    <t>15.08.202611</t>
-  </si>
-  <si>
-    <t>15.08.202612</t>
-  </si>
-  <si>
-    <t>15.08.202613</t>
-  </si>
-  <si>
-    <t>15.08.202614</t>
-  </si>
-  <si>
-    <t>15.08.202615</t>
-  </si>
-  <si>
-    <t>15.08.202616</t>
-  </si>
-  <si>
-    <t>15.08.202617</t>
-  </si>
-  <si>
-    <t>15.08.202618</t>
-  </si>
-  <si>
-    <t>15.08.202619</t>
-  </si>
-  <si>
-    <t>15.08.202620</t>
-  </si>
-  <si>
-    <t>15.08.202621</t>
-  </si>
-  <si>
-    <t>15.08.202622</t>
-  </si>
-  <si>
-    <t>15.08.202623</t>
-  </si>
-  <si>
-    <t>15.08.202624</t>
-  </si>
-  <si>
-    <t>16.08.20261</t>
-  </si>
-  <si>
-    <t>16.08.20262</t>
-  </si>
-  <si>
-    <t>16.08.20263</t>
-  </si>
-  <si>
-    <t>16.08.20264</t>
-  </si>
-  <si>
-    <t>16.08.20265</t>
-  </si>
-  <si>
-    <t>16.08.20266</t>
-  </si>
-  <si>
-    <t>16.08.20267</t>
-  </si>
-  <si>
-    <t>16.08.20268</t>
-  </si>
-  <si>
-    <t>16.08.20269</t>
-  </si>
-  <si>
-    <t>16.08.202610</t>
-  </si>
-  <si>
-    <t>16.08.202611</t>
-  </si>
-  <si>
-    <t>16.08.202612</t>
-  </si>
-  <si>
-    <t>16.08.202613</t>
-  </si>
-  <si>
-    <t>16.08.202614</t>
-  </si>
-  <si>
-    <t>16.08.202615</t>
-  </si>
-  <si>
-    <t>16.08.202616</t>
-  </si>
-  <si>
-    <t>16.08.202617</t>
-  </si>
-  <si>
-    <t>16.08.202618</t>
-  </si>
-  <si>
-    <t>16.08.202619</t>
-  </si>
-  <si>
-    <t>16.08.202620</t>
-  </si>
-  <si>
-    <t>16.08.202621</t>
-  </si>
-  <si>
-    <t>16.08.202622</t>
-  </si>
-  <si>
-    <t>16.08.202623</t>
-  </si>
-  <si>
-    <t>16.08.202624</t>
-  </si>
-  <si>
-    <t>17.08.20261</t>
-  </si>
-  <si>
-    <t>17.08.20262</t>
-  </si>
-  <si>
-    <t>17.08.20263</t>
-  </si>
-  <si>
-    <t>17.08.20264</t>
-  </si>
-  <si>
-    <t>17.08.20265</t>
-  </si>
-  <si>
-    <t>17.08.20266</t>
-  </si>
-  <si>
-    <t>17.08.20267</t>
-  </si>
-  <si>
-    <t>17.08.20268</t>
-  </si>
-  <si>
-    <t>17.08.20269</t>
-  </si>
-  <si>
-    <t>17.08.202610</t>
-  </si>
-  <si>
-    <t>17.08.202611</t>
-  </si>
-  <si>
-    <t>17.08.202612</t>
-  </si>
-  <si>
-    <t>17.08.202613</t>
-  </si>
-  <si>
-    <t>17.08.202614</t>
-  </si>
-  <si>
-    <t>17.08.202615</t>
-  </si>
-  <si>
-    <t>17.08.202616</t>
-  </si>
-  <si>
-    <t>17.08.202617</t>
-  </si>
-  <si>
-    <t>17.08.202618</t>
-  </si>
-  <si>
-    <t>17.08.202619</t>
-  </si>
-  <si>
-    <t>17.08.202620</t>
-  </si>
-  <si>
-    <t>17.08.202621</t>
-  </si>
-  <si>
-    <t>17.08.202622</t>
-  </si>
-  <si>
-    <t>17.08.202623</t>
-  </si>
-  <si>
-    <t>17.08.202624</t>
-  </si>
-  <si>
-    <t>18.08.20261</t>
-  </si>
-  <si>
-    <t>18.08.20262</t>
-  </si>
-  <si>
-    <t>18.08.20263</t>
-  </si>
-  <si>
-    <t>18.08.20264</t>
-  </si>
-  <si>
-    <t>18.08.20265</t>
-  </si>
-  <si>
-    <t>18.08.20266</t>
-  </si>
-  <si>
-    <t>18.08.20267</t>
-  </si>
-  <si>
-    <t>18.08.20268</t>
-  </si>
-  <si>
-    <t>18.08.20269</t>
-  </si>
-  <si>
-    <t>18.08.202610</t>
-  </si>
-  <si>
-    <t>18.08.202611</t>
-  </si>
-  <si>
-    <t>18.08.202612</t>
-  </si>
-  <si>
-    <t>18.08.202613</t>
-  </si>
-  <si>
-    <t>18.08.202614</t>
+    <t>19.08.202614</t>
+  </si>
+  <si>
+    <t>19.08.202615</t>
+  </si>
+  <si>
+    <t>19.08.202616</t>
+  </si>
+  <si>
+    <t>19.08.202617</t>
+  </si>
+  <si>
+    <t>19.08.202618</t>
+  </si>
+  <si>
+    <t>19.08.202619</t>
+  </si>
+  <si>
+    <t>19.08.202620</t>
+  </si>
+  <si>
+    <t>19.08.202621</t>
+  </si>
+  <si>
+    <t>19.08.202622</t>
+  </si>
+  <si>
+    <t>19.08.202623</t>
+  </si>
+  <si>
+    <t>19.08.202624</t>
+  </si>
+  <si>
+    <t>20.08.20261</t>
+  </si>
+  <si>
+    <t>20.08.20262</t>
+  </si>
+  <si>
+    <t>20.08.20263</t>
+  </si>
+  <si>
+    <t>20.08.20264</t>
+  </si>
+  <si>
+    <t>20.08.20265</t>
+  </si>
+  <si>
+    <t>20.08.20266</t>
+  </si>
+  <si>
+    <t>20.08.20267</t>
+  </si>
+  <si>
+    <t>20.08.20268</t>
+  </si>
+  <si>
+    <t>20.08.20269</t>
+  </si>
+  <si>
+    <t>20.08.202610</t>
+  </si>
+  <si>
+    <t>20.08.202611</t>
+  </si>
+  <si>
+    <t>20.08.202612</t>
+  </si>
+  <si>
+    <t>20.08.202613</t>
+  </si>
+  <si>
+    <t>20.08.202614</t>
+  </si>
+  <si>
+    <t>20.08.202615</t>
+  </si>
+  <si>
+    <t>20.08.202616</t>
+  </si>
+  <si>
+    <t>20.08.202617</t>
+  </si>
+  <si>
+    <t>20.08.202618</t>
+  </si>
+  <si>
+    <t>20.08.202619</t>
+  </si>
+  <si>
+    <t>20.08.202620</t>
+  </si>
+  <si>
+    <t>20.08.202621</t>
+  </si>
+  <si>
+    <t>20.08.202622</t>
+  </si>
+  <si>
+    <t>20.08.202623</t>
+  </si>
+  <si>
+    <t>20.08.202624</t>
+  </si>
+  <si>
+    <t>21.08.20261</t>
+  </si>
+  <si>
+    <t>21.08.20262</t>
+  </si>
+  <si>
+    <t>21.08.20263</t>
+  </si>
+  <si>
+    <t>21.08.20264</t>
+  </si>
+  <si>
+    <t>21.08.20265</t>
+  </si>
+  <si>
+    <t>21.08.20266</t>
+  </si>
+  <si>
+    <t>21.08.20267</t>
+  </si>
+  <si>
+    <t>21.08.20268</t>
+  </si>
+  <si>
+    <t>21.08.20269</t>
+  </si>
+  <si>
+    <t>21.08.202610</t>
+  </si>
+  <si>
+    <t>21.08.202611</t>
+  </si>
+  <si>
+    <t>21.08.202612</t>
+  </si>
+  <si>
+    <t>21.08.202613</t>
+  </si>
+  <si>
+    <t>21.08.202614</t>
+  </si>
+  <si>
+    <t>21.08.202615</t>
+  </si>
+  <si>
+    <t>21.08.202616</t>
+  </si>
+  <si>
+    <t>21.08.202617</t>
+  </si>
+  <si>
+    <t>21.08.202618</t>
+  </si>
+  <si>
+    <t>21.08.202619</t>
+  </si>
+  <si>
+    <t>21.08.202620</t>
+  </si>
+  <si>
+    <t>21.08.202621</t>
+  </si>
+  <si>
+    <t>21.08.202622</t>
+  </si>
+  <si>
+    <t>21.08.202623</t>
+  </si>
+  <si>
+    <t>21.08.202624</t>
+  </si>
+  <si>
+    <t>22.08.20261</t>
+  </si>
+  <si>
+    <t>22.08.20262</t>
+  </si>
+  <si>
+    <t>22.08.20263</t>
+  </si>
+  <si>
+    <t>22.08.20264</t>
+  </si>
+  <si>
+    <t>22.08.20265</t>
+  </si>
+  <si>
+    <t>22.08.20266</t>
+  </si>
+  <si>
+    <t>22.08.20267</t>
+  </si>
+  <si>
+    <t>22.08.20268</t>
+  </si>
+  <si>
+    <t>22.08.20269</t>
+  </si>
+  <si>
+    <t>22.08.202610</t>
+  </si>
+  <si>
+    <t>22.08.202611</t>
+  </si>
+  <si>
+    <t>22.08.202612</t>
+  </si>
+  <si>
+    <t>22.08.202613</t>
+  </si>
+  <si>
+    <t>22.08.202614</t>
+  </si>
+  <si>
+    <t>22.08.202615</t>
+  </si>
+  <si>
+    <t>22.08.202616</t>
+  </si>
+  <si>
+    <t>22.08.202617</t>
+  </si>
+  <si>
+    <t>22.08.202618</t>
+  </si>
+  <si>
+    <t>22.08.202619</t>
+  </si>
+  <si>
+    <t>22.08.202620</t>
+  </si>
+  <si>
+    <t>22.08.202621</t>
+  </si>
+  <si>
+    <t>22.08.202622</t>
+  </si>
+  <si>
+    <t>22.08.202623</t>
+  </si>
+  <si>
+    <t>22.08.202624</t>
+  </si>
+  <si>
+    <t>23.08.20261</t>
+  </si>
+  <si>
+    <t>23.08.20262</t>
+  </si>
+  <si>
+    <t>23.08.20263</t>
+  </si>
+  <si>
+    <t>23.08.20264</t>
+  </si>
+  <si>
+    <t>23.08.20265</t>
+  </si>
+  <si>
+    <t>23.08.20266</t>
+  </si>
+  <si>
+    <t>23.08.20267</t>
+  </si>
+  <si>
+    <t>23.08.20268</t>
+  </si>
+  <si>
+    <t>23.08.20269</t>
+  </si>
+  <si>
+    <t>23.08.202610</t>
+  </si>
+  <si>
+    <t>23.08.202611</t>
+  </si>
+  <si>
+    <t>23.08.202612</t>
+  </si>
+  <si>
+    <t>23.08.202613</t>
+  </si>
+  <si>
+    <t>23.08.202614</t>
+  </si>
+  <si>
+    <t>23.08.202615</t>
+  </si>
+  <si>
+    <t>23.08.202616</t>
+  </si>
+  <si>
+    <t>23.08.202617</t>
+  </si>
+  <si>
+    <t>23.08.202618</t>
+  </si>
+  <si>
+    <t>23.08.202619</t>
+  </si>
+  <si>
+    <t>23.08.202620</t>
+  </si>
+  <si>
+    <t>23.08.202621</t>
+  </si>
+  <si>
+    <t>23.08.202622</t>
+  </si>
+  <si>
+    <t>23.08.202623</t>
+  </si>
+  <si>
+    <t>23.08.202624</t>
+  </si>
+  <si>
+    <t>24.08.20261</t>
+  </si>
+  <si>
+    <t>24.08.20262</t>
+  </si>
+  <si>
+    <t>24.08.20263</t>
+  </si>
+  <si>
+    <t>24.08.20264</t>
+  </si>
+  <si>
+    <t>24.08.20265</t>
+  </si>
+  <si>
+    <t>24.08.20266</t>
+  </si>
+  <si>
+    <t>24.08.20267</t>
+  </si>
+  <si>
+    <t>24.08.20268</t>
+  </si>
+  <si>
+    <t>24.08.20269</t>
+  </si>
+  <si>
+    <t>24.08.202610</t>
+  </si>
+  <si>
+    <t>24.08.202611</t>
+  </si>
+  <si>
+    <t>24.08.202612</t>
+  </si>
+  <si>
+    <t>24.08.202613</t>
+  </si>
+  <si>
+    <t>24.08.202614</t>
+  </si>
+  <si>
+    <t>24.08.202615</t>
+  </si>
+  <si>
+    <t>24.08.202616</t>
+  </si>
+  <si>
+    <t>24.08.202617</t>
+  </si>
+  <si>
+    <t>24.08.202618</t>
+  </si>
+  <si>
+    <t>24.08.202619</t>
+  </si>
+  <si>
+    <t>24.08.202620</t>
+  </si>
+  <si>
+    <t>24.08.202621</t>
+  </si>
+  <si>
+    <t>24.08.202622</t>
+  </si>
+  <si>
+    <t>24.08.202623</t>
+  </si>
+  <si>
+    <t>24.08.202624</t>
+  </si>
+  <si>
+    <t>25.08.20261</t>
+  </si>
+  <si>
+    <t>25.08.20262</t>
+  </si>
+  <si>
+    <t>25.08.20263</t>
+  </si>
+  <si>
+    <t>25.08.20264</t>
+  </si>
+  <si>
+    <t>25.08.20265</t>
+  </si>
+  <si>
+    <t>25.08.20266</t>
+  </si>
+  <si>
+    <t>25.08.20267</t>
+  </si>
+  <si>
+    <t>25.08.20268</t>
+  </si>
+  <si>
+    <t>25.08.20269</t>
+  </si>
+  <si>
+    <t>25.08.202610</t>
+  </si>
+  <si>
+    <t>25.08.202611</t>
+  </si>
+  <si>
+    <t>25.08.202612</t>
+  </si>
+  <si>
+    <t>25.08.202613</t>
+  </si>
+  <si>
+    <t>25.08.202614</t>
+  </si>
+  <si>
+    <t>25.08.202615</t>
+  </si>
+  <si>
+    <t>25.08.202616</t>
+  </si>
+  <si>
+    <t>25.08.202617</t>
+  </si>
+  <si>
+    <t>25.08.202618</t>
+  </si>
+  <si>
+    <t>25.08.202619</t>
+  </si>
+  <si>
+    <t>25.08.202620</t>
+  </si>
+  <si>
+    <t>25.08.202621</t>
+  </si>
+  <si>
+    <t>25.08.202622</t>
+  </si>
+  <si>
+    <t>25.08.202623</t>
+  </si>
+  <si>
+    <t>25.08.202624</t>
+  </si>
+  <si>
+    <t>26.08.20261</t>
+  </si>
+  <si>
+    <t>26.08.20262</t>
+  </si>
+  <si>
+    <t>26.08.20263</t>
+  </si>
+  <si>
+    <t>26.08.20264</t>
+  </si>
+  <si>
+    <t>26.08.20265</t>
+  </si>
+  <si>
+    <t>26.08.20266</t>
+  </si>
+  <si>
+    <t>26.08.20267</t>
+  </si>
+  <si>
+    <t>26.08.20268</t>
+  </si>
+  <si>
+    <t>26.08.20269</t>
+  </si>
+  <si>
+    <t>26.08.202610</t>
+  </si>
+  <si>
+    <t>26.08.202611</t>
+  </si>
+  <si>
+    <t>26.08.202612</t>
+  </si>
+  <si>
+    <t>26.08.202613</t>
+  </si>
+  <si>
+    <t>26.08.202614</t>
   </si>
 </sst>
 </file>
@@ -954,10 +960,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:X170"/>
+  <dimension ref="A1:Z170"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:26">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1030,10 +1036,16 @@
       <c r="X1" s="1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="2" spans="1:24">
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:26">
       <c r="A2" s="2">
-        <v>46245</v>
+        <v>46253</v>
       </c>
       <c r="B2">
         <v>14</v>
@@ -1062,16 +1074,19 @@
       <c r="J2">
         <v>0</v>
       </c>
-      <c r="W2" t="s">
-        <v>24</v>
-      </c>
-      <c r="X2">
+      <c r="W2">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z2">
         <v>0.034</v>
       </c>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:26">
       <c r="A3" s="2">
-        <v>46245</v>
+        <v>46253</v>
       </c>
       <c r="B3">
         <v>15</v>
@@ -1100,244 +1115,283 @@
       <c r="J3">
         <v>0.037</v>
       </c>
-      <c r="W3" t="s">
-        <v>25</v>
-      </c>
-      <c r="X3">
+      <c r="W3">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z3">
         <v>0.034</v>
       </c>
     </row>
-    <row r="4" spans="1:24">
+    <row r="4" spans="1:26">
       <c r="A4" s="2">
-        <v>46245</v>
+        <v>46253</v>
       </c>
       <c r="B4">
         <v>16</v>
       </c>
       <c r="C4">
-        <v>2.668</v>
+        <v>1.316</v>
       </c>
       <c r="D4">
-        <v>2.869</v>
+        <v>1.977</v>
       </c>
       <c r="E4">
-        <v>3.841</v>
+        <v>2.874</v>
       </c>
       <c r="F4">
-        <v>2.947</v>
+        <v>2.814</v>
       </c>
       <c r="G4">
-        <v>2.73</v>
+        <v>2.777</v>
       </c>
       <c r="H4">
-        <v>0.833</v>
+        <v>0.962</v>
       </c>
       <c r="I4">
-        <v>1.502</v>
+        <v>1.483</v>
       </c>
       <c r="J4">
-        <v>1.318</v>
-      </c>
-      <c r="W4" t="s">
-        <v>26</v>
+        <v>0.879</v>
+      </c>
+      <c r="W4">
+        <v>0.6312486486486486</v>
       </c>
       <c r="X4">
+        <v>1.154</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z4">
         <v>1.509</v>
       </c>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:26">
       <c r="A5" s="2">
-        <v>46245</v>
+        <v>46253</v>
       </c>
       <c r="B5">
         <v>17</v>
       </c>
       <c r="C5">
-        <v>2.021</v>
+        <v>1.642</v>
       </c>
       <c r="D5">
-        <v>2.596</v>
+        <v>1.526</v>
       </c>
       <c r="E5">
-        <v>3.389</v>
+        <v>1.987</v>
       </c>
       <c r="F5">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="G5">
-        <v>2.34</v>
+        <v>2.318</v>
       </c>
       <c r="H5">
-        <v>0.927</v>
+        <v>1.074</v>
       </c>
       <c r="I5">
-        <v>1.483</v>
+        <v>1.155</v>
       </c>
       <c r="J5">
-        <v>1.002</v>
-      </c>
-      <c r="W5" t="s">
-        <v>27</v>
+        <v>0.655</v>
+      </c>
+      <c r="W5">
+        <v>0.4935135135135135</v>
       </c>
       <c r="X5">
+        <v>3.737</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>29</v>
+      </c>
+      <c r="Z5">
         <v>1.714</v>
       </c>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:26">
       <c r="A6" s="2">
-        <v>46245</v>
+        <v>46253</v>
       </c>
       <c r="B6">
         <v>18</v>
       </c>
       <c r="C6">
-        <v>1.268</v>
+        <v>1.196</v>
       </c>
       <c r="D6">
-        <v>1.669</v>
+        <v>1.293</v>
       </c>
       <c r="E6">
-        <v>2.38</v>
+        <v>1.759</v>
       </c>
       <c r="F6">
-        <v>1.455</v>
+        <v>1.389</v>
       </c>
       <c r="G6">
-        <v>1.679</v>
+        <v>1.475</v>
       </c>
       <c r="H6">
-        <v>0.848</v>
+        <v>0.838</v>
       </c>
       <c r="I6">
-        <v>1.087</v>
+        <v>0.633</v>
       </c>
       <c r="J6">
-        <v>0.754</v>
-      </c>
-      <c r="W6" t="s">
-        <v>28</v>
+        <v>0.327</v>
+      </c>
+      <c r="W6">
+        <v>0.3115864864864865</v>
       </c>
       <c r="X6">
+        <v>2.733</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z6">
         <v>1.603</v>
       </c>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:26">
       <c r="A7" s="2">
-        <v>46245</v>
+        <v>46253</v>
       </c>
       <c r="B7">
         <v>19</v>
       </c>
       <c r="C7">
-        <v>0.613</v>
+        <v>0.545</v>
       </c>
       <c r="D7">
-        <v>0.858</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="E7">
-        <v>1.388</v>
+        <v>1.24</v>
       </c>
       <c r="F7">
-        <v>0.632</v>
+        <v>0.481</v>
       </c>
       <c r="G7">
-        <v>0.915</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="H7">
-        <v>0.627</v>
+        <v>0.485</v>
       </c>
       <c r="I7">
-        <v>0.542</v>
+        <v>0.518</v>
       </c>
       <c r="J7">
-        <v>0.301</v>
-      </c>
-      <c r="W7" t="s">
-        <v>29</v>
+        <v>0.174</v>
+      </c>
+      <c r="W7">
+        <v>0.1079</v>
       </c>
       <c r="X7">
+        <v>1.494</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>31</v>
+      </c>
+      <c r="Z7">
         <v>1.468</v>
       </c>
     </row>
-    <row r="8" spans="1:24">
+    <row r="8" spans="1:26">
       <c r="A8" s="2">
-        <v>46245</v>
+        <v>46253</v>
       </c>
       <c r="B8">
         <v>20</v>
       </c>
       <c r="C8">
-        <v>0.182</v>
+        <v>0.173</v>
       </c>
       <c r="D8">
-        <v>0.239</v>
+        <v>0.203</v>
       </c>
       <c r="E8">
-        <v>0.483</v>
+        <v>0.425</v>
       </c>
       <c r="F8">
-        <v>0.191</v>
+        <v>0.14</v>
       </c>
       <c r="G8">
-        <v>0.268</v>
+        <v>0.194</v>
       </c>
       <c r="H8">
-        <v>0.258</v>
+        <v>0.199</v>
       </c>
       <c r="I8">
-        <v>0.201</v>
+        <v>0.125</v>
       </c>
       <c r="J8">
-        <v>0.096</v>
-      </c>
-      <c r="W8" t="s">
-        <v>30</v>
+        <v>0.102</v>
+      </c>
+      <c r="W8">
+        <v>0.03140540540540541</v>
       </c>
       <c r="X8">
+        <v>0.468</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z8">
         <v>1.235</v>
       </c>
     </row>
-    <row r="9" spans="1:24">
+    <row r="9" spans="1:26">
       <c r="A9" s="2">
-        <v>46245</v>
+        <v>46253</v>
       </c>
       <c r="B9">
         <v>21</v>
       </c>
       <c r="C9">
-        <v>0.021</v>
+        <v>0</v>
       </c>
       <c r="D9">
-        <v>0.022</v>
+        <v>0</v>
       </c>
       <c r="E9">
-        <v>0.048</v>
+        <v>0.029</v>
       </c>
       <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
         <v>0.011</v>
       </c>
-      <c r="G9">
-        <v>0.014</v>
-      </c>
-      <c r="H9">
-        <v>0.012</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="W9" t="s">
-        <v>31</v>
+      <c r="W9">
+        <v>0</v>
       </c>
       <c r="X9">
+        <v>0.051</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z9">
         <v>0.679</v>
       </c>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:26">
       <c r="A10" s="2">
-        <v>46245</v>
+        <v>46253</v>
       </c>
       <c r="B10">
         <v>22</v>
@@ -1364,18 +1418,24 @@
         <v>0</v>
       </c>
       <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="W10" t="s">
-        <v>32</v>
+        <v>0.013</v>
+      </c>
+      <c r="W10">
+        <v>0</v>
       </c>
       <c r="X10">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>34</v>
+      </c>
+      <c r="Z10">
         <v>0.421</v>
       </c>
     </row>
-    <row r="11" spans="1:24">
+    <row r="11" spans="1:26">
       <c r="A11" s="2">
-        <v>46245</v>
+        <v>46253</v>
       </c>
       <c r="B11">
         <v>23</v>
@@ -1402,18 +1462,24 @@
         <v>0</v>
       </c>
       <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="W11" t="s">
-        <v>33</v>
+        <v>0.013</v>
+      </c>
+      <c r="W11">
+        <v>0</v>
       </c>
       <c r="X11">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z11">
         <v>0.044</v>
       </c>
     </row>
-    <row r="12" spans="1:24">
+    <row r="12" spans="1:26">
       <c r="A12" s="2">
-        <v>46245</v>
+        <v>46253</v>
       </c>
       <c r="B12">
         <v>24</v>
@@ -1440,18 +1506,24 @@
         <v>0</v>
       </c>
       <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="W12" t="s">
-        <v>34</v>
+        <v>0.013</v>
+      </c>
+      <c r="W12">
+        <v>0</v>
       </c>
       <c r="X12">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z12">
         <v>0.049</v>
       </c>
     </row>
-    <row r="13" spans="1:24">
+    <row r="13" spans="1:26">
       <c r="A13" s="2">
-        <v>46246</v>
+        <v>46254</v>
       </c>
       <c r="B13">
         <v>1</v>
@@ -1463,7 +1535,7 @@
         <v>0</v>
       </c>
       <c r="E13">
-        <v>0.025</v>
+        <v>0</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -1480,16 +1552,22 @@
       <c r="J13">
         <v>0.014</v>
       </c>
-      <c r="W13" t="s">
-        <v>35</v>
+      <c r="W13">
+        <v>0</v>
       </c>
       <c r="X13">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>37</v>
+      </c>
+      <c r="Z13">
         <v>0.04</v>
       </c>
     </row>
-    <row r="14" spans="1:24">
+    <row r="14" spans="1:26">
       <c r="A14" s="2">
-        <v>46246</v>
+        <v>46254</v>
       </c>
       <c r="B14">
         <v>2</v>
@@ -1501,7 +1579,7 @@
         <v>0</v>
       </c>
       <c r="E14">
-        <v>0.015</v>
+        <v>0</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -1516,18 +1594,24 @@
         <v>0</v>
       </c>
       <c r="J14">
-        <v>0</v>
-      </c>
-      <c r="W14" t="s">
-        <v>36</v>
+        <v>0.014</v>
+      </c>
+      <c r="W14">
+        <v>0</v>
       </c>
       <c r="X14">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:24">
+      <c r="Y14" t="s">
+        <v>38</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26">
       <c r="A15" s="2">
-        <v>46246</v>
+        <v>46254</v>
       </c>
       <c r="B15">
         <v>3</v>
@@ -1539,7 +1623,7 @@
         <v>0</v>
       </c>
       <c r="E15">
-        <v>0.015</v>
+        <v>0</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -1554,18 +1638,24 @@
         <v>0</v>
       </c>
       <c r="J15">
-        <v>0</v>
-      </c>
-      <c r="W15" t="s">
-        <v>37</v>
+        <v>0.014</v>
+      </c>
+      <c r="W15">
+        <v>0</v>
       </c>
       <c r="X15">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:24">
+      <c r="Y15" t="s">
+        <v>39</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26">
       <c r="A16" s="2">
-        <v>46246</v>
+        <v>46254</v>
       </c>
       <c r="B16">
         <v>4</v>
@@ -1577,7 +1667,7 @@
         <v>0</v>
       </c>
       <c r="E16">
-        <v>0.024</v>
+        <v>0</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -1594,16 +1684,22 @@
       <c r="J16">
         <v>0.014</v>
       </c>
-      <c r="W16" t="s">
-        <v>38</v>
+      <c r="W16">
+        <v>0</v>
       </c>
       <c r="X16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:24">
+      <c r="Y16" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:26">
       <c r="A17" s="2">
-        <v>46246</v>
+        <v>46254</v>
       </c>
       <c r="B17">
         <v>5</v>
@@ -1615,7 +1711,7 @@
         <v>0</v>
       </c>
       <c r="E17">
-        <v>0.077</v>
+        <v>0</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -1630,18 +1726,24 @@
         <v>0</v>
       </c>
       <c r="J17">
-        <v>0.014</v>
-      </c>
-      <c r="W17" t="s">
-        <v>39</v>
+        <v>0.015</v>
+      </c>
+      <c r="W17">
+        <v>0</v>
       </c>
       <c r="X17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:24">
+      <c r="Y17" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:26">
       <c r="A18" s="2">
-        <v>46246</v>
+        <v>46254</v>
       </c>
       <c r="B18">
         <v>6</v>
@@ -1653,7 +1755,7 @@
         <v>0</v>
       </c>
       <c r="E18">
-        <v>0.066</v>
+        <v>0</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -1668,568 +1770,658 @@
         <v>0</v>
       </c>
       <c r="J18">
-        <v>0.02</v>
-      </c>
-      <c r="W18" t="s">
-        <v>40</v>
+        <v>0.015</v>
+      </c>
+      <c r="W18">
+        <v>0</v>
       </c>
       <c r="X18">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z18">
         <v>0.014</v>
       </c>
     </row>
-    <row r="19" spans="1:24">
+    <row r="19" spans="1:26">
       <c r="A19" s="2">
-        <v>46246</v>
+        <v>46254</v>
       </c>
       <c r="B19">
         <v>7</v>
       </c>
       <c r="C19">
-        <v>0.018</v>
+        <v>0</v>
       </c>
       <c r="D19">
-        <v>0.024</v>
+        <v>0.017</v>
       </c>
       <c r="E19">
-        <v>0.068</v>
+        <v>0</v>
       </c>
       <c r="F19">
-        <v>0.147</v>
+        <v>0.098</v>
       </c>
       <c r="G19">
-        <v>0.064</v>
+        <v>0.043</v>
       </c>
       <c r="H19">
-        <v>0.044</v>
+        <v>0.02</v>
       </c>
       <c r="I19">
-        <v>0.044</v>
+        <v>0.025</v>
       </c>
       <c r="J19">
-        <v>0.03</v>
-      </c>
-      <c r="W19" t="s">
-        <v>41</v>
+        <v>0.039</v>
+      </c>
+      <c r="W19">
+        <v>0.02198378378378378</v>
       </c>
       <c r="X19">
+        <v>0.043</v>
+      </c>
+      <c r="Y19" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z19">
         <v>0.014</v>
       </c>
     </row>
-    <row r="20" spans="1:24">
+    <row r="20" spans="1:26">
       <c r="A20" s="2">
-        <v>46246</v>
+        <v>46254</v>
       </c>
       <c r="B20">
         <v>8</v>
       </c>
       <c r="C20">
-        <v>0.256</v>
+        <v>0.199</v>
       </c>
       <c r="D20">
-        <v>0.355</v>
+        <v>0.302</v>
       </c>
       <c r="E20">
-        <v>0.476</v>
+        <v>0.36</v>
       </c>
       <c r="F20">
-        <v>0.776</v>
+        <v>0.769</v>
       </c>
       <c r="G20">
-        <v>0.525</v>
+        <v>0.441</v>
       </c>
       <c r="H20">
-        <v>0.368</v>
+        <v>0.301</v>
       </c>
       <c r="I20">
-        <v>0.388</v>
+        <v>0.361</v>
       </c>
       <c r="J20">
-        <v>0.308</v>
-      </c>
-      <c r="W20" t="s">
-        <v>42</v>
+        <v>0.291</v>
+      </c>
+      <c r="W20">
+        <v>0.1725054054054054</v>
       </c>
       <c r="X20">
+        <v>0.5760000000000001</v>
+      </c>
+      <c r="Y20" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z20">
         <v>0.014</v>
       </c>
     </row>
-    <row r="21" spans="1:24">
+    <row r="21" spans="1:26">
       <c r="A21" s="2">
-        <v>46246</v>
+        <v>46254</v>
       </c>
       <c r="B21">
         <v>9</v>
       </c>
       <c r="C21">
-        <v>0.9320000000000001</v>
+        <v>0.918</v>
       </c>
       <c r="D21">
-        <v>0.903</v>
+        <v>0.961</v>
       </c>
       <c r="E21">
-        <v>1.424</v>
+        <v>1.438</v>
       </c>
       <c r="F21">
-        <v>1.958</v>
+        <v>1.779</v>
       </c>
       <c r="G21">
-        <v>1.403</v>
+        <v>1.276</v>
       </c>
       <c r="H21">
-        <v>0.727</v>
+        <v>0.803</v>
       </c>
       <c r="I21">
-        <v>0.787</v>
+        <v>0.78</v>
       </c>
       <c r="J21">
-        <v>0.842</v>
-      </c>
-      <c r="W21" t="s">
-        <v>43</v>
+        <v>0.725</v>
+      </c>
+      <c r="W21">
+        <v>0.399072972972973</v>
       </c>
       <c r="X21">
+        <v>2.123</v>
+      </c>
+      <c r="Y21" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z21">
         <v>0.014</v>
       </c>
     </row>
-    <row r="22" spans="1:24">
+    <row r="22" spans="1:26">
       <c r="A22" s="2">
-        <v>46246</v>
+        <v>46254</v>
       </c>
       <c r="B22">
         <v>10</v>
       </c>
       <c r="C22">
-        <v>1.686</v>
+        <v>1.642</v>
       </c>
       <c r="D22">
-        <v>1.752</v>
+        <v>1.727</v>
       </c>
       <c r="E22">
-        <v>2.482</v>
+        <v>2.425</v>
       </c>
       <c r="F22">
-        <v>2.881</v>
+        <v>2.606</v>
       </c>
       <c r="G22">
-        <v>2.323</v>
+        <v>2.131</v>
       </c>
       <c r="H22">
-        <v>1.071</v>
+        <v>0.948</v>
       </c>
       <c r="I22">
-        <v>1.047</v>
+        <v>1.017</v>
       </c>
       <c r="J22">
-        <v>1.017</v>
-      </c>
-      <c r="W22" t="s">
-        <v>44</v>
+        <v>0.966</v>
+      </c>
+      <c r="W22">
+        <v>0.5845891891891891</v>
       </c>
       <c r="X22">
+        <v>4.178</v>
+      </c>
+      <c r="Y22" t="s">
+        <v>46</v>
+      </c>
+      <c r="Z22">
         <v>0.014</v>
       </c>
     </row>
-    <row r="23" spans="1:24">
+    <row r="23" spans="1:26">
       <c r="A23" s="2">
-        <v>46246</v>
+        <v>46254</v>
       </c>
       <c r="B23">
         <v>11</v>
       </c>
       <c r="C23">
-        <v>2.328</v>
+        <v>2.266</v>
       </c>
       <c r="D23">
-        <v>2.388</v>
+        <v>2.407</v>
       </c>
       <c r="E23">
-        <v>3.428</v>
+        <v>3.426</v>
       </c>
       <c r="F23">
-        <v>3.609</v>
+        <v>3.438</v>
       </c>
       <c r="G23">
-        <v>2.896</v>
+        <v>2.847</v>
       </c>
       <c r="H23">
-        <v>1.303</v>
+        <v>1.548</v>
       </c>
       <c r="I23">
-        <v>1.457</v>
+        <v>1.437</v>
       </c>
       <c r="J23">
-        <v>1.331</v>
-      </c>
-      <c r="W23" t="s">
-        <v>45</v>
+        <v>1.386</v>
+      </c>
+      <c r="W23">
+        <v>0.7712270270270271</v>
       </c>
       <c r="X23">
+        <v>5.257</v>
+      </c>
+      <c r="Y23" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z23">
         <v>0.014</v>
       </c>
     </row>
-    <row r="24" spans="1:24">
+    <row r="24" spans="1:26">
       <c r="A24" s="2">
-        <v>46246</v>
+        <v>46254</v>
       </c>
       <c r="B24">
         <v>12</v>
       </c>
       <c r="C24">
-        <v>2.829</v>
+        <v>2.612</v>
       </c>
       <c r="D24">
-        <v>2.853</v>
+        <v>2.785</v>
       </c>
       <c r="E24">
-        <v>3.81</v>
+        <v>3.909</v>
       </c>
       <c r="F24">
-        <v>4.043</v>
+        <v>4.038</v>
       </c>
       <c r="G24">
-        <v>3.413</v>
+        <v>3.378</v>
       </c>
       <c r="H24">
-        <v>1.462</v>
+        <v>1.625</v>
       </c>
       <c r="I24">
         <v>1.445</v>
       </c>
       <c r="J24">
-        <v>1.536</v>
-      </c>
-      <c r="W24" t="s">
-        <v>46</v>
+        <v>1.55</v>
+      </c>
+      <c r="W24">
+        <v>0.9058216216216216</v>
       </c>
       <c r="X24">
+        <v>6.904</v>
+      </c>
+      <c r="Y24" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z24">
         <v>0.041</v>
       </c>
     </row>
-    <row r="25" spans="1:24">
+    <row r="25" spans="1:26">
       <c r="A25" s="2">
-        <v>46246</v>
+        <v>46254</v>
       </c>
       <c r="B25">
         <v>13</v>
       </c>
       <c r="C25">
-        <v>3.033</v>
+        <v>2.695</v>
       </c>
       <c r="D25">
-        <v>3.173</v>
+        <v>2.849</v>
       </c>
       <c r="E25">
-        <v>3.7</v>
+        <v>3.956</v>
       </c>
       <c r="F25">
-        <v>4.147</v>
+        <v>4.058</v>
       </c>
       <c r="G25">
-        <v>3.552</v>
+        <v>3.504</v>
       </c>
       <c r="H25">
-        <v>1.491</v>
+        <v>1.319</v>
       </c>
       <c r="I25">
         <v>1.445</v>
       </c>
       <c r="J25">
-        <v>1.611</v>
-      </c>
-      <c r="W25" t="s">
-        <v>47</v>
+        <v>1.627</v>
+      </c>
+      <c r="W25">
+        <v>0.910308108108108</v>
       </c>
       <c r="X25">
+        <v>7.090999999999999</v>
+      </c>
+      <c r="Y25" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z25">
         <v>0.06</v>
       </c>
     </row>
-    <row r="26" spans="1:24">
+    <row r="26" spans="1:26">
       <c r="A26" s="2">
-        <v>46246</v>
+        <v>46254</v>
       </c>
       <c r="B26">
         <v>14</v>
       </c>
       <c r="C26">
-        <v>3.102</v>
+        <v>2.693</v>
       </c>
       <c r="D26">
-        <v>3.033</v>
+        <v>2.866</v>
       </c>
       <c r="E26">
-        <v>3.615</v>
+        <v>3.817</v>
       </c>
       <c r="F26">
-        <v>4.054</v>
+        <v>4.053</v>
       </c>
       <c r="G26">
-        <v>3.552</v>
+        <v>3.546</v>
       </c>
       <c r="H26">
-        <v>0.854</v>
+        <v>0.949</v>
       </c>
       <c r="I26">
         <v>1.502</v>
       </c>
       <c r="J26">
-        <v>1.482</v>
-      </c>
-      <c r="W26" t="s">
-        <v>48</v>
+        <v>1.563</v>
+      </c>
+      <c r="W26">
+        <v>0.9091864864864864</v>
       </c>
       <c r="X26">
+        <v>7.092</v>
+      </c>
+      <c r="Y26" t="s">
+        <v>50</v>
+      </c>
+      <c r="Z26">
         <v>0.334</v>
       </c>
     </row>
-    <row r="27" spans="1:24">
+    <row r="27" spans="1:26">
       <c r="A27" s="2">
-        <v>46246</v>
+        <v>46254</v>
       </c>
       <c r="B27">
         <v>15</v>
       </c>
       <c r="C27">
-        <v>2.719</v>
+        <v>2.557</v>
       </c>
       <c r="D27">
-        <v>2.79</v>
+        <v>2.822</v>
       </c>
       <c r="E27">
-        <v>3.607</v>
+        <v>3.853</v>
       </c>
       <c r="F27">
-        <v>3.9</v>
+        <v>3.924</v>
       </c>
       <c r="G27">
-        <v>3.413</v>
+        <v>3.408</v>
       </c>
       <c r="H27">
-        <v>0.831</v>
+        <v>0.927</v>
       </c>
       <c r="I27">
         <v>1.502</v>
       </c>
       <c r="J27">
-        <v>1.334</v>
-      </c>
-      <c r="W27" t="s">
-        <v>49</v>
+        <v>1.377</v>
+      </c>
+      <c r="W27">
+        <v>0.8802486486486486</v>
       </c>
       <c r="X27">
+        <v>7.032</v>
+      </c>
+      <c r="Y27" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z27">
         <v>1.057</v>
       </c>
     </row>
-    <row r="28" spans="1:24">
+    <row r="28" spans="1:26">
       <c r="A28" s="2">
-        <v>46246</v>
+        <v>46254</v>
       </c>
       <c r="B28">
         <v>16</v>
       </c>
       <c r="C28">
-        <v>2.38</v>
+        <v>2.172</v>
       </c>
       <c r="D28">
-        <v>2.674</v>
+        <v>2.553</v>
       </c>
       <c r="E28">
-        <v>3.668</v>
+        <v>3.807</v>
       </c>
       <c r="F28">
-        <v>3.329</v>
+        <v>3.316</v>
       </c>
       <c r="G28">
-        <v>3.097</v>
+        <v>3.04</v>
       </c>
       <c r="H28">
-        <v>0.806</v>
+        <v>0.924</v>
       </c>
       <c r="I28">
         <v>1.502</v>
       </c>
       <c r="J28">
-        <v>1.222</v>
-      </c>
-      <c r="W28" t="s">
-        <v>50</v>
+        <v>1.281</v>
+      </c>
+      <c r="W28">
+        <v>0.7438594594594594</v>
       </c>
       <c r="X28">
+        <v>6.438</v>
+      </c>
+      <c r="Y28" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z28">
         <v>1.652</v>
       </c>
     </row>
-    <row r="29" spans="1:24">
+    <row r="29" spans="1:26">
       <c r="A29" s="2">
-        <v>46246</v>
+        <v>46254</v>
       </c>
       <c r="B29">
         <v>17</v>
       </c>
       <c r="C29">
-        <v>2.04</v>
+        <v>1.928</v>
       </c>
       <c r="D29">
-        <v>2.382</v>
+        <v>2.143</v>
       </c>
       <c r="E29">
-        <v>3.189</v>
+        <v>3.322</v>
       </c>
       <c r="F29">
-        <v>2.399</v>
+        <v>2.387</v>
       </c>
       <c r="G29">
-        <v>2.525</v>
+        <v>2.48</v>
       </c>
       <c r="H29">
-        <v>0.791</v>
+        <v>0.927</v>
       </c>
       <c r="I29">
         <v>1.169</v>
       </c>
       <c r="J29">
-        <v>0.8120000000000001</v>
-      </c>
-      <c r="W29" t="s">
-        <v>51</v>
+        <v>0.904</v>
+      </c>
+      <c r="W29">
+        <v>0.5354621621621621</v>
       </c>
       <c r="X29">
+        <v>5.078</v>
+      </c>
+      <c r="Y29" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z29">
         <v>2.17</v>
       </c>
     </row>
-    <row r="30" spans="1:24">
+    <row r="30" spans="1:26">
       <c r="A30" s="2">
-        <v>46246</v>
+        <v>46254</v>
       </c>
       <c r="B30">
         <v>18</v>
       </c>
       <c r="C30">
-        <v>1.363</v>
+        <v>1.239</v>
       </c>
       <c r="D30">
-        <v>1.764</v>
+        <v>1.439</v>
       </c>
       <c r="E30">
-        <v>2.22</v>
+        <v>2.251</v>
       </c>
       <c r="F30">
-        <v>1.454</v>
+        <v>1.422</v>
       </c>
       <c r="G30">
-        <v>1.655</v>
+        <v>1.625</v>
       </c>
       <c r="H30">
-        <v>0.649</v>
+        <v>0.849</v>
       </c>
       <c r="I30">
-        <v>0.966</v>
+        <v>0.991</v>
       </c>
       <c r="J30">
-        <v>0.333</v>
-      </c>
-      <c r="W30" t="s">
-        <v>52</v>
+        <v>0.59</v>
+      </c>
+      <c r="W30">
+        <v>0.3189891891891892</v>
       </c>
       <c r="X30">
+        <v>3.482</v>
+      </c>
+      <c r="Y30" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z30">
         <v>1.983</v>
       </c>
     </row>
-    <row r="31" spans="1:24">
+    <row r="31" spans="1:26">
       <c r="A31" s="2">
-        <v>46246</v>
+        <v>46254</v>
       </c>
       <c r="B31">
         <v>19</v>
       </c>
       <c r="C31">
-        <v>0.754</v>
+        <v>0.588</v>
       </c>
       <c r="D31">
-        <v>0.955</v>
+        <v>0.726</v>
       </c>
       <c r="E31">
-        <v>1.234</v>
+        <v>1.174</v>
       </c>
       <c r="F31">
-        <v>0.542</v>
+        <v>0.504</v>
       </c>
       <c r="G31">
-        <v>0.792</v>
+        <v>0.752</v>
       </c>
       <c r="H31">
-        <v>0.455</v>
+        <v>0.49</v>
       </c>
       <c r="I31">
-        <v>0.491</v>
+        <v>0.603</v>
       </c>
       <c r="J31">
-        <v>0.217</v>
-      </c>
-      <c r="W31" t="s">
-        <v>53</v>
+        <v>0.223</v>
+      </c>
+      <c r="W31">
+        <v>0.1130594594594595</v>
       </c>
       <c r="X31">
+        <v>1.721</v>
+      </c>
+      <c r="Y31" t="s">
+        <v>55</v>
+      </c>
+      <c r="Z31">
         <v>1.764</v>
       </c>
     </row>
-    <row r="32" spans="1:24">
+    <row r="32" spans="1:26">
       <c r="A32" s="2">
-        <v>46246</v>
+        <v>46254</v>
       </c>
       <c r="B32">
         <v>20</v>
       </c>
       <c r="C32">
-        <v>0.204</v>
+        <v>0.142</v>
       </c>
       <c r="D32">
-        <v>0.275</v>
+        <v>0.188</v>
       </c>
       <c r="E32">
-        <v>0.472</v>
+        <v>0.376</v>
       </c>
       <c r="F32">
-        <v>0.172</v>
+        <v>0.14</v>
       </c>
       <c r="G32">
-        <v>0.248</v>
+        <v>0.192</v>
       </c>
       <c r="H32">
-        <v>0.227</v>
+        <v>0.17</v>
       </c>
       <c r="I32">
-        <v>0.112</v>
+        <v>0.125</v>
       </c>
       <c r="J32">
         <v>0.08599999999999999</v>
       </c>
-      <c r="W32" t="s">
-        <v>54</v>
+      <c r="W32">
+        <v>0.03140540540540541</v>
       </c>
       <c r="X32">
+        <v>0.458</v>
+      </c>
+      <c r="Y32" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z32">
         <v>1.184</v>
       </c>
     </row>
-    <row r="33" spans="1:24">
+    <row r="33" spans="1:26">
       <c r="A33" s="2">
-        <v>46246</v>
+        <v>46254</v>
       </c>
       <c r="B33">
         <v>21</v>
       </c>
       <c r="C33">
-        <v>0.021</v>
+        <v>0</v>
       </c>
       <c r="D33">
-        <v>0.023</v>
+        <v>0</v>
       </c>
       <c r="E33">
-        <v>0.063</v>
+        <v>0</v>
       </c>
       <c r="F33">
-        <v>0.011</v>
+        <v>0</v>
       </c>
       <c r="G33">
-        <v>0.011</v>
+        <v>0</v>
       </c>
       <c r="H33">
         <v>0</v>
@@ -2240,16 +2432,22 @@
       <c r="J33">
         <v>0</v>
       </c>
-      <c r="W33" t="s">
-        <v>55</v>
+      <c r="W33">
+        <v>0</v>
       </c>
       <c r="X33">
+        <v>0.047</v>
+      </c>
+      <c r="Y33" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z33">
         <v>0.583</v>
       </c>
     </row>
-    <row r="34" spans="1:24">
+    <row r="34" spans="1:26">
       <c r="A34" s="2">
-        <v>46246</v>
+        <v>46254</v>
       </c>
       <c r="B34">
         <v>22</v>
@@ -2261,7 +2459,7 @@
         <v>0</v>
       </c>
       <c r="E34">
-        <v>0.061</v>
+        <v>0</v>
       </c>
       <c r="F34">
         <v>0</v>
@@ -2276,18 +2474,24 @@
         <v>0</v>
       </c>
       <c r="J34">
-        <v>0.013</v>
-      </c>
-      <c r="W34" t="s">
-        <v>56</v>
+        <v>0</v>
+      </c>
+      <c r="W34">
+        <v>0</v>
       </c>
       <c r="X34">
+        <v>0</v>
+      </c>
+      <c r="Y34" t="s">
+        <v>58</v>
+      </c>
+      <c r="Z34">
         <v>0.427</v>
       </c>
     </row>
-    <row r="35" spans="1:24">
+    <row r="35" spans="1:26">
       <c r="A35" s="2">
-        <v>46246</v>
+        <v>46254</v>
       </c>
       <c r="B35">
         <v>23</v>
@@ -2299,7 +2503,7 @@
         <v>0</v>
       </c>
       <c r="E35">
-        <v>0.079</v>
+        <v>0</v>
       </c>
       <c r="F35">
         <v>0</v>
@@ -2314,18 +2518,24 @@
         <v>0</v>
       </c>
       <c r="J35">
-        <v>0.013</v>
-      </c>
-      <c r="W35" t="s">
-        <v>57</v>
+        <v>0</v>
+      </c>
+      <c r="W35">
+        <v>0</v>
       </c>
       <c r="X35">
+        <v>0</v>
+      </c>
+      <c r="Y35" t="s">
+        <v>59</v>
+      </c>
+      <c r="Z35">
         <v>0.035</v>
       </c>
     </row>
-    <row r="36" spans="1:24">
+    <row r="36" spans="1:26">
       <c r="A36" s="2">
-        <v>46246</v>
+        <v>46254</v>
       </c>
       <c r="B36">
         <v>24</v>
@@ -2337,7 +2547,7 @@
         <v>0</v>
       </c>
       <c r="E36">
-        <v>0.098</v>
+        <v>0</v>
       </c>
       <c r="F36">
         <v>0</v>
@@ -2352,18 +2562,24 @@
         <v>0</v>
       </c>
       <c r="J36">
-        <v>0.013</v>
-      </c>
-      <c r="W36" t="s">
-        <v>58</v>
+        <v>0</v>
+      </c>
+      <c r="W36">
+        <v>0</v>
       </c>
       <c r="X36">
+        <v>0</v>
+      </c>
+      <c r="Y36" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z36">
         <v>0.091</v>
       </c>
     </row>
-    <row r="37" spans="1:24">
+    <row r="37" spans="1:26">
       <c r="A37" s="2">
-        <v>46247</v>
+        <v>46255</v>
       </c>
       <c r="B37">
         <v>1</v>
@@ -2375,7 +2591,7 @@
         <v>0</v>
       </c>
       <c r="E37">
-        <v>0.161</v>
+        <v>0.014</v>
       </c>
       <c r="F37">
         <v>0</v>
@@ -2392,16 +2608,22 @@
       <c r="J37">
         <v>0.014</v>
       </c>
-      <c r="W37" t="s">
-        <v>59</v>
+      <c r="W37">
+        <v>0</v>
       </c>
       <c r="X37">
+        <v>0</v>
+      </c>
+      <c r="Y37" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z37">
         <v>0.091</v>
       </c>
     </row>
-    <row r="38" spans="1:24">
+    <row r="38" spans="1:26">
       <c r="A38" s="2">
-        <v>46247</v>
+        <v>46255</v>
       </c>
       <c r="B38">
         <v>2</v>
@@ -2413,7 +2635,7 @@
         <v>0</v>
       </c>
       <c r="E38">
-        <v>0.147</v>
+        <v>0.014</v>
       </c>
       <c r="F38">
         <v>0</v>
@@ -2428,18 +2650,24 @@
         <v>0</v>
       </c>
       <c r="J38">
-        <v>0.02</v>
-      </c>
-      <c r="W38" t="s">
-        <v>60</v>
+        <v>0.014</v>
+      </c>
+      <c r="W38">
+        <v>0</v>
       </c>
       <c r="X38">
         <v>0</v>
       </c>
-    </row>
-    <row r="39" spans="1:24">
+      <c r="Y38" t="s">
+        <v>62</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:26">
       <c r="A39" s="2">
-        <v>46247</v>
+        <v>46255</v>
       </c>
       <c r="B39">
         <v>3</v>
@@ -2451,7 +2679,7 @@
         <v>0</v>
       </c>
       <c r="E39">
-        <v>0.128</v>
+        <v>0</v>
       </c>
       <c r="F39">
         <v>0</v>
@@ -2466,18 +2694,24 @@
         <v>0</v>
       </c>
       <c r="J39">
-        <v>0.02</v>
-      </c>
-      <c r="W39" t="s">
-        <v>61</v>
+        <v>0.014</v>
+      </c>
+      <c r="W39">
+        <v>0</v>
       </c>
       <c r="X39">
         <v>0</v>
       </c>
-    </row>
-    <row r="40" spans="1:24">
+      <c r="Y39" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:26">
       <c r="A40" s="2">
-        <v>46247</v>
+        <v>46255</v>
       </c>
       <c r="B40">
         <v>4</v>
@@ -2489,7 +2723,7 @@
         <v>0</v>
       </c>
       <c r="E40">
-        <v>0.092</v>
+        <v>0.012</v>
       </c>
       <c r="F40">
         <v>0</v>
@@ -2504,18 +2738,24 @@
         <v>0</v>
       </c>
       <c r="J40">
-        <v>0.02</v>
-      </c>
-      <c r="W40" t="s">
-        <v>62</v>
+        <v>0.015</v>
+      </c>
+      <c r="W40">
+        <v>0</v>
       </c>
       <c r="X40">
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="1:24">
+      <c r="Y40" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:26">
       <c r="A41" s="2">
-        <v>46247</v>
+        <v>46255</v>
       </c>
       <c r="B41">
         <v>5</v>
@@ -2527,7 +2767,7 @@
         <v>0</v>
       </c>
       <c r="E41">
-        <v>0.06900000000000001</v>
+        <v>0.041</v>
       </c>
       <c r="F41">
         <v>0</v>
@@ -2542,18 +2782,24 @@
         <v>0</v>
       </c>
       <c r="J41">
-        <v>0.02</v>
-      </c>
-      <c r="W41" t="s">
-        <v>63</v>
+        <v>0.015</v>
+      </c>
+      <c r="W41">
+        <v>0</v>
       </c>
       <c r="X41">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="1:24">
+      <c r="Y41" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:26">
       <c r="A42" s="2">
-        <v>46247</v>
+        <v>46255</v>
       </c>
       <c r="B42">
         <v>6</v>
@@ -2565,7 +2811,7 @@
         <v>0</v>
       </c>
       <c r="E42">
-        <v>0</v>
+        <v>0.057</v>
       </c>
       <c r="F42">
         <v>0</v>
@@ -2580,568 +2826,658 @@
         <v>0</v>
       </c>
       <c r="J42">
-        <v>0.02</v>
-      </c>
-      <c r="W42" t="s">
-        <v>64</v>
+        <v>0.021</v>
+      </c>
+      <c r="W42">
+        <v>0</v>
       </c>
       <c r="X42">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="1:24">
+      <c r="Y42" t="s">
+        <v>66</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:26">
       <c r="A43" s="2">
-        <v>46247</v>
+        <v>46255</v>
       </c>
       <c r="B43">
         <v>7</v>
       </c>
       <c r="C43">
-        <v>0.024</v>
+        <v>0.014</v>
       </c>
       <c r="D43">
-        <v>0.023</v>
+        <v>0</v>
       </c>
       <c r="E43">
+        <v>0.045</v>
+      </c>
+      <c r="F43">
+        <v>0.094</v>
+      </c>
+      <c r="G43">
+        <v>0.032</v>
+      </c>
+      <c r="H43">
         <v>0.016</v>
-      </c>
-      <c r="F43">
-        <v>0.098</v>
-      </c>
-      <c r="G43">
-        <v>0.046</v>
-      </c>
-      <c r="H43">
-        <v>0.012</v>
       </c>
       <c r="I43">
         <v>0.021</v>
       </c>
       <c r="J43">
-        <v>0.044</v>
-      </c>
-      <c r="W43" t="s">
-        <v>65</v>
+        <v>0.037</v>
+      </c>
+      <c r="W43">
+        <v>0.02108648648648648</v>
       </c>
       <c r="X43">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:24">
+        <v>0.041</v>
+      </c>
+      <c r="Y43" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:26">
       <c r="A44" s="2">
-        <v>46247</v>
+        <v>46255</v>
       </c>
       <c r="B44">
         <v>8</v>
       </c>
       <c r="C44">
-        <v>0.303</v>
+        <v>0.201</v>
       </c>
       <c r="D44">
-        <v>0.318</v>
+        <v>0.28</v>
       </c>
       <c r="E44">
-        <v>0.197</v>
+        <v>0.362</v>
       </c>
       <c r="F44">
-        <v>0.634</v>
+        <v>0.75</v>
       </c>
       <c r="G44">
-        <v>0.319</v>
+        <v>0.406</v>
       </c>
       <c r="H44">
-        <v>0.145</v>
+        <v>0.296</v>
       </c>
       <c r="I44">
-        <v>0.191</v>
+        <v>0.328</v>
       </c>
       <c r="J44">
-        <v>0.194</v>
-      </c>
-      <c r="W44" t="s">
-        <v>66</v>
+        <v>0.209</v>
+      </c>
+      <c r="W44">
+        <v>0.1682432432432432</v>
       </c>
       <c r="X44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:24">
+        <v>0.537</v>
+      </c>
+      <c r="Y44" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:26">
       <c r="A45" s="2">
-        <v>46247</v>
+        <v>46255</v>
       </c>
       <c r="B45">
         <v>9</v>
       </c>
       <c r="C45">
-        <v>1.001</v>
+        <v>0.899</v>
       </c>
       <c r="D45">
-        <v>0.999</v>
+        <v>1.006</v>
       </c>
       <c r="E45">
-        <v>0.523</v>
+        <v>1.38</v>
       </c>
       <c r="F45">
-        <v>1.401</v>
+        <v>1.722</v>
       </c>
       <c r="G45">
+        <v>1.23</v>
+      </c>
+      <c r="H45">
         <v>0.789</v>
       </c>
-      <c r="H45">
-        <v>0.393</v>
-      </c>
       <c r="I45">
-        <v>0.513</v>
+        <v>0.697</v>
       </c>
       <c r="J45">
-        <v>0.622</v>
-      </c>
-      <c r="W45" t="s">
-        <v>67</v>
+        <v>0.797</v>
+      </c>
+      <c r="W45">
+        <v>0.3862864864864864</v>
       </c>
       <c r="X45">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:24">
+        <v>1.931</v>
+      </c>
+      <c r="Y45" t="s">
+        <v>69</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:26">
       <c r="A46" s="2">
-        <v>46247</v>
+        <v>46255</v>
       </c>
       <c r="B46">
         <v>10</v>
       </c>
       <c r="C46">
-        <v>1.634</v>
+        <v>1.534</v>
       </c>
       <c r="D46">
-        <v>1.696</v>
+        <v>1.645</v>
       </c>
       <c r="E46">
-        <v>0.958</v>
+        <v>2.407</v>
       </c>
       <c r="F46">
-        <v>2.008</v>
+        <v>2.554</v>
       </c>
       <c r="G46">
-        <v>1.636</v>
+        <v>2.131</v>
       </c>
       <c r="H46">
-        <v>0.649</v>
+        <v>1.249</v>
       </c>
       <c r="I46">
-        <v>0.578</v>
+        <v>1.017</v>
       </c>
       <c r="J46">
-        <v>0.944</v>
-      </c>
-      <c r="W46" t="s">
-        <v>68</v>
+        <v>1.005</v>
+      </c>
+      <c r="W46">
+        <v>0.5729243243243243</v>
       </c>
       <c r="X46">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:24">
+        <v>3.96</v>
+      </c>
+      <c r="Y46" t="s">
+        <v>70</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:26">
       <c r="A47" s="2">
-        <v>46247</v>
+        <v>46255</v>
       </c>
       <c r="B47">
         <v>11</v>
       </c>
       <c r="C47">
-        <v>2.017</v>
+        <v>1.749</v>
       </c>
       <c r="D47">
-        <v>2.348</v>
+        <v>2.324</v>
       </c>
       <c r="E47">
-        <v>1.314</v>
+        <v>3.214</v>
       </c>
       <c r="F47">
-        <v>2.329</v>
+        <v>3.457</v>
       </c>
       <c r="G47">
-        <v>1.879</v>
+        <v>2.885</v>
       </c>
       <c r="H47">
-        <v>0.903</v>
+        <v>1.483</v>
       </c>
       <c r="I47">
-        <v>0.882</v>
+        <v>1.437</v>
       </c>
       <c r="J47">
-        <v>1.132</v>
-      </c>
-      <c r="W47" t="s">
-        <v>69</v>
+        <v>1.416</v>
+      </c>
+      <c r="W47">
+        <v>0.7754891891891891</v>
       </c>
       <c r="X47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:24">
+        <v>5.249</v>
+      </c>
+      <c r="Y47" t="s">
+        <v>71</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:26">
       <c r="A48" s="2">
-        <v>46247</v>
+        <v>46255</v>
       </c>
       <c r="B48">
         <v>12</v>
       </c>
       <c r="C48">
-        <v>2.325</v>
+        <v>2.231</v>
       </c>
       <c r="D48">
-        <v>2.801</v>
+        <v>2.515</v>
       </c>
       <c r="E48">
-        <v>1.581</v>
+        <v>3.49</v>
       </c>
       <c r="F48">
-        <v>2.802</v>
+        <v>3.987</v>
       </c>
       <c r="G48">
-        <v>2.352</v>
+        <v>3.378</v>
       </c>
       <c r="H48">
-        <v>1.201</v>
+        <v>1.309</v>
       </c>
       <c r="I48">
-        <v>1.396</v>
+        <v>1.445</v>
       </c>
       <c r="J48">
-        <v>1.243</v>
-      </c>
-      <c r="W48" t="s">
-        <v>70</v>
+        <v>1.572</v>
+      </c>
+      <c r="W48">
+        <v>0.8943810810810811</v>
       </c>
       <c r="X48">
+        <v>6.702</v>
+      </c>
+      <c r="Y48" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z48">
         <v>0.033</v>
       </c>
     </row>
-    <row r="49" spans="1:24">
+    <row r="49" spans="1:26">
       <c r="A49" s="2">
-        <v>46247</v>
+        <v>46255</v>
       </c>
       <c r="B49">
         <v>13</v>
       </c>
       <c r="C49">
-        <v>2.607</v>
+        <v>2.401</v>
       </c>
       <c r="D49">
-        <v>3.074</v>
+        <v>2.696</v>
       </c>
       <c r="E49">
-        <v>1.592</v>
+        <v>3.644</v>
       </c>
       <c r="F49">
-        <v>2.826</v>
+        <v>4.069</v>
       </c>
       <c r="G49">
-        <v>2.654</v>
+        <v>3.447</v>
       </c>
       <c r="H49">
-        <v>1.329</v>
+        <v>1.377</v>
       </c>
       <c r="I49">
-        <v>1.396</v>
+        <v>1.445</v>
       </c>
       <c r="J49">
-        <v>1.422</v>
-      </c>
-      <c r="W49" t="s">
-        <v>71</v>
+        <v>1.487</v>
+      </c>
+      <c r="W49">
+        <v>0.9127756756756756</v>
       </c>
       <c r="X49">
+        <v>7.093</v>
+      </c>
+      <c r="Y49" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z49">
         <v>0.051</v>
       </c>
     </row>
-    <row r="50" spans="1:24">
+    <row r="50" spans="1:26">
       <c r="A50" s="2">
-        <v>46247</v>
+        <v>46255</v>
       </c>
       <c r="B50">
         <v>14</v>
       </c>
       <c r="C50">
-        <v>2.584</v>
+        <v>2.34</v>
       </c>
       <c r="D50">
-        <v>3.113</v>
+        <v>2.684</v>
       </c>
       <c r="E50">
-        <v>1.756</v>
+        <v>3.663</v>
       </c>
       <c r="F50">
-        <v>3.088</v>
+        <v>4.049</v>
       </c>
       <c r="G50">
-        <v>2.779</v>
+        <v>3.546</v>
       </c>
       <c r="H50">
-        <v>1.148</v>
+        <v>1.018</v>
       </c>
       <c r="I50">
-        <v>1.452</v>
+        <v>1.502</v>
       </c>
       <c r="J50">
-        <v>1.418</v>
-      </c>
-      <c r="W50" t="s">
-        <v>72</v>
+        <v>1.457</v>
+      </c>
+      <c r="W50">
+        <v>0.9082891891891892</v>
       </c>
       <c r="X50">
+        <v>7.092</v>
+      </c>
+      <c r="Y50" t="s">
+        <v>74</v>
+      </c>
+      <c r="Z50">
         <v>0.28</v>
       </c>
     </row>
-    <row r="51" spans="1:24">
+    <row r="51" spans="1:26">
       <c r="A51" s="2">
-        <v>46247</v>
+        <v>46255</v>
       </c>
       <c r="B51">
         <v>15</v>
       </c>
       <c r="C51">
-        <v>2.514</v>
+        <v>2.219</v>
       </c>
       <c r="D51">
-        <v>2.937</v>
+        <v>2.659</v>
       </c>
       <c r="E51">
-        <v>2.314</v>
+        <v>3.744</v>
       </c>
       <c r="F51">
-        <v>3.093</v>
+        <v>3.909</v>
       </c>
       <c r="G51">
-        <v>2.761</v>
+        <v>3.408</v>
       </c>
       <c r="H51">
-        <v>1.152</v>
+        <v>0.927</v>
       </c>
       <c r="I51">
-        <v>1.506</v>
+        <v>1.502</v>
       </c>
       <c r="J51">
-        <v>1.316</v>
-      </c>
-      <c r="W51" t="s">
-        <v>73</v>
+        <v>1.331</v>
+      </c>
+      <c r="W51">
+        <v>0.8768837837837837</v>
       </c>
       <c r="X51">
+        <v>7.031</v>
+      </c>
+      <c r="Y51" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z51">
         <v>1.108</v>
       </c>
     </row>
-    <row r="52" spans="1:24">
+    <row r="52" spans="1:26">
       <c r="A52" s="2">
-        <v>46247</v>
+        <v>46255</v>
       </c>
       <c r="B52">
         <v>16</v>
       </c>
       <c r="C52">
-        <v>2.118</v>
+        <v>1.986</v>
       </c>
       <c r="D52">
-        <v>2.688</v>
+        <v>2.5</v>
       </c>
       <c r="E52">
-        <v>2.604</v>
+        <v>3.547</v>
       </c>
       <c r="F52">
-        <v>2.722</v>
+        <v>3.317</v>
       </c>
       <c r="G52">
-        <v>2.52</v>
+        <v>3.04</v>
       </c>
       <c r="H52">
-        <v>1.126</v>
+        <v>0.924</v>
       </c>
       <c r="I52">
-        <v>1.506</v>
+        <v>1.502</v>
       </c>
       <c r="J52">
-        <v>1.207</v>
-      </c>
-      <c r="W52" t="s">
-        <v>74</v>
+        <v>1.229</v>
+      </c>
+      <c r="W52">
+        <v>0.7440837837837838</v>
       </c>
       <c r="X52">
+        <v>6.436</v>
+      </c>
+      <c r="Y52" t="s">
+        <v>76</v>
+      </c>
+      <c r="Z52">
         <v>1.505</v>
       </c>
     </row>
-    <row r="53" spans="1:24">
+    <row r="53" spans="1:26">
       <c r="A53" s="2">
-        <v>46247</v>
+        <v>46255</v>
       </c>
       <c r="B53">
         <v>17</v>
       </c>
       <c r="C53">
-        <v>1.582</v>
+        <v>1.52</v>
       </c>
       <c r="D53">
-        <v>2.146</v>
+        <v>2.11</v>
       </c>
       <c r="E53">
-        <v>2.485</v>
+        <v>3.163</v>
       </c>
       <c r="F53">
-        <v>2.082</v>
+        <v>2.323</v>
       </c>
       <c r="G53">
-        <v>2.09</v>
+        <v>2.48</v>
       </c>
       <c r="H53">
-        <v>1.079</v>
+        <v>0.927</v>
       </c>
       <c r="I53">
-        <v>1.487</v>
+        <v>1.341</v>
       </c>
       <c r="J53">
         <v>0.82</v>
       </c>
-      <c r="W53" t="s">
-        <v>75</v>
+      <c r="W53">
+        <v>0.5211054054054054</v>
       </c>
       <c r="X53">
+        <v>5.021</v>
+      </c>
+      <c r="Y53" t="s">
+        <v>77</v>
+      </c>
+      <c r="Z53">
         <v>2.043</v>
       </c>
     </row>
-    <row r="54" spans="1:24">
+    <row r="54" spans="1:26">
       <c r="A54" s="2">
-        <v>46247</v>
+        <v>46255</v>
       </c>
       <c r="B54">
         <v>18</v>
       </c>
       <c r="C54">
-        <v>1.096</v>
+        <v>1.022</v>
       </c>
       <c r="D54">
-        <v>1.349</v>
+        <v>1.297</v>
       </c>
       <c r="E54">
-        <v>1.826</v>
+        <v>2.241</v>
       </c>
       <c r="F54">
-        <v>1.458</v>
+        <v>1.415</v>
       </c>
       <c r="G54">
-        <v>1.563</v>
+        <v>1.567</v>
       </c>
       <c r="H54">
-        <v>0.826</v>
+        <v>0.825</v>
       </c>
       <c r="I54">
-        <v>1.091</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="J54">
         <v>0.333</v>
       </c>
-      <c r="W54" t="s">
-        <v>76</v>
+      <c r="W54">
+        <v>0.3174189189189189</v>
       </c>
       <c r="X54">
+        <v>3.482</v>
+      </c>
+      <c r="Y54" t="s">
+        <v>78</v>
+      </c>
+      <c r="Z54">
         <v>1.84</v>
       </c>
     </row>
-    <row r="55" spans="1:24">
+    <row r="55" spans="1:26">
       <c r="A55" s="2">
-        <v>46247</v>
+        <v>46255</v>
       </c>
       <c r="B55">
         <v>19</v>
       </c>
       <c r="C55">
-        <v>0.586</v>
+        <v>0.536</v>
       </c>
       <c r="D55">
-        <v>0.656</v>
+        <v>0.658</v>
       </c>
       <c r="E55">
-        <v>1.114</v>
+        <v>1.19</v>
       </c>
       <c r="F55">
-        <v>0.543</v>
+        <v>0.493</v>
       </c>
       <c r="G55">
-        <v>0.869</v>
+        <v>0.722</v>
       </c>
       <c r="H55">
-        <v>0.532</v>
+        <v>0.49</v>
       </c>
       <c r="I55">
-        <v>0.542</v>
+        <v>0.57</v>
       </c>
       <c r="J55">
-        <v>0.208</v>
-      </c>
-      <c r="W55" t="s">
-        <v>77</v>
+        <v>0.217</v>
+      </c>
+      <c r="W55">
+        <v>0.1105918918918919</v>
       </c>
       <c r="X55">
+        <v>1.692</v>
+      </c>
+      <c r="Y55" t="s">
+        <v>79</v>
+      </c>
+      <c r="Z55">
         <v>1.826</v>
       </c>
     </row>
-    <row r="56" spans="1:24">
+    <row r="56" spans="1:26">
       <c r="A56" s="2">
-        <v>46247</v>
+        <v>46255</v>
       </c>
       <c r="B56">
         <v>20</v>
       </c>
       <c r="C56">
-        <v>0.204</v>
+        <v>0.11</v>
       </c>
       <c r="D56">
-        <v>0.179</v>
+        <v>0.137</v>
       </c>
       <c r="E56">
-        <v>0.392</v>
+        <v>0.3</v>
       </c>
       <c r="F56">
-        <v>0.171</v>
+        <v>0.14</v>
       </c>
       <c r="G56">
-        <v>0.242</v>
+        <v>0.192</v>
       </c>
       <c r="H56">
-        <v>0.213</v>
+        <v>0.145</v>
       </c>
       <c r="I56">
-        <v>0.197</v>
+        <v>0.116</v>
       </c>
       <c r="J56">
-        <v>0.08599999999999999</v>
-      </c>
-      <c r="W56" t="s">
-        <v>78</v>
+        <v>0.065</v>
+      </c>
+      <c r="W56">
+        <v>0.03140540540540541</v>
       </c>
       <c r="X56">
+        <v>0.446</v>
+      </c>
+      <c r="Y56" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z56">
         <v>1.02</v>
       </c>
     </row>
-    <row r="57" spans="1:24">
+    <row r="57" spans="1:26">
       <c r="A57" s="2">
-        <v>46247</v>
+        <v>46255</v>
       </c>
       <c r="B57">
         <v>21</v>
       </c>
       <c r="C57">
-        <v>0.023</v>
+        <v>0</v>
       </c>
       <c r="D57">
-        <v>0.018</v>
+        <v>0</v>
       </c>
       <c r="E57">
-        <v>0.08799999999999999</v>
+        <v>0</v>
       </c>
       <c r="F57">
-        <v>0.011</v>
+        <v>0</v>
       </c>
       <c r="G57">
-        <v>0.011</v>
+        <v>0</v>
       </c>
       <c r="H57">
         <v>0</v>
@@ -3152,16 +3488,22 @@
       <c r="J57">
         <v>0</v>
       </c>
-      <c r="W57" t="s">
-        <v>79</v>
+      <c r="W57">
+        <v>0</v>
       </c>
       <c r="X57">
+        <v>0.037</v>
+      </c>
+      <c r="Y57" t="s">
+        <v>81</v>
+      </c>
+      <c r="Z57">
         <v>0.508</v>
       </c>
     </row>
-    <row r="58" spans="1:24">
+    <row r="58" spans="1:26">
       <c r="A58" s="2">
-        <v>46247</v>
+        <v>46255</v>
       </c>
       <c r="B58">
         <v>22</v>
@@ -3173,7 +3515,7 @@
         <v>0</v>
       </c>
       <c r="E58">
-        <v>0.078</v>
+        <v>0</v>
       </c>
       <c r="F58">
         <v>0</v>
@@ -3190,16 +3532,22 @@
       <c r="J58">
         <v>0</v>
       </c>
-      <c r="W58" t="s">
-        <v>80</v>
+      <c r="W58">
+        <v>0</v>
       </c>
       <c r="X58">
+        <v>0</v>
+      </c>
+      <c r="Y58" t="s">
+        <v>82</v>
+      </c>
+      <c r="Z58">
         <v>0.422</v>
       </c>
     </row>
-    <row r="59" spans="1:24">
+    <row r="59" spans="1:26">
       <c r="A59" s="2">
-        <v>46247</v>
+        <v>46255</v>
       </c>
       <c r="B59">
         <v>23</v>
@@ -3211,7 +3559,7 @@
         <v>0</v>
       </c>
       <c r="E59">
-        <v>0.064</v>
+        <v>0</v>
       </c>
       <c r="F59">
         <v>0</v>
@@ -3228,16 +3576,22 @@
       <c r="J59">
         <v>0</v>
       </c>
-      <c r="W59" t="s">
-        <v>81</v>
+      <c r="W59">
+        <v>0</v>
       </c>
       <c r="X59">
+        <v>0</v>
+      </c>
+      <c r="Y59" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z59">
         <v>0.045</v>
       </c>
     </row>
-    <row r="60" spans="1:24">
+    <row r="60" spans="1:26">
       <c r="A60" s="2">
-        <v>46247</v>
+        <v>46255</v>
       </c>
       <c r="B60">
         <v>24</v>
@@ -3249,7 +3603,7 @@
         <v>0</v>
       </c>
       <c r="E60">
-        <v>0.029</v>
+        <v>0</v>
       </c>
       <c r="F60">
         <v>0</v>
@@ -3266,16 +3620,22 @@
       <c r="J60">
         <v>0</v>
       </c>
-      <c r="W60" t="s">
-        <v>82</v>
+      <c r="W60">
+        <v>0</v>
       </c>
       <c r="X60">
+        <v>0</v>
+      </c>
+      <c r="Y60" t="s">
+        <v>84</v>
+      </c>
+      <c r="Z60">
         <v>0.096</v>
       </c>
     </row>
-    <row r="61" spans="1:24">
+    <row r="61" spans="1:26">
       <c r="A61" s="2">
-        <v>46248</v>
+        <v>46256</v>
       </c>
       <c r="B61">
         <v>1</v>
@@ -3287,7 +3647,7 @@
         <v>0</v>
       </c>
       <c r="E61">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="F61">
         <v>0</v>
@@ -3304,16 +3664,22 @@
       <c r="J61">
         <v>0</v>
       </c>
-      <c r="W61" t="s">
-        <v>83</v>
+      <c r="W61">
+        <v>0</v>
       </c>
       <c r="X61">
+        <v>0</v>
+      </c>
+      <c r="Y61" t="s">
+        <v>85</v>
+      </c>
+      <c r="Z61">
         <v>0.096</v>
       </c>
     </row>
-    <row r="62" spans="1:24">
+    <row r="62" spans="1:26">
       <c r="A62" s="2">
-        <v>46248</v>
+        <v>46256</v>
       </c>
       <c r="B62">
         <v>2</v>
@@ -3325,7 +3691,7 @@
         <v>0</v>
       </c>
       <c r="E62">
-        <v>0.06900000000000001</v>
+        <v>0.039</v>
       </c>
       <c r="F62">
         <v>0</v>
@@ -3340,18 +3706,24 @@
         <v>0</v>
       </c>
       <c r="J62">
-        <v>0</v>
-      </c>
-      <c r="W62" t="s">
-        <v>84</v>
+        <v>0.014</v>
+      </c>
+      <c r="W62">
+        <v>0</v>
       </c>
       <c r="X62">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="1:24">
+      <c r="Y62" t="s">
+        <v>86</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:26">
       <c r="A63" s="2">
-        <v>46248</v>
+        <v>46256</v>
       </c>
       <c r="B63">
         <v>3</v>
@@ -3363,7 +3735,7 @@
         <v>0</v>
       </c>
       <c r="E63">
-        <v>0.031</v>
+        <v>0.04</v>
       </c>
       <c r="F63">
         <v>0</v>
@@ -3378,18 +3750,24 @@
         <v>0</v>
       </c>
       <c r="J63">
-        <v>0.02</v>
-      </c>
-      <c r="W63" t="s">
-        <v>85</v>
+        <v>0.014</v>
+      </c>
+      <c r="W63">
+        <v>0</v>
       </c>
       <c r="X63">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="1:24">
+      <c r="Y63" t="s">
+        <v>87</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:26">
       <c r="A64" s="2">
-        <v>46248</v>
+        <v>46256</v>
       </c>
       <c r="B64">
         <v>4</v>
@@ -3401,7 +3779,7 @@
         <v>0</v>
       </c>
       <c r="E64">
-        <v>0.042</v>
+        <v>0.036</v>
       </c>
       <c r="F64">
         <v>0</v>
@@ -3416,18 +3794,24 @@
         <v>0</v>
       </c>
       <c r="J64">
-        <v>0.02</v>
-      </c>
-      <c r="W64" t="s">
-        <v>86</v>
+        <v>0.014</v>
+      </c>
+      <c r="W64">
+        <v>0</v>
       </c>
       <c r="X64">
+        <v>0</v>
+      </c>
+      <c r="Y64" t="s">
+        <v>88</v>
+      </c>
+      <c r="Z64">
         <v>0.014</v>
       </c>
     </row>
-    <row r="65" spans="1:24">
+    <row r="65" spans="1:26">
       <c r="A65" s="2">
-        <v>46248</v>
+        <v>46256</v>
       </c>
       <c r="B65">
         <v>5</v>
@@ -3439,7 +3823,7 @@
         <v>0</v>
       </c>
       <c r="E65">
-        <v>0</v>
+        <v>0.041</v>
       </c>
       <c r="F65">
         <v>0</v>
@@ -3454,18 +3838,24 @@
         <v>0</v>
       </c>
       <c r="J65">
-        <v>0.02</v>
-      </c>
-      <c r="W65" t="s">
-        <v>87</v>
+        <v>0.014</v>
+      </c>
+      <c r="W65">
+        <v>0</v>
       </c>
       <c r="X65">
+        <v>0</v>
+      </c>
+      <c r="Y65" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z65">
         <v>0.011</v>
       </c>
     </row>
-    <row r="66" spans="1:24">
+    <row r="66" spans="1:26">
       <c r="A66" s="2">
-        <v>46248</v>
+        <v>46256</v>
       </c>
       <c r="B66">
         <v>6</v>
@@ -3477,578 +3867,668 @@
         <v>0</v>
       </c>
       <c r="E66">
+        <v>0.01</v>
+      </c>
+      <c r="F66">
+        <v>0</v>
+      </c>
+      <c r="G66">
+        <v>0</v>
+      </c>
+      <c r="H66">
+        <v>0</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>0</v>
+      </c>
+      <c r="W66">
+        <v>0</v>
+      </c>
+      <c r="X66">
+        <v>0</v>
+      </c>
+      <c r="Y66" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z66">
         <v>0.011</v>
       </c>
-      <c r="F66">
-        <v>0</v>
-      </c>
-      <c r="G66">
-        <v>0</v>
-      </c>
-      <c r="H66">
-        <v>0</v>
-      </c>
-      <c r="I66">
-        <v>0</v>
-      </c>
-      <c r="J66">
-        <v>0.02</v>
-      </c>
-      <c r="W66" t="s">
-        <v>88</v>
-      </c>
-      <c r="X66">
-        <v>0.011</v>
-      </c>
-    </row>
-    <row r="67" spans="1:24">
+    </row>
+    <row r="67" spans="1:26">
       <c r="A67" s="2">
-        <v>46248</v>
+        <v>46256</v>
       </c>
       <c r="B67">
         <v>7</v>
       </c>
       <c r="C67">
-        <v>0.022</v>
+        <v>0</v>
       </c>
       <c r="D67">
-        <v>0.023</v>
+        <v>0</v>
       </c>
       <c r="E67">
+        <v>0.012</v>
+      </c>
+      <c r="F67">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="G67">
+        <v>0.031</v>
+      </c>
+      <c r="H67">
         <v>0.016</v>
       </c>
-      <c r="F67">
-        <v>0.156</v>
-      </c>
-      <c r="G67">
-        <v>0.063</v>
-      </c>
-      <c r="H67">
-        <v>0.034</v>
-      </c>
       <c r="I67">
-        <v>0.044</v>
+        <v>0.021</v>
       </c>
       <c r="J67">
-        <v>0.044</v>
-      </c>
-      <c r="W67" t="s">
-        <v>89</v>
+        <v>0.025</v>
+      </c>
+      <c r="W67">
+        <v>0.0157027027027027</v>
       </c>
       <c r="X67">
+        <v>0.041</v>
+      </c>
+      <c r="Y67" t="s">
+        <v>91</v>
+      </c>
+      <c r="Z67">
         <v>0.011</v>
       </c>
     </row>
-    <row r="68" spans="1:24">
+    <row r="68" spans="1:26">
       <c r="A68" s="2">
-        <v>46248</v>
+        <v>46256</v>
       </c>
       <c r="B68">
         <v>8</v>
       </c>
       <c r="C68">
-        <v>0.285</v>
+        <v>0.193</v>
       </c>
       <c r="D68">
-        <v>0.322</v>
+        <v>0.248</v>
       </c>
       <c r="E68">
-        <v>0.298</v>
+        <v>0.374</v>
       </c>
       <c r="F68">
-        <v>0.856</v>
+        <v>0.735</v>
       </c>
       <c r="G68">
-        <v>0.587</v>
+        <v>0.356</v>
       </c>
       <c r="H68">
-        <v>0.236</v>
+        <v>0.296</v>
       </c>
       <c r="I68">
-        <v>0.428</v>
+        <v>0.269</v>
       </c>
       <c r="J68">
-        <v>0.3</v>
-      </c>
-      <c r="W68" t="s">
-        <v>90</v>
+        <v>0.194</v>
+      </c>
+      <c r="W68">
+        <v>0.1648783783783784</v>
       </c>
       <c r="X68">
+        <v>0.5580000000000001</v>
+      </c>
+      <c r="Y68" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z68">
         <v>0.011</v>
       </c>
     </row>
-    <row r="69" spans="1:24">
+    <row r="69" spans="1:26">
       <c r="A69" s="2">
-        <v>46248</v>
+        <v>46256</v>
       </c>
       <c r="B69">
         <v>9</v>
       </c>
       <c r="C69">
-        <v>0.918</v>
+        <v>0.85</v>
       </c>
       <c r="D69">
-        <v>1.176</v>
+        <v>0.854</v>
       </c>
       <c r="E69">
-        <v>0.993</v>
+        <v>1.354</v>
       </c>
       <c r="F69">
-        <v>2.047</v>
+        <v>1.663</v>
       </c>
       <c r="G69">
-        <v>1.519</v>
+        <v>1.004</v>
       </c>
       <c r="H69">
-        <v>0.76</v>
+        <v>0.645</v>
       </c>
       <c r="I69">
-        <v>0.587</v>
+        <v>0.635</v>
       </c>
       <c r="J69">
-        <v>0.883</v>
-      </c>
-      <c r="W69" t="s">
-        <v>91</v>
+        <v>0.714</v>
+      </c>
+      <c r="W69">
+        <v>0.3730513513513513</v>
       </c>
       <c r="X69">
+        <v>2.019</v>
+      </c>
+      <c r="Y69" t="s">
+        <v>93</v>
+      </c>
+      <c r="Z69">
         <v>0.011</v>
       </c>
     </row>
-    <row r="70" spans="1:24">
+    <row r="70" spans="1:26">
       <c r="A70" s="2">
-        <v>46248</v>
+        <v>46256</v>
       </c>
       <c r="B70">
         <v>10</v>
       </c>
       <c r="C70">
-        <v>1.602</v>
+        <v>1.442</v>
       </c>
       <c r="D70">
-        <v>1.816</v>
+        <v>1.456</v>
       </c>
       <c r="E70">
-        <v>2.014</v>
+        <v>2.438</v>
       </c>
       <c r="F70">
-        <v>2.925</v>
+        <v>2.336</v>
       </c>
       <c r="G70">
-        <v>2.376</v>
+        <v>1.797</v>
       </c>
       <c r="H70">
-        <v>0.905</v>
+        <v>0.967</v>
       </c>
       <c r="I70">
-        <v>1.033</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="J70">
-        <v>1.096</v>
-      </c>
-      <c r="W70" t="s">
-        <v>92</v>
+        <v>0.93</v>
+      </c>
+      <c r="W70">
+        <v>0.5240216216216216</v>
       </c>
       <c r="X70">
+        <v>4.148</v>
+      </c>
+      <c r="Y70" t="s">
+        <v>94</v>
+      </c>
+      <c r="Z70">
         <v>0.011</v>
       </c>
     </row>
-    <row r="71" spans="1:24">
+    <row r="71" spans="1:26">
       <c r="A71" s="2">
-        <v>46248</v>
+        <v>46256</v>
       </c>
       <c r="B71">
         <v>11</v>
       </c>
       <c r="C71">
-        <v>2.025</v>
+        <v>1.749</v>
       </c>
       <c r="D71">
-        <v>2.291</v>
+        <v>1.872</v>
       </c>
       <c r="E71">
-        <v>3.055</v>
+        <v>3.464</v>
       </c>
       <c r="F71">
-        <v>3.79</v>
+        <v>2.943</v>
       </c>
       <c r="G71">
-        <v>3.011</v>
+        <v>2.55</v>
       </c>
       <c r="H71">
-        <v>0.837</v>
+        <v>1.443</v>
       </c>
       <c r="I71">
-        <v>1.387</v>
+        <v>1.325</v>
       </c>
       <c r="J71">
-        <v>1.45</v>
-      </c>
-      <c r="W71" t="s">
-        <v>93</v>
+        <v>1.228</v>
+      </c>
+      <c r="W71">
+        <v>0.6601864864864865</v>
       </c>
       <c r="X71">
+        <v>5.319</v>
+      </c>
+      <c r="Y71" t="s">
+        <v>95</v>
+      </c>
+      <c r="Z71">
         <v>0.011</v>
       </c>
     </row>
-    <row r="72" spans="1:24">
+    <row r="72" spans="1:26">
       <c r="A72" s="2">
-        <v>46248</v>
+        <v>46256</v>
       </c>
       <c r="B72">
         <v>12</v>
       </c>
       <c r="C72">
-        <v>2.372</v>
+        <v>2.135</v>
       </c>
       <c r="D72">
-        <v>2.783</v>
+        <v>2.423</v>
       </c>
       <c r="E72">
-        <v>3.669</v>
+        <v>3.916</v>
       </c>
       <c r="F72">
-        <v>4.182</v>
+        <v>3.535</v>
       </c>
       <c r="G72">
-        <v>3.514</v>
+        <v>3.038</v>
       </c>
       <c r="H72">
-        <v>1.16</v>
+        <v>1.496</v>
       </c>
       <c r="I72">
-        <v>1.396</v>
+        <v>1.445</v>
       </c>
       <c r="J72">
-        <v>1.571</v>
-      </c>
-      <c r="W72" t="s">
-        <v>94</v>
+        <v>1.551</v>
+      </c>
+      <c r="W72">
+        <v>0.7929864864864865</v>
       </c>
       <c r="X72">
+        <v>6.923999999999999</v>
+      </c>
+      <c r="Y72" t="s">
+        <v>96</v>
+      </c>
+      <c r="Z72">
         <v>0.038</v>
       </c>
     </row>
-    <row r="73" spans="1:24">
+    <row r="73" spans="1:26">
       <c r="A73" s="2">
-        <v>46248</v>
+        <v>46256</v>
       </c>
       <c r="B73">
         <v>13</v>
       </c>
       <c r="C73">
-        <v>2.694</v>
+        <v>2.289</v>
       </c>
       <c r="D73">
-        <v>3.071</v>
+        <v>2.54</v>
       </c>
       <c r="E73">
-        <v>3.808</v>
+        <v>3.92</v>
       </c>
       <c r="F73">
-        <v>4.246</v>
+        <v>3.853</v>
       </c>
       <c r="G73">
-        <v>3.604</v>
+        <v>3.351</v>
       </c>
       <c r="H73">
-        <v>1.428</v>
+        <v>1.375</v>
       </c>
       <c r="I73">
-        <v>1.396</v>
+        <v>1.445</v>
       </c>
       <c r="J73">
-        <v>1.637</v>
-      </c>
-      <c r="W73" t="s">
-        <v>95</v>
+        <v>1.518</v>
+      </c>
+      <c r="W73">
+        <v>0.8643216216216216</v>
       </c>
       <c r="X73">
+        <v>7.092</v>
+      </c>
+      <c r="Y73" t="s">
+        <v>97</v>
+      </c>
+      <c r="Z73">
         <v>0.056</v>
       </c>
     </row>
-    <row r="74" spans="1:24">
+    <row r="74" spans="1:26">
       <c r="A74" s="2">
-        <v>46248</v>
+        <v>46256</v>
       </c>
       <c r="B74">
         <v>14</v>
       </c>
       <c r="C74">
-        <v>2.6</v>
+        <v>2.287</v>
       </c>
       <c r="D74">
-        <v>3.215</v>
+        <v>2.499</v>
       </c>
       <c r="E74">
-        <v>3.576</v>
+        <v>3.735</v>
       </c>
       <c r="F74">
-        <v>4.229</v>
+        <v>4.067</v>
       </c>
       <c r="G74">
-        <v>3.583</v>
+        <v>3.546</v>
       </c>
       <c r="H74">
-        <v>0.911</v>
+        <v>0.841</v>
       </c>
       <c r="I74">
-        <v>1.452</v>
+        <v>1.502</v>
       </c>
       <c r="J74">
-        <v>1.567</v>
-      </c>
-      <c r="W74" t="s">
-        <v>96</v>
+        <v>1.456</v>
+      </c>
+      <c r="W74">
+        <v>0.9123270270270269</v>
       </c>
       <c r="X74">
+        <v>7.092</v>
+      </c>
+      <c r="Y74" t="s">
+        <v>98</v>
+      </c>
+      <c r="Z74">
         <v>0.29</v>
       </c>
     </row>
-    <row r="75" spans="1:24">
+    <row r="75" spans="1:26">
       <c r="A75" s="2">
-        <v>46248</v>
+        <v>46256</v>
       </c>
       <c r="B75">
         <v>15</v>
       </c>
       <c r="C75">
-        <v>2.622</v>
+        <v>2.051</v>
       </c>
       <c r="D75">
-        <v>3.193</v>
+        <v>2.322</v>
       </c>
       <c r="E75">
-        <v>3.667</v>
+        <v>3.799</v>
       </c>
       <c r="F75">
-        <v>3.65</v>
+        <v>3.926</v>
       </c>
       <c r="G75">
-        <v>3.222</v>
+        <v>3.39</v>
       </c>
       <c r="H75">
-        <v>0.949</v>
+        <v>0.921</v>
       </c>
       <c r="I75">
-        <v>1.506</v>
+        <v>1.502</v>
       </c>
       <c r="J75">
-        <v>1.419</v>
-      </c>
-      <c r="W75" t="s">
-        <v>97</v>
+        <v>1.377</v>
+      </c>
+      <c r="W75">
+        <v>0.8806972972972973</v>
       </c>
       <c r="X75">
+        <v>7.031</v>
+      </c>
+      <c r="Y75" t="s">
+        <v>99</v>
+      </c>
+      <c r="Z75">
         <v>0.96</v>
       </c>
     </row>
-    <row r="76" spans="1:24">
+    <row r="76" spans="1:26">
       <c r="A76" s="2">
-        <v>46248</v>
+        <v>46256</v>
       </c>
       <c r="B76">
         <v>16</v>
       </c>
       <c r="C76">
-        <v>2.449</v>
+        <v>1.563</v>
       </c>
       <c r="D76">
-        <v>2.975</v>
+        <v>1.827</v>
       </c>
       <c r="E76">
-        <v>3.796</v>
+        <v>3.462</v>
       </c>
       <c r="F76">
-        <v>3.01</v>
+        <v>3.337</v>
       </c>
       <c r="G76">
-        <v>2.787</v>
+        <v>3.022</v>
       </c>
       <c r="H76">
-        <v>1.003</v>
+        <v>0.918</v>
       </c>
       <c r="I76">
-        <v>1.461</v>
+        <v>1.502</v>
       </c>
       <c r="J76">
-        <v>1.239</v>
-      </c>
-      <c r="W76" t="s">
-        <v>98</v>
+        <v>1.159</v>
+      </c>
+      <c r="W76">
+        <v>0.7485702702702702</v>
       </c>
       <c r="X76">
+        <v>6.438</v>
+      </c>
+      <c r="Y76" t="s">
+        <v>100</v>
+      </c>
+      <c r="Z76">
         <v>1.436</v>
       </c>
     </row>
-    <row r="77" spans="1:24">
+    <row r="77" spans="1:26">
       <c r="A77" s="2">
-        <v>46248</v>
+        <v>46256</v>
       </c>
       <c r="B77">
         <v>17</v>
       </c>
       <c r="C77">
-        <v>2.081</v>
+        <v>1.412</v>
       </c>
       <c r="D77">
-        <v>2.65</v>
+        <v>1.243</v>
       </c>
       <c r="E77">
-        <v>3.391</v>
+        <v>2.961</v>
       </c>
       <c r="F77">
-        <v>2.004</v>
+        <v>2.309</v>
       </c>
       <c r="G77">
-        <v>2.065</v>
+        <v>2.452</v>
       </c>
       <c r="H77">
-        <v>1.032</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="I77">
+        <v>1.341</v>
+      </c>
+      <c r="J77">
         <v>0.767</v>
       </c>
-      <c r="J77">
-        <v>0.9389999999999999</v>
-      </c>
-      <c r="W77" t="s">
-        <v>99</v>
+      <c r="W77">
+        <v>0.5179648648648648</v>
       </c>
       <c r="X77">
+        <v>5.021</v>
+      </c>
+      <c r="Y77" t="s">
+        <v>101</v>
+      </c>
+      <c r="Z77">
         <v>1.977</v>
       </c>
     </row>
-    <row r="78" spans="1:24">
+    <row r="78" spans="1:26">
       <c r="A78" s="2">
-        <v>46248</v>
+        <v>46256</v>
       </c>
       <c r="B78">
         <v>18</v>
       </c>
       <c r="C78">
-        <v>1.445</v>
+        <v>0.977</v>
       </c>
       <c r="D78">
-        <v>1.877</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="E78">
-        <v>2.415</v>
+        <v>1.855</v>
       </c>
       <c r="F78">
-        <v>1.34</v>
+        <v>1.412</v>
       </c>
       <c r="G78">
-        <v>1.552</v>
+        <v>1.551</v>
       </c>
       <c r="H78">
-        <v>0.923</v>
+        <v>0.825</v>
       </c>
       <c r="I78">
-        <v>0.551</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="J78">
-        <v>0.507</v>
-      </c>
-      <c r="W78" t="s">
-        <v>100</v>
+        <v>0.318</v>
+      </c>
+      <c r="W78">
+        <v>0.3167459459459459</v>
       </c>
       <c r="X78">
+        <v>3.463</v>
+      </c>
+      <c r="Y78" t="s">
+        <v>102</v>
+      </c>
+      <c r="Z78">
         <v>1.827</v>
       </c>
     </row>
-    <row r="79" spans="1:24">
+    <row r="79" spans="1:26">
       <c r="A79" s="2">
-        <v>46248</v>
+        <v>46256</v>
       </c>
       <c r="B79">
         <v>19</v>
       </c>
       <c r="C79">
-        <v>0.74</v>
+        <v>0.428</v>
       </c>
       <c r="D79">
-        <v>0.875</v>
+        <v>0.486</v>
       </c>
       <c r="E79">
-        <v>1.347</v>
+        <v>0.995</v>
       </c>
       <c r="F79">
-        <v>0.468</v>
+        <v>0.467</v>
       </c>
       <c r="G79">
-        <v>0.65</v>
+        <v>0.799</v>
       </c>
       <c r="H79">
-        <v>0.537</v>
+        <v>0.518</v>
       </c>
       <c r="I79">
-        <v>0.52</v>
+        <v>0.57</v>
       </c>
       <c r="J79">
-        <v>0.325</v>
-      </c>
-      <c r="W79" t="s">
-        <v>101</v>
+        <v>0.21</v>
+      </c>
+      <c r="W79">
+        <v>0.1047594594594595</v>
       </c>
       <c r="X79">
+        <v>1.669</v>
+      </c>
+      <c r="Y79" t="s">
+        <v>103</v>
+      </c>
+      <c r="Z79">
         <v>1.35</v>
       </c>
     </row>
-    <row r="80" spans="1:24">
+    <row r="80" spans="1:26">
       <c r="A80" s="2">
-        <v>46248</v>
+        <v>46256</v>
       </c>
       <c r="B80">
         <v>20</v>
       </c>
       <c r="C80">
-        <v>0.172</v>
+        <v>0.103</v>
       </c>
       <c r="D80">
-        <v>0.272</v>
+        <v>0.12</v>
       </c>
       <c r="E80">
-        <v>0.517</v>
+        <v>0.282</v>
       </c>
       <c r="F80">
-        <v>0.139</v>
+        <v>0.134</v>
       </c>
       <c r="G80">
-        <v>0.192</v>
+        <v>0.179</v>
       </c>
       <c r="H80">
-        <v>0.213</v>
+        <v>0.145</v>
       </c>
       <c r="I80">
-        <v>0.116</v>
+        <v>0.112</v>
       </c>
       <c r="J80">
-        <v>0.107</v>
-      </c>
-      <c r="W80" t="s">
-        <v>102</v>
+        <v>0</v>
+      </c>
+      <c r="W80">
+        <v>0.03005945945945946</v>
       </c>
       <c r="X80">
+        <v>0.442</v>
+      </c>
+      <c r="Y80" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z80">
         <v>0.888</v>
       </c>
     </row>
-    <row r="81" spans="1:24">
+    <row r="81" spans="1:26">
       <c r="A81" s="2">
-        <v>46248</v>
+        <v>46256</v>
       </c>
       <c r="B81">
         <v>21</v>
       </c>
       <c r="C81">
+        <v>0</v>
+      </c>
+      <c r="D81">
+        <v>0</v>
+      </c>
+      <c r="E81">
         <v>0.02</v>
       </c>
-      <c r="D81">
-        <v>0.022</v>
-      </c>
-      <c r="E81">
-        <v>0.056</v>
-      </c>
       <c r="F81">
         <v>0</v>
       </c>
@@ -4064,16 +4544,22 @@
       <c r="J81">
         <v>0</v>
       </c>
-      <c r="W81" t="s">
-        <v>103</v>
+      <c r="W81">
+        <v>0</v>
       </c>
       <c r="X81">
+        <v>0.033</v>
+      </c>
+      <c r="Y81" t="s">
+        <v>105</v>
+      </c>
+      <c r="Z81">
         <v>0.297</v>
       </c>
     </row>
-    <row r="82" spans="1:24">
+    <row r="82" spans="1:26">
       <c r="A82" s="2">
-        <v>46248</v>
+        <v>46256</v>
       </c>
       <c r="B82">
         <v>22</v>
@@ -4085,7 +4571,7 @@
         <v>0</v>
       </c>
       <c r="E82">
-        <v>0.027</v>
+        <v>0</v>
       </c>
       <c r="F82">
         <v>0</v>
@@ -4100,18 +4586,24 @@
         <v>0</v>
       </c>
       <c r="J82">
-        <v>0</v>
-      </c>
-      <c r="W82" t="s">
-        <v>104</v>
+        <v>0.019</v>
+      </c>
+      <c r="W82">
+        <v>0</v>
       </c>
       <c r="X82">
+        <v>0</v>
+      </c>
+      <c r="Y82" t="s">
+        <v>106</v>
+      </c>
+      <c r="Z82">
         <v>0.132</v>
       </c>
     </row>
-    <row r="83" spans="1:24">
+    <row r="83" spans="1:26">
       <c r="A83" s="2">
-        <v>46248</v>
+        <v>46256</v>
       </c>
       <c r="B83">
         <v>23</v>
@@ -4123,7 +4615,7 @@
         <v>0</v>
       </c>
       <c r="E83">
-        <v>0.018</v>
+        <v>0</v>
       </c>
       <c r="F83">
         <v>0</v>
@@ -4138,18 +4630,24 @@
         <v>0</v>
       </c>
       <c r="J83">
-        <v>0</v>
-      </c>
-      <c r="W83" t="s">
-        <v>105</v>
+        <v>0.019</v>
+      </c>
+      <c r="W83">
+        <v>0</v>
       </c>
       <c r="X83">
+        <v>0</v>
+      </c>
+      <c r="Y83" t="s">
+        <v>107</v>
+      </c>
+      <c r="Z83">
         <v>0.038</v>
       </c>
     </row>
-    <row r="84" spans="1:24">
+    <row r="84" spans="1:26">
       <c r="A84" s="2">
-        <v>46248</v>
+        <v>46256</v>
       </c>
       <c r="B84">
         <v>24</v>
@@ -4161,7 +4659,7 @@
         <v>0</v>
       </c>
       <c r="E84">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="F84">
         <v>0</v>
@@ -4176,18 +4674,24 @@
         <v>0</v>
       </c>
       <c r="J84">
-        <v>0</v>
-      </c>
-      <c r="W84" t="s">
-        <v>106</v>
+        <v>0.019</v>
+      </c>
+      <c r="W84">
+        <v>0</v>
       </c>
       <c r="X84">
+        <v>0</v>
+      </c>
+      <c r="Y84" t="s">
+        <v>108</v>
+      </c>
+      <c r="Z84">
         <v>0.094</v>
       </c>
     </row>
-    <row r="85" spans="1:24">
+    <row r="85" spans="1:26">
       <c r="A85" s="2">
-        <v>46249</v>
+        <v>46257</v>
       </c>
       <c r="B85">
         <v>1</v>
@@ -4199,7 +4703,7 @@
         <v>0</v>
       </c>
       <c r="E85">
-        <v>0.059</v>
+        <v>0</v>
       </c>
       <c r="F85">
         <v>0</v>
@@ -4214,18 +4718,24 @@
         <v>0</v>
       </c>
       <c r="J85">
-        <v>0.019</v>
-      </c>
-      <c r="W85" t="s">
-        <v>107</v>
+        <v>0.02</v>
+      </c>
+      <c r="W85">
+        <v>0</v>
       </c>
       <c r="X85">
+        <v>0</v>
+      </c>
+      <c r="Y85" t="s">
+        <v>109</v>
+      </c>
+      <c r="Z85">
         <v>0.094</v>
       </c>
     </row>
-    <row r="86" spans="1:24">
+    <row r="86" spans="1:26">
       <c r="A86" s="2">
-        <v>46249</v>
+        <v>46257</v>
       </c>
       <c r="B86">
         <v>2</v>
@@ -4237,7 +4747,7 @@
         <v>0</v>
       </c>
       <c r="E86">
-        <v>0.058</v>
+        <v>0.012</v>
       </c>
       <c r="F86">
         <v>0</v>
@@ -4252,18 +4762,24 @@
         <v>0</v>
       </c>
       <c r="J86">
-        <v>0</v>
-      </c>
-      <c r="W86" t="s">
-        <v>108</v>
+        <v>0.02</v>
+      </c>
+      <c r="W86">
+        <v>0</v>
       </c>
       <c r="X86">
+        <v>0</v>
+      </c>
+      <c r="Y86" t="s">
+        <v>110</v>
+      </c>
+      <c r="Z86">
         <v>0.011</v>
       </c>
     </row>
-    <row r="87" spans="1:24">
+    <row r="87" spans="1:26">
       <c r="A87" s="2">
-        <v>46249</v>
+        <v>46257</v>
       </c>
       <c r="B87">
         <v>3</v>
@@ -4275,7 +4791,7 @@
         <v>0</v>
       </c>
       <c r="E87">
-        <v>0.053</v>
+        <v>0</v>
       </c>
       <c r="F87">
         <v>0</v>
@@ -4290,18 +4806,24 @@
         <v>0</v>
       </c>
       <c r="J87">
-        <v>0</v>
-      </c>
-      <c r="W87" t="s">
-        <v>109</v>
+        <v>0.02</v>
+      </c>
+      <c r="W87">
+        <v>0</v>
       </c>
       <c r="X87">
+        <v>0</v>
+      </c>
+      <c r="Y87" t="s">
+        <v>111</v>
+      </c>
+      <c r="Z87">
         <v>0.011</v>
       </c>
     </row>
-    <row r="88" spans="1:24">
+    <row r="88" spans="1:26">
       <c r="A88" s="2">
-        <v>46249</v>
+        <v>46257</v>
       </c>
       <c r="B88">
         <v>4</v>
@@ -4313,7 +4835,7 @@
         <v>0</v>
       </c>
       <c r="E88">
-        <v>0.045</v>
+        <v>0.011</v>
       </c>
       <c r="F88">
         <v>0</v>
@@ -4328,18 +4850,24 @@
         <v>0</v>
       </c>
       <c r="J88">
-        <v>0</v>
-      </c>
-      <c r="W88" t="s">
-        <v>110</v>
+        <v>0.02</v>
+      </c>
+      <c r="W88">
+        <v>0</v>
       </c>
       <c r="X88">
+        <v>0</v>
+      </c>
+      <c r="Y88" t="s">
+        <v>112</v>
+      </c>
+      <c r="Z88">
         <v>0.011</v>
       </c>
     </row>
-    <row r="89" spans="1:24">
+    <row r="89" spans="1:26">
       <c r="A89" s="2">
-        <v>46249</v>
+        <v>46257</v>
       </c>
       <c r="B89">
         <v>5</v>
@@ -4351,7 +4879,7 @@
         <v>0</v>
       </c>
       <c r="E89">
-        <v>0.014</v>
+        <v>0</v>
       </c>
       <c r="F89">
         <v>0</v>
@@ -4366,18 +4894,24 @@
         <v>0</v>
       </c>
       <c r="J89">
-        <v>0</v>
-      </c>
-      <c r="W89" t="s">
-        <v>111</v>
+        <v>0.026</v>
+      </c>
+      <c r="W89">
+        <v>0</v>
       </c>
       <c r="X89">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="1:24">
+      <c r="Y89" t="s">
+        <v>113</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:26">
       <c r="A90" s="2">
-        <v>46249</v>
+        <v>46257</v>
       </c>
       <c r="B90">
         <v>6</v>
@@ -4404,562 +4938,652 @@
         <v>0</v>
       </c>
       <c r="J90">
-        <v>0.021</v>
-      </c>
-      <c r="W90" t="s">
-        <v>112</v>
+        <v>0.014</v>
+      </c>
+      <c r="W90">
+        <v>0</v>
       </c>
       <c r="X90">
         <v>0</v>
       </c>
-    </row>
-    <row r="91" spans="1:24">
+      <c r="Y90" t="s">
+        <v>114</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:26">
       <c r="A91" s="2">
-        <v>46249</v>
+        <v>46257</v>
       </c>
       <c r="B91">
         <v>7</v>
       </c>
       <c r="C91">
-        <v>0.024</v>
+        <v>0</v>
       </c>
       <c r="D91">
-        <v>0.023</v>
+        <v>0</v>
       </c>
       <c r="E91">
-        <v>0.018</v>
+        <v>0</v>
       </c>
       <c r="F91">
-        <v>0.155</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="G91">
-        <v>0.063</v>
+        <v>0.03</v>
       </c>
       <c r="H91">
-        <v>0.044</v>
+        <v>0.012</v>
       </c>
       <c r="I91">
-        <v>0.044</v>
+        <v>0.015</v>
       </c>
       <c r="J91">
-        <v>0</v>
-      </c>
-      <c r="W91" t="s">
-        <v>113</v>
+        <v>0.03</v>
+      </c>
+      <c r="W91">
+        <v>0.01547837837837838</v>
       </c>
       <c r="X91">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="1:24">
+        <v>0.038</v>
+      </c>
+      <c r="Y91" t="s">
+        <v>115</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:26">
       <c r="A92" s="2">
-        <v>46249</v>
+        <v>46257</v>
       </c>
       <c r="B92">
         <v>8</v>
       </c>
       <c r="C92">
-        <v>0.276</v>
+        <v>0.166</v>
       </c>
       <c r="D92">
-        <v>0.422</v>
+        <v>0.249</v>
       </c>
       <c r="E92">
-        <v>0.492</v>
+        <v>0.304</v>
       </c>
       <c r="F92">
-        <v>0.971</v>
+        <v>0.736</v>
       </c>
       <c r="G92">
-        <v>0.596</v>
+        <v>0.395</v>
       </c>
       <c r="H92">
-        <v>0.397</v>
+        <v>0.236</v>
       </c>
       <c r="I92">
-        <v>0.472</v>
+        <v>0.269</v>
       </c>
       <c r="J92">
-        <v>0.312</v>
-      </c>
-      <c r="W92" t="s">
-        <v>114</v>
+        <v>0.195</v>
+      </c>
+      <c r="W92">
+        <v>0.1651027027027027</v>
       </c>
       <c r="X92">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="1:24">
+        <v>0.582</v>
+      </c>
+      <c r="Y92" t="s">
+        <v>116</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:26">
       <c r="A93" s="2">
-        <v>46249</v>
+        <v>46257</v>
       </c>
       <c r="B93">
         <v>9</v>
       </c>
       <c r="C93">
-        <v>1.006</v>
+        <v>0.846</v>
       </c>
       <c r="D93">
-        <v>1.119</v>
+        <v>0.891</v>
       </c>
       <c r="E93">
-        <v>1.525</v>
+        <v>1.278</v>
       </c>
       <c r="F93">
-        <v>2.129</v>
+        <v>1.738</v>
       </c>
       <c r="G93">
-        <v>1.476</v>
+        <v>1.269</v>
       </c>
       <c r="H93">
-        <v>0.915</v>
+        <v>0.602</v>
       </c>
       <c r="I93">
-        <v>0.928</v>
+        <v>0.659</v>
       </c>
       <c r="J93">
-        <v>0.863</v>
-      </c>
-      <c r="W93" t="s">
-        <v>115</v>
+        <v>0.646</v>
+      </c>
+      <c r="W93">
+        <v>0.3898756756756757</v>
       </c>
       <c r="X93">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="1:24">
+        <v>1.834</v>
+      </c>
+      <c r="Y93" t="s">
+        <v>117</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:26">
       <c r="A94" s="2">
-        <v>46249</v>
+        <v>46257</v>
       </c>
       <c r="B94">
         <v>10</v>
       </c>
       <c r="C94">
-        <v>1.668</v>
+        <v>1.522</v>
       </c>
       <c r="D94">
-        <v>2.076</v>
+        <v>1.583</v>
       </c>
       <c r="E94">
-        <v>2.684</v>
+        <v>2.239</v>
       </c>
       <c r="F94">
-        <v>3.064</v>
+        <v>2.632</v>
       </c>
       <c r="G94">
-        <v>2.397</v>
+        <v>2.105</v>
       </c>
       <c r="H94">
-        <v>0.9409999999999999</v>
+        <v>1.013</v>
       </c>
       <c r="I94">
-        <v>1.163</v>
+        <v>1.021</v>
       </c>
       <c r="J94">
-        <v>1.208</v>
-      </c>
-      <c r="W94" t="s">
-        <v>116</v>
+        <v>1.018</v>
+      </c>
+      <c r="W94">
+        <v>0.5904216216216216</v>
       </c>
       <c r="X94">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="1:24">
+        <v>3.773</v>
+      </c>
+      <c r="Y94" t="s">
+        <v>118</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:26">
       <c r="A95" s="2">
-        <v>46249</v>
+        <v>46257</v>
       </c>
       <c r="B95">
         <v>11</v>
       </c>
       <c r="C95">
-        <v>2.317</v>
+        <v>2.189</v>
       </c>
       <c r="D95">
-        <v>2.791</v>
+        <v>2.288</v>
       </c>
       <c r="E95">
-        <v>3.76</v>
+        <v>3.333</v>
       </c>
       <c r="F95">
-        <v>3.85</v>
+        <v>3.331</v>
       </c>
       <c r="G95">
-        <v>3.042</v>
+        <v>2.83</v>
       </c>
       <c r="H95">
-        <v>0.793</v>
+        <v>1.303</v>
       </c>
       <c r="I95">
-        <v>1.437</v>
+        <v>1.453</v>
       </c>
       <c r="J95">
-        <v>1.473</v>
-      </c>
-      <c r="W95" t="s">
-        <v>117</v>
+        <v>1.287</v>
+      </c>
+      <c r="W95">
+        <v>0.7472243243243243</v>
       </c>
       <c r="X95">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96" spans="1:24">
+        <v>4.758</v>
+      </c>
+      <c r="Y95" t="s">
+        <v>119</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:26">
       <c r="A96" s="2">
-        <v>46249</v>
+        <v>46257</v>
       </c>
       <c r="B96">
         <v>12</v>
       </c>
       <c r="C96">
-        <v>2.652</v>
+        <v>2.503</v>
       </c>
       <c r="D96">
-        <v>3.042</v>
+        <v>2.507</v>
       </c>
       <c r="E96">
-        <v>3.995</v>
+        <v>3.738</v>
       </c>
       <c r="F96">
-        <v>4.164</v>
+        <v>3.937</v>
       </c>
       <c r="G96">
-        <v>3.476</v>
+        <v>3.368</v>
       </c>
       <c r="H96">
-        <v>0.783</v>
+        <v>1.322</v>
       </c>
       <c r="I96">
-        <v>1.396</v>
+        <v>1.445</v>
       </c>
       <c r="J96">
-        <v>1.621</v>
-      </c>
-      <c r="W96" t="s">
-        <v>118</v>
+        <v>1.473</v>
+      </c>
+      <c r="W96">
+        <v>0.8831648648648648</v>
       </c>
       <c r="X96">
+        <v>5.353</v>
+      </c>
+      <c r="Y96" t="s">
+        <v>120</v>
+      </c>
+      <c r="Z96">
         <v>0.192</v>
       </c>
     </row>
-    <row r="97" spans="1:24">
+    <row r="97" spans="1:26">
       <c r="A97" s="2">
-        <v>46249</v>
+        <v>46257</v>
       </c>
       <c r="B97">
         <v>13</v>
       </c>
       <c r="C97">
-        <v>2.828</v>
+        <v>2.662</v>
       </c>
       <c r="D97">
-        <v>3.171</v>
+        <v>2.77</v>
       </c>
       <c r="E97">
-        <v>3.889</v>
+        <v>3.682</v>
       </c>
       <c r="F97">
-        <v>4.251</v>
+        <v>4.103</v>
       </c>
       <c r="G97">
-        <v>3.641</v>
+        <v>3.459</v>
       </c>
       <c r="H97">
-        <v>1.441</v>
+        <v>1.502</v>
       </c>
       <c r="I97">
-        <v>1.396</v>
+        <v>1.445</v>
       </c>
       <c r="J97">
-        <v>1.586</v>
-      </c>
-      <c r="W97" t="s">
-        <v>119</v>
+        <v>1.507</v>
+      </c>
+      <c r="W97">
+        <v>0.9204027027027026</v>
       </c>
       <c r="X97">
+        <v>6.394</v>
+      </c>
+      <c r="Y97" t="s">
+        <v>121</v>
+      </c>
+      <c r="Z97">
         <v>0.21</v>
       </c>
     </row>
-    <row r="98" spans="1:24">
+    <row r="98" spans="1:26">
       <c r="A98" s="2">
-        <v>46249</v>
+        <v>46257</v>
       </c>
       <c r="B98">
         <v>14</v>
       </c>
       <c r="C98">
-        <v>3.109</v>
+        <v>2.908</v>
       </c>
       <c r="D98">
-        <v>3.106</v>
+        <v>2.609</v>
       </c>
       <c r="E98">
-        <v>3.821</v>
+        <v>3.693</v>
       </c>
       <c r="F98">
-        <v>4.251</v>
+        <v>4.074</v>
       </c>
       <c r="G98">
-        <v>3.621</v>
+        <v>3.453</v>
       </c>
       <c r="H98">
-        <v>0.911</v>
+        <v>0.91</v>
       </c>
       <c r="I98">
-        <v>1.363</v>
+        <v>1.502</v>
       </c>
       <c r="J98">
-        <v>1.621</v>
-      </c>
-      <c r="W98" t="s">
-        <v>120</v>
+        <v>1.443</v>
+      </c>
+      <c r="W98">
+        <v>0.9138972972972972</v>
       </c>
       <c r="X98">
+        <v>6.678</v>
+      </c>
+      <c r="Y98" t="s">
+        <v>122</v>
+      </c>
+      <c r="Z98">
         <v>0.501</v>
       </c>
     </row>
-    <row r="99" spans="1:24">
+    <row r="99" spans="1:26">
       <c r="A99" s="2">
-        <v>46249</v>
+        <v>46257</v>
       </c>
       <c r="B99">
         <v>15</v>
       </c>
       <c r="C99">
-        <v>3.026</v>
+        <v>2.479</v>
       </c>
       <c r="D99">
-        <v>3.124</v>
+        <v>2.602</v>
       </c>
       <c r="E99">
-        <v>3.788</v>
+        <v>3.552</v>
       </c>
       <c r="F99">
-        <v>4.044</v>
+        <v>3.851</v>
       </c>
       <c r="G99">
-        <v>3.531</v>
+        <v>3.392</v>
       </c>
       <c r="H99">
-        <v>0.895</v>
+        <v>0.771</v>
       </c>
       <c r="I99">
-        <v>1.417</v>
+        <v>1.502</v>
       </c>
       <c r="J99">
-        <v>1.501</v>
-      </c>
-      <c r="W99" t="s">
-        <v>121</v>
+        <v>1.244</v>
+      </c>
+      <c r="W99">
+        <v>0.8638729729729729</v>
       </c>
       <c r="X99">
+        <v>6.31</v>
+      </c>
+      <c r="Y99" t="s">
+        <v>123</v>
+      </c>
+      <c r="Z99">
         <v>0.678</v>
       </c>
     </row>
-    <row r="100" spans="1:24">
+    <row r="100" spans="1:26">
       <c r="A100" s="2">
-        <v>46249</v>
+        <v>46257</v>
       </c>
       <c r="B100">
         <v>16</v>
       </c>
       <c r="C100">
-        <v>2.643</v>
+        <v>2.179</v>
       </c>
       <c r="D100">
-        <v>2.998</v>
+        <v>2.426</v>
       </c>
       <c r="E100">
-        <v>3.906</v>
+        <v>3.374</v>
       </c>
       <c r="F100">
-        <v>3.175</v>
+        <v>3.181</v>
       </c>
       <c r="G100">
-        <v>2.88</v>
+        <v>2.994</v>
       </c>
       <c r="H100">
-        <v>1.013</v>
+        <v>0.806</v>
       </c>
       <c r="I100">
-        <v>1.334</v>
+        <v>1.169</v>
       </c>
       <c r="J100">
-        <v>1.318</v>
-      </c>
-      <c r="W100" t="s">
-        <v>122</v>
+        <v>1.055</v>
+      </c>
+      <c r="W100">
+        <v>0.7135756756756756</v>
       </c>
       <c r="X100">
+        <v>5.085</v>
+      </c>
+      <c r="Y100" t="s">
+        <v>124</v>
+      </c>
+      <c r="Z100">
         <v>1.135</v>
       </c>
     </row>
-    <row r="101" spans="1:24">
+    <row r="101" spans="1:26">
       <c r="A101" s="2">
-        <v>46249</v>
+        <v>46257</v>
       </c>
       <c r="B101">
         <v>17</v>
       </c>
       <c r="C101">
-        <v>2.085</v>
+        <v>1.928</v>
       </c>
       <c r="D101">
-        <v>2.67</v>
+        <v>1.979</v>
       </c>
       <c r="E101">
-        <v>3.552</v>
+        <v>2.747</v>
       </c>
       <c r="F101">
-        <v>2.048</v>
+        <v>2.248</v>
       </c>
       <c r="G101">
-        <v>2.104</v>
+        <v>2.344</v>
       </c>
       <c r="H101">
-        <v>1.021</v>
+        <v>0.955</v>
       </c>
       <c r="I101">
-        <v>1.314</v>
+        <v>0.957</v>
       </c>
       <c r="J101">
-        <v>1.07</v>
-      </c>
-      <c r="W101" t="s">
-        <v>123</v>
+        <v>0.779</v>
+      </c>
+      <c r="W101">
+        <v>0.5042810810810811</v>
       </c>
       <c r="X101">
+        <v>3.475</v>
+      </c>
+      <c r="Y101" t="s">
+        <v>125</v>
+      </c>
+      <c r="Z101">
         <v>1.387</v>
       </c>
     </row>
-    <row r="102" spans="1:24">
+    <row r="102" spans="1:26">
       <c r="A102" s="2">
-        <v>46249</v>
+        <v>46257</v>
       </c>
       <c r="B102">
         <v>18</v>
       </c>
       <c r="C102">
-        <v>1.488</v>
+        <v>1.047</v>
       </c>
       <c r="D102">
-        <v>1.86</v>
+        <v>1.135</v>
       </c>
       <c r="E102">
-        <v>2.56</v>
+        <v>1.787</v>
       </c>
       <c r="F102">
-        <v>1.43</v>
+        <v>1.222</v>
       </c>
       <c r="G102">
-        <v>1.529</v>
+        <v>1.482</v>
       </c>
       <c r="H102">
-        <v>0.928</v>
+        <v>0.664</v>
       </c>
       <c r="I102">
-        <v>0.924</v>
+        <v>0.633</v>
       </c>
       <c r="J102">
-        <v>0.776</v>
-      </c>
-      <c r="W102" t="s">
-        <v>124</v>
+        <v>0.327</v>
+      </c>
+      <c r="W102">
+        <v>0.2741243243243243</v>
       </c>
       <c r="X102">
+        <v>2.496</v>
+      </c>
+      <c r="Y102" t="s">
+        <v>126</v>
+      </c>
+      <c r="Z102">
         <v>1.534</v>
       </c>
     </row>
-    <row r="103" spans="1:24">
+    <row r="103" spans="1:26">
       <c r="A103" s="2">
-        <v>46249</v>
+        <v>46257</v>
       </c>
       <c r="B103">
         <v>19</v>
       </c>
       <c r="C103">
-        <v>0.6929999999999999</v>
+        <v>0.553</v>
       </c>
       <c r="D103">
-        <v>0.86</v>
+        <v>0.66</v>
       </c>
       <c r="E103">
-        <v>1.25</v>
+        <v>0.819</v>
       </c>
       <c r="F103">
-        <v>0.455</v>
+        <v>0.391</v>
       </c>
       <c r="G103">
-        <v>0.785</v>
+        <v>0.63</v>
       </c>
       <c r="H103">
-        <v>0.5679999999999999</v>
+        <v>0.458</v>
       </c>
       <c r="I103">
-        <v>0.547</v>
+        <v>0.272</v>
       </c>
       <c r="J103">
-        <v>0.463</v>
-      </c>
-      <c r="W103" t="s">
-        <v>125</v>
+        <v>0.205</v>
+      </c>
+      <c r="W103">
+        <v>0.08771081081081081</v>
       </c>
       <c r="X103">
+        <v>1.181</v>
+      </c>
+      <c r="Y103" t="s">
+        <v>127</v>
+      </c>
+      <c r="Z103">
         <v>1.228</v>
       </c>
     </row>
-    <row r="104" spans="1:24">
+    <row r="104" spans="1:26">
       <c r="A104" s="2">
-        <v>46249</v>
+        <v>46257</v>
       </c>
       <c r="B104">
         <v>20</v>
       </c>
       <c r="C104">
-        <v>0.149</v>
+        <v>0.098</v>
       </c>
       <c r="D104">
-        <v>0.233</v>
+        <v>0.128</v>
       </c>
       <c r="E104">
-        <v>0.457</v>
+        <v>0.302</v>
       </c>
       <c r="F104">
-        <v>0.139</v>
+        <v>0.108</v>
       </c>
       <c r="G104">
-        <v>0.187</v>
+        <v>0.123</v>
       </c>
       <c r="H104">
-        <v>0.217</v>
+        <v>0.106</v>
       </c>
       <c r="I104">
-        <v>0.15</v>
+        <v>0.061</v>
       </c>
       <c r="J104">
-        <v>0.111</v>
-      </c>
-      <c r="W104" t="s">
-        <v>126</v>
+        <v>0.036</v>
+      </c>
+      <c r="W104">
+        <v>0.02422702702702702</v>
       </c>
       <c r="X104">
+        <v>0.286</v>
+      </c>
+      <c r="Y104" t="s">
+        <v>128</v>
+      </c>
+      <c r="Z104">
         <v>0.991</v>
       </c>
     </row>
-    <row r="105" spans="1:24">
+    <row r="105" spans="1:26">
       <c r="A105" s="2">
-        <v>46249</v>
+        <v>46257</v>
       </c>
       <c r="B105">
         <v>21</v>
       </c>
       <c r="C105">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="D105">
-        <v>0.021</v>
+        <v>0</v>
       </c>
       <c r="E105">
-        <v>0.033</v>
+        <v>0.018</v>
       </c>
       <c r="F105">
         <v>0</v>
@@ -4974,18 +5598,24 @@
         <v>0</v>
       </c>
       <c r="J105">
-        <v>0</v>
-      </c>
-      <c r="W105" t="s">
-        <v>127</v>
+        <v>0.019</v>
+      </c>
+      <c r="W105">
+        <v>0</v>
       </c>
       <c r="X105">
+        <v>0.01</v>
+      </c>
+      <c r="Y105" t="s">
+        <v>129</v>
+      </c>
+      <c r="Z105">
         <v>0.369</v>
       </c>
     </row>
-    <row r="106" spans="1:24">
+    <row r="106" spans="1:26">
       <c r="A106" s="2">
-        <v>46249</v>
+        <v>46257</v>
       </c>
       <c r="B106">
         <v>22</v>
@@ -4997,7 +5627,7 @@
         <v>0</v>
       </c>
       <c r="E106">
-        <v>0.024</v>
+        <v>0</v>
       </c>
       <c r="F106">
         <v>0</v>
@@ -5012,18 +5642,24 @@
         <v>0</v>
       </c>
       <c r="J106">
-        <v>0</v>
-      </c>
-      <c r="W106" t="s">
-        <v>128</v>
+        <v>0.019</v>
+      </c>
+      <c r="W106">
+        <v>0</v>
       </c>
       <c r="X106">
+        <v>0</v>
+      </c>
+      <c r="Y106" t="s">
+        <v>130</v>
+      </c>
+      <c r="Z106">
         <v>0.421</v>
       </c>
     </row>
-    <row r="107" spans="1:24">
+    <row r="107" spans="1:26">
       <c r="A107" s="2">
-        <v>46249</v>
+        <v>46257</v>
       </c>
       <c r="B107">
         <v>23</v>
@@ -5035,7 +5671,7 @@
         <v>0</v>
       </c>
       <c r="E107">
-        <v>0.037</v>
+        <v>0</v>
       </c>
       <c r="F107">
         <v>0</v>
@@ -5050,18 +5686,24 @@
         <v>0</v>
       </c>
       <c r="J107">
-        <v>0</v>
-      </c>
-      <c r="W107" t="s">
-        <v>129</v>
+        <v>0.025</v>
+      </c>
+      <c r="W107">
+        <v>0</v>
       </c>
       <c r="X107">
+        <v>0</v>
+      </c>
+      <c r="Y107" t="s">
+        <v>131</v>
+      </c>
+      <c r="Z107">
         <v>0.126</v>
       </c>
     </row>
-    <row r="108" spans="1:24">
+    <row r="108" spans="1:26">
       <c r="A108" s="2">
-        <v>46249</v>
+        <v>46257</v>
       </c>
       <c r="B108">
         <v>24</v>
@@ -5073,7 +5715,7 @@
         <v>0</v>
       </c>
       <c r="E108">
-        <v>0.026</v>
+        <v>0</v>
       </c>
       <c r="F108">
         <v>0</v>
@@ -5088,18 +5730,24 @@
         <v>0</v>
       </c>
       <c r="J108">
-        <v>0.018</v>
-      </c>
-      <c r="W108" t="s">
-        <v>130</v>
+        <v>0.025</v>
+      </c>
+      <c r="W108">
+        <v>0</v>
       </c>
       <c r="X108">
+        <v>0</v>
+      </c>
+      <c r="Y108" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z108">
         <v>0.181</v>
       </c>
     </row>
-    <row r="109" spans="1:24">
+    <row r="109" spans="1:26">
       <c r="A109" s="2">
-        <v>46250</v>
+        <v>46258</v>
       </c>
       <c r="B109">
         <v>1</v>
@@ -5111,7 +5759,7 @@
         <v>0</v>
       </c>
       <c r="E109">
-        <v>0.046</v>
+        <v>0</v>
       </c>
       <c r="F109">
         <v>0</v>
@@ -5126,18 +5774,24 @@
         <v>0</v>
       </c>
       <c r="J109">
-        <v>0</v>
-      </c>
-      <c r="W109" t="s">
-        <v>131</v>
+        <v>0.026</v>
+      </c>
+      <c r="W109">
+        <v>0</v>
       </c>
       <c r="X109">
+        <v>0</v>
+      </c>
+      <c r="Y109" t="s">
+        <v>133</v>
+      </c>
+      <c r="Z109">
         <v>0.181</v>
       </c>
     </row>
-    <row r="110" spans="1:24">
+    <row r="110" spans="1:26">
       <c r="A110" s="2">
-        <v>46250</v>
+        <v>46258</v>
       </c>
       <c r="B110">
         <v>2</v>
@@ -5149,7 +5803,7 @@
         <v>0</v>
       </c>
       <c r="E110">
-        <v>0.046</v>
+        <v>0</v>
       </c>
       <c r="F110">
         <v>0</v>
@@ -5164,18 +5818,24 @@
         <v>0</v>
       </c>
       <c r="J110">
-        <v>0</v>
-      </c>
-      <c r="W110" t="s">
-        <v>132</v>
+        <v>0.014</v>
+      </c>
+      <c r="W110">
+        <v>0</v>
       </c>
       <c r="X110">
+        <v>0</v>
+      </c>
+      <c r="Y110" t="s">
+        <v>134</v>
+      </c>
+      <c r="Z110">
         <v>0.109</v>
       </c>
     </row>
-    <row r="111" spans="1:24">
+    <row r="111" spans="1:26">
       <c r="A111" s="2">
-        <v>46250</v>
+        <v>46258</v>
       </c>
       <c r="B111">
         <v>3</v>
@@ -5187,7 +5847,7 @@
         <v>0</v>
       </c>
       <c r="E111">
-        <v>0.047</v>
+        <v>0</v>
       </c>
       <c r="F111">
         <v>0</v>
@@ -5202,18 +5862,24 @@
         <v>0</v>
       </c>
       <c r="J111">
-        <v>0</v>
-      </c>
-      <c r="W111" t="s">
-        <v>133</v>
+        <v>0.014</v>
+      </c>
+      <c r="W111">
+        <v>0</v>
       </c>
       <c r="X111">
+        <v>0</v>
+      </c>
+      <c r="Y111" t="s">
+        <v>135</v>
+      </c>
+      <c r="Z111">
         <v>0.011</v>
       </c>
     </row>
-    <row r="112" spans="1:24">
+    <row r="112" spans="1:26">
       <c r="A112" s="2">
-        <v>46250</v>
+        <v>46258</v>
       </c>
       <c r="B112">
         <v>4</v>
@@ -5225,7 +5891,7 @@
         <v>0</v>
       </c>
       <c r="E112">
-        <v>0.047</v>
+        <v>0</v>
       </c>
       <c r="F112">
         <v>0</v>
@@ -5240,18 +5906,24 @@
         <v>0</v>
       </c>
       <c r="J112">
-        <v>0.021</v>
-      </c>
-      <c r="W112" t="s">
-        <v>134</v>
+        <v>0.014</v>
+      </c>
+      <c r="W112">
+        <v>0</v>
       </c>
       <c r="X112">
+        <v>0</v>
+      </c>
+      <c r="Y112" t="s">
+        <v>136</v>
+      </c>
+      <c r="Z112">
         <v>0.011</v>
       </c>
     </row>
-    <row r="113" spans="1:24">
+    <row r="113" spans="1:26">
       <c r="A113" s="2">
-        <v>46250</v>
+        <v>46258</v>
       </c>
       <c r="B113">
         <v>5</v>
@@ -5263,7 +5935,7 @@
         <v>0</v>
       </c>
       <c r="E113">
-        <v>0.059</v>
+        <v>0</v>
       </c>
       <c r="F113">
         <v>0</v>
@@ -5278,18 +5950,24 @@
         <v>0</v>
       </c>
       <c r="J113">
-        <v>0.021</v>
-      </c>
-      <c r="W113" t="s">
-        <v>135</v>
+        <v>0.014</v>
+      </c>
+      <c r="W113">
+        <v>0</v>
       </c>
       <c r="X113">
         <v>0</v>
       </c>
-    </row>
-    <row r="114" spans="1:24">
+      <c r="Y113" t="s">
+        <v>137</v>
+      </c>
+      <c r="Z113">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:26">
       <c r="A114" s="2">
-        <v>46250</v>
+        <v>46258</v>
       </c>
       <c r="B114">
         <v>6</v>
@@ -5301,7 +5979,7 @@
         <v>0</v>
       </c>
       <c r="E114">
-        <v>0.062</v>
+        <v>0</v>
       </c>
       <c r="F114">
         <v>0</v>
@@ -5316,562 +5994,652 @@
         <v>0</v>
       </c>
       <c r="J114">
-        <v>0.015</v>
-      </c>
-      <c r="W114" t="s">
-        <v>136</v>
+        <v>0.014</v>
+      </c>
+      <c r="W114">
+        <v>0</v>
       </c>
       <c r="X114">
         <v>0</v>
       </c>
-    </row>
-    <row r="115" spans="1:24">
+      <c r="Y114" t="s">
+        <v>138</v>
+      </c>
+      <c r="Z114">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:26">
       <c r="A115" s="2">
-        <v>46250</v>
+        <v>46258</v>
       </c>
       <c r="B115">
         <v>7</v>
       </c>
       <c r="C115">
+        <v>0</v>
+      </c>
+      <c r="D115">
+        <v>0</v>
+      </c>
+      <c r="E115">
+        <v>0</v>
+      </c>
+      <c r="F115">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="G115">
         <v>0.024</v>
       </c>
-      <c r="D115">
-        <v>0.022</v>
-      </c>
-      <c r="E115">
-        <v>0.076</v>
-      </c>
-      <c r="F115">
-        <v>0.136</v>
-      </c>
-      <c r="G115">
-        <v>0.052</v>
-      </c>
       <c r="H115">
-        <v>0.034</v>
+        <v>0.011</v>
       </c>
       <c r="I115">
-        <v>0.034</v>
+        <v>0</v>
       </c>
       <c r="J115">
-        <v>0.039</v>
-      </c>
-      <c r="W115" t="s">
-        <v>137</v>
+        <v>0.038</v>
+      </c>
+      <c r="W115">
+        <v>0.01547837837837838</v>
       </c>
       <c r="X115">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116" spans="1:24">
+        <v>0.038</v>
+      </c>
+      <c r="Y115" t="s">
+        <v>139</v>
+      </c>
+      <c r="Z115">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:26">
       <c r="A116" s="2">
-        <v>46250</v>
+        <v>46258</v>
       </c>
       <c r="B116">
         <v>8</v>
       </c>
       <c r="C116">
-        <v>0.238</v>
+        <v>0.163</v>
       </c>
       <c r="D116">
-        <v>0.315</v>
+        <v>0.186</v>
       </c>
       <c r="E116">
-        <v>0.498</v>
+        <v>0.298</v>
       </c>
       <c r="F116">
-        <v>0.6929999999999999</v>
+        <v>0.708</v>
       </c>
       <c r="G116">
-        <v>0.456</v>
+        <v>0.338</v>
       </c>
       <c r="H116">
-        <v>0.306</v>
+        <v>0.221</v>
       </c>
       <c r="I116">
-        <v>0.361</v>
+        <v>0.249</v>
       </c>
       <c r="J116">
-        <v>0.236</v>
-      </c>
-      <c r="W116" t="s">
-        <v>138</v>
+        <v>0.196</v>
+      </c>
+      <c r="W116">
+        <v>0.1588216216216216</v>
       </c>
       <c r="X116">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117" spans="1:24">
+        <v>0.627</v>
+      </c>
+      <c r="Y116" t="s">
+        <v>140</v>
+      </c>
+      <c r="Z116">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:26">
       <c r="A117" s="2">
-        <v>46250</v>
+        <v>46258</v>
       </c>
       <c r="B117">
         <v>9</v>
       </c>
       <c r="C117">
-        <v>1.008</v>
+        <v>0.734</v>
       </c>
       <c r="D117">
-        <v>1.047</v>
+        <v>0.848</v>
       </c>
       <c r="E117">
-        <v>1.518</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="F117">
-        <v>1.908</v>
+        <v>1.602</v>
       </c>
       <c r="G117">
-        <v>1.465</v>
+        <v>0.995</v>
       </c>
       <c r="H117">
-        <v>0.896</v>
+        <v>0.628</v>
       </c>
       <c r="I117">
-        <v>0.839</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="J117">
-        <v>0.772</v>
-      </c>
-      <c r="W117" t="s">
-        <v>139</v>
+        <v>0.512</v>
+      </c>
+      <c r="W117">
+        <v>0.3593675675675675</v>
       </c>
       <c r="X117">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="118" spans="1:24">
+        <v>1.652</v>
+      </c>
+      <c r="Y117" t="s">
+        <v>141</v>
+      </c>
+      <c r="Z117">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:26">
       <c r="A118" s="2">
-        <v>46250</v>
+        <v>46258</v>
       </c>
       <c r="B118">
         <v>10</v>
       </c>
       <c r="C118">
-        <v>1.721</v>
+        <v>1.309</v>
       </c>
       <c r="D118">
-        <v>2.048</v>
+        <v>1.312</v>
       </c>
       <c r="E118">
-        <v>2.674</v>
+        <v>1.809</v>
       </c>
       <c r="F118">
-        <v>2.901</v>
+        <v>2.5</v>
       </c>
       <c r="G118">
-        <v>2.246</v>
+        <v>2.004</v>
       </c>
       <c r="H118">
-        <v>0.9340000000000001</v>
+        <v>1.294</v>
       </c>
       <c r="I118">
-        <v>1.149</v>
+        <v>1.015</v>
       </c>
       <c r="J118">
-        <v>1.011</v>
-      </c>
-      <c r="W118" t="s">
-        <v>140</v>
+        <v>1.006</v>
+      </c>
+      <c r="W118">
+        <v>0.5608108108108107</v>
       </c>
       <c r="X118">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="119" spans="1:24">
+        <v>3.599</v>
+      </c>
+      <c r="Y118" t="s">
+        <v>142</v>
+      </c>
+      <c r="Z118">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:26">
       <c r="A119" s="2">
-        <v>46250</v>
+        <v>46258</v>
       </c>
       <c r="B119">
         <v>11</v>
       </c>
       <c r="C119">
-        <v>2.386</v>
+        <v>2.187</v>
       </c>
       <c r="D119">
-        <v>2.749</v>
+        <v>2.238</v>
       </c>
       <c r="E119">
-        <v>3.596</v>
+        <v>3.144</v>
       </c>
       <c r="F119">
-        <v>3.737</v>
+        <v>3.333</v>
       </c>
       <c r="G119">
-        <v>2.879</v>
+        <v>2.828</v>
       </c>
       <c r="H119">
-        <v>0.786</v>
+        <v>1.528</v>
       </c>
       <c r="I119">
-        <v>1.437</v>
+        <v>1.417</v>
       </c>
       <c r="J119">
-        <v>1.308</v>
-      </c>
-      <c r="W119" t="s">
-        <v>141</v>
+        <v>1.259</v>
+      </c>
+      <c r="W119">
+        <v>0.747672972972973</v>
       </c>
       <c r="X119">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="120" spans="1:24">
+        <v>4.131</v>
+      </c>
+      <c r="Y119" t="s">
+        <v>143</v>
+      </c>
+      <c r="Z119">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:26">
       <c r="A120" s="2">
-        <v>46250</v>
+        <v>46258</v>
       </c>
       <c r="B120">
         <v>12</v>
       </c>
       <c r="C120">
-        <v>2.863</v>
+        <v>2.661</v>
       </c>
       <c r="D120">
-        <v>3.081</v>
+        <v>2.697</v>
       </c>
       <c r="E120">
-        <v>4.035</v>
+        <v>3.77</v>
       </c>
       <c r="F120">
-        <v>4.096</v>
+        <v>3.916</v>
       </c>
       <c r="G120">
-        <v>3.381</v>
+        <v>3.307</v>
       </c>
       <c r="H120">
-        <v>1.176</v>
+        <v>1.485</v>
       </c>
       <c r="I120">
         <v>1.445</v>
       </c>
       <c r="J120">
-        <v>1.475</v>
-      </c>
-      <c r="W120" t="s">
-        <v>142</v>
+        <v>1.365</v>
+      </c>
+      <c r="W120">
+        <v>0.878454054054054</v>
       </c>
       <c r="X120">
+        <v>5.446</v>
+      </c>
+      <c r="Y120" t="s">
+        <v>144</v>
+      </c>
+      <c r="Z120">
         <v>0.192</v>
       </c>
     </row>
-    <row r="121" spans="1:24">
+    <row r="121" spans="1:26">
       <c r="A121" s="2">
-        <v>46250</v>
+        <v>46258</v>
       </c>
       <c r="B121">
         <v>13</v>
       </c>
       <c r="C121">
-        <v>3.08</v>
+        <v>2.873</v>
       </c>
       <c r="D121">
-        <v>3.088</v>
+        <v>2.854</v>
       </c>
       <c r="E121">
-        <v>3.91</v>
+        <v>3.898</v>
       </c>
       <c r="F121">
-        <v>4.188</v>
+        <v>4.019</v>
       </c>
       <c r="G121">
-        <v>3.578</v>
+        <v>3.436</v>
       </c>
       <c r="H121">
-        <v>1.458</v>
+        <v>1.338</v>
       </c>
       <c r="I121">
         <v>1.445</v>
       </c>
       <c r="J121">
-        <v>1.631</v>
-      </c>
-      <c r="W121" t="s">
-        <v>143</v>
+        <v>1.344</v>
+      </c>
+      <c r="W121">
+        <v>0.9015594594594595</v>
       </c>
       <c r="X121">
+        <v>6.669</v>
+      </c>
+      <c r="Y121" t="s">
+        <v>145</v>
+      </c>
+      <c r="Z121">
         <v>0.21</v>
       </c>
     </row>
-    <row r="122" spans="1:24">
+    <row r="122" spans="1:26">
       <c r="A122" s="2">
-        <v>46250</v>
+        <v>46258</v>
       </c>
       <c r="B122">
         <v>14</v>
       </c>
       <c r="C122">
-        <v>3.141</v>
+        <v>2.731</v>
       </c>
       <c r="D122">
-        <v>3.097</v>
+        <v>2.93</v>
       </c>
       <c r="E122">
-        <v>3.856</v>
+        <v>3.772</v>
       </c>
       <c r="F122">
-        <v>4.198</v>
+        <v>4.015</v>
       </c>
       <c r="G122">
-        <v>3.594</v>
+        <v>3.448</v>
       </c>
       <c r="H122">
-        <v>0.978</v>
+        <v>0.862</v>
       </c>
       <c r="I122">
         <v>1.502</v>
       </c>
       <c r="J122">
-        <v>1.57</v>
-      </c>
-      <c r="W122" t="s">
-        <v>144</v>
+        <v>1.321</v>
+      </c>
+      <c r="W122">
+        <v>0.900662162162162</v>
       </c>
       <c r="X122">
+        <v>6.871</v>
+      </c>
+      <c r="Y122" t="s">
+        <v>146</v>
+      </c>
+      <c r="Z122">
         <v>0.501</v>
       </c>
     </row>
-    <row r="123" spans="1:24">
+    <row r="123" spans="1:26">
       <c r="A123" s="2">
-        <v>46250</v>
+        <v>46258</v>
       </c>
       <c r="B123">
         <v>15</v>
       </c>
       <c r="C123">
-        <v>3.006</v>
+        <v>2.628</v>
       </c>
       <c r="D123">
-        <v>3.116</v>
+        <v>2.731</v>
       </c>
       <c r="E123">
-        <v>3.881</v>
+        <v>3.644</v>
       </c>
       <c r="F123">
-        <v>4.018</v>
+        <v>3.843</v>
       </c>
       <c r="G123">
-        <v>3.461</v>
+        <v>3.39</v>
       </c>
       <c r="H123">
-        <v>1.054</v>
+        <v>1.005</v>
       </c>
       <c r="I123">
         <v>1.502</v>
       </c>
       <c r="J123">
-        <v>1.548</v>
-      </c>
-      <c r="W123" t="s">
-        <v>145</v>
+        <v>1.087</v>
+      </c>
+      <c r="W123">
+        <v>0.8620783783783783</v>
       </c>
       <c r="X123">
+        <v>6.739</v>
+      </c>
+      <c r="Y123" t="s">
+        <v>147</v>
+      </c>
+      <c r="Z123">
         <v>0.678</v>
       </c>
     </row>
-    <row r="124" spans="1:24">
+    <row r="124" spans="1:26">
       <c r="A124" s="2">
-        <v>46250</v>
+        <v>46258</v>
       </c>
       <c r="B124">
         <v>16</v>
       </c>
       <c r="C124">
-        <v>2.646</v>
+        <v>2.095</v>
       </c>
       <c r="D124">
-        <v>2.996</v>
+        <v>2.542</v>
       </c>
       <c r="E124">
-        <v>3.888</v>
+        <v>3.398</v>
       </c>
       <c r="F124">
-        <v>3.393</v>
+        <v>3.181</v>
       </c>
       <c r="G124">
-        <v>3.12</v>
+        <v>2.997</v>
       </c>
       <c r="H124">
-        <v>1.109</v>
+        <v>0.953</v>
       </c>
       <c r="I124">
-        <v>1.506</v>
+        <v>1.502</v>
       </c>
       <c r="J124">
-        <v>1.285</v>
-      </c>
-      <c r="W124" t="s">
-        <v>146</v>
+        <v>0.944</v>
+      </c>
+      <c r="W124">
+        <v>0.7135756756756756</v>
       </c>
       <c r="X124">
+        <v>6.007</v>
+      </c>
+      <c r="Y124" t="s">
+        <v>148</v>
+      </c>
+      <c r="Z124">
         <v>0.954</v>
       </c>
     </row>
-    <row r="125" spans="1:24">
+    <row r="125" spans="1:26">
       <c r="A125" s="2">
-        <v>46250</v>
+        <v>46258</v>
       </c>
       <c r="B125">
         <v>17</v>
       </c>
       <c r="C125">
-        <v>2.076</v>
+        <v>1.747</v>
       </c>
       <c r="D125">
-        <v>2.659</v>
+        <v>2.086</v>
       </c>
       <c r="E125">
-        <v>3.473</v>
+        <v>2.661</v>
       </c>
       <c r="F125">
-        <v>2.416</v>
+        <v>2.258</v>
       </c>
       <c r="G125">
-        <v>2.556</v>
+        <v>2.34</v>
       </c>
       <c r="H125">
-        <v>1.137</v>
+        <v>0.996</v>
       </c>
       <c r="I125">
-        <v>1.487</v>
+        <v>1.183</v>
       </c>
       <c r="J125">
-        <v>1.07</v>
-      </c>
-      <c r="W125" t="s">
-        <v>147</v>
+        <v>0.729</v>
+      </c>
+      <c r="W125">
+        <v>0.5065243243243243</v>
       </c>
       <c r="X125">
+        <v>4.634</v>
+      </c>
+      <c r="Y125" t="s">
+        <v>149</v>
+      </c>
+      <c r="Z125">
         <v>1.021</v>
       </c>
     </row>
-    <row r="126" spans="1:24">
+    <row r="126" spans="1:26">
       <c r="A126" s="2">
-        <v>46250</v>
+        <v>46258</v>
       </c>
       <c r="B126">
         <v>18</v>
       </c>
       <c r="C126">
-        <v>1.488</v>
+        <v>1.061</v>
       </c>
       <c r="D126">
-        <v>1.821</v>
+        <v>1.152</v>
       </c>
       <c r="E126">
-        <v>2.476</v>
+        <v>1.761</v>
       </c>
       <c r="F126">
-        <v>1.489</v>
+        <v>1.292</v>
       </c>
       <c r="G126">
-        <v>1.74</v>
+        <v>1.42</v>
       </c>
       <c r="H126">
-        <v>0.996</v>
+        <v>0.79</v>
       </c>
       <c r="I126">
-        <v>1.049</v>
+        <v>0.681</v>
       </c>
       <c r="J126">
-        <v>0.695</v>
-      </c>
-      <c r="W126" t="s">
-        <v>148</v>
+        <v>0.324</v>
+      </c>
+      <c r="W126">
+        <v>0.289827027027027</v>
       </c>
       <c r="X126">
+        <v>2.698</v>
+      </c>
+      <c r="Y126" t="s">
+        <v>150</v>
+      </c>
+      <c r="Z126">
         <v>0.797</v>
       </c>
     </row>
-    <row r="127" spans="1:24">
+    <row r="127" spans="1:26">
       <c r="A127" s="2">
-        <v>46250</v>
+        <v>46258</v>
       </c>
       <c r="B127">
         <v>19</v>
       </c>
       <c r="C127">
-        <v>0.637</v>
+        <v>0.536</v>
       </c>
       <c r="D127">
-        <v>0.83</v>
+        <v>0.649</v>
       </c>
       <c r="E127">
-        <v>1.264</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="F127">
-        <v>0.55</v>
+        <v>0.405</v>
       </c>
       <c r="G127">
-        <v>1.014</v>
+        <v>0.616</v>
       </c>
       <c r="H127">
-        <v>0.5659999999999999</v>
+        <v>0.434</v>
       </c>
       <c r="I127">
-        <v>0.57</v>
+        <v>0.42</v>
       </c>
       <c r="J127">
-        <v>0.445</v>
-      </c>
-      <c r="W127" t="s">
-        <v>149</v>
+        <v>0.215</v>
+      </c>
+      <c r="W127">
+        <v>0.09085135135135135</v>
       </c>
       <c r="X127">
+        <v>1.448</v>
+      </c>
+      <c r="Y127" t="s">
+        <v>151</v>
+      </c>
+      <c r="Z127">
         <v>0.505</v>
       </c>
     </row>
-    <row r="128" spans="1:24">
+    <row r="128" spans="1:26">
       <c r="A128" s="2">
-        <v>46250</v>
+        <v>46258</v>
       </c>
       <c r="B128">
         <v>20</v>
       </c>
       <c r="C128">
-        <v>0.16</v>
+        <v>0.098</v>
       </c>
       <c r="D128">
-        <v>0.234</v>
+        <v>0.128</v>
       </c>
       <c r="E128">
-        <v>0.457</v>
+        <v>0.269</v>
       </c>
       <c r="F128">
-        <v>0.165</v>
+        <v>0.108</v>
       </c>
       <c r="G128">
-        <v>0.216</v>
+        <v>0.123</v>
       </c>
       <c r="H128">
-        <v>0.217</v>
+        <v>0.145</v>
       </c>
       <c r="I128">
-        <v>0.15</v>
+        <v>0.074</v>
       </c>
       <c r="J128">
-        <v>0.089</v>
-      </c>
-      <c r="W128" t="s">
-        <v>150</v>
+        <v>0.016</v>
+      </c>
+      <c r="W128">
+        <v>0.02422702702702702</v>
       </c>
       <c r="X128">
+        <v>0.354</v>
+      </c>
+      <c r="Y128" t="s">
+        <v>152</v>
+      </c>
+      <c r="Z128">
         <v>0.505</v>
       </c>
     </row>
-    <row r="129" spans="1:24">
+    <row r="129" spans="1:26">
       <c r="A129" s="2">
-        <v>46250</v>
+        <v>46258</v>
       </c>
       <c r="B129">
         <v>21</v>
       </c>
       <c r="C129">
-        <v>0.014</v>
+        <v>0</v>
       </c>
       <c r="D129">
-        <v>0.022</v>
+        <v>0</v>
       </c>
       <c r="E129">
-        <v>0.032</v>
+        <v>0</v>
       </c>
       <c r="F129">
         <v>0</v>
@@ -5888,16 +6656,22 @@
       <c r="J129">
         <v>0</v>
       </c>
-      <c r="W129" t="s">
-        <v>151</v>
+      <c r="W129">
+        <v>0</v>
       </c>
       <c r="X129">
+        <v>0.024</v>
+      </c>
+      <c r="Y129" t="s">
+        <v>153</v>
+      </c>
+      <c r="Z129">
         <v>0.465</v>
       </c>
     </row>
-    <row r="130" spans="1:24">
+    <row r="130" spans="1:26">
       <c r="A130" s="2">
-        <v>46250</v>
+        <v>46258</v>
       </c>
       <c r="B130">
         <v>22</v>
@@ -5909,7 +6683,7 @@
         <v>0</v>
       </c>
       <c r="E130">
-        <v>0.018</v>
+        <v>0</v>
       </c>
       <c r="F130">
         <v>0</v>
@@ -5924,18 +6698,24 @@
         <v>0</v>
       </c>
       <c r="J130">
-        <v>0</v>
-      </c>
-      <c r="W130" t="s">
-        <v>152</v>
+        <v>0.013</v>
+      </c>
+      <c r="W130">
+        <v>0</v>
       </c>
       <c r="X130">
+        <v>0</v>
+      </c>
+      <c r="Y130" t="s">
+        <v>154</v>
+      </c>
+      <c r="Z130">
         <v>0.242</v>
       </c>
     </row>
-    <row r="131" spans="1:24">
+    <row r="131" spans="1:26">
       <c r="A131" s="2">
-        <v>46250</v>
+        <v>46258</v>
       </c>
       <c r="B131">
         <v>23</v>
@@ -5947,7 +6727,7 @@
         <v>0</v>
       </c>
       <c r="E131">
-        <v>0.024</v>
+        <v>0</v>
       </c>
       <c r="F131">
         <v>0</v>
@@ -5962,18 +6742,24 @@
         <v>0</v>
       </c>
       <c r="J131">
-        <v>0</v>
-      </c>
-      <c r="W131" t="s">
-        <v>153</v>
+        <v>0.013</v>
+      </c>
+      <c r="W131">
+        <v>0</v>
       </c>
       <c r="X131">
+        <v>0</v>
+      </c>
+      <c r="Y131" t="s">
+        <v>155</v>
+      </c>
+      <c r="Z131">
         <v>0.195</v>
       </c>
     </row>
-    <row r="132" spans="1:24">
+    <row r="132" spans="1:26">
       <c r="A132" s="2">
-        <v>46250</v>
+        <v>46258</v>
       </c>
       <c r="B132">
         <v>24</v>
@@ -5985,7 +6771,7 @@
         <v>0</v>
       </c>
       <c r="E132">
-        <v>0.024</v>
+        <v>0</v>
       </c>
       <c r="F132">
         <v>0</v>
@@ -6000,18 +6786,24 @@
         <v>0</v>
       </c>
       <c r="J132">
-        <v>0</v>
-      </c>
-      <c r="W132" t="s">
-        <v>154</v>
+        <v>0.013</v>
+      </c>
+      <c r="W132">
+        <v>0</v>
       </c>
       <c r="X132">
+        <v>0</v>
+      </c>
+      <c r="Y132" t="s">
+        <v>156</v>
+      </c>
+      <c r="Z132">
         <v>0.25</v>
       </c>
     </row>
-    <row r="133" spans="1:24">
+    <row r="133" spans="1:26">
       <c r="A133" s="2">
-        <v>46251</v>
+        <v>46259</v>
       </c>
       <c r="B133">
         <v>1</v>
@@ -6023,7 +6815,7 @@
         <v>0</v>
       </c>
       <c r="E133">
-        <v>0.025</v>
+        <v>0</v>
       </c>
       <c r="F133">
         <v>0</v>
@@ -6038,18 +6830,24 @@
         <v>0</v>
       </c>
       <c r="J133">
-        <v>0</v>
-      </c>
-      <c r="W133" t="s">
-        <v>155</v>
+        <v>0.014</v>
+      </c>
+      <c r="W133">
+        <v>0</v>
       </c>
       <c r="X133">
+        <v>0</v>
+      </c>
+      <c r="Y133" t="s">
+        <v>157</v>
+      </c>
+      <c r="Z133">
         <v>0.25</v>
       </c>
     </row>
-    <row r="134" spans="1:24">
+    <row r="134" spans="1:26">
       <c r="A134" s="2">
-        <v>46251</v>
+        <v>46259</v>
       </c>
       <c r="B134">
         <v>2</v>
@@ -6061,7 +6859,7 @@
         <v>0</v>
       </c>
       <c r="E134">
-        <v>0.063</v>
+        <v>0</v>
       </c>
       <c r="F134">
         <v>0</v>
@@ -6076,18 +6874,24 @@
         <v>0</v>
       </c>
       <c r="J134">
-        <v>0</v>
-      </c>
-      <c r="W134" t="s">
-        <v>156</v>
+        <v>0.014</v>
+      </c>
+      <c r="W134">
+        <v>0</v>
       </c>
       <c r="X134">
+        <v>0</v>
+      </c>
+      <c r="Y134" t="s">
+        <v>158</v>
+      </c>
+      <c r="Z134">
         <v>0.109</v>
       </c>
     </row>
-    <row r="135" spans="1:24">
+    <row r="135" spans="1:26">
       <c r="A135" s="2">
-        <v>46251</v>
+        <v>46259</v>
       </c>
       <c r="B135">
         <v>3</v>
@@ -6099,7 +6903,7 @@
         <v>0</v>
       </c>
       <c r="E135">
-        <v>0.045</v>
+        <v>0</v>
       </c>
       <c r="F135">
         <v>0</v>
@@ -6114,18 +6918,24 @@
         <v>0</v>
       </c>
       <c r="J135">
-        <v>0</v>
-      </c>
-      <c r="W135" t="s">
-        <v>157</v>
+        <v>0.014</v>
+      </c>
+      <c r="W135">
+        <v>0</v>
       </c>
       <c r="X135">
+        <v>0</v>
+      </c>
+      <c r="Y135" t="s">
+        <v>159</v>
+      </c>
+      <c r="Z135">
         <v>0.112</v>
       </c>
     </row>
-    <row r="136" spans="1:24">
+    <row r="136" spans="1:26">
       <c r="A136" s="2">
-        <v>46251</v>
+        <v>46259</v>
       </c>
       <c r="B136">
         <v>4</v>
@@ -6137,7 +6947,7 @@
         <v>0</v>
       </c>
       <c r="E136">
-        <v>0.049</v>
+        <v>0</v>
       </c>
       <c r="F136">
         <v>0</v>
@@ -6152,18 +6962,24 @@
         <v>0</v>
       </c>
       <c r="J136">
-        <v>0</v>
-      </c>
-      <c r="W136" t="s">
-        <v>158</v>
+        <v>0.014</v>
+      </c>
+      <c r="W136">
+        <v>0</v>
       </c>
       <c r="X136">
+        <v>0</v>
+      </c>
+      <c r="Y136" t="s">
+        <v>160</v>
+      </c>
+      <c r="Z136">
         <v>0.112</v>
       </c>
     </row>
-    <row r="137" spans="1:24">
+    <row r="137" spans="1:26">
       <c r="A137" s="2">
-        <v>46251</v>
+        <v>46259</v>
       </c>
       <c r="B137">
         <v>5</v>
@@ -6175,7 +6991,7 @@
         <v>0</v>
       </c>
       <c r="E137">
-        <v>0.047</v>
+        <v>0</v>
       </c>
       <c r="F137">
         <v>0</v>
@@ -6190,18 +7006,24 @@
         <v>0</v>
       </c>
       <c r="J137">
-        <v>0.021</v>
-      </c>
-      <c r="W137" t="s">
-        <v>159</v>
+        <v>0.014</v>
+      </c>
+      <c r="W137">
+        <v>0</v>
       </c>
       <c r="X137">
+        <v>0</v>
+      </c>
+      <c r="Y137" t="s">
+        <v>161</v>
+      </c>
+      <c r="Z137">
         <v>0.01</v>
       </c>
     </row>
-    <row r="138" spans="1:24">
+    <row r="138" spans="1:26">
       <c r="A138" s="2">
-        <v>46251</v>
+        <v>46259</v>
       </c>
       <c r="B138">
         <v>6</v>
@@ -6213,7 +7035,7 @@
         <v>0</v>
       </c>
       <c r="E138">
-        <v>0.048</v>
+        <v>0</v>
       </c>
       <c r="F138">
         <v>0</v>
@@ -6228,562 +7050,652 @@
         <v>0</v>
       </c>
       <c r="J138">
-        <v>0.015</v>
-      </c>
-      <c r="W138" t="s">
-        <v>160</v>
+        <v>0.014</v>
+      </c>
+      <c r="W138">
+        <v>0</v>
       </c>
       <c r="X138">
+        <v>0</v>
+      </c>
+      <c r="Y138" t="s">
+        <v>162</v>
+      </c>
+      <c r="Z138">
         <v>0.01</v>
       </c>
     </row>
-    <row r="139" spans="1:24">
+    <row r="139" spans="1:26">
       <c r="A139" s="2">
-        <v>46251</v>
+        <v>46259</v>
       </c>
       <c r="B139">
         <v>7</v>
       </c>
       <c r="C139">
+        <v>0</v>
+      </c>
+      <c r="D139">
+        <v>0</v>
+      </c>
+      <c r="E139">
+        <v>0.012</v>
+      </c>
+      <c r="F139">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="G139">
         <v>0.024</v>
       </c>
-      <c r="D139">
-        <v>0.022</v>
-      </c>
-      <c r="E139">
-        <v>0.059</v>
-      </c>
-      <c r="F139">
-        <v>0.136</v>
-      </c>
-      <c r="G139">
-        <v>0.052</v>
-      </c>
       <c r="H139">
-        <v>0.034</v>
+        <v>0</v>
       </c>
       <c r="I139">
-        <v>0.034</v>
+        <v>0</v>
       </c>
       <c r="J139">
-        <v>0.045</v>
-      </c>
-      <c r="W139" t="s">
-        <v>161</v>
+        <v>0.038</v>
+      </c>
+      <c r="W139">
+        <v>0.01547837837837838</v>
       </c>
       <c r="X139">
+        <v>0.038</v>
+      </c>
+      <c r="Y139" t="s">
+        <v>163</v>
+      </c>
+      <c r="Z139">
         <v>0.015</v>
       </c>
     </row>
-    <row r="140" spans="1:24">
+    <row r="140" spans="1:26">
       <c r="A140" s="2">
-        <v>46251</v>
+        <v>46259</v>
       </c>
       <c r="B140">
         <v>8</v>
       </c>
       <c r="C140">
-        <v>0.251</v>
+        <v>0.236</v>
       </c>
       <c r="D140">
-        <v>0.315</v>
+        <v>0.188</v>
       </c>
       <c r="E140">
-        <v>0.483</v>
+        <v>0.275</v>
       </c>
       <c r="F140">
-        <v>0.753</v>
+        <v>0.707</v>
       </c>
       <c r="G140">
-        <v>0.455</v>
+        <v>0.364</v>
       </c>
       <c r="H140">
-        <v>0.347</v>
+        <v>0.221</v>
       </c>
       <c r="I140">
-        <v>0.361</v>
+        <v>0.208</v>
       </c>
       <c r="J140">
-        <v>0.265</v>
-      </c>
-      <c r="W140" t="s">
-        <v>162</v>
+        <v>0.196</v>
+      </c>
+      <c r="W140">
+        <v>0.1585972972972973</v>
       </c>
       <c r="X140">
+        <v>0.642</v>
+      </c>
+      <c r="Y140" t="s">
+        <v>164</v>
+      </c>
+      <c r="Z140">
         <v>0.015</v>
       </c>
     </row>
-    <row r="141" spans="1:24">
+    <row r="141" spans="1:26">
       <c r="A141" s="2">
-        <v>46251</v>
+        <v>46259</v>
       </c>
       <c r="B141">
         <v>9</v>
       </c>
       <c r="C141">
-        <v>0.9379999999999999</v>
+        <v>0.726</v>
       </c>
       <c r="D141">
-        <v>0.957</v>
+        <v>0.776</v>
       </c>
       <c r="E141">
-        <v>1.44</v>
+        <v>1.11</v>
       </c>
       <c r="F141">
-        <v>1.952</v>
+        <v>1.738</v>
       </c>
       <c r="G141">
-        <v>1.341</v>
+        <v>1.178</v>
       </c>
       <c r="H141">
-        <v>0.889</v>
+        <v>0.647</v>
       </c>
       <c r="I141">
-        <v>0.894</v>
+        <v>0.678</v>
       </c>
       <c r="J141">
-        <v>0.785</v>
-      </c>
-      <c r="W141" t="s">
-        <v>163</v>
+        <v>0.628</v>
+      </c>
+      <c r="W141">
+        <v>0.3898756756756757</v>
       </c>
       <c r="X141">
+        <v>1.904</v>
+      </c>
+      <c r="Y141" t="s">
+        <v>165</v>
+      </c>
+      <c r="Z141">
         <v>0.015</v>
       </c>
     </row>
-    <row r="142" spans="1:24">
+    <row r="142" spans="1:26">
       <c r="A142" s="2">
-        <v>46251</v>
+        <v>46259</v>
       </c>
       <c r="B142">
         <v>10</v>
       </c>
       <c r="C142">
-        <v>1.705</v>
+        <v>1.291</v>
       </c>
       <c r="D142">
+        <v>1.267</v>
+      </c>
+      <c r="E142">
         <v>1.965</v>
       </c>
-      <c r="E142">
-        <v>2.596</v>
-      </c>
       <c r="F142">
-        <v>2.887</v>
+        <v>2.588</v>
       </c>
       <c r="G142">
-        <v>2.296</v>
+        <v>2.073</v>
       </c>
       <c r="H142">
-        <v>0.93</v>
+        <v>0.863</v>
       </c>
       <c r="I142">
-        <v>1.163</v>
+        <v>1.055</v>
       </c>
       <c r="J142">
-        <v>1.086</v>
-      </c>
-      <c r="W142" t="s">
-        <v>164</v>
+        <v>1.014</v>
+      </c>
+      <c r="W142">
+        <v>0.5805513513513513</v>
       </c>
       <c r="X142">
+        <v>3.911</v>
+      </c>
+      <c r="Y142" t="s">
+        <v>166</v>
+      </c>
+      <c r="Z142">
         <v>0.015</v>
       </c>
     </row>
-    <row r="143" spans="1:24">
+    <row r="143" spans="1:26">
       <c r="A143" s="2">
-        <v>46251</v>
+        <v>46259</v>
       </c>
       <c r="B143">
         <v>11</v>
       </c>
       <c r="C143">
-        <v>2.32</v>
+        <v>1.682</v>
       </c>
       <c r="D143">
-        <v>2.745</v>
+        <v>1.922</v>
       </c>
       <c r="E143">
-        <v>3.576</v>
+        <v>3.115</v>
       </c>
       <c r="F143">
-        <v>3.727</v>
+        <v>3.249</v>
       </c>
       <c r="G143">
-        <v>2.918</v>
+        <v>2.732</v>
       </c>
       <c r="H143">
-        <v>1.204</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="I143">
-        <v>1.437</v>
+        <v>1.535</v>
       </c>
       <c r="J143">
-        <v>1.348</v>
-      </c>
-      <c r="W143" t="s">
-        <v>165</v>
+        <v>1.241</v>
+      </c>
+      <c r="W143">
+        <v>0.7288297297297297</v>
       </c>
       <c r="X143">
+        <v>5.007</v>
+      </c>
+      <c r="Y143" t="s">
+        <v>167</v>
+      </c>
+      <c r="Z143">
         <v>0.01</v>
       </c>
     </row>
-    <row r="144" spans="1:24">
+    <row r="144" spans="1:26">
       <c r="A144" s="2">
-        <v>46251</v>
+        <v>46259</v>
       </c>
       <c r="B144">
         <v>12</v>
       </c>
       <c r="C144">
-        <v>2.772</v>
+        <v>1.809</v>
       </c>
       <c r="D144">
-        <v>2.961</v>
+        <v>1.974</v>
       </c>
       <c r="E144">
-        <v>3.972</v>
+        <v>3.83</v>
       </c>
       <c r="F144">
-        <v>4.095</v>
+        <v>3.652</v>
       </c>
       <c r="G144">
-        <v>3.404</v>
+        <v>3.026</v>
       </c>
       <c r="H144">
-        <v>1.469</v>
+        <v>1.463</v>
       </c>
       <c r="I144">
-        <v>1.445</v>
+        <v>1.465</v>
       </c>
       <c r="J144">
-        <v>1.475</v>
-      </c>
-      <c r="W144" t="s">
-        <v>166</v>
+        <v>1.532</v>
+      </c>
+      <c r="W144">
+        <v>0.8192324324324324</v>
       </c>
       <c r="X144">
+        <v>5.944</v>
+      </c>
+      <c r="Y144" t="s">
+        <v>168</v>
+      </c>
+      <c r="Z144">
         <v>0.038</v>
       </c>
     </row>
-    <row r="145" spans="1:24">
+    <row r="145" spans="1:26">
       <c r="A145" s="2">
-        <v>46251</v>
+        <v>46259</v>
       </c>
       <c r="B145">
         <v>13</v>
       </c>
       <c r="C145">
-        <v>3.079</v>
+        <v>2.139</v>
       </c>
       <c r="D145">
-        <v>3.088</v>
+        <v>2.382</v>
       </c>
       <c r="E145">
-        <v>3.911</v>
+        <v>3.939</v>
       </c>
       <c r="F145">
-        <v>4.186</v>
+        <v>3.772</v>
       </c>
       <c r="G145">
-        <v>3.543</v>
+        <v>3.156</v>
       </c>
       <c r="H145">
-        <v>1.495</v>
+        <v>1.502</v>
       </c>
       <c r="I145">
         <v>1.445</v>
       </c>
       <c r="J145">
-        <v>1.519</v>
-      </c>
-      <c r="W145" t="s">
-        <v>167</v>
+        <v>1.474</v>
+      </c>
+      <c r="W145">
+        <v>0.8461513513513512</v>
       </c>
       <c r="X145">
+        <v>6.850000000000001</v>
+      </c>
+      <c r="Y145" t="s">
+        <v>169</v>
+      </c>
+      <c r="Z145">
         <v>0.056</v>
       </c>
     </row>
-    <row r="146" spans="1:24">
+    <row r="146" spans="1:26">
       <c r="A146" s="2">
-        <v>46251</v>
+        <v>46259</v>
       </c>
       <c r="B146">
         <v>14</v>
       </c>
       <c r="C146">
-        <v>3.136</v>
+        <v>2.203</v>
       </c>
       <c r="D146">
-        <v>3.097</v>
+        <v>2.38</v>
       </c>
       <c r="E146">
-        <v>3.847</v>
+        <v>3.853</v>
       </c>
       <c r="F146">
-        <v>4.184</v>
+        <v>3.692</v>
       </c>
       <c r="G146">
-        <v>3.594</v>
+        <v>3.202</v>
       </c>
       <c r="H146">
-        <v>1.094</v>
+        <v>1.155</v>
       </c>
       <c r="I146">
         <v>1.502</v>
       </c>
       <c r="J146">
-        <v>1.57</v>
-      </c>
-      <c r="W146" t="s">
-        <v>168</v>
+        <v>1.45</v>
+      </c>
+      <c r="W146">
+        <v>0.8282054054054054</v>
       </c>
       <c r="X146">
+        <v>6.889</v>
+      </c>
+      <c r="Y146" t="s">
+        <v>170</v>
+      </c>
+      <c r="Z146">
         <v>0.462</v>
       </c>
     </row>
-    <row r="147" spans="1:24">
+    <row r="147" spans="1:26">
       <c r="A147" s="2">
-        <v>46251</v>
+        <v>46259</v>
       </c>
       <c r="B147">
         <v>15</v>
       </c>
       <c r="C147">
-        <v>2.981</v>
+        <v>2.048</v>
       </c>
       <c r="D147">
-        <v>3.129</v>
+        <v>2.156</v>
       </c>
       <c r="E147">
-        <v>3.853</v>
+        <v>3.71</v>
       </c>
       <c r="F147">
-        <v>4.008</v>
+        <v>3.564</v>
       </c>
       <c r="G147">
-        <v>3.526</v>
+        <v>3.154</v>
       </c>
       <c r="H147">
-        <v>0.93</v>
+        <v>0.831</v>
       </c>
       <c r="I147">
         <v>1.502</v>
       </c>
       <c r="J147">
-        <v>1.548</v>
-      </c>
-      <c r="W147" t="s">
-        <v>169</v>
+        <v>1.309</v>
+      </c>
+      <c r="W147">
+        <v>0.7994918918918918</v>
       </c>
       <c r="X147">
+        <v>7.008</v>
+      </c>
+      <c r="Y147" t="s">
+        <v>171</v>
+      </c>
+      <c r="Z147">
         <v>0.314</v>
       </c>
     </row>
-    <row r="148" spans="1:24">
+    <row r="148" spans="1:26">
       <c r="A148" s="2">
-        <v>46251</v>
+        <v>46259</v>
       </c>
       <c r="B148">
         <v>16</v>
       </c>
       <c r="C148">
-        <v>2.62</v>
+        <v>1.618</v>
       </c>
       <c r="D148">
-        <v>2.996</v>
+        <v>1.842</v>
       </c>
       <c r="E148">
-        <v>3.873</v>
+        <v>3.413</v>
       </c>
       <c r="F148">
-        <v>3.413</v>
+        <v>2.943</v>
       </c>
       <c r="G148">
-        <v>3.173</v>
+        <v>2.706</v>
       </c>
       <c r="H148">
-        <v>0.769</v>
+        <v>0.961</v>
       </c>
       <c r="I148">
-        <v>1.506</v>
+        <v>1.502</v>
       </c>
       <c r="J148">
-        <v>1.285</v>
-      </c>
-      <c r="W148" t="s">
-        <v>170</v>
+        <v>1.149</v>
+      </c>
+      <c r="W148">
+        <v>0.6601864864864865</v>
       </c>
       <c r="X148">
+        <v>6.195</v>
+      </c>
+      <c r="Y148" t="s">
+        <v>172</v>
+      </c>
+      <c r="Z148">
         <v>0.43</v>
       </c>
     </row>
-    <row r="149" spans="1:24">
+    <row r="149" spans="1:26">
       <c r="A149" s="2">
-        <v>46251</v>
+        <v>46259</v>
       </c>
       <c r="B149">
         <v>17</v>
       </c>
       <c r="C149">
-        <v>2.04</v>
+        <v>1.274</v>
       </c>
       <c r="D149">
-        <v>2.677</v>
+        <v>1.495</v>
       </c>
       <c r="E149">
-        <v>3.502</v>
+        <v>2.429</v>
       </c>
       <c r="F149">
-        <v>2.407</v>
+        <v>2.032</v>
       </c>
       <c r="G149">
-        <v>2.564</v>
+        <v>2.13</v>
       </c>
       <c r="H149">
-        <v>0.779</v>
+        <v>0.947</v>
       </c>
       <c r="I149">
-        <v>1.487</v>
+        <v>1.158</v>
       </c>
       <c r="J149">
-        <v>1.07</v>
-      </c>
-      <c r="W149" t="s">
-        <v>171</v>
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="W149">
+        <v>0.455827027027027</v>
       </c>
       <c r="X149">
+        <v>4.6</v>
+      </c>
+      <c r="Y149" t="s">
+        <v>173</v>
+      </c>
+      <c r="Z149">
         <v>0.734</v>
       </c>
     </row>
-    <row r="150" spans="1:24">
+    <row r="150" spans="1:26">
       <c r="A150" s="2">
-        <v>46251</v>
+        <v>46259</v>
       </c>
       <c r="B150">
         <v>18</v>
       </c>
       <c r="C150">
-        <v>1.483</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="D150">
-        <v>1.821</v>
+        <v>0.98</v>
       </c>
       <c r="E150">
-        <v>2.525</v>
+        <v>1.617</v>
       </c>
       <c r="F150">
-        <v>1.502</v>
+        <v>1.229</v>
       </c>
       <c r="G150">
-        <v>1.812</v>
+        <v>1.485</v>
       </c>
       <c r="H150">
-        <v>0.665</v>
+        <v>0.761</v>
       </c>
       <c r="I150">
-        <v>0.799</v>
+        <v>0.667</v>
       </c>
       <c r="J150">
-        <v>0.707</v>
-      </c>
-      <c r="W150" t="s">
-        <v>172</v>
+        <v>0.353</v>
+      </c>
+      <c r="W150">
+        <v>0.2756945945945946</v>
       </c>
       <c r="X150">
+        <v>2.63</v>
+      </c>
+      <c r="Y150" t="s">
+        <v>174</v>
+      </c>
+      <c r="Z150">
         <v>0.5669999999999999</v>
       </c>
     </row>
-    <row r="151" spans="1:24">
+    <row r="151" spans="1:26">
       <c r="A151" s="2">
-        <v>46251</v>
+        <v>46259</v>
       </c>
       <c r="B151">
         <v>19</v>
       </c>
       <c r="C151">
-        <v>0.641</v>
+        <v>0.388</v>
       </c>
       <c r="D151">
-        <v>0.8149999999999999</v>
+        <v>0.41</v>
       </c>
       <c r="E151">
-        <v>1.316</v>
+        <v>0.732</v>
       </c>
       <c r="F151">
-        <v>0.533</v>
+        <v>0.325</v>
       </c>
       <c r="G151">
-        <v>1.014</v>
+        <v>0.503</v>
       </c>
       <c r="H151">
-        <v>0.537</v>
+        <v>0.469</v>
       </c>
       <c r="I151">
-        <v>0.547</v>
+        <v>0.42</v>
       </c>
       <c r="J151">
-        <v>0.389</v>
-      </c>
-      <c r="W151" t="s">
-        <v>173</v>
+        <v>0.231</v>
+      </c>
+      <c r="W151">
+        <v>0.0729054054054054</v>
       </c>
       <c r="X151">
+        <v>1.338</v>
+      </c>
+      <c r="Y151" t="s">
+        <v>175</v>
+      </c>
+      <c r="Z151">
         <v>0.41</v>
       </c>
     </row>
-    <row r="152" spans="1:24">
+    <row r="152" spans="1:26">
       <c r="A152" s="2">
-        <v>46251</v>
+        <v>46259</v>
       </c>
       <c r="B152">
         <v>20</v>
       </c>
       <c r="C152">
-        <v>0.151</v>
+        <v>0.058</v>
       </c>
       <c r="D152">
-        <v>0.207</v>
+        <v>0.082</v>
       </c>
       <c r="E152">
-        <v>0.452</v>
+        <v>0.202</v>
       </c>
       <c r="F152">
-        <v>0.161</v>
+        <v>0.074</v>
       </c>
       <c r="G152">
-        <v>0.21</v>
+        <v>0.094</v>
       </c>
       <c r="H152">
-        <v>0.213</v>
+        <v>0.106</v>
       </c>
       <c r="I152">
-        <v>0.15</v>
+        <v>0.064</v>
       </c>
       <c r="J152">
-        <v>0.08500000000000001</v>
-      </c>
-      <c r="W152" t="s">
-        <v>174</v>
+        <v>0.026</v>
+      </c>
+      <c r="W152">
+        <v>0.0166</v>
       </c>
       <c r="X152">
+        <v>0.312</v>
+      </c>
+      <c r="Y152" t="s">
+        <v>176</v>
+      </c>
+      <c r="Z152">
         <v>0.289</v>
       </c>
     </row>
-    <row r="153" spans="1:24">
+    <row r="153" spans="1:26">
       <c r="A153" s="2">
-        <v>46251</v>
+        <v>46259</v>
       </c>
       <c r="B153">
         <v>21</v>
       </c>
       <c r="C153">
-        <v>0.011</v>
+        <v>0</v>
       </c>
       <c r="D153">
-        <v>0.016</v>
+        <v>0</v>
       </c>
       <c r="E153">
-        <v>0.032</v>
+        <v>0</v>
       </c>
       <c r="F153">
         <v>0</v>
@@ -6798,18 +7710,24 @@
         <v>0</v>
       </c>
       <c r="J153">
-        <v>0</v>
-      </c>
-      <c r="W153" t="s">
-        <v>175</v>
+        <v>0.025</v>
+      </c>
+      <c r="W153">
+        <v>0</v>
       </c>
       <c r="X153">
+        <v>0.022</v>
+      </c>
+      <c r="Y153" t="s">
+        <v>177</v>
+      </c>
+      <c r="Z153">
         <v>0.336</v>
       </c>
     </row>
-    <row r="154" spans="1:24">
+    <row r="154" spans="1:26">
       <c r="A154" s="2">
-        <v>46251</v>
+        <v>46259</v>
       </c>
       <c r="B154">
         <v>22</v>
@@ -6821,7 +7739,7 @@
         <v>0</v>
       </c>
       <c r="E154">
-        <v>0.016</v>
+        <v>0</v>
       </c>
       <c r="F154">
         <v>0</v>
@@ -6836,18 +7754,24 @@
         <v>0</v>
       </c>
       <c r="J154">
-        <v>0</v>
-      </c>
-      <c r="W154" t="s">
-        <v>176</v>
+        <v>0.013</v>
+      </c>
+      <c r="W154">
+        <v>0</v>
       </c>
       <c r="X154">
+        <v>0</v>
+      </c>
+      <c r="Y154" t="s">
+        <v>178</v>
+      </c>
+      <c r="Z154">
         <v>0.244</v>
       </c>
     </row>
-    <row r="155" spans="1:24">
+    <row r="155" spans="1:26">
       <c r="A155" s="2">
-        <v>46251</v>
+        <v>46259</v>
       </c>
       <c r="B155">
         <v>23</v>
@@ -6859,7 +7783,7 @@
         <v>0</v>
       </c>
       <c r="E155">
-        <v>0.017</v>
+        <v>0</v>
       </c>
       <c r="F155">
         <v>0</v>
@@ -6874,18 +7798,24 @@
         <v>0</v>
       </c>
       <c r="J155">
-        <v>0</v>
-      </c>
-      <c r="W155" t="s">
-        <v>177</v>
+        <v>0.013</v>
+      </c>
+      <c r="W155">
+        <v>0</v>
       </c>
       <c r="X155">
+        <v>0</v>
+      </c>
+      <c r="Y155" t="s">
+        <v>179</v>
+      </c>
+      <c r="Z155">
         <v>0.197</v>
       </c>
     </row>
-    <row r="156" spans="1:24">
+    <row r="156" spans="1:26">
       <c r="A156" s="2">
-        <v>46251</v>
+        <v>46259</v>
       </c>
       <c r="B156">
         <v>24</v>
@@ -6897,7 +7827,7 @@
         <v>0</v>
       </c>
       <c r="E156">
-        <v>0.018</v>
+        <v>0</v>
       </c>
       <c r="F156">
         <v>0</v>
@@ -6912,18 +7842,24 @@
         <v>0</v>
       </c>
       <c r="J156">
-        <v>0</v>
-      </c>
-      <c r="W156" t="s">
-        <v>178</v>
+        <v>0.013</v>
+      </c>
+      <c r="W156">
+        <v>0</v>
       </c>
       <c r="X156">
+        <v>0</v>
+      </c>
+      <c r="Y156" t="s">
+        <v>180</v>
+      </c>
+      <c r="Z156">
         <v>0.252</v>
       </c>
     </row>
-    <row r="157" spans="1:24">
+    <row r="157" spans="1:26">
       <c r="A157" s="2">
-        <v>46252</v>
+        <v>46260</v>
       </c>
       <c r="B157">
         <v>1</v>
@@ -6935,7 +7871,7 @@
         <v>0</v>
       </c>
       <c r="E157">
-        <v>0.041</v>
+        <v>0</v>
       </c>
       <c r="F157">
         <v>0</v>
@@ -6952,16 +7888,22 @@
       <c r="J157">
         <v>0.014</v>
       </c>
-      <c r="W157" t="s">
-        <v>179</v>
+      <c r="W157">
+        <v>0</v>
       </c>
       <c r="X157">
+        <v>0</v>
+      </c>
+      <c r="Y157" t="s">
+        <v>181</v>
+      </c>
+      <c r="Z157">
         <v>0.252</v>
       </c>
     </row>
-    <row r="158" spans="1:24">
+    <row r="158" spans="1:26">
       <c r="A158" s="2">
-        <v>46252</v>
+        <v>46260</v>
       </c>
       <c r="B158">
         <v>2</v>
@@ -6973,7 +7915,7 @@
         <v>0</v>
       </c>
       <c r="E158">
-        <v>0.045</v>
+        <v>0</v>
       </c>
       <c r="F158">
         <v>0</v>
@@ -6990,16 +7932,22 @@
       <c r="J158">
         <v>0.014</v>
       </c>
-      <c r="W158" t="s">
-        <v>180</v>
+      <c r="W158">
+        <v>0</v>
       </c>
       <c r="X158">
+        <v>0</v>
+      </c>
+      <c r="Y158" t="s">
+        <v>182</v>
+      </c>
+      <c r="Z158">
         <v>0.112</v>
       </c>
     </row>
-    <row r="159" spans="1:24">
+    <row r="159" spans="1:26">
       <c r="A159" s="2">
-        <v>46252</v>
+        <v>46260</v>
       </c>
       <c r="B159">
         <v>3</v>
@@ -7011,7 +7959,7 @@
         <v>0</v>
       </c>
       <c r="E159">
-        <v>0.032</v>
+        <v>0</v>
       </c>
       <c r="F159">
         <v>0</v>
@@ -7026,18 +7974,24 @@
         <v>0</v>
       </c>
       <c r="J159">
-        <v>0.02</v>
-      </c>
-      <c r="W159" t="s">
-        <v>181</v>
+        <v>0.014</v>
+      </c>
+      <c r="W159">
+        <v>0</v>
       </c>
       <c r="X159">
+        <v>0</v>
+      </c>
+      <c r="Y159" t="s">
+        <v>183</v>
+      </c>
+      <c r="Z159">
         <v>0.112</v>
       </c>
     </row>
-    <row r="160" spans="1:24">
+    <row r="160" spans="1:26">
       <c r="A160" s="2">
-        <v>46252</v>
+        <v>46260</v>
       </c>
       <c r="B160">
         <v>4</v>
@@ -7049,7 +8003,7 @@
         <v>0</v>
       </c>
       <c r="E160">
-        <v>0.033</v>
+        <v>0</v>
       </c>
       <c r="F160">
         <v>0</v>
@@ -7064,18 +8018,24 @@
         <v>0</v>
       </c>
       <c r="J160">
-        <v>0.021</v>
-      </c>
-      <c r="W160" t="s">
-        <v>182</v>
+        <v>0.014</v>
+      </c>
+      <c r="W160">
+        <v>0</v>
       </c>
       <c r="X160">
+        <v>0</v>
+      </c>
+      <c r="Y160" t="s">
+        <v>184</v>
+      </c>
+      <c r="Z160">
         <v>0.112</v>
       </c>
     </row>
-    <row r="161" spans="1:24">
+    <row r="161" spans="1:26">
       <c r="A161" s="2">
-        <v>46252</v>
+        <v>46260</v>
       </c>
       <c r="B161">
         <v>5</v>
@@ -7087,7 +8047,7 @@
         <v>0</v>
       </c>
       <c r="E161">
-        <v>0.025</v>
+        <v>0.015</v>
       </c>
       <c r="F161">
         <v>0</v>
@@ -7102,18 +8062,24 @@
         <v>0</v>
       </c>
       <c r="J161">
-        <v>0.021</v>
-      </c>
-      <c r="W161" t="s">
-        <v>183</v>
+        <v>0.014</v>
+      </c>
+      <c r="W161">
+        <v>0</v>
       </c>
       <c r="X161">
+        <v>0</v>
+      </c>
+      <c r="Y161" t="s">
+        <v>185</v>
+      </c>
+      <c r="Z161">
         <v>0.01</v>
       </c>
     </row>
-    <row r="162" spans="1:24">
+    <row r="162" spans="1:26">
       <c r="A162" s="2">
-        <v>46252</v>
+        <v>46260</v>
       </c>
       <c r="B162">
         <v>6</v>
@@ -7125,7 +8091,7 @@
         <v>0</v>
       </c>
       <c r="E162">
-        <v>0.049</v>
+        <v>0</v>
       </c>
       <c r="F162">
         <v>0</v>
@@ -7140,316 +8106,370 @@
         <v>0</v>
       </c>
       <c r="J162">
-        <v>0.015</v>
-      </c>
-      <c r="W162" t="s">
-        <v>184</v>
+        <v>0.014</v>
+      </c>
+      <c r="W162">
+        <v>0</v>
       </c>
       <c r="X162">
+        <v>0</v>
+      </c>
+      <c r="Y162" t="s">
+        <v>186</v>
+      </c>
+      <c r="Z162">
         <v>0.01</v>
       </c>
     </row>
-    <row r="163" spans="1:24">
+    <row r="163" spans="1:26">
       <c r="A163" s="2">
-        <v>46252</v>
+        <v>46260</v>
       </c>
       <c r="B163">
         <v>7</v>
       </c>
       <c r="C163">
-        <v>0.016</v>
+        <v>0</v>
       </c>
       <c r="D163">
-        <v>0.017</v>
+        <v>0</v>
       </c>
       <c r="E163">
-        <v>0.031</v>
+        <v>0</v>
       </c>
       <c r="F163">
-        <v>0.099</v>
+        <v>0.039</v>
       </c>
       <c r="G163">
-        <v>0.043</v>
+        <v>0.015</v>
       </c>
       <c r="H163">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="I163">
-        <v>0.025</v>
+        <v>0</v>
       </c>
       <c r="J163">
-        <v>0</v>
-      </c>
-      <c r="W163" t="s">
-        <v>185</v>
+        <v>0.038</v>
+      </c>
+      <c r="W163">
+        <v>0.008748648648648648</v>
       </c>
       <c r="X163">
+        <v>0.039</v>
+      </c>
+      <c r="Y163" t="s">
+        <v>187</v>
+      </c>
+      <c r="Z163">
         <v>0.01</v>
       </c>
     </row>
-    <row r="164" spans="1:24">
+    <row r="164" spans="1:26">
       <c r="A164" s="2">
-        <v>46252</v>
+        <v>46260</v>
       </c>
       <c r="B164">
         <v>8</v>
       </c>
       <c r="C164">
-        <v>0.229</v>
+        <v>0.177</v>
       </c>
       <c r="D164">
-        <v>0.28</v>
+        <v>0.175</v>
       </c>
       <c r="E164">
-        <v>0.388</v>
+        <v>0.273</v>
       </c>
       <c r="F164">
-        <v>0.68</v>
+        <v>0.492</v>
       </c>
       <c r="G164">
-        <v>0.463</v>
+        <v>0.257</v>
       </c>
       <c r="H164">
-        <v>0.306</v>
+        <v>0.168</v>
       </c>
       <c r="I164">
-        <v>0.335</v>
+        <v>0.143</v>
       </c>
       <c r="J164">
-        <v>0.233</v>
-      </c>
-      <c r="W164" t="s">
-        <v>186</v>
+        <v>0.075</v>
+      </c>
+      <c r="W164">
+        <v>0.1103675675675676</v>
       </c>
       <c r="X164">
+        <v>0.546</v>
+      </c>
+      <c r="Y164" t="s">
+        <v>188</v>
+      </c>
+      <c r="Z164">
         <v>0.01</v>
       </c>
     </row>
-    <row r="165" spans="1:24">
+    <row r="165" spans="1:26">
       <c r="A165" s="2">
-        <v>46252</v>
+        <v>46260</v>
       </c>
       <c r="B165">
         <v>9</v>
       </c>
       <c r="C165">
-        <v>0.918</v>
+        <v>0.614</v>
       </c>
       <c r="D165">
-        <v>1.038</v>
+        <v>0.699</v>
       </c>
       <c r="E165">
-        <v>1.477</v>
+        <v>1.05</v>
       </c>
       <c r="F165">
-        <v>1.769</v>
+        <v>1.386</v>
       </c>
       <c r="G165">
-        <v>1.344</v>
+        <v>0.802</v>
       </c>
       <c r="H165">
-        <v>0.881</v>
+        <v>0.529</v>
       </c>
       <c r="I165">
-        <v>0.603</v>
+        <v>0.443</v>
       </c>
       <c r="J165">
-        <v>0.797</v>
-      </c>
-      <c r="W165" t="s">
-        <v>187</v>
+        <v>0.524</v>
+      </c>
+      <c r="W165">
+        <v>0.3109135135135135</v>
       </c>
       <c r="X165">
+        <v>1.541</v>
+      </c>
+      <c r="Y165" t="s">
+        <v>189</v>
+      </c>
+      <c r="Z165">
         <v>0.01</v>
       </c>
     </row>
-    <row r="166" spans="1:24">
+    <row r="166" spans="1:26">
       <c r="A166" s="2">
-        <v>46252</v>
+        <v>46260</v>
       </c>
       <c r="B166">
         <v>10</v>
       </c>
       <c r="C166">
-        <v>1.721</v>
+        <v>1.115</v>
       </c>
       <c r="D166">
-        <v>1.843</v>
+        <v>1.245</v>
       </c>
       <c r="E166">
-        <v>2.519</v>
+        <v>1.912</v>
       </c>
       <c r="F166">
-        <v>2.681</v>
+        <v>2.099</v>
       </c>
       <c r="G166">
-        <v>2.228</v>
+        <v>1.676</v>
       </c>
       <c r="H166">
-        <v>0.93</v>
+        <v>0.626</v>
       </c>
       <c r="I166">
-        <v>1.071</v>
+        <v>0.667</v>
       </c>
       <c r="J166">
-        <v>0.949</v>
-      </c>
-      <c r="W166" t="s">
-        <v>188</v>
+        <v>0.972</v>
+      </c>
+      <c r="W166">
+        <v>0.4708567567567568</v>
       </c>
       <c r="X166">
+        <v>3.48</v>
+      </c>
+      <c r="Y166" t="s">
+        <v>190</v>
+      </c>
+      <c r="Z166">
         <v>0.01</v>
       </c>
     </row>
-    <row r="167" spans="1:24">
+    <row r="167" spans="1:26">
       <c r="A167" s="2">
-        <v>46252</v>
+        <v>46260</v>
       </c>
       <c r="B167">
         <v>11</v>
       </c>
       <c r="C167">
-        <v>2.313</v>
+        <v>1.628</v>
       </c>
       <c r="D167">
-        <v>2.743</v>
+        <v>1.933</v>
       </c>
       <c r="E167">
-        <v>3.563</v>
+        <v>2.896</v>
       </c>
       <c r="F167">
-        <v>3.677</v>
+        <v>2.542</v>
       </c>
       <c r="G167">
-        <v>2.893</v>
+        <v>2.055</v>
       </c>
       <c r="H167">
-        <v>1.448</v>
+        <v>1.017</v>
       </c>
       <c r="I167">
-        <v>1.437</v>
+        <v>0.914</v>
       </c>
       <c r="J167">
-        <v>1.386</v>
-      </c>
-      <c r="W167" t="s">
-        <v>189</v>
+        <v>1.082</v>
+      </c>
+      <c r="W167">
+        <v>0.5702324324324324</v>
       </c>
       <c r="X167">
+        <v>4.176</v>
+      </c>
+      <c r="Y167" t="s">
+        <v>191</v>
+      </c>
+      <c r="Z167">
         <v>0.01</v>
       </c>
     </row>
-    <row r="168" spans="1:24">
+    <row r="168" spans="1:26">
       <c r="A168" s="2">
-        <v>46252</v>
+        <v>46260</v>
       </c>
       <c r="B168">
         <v>12</v>
       </c>
       <c r="C168">
-        <v>2.814</v>
+        <v>1.921</v>
       </c>
       <c r="D168">
-        <v>2.967</v>
+        <v>2.274</v>
       </c>
       <c r="E168">
-        <v>3.971</v>
+        <v>3.656</v>
       </c>
       <c r="F168">
-        <v>4.136</v>
+        <v>2.841</v>
       </c>
       <c r="G168">
-        <v>3.482</v>
+        <v>2.515</v>
       </c>
       <c r="H168">
-        <v>1.49</v>
+        <v>1.307</v>
       </c>
       <c r="I168">
-        <v>1.445</v>
+        <v>1.019</v>
       </c>
       <c r="J168">
-        <v>1.582</v>
-      </c>
-      <c r="W168" t="s">
-        <v>190</v>
+        <v>1.218</v>
+      </c>
+      <c r="W168">
+        <v>0.6373054054054054</v>
       </c>
       <c r="X168">
+        <v>4.733000000000001</v>
+      </c>
+      <c r="Y168" t="s">
+        <v>192</v>
+      </c>
+      <c r="Z168">
         <v>0.194</v>
       </c>
     </row>
-    <row r="169" spans="1:24">
+    <row r="169" spans="1:26">
       <c r="A169" s="2">
-        <v>46252</v>
+        <v>46260</v>
       </c>
       <c r="B169">
         <v>13</v>
       </c>
       <c r="C169">
-        <v>3.052</v>
+        <v>2.249</v>
       </c>
       <c r="D169">
-        <v>3.053</v>
+        <v>2.529</v>
       </c>
       <c r="E169">
-        <v>3.921</v>
+        <v>3.846</v>
       </c>
       <c r="F169">
-        <v>4.206</v>
+        <v>2.857</v>
       </c>
       <c r="G169">
-        <v>3.583</v>
+        <v>2.741</v>
       </c>
       <c r="H169">
-        <v>1.5</v>
+        <v>1.431</v>
       </c>
       <c r="I169">
-        <v>1.396</v>
+        <v>1.307</v>
       </c>
       <c r="J169">
-        <v>1.665</v>
-      </c>
-      <c r="W169" t="s">
-        <v>191</v>
+        <v>1.186</v>
+      </c>
+      <c r="W169">
+        <v>0.6408945945945946</v>
       </c>
       <c r="X169">
+        <v>5.13</v>
+      </c>
+      <c r="Y169" t="s">
+        <v>193</v>
+      </c>
+      <c r="Z169">
         <v>0.212</v>
       </c>
     </row>
-    <row r="170" spans="1:24">
+    <row r="170" spans="1:26">
       <c r="A170" s="2">
-        <v>46252</v>
+        <v>46260</v>
       </c>
       <c r="B170">
         <v>14</v>
       </c>
       <c r="C170">
-        <v>3.124</v>
+        <v>2.356</v>
       </c>
       <c r="D170">
-        <v>3.097</v>
+        <v>2.717</v>
       </c>
       <c r="E170">
-        <v>3.81</v>
+        <v>3.69</v>
       </c>
       <c r="F170">
-        <v>4.138</v>
+        <v>3.001</v>
       </c>
       <c r="G170">
-        <v>3.538</v>
+        <v>2.793</v>
       </c>
       <c r="H170">
-        <v>0.835</v>
+        <v>1.078</v>
       </c>
       <c r="I170">
-        <v>1.452</v>
+        <v>1.315</v>
       </c>
       <c r="J170">
-        <v>1.617</v>
-      </c>
-      <c r="W170" t="s">
-        <v>192</v>
+        <v>1.313</v>
+      </c>
+      <c r="W170">
+        <v>0.6731972972972973</v>
       </c>
       <c r="X170">
+        <v>4.654</v>
+      </c>
+      <c r="Y170" t="s">
+        <v>194</v>
+      </c>
+      <c r="Z170">
         <v>1.081</v>
       </c>
     </row>
